--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -540,13 +540,13 @@
         <v>1143</v>
       </c>
       <c r="D5" t="n">
-        <v>5226.3</v>
+        <v>5169.7</v>
       </c>
       <c r="E5" t="n">
-        <v>5745.8</v>
+        <v>5729.1</v>
       </c>
       <c r="F5" t="n">
-        <v>6182.3</v>
+        <v>6172.3</v>
       </c>
     </row>
     <row r="6">
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4595</v>
+        <v>4571</v>
       </c>
       <c r="D6" t="n">
-        <v>17022</v>
+        <v>17063.8</v>
       </c>
       <c r="E6" t="n">
-        <v>23376.2</v>
+        <v>23491.7</v>
       </c>
       <c r="F6" t="n">
-        <v>29031.6</v>
+        <v>29523.5</v>
       </c>
     </row>
     <row r="7">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27876</v>
+        <v>27949</v>
       </c>
       <c r="D9" t="n">
-        <v>101573</v>
+        <v>102265.5</v>
       </c>
       <c r="E9" t="n">
-        <v>112196.6</v>
+        <v>113377.6</v>
       </c>
       <c r="F9" t="n">
-        <v>119873.2</v>
+        <v>121044.4</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>648227</v>
+        <v>650541</v>
       </c>
       <c r="D10" t="n">
-        <v>2753991.7</v>
+        <v>2767812.5</v>
       </c>
       <c r="E10" t="n">
-        <v>4062358</v>
+        <v>4043634.6</v>
       </c>
       <c r="F10" t="n">
-        <v>4025636.2</v>
+        <v>3939915.6</v>
       </c>
     </row>
     <row r="11">
@@ -705,16 +705,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8068</v>
+        <v>8312</v>
       </c>
       <c r="D12" t="n">
-        <v>30130.8</v>
+        <v>30345.1</v>
       </c>
       <c r="E12" t="n">
-        <v>32790.8</v>
+        <v>32907.2</v>
       </c>
       <c r="F12" t="n">
-        <v>33660.7</v>
+        <v>33721.5</v>
       </c>
     </row>
     <row r="13">
@@ -729,16 +729,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14338</v>
+        <v>14500</v>
       </c>
       <c r="D13" t="n">
-        <v>55023.3</v>
+        <v>56369.3</v>
       </c>
       <c r="E13" t="n">
-        <v>67091.3</v>
+        <v>69187.3</v>
       </c>
       <c r="F13" t="n">
-        <v>71796.7</v>
+        <v>72135</v>
       </c>
     </row>
     <row r="14">
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D16" t="n">
-        <v>1449.8</v>
+        <v>1452.7</v>
       </c>
       <c r="E16" t="n">
-        <v>2000.7</v>
+        <v>2000.3</v>
       </c>
       <c r="F16" t="n">
-        <v>2027.6</v>
+        <v>2036.9</v>
       </c>
     </row>
     <row r="17">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10486.2</v>
+        <v>10434.4</v>
       </c>
       <c r="E18" t="n">
-        <v>12287.3</v>
+        <v>12149.2</v>
       </c>
       <c r="F18" t="n">
-        <v>13453.6</v>
+        <v>13426.9</v>
       </c>
     </row>
     <row r="19">
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="D23" t="n">
-        <v>7263.8</v>
+        <v>7269.1</v>
       </c>
       <c r="E23" t="n">
-        <v>8698.200000000001</v>
+        <v>8732.5</v>
       </c>
       <c r="F23" t="n">
-        <v>10234.5</v>
+        <v>10306.5</v>
       </c>
     </row>
     <row r="24">
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="D26" t="n">
-        <v>956.5</v>
+        <v>955.3</v>
       </c>
       <c r="E26" t="n">
-        <v>1664.6</v>
+        <v>1620.8</v>
       </c>
       <c r="F26" t="n">
-        <v>2918.6</v>
+        <v>2823.6</v>
       </c>
     </row>
     <row r="27">
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1112</v>
+        <v>1038</v>
       </c>
       <c r="D28" t="n">
-        <v>4633.6</v>
+        <v>4357.2</v>
       </c>
       <c r="E28" t="n">
-        <v>7872.2</v>
+        <v>7439.7</v>
       </c>
       <c r="F28" t="n">
-        <v>8809.299999999999</v>
+        <v>8169.2</v>
       </c>
     </row>
     <row r="29">
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1494</v>
+        <v>1502</v>
       </c>
       <c r="D29" t="n">
-        <v>7586.8</v>
+        <v>7610.5</v>
       </c>
       <c r="E29" t="n">
-        <v>8482.799999999999</v>
+        <v>8508.299999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>8927.5</v>
+        <v>8956</v>
       </c>
     </row>
     <row r="30">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="D32" t="n">
-        <v>2128.8</v>
+        <v>2130.5</v>
       </c>
       <c r="E32" t="n">
-        <v>2358.5</v>
+        <v>2350.3</v>
       </c>
       <c r="F32" t="n">
-        <v>2496.2</v>
+        <v>2458.2</v>
       </c>
     </row>
     <row r="33">
@@ -1200,16 +1200,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31627</v>
+        <v>31377</v>
       </c>
       <c r="D33" t="n">
-        <v>118832.8</v>
+        <v>119102.2</v>
       </c>
       <c r="E33" t="n">
-        <v>133309.8</v>
+        <v>133173.4</v>
       </c>
       <c r="F33" t="n">
-        <v>146139.6</v>
+        <v>145756.5</v>
       </c>
     </row>
     <row r="34">
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7553</v>
+        <v>7489</v>
       </c>
       <c r="D34" t="n">
-        <v>32017.8</v>
+        <v>31736.7</v>
       </c>
       <c r="E34" t="n">
-        <v>40240.6</v>
+        <v>40076.2</v>
       </c>
       <c r="F34" t="n">
-        <v>45668.3</v>
+        <v>45608.8</v>
       </c>
     </row>
     <row r="35">
@@ -1251,13 +1251,13 @@
         <v>5604</v>
       </c>
       <c r="D35" t="n">
-        <v>21007.1</v>
+        <v>21132.5</v>
       </c>
       <c r="E35" t="n">
-        <v>23515.9</v>
+        <v>23517.5</v>
       </c>
       <c r="F35" t="n">
-        <v>25014.6</v>
+        <v>25037.6</v>
       </c>
     </row>
     <row r="36">
@@ -1275,10 +1275,10 @@
         <v>1344</v>
       </c>
       <c r="D36" t="n">
-        <v>4617.1</v>
+        <v>4617</v>
       </c>
       <c r="E36" t="n">
-        <v>5073.7</v>
+        <v>5073.1</v>
       </c>
       <c r="F36" t="n">
         <v>5900.8</v>
@@ -1299,13 +1299,13 @@
         <v>850494</v>
       </c>
       <c r="D37" t="n">
-        <v>3742869.5</v>
+        <v>3832403.5</v>
       </c>
       <c r="E37" t="n">
-        <v>5264743.6</v>
+        <v>5422607.5</v>
       </c>
       <c r="F37" t="n">
-        <v>5106293</v>
+        <v>5327749.5</v>
       </c>
     </row>
     <row r="38">
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5910</v>
+        <v>6107</v>
       </c>
       <c r="D38" t="n">
-        <v>21482.1</v>
+        <v>21714.4</v>
       </c>
       <c r="E38" t="n">
-        <v>19537.1</v>
+        <v>19715.2</v>
       </c>
       <c r="F38" t="n">
-        <v>19834.1</v>
+        <v>19922.1</v>
       </c>
     </row>
     <row r="39">
@@ -1371,13 +1371,13 @@
         <v>4406</v>
       </c>
       <c r="D40" t="n">
-        <v>16669.4</v>
+        <v>16669</v>
       </c>
       <c r="E40" t="n">
-        <v>18989.7</v>
+        <v>18990.1</v>
       </c>
       <c r="F40" t="n">
-        <v>21819.4</v>
+        <v>21819.9</v>
       </c>
     </row>
     <row r="41">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-619</v>
+        <v>-523</v>
       </c>
       <c r="D42" t="n">
-        <v>-119.5</v>
+        <v>82.7</v>
       </c>
       <c r="E42" t="n">
-        <v>14700.9</v>
+        <v>14829.6</v>
       </c>
       <c r="F42" t="n">
-        <v>25631.2</v>
+        <v>25291.6</v>
       </c>
     </row>
     <row r="43">
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17794</v>
+        <v>18359</v>
       </c>
       <c r="D44" t="n">
-        <v>40427.4</v>
+        <v>41243</v>
       </c>
       <c r="E44" t="n">
-        <v>26644.7</v>
+        <v>26789.7</v>
       </c>
       <c r="F44" t="n">
-        <v>27547.9</v>
+        <v>27554.5</v>
       </c>
     </row>
     <row r="45">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D45" t="n">
-        <v>3464.6</v>
+        <v>3474.3</v>
       </c>
       <c r="E45" t="n">
-        <v>3725.5</v>
+        <v>3735.5</v>
       </c>
       <c r="F45" t="n">
-        <v>3888.4</v>
+        <v>3891.1</v>
       </c>
     </row>
     <row r="46">
@@ -1539,13 +1539,13 @@
         <v>742</v>
       </c>
       <c r="D47" t="n">
-        <v>3232.2</v>
+        <v>3244.5</v>
       </c>
       <c r="E47" t="n">
-        <v>4451.1</v>
+        <v>4495.9</v>
       </c>
       <c r="F47" t="n">
-        <v>5509.4</v>
+        <v>5694.8</v>
       </c>
     </row>
     <row r="48">
@@ -1581,13 +1581,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D49" t="n">
-        <v>1749.9</v>
+        <v>1760.9</v>
       </c>
       <c r="E49" t="n">
-        <v>2239.5</v>
+        <v>2249.2</v>
       </c>
       <c r="F49" t="n">
         <v>2685.3</v>
@@ -1605,16 +1605,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3938</v>
+        <v>4015</v>
       </c>
       <c r="D50" t="n">
-        <v>16321.6</v>
+        <v>16524.3</v>
       </c>
       <c r="E50" t="n">
-        <v>29922.4</v>
+        <v>31390.1</v>
       </c>
       <c r="F50" t="n">
-        <v>45557.4</v>
+        <v>49657.5</v>
       </c>
     </row>
     <row r="51">
@@ -1629,13 +1629,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D51" t="n">
-        <v>359.5</v>
+        <v>379.5</v>
       </c>
       <c r="E51" t="n">
-        <v>440</v>
+        <v>441.7</v>
       </c>
       <c r="F51" t="n">
         <v>581.3</v>
@@ -1680,13 +1680,13 @@
         <v>14211</v>
       </c>
       <c r="D53" t="n">
-        <v>56430.5</v>
+        <v>56417.8</v>
       </c>
       <c r="E53" t="n">
-        <v>67800.5</v>
+        <v>67968.8</v>
       </c>
       <c r="F53" t="n">
-        <v>78345</v>
+        <v>78474.8</v>
       </c>
     </row>
     <row r="54">
@@ -1725,16 +1725,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1257</v>
+        <v>1213</v>
       </c>
       <c r="D55" t="n">
-        <v>3843.6</v>
+        <v>3751.4</v>
       </c>
       <c r="E55" t="n">
-        <v>5392.3</v>
+        <v>5370.1</v>
       </c>
       <c r="F55" t="n">
-        <v>6613.2</v>
+        <v>6603.2</v>
       </c>
     </row>
     <row r="56">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3933</v>
+        <v>3902</v>
       </c>
       <c r="D58" t="n">
-        <v>15077.2</v>
+        <v>14993.6</v>
       </c>
       <c r="E58" t="n">
-        <v>20347</v>
+        <v>20241</v>
       </c>
       <c r="F58" t="n">
-        <v>23773.6</v>
+        <v>23704.1</v>
       </c>
     </row>
     <row r="59">
@@ -1821,16 +1821,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9345</v>
+        <v>9415</v>
       </c>
       <c r="D59" t="n">
-        <v>35195.9</v>
+        <v>35619.5</v>
       </c>
       <c r="E59" t="n">
-        <v>24390.5</v>
+        <v>24566.4</v>
       </c>
       <c r="F59" t="n">
-        <v>22463.2</v>
+        <v>22576.3</v>
       </c>
     </row>
     <row r="60">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1709</v>
+        <v>1803</v>
       </c>
       <c r="D60" t="n">
-        <v>11487.2</v>
+        <v>11679.8</v>
       </c>
       <c r="E60" t="n">
-        <v>13573.3</v>
+        <v>13870.9</v>
       </c>
       <c r="F60" t="n">
-        <v>15312.2</v>
+        <v>15782.4</v>
       </c>
     </row>
     <row r="61">
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>968</v>
+        <v>1380</v>
       </c>
       <c r="D61" t="n">
-        <v>785.3</v>
+        <v>1671</v>
       </c>
       <c r="E61" t="n">
-        <v>2720.4</v>
+        <v>2610.4</v>
       </c>
       <c r="F61" t="n">
-        <v>4923.2</v>
+        <v>4783.5</v>
       </c>
     </row>
     <row r="62">
@@ -1893,16 +1893,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3152</v>
+        <v>3182</v>
       </c>
       <c r="D62" t="n">
-        <v>11253.4</v>
+        <v>11608</v>
       </c>
       <c r="E62" t="n">
-        <v>8457.200000000001</v>
+        <v>8554.9</v>
       </c>
       <c r="F62" t="n">
-        <v>8962.799999999999</v>
+        <v>9030.200000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1917,16 +1917,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>598</v>
+        <v>576</v>
       </c>
       <c r="D63" t="n">
-        <v>2344.7</v>
+        <v>2314.2</v>
       </c>
       <c r="E63" t="n">
-        <v>2917.7</v>
+        <v>2836.9</v>
       </c>
       <c r="F63" t="n">
-        <v>3226.4</v>
+        <v>3126.8</v>
       </c>
     </row>
     <row r="64">
@@ -1941,16 +1941,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1302</v>
+        <v>1401</v>
       </c>
       <c r="D64" t="n">
-        <v>3738.1</v>
+        <v>3904.6</v>
       </c>
       <c r="E64" t="n">
-        <v>4289.7</v>
+        <v>4430.3</v>
       </c>
       <c r="F64" t="n">
-        <v>4739.6</v>
+        <v>4902.9</v>
       </c>
     </row>
     <row r="65">
@@ -1989,16 +1989,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9106</v>
+        <v>9114</v>
       </c>
       <c r="D66" t="n">
-        <v>37138</v>
+        <v>37203.2</v>
       </c>
       <c r="E66" t="n">
-        <v>42446.2</v>
+        <v>42456.2</v>
       </c>
       <c r="F66" t="n">
-        <v>46417.6</v>
+        <v>46498.1</v>
       </c>
     </row>
     <row r="67">
@@ -2013,16 +2013,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10249</v>
+        <v>10170</v>
       </c>
       <c r="D67" t="n">
-        <v>42579.6</v>
+        <v>42629.6</v>
       </c>
       <c r="E67" t="n">
-        <v>54915.1</v>
+        <v>54900.1</v>
       </c>
       <c r="F67" t="n">
-        <v>61734.6</v>
+        <v>61729.9</v>
       </c>
     </row>
     <row r="68">
@@ -2061,16 +2061,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D69" t="n">
-        <v>1869.5</v>
+        <v>1879.9</v>
       </c>
       <c r="E69" t="n">
-        <v>2366.9</v>
+        <v>2386.1</v>
       </c>
       <c r="F69" t="n">
-        <v>3050.1</v>
+        <v>3072.4</v>
       </c>
     </row>
     <row r="70">
@@ -2109,16 +2109,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5958</v>
+        <v>6159</v>
       </c>
       <c r="D71" t="n">
-        <v>22124.8</v>
+        <v>22401.3</v>
       </c>
       <c r="E71" t="n">
-        <v>20517.6</v>
+        <v>20758.2</v>
       </c>
       <c r="F71" t="n">
-        <v>20670.3</v>
+        <v>20808.3</v>
       </c>
     </row>
     <row r="72">
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5271</v>
+        <v>5290</v>
       </c>
       <c r="D72" t="n">
-        <v>19110.6</v>
+        <v>19147.2</v>
       </c>
       <c r="E72" t="n">
-        <v>20293.2</v>
+        <v>20290.9</v>
       </c>
       <c r="F72" t="n">
-        <v>21534.7</v>
+        <v>21493</v>
       </c>
     </row>
     <row r="73">
@@ -2159,12 +2159,6 @@
       <c r="C73" t="n">
         <v>578</v>
       </c>
-      <c r="D73" t="n">
-        <v>2307</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2674</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2202,16 +2196,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2293</v>
+        <v>2330</v>
       </c>
       <c r="D75" t="n">
-        <v>8321.200000000001</v>
+        <v>8358.200000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>10627.7</v>
+        <v>10647.7</v>
       </c>
       <c r="F75" t="n">
-        <v>11783.6</v>
+        <v>11831.3</v>
       </c>
     </row>
     <row r="76">
@@ -2226,16 +2220,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="D76" t="n">
-        <v>4276.4</v>
+        <v>4279.2</v>
       </c>
       <c r="E76" t="n">
-        <v>4995.8</v>
+        <v>4997.4</v>
       </c>
       <c r="F76" t="n">
-        <v>5791.9</v>
+        <v>5789.7</v>
       </c>
     </row>
     <row r="77">
@@ -2250,16 +2244,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2652</v>
+        <v>2682</v>
       </c>
       <c r="D77" t="n">
-        <v>9987</v>
+        <v>10136.5</v>
       </c>
       <c r="E77" t="n">
-        <v>11412.8</v>
+        <v>11688.8</v>
       </c>
       <c r="F77" t="n">
-        <v>12195.3</v>
+        <v>12472.5</v>
       </c>
     </row>
     <row r="78">
@@ -2274,13 +2268,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="D78" t="n">
-        <v>8024.1</v>
+        <v>8034.7</v>
       </c>
       <c r="E78" t="n">
-        <v>8607.299999999999</v>
+        <v>8618.5</v>
       </c>
       <c r="F78" t="n">
         <v>9113.799999999999</v>
@@ -2298,16 +2292,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9540</v>
+        <v>9437</v>
       </c>
       <c r="D79" t="n">
-        <v>37032.5</v>
+        <v>37054.8</v>
       </c>
       <c r="E79" t="n">
-        <v>39694.8</v>
+        <v>39842.8</v>
       </c>
       <c r="F79" t="n">
-        <v>42426.6</v>
+        <v>42556.9</v>
       </c>
     </row>
     <row r="80">
@@ -2322,16 +2316,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2188</v>
+        <v>2179</v>
       </c>
       <c r="D80" t="n">
-        <v>8858.799999999999</v>
+        <v>8839.6</v>
       </c>
       <c r="E80" t="n">
-        <v>10346.4</v>
+        <v>10306.5</v>
       </c>
       <c r="F80" t="n">
-        <v>11488.3</v>
+        <v>11529.4</v>
       </c>
     </row>
     <row r="81">
@@ -2370,16 +2364,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1462</v>
+        <v>1495</v>
       </c>
       <c r="D82" t="n">
-        <v>5779.2</v>
+        <v>5839.5</v>
       </c>
       <c r="E82" t="n">
-        <v>6028.2</v>
+        <v>6010.8</v>
       </c>
       <c r="F82" t="n">
-        <v>6313.5</v>
+        <v>6274.3</v>
       </c>
     </row>
     <row r="83">
@@ -2418,16 +2412,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D84" t="n">
-        <v>3348.2</v>
+        <v>3339.9</v>
       </c>
       <c r="E84" t="n">
-        <v>3651.5</v>
+        <v>3636.7</v>
       </c>
       <c r="F84" t="n">
-        <v>3717.2</v>
+        <v>3692.6</v>
       </c>
     </row>
     <row r="85">
@@ -2442,16 +2436,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6136</v>
+        <v>6133</v>
       </c>
       <c r="D85" t="n">
-        <v>20737.3</v>
+        <v>20721.3</v>
       </c>
       <c r="E85" t="n">
-        <v>22559</v>
+        <v>22526.8</v>
       </c>
       <c r="F85" t="n">
-        <v>23920.2</v>
+        <v>23847.4</v>
       </c>
     </row>
     <row r="86">
@@ -2466,16 +2460,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3067</v>
+        <v>3062</v>
       </c>
       <c r="D86" t="n">
-        <v>11140</v>
+        <v>11111.1</v>
       </c>
       <c r="E86" t="n">
-        <v>11942.1</v>
+        <v>11959</v>
       </c>
       <c r="F86" t="n">
-        <v>12702.2</v>
+        <v>12715.1</v>
       </c>
     </row>
     <row r="87">
@@ -2490,7 +2484,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10545</v>
+        <v>10237</v>
       </c>
       <c r="D87" t="n">
         <v>33019.2</v>
@@ -2514,16 +2508,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3830</v>
+        <v>3843</v>
       </c>
       <c r="D88" t="n">
-        <v>15061.6</v>
+        <v>15067.6</v>
       </c>
       <c r="E88" t="n">
         <v>16299.9</v>
       </c>
       <c r="F88" t="n">
-        <v>17235</v>
+        <v>17227</v>
       </c>
     </row>
     <row r="89">
@@ -2586,13 +2580,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D91" t="n">
-        <v>1860.2</v>
+        <v>1856.2</v>
       </c>
       <c r="E91" t="n">
-        <v>2235.7</v>
+        <v>2235.1</v>
       </c>
       <c r="F91" t="n">
         <v>2456</v>
@@ -2610,7 +2604,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>24552</v>
+        <v>24551</v>
       </c>
       <c r="D92" t="n">
         <v>98678.39999999999</v>
@@ -2658,16 +2652,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5717</v>
+        <v>5693</v>
       </c>
       <c r="D94" t="n">
-        <v>24009.3</v>
+        <v>23970.7</v>
       </c>
       <c r="E94" t="n">
-        <v>27681.3</v>
+        <v>27661</v>
       </c>
       <c r="F94" t="n">
-        <v>31261.7</v>
+        <v>31280.1</v>
       </c>
     </row>
     <row r="95">
@@ -2682,16 +2676,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2234</v>
+        <v>2226</v>
       </c>
       <c r="D95" t="n">
-        <v>9356.9</v>
+        <v>9376.9</v>
       </c>
       <c r="E95" t="n">
-        <v>10898.9</v>
+        <v>10913.1</v>
       </c>
       <c r="F95" t="n">
-        <v>12550.9</v>
+        <v>12611.7</v>
       </c>
     </row>
     <row r="96">
@@ -2730,16 +2724,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D97" t="n">
-        <v>5044</v>
+        <v>5021.2</v>
       </c>
       <c r="E97" t="n">
-        <v>5934.2</v>
+        <v>5888.8</v>
       </c>
       <c r="F97" t="n">
-        <v>6107.5</v>
+        <v>6011.7</v>
       </c>
     </row>
     <row r="98">
@@ -2754,16 +2748,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5746</v>
+        <v>6257</v>
       </c>
       <c r="D98" t="n">
-        <v>21122.5</v>
+        <v>21724.8</v>
       </c>
       <c r="E98" t="n">
-        <v>20023.6</v>
+        <v>20349.5</v>
       </c>
       <c r="F98" t="n">
-        <v>20358.3</v>
+        <v>20600.4</v>
       </c>
     </row>
     <row r="99">
@@ -2778,16 +2772,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5006</v>
+        <v>5217</v>
       </c>
       <c r="D99" t="n">
-        <v>18354.6</v>
+        <v>18987.4</v>
       </c>
       <c r="E99" t="n">
-        <v>23361.2</v>
+        <v>23507.6</v>
       </c>
       <c r="F99" t="n">
-        <v>27990.8</v>
+        <v>27892.4</v>
       </c>
     </row>
     <row r="100">
@@ -2826,16 +2820,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1481</v>
+        <v>1508</v>
       </c>
       <c r="D101" t="n">
-        <v>6922.8</v>
+        <v>6988.2</v>
       </c>
       <c r="E101" t="n">
-        <v>7217.9</v>
+        <v>7254.8</v>
       </c>
       <c r="F101" t="n">
-        <v>8205.799999999999</v>
+        <v>8244.9</v>
       </c>
     </row>
     <row r="102">
@@ -2853,13 +2847,13 @@
         <v>3517</v>
       </c>
       <c r="D102" t="n">
-        <v>13927.6</v>
+        <v>13940.8</v>
       </c>
       <c r="E102" t="n">
-        <v>15047.8</v>
+        <v>15092.4</v>
       </c>
       <c r="F102" t="n">
-        <v>15748.5</v>
+        <v>15771.5</v>
       </c>
     </row>
     <row r="103">
@@ -2874,16 +2868,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1026</v>
+        <v>1002</v>
       </c>
       <c r="D103" t="n">
-        <v>4699.8</v>
+        <v>4679.8</v>
       </c>
       <c r="E103" t="n">
-        <v>6659.8</v>
+        <v>6650.4</v>
       </c>
       <c r="F103" t="n">
-        <v>8069.8</v>
+        <v>8075.1</v>
       </c>
     </row>
     <row r="104">
@@ -2922,16 +2916,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>724</v>
+        <v>751</v>
       </c>
       <c r="D105" t="n">
-        <v>3358.1</v>
+        <v>3421.5</v>
       </c>
       <c r="E105" t="n">
-        <v>3999.1</v>
+        <v>3992.5</v>
       </c>
       <c r="F105" t="n">
-        <v>4304.6</v>
+        <v>4283.7</v>
       </c>
     </row>
     <row r="106">
@@ -2946,16 +2940,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3535</v>
+        <v>3808</v>
       </c>
       <c r="D106" t="n">
-        <v>14268.5</v>
+        <v>15532.2</v>
       </c>
       <c r="E106" t="n">
-        <v>39453.1</v>
+        <v>42457.5</v>
       </c>
       <c r="F106" t="n">
-        <v>54547.7</v>
+        <v>59569.1</v>
       </c>
     </row>
     <row r="107">
@@ -2994,16 +2988,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>22230</v>
+        <v>22193</v>
       </c>
       <c r="D108" t="n">
-        <v>76847.10000000001</v>
+        <v>76844.60000000001</v>
       </c>
       <c r="E108" t="n">
-        <v>81755.10000000001</v>
+        <v>81715.8</v>
       </c>
       <c r="F108" t="n">
-        <v>85200.2</v>
+        <v>85049.5</v>
       </c>
     </row>
     <row r="109">
@@ -3018,16 +3012,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D109" t="n">
-        <v>2496.6</v>
+        <v>2487.6</v>
       </c>
       <c r="E109" t="n">
-        <v>3337</v>
+        <v>3312.3</v>
       </c>
       <c r="F109" t="n">
-        <v>4291</v>
+        <v>4295.2</v>
       </c>
     </row>
     <row r="110">
@@ -3066,16 +3060,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1446</v>
+        <v>1434</v>
       </c>
       <c r="D111" t="n">
-        <v>6174.8</v>
+        <v>6162.8</v>
       </c>
       <c r="E111" t="n">
-        <v>7034.6</v>
+        <v>7022.6</v>
       </c>
       <c r="F111" t="n">
-        <v>7926.7</v>
+        <v>7902.2</v>
       </c>
     </row>
     <row r="112">
@@ -3093,13 +3087,13 @@
         <v>10580</v>
       </c>
       <c r="D112" t="n">
-        <v>39761.6</v>
+        <v>42384.2</v>
       </c>
       <c r="E112" t="n">
-        <v>44047.7</v>
+        <v>45628.6</v>
       </c>
       <c r="F112" t="n">
-        <v>53580.1</v>
+        <v>55174.1</v>
       </c>
     </row>
     <row r="113">
@@ -3114,16 +3108,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="D113" t="n">
-        <v>2436.4</v>
+        <v>2517.9</v>
       </c>
       <c r="E113" t="n">
-        <v>2285.7</v>
+        <v>2311</v>
       </c>
       <c r="F113" t="n">
-        <v>3228.6</v>
+        <v>3257.2</v>
       </c>
     </row>
     <row r="114">
@@ -3141,13 +3135,13 @@
         <v>4017</v>
       </c>
       <c r="D114" t="n">
-        <v>17618.7</v>
+        <v>17705.6</v>
       </c>
       <c r="E114" t="n">
-        <v>20984.4</v>
+        <v>21003.2</v>
       </c>
       <c r="F114" t="n">
-        <v>24698.8</v>
+        <v>24637.2</v>
       </c>
     </row>
     <row r="115">
@@ -3210,16 +3204,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="D117" t="n">
-        <v>4345.3</v>
+        <v>4359.2</v>
       </c>
       <c r="E117" t="n">
-        <v>5236.6</v>
+        <v>5268.4</v>
       </c>
       <c r="F117" t="n">
-        <v>5604.9</v>
+        <v>5649.9</v>
       </c>
     </row>
     <row r="118">
@@ -3234,16 +3228,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>9591</v>
+        <v>10145</v>
       </c>
       <c r="D118" t="n">
-        <v>34673.7</v>
+        <v>35060.4</v>
       </c>
       <c r="E118" t="n">
-        <v>31874.9</v>
+        <v>32190.9</v>
       </c>
       <c r="F118" t="n">
-        <v>32317.2</v>
+        <v>32379.5</v>
       </c>
     </row>
     <row r="119">
@@ -3285,13 +3279,13 @@
         <v>355</v>
       </c>
       <c r="D120" t="n">
-        <v>1515.1</v>
+        <v>1522.5</v>
       </c>
       <c r="E120" t="n">
-        <v>2029.4</v>
+        <v>2035.3</v>
       </c>
       <c r="F120" t="n">
-        <v>2509.1</v>
+        <v>2477.5</v>
       </c>
     </row>
     <row r="121">
@@ -3306,16 +3300,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="D121" t="n">
-        <v>5764.2</v>
+        <v>5763.7</v>
       </c>
       <c r="E121" t="n">
-        <v>6140.9</v>
+        <v>5993.2</v>
       </c>
       <c r="F121" t="n">
-        <v>6939.2</v>
+        <v>6656.3</v>
       </c>
     </row>
     <row r="122">
@@ -3378,16 +3372,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2075</v>
+        <v>2121</v>
       </c>
       <c r="D124" t="n">
-        <v>5590.4</v>
+        <v>5637.1</v>
       </c>
       <c r="E124" t="n">
-        <v>5992.6</v>
+        <v>6005.9</v>
       </c>
       <c r="F124" t="n">
-        <v>6216.9</v>
+        <v>6231.9</v>
       </c>
     </row>
     <row r="125">
@@ -3402,16 +3396,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D125" t="n">
-        <v>2442</v>
+        <v>2407.6</v>
       </c>
       <c r="E125" t="n">
-        <v>3678.6</v>
+        <v>3687.6</v>
       </c>
       <c r="F125" t="n">
-        <v>4513.2</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="126">
@@ -3429,13 +3423,13 @@
         <v>5218</v>
       </c>
       <c r="D126" t="n">
-        <v>21777.1</v>
+        <v>21784.2</v>
       </c>
       <c r="E126" t="n">
-        <v>23327.9</v>
+        <v>23322.1</v>
       </c>
       <c r="F126" t="n">
-        <v>24468.7</v>
+        <v>24482.1</v>
       </c>
     </row>
     <row r="127">
@@ -3450,16 +3444,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>16554</v>
+        <v>16577</v>
       </c>
       <c r="D127" t="n">
-        <v>60316.2</v>
+        <v>60367.7</v>
       </c>
       <c r="E127" t="n">
-        <v>63092.1</v>
+        <v>63117.4</v>
       </c>
       <c r="F127" t="n">
-        <v>66160.60000000001</v>
+        <v>65992.2</v>
       </c>
     </row>
     <row r="128">
@@ -3474,13 +3468,13 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>8076.7</v>
+        <v>8132.5</v>
       </c>
       <c r="E128" t="n">
-        <v>9033.6</v>
+        <v>9055.200000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>8843</v>
+        <v>8905.200000000001</v>
       </c>
     </row>
     <row r="129">
@@ -3495,16 +3489,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="D129" t="n">
-        <v>4613.4</v>
+        <v>4637.6</v>
       </c>
       <c r="E129" t="n">
-        <v>5257.9</v>
+        <v>5278.1</v>
       </c>
       <c r="F129" t="n">
-        <v>5839.2</v>
+        <v>5882.1</v>
       </c>
     </row>
     <row r="130">
@@ -3534,16 +3528,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>13895</v>
+        <v>13980</v>
       </c>
       <c r="D131" t="n">
-        <v>50970.7</v>
+        <v>50950.2</v>
       </c>
       <c r="E131" t="n">
-        <v>31170</v>
+        <v>31187.9</v>
       </c>
       <c r="F131" t="n">
-        <v>34632.2</v>
+        <v>36712.4</v>
       </c>
     </row>
     <row r="132">
@@ -3582,16 +3576,16 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="D133" t="n">
-        <v>3619.2</v>
+        <v>3617.8</v>
       </c>
       <c r="E133" t="n">
-        <v>3617.9</v>
+        <v>3606.6</v>
       </c>
       <c r="F133" t="n">
-        <v>3995.7</v>
+        <v>3982.7</v>
       </c>
     </row>
     <row r="134">
@@ -3606,16 +3600,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>25205</v>
+        <v>25740</v>
       </c>
       <c r="D134" t="n">
-        <v>92326.8</v>
+        <v>92733.10000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>94131.89999999999</v>
+        <v>94340.8</v>
       </c>
       <c r="F134" t="n">
-        <v>96926.39999999999</v>
+        <v>97139.5</v>
       </c>
     </row>
     <row r="135">
@@ -3657,13 +3651,13 @@
         <v>787</v>
       </c>
       <c r="D136" t="n">
-        <v>3043.3</v>
+        <v>3032.2</v>
       </c>
       <c r="E136" t="n">
-        <v>3524</v>
+        <v>3488.4</v>
       </c>
       <c r="F136" t="n">
-        <v>3360.5</v>
+        <v>3305.5</v>
       </c>
     </row>
     <row r="137">
@@ -3702,16 +3696,16 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D138" t="n">
-        <v>2748.8</v>
+        <v>2803.7</v>
       </c>
       <c r="E138" t="n">
-        <v>3104.2</v>
+        <v>3114.5</v>
       </c>
       <c r="F138" t="n">
-        <v>3326.2</v>
+        <v>3340.5</v>
       </c>
     </row>
     <row r="139">
@@ -3750,16 +3744,16 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3388</v>
+        <v>3328</v>
       </c>
       <c r="D140" t="n">
-        <v>11174.3</v>
+        <v>11090.9</v>
       </c>
       <c r="E140" t="n">
-        <v>12022.1</v>
+        <v>11963.5</v>
       </c>
       <c r="F140" t="n">
-        <v>12739.8</v>
+        <v>12679.9</v>
       </c>
     </row>
     <row r="141">
@@ -3774,16 +3768,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2129</v>
+        <v>2101</v>
       </c>
       <c r="D141" t="n">
-        <v>6665.5</v>
+        <v>6646.1</v>
       </c>
       <c r="E141" t="n">
-        <v>7159.7</v>
+        <v>7169.7</v>
       </c>
       <c r="F141" t="n">
-        <v>7616.2</v>
+        <v>7576.4</v>
       </c>
     </row>
     <row r="142">
@@ -3798,13 +3792,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="D142" t="n">
-        <v>5624.7</v>
+        <v>5599.1</v>
       </c>
       <c r="E142" t="n">
-        <v>6565.3</v>
+        <v>6533.8</v>
       </c>
       <c r="F142" t="n">
         <v>7229.4</v>
@@ -3822,16 +3816,16 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5250</v>
+        <v>5313</v>
       </c>
       <c r="D143" t="n">
-        <v>21343.7</v>
+        <v>21431.1</v>
       </c>
       <c r="E143" t="n">
-        <v>23655.5</v>
+        <v>23669.5</v>
       </c>
       <c r="F143" t="n">
-        <v>25920.6</v>
+        <v>25886.4</v>
       </c>
     </row>
     <row r="144">
@@ -3846,16 +3840,16 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="D144" t="n">
-        <v>3116.3</v>
+        <v>3148.2</v>
       </c>
       <c r="E144" t="n">
-        <v>3592</v>
+        <v>3633</v>
       </c>
       <c r="F144" t="n">
-        <v>4045.2</v>
+        <v>4096.7</v>
       </c>
     </row>
     <row r="145">
@@ -3870,16 +3864,16 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2846</v>
+        <v>2872</v>
       </c>
       <c r="D145" t="n">
-        <v>10119.9</v>
+        <v>10076.6</v>
       </c>
       <c r="E145" t="n">
-        <v>10878.2</v>
+        <v>10814.8</v>
       </c>
       <c r="F145" t="n">
-        <v>11448</v>
+        <v>11377.3</v>
       </c>
     </row>
     <row r="146">
@@ -3897,13 +3891,13 @@
         <v>210</v>
       </c>
       <c r="D146" t="n">
-        <v>832.5</v>
+        <v>804.6</v>
       </c>
       <c r="E146" t="n">
-        <v>930.3</v>
+        <v>937.8</v>
       </c>
       <c r="F146" t="n">
-        <v>1021</v>
+        <v>1023.2</v>
       </c>
     </row>
     <row r="147">
@@ -3942,16 +3936,16 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D148" t="n">
-        <v>2326.2</v>
+        <v>2327.5</v>
       </c>
       <c r="E148" t="n">
-        <v>2746.1</v>
+        <v>2766.5</v>
       </c>
       <c r="F148" t="n">
-        <v>3147.5</v>
+        <v>3194</v>
       </c>
     </row>
     <row r="149">
@@ -3966,16 +3960,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D149" t="n">
-        <v>4038.7</v>
+        <v>4028.2</v>
       </c>
       <c r="E149" t="n">
-        <v>4725.9</v>
+        <v>4685.9</v>
       </c>
       <c r="F149" t="n">
-        <v>5271.8</v>
+        <v>5234.6</v>
       </c>
     </row>
     <row r="150">
@@ -3990,7 +3984,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5982</v>
+        <v>5997</v>
       </c>
       <c r="D150" t="n">
         <v>24946.2</v>
@@ -4014,16 +4008,16 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1905</v>
+        <v>1941</v>
       </c>
       <c r="D151" t="n">
-        <v>7537.3</v>
+        <v>7591.4</v>
       </c>
       <c r="E151" t="n">
-        <v>9145.9</v>
+        <v>9204.1</v>
       </c>
       <c r="F151" t="n">
-        <v>10099.3</v>
+        <v>10163</v>
       </c>
     </row>
     <row r="152">
@@ -4062,16 +4056,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3576</v>
+        <v>3671</v>
       </c>
       <c r="D153" t="n">
-        <v>14624.1</v>
+        <v>14812.8</v>
       </c>
       <c r="E153" t="n">
-        <v>15762.8</v>
+        <v>15832.8</v>
       </c>
       <c r="F153" t="n">
-        <v>17017.6</v>
+        <v>17211.9</v>
       </c>
     </row>
     <row r="154">
@@ -4110,16 +4104,16 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2845</v>
+        <v>2842</v>
       </c>
       <c r="D155" t="n">
-        <v>12451.1</v>
+        <v>12432</v>
       </c>
       <c r="E155" t="n">
-        <v>15397.3</v>
+        <v>15390.2</v>
       </c>
       <c r="F155" t="n">
-        <v>18794.8</v>
+        <v>18811.5</v>
       </c>
     </row>
     <row r="156">
@@ -4134,16 +4128,16 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1940</v>
+        <v>1945</v>
       </c>
       <c r="D156" t="n">
-        <v>6829.1</v>
+        <v>6812.6</v>
       </c>
       <c r="E156" t="n">
-        <v>8533.200000000001</v>
+        <v>8492.700000000001</v>
       </c>
       <c r="F156" t="n">
-        <v>10361.5</v>
+        <v>10354.5</v>
       </c>
     </row>
     <row r="157">
@@ -4161,7 +4155,7 @@
         <v>1376</v>
       </c>
       <c r="D157" t="n">
-        <v>6508</v>
+        <v>6507.6</v>
       </c>
       <c r="E157" t="n">
         <v>7041.8</v>
@@ -4182,13 +4176,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="D158" t="n">
-        <v>2758</v>
+        <v>2744.2</v>
       </c>
       <c r="E158" t="n">
-        <v>4893.2</v>
+        <v>4888.5</v>
       </c>
       <c r="F158" t="n">
         <v>6189.8</v>
@@ -4206,16 +4200,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1674</v>
+        <v>1735</v>
       </c>
       <c r="D159" t="n">
-        <v>6868.8</v>
+        <v>7140.1</v>
       </c>
       <c r="E159" t="n">
-        <v>9190.700000000001</v>
+        <v>9637.700000000001</v>
       </c>
       <c r="F159" t="n">
-        <v>11352.8</v>
+        <v>12055.9</v>
       </c>
     </row>
     <row r="160">
@@ -4230,16 +4224,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D160" t="n">
-        <v>1880.4</v>
+        <v>1888.8</v>
       </c>
       <c r="E160" t="n">
-        <v>2144</v>
+        <v>2153.5</v>
       </c>
       <c r="F160" t="n">
-        <v>2397.4</v>
+        <v>2409.9</v>
       </c>
     </row>
     <row r="161">
@@ -4254,16 +4248,16 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="D161" t="n">
-        <v>2898.9</v>
+        <v>2910.9</v>
       </c>
       <c r="E161" t="n">
-        <v>3183.1</v>
+        <v>3201.2</v>
       </c>
       <c r="F161" t="n">
-        <v>3423.3</v>
+        <v>3447.5</v>
       </c>
     </row>
     <row r="162">
@@ -4302,16 +4296,16 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D163" t="n">
-        <v>4444.8</v>
+        <v>4462.8</v>
       </c>
       <c r="E163" t="n">
-        <v>5259.2</v>
+        <v>5285.2</v>
       </c>
       <c r="F163" t="n">
-        <v>5628.6</v>
+        <v>5652.6</v>
       </c>
     </row>
     <row r="164">
@@ -4422,16 +4416,16 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="D168" t="n">
-        <v>2782.4</v>
+        <v>2774.2</v>
       </c>
       <c r="E168" t="n">
-        <v>3700.4</v>
+        <v>3692.2</v>
       </c>
       <c r="F168" t="n">
-        <v>4723.6</v>
+        <v>4669.3</v>
       </c>
     </row>
     <row r="169">
@@ -4446,16 +4440,16 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>12798</v>
+        <v>12888</v>
       </c>
       <c r="D169" t="n">
-        <v>43303.2</v>
+        <v>43419.9</v>
       </c>
       <c r="E169" t="n">
-        <v>47726.6</v>
+        <v>47767.7</v>
       </c>
       <c r="F169" t="n">
-        <v>50690.1</v>
+        <v>50466.5</v>
       </c>
     </row>
     <row r="170">
@@ -4470,13 +4464,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1821</v>
+        <v>1829</v>
       </c>
       <c r="D170" t="n">
-        <v>7088.4</v>
+        <v>7092.9</v>
       </c>
       <c r="E170" t="n">
-        <v>8172.6</v>
+        <v>8168.1</v>
       </c>
       <c r="F170" t="n">
         <v>8940.6</v>
@@ -4521,13 +4515,13 @@
         <v>10003</v>
       </c>
       <c r="D172" t="n">
-        <v>38921.6</v>
+        <v>39168.8</v>
       </c>
       <c r="E172" t="n">
-        <v>45762.3</v>
+        <v>46037.2</v>
       </c>
       <c r="F172" t="n">
-        <v>51602.7</v>
+        <v>52136.8</v>
       </c>
     </row>
     <row r="173">
@@ -4542,16 +4536,16 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1480</v>
+        <v>1499</v>
       </c>
       <c r="D173" t="n">
-        <v>2636.4</v>
+        <v>2659.2</v>
       </c>
       <c r="E173" t="n">
-        <v>4927.2</v>
+        <v>4935</v>
       </c>
       <c r="F173" t="n">
-        <v>5503</v>
+        <v>5511.5</v>
       </c>
     </row>
     <row r="174">
@@ -4593,13 +4587,13 @@
         <v>2034</v>
       </c>
       <c r="D175" t="n">
-        <v>11620.7</v>
+        <v>11444.5</v>
       </c>
       <c r="E175" t="n">
-        <v>40233</v>
+        <v>39869.5</v>
       </c>
       <c r="F175" t="n">
-        <v>60285.2</v>
+        <v>61536.8</v>
       </c>
     </row>
     <row r="176">
@@ -4617,10 +4611,10 @@
         <v>1199</v>
       </c>
       <c r="D176" t="n">
-        <v>5086.2</v>
+        <v>5086.1</v>
       </c>
       <c r="E176" t="n">
-        <v>5624.6</v>
+        <v>5624.8</v>
       </c>
       <c r="F176" t="n">
         <v>6159</v>
@@ -4665,10 +4659,10 @@
         <v>969</v>
       </c>
       <c r="D178" t="n">
-        <v>5294.7</v>
+        <v>5294.5</v>
       </c>
       <c r="E178" t="n">
-        <v>5593.2</v>
+        <v>5592.8</v>
       </c>
       <c r="F178" t="n">
         <v>5983.8</v>
@@ -4773,16 +4767,16 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D183" t="n">
-        <v>1617.9</v>
+        <v>1606.1</v>
       </c>
       <c r="E183" t="n">
-        <v>2200.1</v>
+        <v>2195.5</v>
       </c>
       <c r="F183" t="n">
-        <v>2794</v>
+        <v>2769.4</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:N181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -436,12 +436,20 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-06 · 첫 스냅샷</t>
+          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-13 · 전주 2026-07-06</t>
         </is>
       </c>
     </row>
@@ -463,17 +471,57 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>이번분기 전주</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>이번분기 변동%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>2026E(2026.12) 영업이익</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2026E 전주</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026E 변동%</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2027E(2027.12) 영업이익</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2027E 전주</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2027E 변동%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>2028E(2028.12) 영업이익</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2028E 전주</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2028E 변동%</t>
         </is>
       </c>
     </row>
@@ -489,16 +537,40 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>615</v>
+      </c>
+      <c r="D3" t="n">
         <v>601</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1958.2</v>
+      </c>
+      <c r="G3" t="n">
         <v>1935</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2060.6</v>
+      </c>
+      <c r="J3" t="n">
         <v>2019.7</v>
       </c>
-      <c r="F3" t="n">
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2183</v>
+      </c>
+      <c r="M3" t="n">
         <v>2119.6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -516,13 +588,37 @@
         <v>612</v>
       </c>
       <c r="D4" t="n">
+        <v>612</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1321.9</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>1321.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>2176.3</v>
       </c>
-      <c r="F4" t="n">
+      <c r="J4" t="n">
+        <v>2176.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>2997.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2997.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -537,16 +633,40 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>1140</v>
+      </c>
+      <c r="D5" t="n">
         <v>1143</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5163</v>
+      </c>
+      <c r="G5" t="n">
         <v>5169.7</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5718.2</v>
+      </c>
+      <c r="J5" t="n">
         <v>5729.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="K5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6160.5</v>
+      </c>
+      <c r="M5" t="n">
         <v>6172.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="6">
@@ -564,13 +684,37 @@
         <v>4571</v>
       </c>
       <c r="D6" t="n">
+        <v>4571</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>17063.8</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
+        <v>17063.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>23491.7</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
+        <v>23491.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>29523.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29523.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -588,13 +732,37 @@
         <v>1554</v>
       </c>
       <c r="D7" t="n">
+        <v>1554</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>5348</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>5348</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>5057.5</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
+        <v>5057.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>5435</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5435</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -612,13 +780,37 @@
         <v>1365</v>
       </c>
       <c r="D8" t="n">
+        <v>1365</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>4574</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
+        <v>4574</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>4536</v>
       </c>
-      <c r="F8" t="n">
+      <c r="J8" t="n">
+        <v>4536</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>5420</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5420</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -633,16 +825,40 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>27920</v>
+      </c>
+      <c r="D9" t="n">
         <v>27949</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>102466.9</v>
+      </c>
+      <c r="G9" t="n">
         <v>102265.5</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>113527.7</v>
+      </c>
+      <c r="J9" t="n">
         <v>113377.6</v>
       </c>
-      <c r="F9" t="n">
+      <c r="K9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>120853.9</v>
+      </c>
+      <c r="M9" t="n">
         <v>121044.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="10">
@@ -660,13 +876,37 @@
         <v>650541</v>
       </c>
       <c r="D10" t="n">
+        <v>650541</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>2767812.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
+        <v>2767812.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>4043634.6</v>
       </c>
-      <c r="F10" t="n">
+      <c r="J10" t="n">
+        <v>4043634.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>3939915.6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3939915.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -684,13 +924,37 @@
         <v>2005</v>
       </c>
       <c r="D11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8244.4</v>
+      </c>
+      <c r="G11" t="n">
         <v>8242.299999999999</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11142.2</v>
+      </c>
+      <c r="J11" t="n">
         <v>11144</v>
       </c>
-      <c r="F11" t="n">
+      <c r="K11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13845.2</v>
+      </c>
+      <c r="M11" t="n">
         <v>13889.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="12">
@@ -708,13 +972,37 @@
         <v>8312</v>
       </c>
       <c r="D12" t="n">
+        <v>8312</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>30345.1</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
+        <v>30345.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>32907.2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="J12" t="n">
+        <v>32907.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>33721.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>33721.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -732,13 +1020,37 @@
         <v>14500</v>
       </c>
       <c r="D13" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>56369.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
+        <v>56369.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>69187.3</v>
       </c>
-      <c r="F13" t="n">
+      <c r="J13" t="n">
+        <v>69187.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>72135</v>
+      </c>
+      <c r="M13" t="n">
+        <v>72135</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -756,13 +1068,37 @@
         <v>886</v>
       </c>
       <c r="D14" t="n">
+        <v>886</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>3667.7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
+        <v>3667.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>4733.7</v>
       </c>
-      <c r="F14" t="n">
+      <c r="J14" t="n">
+        <v>4733.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>5485.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5485.5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -780,13 +1116,37 @@
         <v>7075</v>
       </c>
       <c r="D15" t="n">
+        <v>7075</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>27186.7</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
+        <v>27186.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>30305.6</v>
       </c>
-      <c r="F15" t="n">
+      <c r="J15" t="n">
+        <v>30305.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>31530.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>31530.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -801,16 +1161,40 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>508</v>
+      </c>
+      <c r="D16" t="n">
         <v>513</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1464.4</v>
+      </c>
+      <c r="G16" t="n">
         <v>1452.7</v>
       </c>
-      <c r="E16" t="n">
+      <c r="H16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2038.9</v>
+      </c>
+      <c r="J16" t="n">
         <v>2000.3</v>
       </c>
-      <c r="F16" t="n">
+      <c r="K16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2062.4</v>
+      </c>
+      <c r="M16" t="n">
         <v>2036.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="17">
@@ -828,13 +1212,37 @@
         <v>426</v>
       </c>
       <c r="D17" t="n">
+        <v>426</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>1963.7</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
+        <v>1963.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>2356.2</v>
       </c>
-      <c r="F17" t="n">
+      <c r="J17" t="n">
+        <v>2356.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>3058</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3058</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -848,14 +1256,32 @@
           <t>현대해상</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>10434.4</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
+        <v>10434.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>12149.2</v>
       </c>
-      <c r="F18" t="n">
+      <c r="J18" t="n">
+        <v>12149.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>13426.9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>13426.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -873,13 +1299,37 @@
         <v>396</v>
       </c>
       <c r="D19" t="n">
+        <v>396</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>1830.5</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
+        <v>1830.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>2044</v>
       </c>
-      <c r="F19" t="n">
+      <c r="J19" t="n">
+        <v>2044</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2060</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2060</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -897,7 +1347,19 @@
         <v>1224</v>
       </c>
       <c r="D20" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>6028</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6028</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -915,13 +1377,37 @@
         <v>1051</v>
       </c>
       <c r="D21" t="n">
+        <v>1051</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>4153.2</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
+        <v>4153.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>4725</v>
       </c>
-      <c r="F21" t="n">
+      <c r="J21" t="n">
+        <v>4725</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>5072.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5072.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -939,13 +1425,37 @@
         <v>422</v>
       </c>
       <c r="D22" t="n">
+        <v>422</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>1767.5</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
+        <v>1767.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>2913</v>
       </c>
-      <c r="F22" t="n">
+      <c r="J22" t="n">
+        <v>2913</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>4827</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4827</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -960,16 +1470,40 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1790</v>
+      </c>
+      <c r="D23" t="n">
         <v>1767</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7298.4</v>
+      </c>
+      <c r="G23" t="n">
         <v>7269.1</v>
       </c>
-      <c r="E23" t="n">
+      <c r="H23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8765.200000000001</v>
+      </c>
+      <c r="J23" t="n">
         <v>8732.5</v>
       </c>
-      <c r="F23" t="n">
+      <c r="K23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10284.3</v>
+      </c>
+      <c r="M23" t="n">
         <v>10306.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="24">
@@ -987,13 +1521,37 @@
         <v>-2207</v>
       </c>
       <c r="D24" t="n">
+        <v>-2207</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>8666.299999999999</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
+        <v>8666.299999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>20882.1</v>
       </c>
-      <c r="F24" t="n">
+      <c r="J24" t="n">
+        <v>20882.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>25171.4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>25171.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1011,13 +1569,37 @@
         <v>4161</v>
       </c>
       <c r="D25" t="n">
+        <v>4161</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>16182.7</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
+        <v>16182.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>20528.9</v>
       </c>
-      <c r="F25" t="n">
+      <c r="J25" t="n">
+        <v>20528.9</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>21051.1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>21051.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1032,16 +1614,40 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>283</v>
+      </c>
+      <c r="D26" t="n">
         <v>284</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>952.8</v>
+      </c>
+      <c r="G26" t="n">
         <v>955.3</v>
       </c>
-      <c r="E26" t="n">
+      <c r="H26" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1606.5</v>
+      </c>
+      <c r="J26" t="n">
         <v>1620.8</v>
       </c>
-      <c r="F26" t="n">
+      <c r="K26" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2814.7</v>
+      </c>
+      <c r="M26" t="n">
         <v>2823.6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="27">
@@ -1059,13 +1665,37 @@
         <v>357</v>
       </c>
       <c r="D27" t="n">
+        <v>357</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>1388</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
+        <v>1388</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>1592.5</v>
       </c>
-      <c r="F27" t="n">
+      <c r="J27" t="n">
+        <v>1592.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1730</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1730</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1080,16 +1710,40 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D28" t="n">
         <v>1038</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4371.2</v>
+      </c>
+      <c r="G28" t="n">
         <v>4357.2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="H28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7567</v>
+      </c>
+      <c r="J28" t="n">
         <v>7439.7</v>
       </c>
-      <c r="F28" t="n">
+      <c r="K28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>8315.4</v>
+      </c>
+      <c r="M28" t="n">
         <v>8169.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="29">
@@ -1107,13 +1761,37 @@
         <v>1502</v>
       </c>
       <c r="D29" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>7610.5</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
+        <v>7610.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>8508.299999999999</v>
       </c>
-      <c r="F29" t="n">
+      <c r="J29" t="n">
+        <v>8508.299999999999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>8956</v>
+      </c>
+      <c r="M29" t="n">
+        <v>8956</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1806,40 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>485</v>
+      </c>
+      <c r="D30" t="n">
         <v>484</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2133.8</v>
+      </c>
+      <c r="G30" t="n">
         <v>2120.6</v>
       </c>
-      <c r="E30" t="n">
+      <c r="H30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2307.4</v>
+      </c>
+      <c r="J30" t="n">
         <v>2292.7</v>
       </c>
-      <c r="F30" t="n">
+      <c r="K30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2449.6</v>
+      </c>
+      <c r="M30" t="n">
         <v>2433.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="31">
@@ -1155,13 +1857,37 @@
         <v>1613</v>
       </c>
       <c r="D31" t="n">
+        <v>1613</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>3797</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
+        <v>3797</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>4472.5</v>
       </c>
-      <c r="F31" t="n">
+      <c r="J31" t="n">
+        <v>4472.5</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>7397.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7397.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1176,16 +1902,40 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>651</v>
+      </c>
+      <c r="D32" t="n">
         <v>631</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2138.2</v>
+      </c>
+      <c r="G32" t="n">
         <v>2130.5</v>
       </c>
-      <c r="E32" t="n">
+      <c r="H32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2364.6</v>
+      </c>
+      <c r="J32" t="n">
         <v>2350.3</v>
       </c>
-      <c r="F32" t="n">
+      <c r="K32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2497</v>
+      </c>
+      <c r="M32" t="n">
         <v>2458.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="33">
@@ -1200,16 +1950,40 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>31086</v>
+      </c>
+      <c r="D33" t="n">
         <v>31377</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>118721.8</v>
+      </c>
+      <c r="G33" t="n">
         <v>119102.2</v>
       </c>
-      <c r="E33" t="n">
+      <c r="H33" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>133560</v>
+      </c>
+      <c r="J33" t="n">
         <v>133173.4</v>
       </c>
-      <c r="F33" t="n">
+      <c r="K33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>146466.8</v>
+      </c>
+      <c r="M33" t="n">
         <v>145756.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -1224,16 +1998,40 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>7419</v>
+      </c>
+      <c r="D34" t="n">
         <v>7489</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>31078.4</v>
+      </c>
+      <c r="G34" t="n">
         <v>31736.7</v>
       </c>
-      <c r="E34" t="n">
+      <c r="H34" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>38922.9</v>
+      </c>
+      <c r="J34" t="n">
         <v>40076.2</v>
       </c>
-      <c r="F34" t="n">
+      <c r="K34" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>44719.4</v>
+      </c>
+      <c r="M34" t="n">
         <v>45608.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
@@ -1251,13 +2049,37 @@
         <v>5604</v>
       </c>
       <c r="D35" t="n">
+        <v>5604</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
         <v>21132.5</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
+        <v>21132.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>23517.5</v>
       </c>
-      <c r="F35" t="n">
+      <c r="J35" t="n">
+        <v>23517.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>25037.6</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25037.6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1275,13 +2097,37 @@
         <v>1344</v>
       </c>
       <c r="D36" t="n">
+        <v>1344</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
         <v>4617</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
+        <v>4617</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>5073.1</v>
       </c>
-      <c r="F36" t="n">
+      <c r="J36" t="n">
+        <v>5073.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>5900.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5900.8</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1299,13 +2145,37 @@
         <v>850494</v>
       </c>
       <c r="D37" t="n">
+        <v>850494</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
         <v>3832403.5</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
+        <v>3832403.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>5422607.5</v>
       </c>
-      <c r="F37" t="n">
+      <c r="J37" t="n">
+        <v>5422607.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>5327749.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5327749.5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1320,16 +2190,40 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>6194</v>
+      </c>
+      <c r="D38" t="n">
         <v>6107</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21770.4</v>
+      </c>
+      <c r="G38" t="n">
         <v>21714.4</v>
       </c>
-      <c r="E38" t="n">
+      <c r="H38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>19816.4</v>
+      </c>
+      <c r="J38" t="n">
         <v>19715.2</v>
       </c>
-      <c r="F38" t="n">
+      <c r="K38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L38" t="n">
         <v>19922.1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19922.1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1347,13 +2241,37 @@
         <v>1265</v>
       </c>
       <c r="D39" t="n">
+        <v>1265</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
         <v>5524</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
+        <v>5524</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>5847.8</v>
       </c>
-      <c r="F39" t="n">
+      <c r="J39" t="n">
+        <v>5847.8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>6013</v>
+      </c>
+      <c r="M39" t="n">
+        <v>6013</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1371,13 +2289,37 @@
         <v>4406</v>
       </c>
       <c r="D40" t="n">
+        <v>4406</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
         <v>16669</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
+        <v>16669</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>18990.1</v>
       </c>
-      <c r="F40" t="n">
+      <c r="J40" t="n">
+        <v>18990.1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>21819.9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>21819.9</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1395,13 +2337,37 @@
         <v>210</v>
       </c>
       <c r="D41" t="n">
+        <v>210</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
         <v>747.3</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
+        <v>747.3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>972.3</v>
       </c>
-      <c r="F41" t="n">
+      <c r="J41" t="n">
+        <v>972.3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1352.6</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1352.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1419,13 +2385,37 @@
         <v>-523</v>
       </c>
       <c r="D42" t="n">
+        <v>-523</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
         <v>82.7</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>14829.6</v>
       </c>
-      <c r="F42" t="n">
+      <c r="J42" t="n">
+        <v>14829.6</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>25291.6</v>
+      </c>
+      <c r="M42" t="n">
+        <v>25291.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1443,13 +2433,37 @@
         <v>675</v>
       </c>
       <c r="D43" t="n">
+        <v>675</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
         <v>2274.3</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
+        <v>2274.3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>2417.5</v>
       </c>
-      <c r="F43" t="n">
+      <c r="J43" t="n">
+        <v>2417.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>2694</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2694</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1464,16 +2478,40 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>19019</v>
+      </c>
+      <c r="D44" t="n">
         <v>18359</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>41655.9</v>
+      </c>
+      <c r="G44" t="n">
         <v>41243</v>
       </c>
-      <c r="E44" t="n">
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>26985.4</v>
+      </c>
+      <c r="J44" t="n">
         <v>26789.7</v>
       </c>
-      <c r="F44" t="n">
+      <c r="K44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L44" t="n">
         <v>27554.5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>27554.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1488,16 +2526,40 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D45" t="n">
         <v>1019</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3470.8</v>
+      </c>
+      <c r="G45" t="n">
         <v>3474.3</v>
       </c>
-      <c r="E45" t="n">
+      <c r="H45" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3736.8</v>
+      </c>
+      <c r="J45" t="n">
         <v>3735.5</v>
       </c>
-      <c r="F45" t="n">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3886.5</v>
+      </c>
+      <c r="M45" t="n">
         <v>3891.1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="46">
@@ -1515,13 +2577,37 @@
         <v>1401</v>
       </c>
       <c r="D46" t="n">
+        <v>1401</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
         <v>5719.5</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
+        <v>5719.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>6499.5</v>
       </c>
-      <c r="F46" t="n">
+      <c r="J46" t="n">
+        <v>6499.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>7120</v>
+      </c>
+      <c r="M46" t="n">
+        <v>7120</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1536,16 +2622,40 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>746</v>
+      </c>
+      <c r="D47" t="n">
         <v>742</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3259</v>
+      </c>
+      <c r="G47" t="n">
         <v>3244.5</v>
       </c>
-      <c r="E47" t="n">
+      <c r="H47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4554.5</v>
+      </c>
+      <c r="J47" t="n">
         <v>4495.9</v>
       </c>
-      <c r="F47" t="n">
+      <c r="K47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5798.5</v>
+      </c>
+      <c r="M47" t="n">
         <v>5694.8</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="48">
@@ -1563,10 +2673,28 @@
         <v>13</v>
       </c>
       <c r="D48" t="n">
+        <v>13</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
         <v>131</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
+        <v>131</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>454</v>
+      </c>
+      <c r="J48" t="n">
+        <v>454</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1581,16 +2709,40 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>531</v>
+      </c>
+      <c r="D49" t="n">
         <v>516</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1805.1</v>
+      </c>
+      <c r="G49" t="n">
         <v>1760.9</v>
       </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2301.7</v>
+      </c>
+      <c r="J49" t="n">
         <v>2249.2</v>
       </c>
-      <c r="F49" t="n">
+      <c r="K49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>2678.5</v>
+      </c>
+      <c r="M49" t="n">
         <v>2685.3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="50">
@@ -1608,13 +2760,37 @@
         <v>4015</v>
       </c>
       <c r="D50" t="n">
+        <v>4015</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
         <v>16524.3</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
+        <v>16524.3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>31390.1</v>
       </c>
-      <c r="F50" t="n">
+      <c r="J50" t="n">
+        <v>31390.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
         <v>49657.5</v>
+      </c>
+      <c r="M50" t="n">
+        <v>49657.5</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1632,13 +2808,37 @@
         <v>122</v>
       </c>
       <c r="D51" t="n">
+        <v>122</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
         <v>379.5</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
+        <v>379.5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>441.7</v>
       </c>
-      <c r="F51" t="n">
+      <c r="J51" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
         <v>581.3</v>
+      </c>
+      <c r="M51" t="n">
+        <v>581.3</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1656,13 +2856,37 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
         <v>16.6</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>88.3</v>
       </c>
-      <c r="F52" t="n">
+      <c r="J52" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>229.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1680,13 +2904,37 @@
         <v>14211</v>
       </c>
       <c r="D53" t="n">
+        <v>14211</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
         <v>56417.8</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
+        <v>56417.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>67968.8</v>
       </c>
-      <c r="F53" t="n">
+      <c r="J53" t="n">
+        <v>67968.8</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>78474.8</v>
+      </c>
+      <c r="M53" t="n">
+        <v>78474.8</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1701,16 +2949,40 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>1804</v>
+      </c>
+      <c r="D54" t="n">
         <v>1792</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7641.5</v>
+      </c>
+      <c r="G54" t="n">
         <v>7617.8</v>
       </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>12300.9</v>
+      </c>
+      <c r="J54" t="n">
         <v>12306.4</v>
       </c>
-      <c r="F54" t="n">
+      <c r="K54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>15192.5</v>
+      </c>
+      <c r="M54" t="n">
         <v>15132.3</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="55">
@@ -1728,13 +3000,37 @@
         <v>1213</v>
       </c>
       <c r="D55" t="n">
+        <v>1213</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
         <v>3751.4</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
+        <v>3751.4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
         <v>5370.1</v>
       </c>
-      <c r="F55" t="n">
+      <c r="J55" t="n">
+        <v>5370.1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
         <v>6603.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>6603.2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1752,13 +3048,37 @@
         <v>1590</v>
       </c>
       <c r="D56" t="n">
+        <v>1590</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
         <v>6602.2</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
+        <v>6602.2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
         <v>9331.700000000001</v>
       </c>
-      <c r="F56" t="n">
+      <c r="J56" t="n">
+        <v>9331.700000000001</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
         <v>12279.5</v>
+      </c>
+      <c r="M56" t="n">
+        <v>12279.5</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1773,16 +3093,40 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>5918</v>
+      </c>
+      <c r="D57" t="n">
         <v>5765</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F57" t="n">
+        <v>23854.4</v>
+      </c>
+      <c r="G57" t="n">
         <v>23035.3</v>
       </c>
-      <c r="E57" t="n">
+      <c r="H57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I57" t="n">
+        <v>21792.2</v>
+      </c>
+      <c r="J57" t="n">
         <v>21193.5</v>
       </c>
-      <c r="F57" t="n">
+      <c r="K57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L57" t="n">
+        <v>23102.8</v>
+      </c>
+      <c r="M57" t="n">
         <v>22422.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1800,13 +3144,37 @@
         <v>3902</v>
       </c>
       <c r="D58" t="n">
+        <v>3902</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>14956.6</v>
+      </c>
+      <c r="G58" t="n">
         <v>14993.6</v>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>20358</v>
+      </c>
+      <c r="J58" t="n">
         <v>20241</v>
       </c>
-      <c r="F58" t="n">
+      <c r="K58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L58" t="n">
+        <v>23869.4</v>
+      </c>
+      <c r="M58" t="n">
         <v>23704.1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="59">
@@ -1824,13 +3192,37 @@
         <v>9415</v>
       </c>
       <c r="D59" t="n">
+        <v>9415</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
         <v>35619.5</v>
       </c>
-      <c r="E59" t="n">
+      <c r="G59" t="n">
+        <v>35619.5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>24566.4</v>
       </c>
-      <c r="F59" t="n">
+      <c r="J59" t="n">
+        <v>24566.4</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
         <v>22576.3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>22576.3</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1848,13 +3240,37 @@
         <v>1803</v>
       </c>
       <c r="D60" t="n">
+        <v>1803</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
         <v>11679.8</v>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
+        <v>11679.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>13870.9</v>
       </c>
-      <c r="F60" t="n">
+      <c r="J60" t="n">
+        <v>13870.9</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
         <v>15782.4</v>
+      </c>
+      <c r="M60" t="n">
+        <v>15782.4</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1872,13 +3288,37 @@
         <v>1380</v>
       </c>
       <c r="D61" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
         <v>1671</v>
       </c>
-      <c r="E61" t="n">
+      <c r="G61" t="n">
+        <v>1671</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>2610.4</v>
       </c>
-      <c r="F61" t="n">
+      <c r="J61" t="n">
+        <v>2610.4</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
         <v>4783.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>4783.5</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1896,13 +3336,37 @@
         <v>3182</v>
       </c>
       <c r="D62" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
         <v>11608</v>
       </c>
-      <c r="E62" t="n">
+      <c r="G62" t="n">
+        <v>11608</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
         <v>8554.9</v>
       </c>
-      <c r="F62" t="n">
+      <c r="J62" t="n">
+        <v>8554.9</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
         <v>9030.200000000001</v>
+      </c>
+      <c r="M62" t="n">
+        <v>9030.200000000001</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1920,13 +3384,37 @@
         <v>576</v>
       </c>
       <c r="D63" t="n">
+        <v>576</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
         <v>2314.2</v>
       </c>
-      <c r="E63" t="n">
+      <c r="G63" t="n">
+        <v>2314.2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>2836.9</v>
       </c>
-      <c r="F63" t="n">
+      <c r="J63" t="n">
+        <v>2836.9</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
         <v>3126.8</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3126.8</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1944,13 +3432,37 @@
         <v>1401</v>
       </c>
       <c r="D64" t="n">
+        <v>1401</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
         <v>3904.6</v>
       </c>
-      <c r="E64" t="n">
+      <c r="G64" t="n">
+        <v>3904.6</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
         <v>4430.3</v>
       </c>
-      <c r="F64" t="n">
+      <c r="J64" t="n">
+        <v>4430.3</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
         <v>4902.9</v>
+      </c>
+      <c r="M64" t="n">
+        <v>4902.9</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1968,13 +3480,37 @@
         <v>-187</v>
       </c>
       <c r="D65" t="n">
+        <v>-187</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
         <v>-604.5</v>
       </c>
-      <c r="E65" t="n">
+      <c r="G65" t="n">
+        <v>-604.5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>844.5</v>
       </c>
-      <c r="F65" t="n">
+      <c r="J65" t="n">
+        <v>844.5</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
         <v>2398.8</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2398.8</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1989,16 +3525,40 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>9088</v>
+      </c>
+      <c r="D66" t="n">
         <v>9114</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F66" t="n">
+        <v>37234.8</v>
+      </c>
+      <c r="G66" t="n">
         <v>37203.2</v>
       </c>
-      <c r="E66" t="n">
+      <c r="H66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>42459</v>
+      </c>
+      <c r="J66" t="n">
         <v>42456.2</v>
       </c>
-      <c r="F66" t="n">
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>46500.8</v>
+      </c>
+      <c r="M66" t="n">
         <v>46498.1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2013,16 +3573,40 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>10136</v>
+      </c>
+      <c r="D67" t="n">
         <v>10170</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>42647.9</v>
+      </c>
+      <c r="G67" t="n">
         <v>42629.6</v>
       </c>
-      <c r="E67" t="n">
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>55103.9</v>
+      </c>
+      <c r="J67" t="n">
         <v>54900.1</v>
       </c>
-      <c r="F67" t="n">
+      <c r="K67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L67" t="n">
+        <v>62256.4</v>
+      </c>
+      <c r="M67" t="n">
         <v>61729.9</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="68">
@@ -2040,13 +3624,37 @@
         <v>563</v>
       </c>
       <c r="D68" t="n">
+        <v>563</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
         <v>1961</v>
       </c>
-      <c r="E68" t="n">
+      <c r="G68" t="n">
+        <v>1961</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>2539.8</v>
       </c>
-      <c r="F68" t="n">
+      <c r="J68" t="n">
+        <v>2539.8</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
         <v>2681</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2681</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2064,13 +3672,37 @@
         <v>502</v>
       </c>
       <c r="D69" t="n">
+        <v>502</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
         <v>1879.9</v>
       </c>
-      <c r="E69" t="n">
+      <c r="G69" t="n">
+        <v>1879.9</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>2386.1</v>
       </c>
-      <c r="F69" t="n">
+      <c r="J69" t="n">
+        <v>2386.1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
         <v>3072.4</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3072.4</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2088,13 +3720,37 @@
         <v>19122</v>
       </c>
       <c r="D70" t="n">
+        <v>19122</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
         <v>97617.5</v>
       </c>
-      <c r="E70" t="n">
+      <c r="G70" t="n">
+        <v>97617.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
         <v>134651.3</v>
       </c>
-      <c r="F70" t="n">
+      <c r="J70" t="n">
+        <v>134651.3</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
         <v>148583.9</v>
+      </c>
+      <c r="M70" t="n">
+        <v>148583.9</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2109,16 +3765,40 @@
         </is>
       </c>
       <c r="C71" t="n">
+        <v>6435</v>
+      </c>
+      <c r="D71" t="n">
         <v>6159</v>
       </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>22640.4</v>
+      </c>
+      <c r="G71" t="n">
         <v>22401.3</v>
       </c>
-      <c r="E71" t="n">
+      <c r="H71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>20996.1</v>
+      </c>
+      <c r="J71" t="n">
         <v>20758.2</v>
       </c>
-      <c r="F71" t="n">
+      <c r="K71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>20937.6</v>
+      </c>
+      <c r="M71" t="n">
         <v>20808.3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="72">
@@ -2133,2650 +3813,5236 @@
         </is>
       </c>
       <c r="C72" t="n">
+        <v>5307</v>
+      </c>
+      <c r="D72" t="n">
         <v>5290</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F72" t="n">
+        <v>19164.7</v>
+      </c>
+      <c r="G72" t="n">
         <v>19147.2</v>
       </c>
-      <c r="E72" t="n">
+      <c r="H72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>20300.4</v>
+      </c>
+      <c r="J72" t="n">
         <v>20290.9</v>
       </c>
-      <c r="F72" t="n">
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>21507.9</v>
+      </c>
+      <c r="M72" t="n">
         <v>21493</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>017800</t>
+          <t>017960</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>현대엘리베이터</t>
+          <t>한국카본</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>578</v>
+        <v>470</v>
+      </c>
+      <c r="D73" t="n">
+        <v>470</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1798.3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1798.3</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1964.3</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1964.3</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1946.5</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1946.5</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>017960</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>한국카본</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>470</v>
+        <v>2349</v>
       </c>
       <c r="D74" t="n">
-        <v>1798.3</v>
+        <v>2330</v>
       </c>
       <c r="E74" t="n">
-        <v>1964.3</v>
+        <v>0.8</v>
       </c>
       <c r="F74" t="n">
-        <v>1946.5</v>
+        <v>8342.200000000001</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8358.200000000001</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>10645.7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>10647.7</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>11844.7</v>
+      </c>
+      <c r="M74" t="n">
+        <v>11831.3</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>018880</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>한온시스템</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2330</v>
+        <v>1095</v>
       </c>
       <c r="D75" t="n">
-        <v>8358.200000000001</v>
+        <v>1095</v>
       </c>
       <c r="E75" t="n">
-        <v>10647.7</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>11831.3</v>
+        <v>4279.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4279.2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>4997.4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4997.4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5789.7</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5789.7</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>018880</t>
+          <t>021240</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한온시스템</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1095</v>
+        <v>2682</v>
       </c>
       <c r="D76" t="n">
-        <v>4279.2</v>
+        <v>2682</v>
       </c>
       <c r="E76" t="n">
-        <v>4997.4</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>5789.7</v>
+        <v>10136.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>10136.5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>11688.8</v>
+      </c>
+      <c r="J76" t="n">
+        <v>11688.8</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>12472.5</v>
+      </c>
+      <c r="M76" t="n">
+        <v>12472.5</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>021240</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2682</v>
+        <v>1104</v>
       </c>
       <c r="D77" t="n">
-        <v>10136.5</v>
+        <v>1104</v>
       </c>
       <c r="E77" t="n">
-        <v>11688.8</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>12472.5</v>
+        <v>8034.7</v>
+      </c>
+      <c r="G77" t="n">
+        <v>8034.7</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>8618.5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>8618.5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>9113.799999999999</v>
+      </c>
+      <c r="M77" t="n">
+        <v>9113.799999999999</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>024110</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1104</v>
+        <v>9431</v>
       </c>
       <c r="D78" t="n">
-        <v>8034.7</v>
+        <v>9437</v>
       </c>
       <c r="E78" t="n">
-        <v>8618.5</v>
+        <v>-0.1</v>
       </c>
       <c r="F78" t="n">
-        <v>9113.799999999999</v>
+        <v>37016.5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>37054.8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>39830.2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>39842.8</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>42552.4</v>
+      </c>
+      <c r="M78" t="n">
+        <v>42556.9</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>024110</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9437</v>
+        <v>2179</v>
       </c>
       <c r="D79" t="n">
-        <v>37054.8</v>
+        <v>2179</v>
       </c>
       <c r="E79" t="n">
-        <v>39842.8</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>42556.9</v>
+        <v>8839.6</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8839.6</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>10306.5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>10306.5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>11529.4</v>
+      </c>
+      <c r="M79" t="n">
+        <v>11529.4</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>028260</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2179</v>
+        <v>8652</v>
       </c>
       <c r="D80" t="n">
-        <v>8839.6</v>
+        <v>8652</v>
       </c>
       <c r="E80" t="n">
-        <v>10306.5</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>11529.4</v>
+        <v>36331.4</v>
+      </c>
+      <c r="G80" t="n">
+        <v>36331.4</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>41180.2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>41180.2</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>45141.3</v>
+      </c>
+      <c r="M80" t="n">
+        <v>45141.3</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>028260</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8652</v>
+        <v>1503</v>
       </c>
       <c r="D81" t="n">
-        <v>36331.4</v>
+        <v>1495</v>
       </c>
       <c r="E81" t="n">
-        <v>41180.2</v>
+        <v>0.5</v>
       </c>
       <c r="F81" t="n">
-        <v>45141.3</v>
+        <v>5854.9</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5839.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6091.5</v>
+      </c>
+      <c r="J81" t="n">
+        <v>6010.8</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6368.1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>6274.3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>029780</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성카드</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1495</v>
+        <v>2131</v>
       </c>
       <c r="D82" t="n">
-        <v>5839.5</v>
+        <v>2131</v>
       </c>
       <c r="E82" t="n">
-        <v>6010.8</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>6274.3</v>
+        <v>8470</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8470</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>9226.700000000001</v>
+      </c>
+      <c r="J82" t="n">
+        <v>9226.700000000001</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>9336.700000000001</v>
+      </c>
+      <c r="M82" t="n">
+        <v>9336.700000000001</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>029780</t>
+          <t>030000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2131</v>
+        <v>942</v>
       </c>
       <c r="D83" t="n">
-        <v>8470</v>
+        <v>942</v>
       </c>
       <c r="E83" t="n">
-        <v>9226.700000000001</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>9336.700000000001</v>
+        <v>3339.9</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3339.9</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3636.7</v>
+      </c>
+      <c r="J83" t="n">
+        <v>3636.7</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>3692.6</v>
+      </c>
+      <c r="M83" t="n">
+        <v>3692.6</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>030000</t>
+          <t>030200</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>942</v>
+        <v>6081</v>
       </c>
       <c r="D84" t="n">
-        <v>3339.9</v>
+        <v>6133</v>
       </c>
       <c r="E84" t="n">
-        <v>3636.7</v>
+        <v>-0.8</v>
       </c>
       <c r="F84" t="n">
-        <v>3692.6</v>
+        <v>20653.3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>20721.3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I84" t="n">
+        <v>22502.9</v>
+      </c>
+      <c r="J84" t="n">
+        <v>22526.8</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>23821.8</v>
+      </c>
+      <c r="M84" t="n">
+        <v>23847.4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>030200</t>
+          <t>032640</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6133</v>
+        <v>3062</v>
       </c>
       <c r="D85" t="n">
-        <v>20721.3</v>
+        <v>3062</v>
       </c>
       <c r="E85" t="n">
-        <v>22526.8</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>23847.4</v>
+        <v>11111.1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>11111.1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>11959</v>
+      </c>
+      <c r="J85" t="n">
+        <v>11959</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>12715.1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>12715.1</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>032640</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3062</v>
+        <v>10237</v>
       </c>
       <c r="D86" t="n">
-        <v>11111.1</v>
+        <v>10237</v>
       </c>
       <c r="E86" t="n">
-        <v>11959</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>12715.1</v>
+        <v>33019.2</v>
+      </c>
+      <c r="G86" t="n">
+        <v>33019.2</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>52718.3</v>
+      </c>
+      <c r="J86" t="n">
+        <v>52718.3</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>33462</v>
+      </c>
+      <c r="M86" t="n">
+        <v>33462</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>033780</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10237</v>
+        <v>3866</v>
       </c>
       <c r="D87" t="n">
-        <v>33019.2</v>
+        <v>3843</v>
       </c>
       <c r="E87" t="n">
-        <v>52718.3</v>
+        <v>0.6</v>
       </c>
       <c r="F87" t="n">
-        <v>33462</v>
+        <v>15108.4</v>
+      </c>
+      <c r="G87" t="n">
+        <v>15067.6</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I87" t="n">
+        <v>16302.5</v>
+      </c>
+      <c r="J87" t="n">
+        <v>16299.9</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>17252.5</v>
+      </c>
+      <c r="M87" t="n">
+        <v>17227</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>033780</t>
+          <t>034020</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3843</v>
+        <v>2659</v>
       </c>
       <c r="D88" t="n">
-        <v>15067.6</v>
+        <v>2659</v>
       </c>
       <c r="E88" t="n">
-        <v>16299.9</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>17227</v>
+        <v>11195.5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>11195.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>16045.1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>16045.1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>21149.6</v>
+      </c>
+      <c r="M88" t="n">
+        <v>21149.6</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2659</v>
+        <v>-952</v>
       </c>
       <c r="D89" t="n">
-        <v>11195.5</v>
+        <v>-952</v>
       </c>
       <c r="E89" t="n">
-        <v>16045.1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>21149.6</v>
+        <v>11083.4</v>
+      </c>
+      <c r="G89" t="n">
+        <v>11083.4</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>15177.6</v>
+      </c>
+      <c r="J89" t="n">
+        <v>15177.6</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>17727.4</v>
+      </c>
+      <c r="M89" t="n">
+        <v>17727.4</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-952</v>
+        <v>498</v>
       </c>
       <c r="D90" t="n">
-        <v>11083.4</v>
+        <v>498</v>
       </c>
       <c r="E90" t="n">
-        <v>15177.6</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>17727.4</v>
+        <v>1856.2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1856.2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2235.1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2235.1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>2456</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2456</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>498</v>
+        <v>24551</v>
       </c>
       <c r="D91" t="n">
-        <v>1856.2</v>
+        <v>24551</v>
       </c>
       <c r="E91" t="n">
-        <v>2235.1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>2456</v>
+        <v>98678.39999999999</v>
+      </c>
+      <c r="G91" t="n">
+        <v>98678.39999999999</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>115192</v>
+      </c>
+      <c r="J91" t="n">
+        <v>115192</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>145506.2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>145506.2</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>035250</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>강원랜드</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>24551</v>
+        <v>489</v>
       </c>
       <c r="D92" t="n">
-        <v>98678.39999999999</v>
+        <v>489</v>
       </c>
       <c r="E92" t="n">
-        <v>115192</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>145506.2</v>
+        <v>2212.7</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2212.7</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>2287.4</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2287.4</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>2883.4</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2883.4</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>035250</t>
+          <t>035420</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>강원랜드</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>489</v>
+        <v>5693</v>
       </c>
       <c r="D93" t="n">
-        <v>2212.7</v>
+        <v>5693</v>
       </c>
       <c r="E93" t="n">
-        <v>2287.4</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>2883.4</v>
+        <v>23973.6</v>
+      </c>
+      <c r="G93" t="n">
+        <v>23970.7</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>27672</v>
+      </c>
+      <c r="J93" t="n">
+        <v>27661</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>31358.5</v>
+      </c>
+      <c r="M93" t="n">
+        <v>31280.1</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5693</v>
+        <v>2229</v>
       </c>
       <c r="D94" t="n">
-        <v>23970.7</v>
+        <v>2226</v>
       </c>
       <c r="E94" t="n">
-        <v>27661</v>
+        <v>0.1</v>
       </c>
       <c r="F94" t="n">
-        <v>31280.1</v>
+        <v>9387.299999999999</v>
+      </c>
+      <c r="G94" t="n">
+        <v>9376.9</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>10959.7</v>
+      </c>
+      <c r="J94" t="n">
+        <v>10913.1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L94" t="n">
+        <v>12671.7</v>
+      </c>
+      <c r="M94" t="n">
+        <v>12611.7</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>036460</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2226</v>
+        <v>4305</v>
       </c>
       <c r="D95" t="n">
-        <v>9376.9</v>
+        <v>4305</v>
       </c>
       <c r="E95" t="n">
-        <v>10913.1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>12611.7</v>
+        <v>22650.5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>22650.5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>21915.1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>21915.1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>22082.9</v>
+      </c>
+      <c r="M95" t="n">
+        <v>22082.9</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>036460</t>
+          <t>036570</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4305</v>
+        <v>1270</v>
       </c>
       <c r="D96" t="n">
-        <v>22650.5</v>
+        <v>1266</v>
       </c>
       <c r="E96" t="n">
-        <v>21915.1</v>
+        <v>0.3</v>
       </c>
       <c r="F96" t="n">
-        <v>22082.9</v>
+        <v>5026.8</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5021.2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>5876.9</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5888.8</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L96" t="n">
+        <v>5924.6</v>
+      </c>
+      <c r="M96" t="n">
+        <v>6011.7</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>036570</t>
+          <t>039490</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>키움증권</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1266</v>
+        <v>6375</v>
       </c>
       <c r="D97" t="n">
-        <v>5021.2</v>
+        <v>6257</v>
       </c>
       <c r="E97" t="n">
-        <v>5888.8</v>
+        <v>1.9</v>
       </c>
       <c r="F97" t="n">
-        <v>6011.7</v>
+        <v>21921.9</v>
+      </c>
+      <c r="G97" t="n">
+        <v>21724.8</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I97" t="n">
+        <v>20426.9</v>
+      </c>
+      <c r="J97" t="n">
+        <v>20349.5</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L97" t="n">
+        <v>20600.4</v>
+      </c>
+      <c r="M97" t="n">
+        <v>20600.4</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>039490</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>키움증권</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6257</v>
+        <v>5252</v>
       </c>
       <c r="D98" t="n">
-        <v>21724.8</v>
+        <v>5217</v>
       </c>
       <c r="E98" t="n">
-        <v>20349.5</v>
+        <v>0.7</v>
       </c>
       <c r="F98" t="n">
-        <v>20600.4</v>
+        <v>19011.6</v>
+      </c>
+      <c r="G98" t="n">
+        <v>18987.4</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>23489.7</v>
+      </c>
+      <c r="J98" t="n">
+        <v>23507.6</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>27891.2</v>
+      </c>
+      <c r="M98" t="n">
+        <v>27892.4</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5217</v>
+        <v>1103</v>
       </c>
       <c r="D99" t="n">
-        <v>18987.4</v>
+        <v>1103</v>
       </c>
       <c r="E99" t="n">
-        <v>23507.6</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>27892.4</v>
+        <v>3694</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3694</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5719</v>
+      </c>
+      <c r="J99" t="n">
+        <v>5719</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>7297</v>
+      </c>
+      <c r="M99" t="n">
+        <v>7297</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>047040</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1103</v>
+        <v>1508</v>
       </c>
       <c r="D100" t="n">
-        <v>3694</v>
+        <v>1508</v>
       </c>
       <c r="E100" t="n">
-        <v>5719</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>7297</v>
+        <v>7131.3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>6988.2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" t="n">
+        <v>7346.9</v>
+      </c>
+      <c r="J100" t="n">
+        <v>7254.8</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L100" t="n">
+        <v>8381.4</v>
+      </c>
+      <c r="M100" t="n">
+        <v>8244.9</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>047050</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1508</v>
+        <v>3517</v>
       </c>
       <c r="D101" t="n">
-        <v>6988.2</v>
+        <v>3517</v>
       </c>
       <c r="E101" t="n">
-        <v>7254.8</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>8244.9</v>
+        <v>13940.8</v>
+      </c>
+      <c r="G101" t="n">
+        <v>13940.8</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>15092.4</v>
+      </c>
+      <c r="J101" t="n">
+        <v>15092.4</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>15771.5</v>
+      </c>
+      <c r="M101" t="n">
+        <v>15771.5</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>047050</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3517</v>
+        <v>1002</v>
       </c>
       <c r="D102" t="n">
-        <v>13940.8</v>
+        <v>1002</v>
       </c>
       <c r="E102" t="n">
-        <v>15092.4</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>15771.5</v>
+        <v>4679.8</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4679.8</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6650.4</v>
+      </c>
+      <c r="J102" t="n">
+        <v>6650.4</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>8075.1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>8075.1</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>051600</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>한전KPS</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1002</v>
+        <v>623</v>
       </c>
       <c r="D103" t="n">
-        <v>4679.8</v>
+        <v>623</v>
       </c>
       <c r="E103" t="n">
-        <v>6650.4</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>8075.1</v>
+        <v>1899.6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1899.6</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2004</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2004</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>2075.3</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2075.3</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>051600</t>
+          <t>051900</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한전KPS</t>
+          <t>LG생활건강</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>623</v>
+        <v>751</v>
       </c>
       <c r="D104" t="n">
-        <v>1899.6</v>
+        <v>751</v>
       </c>
       <c r="E104" t="n">
-        <v>2004</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>2075.3</v>
+        <v>3421.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3421.5</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>3992.5</v>
+      </c>
+      <c r="J104" t="n">
+        <v>3992.5</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>4283.7</v>
+      </c>
+      <c r="M104" t="n">
+        <v>4283.7</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>051900</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LG생활건강</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>751</v>
+        <v>3808</v>
       </c>
       <c r="D105" t="n">
-        <v>3421.5</v>
+        <v>3808</v>
       </c>
       <c r="E105" t="n">
-        <v>3992.5</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>4283.7</v>
+        <v>15532.2</v>
+      </c>
+      <c r="G105" t="n">
+        <v>15532.2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>42457.5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>42457.5</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>59569.1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>59569.1</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3808</v>
+        <v>141</v>
       </c>
       <c r="D106" t="n">
-        <v>15532.2</v>
+        <v>141</v>
       </c>
       <c r="E106" t="n">
-        <v>42457.5</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>59569.1</v>
+        <v>737.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>992.8</v>
+      </c>
+      <c r="J106" t="n">
+        <v>992.8</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1641.4</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1641.4</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>055550</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>141</v>
+        <v>22349</v>
       </c>
       <c r="D107" t="n">
-        <v>737.5</v>
+        <v>22193</v>
       </c>
       <c r="E107" t="n">
-        <v>992.8</v>
+        <v>0.7</v>
       </c>
       <c r="F107" t="n">
-        <v>1641.4</v>
+        <v>76926.5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>76844.60000000001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>81714.5</v>
+      </c>
+      <c r="J107" t="n">
+        <v>81715.8</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>85120.2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>85049.5</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>055550</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>22193</v>
+        <v>603</v>
       </c>
       <c r="D108" t="n">
-        <v>76844.60000000001</v>
+        <v>603</v>
       </c>
       <c r="E108" t="n">
-        <v>81715.8</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>85049.5</v>
+        <v>2487.6</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2487.6</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3312.3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>3312.3</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="M108" t="n">
+        <v>4295.2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>064350</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>현대로템</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>603</v>
+        <v>2768</v>
       </c>
       <c r="D109" t="n">
-        <v>2487.6</v>
+        <v>2768</v>
       </c>
       <c r="E109" t="n">
-        <v>3312.3</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>4295.2</v>
+        <v>11805.3</v>
+      </c>
+      <c r="G109" t="n">
+        <v>11805.3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>15557.9</v>
+      </c>
+      <c r="J109" t="n">
+        <v>15557.9</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>18626.1</v>
+      </c>
+      <c r="M109" t="n">
+        <v>18626.1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>064350</t>
+          <t>064400</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>현대로템</t>
+          <t>LG씨엔에스</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2768</v>
+        <v>1434</v>
       </c>
       <c r="D110" t="n">
-        <v>11805.3</v>
+        <v>1434</v>
       </c>
       <c r="E110" t="n">
-        <v>15557.9</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>18626.1</v>
+        <v>6162.8</v>
+      </c>
+      <c r="G110" t="n">
+        <v>6162.8</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>7022.6</v>
+      </c>
+      <c r="J110" t="n">
+        <v>7022.6</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>7902.2</v>
+      </c>
+      <c r="M110" t="n">
+        <v>7902.2</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>064400</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LG씨엔에스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1434</v>
+        <v>10580</v>
       </c>
       <c r="D111" t="n">
-        <v>6162.8</v>
+        <v>10580</v>
       </c>
       <c r="E111" t="n">
-        <v>7022.6</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>7902.2</v>
+        <v>42384.2</v>
+      </c>
+      <c r="G111" t="n">
+        <v>42384.2</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>45628.6</v>
+      </c>
+      <c r="J111" t="n">
+        <v>45628.6</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>55174.1</v>
+      </c>
+      <c r="M111" t="n">
+        <v>55174.1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10580</v>
+        <v>502</v>
       </c>
       <c r="D112" t="n">
-        <v>42384.2</v>
+        <v>502</v>
       </c>
       <c r="E112" t="n">
-        <v>45628.6</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>55174.1</v>
+        <v>2517.9</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2517.9</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2311</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2311</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>3257.2</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3257.2</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>068270</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>502</v>
+        <v>4017</v>
       </c>
       <c r="D113" t="n">
-        <v>2517.9</v>
+        <v>4017</v>
       </c>
       <c r="E113" t="n">
-        <v>2311</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>3257.2</v>
+        <v>17804.2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>17705.6</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I113" t="n">
+        <v>21031.7</v>
+      </c>
+      <c r="J113" t="n">
+        <v>21003.2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L113" t="n">
+        <v>24695.9</v>
+      </c>
+      <c r="M113" t="n">
+        <v>24637.2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>068270</t>
+          <t>069260</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>TKG휴켐스</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4017</v>
+        <v>269</v>
       </c>
       <c r="D114" t="n">
-        <v>17705.6</v>
+        <v>269</v>
       </c>
       <c r="E114" t="n">
-        <v>21003.2</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>24637.2</v>
+        <v>868.5</v>
+      </c>
+      <c r="G114" t="n">
+        <v>868.5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>869</v>
+      </c>
+      <c r="J114" t="n">
+        <v>869</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>699</v>
+      </c>
+      <c r="M114" t="n">
+        <v>699</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>069260</t>
+          <t>069620</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TKG휴켐스</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>269</v>
+        <v>544</v>
       </c>
       <c r="D115" t="n">
-        <v>868.5</v>
+        <v>544</v>
       </c>
       <c r="E115" t="n">
-        <v>869</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>699</v>
+        <v>2065.2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2065.2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>2402.6</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2402.6</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>3619.6</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3619.6</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>069620</t>
+          <t>069960</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>현대백화점</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>544</v>
+        <v>858</v>
       </c>
       <c r="D116" t="n">
-        <v>2065.2</v>
+        <v>858</v>
       </c>
       <c r="E116" t="n">
-        <v>2402.6</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>3619.6</v>
+        <v>4359.2</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4359.2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5268.4</v>
+      </c>
+      <c r="J116" t="n">
+        <v>5268.4</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>5649.9</v>
+      </c>
+      <c r="M116" t="n">
+        <v>5649.9</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>069960</t>
+          <t>071050</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>현대백화점</t>
+          <t>한국금융지주</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>858</v>
+        <v>10415</v>
       </c>
       <c r="D117" t="n">
-        <v>4359.2</v>
+        <v>10145</v>
       </c>
       <c r="E117" t="n">
-        <v>5268.4</v>
+        <v>2.7</v>
       </c>
       <c r="F117" t="n">
-        <v>5649.9</v>
+        <v>35232.8</v>
+      </c>
+      <c r="G117" t="n">
+        <v>35060.4</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I117" t="n">
+        <v>32313.2</v>
+      </c>
+      <c r="J117" t="n">
+        <v>32190.9</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L117" t="n">
+        <v>32379.5</v>
+      </c>
+      <c r="M117" t="n">
+        <v>32379.5</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>071050</t>
+          <t>071320</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>한국금융지주</t>
+          <t>지역난방공사</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>10145</v>
+        <v>-246</v>
       </c>
       <c r="D118" t="n">
-        <v>35060.4</v>
+        <v>-246</v>
       </c>
       <c r="E118" t="n">
-        <v>32190.9</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>32379.5</v>
+        <v>4004</v>
+      </c>
+      <c r="G118" t="n">
+        <v>4004</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>3934</v>
+      </c>
+      <c r="J118" t="n">
+        <v>3934</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>4419.5</v>
+      </c>
+      <c r="M118" t="n">
+        <v>4419.5</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>071320</t>
+          <t>071970</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>지역난방공사</t>
+          <t>HD현대마린엔진</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-246</v>
+        <v>355</v>
       </c>
       <c r="D119" t="n">
-        <v>4004</v>
+        <v>355</v>
       </c>
       <c r="E119" t="n">
-        <v>3934</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>4419.5</v>
+        <v>1522.5</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1522.5</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2035.3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2035.3</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2477.5</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2477.5</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>071970</t>
+          <t>073240</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HD현대마린엔진</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>355</v>
+        <v>1455</v>
       </c>
       <c r="D120" t="n">
-        <v>1522.5</v>
+        <v>1455</v>
       </c>
       <c r="E120" t="n">
-        <v>2035.3</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>2477.5</v>
+        <v>5763.7</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5763.7</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>5993.2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>5993.2</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>6656.3</v>
+      </c>
+      <c r="M120" t="n">
+        <v>6656.3</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1455</v>
+        <v>11636</v>
       </c>
       <c r="D121" t="n">
-        <v>5763.7</v>
+        <v>11636</v>
       </c>
       <c r="E121" t="n">
-        <v>5993.2</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>6656.3</v>
+        <v>41969.8</v>
+      </c>
+      <c r="G121" t="n">
+        <v>41969.8</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>33273.2</v>
+      </c>
+      <c r="J121" t="n">
+        <v>33273.2</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>34176</v>
+      </c>
+      <c r="M121" t="n">
+        <v>34176</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>079550</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LIG디펜스앤에어로스페이스</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>11636</v>
+        <v>1049</v>
       </c>
       <c r="D122" t="n">
-        <v>41969.8</v>
+        <v>1049</v>
       </c>
       <c r="E122" t="n">
-        <v>33273.2</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>34176</v>
+        <v>4500.6</v>
+      </c>
+      <c r="G122" t="n">
+        <v>4500.6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>6182.2</v>
+      </c>
+      <c r="J122" t="n">
+        <v>6182.2</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>8117.6</v>
+      </c>
+      <c r="M122" t="n">
+        <v>8117.6</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>079550</t>
+          <t>081660</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LIG디펜스앤에어로스페이스</t>
+          <t>미스토홀딩스</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1049</v>
+        <v>2121</v>
       </c>
       <c r="D123" t="n">
-        <v>4500.6</v>
+        <v>2121</v>
       </c>
       <c r="E123" t="n">
-        <v>6182.2</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>8117.6</v>
+        <v>5637.1</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5637.1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>6005.9</v>
+      </c>
+      <c r="J123" t="n">
+        <v>6005.9</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>6231.9</v>
+      </c>
+      <c r="M123" t="n">
+        <v>6231.9</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>081660</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>미스토홀딩스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2121</v>
+        <v>595</v>
       </c>
       <c r="D124" t="n">
-        <v>5637.1</v>
+        <v>595</v>
       </c>
       <c r="E124" t="n">
-        <v>6005.9</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>6231.9</v>
+        <v>2407.6</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2407.6</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>3687.6</v>
+      </c>
+      <c r="J124" t="n">
+        <v>3687.6</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>4521.6</v>
+      </c>
+      <c r="M124" t="n">
+        <v>4521.6</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>086280</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>현대글로비스</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>595</v>
+        <v>5168</v>
       </c>
       <c r="D125" t="n">
-        <v>2407.6</v>
+        <v>5218</v>
       </c>
       <c r="E125" t="n">
-        <v>3687.6</v>
+        <v>-1</v>
       </c>
       <c r="F125" t="n">
-        <v>4521.6</v>
+        <v>21752.8</v>
+      </c>
+      <c r="G125" t="n">
+        <v>21784.2</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I125" t="n">
+        <v>23346</v>
+      </c>
+      <c r="J125" t="n">
+        <v>23322.1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L125" t="n">
+        <v>24506.1</v>
+      </c>
+      <c r="M125" t="n">
+        <v>24482.1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>086280</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>현대글로비스</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>5218</v>
+        <v>16571</v>
       </c>
       <c r="D126" t="n">
-        <v>21784.2</v>
+        <v>16577</v>
       </c>
       <c r="E126" t="n">
-        <v>23322.1</v>
+        <v>-0</v>
       </c>
       <c r="F126" t="n">
-        <v>24482.1</v>
+        <v>60434.6</v>
+      </c>
+      <c r="G126" t="n">
+        <v>60367.7</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I126" t="n">
+        <v>63113.2</v>
+      </c>
+      <c r="J126" t="n">
+        <v>63117.4</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>65920.60000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>65992.2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>088350</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>16577</v>
-      </c>
-      <c r="D127" t="n">
-        <v>60367.7</v>
-      </c>
-      <c r="E127" t="n">
-        <v>63117.4</v>
+          <t>한화생명</t>
+        </is>
       </c>
       <c r="F127" t="n">
-        <v>65992.2</v>
+        <v>8132.5</v>
+      </c>
+      <c r="G127" t="n">
+        <v>8132.5</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>9055.200000000001</v>
+      </c>
+      <c r="J127" t="n">
+        <v>9055.200000000001</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>8905.200000000001</v>
+      </c>
+      <c r="M127" t="n">
+        <v>8905.200000000001</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>088350</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>한화생명</t>
-        </is>
+          <t>아모레퍼시픽</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>984</v>
       </c>
       <c r="D128" t="n">
-        <v>8132.5</v>
+        <v>984</v>
       </c>
       <c r="E128" t="n">
-        <v>9055.200000000001</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>8905.200000000001</v>
+        <v>4637.6</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4637.6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>5278.1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>5278.1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>5882.1</v>
+      </c>
+      <c r="M128" t="n">
+        <v>5882.1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>984</v>
+        <v>153</v>
       </c>
       <c r="D129" t="n">
-        <v>4637.6</v>
+        <v>153</v>
       </c>
       <c r="E129" t="n">
-        <v>5278.1</v>
-      </c>
-      <c r="F129" t="n">
-        <v>5882.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>153</v>
+        <v>14123</v>
+      </c>
+      <c r="D130" t="n">
+        <v>13980</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>50950.2</v>
+      </c>
+      <c r="G130" t="n">
+        <v>50950.2</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>31187.9</v>
+      </c>
+      <c r="J130" t="n">
+        <v>31187.9</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>36712.4</v>
+      </c>
+      <c r="M130" t="n">
+        <v>36712.4</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>097950</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>CJ제일제당</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>13980</v>
+        <v>2773</v>
       </c>
       <c r="D131" t="n">
-        <v>50950.2</v>
+        <v>2787</v>
       </c>
       <c r="E131" t="n">
-        <v>31187.9</v>
+        <v>-0.5</v>
       </c>
       <c r="F131" t="n">
-        <v>36712.4</v>
+        <v>12855.1</v>
+      </c>
+      <c r="G131" t="n">
+        <v>12921.1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I131" t="n">
+        <v>14545.4</v>
+      </c>
+      <c r="J131" t="n">
+        <v>14542.5</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>15955.2</v>
+      </c>
+      <c r="M131" t="n">
+        <v>15806</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>097950</t>
+          <t>103140</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CJ제일제당</t>
+          <t>풍산</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2787</v>
+        <v>831</v>
       </c>
       <c r="D132" t="n">
-        <v>12921.1</v>
+        <v>831</v>
       </c>
       <c r="E132" t="n">
-        <v>14542.5</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>15806</v>
+        <v>3617.8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3617.8</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>3606.6</v>
+      </c>
+      <c r="J132" t="n">
+        <v>3606.6</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>3982.7</v>
+      </c>
+      <c r="M132" t="n">
+        <v>3982.7</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>103140</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>풍산</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>831</v>
+        <v>25959</v>
       </c>
       <c r="D133" t="n">
-        <v>3617.8</v>
+        <v>25740</v>
       </c>
       <c r="E133" t="n">
-        <v>3606.6</v>
+        <v>0.9</v>
       </c>
       <c r="F133" t="n">
-        <v>3982.7</v>
+        <v>92995.5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>92733.10000000001</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I133" t="n">
+        <v>94516.7</v>
+      </c>
+      <c r="J133" t="n">
+        <v>94340.8</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L133" t="n">
+        <v>97229.5</v>
+      </c>
+      <c r="M133" t="n">
+        <v>97139.5</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>111770</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>영원무역</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>25740</v>
+        <v>1828</v>
       </c>
       <c r="D134" t="n">
-        <v>92733.10000000001</v>
+        <v>1826</v>
       </c>
       <c r="E134" t="n">
-        <v>94340.8</v>
+        <v>0.1</v>
       </c>
       <c r="F134" t="n">
-        <v>97139.5</v>
+        <v>6361.3</v>
+      </c>
+      <c r="G134" t="n">
+        <v>6361.3</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>6985.6</v>
+      </c>
+      <c r="J134" t="n">
+        <v>6986.7</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>7521.4</v>
+      </c>
+      <c r="M134" t="n">
+        <v>7460</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>111770</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>영원무역</t>
+          <t>씨에스윈드</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1826</v>
+        <v>787</v>
       </c>
       <c r="D135" t="n">
-        <v>6361.3</v>
+        <v>787</v>
       </c>
       <c r="E135" t="n">
-        <v>6986.7</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>7460</v>
+        <v>3032.2</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3032.2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>3488.4</v>
+      </c>
+      <c r="J135" t="n">
+        <v>3488.4</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>3305.5</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3305.5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>112610</t>
+          <t>120110</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>씨에스윈드</t>
+          <t>코오롱인더</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>787</v>
+        <v>712</v>
       </c>
       <c r="D136" t="n">
-        <v>3032.2</v>
+        <v>712</v>
       </c>
       <c r="E136" t="n">
-        <v>3488.4</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>3305.5</v>
+        <v>2243.2</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2243.2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2576.2</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2576.2</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>2981.2</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2981.2</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>120110</t>
+          <t>128940</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>코오롱인더</t>
+          <t>한미약품</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>712</v>
+        <v>866</v>
       </c>
       <c r="D137" t="n">
-        <v>2243.2</v>
+        <v>632</v>
       </c>
       <c r="E137" t="n">
-        <v>2576.2</v>
+        <v>37</v>
       </c>
       <c r="F137" t="n">
-        <v>2981.2</v>
+        <v>2961.1</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2803.7</v>
+      </c>
+      <c r="H137" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I137" t="n">
+        <v>3106.5</v>
+      </c>
+      <c r="J137" t="n">
+        <v>3114.5</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="L137" t="n">
+        <v>3328.3</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3340.5</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>128940</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>632</v>
+        <v>9092</v>
       </c>
       <c r="D138" t="n">
-        <v>2803.7</v>
+        <v>9092</v>
       </c>
       <c r="E138" t="n">
-        <v>3114.5</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>3340.5</v>
+        <v>32058</v>
+      </c>
+      <c r="G138" t="n">
+        <v>32058</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>34091.5</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34091.5</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>35486.3</v>
+      </c>
+      <c r="M138" t="n">
+        <v>35486.3</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9092</v>
+        <v>3328</v>
       </c>
       <c r="D139" t="n">
-        <v>32058</v>
+        <v>3328</v>
       </c>
       <c r="E139" t="n">
-        <v>34091.5</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>35486.3</v>
+        <v>11090.9</v>
+      </c>
+      <c r="G139" t="n">
+        <v>11090.9</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>11963.5</v>
+      </c>
+      <c r="J139" t="n">
+        <v>11963.5</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>12679.9</v>
+      </c>
+      <c r="M139" t="n">
+        <v>12679.9</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>139130</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>iM금융지주</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3328</v>
+        <v>2101</v>
       </c>
       <c r="D140" t="n">
-        <v>11090.9</v>
+        <v>2101</v>
       </c>
       <c r="E140" t="n">
-        <v>11963.5</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>12679.9</v>
+        <v>6606.6</v>
+      </c>
+      <c r="G140" t="n">
+        <v>6646.1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I140" t="n">
+        <v>7148.2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>7169.7</v>
+      </c>
+      <c r="K140" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="L140" t="n">
+        <v>7563.8</v>
+      </c>
+      <c r="M140" t="n">
+        <v>7576.4</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>139130</t>
+          <t>139480</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>iM금융지주</t>
+          <t>이마트</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2101</v>
+        <v>611</v>
       </c>
       <c r="D141" t="n">
-        <v>6646.1</v>
+        <v>672</v>
       </c>
       <c r="E141" t="n">
-        <v>7169.7</v>
+        <v>-9.1</v>
       </c>
       <c r="F141" t="n">
-        <v>7576.4</v>
+        <v>5488.2</v>
+      </c>
+      <c r="G141" t="n">
+        <v>5599.1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I141" t="n">
+        <v>6514.8</v>
+      </c>
+      <c r="J141" t="n">
+        <v>6533.8</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="L141" t="n">
+        <v>7220.6</v>
+      </c>
+      <c r="M141" t="n">
+        <v>7229.4</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>139480</t>
+          <t>161390</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>이마트</t>
+          <t>한국타이어앤테크놀로지</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>672</v>
+        <v>5313</v>
       </c>
       <c r="D142" t="n">
-        <v>5599.1</v>
+        <v>5313</v>
       </c>
       <c r="E142" t="n">
-        <v>6533.8</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>7229.4</v>
+        <v>21431.1</v>
+      </c>
+      <c r="G142" t="n">
+        <v>21431.1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>23669.5</v>
+      </c>
+      <c r="J142" t="n">
+        <v>23669.5</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>25886.4</v>
+      </c>
+      <c r="M142" t="n">
+        <v>25886.4</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>161390</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>한국타이어앤테크놀로지</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5313</v>
+        <v>953</v>
       </c>
       <c r="D143" t="n">
-        <v>21431.1</v>
+        <v>953</v>
       </c>
       <c r="E143" t="n">
-        <v>23669.5</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>25886.4</v>
+        <v>3148.2</v>
+      </c>
+      <c r="G143" t="n">
+        <v>3148.2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>3633</v>
+      </c>
+      <c r="J143" t="n">
+        <v>3633</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>4096.7</v>
+      </c>
+      <c r="M143" t="n">
+        <v>4096.7</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>175330</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>JB금융지주</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>953</v>
+        <v>2872</v>
       </c>
       <c r="D144" t="n">
-        <v>3148.2</v>
+        <v>2872</v>
       </c>
       <c r="E144" t="n">
-        <v>3633</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>4096.7</v>
+        <v>10076.6</v>
+      </c>
+      <c r="G144" t="n">
+        <v>10076.6</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>10814.8</v>
+      </c>
+      <c r="J144" t="n">
+        <v>10814.8</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>11377.3</v>
+      </c>
+      <c r="M144" t="n">
+        <v>11377.3</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>175330</t>
+          <t>185750</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>JB금융지주</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2872</v>
+        <v>210</v>
       </c>
       <c r="D145" t="n">
-        <v>10076.6</v>
+        <v>210</v>
       </c>
       <c r="E145" t="n">
-        <v>10814.8</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>11377.3</v>
+        <v>804.6</v>
+      </c>
+      <c r="G145" t="n">
+        <v>804.6</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>937.8</v>
+      </c>
+      <c r="J145" t="n">
+        <v>937.8</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1023.2</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1023.2</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>185750</t>
+          <t>192080</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>더블유게임즈</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>210</v>
+        <v>704</v>
       </c>
       <c r="D146" t="n">
-        <v>804.6</v>
+        <v>704</v>
       </c>
       <c r="E146" t="n">
-        <v>937.8</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>1023.2</v>
+        <v>2852.6</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2852.6</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>3117.2</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3117.2</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="M146" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>192080</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>더블유게임즈</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="D147" t="n">
-        <v>2852.6</v>
+        <v>695</v>
       </c>
       <c r="E147" t="n">
-        <v>3117.2</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>3347.5</v>
+        <v>2327.5</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2327.5</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>2766.5</v>
+      </c>
+      <c r="J147" t="n">
+        <v>2766.5</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>3194</v>
+      </c>
+      <c r="M147" t="n">
+        <v>3194</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>204320</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>HL만도</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>695</v>
+        <v>1037</v>
       </c>
       <c r="D148" t="n">
-        <v>2327.5</v>
+        <v>1037</v>
       </c>
       <c r="E148" t="n">
-        <v>2766.5</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>3194</v>
+        <v>4028.2</v>
+      </c>
+      <c r="G148" t="n">
+        <v>4028.2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>4685.9</v>
+      </c>
+      <c r="J148" t="n">
+        <v>4685.9</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>5234.6</v>
+      </c>
+      <c r="M148" t="n">
+        <v>5234.6</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>204320</t>
+          <t>207940</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HL만도</t>
+          <t>삼성바이오로직스</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1037</v>
+        <v>5997</v>
       </c>
       <c r="D149" t="n">
-        <v>4028.2</v>
+        <v>5997</v>
       </c>
       <c r="E149" t="n">
-        <v>4685.9</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>5234.6</v>
+        <v>24946.2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>24946.2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>29031.6</v>
+      </c>
+      <c r="J149" t="n">
+        <v>29031.6</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>31997.5</v>
+      </c>
+      <c r="M149" t="n">
+        <v>31997.5</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>207940</t>
+          <t>241560</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>두산밥캣</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5997</v>
+        <v>1941</v>
       </c>
       <c r="D150" t="n">
-        <v>24946.2</v>
+        <v>1941</v>
       </c>
       <c r="E150" t="n">
-        <v>29031.6</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>31997.5</v>
+        <v>7591.4</v>
+      </c>
+      <c r="G150" t="n">
+        <v>7591.4</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>9204.1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>9204.1</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>10163</v>
+      </c>
+      <c r="M150" t="n">
+        <v>10163</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>241560</t>
+          <t>251270</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>두산밥캣</t>
+          <t>넷마블</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1941</v>
+        <v>964</v>
       </c>
       <c r="D151" t="n">
-        <v>7591.4</v>
+        <v>1023</v>
       </c>
       <c r="E151" t="n">
-        <v>9204.1</v>
+        <v>-5.8</v>
       </c>
       <c r="F151" t="n">
-        <v>10163</v>
+        <v>3714.5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>3834.4</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="I151" t="n">
+        <v>4314.8</v>
+      </c>
+      <c r="J151" t="n">
+        <v>4403.6</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L151" t="n">
+        <v>4476</v>
+      </c>
+      <c r="M151" t="n">
+        <v>4553.1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>251270</t>
+          <t>259960</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>넷마블</t>
+          <t>크래프톤</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1023</v>
+        <v>3671</v>
       </c>
       <c r="D152" t="n">
-        <v>3834.4</v>
+        <v>3671</v>
       </c>
       <c r="E152" t="n">
-        <v>4403.6</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>4553.1</v>
+        <v>14812.8</v>
+      </c>
+      <c r="G152" t="n">
+        <v>14812.8</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>15832.8</v>
+      </c>
+      <c r="J152" t="n">
+        <v>15832.8</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>17211.9</v>
+      </c>
+      <c r="M152" t="n">
+        <v>17211.9</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>259960</t>
+          <t>267250</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>크래프톤</t>
+          <t>HD현대</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3671</v>
+        <v>20915</v>
       </c>
       <c r="D153" t="n">
-        <v>14812.8</v>
+        <v>20915</v>
       </c>
       <c r="E153" t="n">
-        <v>15832.8</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>17211.9</v>
+        <v>90457.39999999999</v>
+      </c>
+      <c r="G153" t="n">
+        <v>90457.39999999999</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>99220.39999999999</v>
+      </c>
+      <c r="J153" t="n">
+        <v>99220.39999999999</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>104542.5</v>
+      </c>
+      <c r="M153" t="n">
+        <v>104542.5</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>267250</t>
+          <t>267260</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>HD현대</t>
+          <t>HD현대일렉트릭</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>20915</v>
+        <v>2811</v>
       </c>
       <c r="D154" t="n">
-        <v>90457.39999999999</v>
+        <v>2842</v>
       </c>
       <c r="E154" t="n">
-        <v>99220.39999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="F154" t="n">
-        <v>104542.5</v>
+        <v>12375.1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>12432</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I154" t="n">
+        <v>15394.8</v>
+      </c>
+      <c r="J154" t="n">
+        <v>15390.2</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>18919</v>
+      </c>
+      <c r="M154" t="n">
+        <v>18811.5</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>267260</t>
+          <t>267270</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HD현대일렉트릭</t>
+          <t>HD건설기계</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2842</v>
+        <v>1987</v>
       </c>
       <c r="D155" t="n">
-        <v>12432</v>
+        <v>1945</v>
       </c>
       <c r="E155" t="n">
-        <v>15390.2</v>
+        <v>2.2</v>
       </c>
       <c r="F155" t="n">
-        <v>18811.5</v>
+        <v>6959.4</v>
+      </c>
+      <c r="G155" t="n">
+        <v>6812.6</v>
+      </c>
+      <c r="H155" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I155" t="n">
+        <v>8809.700000000001</v>
+      </c>
+      <c r="J155" t="n">
+        <v>8492.700000000001</v>
+      </c>
+      <c r="K155" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L155" t="n">
+        <v>10474.8</v>
+      </c>
+      <c r="M155" t="n">
+        <v>10354.5</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>267270</t>
+          <t>271560</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HD건설기계</t>
+          <t>오리온</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1945</v>
+        <v>1376</v>
       </c>
       <c r="D156" t="n">
-        <v>6812.6</v>
+        <v>1376</v>
       </c>
       <c r="E156" t="n">
-        <v>8492.700000000001</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>10354.5</v>
+        <v>6507.6</v>
+      </c>
+      <c r="G156" t="n">
+        <v>6507.6</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7041.8</v>
+      </c>
+      <c r="J156" t="n">
+        <v>7041.8</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>7619.4</v>
+      </c>
+      <c r="M156" t="n">
+        <v>7619.4</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>271560</t>
+          <t>272210</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>오리온</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1376</v>
+        <v>604</v>
       </c>
       <c r="D157" t="n">
-        <v>6507.6</v>
+        <v>604</v>
       </c>
       <c r="E157" t="n">
-        <v>7041.8</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>7619.4</v>
+        <v>2744.2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2744.2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>4888.5</v>
+      </c>
+      <c r="J157" t="n">
+        <v>4888.5</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>6189.8</v>
+      </c>
+      <c r="M157" t="n">
+        <v>6189.8</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>278470</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>에이피알</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>604</v>
+        <v>1735</v>
       </c>
       <c r="D158" t="n">
-        <v>2744.2</v>
+        <v>1735</v>
       </c>
       <c r="E158" t="n">
-        <v>4888.5</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>6189.8</v>
+        <v>7140.1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>7140.1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>9637.700000000001</v>
+      </c>
+      <c r="J158" t="n">
+        <v>9637.700000000001</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>12055.9</v>
+      </c>
+      <c r="M158" t="n">
+        <v>12055.9</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>278470</t>
+          <t>280360</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>에이피알</t>
+          <t>롯데웰푸드</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1735</v>
+        <v>461</v>
       </c>
       <c r="D159" t="n">
-        <v>7140.1</v>
+        <v>461</v>
       </c>
       <c r="E159" t="n">
-        <v>9637.700000000001</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>12055.9</v>
+        <v>1888.8</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1888.8</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>2153.5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>2153.5</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2409.9</v>
+      </c>
+      <c r="M159" t="n">
+        <v>2409.9</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>280360</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>롯데웰푸드</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>461</v>
+        <v>759</v>
       </c>
       <c r="D160" t="n">
-        <v>1888.8</v>
+        <v>747</v>
       </c>
       <c r="E160" t="n">
-        <v>2153.5</v>
+        <v>1.6</v>
       </c>
       <c r="F160" t="n">
-        <v>2409.9</v>
+        <v>2941.1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2910.9</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="n">
+        <v>3228.1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3201.2</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3473.8</v>
+      </c>
+      <c r="M160" t="n">
+        <v>3447.5</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>285130</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>SK케미칼</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>747</v>
+        <v>-15</v>
       </c>
       <c r="D161" t="n">
-        <v>2910.9</v>
+        <v>-15</v>
       </c>
       <c r="E161" t="n">
-        <v>3201.2</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>3447.5</v>
+        <v>69</v>
+      </c>
+      <c r="G161" t="n">
+        <v>69</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>1050.5</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1050.5</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1660</v>
+      </c>
+      <c r="M161" t="n">
+        <v>1660</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>285130</t>
+          <t>298020</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SK케미칼</t>
+          <t>효성티앤씨</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-15</v>
+        <v>1279</v>
       </c>
       <c r="D162" t="n">
-        <v>69</v>
+        <v>1279</v>
       </c>
       <c r="E162" t="n">
-        <v>1050.5</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>1660</v>
+        <v>4462.8</v>
+      </c>
+      <c r="G162" t="n">
+        <v>4462.8</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>5285.2</v>
+      </c>
+      <c r="J162" t="n">
+        <v>5285.2</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>5652.6</v>
+      </c>
+      <c r="M162" t="n">
+        <v>5652.6</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>298020</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>효성티앤씨</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1279</v>
+        <v>2845</v>
       </c>
       <c r="D163" t="n">
-        <v>4462.8</v>
+        <v>2845</v>
       </c>
       <c r="E163" t="n">
-        <v>5285.2</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>5652.6</v>
+        <v>10942.1</v>
+      </c>
+      <c r="G163" t="n">
+        <v>10942.1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>15477.6</v>
+      </c>
+      <c r="J163" t="n">
+        <v>15477.6</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>19558.8</v>
+      </c>
+      <c r="M163" t="n">
+        <v>19558.8</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>298050</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>HS효성첨단소재</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2845</v>
+        <v>552</v>
       </c>
       <c r="D164" t="n">
-        <v>10942.1</v>
+        <v>552</v>
       </c>
       <c r="E164" t="n">
-        <v>15477.6</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>19558.8</v>
+        <v>2071.2</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2071.2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>2550.6</v>
+      </c>
+      <c r="J164" t="n">
+        <v>2550.6</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>2729.6</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2729.6</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>298050</t>
+          <t>300720</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>HS효성첨단소재</t>
+          <t>한일시멘트</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>552</v>
+        <v>400</v>
       </c>
       <c r="D165" t="n">
-        <v>2071.2</v>
+        <v>400</v>
       </c>
       <c r="E165" t="n">
-        <v>2550.6</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>2729.6</v>
+        <v>1150</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>1480</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1480</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1630</v>
+      </c>
+      <c r="M165" t="n">
+        <v>1630</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>300720</t>
+          <t>302440</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>한일시멘트</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>400</v>
+        <v>-399</v>
       </c>
       <c r="D166" t="n">
-        <v>1150</v>
+        <v>-399</v>
       </c>
       <c r="E166" t="n">
-        <v>1480</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>1630</v>
+        <v>-1294.7</v>
+      </c>
+      <c r="G166" t="n">
+        <v>-1294.7</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>-953.7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>-953.7</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>-66.7</v>
+      </c>
+      <c r="M166" t="n">
+        <v>-66.7</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>302440</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>-399</v>
+        <v>785</v>
       </c>
       <c r="D167" t="n">
-        <v>-1294.7</v>
+        <v>798</v>
       </c>
       <c r="E167" t="n">
-        <v>-953.7</v>
+        <v>-1.6</v>
       </c>
       <c r="F167" t="n">
-        <v>-66.7</v>
+        <v>2766.1</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2774.2</v>
+      </c>
+      <c r="H167" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I167" t="n">
+        <v>3678.5</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3692.2</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L167" t="n">
+        <v>4633.6</v>
+      </c>
+      <c r="M167" t="n">
+        <v>4669.3</v>
+      </c>
+      <c r="N167" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>307950</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>798</v>
+        <v>12900</v>
       </c>
       <c r="D168" t="n">
-        <v>2774.2</v>
+        <v>12888</v>
       </c>
       <c r="E168" t="n">
-        <v>3692.2</v>
+        <v>0.1</v>
       </c>
       <c r="F168" t="n">
-        <v>4669.3</v>
+        <v>43417.7</v>
+      </c>
+      <c r="G168" t="n">
+        <v>43419.9</v>
+      </c>
+      <c r="H168" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>47710.4</v>
+      </c>
+      <c r="J168" t="n">
+        <v>47767.7</v>
+      </c>
+      <c r="K168" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>50412.4</v>
+      </c>
+      <c r="M168" t="n">
+        <v>50466.5</v>
+      </c>
+      <c r="N168" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>323410</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>12888</v>
+        <v>1833</v>
       </c>
       <c r="D169" t="n">
-        <v>43419.9</v>
+        <v>1829</v>
       </c>
       <c r="E169" t="n">
-        <v>47767.7</v>
+        <v>0.2</v>
       </c>
       <c r="F169" t="n">
-        <v>50466.5</v>
+        <v>7101.1</v>
+      </c>
+      <c r="G169" t="n">
+        <v>7092.9</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>8165.4</v>
+      </c>
+      <c r="J169" t="n">
+        <v>8168.1</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>8919.4</v>
+      </c>
+      <c r="M169" t="n">
+        <v>8940.6</v>
+      </c>
+      <c r="N169" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>323410</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1829</v>
+        <v>845</v>
       </c>
       <c r="D170" t="n">
-        <v>7092.9</v>
+        <v>850</v>
       </c>
       <c r="E170" t="n">
-        <v>8168.1</v>
+        <v>-0.6</v>
       </c>
       <c r="F170" t="n">
-        <v>8940.6</v>
+        <v>3377.3</v>
+      </c>
+      <c r="G170" t="n">
+        <v>3376.7</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" t="n">
+        <v>4511.6</v>
+      </c>
+      <c r="J170" t="n">
+        <v>4497.3</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L170" t="n">
+        <v>5545</v>
+      </c>
+      <c r="M170" t="n">
+        <v>5597.5</v>
+      </c>
+      <c r="N170" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>329180</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>850</v>
+        <v>9902</v>
       </c>
       <c r="D171" t="n">
-        <v>3376.7</v>
+        <v>10003</v>
       </c>
       <c r="E171" t="n">
-        <v>4497.3</v>
+        <v>-1</v>
       </c>
       <c r="F171" t="n">
-        <v>5597.5</v>
+        <v>38897.6</v>
+      </c>
+      <c r="G171" t="n">
+        <v>39168.8</v>
+      </c>
+      <c r="H171" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="I171" t="n">
+        <v>45686.3</v>
+      </c>
+      <c r="J171" t="n">
+        <v>46037.2</v>
+      </c>
+      <c r="K171" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="L171" t="n">
+        <v>51979.2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>52136.8</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>329180</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>10003</v>
+        <v>1499</v>
       </c>
       <c r="D172" t="n">
-        <v>39168.8</v>
+        <v>1499</v>
       </c>
       <c r="E172" t="n">
-        <v>46037.2</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>52136.8</v>
+        <v>2659.2</v>
+      </c>
+      <c r="G172" t="n">
+        <v>2659.2</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>4935</v>
+      </c>
+      <c r="J172" t="n">
+        <v>4935</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>5511.5</v>
+      </c>
+      <c r="M172" t="n">
+        <v>5511.5</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>361610</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>SK아이이테크놀로지</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1499</v>
+        <v>-664</v>
       </c>
       <c r="D173" t="n">
-        <v>2659.2</v>
+        <v>-664</v>
       </c>
       <c r="E173" t="n">
-        <v>4935</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>5511.5</v>
+        <v>-2448.4</v>
+      </c>
+      <c r="G173" t="n">
+        <v>-2448.4</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>-938</v>
+      </c>
+      <c r="J173" t="n">
+        <v>-938</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="M173" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>361610</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>SK아이이테크놀로지</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>-664</v>
+        <v>2034</v>
       </c>
       <c r="D174" t="n">
-        <v>-2448.4</v>
+        <v>2034</v>
       </c>
       <c r="E174" t="n">
-        <v>-938</v>
+        <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>203.6</v>
+        <v>11444.5</v>
+      </c>
+      <c r="G174" t="n">
+        <v>11444.5</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>39869.5</v>
+      </c>
+      <c r="J174" t="n">
+        <v>39869.5</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>61536.8</v>
+      </c>
+      <c r="M174" t="n">
+        <v>61536.8</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2034</v>
+        <v>1199</v>
       </c>
       <c r="D175" t="n">
-        <v>11444.5</v>
+        <v>1199</v>
       </c>
       <c r="E175" t="n">
-        <v>39869.5</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>61536.8</v>
+        <v>5129.8</v>
+      </c>
+      <c r="G175" t="n">
+        <v>5086.1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I175" t="n">
+        <v>5671.2</v>
+      </c>
+      <c r="J175" t="n">
+        <v>5624.8</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L175" t="n">
+        <v>6198.3</v>
+      </c>
+      <c r="M175" t="n">
+        <v>6159</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>377300</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>카카오페이</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1199</v>
+        <v>323</v>
       </c>
       <c r="D176" t="n">
-        <v>5086.1</v>
+        <v>323</v>
       </c>
       <c r="E176" t="n">
-        <v>5624.8</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>6159</v>
+        <v>1388.2</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1388.2</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2719</v>
+      </c>
+      <c r="M176" t="n">
+        <v>2719</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>377300</t>
+          <t>383220</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>카카오페이</t>
+          <t>F&amp;F</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>323</v>
+        <v>969</v>
       </c>
       <c r="D177" t="n">
-        <v>1388.2</v>
+        <v>969</v>
       </c>
       <c r="E177" t="n">
-        <v>1925.5</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>2719</v>
+        <v>5294.5</v>
+      </c>
+      <c r="G177" t="n">
+        <v>5294.5</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>5592.8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>5592.8</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>5983.8</v>
+      </c>
+      <c r="M177" t="n">
+        <v>5983.8</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>383220</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>969</v>
+        <v>99084</v>
       </c>
       <c r="D178" t="n">
-        <v>5294.5</v>
+        <v>99084</v>
       </c>
       <c r="E178" t="n">
-        <v>5592.8</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>5983.8</v>
+        <v>430391.9</v>
+      </c>
+      <c r="G178" t="n">
+        <v>430391.9</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>541747.7</v>
+      </c>
+      <c r="J178" t="n">
+        <v>541747.7</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>583359</v>
+      </c>
+      <c r="M178" t="n">
+        <v>583359</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>99084</v>
+        <v>1055</v>
       </c>
       <c r="D179" t="n">
-        <v>430391.9</v>
+        <v>1077</v>
       </c>
       <c r="E179" t="n">
-        <v>541747.7</v>
+        <v>-2</v>
       </c>
       <c r="F179" t="n">
-        <v>583359</v>
+        <v>4346.1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>4394.7</v>
+      </c>
+      <c r="H179" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>5498.2</v>
+      </c>
+      <c r="J179" t="n">
+        <v>5562.8</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L179" t="n">
+        <v>6666.5</v>
+      </c>
+      <c r="M179" t="n">
+        <v>6650.8</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>443060</t>
+          <t>456040</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>OCI</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1077</v>
+        <v>462</v>
       </c>
       <c r="D180" t="n">
-        <v>4394.7</v>
+        <v>481</v>
       </c>
       <c r="E180" t="n">
-        <v>5562.8</v>
+        <v>-4</v>
       </c>
       <c r="F180" t="n">
-        <v>6650.8</v>
+        <v>1669.7</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1698.3</v>
+      </c>
+      <c r="H180" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1943.7</v>
+      </c>
+      <c r="J180" t="n">
+        <v>2071.3</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2033.3</v>
+      </c>
+      <c r="M180" t="n">
+        <v>2153.3</v>
+      </c>
+      <c r="N180" t="n">
+        <v>-5.6</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>456040</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OCI</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>481</v>
+        <v>414</v>
       </c>
       <c r="D181" t="n">
-        <v>1698.3</v>
+        <v>414</v>
       </c>
       <c r="E181" t="n">
-        <v>2071.3</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>2153.3</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>457190</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>이수스페셜티케미컬</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>483650</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>달바글로벌</t>
-        </is>
-      </c>
-      <c r="C183" t="n">
-        <v>414</v>
-      </c>
-      <c r="D183" t="n">
         <v>1606.1</v>
       </c>
-      <c r="E183" t="n">
+      <c r="G181" t="n">
+        <v>1606.1</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
         <v>2195.5</v>
       </c>
-      <c r="F183" t="n">
+      <c r="J181" t="n">
+        <v>2195.5</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
         <v>2769.4</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2769.4</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N181"/>
+  <dimension ref="A1:Q181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,9 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +479,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>이번분기 변동%</t>
+          <t>이번분기 컨센변동%</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -491,7 +494,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026E 변동%</t>
+          <t>2026E 컨센변동%</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -506,7 +509,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2027E 변동%</t>
+          <t>2027E 컨센변동%</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -521,7 +524,22 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2028E 변동%</t>
+          <t>2028E 컨센변동%</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>현재 종가</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>전주 종가</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>주가변동%</t>
         </is>
       </c>
     </row>
@@ -572,6 +590,15 @@
       <c r="N3" t="n">
         <v>3</v>
       </c>
+      <c r="O3" t="n">
+        <v>14960</v>
+      </c>
+      <c r="P3" t="n">
+        <v>15150</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -620,6 +647,15 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
+      <c r="O4" t="n">
+        <v>68100</v>
+      </c>
+      <c r="P4" t="n">
+        <v>69100</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -668,6 +704,15 @@
       <c r="N5" t="n">
         <v>-0.2</v>
       </c>
+      <c r="O5" t="n">
+        <v>73600</v>
+      </c>
+      <c r="P5" t="n">
+        <v>74300</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,6 +761,15 @@
       <c r="N6" t="n">
         <v>0</v>
       </c>
+      <c r="O6" t="n">
+        <v>1238000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1268000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -764,6 +818,15 @@
       <c r="N7" t="n">
         <v>0</v>
       </c>
+      <c r="O7" t="n">
+        <v>45550</v>
+      </c>
+      <c r="P7" t="n">
+        <v>44300</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -812,6 +875,15 @@
       <c r="N8" t="n">
         <v>0</v>
       </c>
+      <c r="O8" t="n">
+        <v>24650</v>
+      </c>
+      <c r="P8" t="n">
+        <v>25600</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -860,6 +932,15 @@
       <c r="N9" t="n">
         <v>-0.2</v>
       </c>
+      <c r="O9" t="n">
+        <v>143500</v>
+      </c>
+      <c r="P9" t="n">
+        <v>156800</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-8.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -908,6 +989,15 @@
       <c r="N10" t="n">
         <v>0</v>
       </c>
+      <c r="O10" t="n">
+        <v>1845000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2076000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-11.1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -956,6 +1046,15 @@
       <c r="N11" t="n">
         <v>-0.3</v>
       </c>
+      <c r="O11" t="n">
+        <v>101500</v>
+      </c>
+      <c r="P11" t="n">
+        <v>100700</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1004,6 +1103,15 @@
       <c r="N12" t="n">
         <v>0</v>
       </c>
+      <c r="O12" t="n">
+        <v>639000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>671000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-4.8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1052,6 +1160,15 @@
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>92300</v>
+      </c>
+      <c r="P13" t="n">
+        <v>93400</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1100,6 +1217,15 @@
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>110700</v>
+      </c>
+      <c r="P14" t="n">
+        <v>111800</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1148,6 +1274,15 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>142600</v>
+      </c>
+      <c r="P15" t="n">
+        <v>142300</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1196,6 +1331,15 @@
       <c r="N16" t="n">
         <v>1.3</v>
       </c>
+      <c r="O16" t="n">
+        <v>30250</v>
+      </c>
+      <c r="P16" t="n">
+        <v>30150</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1244,6 +1388,15 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
+      <c r="O17" t="n">
+        <v>28300</v>
+      </c>
+      <c r="P17" t="n">
+        <v>28200</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1283,6 +1436,15 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="n">
+        <v>38550</v>
+      </c>
+      <c r="P18" t="n">
+        <v>37950</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1331,6 +1493,15 @@
       <c r="N19" t="n">
         <v>0</v>
       </c>
+      <c r="O19" t="n">
+        <v>17500</v>
+      </c>
+      <c r="P19" t="n">
+        <v>17550</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1361,6 +1532,15 @@
       <c r="H20" t="n">
         <v>0</v>
       </c>
+      <c r="O20" t="n">
+        <v>26800</v>
+      </c>
+      <c r="P20" t="n">
+        <v>26050</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1409,6 +1589,15 @@
       <c r="N21" t="n">
         <v>0</v>
       </c>
+      <c r="O21" t="n">
+        <v>434000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>447500</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1457,6 +1646,15 @@
       <c r="N22" t="n">
         <v>0</v>
       </c>
+      <c r="O22" t="n">
+        <v>103700</v>
+      </c>
+      <c r="P22" t="n">
+        <v>105100</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1505,6 +1703,15 @@
       <c r="N23" t="n">
         <v>-0.2</v>
       </c>
+      <c r="O23" t="n">
+        <v>1110000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1146000</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1553,6 +1760,15 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>25850</v>
+      </c>
+      <c r="P24" t="n">
+        <v>28150</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-8.199999999999999</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1601,6 +1817,15 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
+      <c r="O25" t="n">
+        <v>99300</v>
+      </c>
+      <c r="P25" t="n">
+        <v>102500</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1649,6 +1874,15 @@
       <c r="N26" t="n">
         <v>-0.3</v>
       </c>
+      <c r="O26" t="n">
+        <v>150700</v>
+      </c>
+      <c r="P26" t="n">
+        <v>144700</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1697,6 +1931,15 @@
       <c r="N27" t="n">
         <v>0</v>
       </c>
+      <c r="O27" t="n">
+        <v>46000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>43350</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1745,6 +1988,15 @@
       <c r="N28" t="n">
         <v>1.8</v>
       </c>
+      <c r="O28" t="n">
+        <v>26800</v>
+      </c>
+      <c r="P28" t="n">
+        <v>26900</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1793,6 +2045,15 @@
       <c r="N29" t="n">
         <v>0</v>
       </c>
+      <c r="O29" t="n">
+        <v>591000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>625000</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-5.4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1841,6 +2102,15 @@
       <c r="N30" t="n">
         <v>0.7</v>
       </c>
+      <c r="O30" t="n">
+        <v>356000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>362000</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-1.7</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1889,6 +2159,15 @@
       <c r="N31" t="n">
         <v>0</v>
       </c>
+      <c r="O31" t="n">
+        <v>23050</v>
+      </c>
+      <c r="P31" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1937,6 +2216,15 @@
       <c r="N32" t="n">
         <v>1.6</v>
       </c>
+      <c r="O32" t="n">
+        <v>101600</v>
+      </c>
+      <c r="P32" t="n">
+        <v>100500</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1985,6 +2273,15 @@
       <c r="N33" t="n">
         <v>0.5</v>
       </c>
+      <c r="O33" t="n">
+        <v>444000</v>
+      </c>
+      <c r="P33" t="n">
+        <v>462500</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2033,6 +2330,15 @@
       <c r="N34" t="n">
         <v>-2</v>
       </c>
+      <c r="O34" t="n">
+        <v>308000</v>
+      </c>
+      <c r="P34" t="n">
+        <v>304000</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2081,6 +2387,15 @@
       <c r="N35" t="n">
         <v>0</v>
       </c>
+      <c r="O35" t="n">
+        <v>159100</v>
+      </c>
+      <c r="P35" t="n">
+        <v>151400</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2129,6 +2444,15 @@
       <c r="N36" t="n">
         <v>0</v>
       </c>
+      <c r="O36" t="n">
+        <v>54200</v>
+      </c>
+      <c r="P36" t="n">
+        <v>57400</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2177,6 +2501,15 @@
       <c r="N37" t="n">
         <v>0</v>
       </c>
+      <c r="O37" t="n">
+        <v>254500</v>
+      </c>
+      <c r="P37" t="n">
+        <v>277500</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-8.300000000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2225,6 +2558,15 @@
       <c r="N38" t="n">
         <v>0</v>
       </c>
+      <c r="O38" t="n">
+        <v>31150</v>
+      </c>
+      <c r="P38" t="n">
+        <v>30650</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2273,6 +2615,15 @@
       <c r="N39" t="n">
         <v>0</v>
       </c>
+      <c r="O39" t="n">
+        <v>34500</v>
+      </c>
+      <c r="P39" t="n">
+        <v>35100</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-1.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2321,6 +2672,15 @@
       <c r="N40" t="n">
         <v>0</v>
       </c>
+      <c r="O40" t="n">
+        <v>303500</v>
+      </c>
+      <c r="P40" t="n">
+        <v>308500</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2369,6 +2729,15 @@
       <c r="N41" t="n">
         <v>0</v>
       </c>
+      <c r="O41" t="n">
+        <v>120500</v>
+      </c>
+      <c r="P41" t="n">
+        <v>121200</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>-0.6</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2417,6 +2786,15 @@
       <c r="N42" t="n">
         <v>0</v>
       </c>
+      <c r="O42" t="n">
+        <v>440000</v>
+      </c>
+      <c r="P42" t="n">
+        <v>412000</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2465,6 +2843,15 @@
       <c r="N43" t="n">
         <v>0</v>
       </c>
+      <c r="O43" t="n">
+        <v>105600</v>
+      </c>
+      <c r="P43" t="n">
+        <v>102600</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2513,6 +2900,15 @@
       <c r="N44" t="n">
         <v>0</v>
       </c>
+      <c r="O44" t="n">
+        <v>40000</v>
+      </c>
+      <c r="P44" t="n">
+        <v>40500</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2561,6 +2957,15 @@
       <c r="N45" t="n">
         <v>-0.1</v>
       </c>
+      <c r="O45" t="n">
+        <v>26600</v>
+      </c>
+      <c r="P45" t="n">
+        <v>25050</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2609,6 +3014,15 @@
       <c r="N46" t="n">
         <v>0</v>
       </c>
+      <c r="O46" t="n">
+        <v>37900</v>
+      </c>
+      <c r="P46" t="n">
+        <v>35400</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>7.1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2657,6 +3071,15 @@
       <c r="N47" t="n">
         <v>1.8</v>
       </c>
+      <c r="O47" t="n">
+        <v>99600</v>
+      </c>
+      <c r="P47" t="n">
+        <v>87800</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>13.4</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2696,6 +3119,15 @@
       <c r="K48" t="n">
         <v>0</v>
       </c>
+      <c r="O48" t="n">
+        <v>13970</v>
+      </c>
+      <c r="P48" t="n">
+        <v>13950</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2744,6 +3176,15 @@
       <c r="N49" t="n">
         <v>-0.3</v>
       </c>
+      <c r="O49" t="n">
+        <v>49750</v>
+      </c>
+      <c r="P49" t="n">
+        <v>51500</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-3.4</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2792,6 +3233,15 @@
       <c r="N50" t="n">
         <v>0</v>
       </c>
+      <c r="O50" t="n">
+        <v>1289000</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1479000</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-12.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2840,6 +3290,15 @@
       <c r="N51" t="n">
         <v>0</v>
       </c>
+      <c r="O51" t="n">
+        <v>34800</v>
+      </c>
+      <c r="P51" t="n">
+        <v>34300</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2888,6 +3347,15 @@
       <c r="N52" t="n">
         <v>0</v>
       </c>
+      <c r="O52" t="n">
+        <v>55200</v>
+      </c>
+      <c r="P52" t="n">
+        <v>58700</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2936,6 +3404,15 @@
       <c r="N53" t="n">
         <v>0</v>
       </c>
+      <c r="O53" t="n">
+        <v>341500</v>
+      </c>
+      <c r="P53" t="n">
+        <v>340000</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2984,6 +3461,15 @@
       <c r="N54" t="n">
         <v>0.4</v>
       </c>
+      <c r="O54" t="n">
+        <v>32000</v>
+      </c>
+      <c r="P54" t="n">
+        <v>29850</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3032,6 +3518,15 @@
       <c r="N55" t="n">
         <v>0</v>
       </c>
+      <c r="O55" t="n">
+        <v>204500</v>
+      </c>
+      <c r="P55" t="n">
+        <v>180500</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>13.3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3080,6 +3575,15 @@
       <c r="N56" t="n">
         <v>0</v>
       </c>
+      <c r="O56" t="n">
+        <v>184500</v>
+      </c>
+      <c r="P56" t="n">
+        <v>183500</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3128,6 +3632,15 @@
       <c r="N57" t="n">
         <v>3</v>
       </c>
+      <c r="O57" t="n">
+        <v>1025000</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-0.9</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3176,6 +3689,15 @@
       <c r="N58" t="n">
         <v>0.7</v>
       </c>
+      <c r="O58" t="n">
+        <v>22050</v>
+      </c>
+      <c r="P58" t="n">
+        <v>21150</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3224,6 +3746,15 @@
       <c r="N59" t="n">
         <v>0</v>
       </c>
+      <c r="O59" t="n">
+        <v>139500</v>
+      </c>
+      <c r="P59" t="n">
+        <v>131600</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3272,6 +3803,15 @@
       <c r="N60" t="n">
         <v>0</v>
       </c>
+      <c r="O60" t="n">
+        <v>661000</v>
+      </c>
+      <c r="P60" t="n">
+        <v>763000</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>-13.4</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3320,6 +3860,15 @@
       <c r="N61" t="n">
         <v>0</v>
       </c>
+      <c r="O61" t="n">
+        <v>60600</v>
+      </c>
+      <c r="P61" t="n">
+        <v>60700</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3368,6 +3917,15 @@
       <c r="N62" t="n">
         <v>0</v>
       </c>
+      <c r="O62" t="n">
+        <v>19550</v>
+      </c>
+      <c r="P62" t="n">
+        <v>20050</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>-2.5</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3416,6 +3974,15 @@
       <c r="N63" t="n">
         <v>0</v>
       </c>
+      <c r="O63" t="n">
+        <v>59900</v>
+      </c>
+      <c r="P63" t="n">
+        <v>60600</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3464,6 +4031,15 @@
       <c r="N64" t="n">
         <v>0</v>
       </c>
+      <c r="O64" t="n">
+        <v>117400</v>
+      </c>
+      <c r="P64" t="n">
+        <v>112500</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3512,6 +4088,15 @@
       <c r="N65" t="n">
         <v>0</v>
       </c>
+      <c r="O65" t="n">
+        <v>88000</v>
+      </c>
+      <c r="P65" t="n">
+        <v>88700</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3560,6 +4145,15 @@
       <c r="N66" t="n">
         <v>0</v>
       </c>
+      <c r="O66" t="n">
+        <v>487500</v>
+      </c>
+      <c r="P66" t="n">
+        <v>488500</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3608,6 +4202,15 @@
       <c r="N67" t="n">
         <v>0.9</v>
       </c>
+      <c r="O67" t="n">
+        <v>936000</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1041000</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3656,6 +4259,15 @@
       <c r="N68" t="n">
         <v>0</v>
       </c>
+      <c r="O68" t="n">
+        <v>71700</v>
+      </c>
+      <c r="P68" t="n">
+        <v>71800</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3704,6 +4316,15 @@
       <c r="N69" t="n">
         <v>0</v>
       </c>
+      <c r="O69" t="n">
+        <v>260000</v>
+      </c>
+      <c r="P69" t="n">
+        <v>238000</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>9.199999999999999</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3752,6 +4373,15 @@
       <c r="N70" t="n">
         <v>0</v>
       </c>
+      <c r="O70" t="n">
+        <v>34250</v>
+      </c>
+      <c r="P70" t="n">
+        <v>36750</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-6.8</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3800,6 +4430,15 @@
       <c r="N71" t="n">
         <v>0.6</v>
       </c>
+      <c r="O71" t="n">
+        <v>108800</v>
+      </c>
+      <c r="P71" t="n">
+        <v>111700</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>-2.6</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3848,6 +4487,15 @@
       <c r="N72" t="n">
         <v>0.1</v>
       </c>
+      <c r="O72" t="n">
+        <v>85700</v>
+      </c>
+      <c r="P72" t="n">
+        <v>84000</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3896,6 +4544,15 @@
       <c r="N73" t="n">
         <v>0</v>
       </c>
+      <c r="O73" t="n">
+        <v>24600</v>
+      </c>
+      <c r="P73" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3944,6 +4601,15 @@
       <c r="N74" t="n">
         <v>0.1</v>
       </c>
+      <c r="O74" t="n">
+        <v>190200</v>
+      </c>
+      <c r="P74" t="n">
+        <v>194300</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>-2.1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3992,6 +4658,15 @@
       <c r="N75" t="n">
         <v>0</v>
       </c>
+      <c r="O75" t="n">
+        <v>3440</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3575</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>-3.8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4040,6 +4715,15 @@
       <c r="N76" t="n">
         <v>0</v>
       </c>
+      <c r="O76" t="n">
+        <v>91700</v>
+      </c>
+      <c r="P76" t="n">
+        <v>91700</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4088,6 +4772,15 @@
       <c r="N77" t="n">
         <v>0</v>
       </c>
+      <c r="O77" t="n">
+        <v>154300</v>
+      </c>
+      <c r="P77" t="n">
+        <v>159600</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>-3.3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4136,6 +4829,15 @@
       <c r="N78" t="n">
         <v>-0</v>
       </c>
+      <c r="O78" t="n">
+        <v>21150</v>
+      </c>
+      <c r="P78" t="n">
+        <v>20950</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4184,6 +4886,15 @@
       <c r="N79" t="n">
         <v>0</v>
       </c>
+      <c r="O79" t="n">
+        <v>41100</v>
+      </c>
+      <c r="P79" t="n">
+        <v>43500</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>-5.5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4232,6 +4943,15 @@
       <c r="N80" t="n">
         <v>0</v>
       </c>
+      <c r="O80" t="n">
+        <v>361000</v>
+      </c>
+      <c r="P80" t="n">
+        <v>395000</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>-8.6</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4280,6 +5000,15 @@
       <c r="N81" t="n">
         <v>1.5</v>
       </c>
+      <c r="O81" t="n">
+        <v>5240</v>
+      </c>
+      <c r="P81" t="n">
+        <v>5170</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4328,6 +5057,15 @@
       <c r="N82" t="n">
         <v>0</v>
       </c>
+      <c r="O82" t="n">
+        <v>47800</v>
+      </c>
+      <c r="P82" t="n">
+        <v>48850</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>-2.1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4376,6 +5114,15 @@
       <c r="N83" t="n">
         <v>0</v>
       </c>
+      <c r="O83" t="n">
+        <v>18760</v>
+      </c>
+      <c r="P83" t="n">
+        <v>18980</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>-1.2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4424,6 +5171,15 @@
       <c r="N84" t="n">
         <v>-0.1</v>
       </c>
+      <c r="O84" t="n">
+        <v>52700</v>
+      </c>
+      <c r="P84" t="n">
+        <v>55400</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>-4.9</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4472,6 +5228,15 @@
       <c r="N85" t="n">
         <v>0</v>
       </c>
+      <c r="O85" t="n">
+        <v>14530</v>
+      </c>
+      <c r="P85" t="n">
+        <v>14810</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>-1.9</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4520,6 +5285,15 @@
       <c r="N86" t="n">
         <v>0</v>
       </c>
+      <c r="O86" t="n">
+        <v>326000</v>
+      </c>
+      <c r="P86" t="n">
+        <v>346000</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>-5.8</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4568,6 +5342,15 @@
       <c r="N87" t="n">
         <v>0.1</v>
       </c>
+      <c r="O87" t="n">
+        <v>174300</v>
+      </c>
+      <c r="P87" t="n">
+        <v>184300</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>-5.4</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4616,6 +5399,15 @@
       <c r="N88" t="n">
         <v>0</v>
       </c>
+      <c r="O88" t="n">
+        <v>73200</v>
+      </c>
+      <c r="P88" t="n">
+        <v>74000</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4664,6 +5456,15 @@
       <c r="N89" t="n">
         <v>0</v>
       </c>
+      <c r="O89" t="n">
+        <v>10360</v>
+      </c>
+      <c r="P89" t="n">
+        <v>11240</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>-7.8</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4712,6 +5513,15 @@
       <c r="N90" t="n">
         <v>0</v>
       </c>
+      <c r="O90" t="n">
+        <v>12550</v>
+      </c>
+      <c r="P90" t="n">
+        <v>12920</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>-2.9</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4760,6 +5570,15 @@
       <c r="N91" t="n">
         <v>0</v>
       </c>
+      <c r="O91" t="n">
+        <v>583000</v>
+      </c>
+      <c r="P91" t="n">
+        <v>596000</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>-2.2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4808,6 +5627,15 @@
       <c r="N92" t="n">
         <v>0</v>
       </c>
+      <c r="O92" t="n">
+        <v>14680</v>
+      </c>
+      <c r="P92" t="n">
+        <v>14780</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>-0.7</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4856,6 +5684,15 @@
       <c r="N93" t="n">
         <v>0.3</v>
       </c>
+      <c r="O93" t="n">
+        <v>188000</v>
+      </c>
+      <c r="P93" t="n">
+        <v>192700</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4904,6 +5741,15 @@
       <c r="N94" t="n">
         <v>0.5</v>
       </c>
+      <c r="O94" t="n">
+        <v>34750</v>
+      </c>
+      <c r="P94" t="n">
+        <v>34650</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4952,6 +5798,15 @@
       <c r="N95" t="n">
         <v>0</v>
       </c>
+      <c r="O95" t="n">
+        <v>32700</v>
+      </c>
+      <c r="P95" t="n">
+        <v>33200</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5000,6 +5855,15 @@
       <c r="N96" t="n">
         <v>-1.4</v>
       </c>
+      <c r="O96" t="n">
+        <v>240500</v>
+      </c>
+      <c r="P96" t="n">
+        <v>258500</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5048,6 +5912,15 @@
       <c r="N97" t="n">
         <v>0</v>
       </c>
+      <c r="O97" t="n">
+        <v>323500</v>
+      </c>
+      <c r="P97" t="n">
+        <v>334500</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>-3.3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5096,6 +5969,15 @@
       <c r="N98" t="n">
         <v>-0</v>
       </c>
+      <c r="O98" t="n">
+        <v>78800</v>
+      </c>
+      <c r="P98" t="n">
+        <v>82000</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>-3.9</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5144,6 +6026,15 @@
       <c r="N99" t="n">
         <v>0</v>
       </c>
+      <c r="O99" t="n">
+        <v>205500</v>
+      </c>
+      <c r="P99" t="n">
+        <v>199200</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5192,6 +6083,15 @@
       <c r="N100" t="n">
         <v>1.7</v>
       </c>
+      <c r="O100" t="n">
+        <v>16010</v>
+      </c>
+      <c r="P100" t="n">
+        <v>15830</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5240,6 +6140,15 @@
       <c r="N101" t="n">
         <v>0</v>
       </c>
+      <c r="O101" t="n">
+        <v>50600</v>
+      </c>
+      <c r="P101" t="n">
+        <v>48750</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5288,6 +6197,15 @@
       <c r="N102" t="n">
         <v>0</v>
       </c>
+      <c r="O102" t="n">
+        <v>143500</v>
+      </c>
+      <c r="P102" t="n">
+        <v>142000</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5336,6 +6254,15 @@
       <c r="N103" t="n">
         <v>0</v>
       </c>
+      <c r="O103" t="n">
+        <v>44050</v>
+      </c>
+      <c r="P103" t="n">
+        <v>43900</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5384,6 +6311,15 @@
       <c r="N104" t="n">
         <v>0</v>
       </c>
+      <c r="O104" t="n">
+        <v>248500</v>
+      </c>
+      <c r="P104" t="n">
+        <v>256000</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>-2.9</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5432,6 +6368,15 @@
       <c r="N105" t="n">
         <v>0</v>
       </c>
+      <c r="O105" t="n">
+        <v>260500</v>
+      </c>
+      <c r="P105" t="n">
+        <v>255000</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5480,6 +6425,15 @@
       <c r="N106" t="n">
         <v>0</v>
       </c>
+      <c r="O106" t="n">
+        <v>97600</v>
+      </c>
+      <c r="P106" t="n">
+        <v>94900</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5528,6 +6482,15 @@
       <c r="N107" t="n">
         <v>0.1</v>
       </c>
+      <c r="O107" t="n">
+        <v>108600</v>
+      </c>
+      <c r="P107" t="n">
+        <v>107300</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5576,6 +6539,15 @@
       <c r="N108" t="n">
         <v>0</v>
       </c>
+      <c r="O108" t="n">
+        <v>169800</v>
+      </c>
+      <c r="P108" t="n">
+        <v>178200</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>-4.7</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5624,6 +6596,15 @@
       <c r="N109" t="n">
         <v>0</v>
       </c>
+      <c r="O109" t="n">
+        <v>170000</v>
+      </c>
+      <c r="P109" t="n">
+        <v>169100</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5672,6 +6653,15 @@
       <c r="N110" t="n">
         <v>0</v>
       </c>
+      <c r="O110" t="n">
+        <v>68200</v>
+      </c>
+      <c r="P110" t="n">
+        <v>71200</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>-4.2</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5720,6 +6710,15 @@
       <c r="N111" t="n">
         <v>0</v>
       </c>
+      <c r="O111" t="n">
+        <v>185600</v>
+      </c>
+      <c r="P111" t="n">
+        <v>195800</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>-5.2</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5768,6 +6767,15 @@
       <c r="N112" t="n">
         <v>0</v>
       </c>
+      <c r="O112" t="n">
+        <v>101300</v>
+      </c>
+      <c r="P112" t="n">
+        <v>91800</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>10.3</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5816,6 +6824,15 @@
       <c r="N113" t="n">
         <v>0.2</v>
       </c>
+      <c r="O113" t="n">
+        <v>175100</v>
+      </c>
+      <c r="P113" t="n">
+        <v>176800</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5864,6 +6881,15 @@
       <c r="N114" t="n">
         <v>0</v>
       </c>
+      <c r="O114" t="n">
+        <v>15520</v>
+      </c>
+      <c r="P114" t="n">
+        <v>15620</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>-0.6</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5912,6 +6938,15 @@
       <c r="N115" t="n">
         <v>0</v>
       </c>
+      <c r="O115" t="n">
+        <v>132500</v>
+      </c>
+      <c r="P115" t="n">
+        <v>134900</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5960,6 +6995,15 @@
       <c r="N116" t="n">
         <v>0</v>
       </c>
+      <c r="O116" t="n">
+        <v>157900</v>
+      </c>
+      <c r="P116" t="n">
+        <v>168700</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>-6.4</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6008,6 +7052,15 @@
       <c r="N117" t="n">
         <v>0</v>
       </c>
+      <c r="O117" t="n">
+        <v>237000</v>
+      </c>
+      <c r="P117" t="n">
+        <v>233500</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6056,6 +7109,15 @@
       <c r="N118" t="n">
         <v>0</v>
       </c>
+      <c r="O118" t="n">
+        <v>66700</v>
+      </c>
+      <c r="P118" t="n">
+        <v>67400</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6104,6 +7166,15 @@
       <c r="N119" t="n">
         <v>0</v>
       </c>
+      <c r="O119" t="n">
+        <v>59600</v>
+      </c>
+      <c r="P119" t="n">
+        <v>55900</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>6.6</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6152,6 +7223,15 @@
       <c r="N120" t="n">
         <v>0</v>
       </c>
+      <c r="O120" t="n">
+        <v>7160</v>
+      </c>
+      <c r="P120" t="n">
+        <v>6400</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>11.9</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6200,6 +7280,15 @@
       <c r="N121" t="n">
         <v>0</v>
       </c>
+      <c r="O121" t="n">
+        <v>79500</v>
+      </c>
+      <c r="P121" t="n">
+        <v>78600</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6248,6 +7337,15 @@
       <c r="N122" t="n">
         <v>0</v>
       </c>
+      <c r="O122" t="n">
+        <v>725000</v>
+      </c>
+      <c r="P122" t="n">
+        <v>714000</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6296,6 +7394,15 @@
       <c r="N123" t="n">
         <v>0</v>
       </c>
+      <c r="O123" t="n">
+        <v>45150</v>
+      </c>
+      <c r="P123" t="n">
+        <v>47850</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6344,6 +7451,15 @@
       <c r="N124" t="n">
         <v>0</v>
       </c>
+      <c r="O124" t="n">
+        <v>46200</v>
+      </c>
+      <c r="P124" t="n">
+        <v>44750</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6392,6 +7508,15 @@
       <c r="N125" t="n">
         <v>0.1</v>
       </c>
+      <c r="O125" t="n">
+        <v>187800</v>
+      </c>
+      <c r="P125" t="n">
+        <v>190400</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>-1.4</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6440,6 +7565,15 @@
       <c r="N126" t="n">
         <v>-0.1</v>
       </c>
+      <c r="O126" t="n">
+        <v>132600</v>
+      </c>
+      <c r="P126" t="n">
+        <v>122300</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>8.4</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6479,6 +7613,15 @@
       <c r="N127" t="n">
         <v>0</v>
       </c>
+      <c r="O127" t="n">
+        <v>4355</v>
+      </c>
+      <c r="P127" t="n">
+        <v>4335</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6527,6 +7670,15 @@
       <c r="N128" t="n">
         <v>0</v>
       </c>
+      <c r="O128" t="n">
+        <v>121600</v>
+      </c>
+      <c r="P128" t="n">
+        <v>124300</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>-2.2</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6548,6 +7700,15 @@
       <c r="E129" t="n">
         <v>0</v>
       </c>
+      <c r="O129" t="n">
+        <v>12340</v>
+      </c>
+      <c r="P129" t="n">
+        <v>10740</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6596,6 +7757,15 @@
       <c r="N130" t="n">
         <v>0</v>
       </c>
+      <c r="O130" t="n">
+        <v>110200</v>
+      </c>
+      <c r="P130" t="n">
+        <v>99800</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>10.4</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6644,6 +7814,15 @@
       <c r="N131" t="n">
         <v>0.9</v>
       </c>
+      <c r="O131" t="n">
+        <v>191900</v>
+      </c>
+      <c r="P131" t="n">
+        <v>198200</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6692,6 +7871,15 @@
       <c r="N132" t="n">
         <v>0</v>
       </c>
+      <c r="O132" t="n">
+        <v>62800</v>
+      </c>
+      <c r="P132" t="n">
+        <v>62500</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6740,6 +7928,15 @@
       <c r="N133" t="n">
         <v>0.1</v>
       </c>
+      <c r="O133" t="n">
+        <v>186200</v>
+      </c>
+      <c r="P133" t="n">
+        <v>171000</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>8.9</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6788,6 +7985,15 @@
       <c r="N134" t="n">
         <v>0.8</v>
       </c>
+      <c r="O134" t="n">
+        <v>84600</v>
+      </c>
+      <c r="P134" t="n">
+        <v>85400</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>-0.9</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6836,6 +8042,15 @@
       <c r="N135" t="n">
         <v>0</v>
       </c>
+      <c r="O135" t="n">
+        <v>41400</v>
+      </c>
+      <c r="P135" t="n">
+        <v>39050</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6884,6 +8099,15 @@
       <c r="N136" t="n">
         <v>0</v>
       </c>
+      <c r="O136" t="n">
+        <v>53400</v>
+      </c>
+      <c r="P136" t="n">
+        <v>56100</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-4.8</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6932,6 +8156,15 @@
       <c r="N137" t="n">
         <v>-0.4</v>
       </c>
+      <c r="O137" t="n">
+        <v>381500</v>
+      </c>
+      <c r="P137" t="n">
+        <v>409000</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-6.7</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6980,6 +8213,15 @@
       <c r="N138" t="n">
         <v>0</v>
       </c>
+      <c r="O138" t="n">
+        <v>117000</v>
+      </c>
+      <c r="P138" t="n">
+        <v>113700</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7028,6 +8270,15 @@
       <c r="N139" t="n">
         <v>0</v>
       </c>
+      <c r="O139" t="n">
+        <v>18160</v>
+      </c>
+      <c r="P139" t="n">
+        <v>17930</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7076,6 +8327,15 @@
       <c r="N140" t="n">
         <v>-0.2</v>
       </c>
+      <c r="O140" t="n">
+        <v>18220</v>
+      </c>
+      <c r="P140" t="n">
+        <v>18090</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7124,6 +8384,15 @@
       <c r="N141" t="n">
         <v>-0.1</v>
       </c>
+      <c r="O141" t="n">
+        <v>82300</v>
+      </c>
+      <c r="P141" t="n">
+        <v>81100</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7172,6 +8441,15 @@
       <c r="N142" t="n">
         <v>0</v>
       </c>
+      <c r="O142" t="n">
+        <v>69700</v>
+      </c>
+      <c r="P142" t="n">
+        <v>73000</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>-4.5</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7220,6 +8498,15 @@
       <c r="N143" t="n">
         <v>0</v>
       </c>
+      <c r="O143" t="n">
+        <v>115800</v>
+      </c>
+      <c r="P143" t="n">
+        <v>112100</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7268,6 +8555,15 @@
       <c r="N144" t="n">
         <v>0</v>
       </c>
+      <c r="O144" t="n">
+        <v>28000</v>
+      </c>
+      <c r="P144" t="n">
+        <v>26000</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7316,6 +8612,15 @@
       <c r="N145" t="n">
         <v>0</v>
       </c>
+      <c r="O145" t="n">
+        <v>70400</v>
+      </c>
+      <c r="P145" t="n">
+        <v>69600</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7364,6 +8669,15 @@
       <c r="N146" t="n">
         <v>0</v>
       </c>
+      <c r="O146" t="n">
+        <v>61100</v>
+      </c>
+      <c r="P146" t="n">
+        <v>64500</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>-5.3</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7412,6 +8726,15 @@
       <c r="N147" t="n">
         <v>0</v>
       </c>
+      <c r="O147" t="n">
+        <v>184300</v>
+      </c>
+      <c r="P147" t="n">
+        <v>179600</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7460,6 +8783,15 @@
       <c r="N148" t="n">
         <v>0</v>
       </c>
+      <c r="O148" t="n">
+        <v>47600</v>
+      </c>
+      <c r="P148" t="n">
+        <v>48700</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>-2.3</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7508,6 +8840,15 @@
       <c r="N149" t="n">
         <v>0</v>
       </c>
+      <c r="O149" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1363000</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7556,6 +8897,15 @@
       <c r="N150" t="n">
         <v>0</v>
       </c>
+      <c r="O150" t="n">
+        <v>61600</v>
+      </c>
+      <c r="P150" t="n">
+        <v>61400</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7604,6 +8954,15 @@
       <c r="N151" t="n">
         <v>-1.7</v>
       </c>
+      <c r="O151" t="n">
+        <v>38150</v>
+      </c>
+      <c r="P151" t="n">
+        <v>38800</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>-1.7</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7652,6 +9011,15 @@
       <c r="N152" t="n">
         <v>0</v>
       </c>
+      <c r="O152" t="n">
+        <v>238000</v>
+      </c>
+      <c r="P152" t="n">
+        <v>245000</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>-2.9</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7700,6 +9068,15 @@
       <c r="N153" t="n">
         <v>0</v>
       </c>
+      <c r="O153" t="n">
+        <v>198000</v>
+      </c>
+      <c r="P153" t="n">
+        <v>193700</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7748,6 +9125,15 @@
       <c r="N154" t="n">
         <v>0.6</v>
       </c>
+      <c r="O154" t="n">
+        <v>788000</v>
+      </c>
+      <c r="P154" t="n">
+        <v>814000</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7796,6 +9182,15 @@
       <c r="N155" t="n">
         <v>1.2</v>
       </c>
+      <c r="O155" t="n">
+        <v>127000</v>
+      </c>
+      <c r="P155" t="n">
+        <v>125300</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7844,6 +9239,15 @@
       <c r="N156" t="n">
         <v>0</v>
       </c>
+      <c r="O156" t="n">
+        <v>133700</v>
+      </c>
+      <c r="P156" t="n">
+        <v>140300</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>-4.7</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7892,6 +9296,15 @@
       <c r="N157" t="n">
         <v>0</v>
       </c>
+      <c r="O157" t="n">
+        <v>66500</v>
+      </c>
+      <c r="P157" t="n">
+        <v>64900</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7940,6 +9353,15 @@
       <c r="N158" t="n">
         <v>0</v>
       </c>
+      <c r="O158" t="n">
+        <v>380000</v>
+      </c>
+      <c r="P158" t="n">
+        <v>385500</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>-1.4</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7988,6 +9410,15 @@
       <c r="N159" t="n">
         <v>0</v>
       </c>
+      <c r="O159" t="n">
+        <v>107800</v>
+      </c>
+      <c r="P159" t="n">
+        <v>105600</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8036,6 +9467,15 @@
       <c r="N160" t="n">
         <v>0.8</v>
       </c>
+      <c r="O160" t="n">
+        <v>127800</v>
+      </c>
+      <c r="P160" t="n">
+        <v>125400</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8084,6 +9524,15 @@
       <c r="N161" t="n">
         <v>0</v>
       </c>
+      <c r="O161" t="n">
+        <v>39850</v>
+      </c>
+      <c r="P161" t="n">
+        <v>40600</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8132,6 +9581,15 @@
       <c r="N162" t="n">
         <v>0</v>
       </c>
+      <c r="O162" t="n">
+        <v>272000</v>
+      </c>
+      <c r="P162" t="n">
+        <v>268000</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8180,6 +9638,15 @@
       <c r="N163" t="n">
         <v>0</v>
       </c>
+      <c r="O163" t="n">
+        <v>2666000</v>
+      </c>
+      <c r="P163" t="n">
+        <v>2689000</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>-0.9</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8228,6 +9695,15 @@
       <c r="N164" t="n">
         <v>0</v>
       </c>
+      <c r="O164" t="n">
+        <v>145000</v>
+      </c>
+      <c r="P164" t="n">
+        <v>150200</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8276,6 +9752,15 @@
       <c r="N165" t="n">
         <v>0</v>
       </c>
+      <c r="O165" t="n">
+        <v>14310</v>
+      </c>
+      <c r="P165" t="n">
+        <v>14470</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8324,6 +9809,15 @@
       <c r="N166" t="n">
         <v>0</v>
       </c>
+      <c r="O166" t="n">
+        <v>36300</v>
+      </c>
+      <c r="P166" t="n">
+        <v>37950</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>-4.3</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8372,6 +9866,15 @@
       <c r="N167" t="n">
         <v>-0.8</v>
       </c>
+      <c r="O167" t="n">
+        <v>438000</v>
+      </c>
+      <c r="P167" t="n">
+        <v>441500</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8420,6 +9923,15 @@
       <c r="N168" t="n">
         <v>-0.1</v>
       </c>
+      <c r="O168" t="n">
+        <v>31200</v>
+      </c>
+      <c r="P168" t="n">
+        <v>30700</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8468,6 +9980,15 @@
       <c r="N169" t="n">
         <v>-0.2</v>
       </c>
+      <c r="O169" t="n">
+        <v>23300</v>
+      </c>
+      <c r="P169" t="n">
+        <v>22000</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8516,6 +10037,15 @@
       <c r="N170" t="n">
         <v>-0.9</v>
       </c>
+      <c r="O170" t="n">
+        <v>79300</v>
+      </c>
+      <c r="P170" t="n">
+        <v>82100</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>-3.4</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8564,6 +10094,15 @@
       <c r="N171" t="n">
         <v>-0.3</v>
       </c>
+      <c r="O171" t="n">
+        <v>487500</v>
+      </c>
+      <c r="P171" t="n">
+        <v>517000</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>-5.7</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8612,6 +10151,15 @@
       <c r="N172" t="n">
         <v>0</v>
       </c>
+      <c r="O172" t="n">
+        <v>213000</v>
+      </c>
+      <c r="P172" t="n">
+        <v>230000</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>-7.4</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8660,6 +10208,15 @@
       <c r="N173" t="n">
         <v>0</v>
       </c>
+      <c r="O173" t="n">
+        <v>14460</v>
+      </c>
+      <c r="P173" t="n">
+        <v>14400</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8708,6 +10265,15 @@
       <c r="N174" t="n">
         <v>0</v>
       </c>
+      <c r="O174" t="n">
+        <v>328500</v>
+      </c>
+      <c r="P174" t="n">
+        <v>315500</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>4.1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8756,6 +10322,15 @@
       <c r="N175" t="n">
         <v>0.6</v>
       </c>
+      <c r="O175" t="n">
+        <v>60300</v>
+      </c>
+      <c r="P175" t="n">
+        <v>59700</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8804,6 +10379,15 @@
       <c r="N176" t="n">
         <v>0</v>
       </c>
+      <c r="O176" t="n">
+        <v>39750</v>
+      </c>
+      <c r="P176" t="n">
+        <v>38150</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>4.2</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8852,6 +10436,15 @@
       <c r="N177" t="n">
         <v>0</v>
       </c>
+      <c r="O177" t="n">
+        <v>79900</v>
+      </c>
+      <c r="P177" t="n">
+        <v>80200</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8900,6 +10493,15 @@
       <c r="N178" t="n">
         <v>0</v>
       </c>
+      <c r="O178" t="n">
+        <v>1161000</v>
+      </c>
+      <c r="P178" t="n">
+        <v>1270000</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>-8.6</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8948,6 +10550,15 @@
       <c r="N179" t="n">
         <v>0.2</v>
       </c>
+      <c r="O179" t="n">
+        <v>193600</v>
+      </c>
+      <c r="P179" t="n">
+        <v>197600</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8996,6 +10607,15 @@
       <c r="N180" t="n">
         <v>-5.6</v>
       </c>
+      <c r="O180" t="n">
+        <v>92100</v>
+      </c>
+      <c r="P180" t="n">
+        <v>83700</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9043,6 +10663,15 @@
       </c>
       <c r="N181" t="n">
         <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>199500</v>
+      </c>
+      <c r="P181" t="n">
+        <v>217500</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>-8.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-13 · 전주 2026-07-06</t>
+          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-16 · 전주 2026-07-13</t>
         </is>
       </c>
     </row>
@@ -558,46 +558,46 @@
         <v>615</v>
       </c>
       <c r="D3" t="n">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1958.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1935</v>
+        <v>1958.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>2060.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2019.7</v>
+        <v>2060.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>2183</v>
       </c>
       <c r="M3" t="n">
-        <v>2119.6</v>
+        <v>2183</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>14910</v>
+      </c>
+      <c r="P3" t="n">
         <v>14960</v>
       </c>
-      <c r="P3" t="n">
-        <v>15150</v>
-      </c>
       <c r="Q3" t="n">
-        <v>-1.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="4">
@@ -612,49 +612,49 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>612</v>
+        <v>571</v>
       </c>
       <c r="D4" t="n">
         <v>612</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-6.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1321.9</v>
+        <v>1311.3</v>
       </c>
       <c r="G4" t="n">
         <v>1321.9</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2176.3</v>
+        <v>2224.1</v>
       </c>
       <c r="J4" t="n">
         <v>2176.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="L4" t="n">
-        <v>2997.6</v>
+        <v>2994</v>
       </c>
       <c r="M4" t="n">
         <v>2997.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O4" t="n">
+        <v>70800</v>
+      </c>
+      <c r="P4" t="n">
         <v>68100</v>
       </c>
-      <c r="P4" t="n">
-        <v>69100</v>
-      </c>
       <c r="Q4" t="n">
-        <v>-1.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -672,46 +672,46 @@
         <v>1140</v>
       </c>
       <c r="D5" t="n">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>5163</v>
       </c>
       <c r="G5" t="n">
-        <v>5169.7</v>
+        <v>5163</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>5718.2</v>
       </c>
       <c r="J5" t="n">
-        <v>5729.1</v>
+        <v>5718.2</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>6160.5</v>
       </c>
       <c r="M5" t="n">
-        <v>6172.3</v>
+        <v>6160.5</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>72500</v>
+      </c>
+      <c r="P5" t="n">
         <v>73600</v>
       </c>
-      <c r="P5" t="n">
-        <v>74300</v>
-      </c>
       <c r="Q5" t="n">
-        <v>-0.9</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="6">
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>1202000</v>
+      </c>
+      <c r="P6" t="n">
         <v>1238000</v>
       </c>
-      <c r="P6" t="n">
-        <v>1268000</v>
-      </c>
       <c r="Q6" t="n">
-        <v>-2.4</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="7">
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>46450</v>
+      </c>
+      <c r="P7" t="n">
         <v>45550</v>
       </c>
-      <c r="P7" t="n">
-        <v>44300</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,13 +876,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>25250</v>
+      </c>
+      <c r="P8" t="n">
         <v>24650</v>
       </c>
-      <c r="P8" t="n">
-        <v>25600</v>
-      </c>
       <c r="Q8" t="n">
-        <v>-3.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -897,49 +897,49 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>27946</v>
+      </c>
+      <c r="D9" t="n">
         <v>27920</v>
       </c>
-      <c r="D9" t="n">
-        <v>27949</v>
-      </c>
       <c r="E9" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
+        <v>102821.2</v>
+      </c>
+      <c r="G9" t="n">
         <v>102466.9</v>
       </c>
-      <c r="G9" t="n">
-        <v>102265.5</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I9" t="n">
+        <v>113657.1</v>
+      </c>
+      <c r="J9" t="n">
         <v>113527.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>113377.6</v>
       </c>
       <c r="K9" t="n">
         <v>0.1</v>
       </c>
       <c r="L9" t="n">
+        <v>119510.4</v>
+      </c>
+      <c r="M9" t="n">
         <v>120853.9</v>
       </c>
-      <c r="M9" t="n">
-        <v>121044.4</v>
-      </c>
       <c r="N9" t="n">
-        <v>-0.2</v>
+        <v>-1.1</v>
       </c>
       <c r="O9" t="n">
+        <v>149700</v>
+      </c>
+      <c r="P9" t="n">
         <v>143500</v>
       </c>
-      <c r="P9" t="n">
-        <v>156800</v>
-      </c>
       <c r="Q9" t="n">
-        <v>-8.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="10">
@@ -954,49 +954,49 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>650541</v>
+        <v>641632</v>
       </c>
       <c r="D10" t="n">
         <v>650541</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="F10" t="n">
-        <v>2767812.5</v>
+        <v>2728835.8</v>
       </c>
       <c r="G10" t="n">
         <v>2767812.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4043634.6</v>
+        <v>3981826.7</v>
       </c>
       <c r="J10" t="n">
         <v>4043634.6</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="L10" t="n">
-        <v>3939915.6</v>
+        <v>3871437.2</v>
       </c>
       <c r="M10" t="n">
         <v>3939915.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="O10" t="n">
+        <v>1842000</v>
+      </c>
+      <c r="P10" t="n">
         <v>1845000</v>
       </c>
-      <c r="P10" t="n">
-        <v>2076000</v>
-      </c>
       <c r="Q10" t="n">
-        <v>-11.1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="11">
@@ -1023,7 +1023,7 @@
         <v>8244.4</v>
       </c>
       <c r="G11" t="n">
-        <v>8242.299999999999</v>
+        <v>8244.4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1032,28 +1032,28 @@
         <v>11142.2</v>
       </c>
       <c r="J11" t="n">
-        <v>11144</v>
+        <v>11142.2</v>
       </c>
       <c r="K11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>13878.5</v>
+      </c>
+      <c r="M11" t="n">
         <v>13845.2</v>
       </c>
-      <c r="M11" t="n">
-        <v>13889.2</v>
-      </c>
       <c r="N11" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O11" t="n">
+        <v>99000</v>
+      </c>
+      <c r="P11" t="n">
         <v>101500</v>
       </c>
-      <c r="P11" t="n">
-        <v>100700</v>
-      </c>
       <c r="Q11" t="n">
-        <v>0.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="12">
@@ -1068,49 +1068,49 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8312</v>
+        <v>8669</v>
       </c>
       <c r="D12" t="n">
         <v>8312</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="F12" t="n">
-        <v>30345.1</v>
+        <v>30745.2</v>
       </c>
       <c r="G12" t="n">
         <v>30345.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>32907.2</v>
+        <v>33631.5</v>
       </c>
       <c r="J12" t="n">
         <v>32907.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="L12" t="n">
-        <v>33721.5</v>
+        <v>34054.8</v>
       </c>
       <c r="M12" t="n">
         <v>33721.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
+        <v>701000</v>
+      </c>
+      <c r="P12" t="n">
         <v>639000</v>
       </c>
-      <c r="P12" t="n">
-        <v>671000</v>
-      </c>
       <c r="Q12" t="n">
-        <v>-4.8</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1134,22 +1134,22 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>56369.3</v>
+        <v>55718.1</v>
       </c>
       <c r="G13" t="n">
         <v>56369.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>69187.3</v>
+        <v>67947</v>
       </c>
       <c r="J13" t="n">
         <v>69187.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="L13" t="n">
         <v>72135</v>
@@ -1161,13 +1161,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>93200</v>
+      </c>
+      <c r="P13" t="n">
         <v>92300</v>
       </c>
-      <c r="P13" t="n">
-        <v>93400</v>
-      </c>
       <c r="Q13" t="n">
-        <v>-1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>109600</v>
+      </c>
+      <c r="P14" t="n">
         <v>110700</v>
-      </c>
-      <c r="P14" t="n">
-        <v>111800</v>
       </c>
       <c r="Q14" t="n">
         <v>-1</v>
@@ -1275,13 +1275,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>135700</v>
+      </c>
+      <c r="P15" t="n">
         <v>142600</v>
       </c>
-      <c r="P15" t="n">
-        <v>142300</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.2</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="16">
@@ -1296,49 +1296,49 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>516</v>
+      </c>
+      <c r="D16" t="n">
         <v>508</v>
       </c>
-      <c r="D16" t="n">
-        <v>513</v>
-      </c>
       <c r="E16" t="n">
-        <v>-1</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="n">
+        <v>1504</v>
+      </c>
+      <c r="G16" t="n">
         <v>1464.4</v>
       </c>
-      <c r="G16" t="n">
-        <v>1452.7</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="I16" t="n">
+        <v>2024.1</v>
+      </c>
+      <c r="J16" t="n">
         <v>2038.9</v>
       </c>
-      <c r="J16" t="n">
-        <v>2000.3</v>
-      </c>
       <c r="K16" t="n">
-        <v>1.9</v>
+        <v>-0.7</v>
       </c>
       <c r="L16" t="n">
+        <v>2335.4</v>
+      </c>
+      <c r="M16" t="n">
         <v>2062.4</v>
       </c>
-      <c r="M16" t="n">
-        <v>2036.9</v>
-      </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="O16" t="n">
+        <v>32500</v>
+      </c>
+      <c r="P16" t="n">
         <v>30250</v>
       </c>
-      <c r="P16" t="n">
-        <v>30150</v>
-      </c>
       <c r="Q16" t="n">
-        <v>0.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17">
@@ -1353,49 +1353,49 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D17" t="n">
         <v>426</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="F17" t="n">
-        <v>1963.7</v>
+        <v>1995.6</v>
       </c>
       <c r="G17" t="n">
         <v>1963.7</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2356.2</v>
+        <v>2252.9</v>
       </c>
       <c r="J17" t="n">
         <v>2356.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="L17" t="n">
-        <v>3058</v>
+        <v>2899.4</v>
       </c>
       <c r="M17" t="n">
         <v>3058</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-5.2</v>
       </c>
       <c r="O17" t="n">
+        <v>27700</v>
+      </c>
+      <c r="P17" t="n">
         <v>28300</v>
       </c>
-      <c r="P17" t="n">
-        <v>28200</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0.4</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="18">
@@ -1410,40 +1410,40 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10434.4</v>
+        <v>10521.3</v>
       </c>
       <c r="G18" t="n">
         <v>10434.4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I18" t="n">
-        <v>12149.2</v>
+        <v>12179.5</v>
       </c>
       <c r="J18" t="n">
         <v>12149.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L18" t="n">
-        <v>13426.9</v>
+        <v>13329</v>
       </c>
       <c r="M18" t="n">
         <v>13426.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O18" t="n">
+        <v>38300</v>
+      </c>
+      <c r="P18" t="n">
         <v>38550</v>
       </c>
-      <c r="P18" t="n">
-        <v>37950</v>
-      </c>
       <c r="Q18" t="n">
-        <v>1.6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="19">
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
+        <v>17260</v>
+      </c>
+      <c r="P19" t="n">
         <v>17500</v>
       </c>
-      <c r="P19" t="n">
-        <v>17550</v>
-      </c>
       <c r="Q19" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="20">
@@ -1533,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
+        <v>26050</v>
+      </c>
+      <c r="P20" t="n">
         <v>26800</v>
       </c>
-      <c r="P20" t="n">
-        <v>26050</v>
-      </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="21">
@@ -1590,13 +1590,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>420000</v>
+      </c>
+      <c r="P21" t="n">
         <v>434000</v>
       </c>
-      <c r="P21" t="n">
-        <v>447500</v>
-      </c>
       <c r="Q21" t="n">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="22">
@@ -1647,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>99600</v>
+      </c>
+      <c r="P22" t="n">
         <v>103700</v>
       </c>
-      <c r="P22" t="n">
-        <v>105100</v>
-      </c>
       <c r="Q22" t="n">
-        <v>-1.3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="23">
@@ -1668,49 +1668,49 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1786</v>
+      </c>
+      <c r="D23" t="n">
         <v>1790</v>
       </c>
-      <c r="D23" t="n">
-        <v>1767</v>
-      </c>
       <c r="E23" t="n">
-        <v>1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="F23" t="n">
+        <v>7296.7</v>
+      </c>
+      <c r="G23" t="n">
         <v>7298.4</v>
       </c>
-      <c r="G23" t="n">
-        <v>7269.1</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.4</v>
+        <v>-0</v>
       </c>
       <c r="I23" t="n">
+        <v>8769.6</v>
+      </c>
+      <c r="J23" t="n">
         <v>8765.200000000001</v>
       </c>
-      <c r="J23" t="n">
-        <v>8732.5</v>
-      </c>
       <c r="K23" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L23" t="n">
+        <v>10286.4</v>
+      </c>
+      <c r="M23" t="n">
         <v>10284.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>10306.5</v>
-      </c>
       <c r="N23" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>1069000</v>
+      </c>
+      <c r="P23" t="n">
         <v>1110000</v>
       </c>
-      <c r="P23" t="n">
-        <v>1146000</v>
-      </c>
       <c r="Q23" t="n">
-        <v>-3.1</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="24">
@@ -1725,49 +1725,49 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-2207</v>
+        <v>-2377</v>
       </c>
       <c r="D24" t="n">
         <v>-2207</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-7.7</v>
       </c>
       <c r="F24" t="n">
-        <v>8666.299999999999</v>
+        <v>11051.5</v>
       </c>
       <c r="G24" t="n">
         <v>8666.299999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="I24" t="n">
-        <v>20882.1</v>
+        <v>22324.6</v>
       </c>
       <c r="J24" t="n">
         <v>20882.1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="L24" t="n">
-        <v>25171.4</v>
+        <v>26471.7</v>
       </c>
       <c r="M24" t="n">
         <v>25171.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O24" t="n">
+        <v>26500</v>
+      </c>
+      <c r="P24" t="n">
         <v>25850</v>
       </c>
-      <c r="P24" t="n">
-        <v>28150</v>
-      </c>
       <c r="Q24" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -1818,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
+        <v>98800</v>
+      </c>
+      <c r="P25" t="n">
         <v>99300</v>
       </c>
-      <c r="P25" t="n">
-        <v>102500</v>
-      </c>
       <c r="Q25" t="n">
-        <v>-3.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="26">
@@ -1839,49 +1839,49 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>292</v>
+      </c>
+      <c r="D26" t="n">
         <v>283</v>
       </c>
-      <c r="D26" t="n">
-        <v>284</v>
-      </c>
       <c r="E26" t="n">
-        <v>-0.4</v>
+        <v>3.2</v>
       </c>
       <c r="F26" t="n">
+        <v>997.3</v>
+      </c>
+      <c r="G26" t="n">
         <v>952.8</v>
       </c>
-      <c r="G26" t="n">
-        <v>955.3</v>
-      </c>
       <c r="H26" t="n">
-        <v>-0.3</v>
+        <v>4.7</v>
       </c>
       <c r="I26" t="n">
+        <v>1648.4</v>
+      </c>
+      <c r="J26" t="n">
         <v>1606.5</v>
       </c>
-      <c r="J26" t="n">
-        <v>1620.8</v>
-      </c>
       <c r="K26" t="n">
-        <v>-0.9</v>
+        <v>2.6</v>
       </c>
       <c r="L26" t="n">
+        <v>2856.9</v>
+      </c>
+      <c r="M26" t="n">
         <v>2814.7</v>
       </c>
-      <c r="M26" t="n">
-        <v>2823.6</v>
-      </c>
       <c r="N26" t="n">
-        <v>-0.3</v>
+        <v>1.5</v>
       </c>
       <c r="O26" t="n">
+        <v>147600</v>
+      </c>
+      <c r="P26" t="n">
         <v>150700</v>
       </c>
-      <c r="P26" t="n">
-        <v>144700</v>
-      </c>
       <c r="Q26" t="n">
-        <v>4.1</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="27">
@@ -1932,13 +1932,13 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
+        <v>45650</v>
+      </c>
+      <c r="P27" t="n">
         <v>46000</v>
       </c>
-      <c r="P27" t="n">
-        <v>43350</v>
-      </c>
       <c r="Q27" t="n">
-        <v>6.1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="28">
@@ -1953,49 +1953,49 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>866</v>
+      </c>
+      <c r="D28" t="n">
         <v>1027</v>
       </c>
-      <c r="D28" t="n">
-        <v>1038</v>
-      </c>
       <c r="E28" t="n">
-        <v>-1.1</v>
+        <v>-15.7</v>
       </c>
       <c r="F28" t="n">
+        <v>4077.3</v>
+      </c>
+      <c r="G28" t="n">
         <v>4371.2</v>
       </c>
-      <c r="G28" t="n">
-        <v>4357.2</v>
-      </c>
       <c r="H28" t="n">
-        <v>0.3</v>
+        <v>-6.7</v>
       </c>
       <c r="I28" t="n">
+        <v>7113.6</v>
+      </c>
+      <c r="J28" t="n">
         <v>7567</v>
       </c>
-      <c r="J28" t="n">
-        <v>7439.7</v>
-      </c>
       <c r="K28" t="n">
-        <v>1.7</v>
+        <v>-6</v>
       </c>
       <c r="L28" t="n">
+        <v>8048.5</v>
+      </c>
+      <c r="M28" t="n">
         <v>8315.4</v>
       </c>
-      <c r="M28" t="n">
-        <v>8169.2</v>
-      </c>
       <c r="N28" t="n">
-        <v>1.8</v>
+        <v>-3.2</v>
       </c>
       <c r="O28" t="n">
+        <v>26550</v>
+      </c>
+      <c r="P28" t="n">
         <v>26800</v>
       </c>
-      <c r="P28" t="n">
-        <v>26900</v>
-      </c>
       <c r="Q28" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="29">
@@ -2010,49 +2010,49 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1502</v>
+        <v>1526</v>
       </c>
       <c r="D29" t="n">
         <v>1502</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="F29" t="n">
-        <v>7610.5</v>
+        <v>7675.2</v>
       </c>
       <c r="G29" t="n">
         <v>7610.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I29" t="n">
-        <v>8508.299999999999</v>
+        <v>8596.9</v>
       </c>
       <c r="J29" t="n">
         <v>8508.299999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>8956</v>
+        <v>9078.200000000001</v>
       </c>
       <c r="M29" t="n">
         <v>8956</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O29" t="n">
+        <v>589000</v>
+      </c>
+      <c r="P29" t="n">
         <v>591000</v>
       </c>
-      <c r="P29" t="n">
-        <v>625000</v>
-      </c>
       <c r="Q29" t="n">
-        <v>-5.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="30">
@@ -2067,49 +2067,49 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>492</v>
+      </c>
+      <c r="D30" t="n">
         <v>485</v>
       </c>
-      <c r="D30" t="n">
-        <v>484</v>
-      </c>
       <c r="E30" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="F30" t="n">
+        <v>2144</v>
+      </c>
+      <c r="G30" t="n">
         <v>2133.8</v>
       </c>
-      <c r="G30" t="n">
-        <v>2120.6</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I30" t="n">
+        <v>2321.7</v>
+      </c>
+      <c r="J30" t="n">
         <v>2307.4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2292.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.6</v>
       </c>
       <c r="L30" t="n">
+        <v>2454.5</v>
+      </c>
+      <c r="M30" t="n">
         <v>2449.6</v>
       </c>
-      <c r="M30" t="n">
-        <v>2433.3</v>
-      </c>
       <c r="N30" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="O30" t="n">
+        <v>349500</v>
+      </c>
+      <c r="P30" t="n">
         <v>356000</v>
       </c>
-      <c r="P30" t="n">
-        <v>362000</v>
-      </c>
       <c r="Q30" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="31">
@@ -2160,13 +2160,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
+        <v>22800</v>
+      </c>
+      <c r="P31" t="n">
         <v>23050</v>
       </c>
-      <c r="P31" t="n">
-        <v>24000</v>
-      </c>
       <c r="Q31" t="n">
-        <v>-4</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="32">
@@ -2181,49 +2181,49 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>647</v>
+      </c>
+      <c r="D32" t="n">
         <v>651</v>
       </c>
-      <c r="D32" t="n">
-        <v>631</v>
-      </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>-0.6</v>
       </c>
       <c r="F32" t="n">
+        <v>2131.6</v>
+      </c>
+      <c r="G32" t="n">
         <v>2138.2</v>
       </c>
-      <c r="G32" t="n">
-        <v>2130.5</v>
-      </c>
       <c r="H32" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="I32" t="n">
+        <v>2351.1</v>
+      </c>
+      <c r="J32" t="n">
         <v>2364.6</v>
       </c>
-      <c r="J32" t="n">
-        <v>2350.3</v>
-      </c>
       <c r="K32" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
       <c r="L32" t="n">
+        <v>2484.3</v>
+      </c>
+      <c r="M32" t="n">
         <v>2497</v>
       </c>
-      <c r="M32" t="n">
-        <v>2458.2</v>
-      </c>
       <c r="N32" t="n">
-        <v>1.6</v>
+        <v>-0.5</v>
       </c>
       <c r="O32" t="n">
+        <v>99400</v>
+      </c>
+      <c r="P32" t="n">
         <v>101600</v>
       </c>
-      <c r="P32" t="n">
-        <v>100500</v>
-      </c>
       <c r="Q32" t="n">
-        <v>1.1</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="33">
@@ -2238,49 +2238,49 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>30293</v>
+      </c>
+      <c r="D33" t="n">
         <v>31086</v>
       </c>
-      <c r="D33" t="n">
-        <v>31377</v>
-      </c>
       <c r="E33" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>117983.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>118721.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>132991</v>
+      </c>
+      <c r="J33" t="n">
+        <v>133560</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>145128.6</v>
+      </c>
+      <c r="M33" t="n">
+        <v>146466.8</v>
+      </c>
+      <c r="N33" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F33" t="n">
-        <v>118721.8</v>
-      </c>
-      <c r="G33" t="n">
-        <v>119102.2</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="I33" t="n">
-        <v>133560</v>
-      </c>
-      <c r="J33" t="n">
-        <v>133173.4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>146466.8</v>
-      </c>
-      <c r="M33" t="n">
-        <v>145756.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.5</v>
-      </c>
       <c r="O33" t="n">
+        <v>425000</v>
+      </c>
+      <c r="P33" t="n">
         <v>444000</v>
       </c>
-      <c r="P33" t="n">
-        <v>462500</v>
-      </c>
       <c r="Q33" t="n">
-        <v>-4</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="34">
@@ -2295,49 +2295,49 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>7241</v>
+      </c>
+      <c r="D34" t="n">
         <v>7419</v>
       </c>
-      <c r="D34" t="n">
-        <v>7489</v>
-      </c>
       <c r="E34" t="n">
-        <v>-0.9</v>
+        <v>-2.4</v>
       </c>
       <c r="F34" t="n">
+        <v>30676.6</v>
+      </c>
+      <c r="G34" t="n">
         <v>31078.4</v>
       </c>
-      <c r="G34" t="n">
-        <v>31736.7</v>
-      </c>
       <c r="H34" t="n">
-        <v>-2.1</v>
+        <v>-1.3</v>
       </c>
       <c r="I34" t="n">
+        <v>38245.5</v>
+      </c>
+      <c r="J34" t="n">
         <v>38922.9</v>
       </c>
-      <c r="J34" t="n">
-        <v>40076.2</v>
-      </c>
       <c r="K34" t="n">
-        <v>-2.9</v>
+        <v>-1.7</v>
       </c>
       <c r="L34" t="n">
+        <v>44284.7</v>
+      </c>
+      <c r="M34" t="n">
         <v>44719.4</v>
       </c>
-      <c r="M34" t="n">
-        <v>45608.8</v>
-      </c>
       <c r="N34" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O34" t="n">
+        <v>311500</v>
+      </c>
+      <c r="P34" t="n">
         <v>308000</v>
       </c>
-      <c r="P34" t="n">
-        <v>304000</v>
-      </c>
       <c r="Q34" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="35">
@@ -2361,40 +2361,40 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>21132.5</v>
+        <v>21293.7</v>
       </c>
       <c r="G35" t="n">
         <v>21132.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>23517.5</v>
+        <v>23130.1</v>
       </c>
       <c r="J35" t="n">
         <v>23517.5</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="L35" t="n">
-        <v>25037.6</v>
+        <v>24397.6</v>
       </c>
       <c r="M35" t="n">
         <v>25037.6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="O35" t="n">
+        <v>163000</v>
+      </c>
+      <c r="P35" t="n">
         <v>159100</v>
       </c>
-      <c r="P35" t="n">
-        <v>151400</v>
-      </c>
       <c r="Q35" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="36">
@@ -2445,13 +2445,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
+        <v>54400</v>
+      </c>
+      <c r="P36" t="n">
         <v>54200</v>
       </c>
-      <c r="P36" t="n">
-        <v>57400</v>
-      </c>
       <c r="Q36" t="n">
-        <v>-5.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37">
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>3832403.5</v>
+        <v>3832403.6</v>
       </c>
       <c r="G37" t="n">
         <v>3832403.5</v>
@@ -2484,13 +2484,13 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5422607.5</v>
+        <v>5422607.3</v>
       </c>
       <c r="J37" t="n">
         <v>5422607.5</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L37" t="n">
         <v>5327749.5</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
+        <v>255000</v>
+      </c>
+      <c r="P37" t="n">
         <v>254500</v>
       </c>
-      <c r="P37" t="n">
-        <v>277500</v>
-      </c>
       <c r="Q37" t="n">
-        <v>-8.300000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="38">
@@ -2526,28 +2526,28 @@
         <v>6194</v>
       </c>
       <c r="D38" t="n">
-        <v>6107</v>
+        <v>6194</v>
       </c>
       <c r="E38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>21770.4</v>
       </c>
       <c r="G38" t="n">
-        <v>21714.4</v>
+        <v>21770.4</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>19816.4</v>
       </c>
       <c r="J38" t="n">
-        <v>19715.2</v>
+        <v>19816.4</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>19922.1</v>
@@ -2559,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
+        <v>31000</v>
+      </c>
+      <c r="P38" t="n">
         <v>31150</v>
       </c>
-      <c r="P38" t="n">
-        <v>30650</v>
-      </c>
       <c r="Q38" t="n">
-        <v>1.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="39">
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
+        <v>33350</v>
+      </c>
+      <c r="P39" t="n">
         <v>34500</v>
       </c>
-      <c r="P39" t="n">
-        <v>35100</v>
-      </c>
       <c r="Q39" t="n">
-        <v>-1.7</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="40">
@@ -2646,40 +2646,40 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>16669</v>
+        <v>16923.6</v>
       </c>
       <c r="G40" t="n">
         <v>16669</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I40" t="n">
-        <v>18990.1</v>
+        <v>19159.2</v>
       </c>
       <c r="J40" t="n">
         <v>18990.1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L40" t="n">
-        <v>21819.9</v>
+        <v>21845.4</v>
       </c>
       <c r="M40" t="n">
         <v>21819.9</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O40" t="n">
+        <v>288000</v>
+      </c>
+      <c r="P40" t="n">
         <v>303500</v>
       </c>
-      <c r="P40" t="n">
-        <v>308500</v>
-      </c>
       <c r="Q40" t="n">
-        <v>-1.6</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="41">
@@ -2730,13 +2730,13 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
+        <v>122800</v>
+      </c>
+      <c r="P41" t="n">
         <v>120500</v>
       </c>
-      <c r="P41" t="n">
-        <v>121200</v>
-      </c>
       <c r="Q41" t="n">
-        <v>-0.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="42">
@@ -2751,22 +2751,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-523</v>
+        <v>-449</v>
       </c>
       <c r="D42" t="n">
         <v>-523</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="F42" t="n">
-        <v>82.7</v>
+        <v>217.5</v>
       </c>
       <c r="G42" t="n">
         <v>82.7</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="I42" t="n">
         <v>14829.6</v>
@@ -2787,13 +2787,13 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
+        <v>434500</v>
+      </c>
+      <c r="P42" t="n">
         <v>440000</v>
       </c>
-      <c r="P42" t="n">
-        <v>412000</v>
-      </c>
       <c r="Q42" t="n">
-        <v>6.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="43">
@@ -2844,13 +2844,13 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
+        <v>105400</v>
+      </c>
+      <c r="P43" t="n">
         <v>105600</v>
       </c>
-      <c r="P43" t="n">
-        <v>102600</v>
-      </c>
       <c r="Q43" t="n">
-        <v>2.9</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="44">
@@ -2865,49 +2865,49 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>19098</v>
+      </c>
+      <c r="D44" t="n">
         <v>19019</v>
       </c>
-      <c r="D44" t="n">
-        <v>18359</v>
-      </c>
       <c r="E44" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="F44" t="n">
+        <v>42131.5</v>
+      </c>
+      <c r="G44" t="n">
         <v>41655.9</v>
       </c>
-      <c r="G44" t="n">
-        <v>41243</v>
-      </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I44" t="n">
+        <v>27027.3</v>
+      </c>
+      <c r="J44" t="n">
         <v>26985.4</v>
       </c>
-      <c r="J44" t="n">
-        <v>26789.7</v>
-      </c>
       <c r="K44" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="L44" t="n">
-        <v>27554.5</v>
+        <v>27637.9</v>
       </c>
       <c r="M44" t="n">
         <v>27554.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O44" t="n">
+        <v>40050</v>
+      </c>
+      <c r="P44" t="n">
         <v>40000</v>
       </c>
-      <c r="P44" t="n">
-        <v>40500</v>
-      </c>
       <c r="Q44" t="n">
-        <v>-1.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
@@ -2922,49 +2922,49 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D45" t="n">
         <v>1018</v>
       </c>
-      <c r="D45" t="n">
-        <v>1019</v>
-      </c>
       <c r="E45" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="F45" t="n">
+        <v>3481.6</v>
+      </c>
+      <c r="G45" t="n">
         <v>3470.8</v>
       </c>
-      <c r="G45" t="n">
-        <v>3474.3</v>
-      </c>
       <c r="H45" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I45" t="n">
+        <v>3743.9</v>
+      </c>
+      <c r="J45" t="n">
         <v>3736.8</v>
       </c>
-      <c r="J45" t="n">
-        <v>3735.5</v>
-      </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L45" t="n">
+        <v>3883</v>
+      </c>
+      <c r="M45" t="n">
         <v>3886.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3891.1</v>
       </c>
       <c r="N45" t="n">
         <v>-0.1</v>
       </c>
       <c r="O45" t="n">
+        <v>26400</v>
+      </c>
+      <c r="P45" t="n">
         <v>26600</v>
       </c>
-      <c r="P45" t="n">
-        <v>25050</v>
-      </c>
       <c r="Q45" t="n">
-        <v>6.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="46">
@@ -2979,49 +2979,49 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1401</v>
+        <v>1461</v>
       </c>
       <c r="D46" t="n">
         <v>1401</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="F46" t="n">
-        <v>5719.5</v>
+        <v>5836.5</v>
       </c>
       <c r="G46" t="n">
         <v>5719.5</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>6499.5</v>
+        <v>6604.5</v>
       </c>
       <c r="J46" t="n">
         <v>6499.5</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L46" t="n">
-        <v>7120</v>
+        <v>7196.5</v>
       </c>
       <c r="M46" t="n">
         <v>7120</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O46" t="n">
+        <v>40800</v>
+      </c>
+      <c r="P46" t="n">
         <v>37900</v>
       </c>
-      <c r="P46" t="n">
-        <v>35400</v>
-      </c>
       <c r="Q46" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="47">
@@ -3036,49 +3036,49 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>751</v>
+      </c>
+      <c r="D47" t="n">
         <v>746</v>
       </c>
-      <c r="D47" t="n">
-        <v>742</v>
-      </c>
       <c r="E47" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F47" t="n">
+        <v>3272.1</v>
+      </c>
+      <c r="G47" t="n">
         <v>3259</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3244.5</v>
       </c>
       <c r="H47" t="n">
         <v>0.4</v>
       </c>
       <c r="I47" t="n">
+        <v>4603.5</v>
+      </c>
+      <c r="J47" t="n">
         <v>4554.5</v>
       </c>
-      <c r="J47" t="n">
-        <v>4495.9</v>
-      </c>
       <c r="K47" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="L47" t="n">
+        <v>5890.1</v>
+      </c>
+      <c r="M47" t="n">
         <v>5798.5</v>
       </c>
-      <c r="M47" t="n">
-        <v>5694.8</v>
-      </c>
       <c r="N47" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O47" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P47" t="n">
         <v>99600</v>
       </c>
-      <c r="P47" t="n">
-        <v>87800</v>
-      </c>
       <c r="Q47" t="n">
-        <v>13.4</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="48">
@@ -3120,13 +3120,13 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
+        <v>13480</v>
+      </c>
+      <c r="P48" t="n">
         <v>13970</v>
       </c>
-      <c r="P48" t="n">
-        <v>13950</v>
-      </c>
       <c r="Q48" t="n">
-        <v>0.1</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="49">
@@ -3144,46 +3144,46 @@
         <v>531</v>
       </c>
       <c r="D49" t="n">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="E49" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>1805.1</v>
       </c>
       <c r="G49" t="n">
-        <v>1760.9</v>
+        <v>1805.1</v>
       </c>
       <c r="H49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>2301.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2249.2</v>
+        <v>2301.7</v>
       </c>
       <c r="K49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>2678.5</v>
       </c>
       <c r="M49" t="n">
-        <v>2685.3</v>
+        <v>2678.5</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
+        <v>47800</v>
+      </c>
+      <c r="P49" t="n">
         <v>49750</v>
       </c>
-      <c r="P49" t="n">
-        <v>51500</v>
-      </c>
       <c r="Q49" t="n">
-        <v>-3.4</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="50">
@@ -3234,13 +3234,13 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
+        <v>1277000</v>
+      </c>
+      <c r="P50" t="n">
         <v>1289000</v>
       </c>
-      <c r="P50" t="n">
-        <v>1479000</v>
-      </c>
       <c r="Q50" t="n">
-        <v>-12.8</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="51">
@@ -3291,13 +3291,13 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
+        <v>35400</v>
+      </c>
+      <c r="P51" t="n">
         <v>34800</v>
       </c>
-      <c r="P51" t="n">
-        <v>34300</v>
-      </c>
       <c r="Q51" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="52">
@@ -3348,13 +3348,13 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
+        <v>52800</v>
+      </c>
+      <c r="P52" t="n">
         <v>55200</v>
       </c>
-      <c r="P52" t="n">
-        <v>58700</v>
-      </c>
       <c r="Q52" t="n">
-        <v>-6</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="53">
@@ -3369,49 +3369,49 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>14211</v>
+        <v>14693</v>
       </c>
       <c r="D53" t="n">
         <v>14211</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="F53" t="n">
-        <v>56417.8</v>
+        <v>57969.2</v>
       </c>
       <c r="G53" t="n">
         <v>56417.8</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I53" t="n">
-        <v>67968.8</v>
+        <v>69012.2</v>
       </c>
       <c r="J53" t="n">
         <v>67968.8</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L53" t="n">
-        <v>78474.8</v>
+        <v>80641.10000000001</v>
       </c>
       <c r="M53" t="n">
         <v>78474.8</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O53" t="n">
+        <v>354000</v>
+      </c>
+      <c r="P53" t="n">
         <v>341500</v>
       </c>
-      <c r="P53" t="n">
-        <v>340000</v>
-      </c>
       <c r="Q53" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="54">
@@ -3429,46 +3429,46 @@
         <v>1804</v>
       </c>
       <c r="D54" t="n">
-        <v>1792</v>
+        <v>1804</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>7641.5</v>
       </c>
       <c r="G54" t="n">
-        <v>7617.8</v>
+        <v>7641.5</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>12300.9</v>
       </c>
       <c r="J54" t="n">
-        <v>12306.4</v>
+        <v>12300.9</v>
       </c>
       <c r="K54" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>15192.5</v>
       </c>
       <c r="M54" t="n">
-        <v>15132.3</v>
+        <v>15192.5</v>
       </c>
       <c r="N54" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
+        <v>27600</v>
+      </c>
+      <c r="P54" t="n">
         <v>32000</v>
       </c>
-      <c r="P54" t="n">
-        <v>29850</v>
-      </c>
       <c r="Q54" t="n">
-        <v>7.2</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="55">
@@ -3483,49 +3483,49 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="D55" t="n">
         <v>1213</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F55" t="n">
-        <v>3751.4</v>
+        <v>3787.1</v>
       </c>
       <c r="G55" t="n">
         <v>3751.4</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>5370.1</v>
+        <v>5418.3</v>
       </c>
       <c r="J55" t="n">
         <v>5370.1</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L55" t="n">
-        <v>6603.2</v>
+        <v>6630.9</v>
       </c>
       <c r="M55" t="n">
         <v>6603.2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O55" t="n">
+        <v>194300</v>
+      </c>
+      <c r="P55" t="n">
         <v>204500</v>
       </c>
-      <c r="P55" t="n">
-        <v>180500</v>
-      </c>
       <c r="Q55" t="n">
-        <v>13.3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="56">
@@ -3540,49 +3540,49 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1590</v>
+        <v>1607</v>
       </c>
       <c r="D56" t="n">
         <v>1590</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F56" t="n">
-        <v>6602.2</v>
+        <v>6627.8</v>
       </c>
       <c r="G56" t="n">
         <v>6602.2</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I56" t="n">
-        <v>9331.700000000001</v>
+        <v>9288.200000000001</v>
       </c>
       <c r="J56" t="n">
         <v>9331.700000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L56" t="n">
-        <v>12279.5</v>
+        <v>12036.9</v>
       </c>
       <c r="M56" t="n">
         <v>12279.5</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O56" t="n">
+        <v>190000</v>
+      </c>
+      <c r="P56" t="n">
         <v>184500</v>
       </c>
-      <c r="P56" t="n">
-        <v>183500</v>
-      </c>
       <c r="Q56" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3600,46 +3600,46 @@
         <v>5918</v>
       </c>
       <c r="D57" t="n">
-        <v>5765</v>
+        <v>5918</v>
       </c>
       <c r="E57" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>23854.4</v>
       </c>
       <c r="G57" t="n">
-        <v>23035.3</v>
+        <v>23854.4</v>
       </c>
       <c r="H57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>21792.2</v>
       </c>
       <c r="J57" t="n">
-        <v>21193.5</v>
+        <v>21792.2</v>
       </c>
       <c r="K57" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>23102.8</v>
       </c>
       <c r="M57" t="n">
-        <v>22422.2</v>
+        <v>23102.8</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
+        <v>1029000</v>
+      </c>
+      <c r="P57" t="n">
         <v>1025000</v>
       </c>
-      <c r="P57" t="n">
-        <v>1034000</v>
-      </c>
       <c r="Q57" t="n">
-        <v>-0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="58">
@@ -3654,49 +3654,49 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3902</v>
+        <v>3735</v>
       </c>
       <c r="D58" t="n">
         <v>3902</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="F58" t="n">
+        <v>14605.2</v>
+      </c>
+      <c r="G58" t="n">
         <v>14956.6</v>
       </c>
-      <c r="G58" t="n">
-        <v>14993.6</v>
-      </c>
       <c r="H58" t="n">
-        <v>-0.2</v>
+        <v>-2.3</v>
       </c>
       <c r="I58" t="n">
+        <v>20139.2</v>
+      </c>
+      <c r="J58" t="n">
         <v>20358</v>
       </c>
-      <c r="J58" t="n">
-        <v>20241</v>
-      </c>
       <c r="K58" t="n">
-        <v>0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="L58" t="n">
+        <v>23690.3</v>
+      </c>
+      <c r="M58" t="n">
         <v>23869.4</v>
       </c>
-      <c r="M58" t="n">
-        <v>23704.1</v>
-      </c>
       <c r="N58" t="n">
-        <v>0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="O58" t="n">
+        <v>22300</v>
+      </c>
+      <c r="P58" t="n">
         <v>22050</v>
       </c>
-      <c r="P58" t="n">
-        <v>21150</v>
-      </c>
       <c r="Q58" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="59">
@@ -3711,49 +3711,49 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9415</v>
+        <v>9592</v>
       </c>
       <c r="D59" t="n">
         <v>9415</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F59" t="n">
-        <v>35619.5</v>
+        <v>35895.3</v>
       </c>
       <c r="G59" t="n">
         <v>35619.5</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I59" t="n">
-        <v>24566.4</v>
+        <v>26366.1</v>
       </c>
       <c r="J59" t="n">
         <v>24566.4</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="L59" t="n">
-        <v>22576.3</v>
+        <v>23703.9</v>
       </c>
       <c r="M59" t="n">
         <v>22576.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
+        <v>144900</v>
+      </c>
+      <c r="P59" t="n">
         <v>139500</v>
       </c>
-      <c r="P59" t="n">
-        <v>131600</v>
-      </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="60">
@@ -3804,13 +3804,13 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
+        <v>668000</v>
+      </c>
+      <c r="P60" t="n">
         <v>661000</v>
       </c>
-      <c r="P60" t="n">
-        <v>763000</v>
-      </c>
       <c r="Q60" t="n">
-        <v>-13.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="61">
@@ -3861,13 +3861,13 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
+        <v>61000</v>
+      </c>
+      <c r="P61" t="n">
         <v>60600</v>
       </c>
-      <c r="P61" t="n">
-        <v>60700</v>
-      </c>
       <c r="Q61" t="n">
-        <v>-0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="62">
@@ -3882,31 +3882,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3182</v>
+        <v>3275</v>
       </c>
       <c r="D62" t="n">
         <v>3182</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="F62" t="n">
-        <v>11608</v>
+        <v>11807.9</v>
       </c>
       <c r="G62" t="n">
         <v>11608</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I62" t="n">
-        <v>8554.9</v>
+        <v>8617.9</v>
       </c>
       <c r="J62" t="n">
         <v>8554.9</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L62" t="n">
         <v>9030.200000000001</v>
@@ -3918,13 +3918,13 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
+        <v>20050</v>
+      </c>
+      <c r="P62" t="n">
         <v>19550</v>
       </c>
-      <c r="P62" t="n">
-        <v>20050</v>
-      </c>
       <c r="Q62" t="n">
-        <v>-2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="63">
@@ -3939,49 +3939,49 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>576</v>
+        <v>530</v>
       </c>
       <c r="D63" t="n">
         <v>576</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="F63" t="n">
-        <v>2314.2</v>
+        <v>2256.9</v>
       </c>
       <c r="G63" t="n">
         <v>2314.2</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="I63" t="n">
-        <v>2836.9</v>
+        <v>2802.8</v>
       </c>
       <c r="J63" t="n">
         <v>2836.9</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="L63" t="n">
-        <v>3126.8</v>
+        <v>3111.2</v>
       </c>
       <c r="M63" t="n">
         <v>3126.8</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O63" t="n">
+        <v>57600</v>
+      </c>
+      <c r="P63" t="n">
         <v>59900</v>
       </c>
-      <c r="P63" t="n">
-        <v>60600</v>
-      </c>
       <c r="Q63" t="n">
-        <v>-1.2</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="64">
@@ -3996,49 +3996,49 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1401</v>
+        <v>1437</v>
       </c>
       <c r="D64" t="n">
         <v>1401</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="F64" t="n">
-        <v>3904.6</v>
+        <v>3948.2</v>
       </c>
       <c r="G64" t="n">
         <v>3904.6</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>4430.3</v>
+        <v>4448.1</v>
       </c>
       <c r="J64" t="n">
         <v>4430.3</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L64" t="n">
-        <v>4902.9</v>
+        <v>4909.2</v>
       </c>
       <c r="M64" t="n">
         <v>4902.9</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O64" t="n">
+        <v>123500</v>
+      </c>
+      <c r="P64" t="n">
         <v>117400</v>
       </c>
-      <c r="P64" t="n">
-        <v>112500</v>
-      </c>
       <c r="Q64" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="65">
@@ -4089,13 +4089,13 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
+        <v>85200</v>
+      </c>
+      <c r="P65" t="n">
         <v>88000</v>
       </c>
-      <c r="P65" t="n">
-        <v>88700</v>
-      </c>
       <c r="Q65" t="n">
-        <v>-0.8</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="66">
@@ -4110,49 +4110,49 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>9096</v>
+      </c>
+      <c r="D66" t="n">
         <v>9088</v>
       </c>
-      <c r="D66" t="n">
-        <v>9114</v>
-      </c>
       <c r="E66" t="n">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F66" t="n">
+        <v>37335.7</v>
+      </c>
+      <c r="G66" t="n">
         <v>37234.8</v>
       </c>
-      <c r="G66" t="n">
-        <v>37203.2</v>
-      </c>
       <c r="H66" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I66" t="n">
+        <v>42530.4</v>
+      </c>
+      <c r="J66" t="n">
         <v>42459</v>
       </c>
-      <c r="J66" t="n">
-        <v>42456.2</v>
-      </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L66" t="n">
+        <v>46497.8</v>
+      </c>
+      <c r="M66" t="n">
         <v>46500.8</v>
       </c>
-      <c r="M66" t="n">
-        <v>46498.1</v>
-      </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O66" t="n">
+        <v>482000</v>
+      </c>
+      <c r="P66" t="n">
         <v>487500</v>
       </c>
-      <c r="P66" t="n">
-        <v>488500</v>
-      </c>
       <c r="Q66" t="n">
-        <v>-0.2</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="67">
@@ -4167,49 +4167,49 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>10025</v>
+      </c>
+      <c r="D67" t="n">
         <v>10136</v>
       </c>
-      <c r="D67" t="n">
-        <v>10170</v>
-      </c>
       <c r="E67" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="F67" t="n">
+        <v>42746.8</v>
+      </c>
+      <c r="G67" t="n">
         <v>42647.9</v>
       </c>
-      <c r="G67" t="n">
-        <v>42629.6</v>
-      </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I67" t="n">
+        <v>55240.3</v>
+      </c>
+      <c r="J67" t="n">
         <v>55103.9</v>
       </c>
-      <c r="J67" t="n">
-        <v>54900.1</v>
-      </c>
       <c r="K67" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L67" t="n">
+        <v>61947.8</v>
+      </c>
+      <c r="M67" t="n">
         <v>62256.4</v>
       </c>
-      <c r="M67" t="n">
-        <v>61729.9</v>
-      </c>
       <c r="N67" t="n">
-        <v>0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="O67" t="n">
+        <v>943000</v>
+      </c>
+      <c r="P67" t="n">
         <v>936000</v>
       </c>
-      <c r="P67" t="n">
-        <v>1041000</v>
-      </c>
       <c r="Q67" t="n">
-        <v>-10.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="68">
@@ -4260,13 +4260,13 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
+        <v>72100</v>
+      </c>
+      <c r="P68" t="n">
         <v>71700</v>
       </c>
-      <c r="P68" t="n">
-        <v>71800</v>
-      </c>
       <c r="Q68" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="69">
@@ -4281,49 +4281,49 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D69" t="n">
         <v>502</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1879.9</v>
+        <v>1889.2</v>
       </c>
       <c r="G69" t="n">
         <v>1879.9</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I69" t="n">
-        <v>2386.1</v>
+        <v>2374</v>
       </c>
       <c r="J69" t="n">
         <v>2386.1</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L69" t="n">
-        <v>3072.4</v>
+        <v>2982.6</v>
       </c>
       <c r="M69" t="n">
         <v>3072.4</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="O69" t="n">
+        <v>244500</v>
+      </c>
+      <c r="P69" t="n">
         <v>260000</v>
       </c>
-      <c r="P69" t="n">
-        <v>238000</v>
-      </c>
       <c r="Q69" t="n">
-        <v>9.199999999999999</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="70">
@@ -4338,49 +4338,49 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>19122</v>
+        <v>19553</v>
       </c>
       <c r="D70" t="n">
         <v>19122</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="F70" t="n">
-        <v>97617.5</v>
+        <v>98532.2</v>
       </c>
       <c r="G70" t="n">
         <v>97617.5</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>134651.3</v>
+        <v>136740.3</v>
       </c>
       <c r="J70" t="n">
         <v>134651.3</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L70" t="n">
-        <v>148583.9</v>
+        <v>149138.7</v>
       </c>
       <c r="M70" t="n">
         <v>148583.9</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O70" t="n">
+        <v>34050</v>
+      </c>
+      <c r="P70" t="n">
         <v>34250</v>
       </c>
-      <c r="P70" t="n">
-        <v>36750</v>
-      </c>
       <c r="Q70" t="n">
-        <v>-6.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="71">
@@ -4395,49 +4395,49 @@
         </is>
       </c>
       <c r="C71" t="n">
+        <v>6617</v>
+      </c>
+      <c r="D71" t="n">
         <v>6435</v>
       </c>
-      <c r="D71" t="n">
-        <v>6159</v>
-      </c>
       <c r="E71" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="F71" t="n">
+        <v>23027.4</v>
+      </c>
+      <c r="G71" t="n">
         <v>22640.4</v>
       </c>
-      <c r="G71" t="n">
-        <v>22401.3</v>
-      </c>
       <c r="H71" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="I71" t="n">
+        <v>21231.4</v>
+      </c>
+      <c r="J71" t="n">
         <v>20996.1</v>
-      </c>
-      <c r="J71" t="n">
-        <v>20758.2</v>
       </c>
       <c r="K71" t="n">
         <v>1.1</v>
       </c>
       <c r="L71" t="n">
+        <v>21175.6</v>
+      </c>
+      <c r="M71" t="n">
         <v>20937.6</v>
       </c>
-      <c r="M71" t="n">
-        <v>20808.3</v>
-      </c>
       <c r="N71" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="O71" t="n">
+        <v>107700</v>
+      </c>
+      <c r="P71" t="n">
         <v>108800</v>
       </c>
-      <c r="P71" t="n">
-        <v>111700</v>
-      </c>
       <c r="Q71" t="n">
-        <v>-2.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72">
@@ -4452,49 +4452,49 @@
         </is>
       </c>
       <c r="C72" t="n">
+        <v>5425</v>
+      </c>
+      <c r="D72" t="n">
         <v>5307</v>
       </c>
-      <c r="D72" t="n">
-        <v>5290</v>
-      </c>
       <c r="E72" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="F72" t="n">
+        <v>19372.4</v>
+      </c>
+      <c r="G72" t="n">
         <v>19164.7</v>
       </c>
-      <c r="G72" t="n">
-        <v>19147.2</v>
-      </c>
       <c r="H72" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="I72" t="n">
+        <v>20475.3</v>
+      </c>
+      <c r="J72" t="n">
         <v>20300.4</v>
       </c>
-      <c r="J72" t="n">
-        <v>20290.9</v>
-      </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L72" t="n">
+        <v>21634.8</v>
+      </c>
+      <c r="M72" t="n">
         <v>21507.9</v>
       </c>
-      <c r="M72" t="n">
-        <v>21493</v>
-      </c>
       <c r="N72" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="O72" t="n">
+        <v>89700</v>
+      </c>
+      <c r="P72" t="n">
         <v>85700</v>
       </c>
-      <c r="P72" t="n">
-        <v>84000</v>
-      </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="73">
@@ -4509,49 +4509,49 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D73" t="n">
         <v>470</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F73" t="n">
-        <v>1798.3</v>
+        <v>1818.3</v>
       </c>
       <c r="G73" t="n">
         <v>1798.3</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>1964.3</v>
+        <v>1997.7</v>
       </c>
       <c r="J73" t="n">
         <v>1964.3</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L73" t="n">
-        <v>1946.5</v>
+        <v>2141.5</v>
       </c>
       <c r="M73" t="n">
         <v>1946.5</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O73" t="n">
+        <v>23450</v>
+      </c>
+      <c r="P73" t="n">
         <v>24600</v>
       </c>
-      <c r="P73" t="n">
-        <v>24000</v>
-      </c>
       <c r="Q73" t="n">
-        <v>2.5</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="74">
@@ -4566,49 +4566,49 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>2368</v>
+      </c>
+      <c r="D74" t="n">
         <v>2349</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2330</v>
       </c>
       <c r="E74" t="n">
         <v>0.8</v>
       </c>
       <c r="F74" t="n">
+        <v>8360.799999999999</v>
+      </c>
+      <c r="G74" t="n">
         <v>8342.200000000001</v>
       </c>
-      <c r="G74" t="n">
-        <v>8358.200000000001</v>
-      </c>
       <c r="H74" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="I74" t="n">
+        <v>10668.7</v>
+      </c>
+      <c r="J74" t="n">
         <v>10645.7</v>
       </c>
-      <c r="J74" t="n">
-        <v>10647.7</v>
-      </c>
       <c r="K74" t="n">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="L74" t="n">
+        <v>12020.2</v>
+      </c>
+      <c r="M74" t="n">
         <v>11844.7</v>
       </c>
-      <c r="M74" t="n">
-        <v>11831.3</v>
-      </c>
       <c r="N74" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="O74" t="n">
+        <v>199300</v>
+      </c>
+      <c r="P74" t="n">
         <v>190200</v>
       </c>
-      <c r="P74" t="n">
-        <v>194300</v>
-      </c>
       <c r="Q74" t="n">
-        <v>-2.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="75">
@@ -4623,49 +4623,49 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D75" t="n">
         <v>1095</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F75" t="n">
-        <v>4279.2</v>
+        <v>4287.6</v>
       </c>
       <c r="G75" t="n">
         <v>4279.2</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I75" t="n">
-        <v>4997.4</v>
+        <v>5039.6</v>
       </c>
       <c r="J75" t="n">
         <v>4997.4</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L75" t="n">
-        <v>5789.7</v>
+        <v>5833.9</v>
       </c>
       <c r="M75" t="n">
         <v>5789.7</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O75" t="n">
+        <v>3490</v>
+      </c>
+      <c r="P75" t="n">
         <v>3440</v>
       </c>
-      <c r="P75" t="n">
-        <v>3575</v>
-      </c>
       <c r="Q75" t="n">
-        <v>-3.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="76">
@@ -4680,16 +4680,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2682</v>
+        <v>2675</v>
       </c>
       <c r="D76" t="n">
         <v>2682</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F76" t="n">
-        <v>10136.5</v>
+        <v>10139.2</v>
       </c>
       <c r="G76" t="n">
         <v>10136.5</v>
@@ -4698,13 +4698,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>11688.8</v>
+        <v>11678.2</v>
       </c>
       <c r="J76" t="n">
         <v>11688.8</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L76" t="n">
         <v>12472.5</v>
@@ -4716,13 +4716,13 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>91700</v>
+        <v>96700</v>
       </c>
       <c r="P76" t="n">
         <v>91700</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="77">
@@ -4737,49 +4737,49 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1104</v>
+        <v>1129</v>
       </c>
       <c r="D77" t="n">
         <v>1104</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="F77" t="n">
-        <v>8034.7</v>
+        <v>8112.6</v>
       </c>
       <c r="G77" t="n">
         <v>8034.7</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>8618.5</v>
+        <v>8722.4</v>
       </c>
       <c r="J77" t="n">
         <v>8618.5</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L77" t="n">
-        <v>9113.799999999999</v>
+        <v>9228.4</v>
       </c>
       <c r="M77" t="n">
         <v>9113.799999999999</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O77" t="n">
+        <v>140800</v>
+      </c>
+      <c r="P77" t="n">
         <v>154300</v>
       </c>
-      <c r="P77" t="n">
-        <v>159600</v>
-      </c>
       <c r="Q77" t="n">
-        <v>-3.3</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -4794,49 +4794,49 @@
         </is>
       </c>
       <c r="C78" t="n">
+        <v>9260</v>
+      </c>
+      <c r="D78" t="n">
         <v>9431</v>
       </c>
-      <c r="D78" t="n">
-        <v>9437</v>
-      </c>
       <c r="E78" t="n">
-        <v>-0.1</v>
+        <v>-1.8</v>
       </c>
       <c r="F78" t="n">
+        <v>36894.8</v>
+      </c>
+      <c r="G78" t="n">
         <v>37016.5</v>
       </c>
-      <c r="G78" t="n">
-        <v>37054.8</v>
-      </c>
       <c r="H78" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="I78" t="n">
+        <v>39631.1</v>
+      </c>
+      <c r="J78" t="n">
         <v>39830.2</v>
       </c>
-      <c r="J78" t="n">
-        <v>39842.8</v>
-      </c>
       <c r="K78" t="n">
-        <v>-0</v>
+        <v>-0.5</v>
       </c>
       <c r="L78" t="n">
+        <v>42250.5</v>
+      </c>
+      <c r="M78" t="n">
         <v>42552.4</v>
       </c>
-      <c r="M78" t="n">
-        <v>42556.9</v>
-      </c>
       <c r="N78" t="n">
-        <v>-0</v>
+        <v>-0.7</v>
       </c>
       <c r="O78" t="n">
+        <v>21600</v>
+      </c>
+      <c r="P78" t="n">
         <v>21150</v>
       </c>
-      <c r="P78" t="n">
-        <v>20950</v>
-      </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="79">
@@ -4851,49 +4851,49 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2179</v>
+        <v>2188</v>
       </c>
       <c r="D79" t="n">
         <v>2179</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F79" t="n">
-        <v>8839.6</v>
+        <v>8845.299999999999</v>
       </c>
       <c r="G79" t="n">
         <v>8839.6</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I79" t="n">
-        <v>10306.5</v>
+        <v>10313.1</v>
       </c>
       <c r="J79" t="n">
         <v>10306.5</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L79" t="n">
-        <v>11529.4</v>
+        <v>11551.5</v>
       </c>
       <c r="M79" t="n">
         <v>11529.4</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O79" t="n">
+        <v>40850</v>
+      </c>
+      <c r="P79" t="n">
         <v>41100</v>
       </c>
-      <c r="P79" t="n">
-        <v>43500</v>
-      </c>
       <c r="Q79" t="n">
-        <v>-5.5</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="80">
@@ -4944,13 +4944,13 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
+        <v>346000</v>
+      </c>
+      <c r="P80" t="n">
         <v>361000</v>
       </c>
-      <c r="P80" t="n">
-        <v>395000</v>
-      </c>
       <c r="Q80" t="n">
-        <v>-8.6</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="81">
@@ -4965,49 +4965,49 @@
         </is>
       </c>
       <c r="C81" t="n">
+        <v>1546</v>
+      </c>
+      <c r="D81" t="n">
         <v>1503</v>
       </c>
-      <c r="D81" t="n">
-        <v>1495</v>
-      </c>
       <c r="E81" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="F81" t="n">
+        <v>5936.6</v>
+      </c>
+      <c r="G81" t="n">
         <v>5854.9</v>
       </c>
-      <c r="G81" t="n">
-        <v>5839.5</v>
-      </c>
       <c r="H81" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="I81" t="n">
+        <v>6133.7</v>
+      </c>
+      <c r="J81" t="n">
         <v>6091.5</v>
       </c>
-      <c r="J81" t="n">
-        <v>6010.8</v>
-      </c>
       <c r="K81" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="L81" t="n">
+        <v>6369.3</v>
+      </c>
+      <c r="M81" t="n">
         <v>6368.1</v>
       </c>
-      <c r="M81" t="n">
-        <v>6274.3</v>
-      </c>
       <c r="N81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
+        <v>5160</v>
+      </c>
+      <c r="P81" t="n">
         <v>5240</v>
       </c>
-      <c r="P81" t="n">
-        <v>5170</v>
-      </c>
       <c r="Q81" t="n">
-        <v>1.4</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="82">
@@ -5022,49 +5022,49 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2131</v>
+        <v>2144</v>
       </c>
       <c r="D82" t="n">
         <v>2131</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F82" t="n">
-        <v>8470</v>
+        <v>8315</v>
       </c>
       <c r="G82" t="n">
         <v>8470</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="I82" t="n">
-        <v>9226.700000000001</v>
+        <v>8912.5</v>
       </c>
       <c r="J82" t="n">
         <v>9226.700000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
       <c r="L82" t="n">
-        <v>9336.700000000001</v>
+        <v>9062.5</v>
       </c>
       <c r="M82" t="n">
         <v>9336.700000000001</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="O82" t="n">
+        <v>47050</v>
+      </c>
+      <c r="P82" t="n">
         <v>47800</v>
       </c>
-      <c r="P82" t="n">
-        <v>48850</v>
-      </c>
       <c r="Q82" t="n">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="83">
@@ -5079,49 +5079,49 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D83" t="n">
         <v>942</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F83" t="n">
-        <v>3339.9</v>
+        <v>3331.9</v>
       </c>
       <c r="G83" t="n">
         <v>3339.9</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I83" t="n">
-        <v>3636.7</v>
+        <v>3627.7</v>
       </c>
       <c r="J83" t="n">
         <v>3636.7</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L83" t="n">
-        <v>3692.6</v>
+        <v>3685.9</v>
       </c>
       <c r="M83" t="n">
         <v>3692.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O83" t="n">
+        <v>18610</v>
+      </c>
+      <c r="P83" t="n">
         <v>18760</v>
       </c>
-      <c r="P83" t="n">
-        <v>18980</v>
-      </c>
       <c r="Q83" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="84">
@@ -5136,49 +5136,49 @@
         </is>
       </c>
       <c r="C84" t="n">
+        <v>6038</v>
+      </c>
+      <c r="D84" t="n">
         <v>6081</v>
       </c>
-      <c r="D84" t="n">
-        <v>6133</v>
-      </c>
       <c r="E84" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="F84" t="n">
+        <v>20519.3</v>
+      </c>
+      <c r="G84" t="n">
         <v>20653.3</v>
       </c>
-      <c r="G84" t="n">
-        <v>20721.3</v>
-      </c>
       <c r="H84" t="n">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="I84" t="n">
+        <v>22467.7</v>
+      </c>
+      <c r="J84" t="n">
         <v>22502.9</v>
       </c>
-      <c r="J84" t="n">
-        <v>22526.8</v>
-      </c>
       <c r="K84" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="L84" t="n">
+        <v>23804.6</v>
+      </c>
+      <c r="M84" t="n">
         <v>23821.8</v>
-      </c>
-      <c r="M84" t="n">
-        <v>23847.4</v>
       </c>
       <c r="N84" t="n">
         <v>-0.1</v>
       </c>
       <c r="O84" t="n">
+        <v>52400</v>
+      </c>
+      <c r="P84" t="n">
         <v>52700</v>
       </c>
-      <c r="P84" t="n">
-        <v>55400</v>
-      </c>
       <c r="Q84" t="n">
-        <v>-4.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="85">
@@ -5193,49 +5193,49 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3062</v>
+        <v>3072</v>
       </c>
       <c r="D85" t="n">
         <v>3062</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F85" t="n">
-        <v>11111.1</v>
+        <v>11105.5</v>
       </c>
       <c r="G85" t="n">
         <v>11111.1</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I85" t="n">
-        <v>11959</v>
+        <v>11996.9</v>
       </c>
       <c r="J85" t="n">
         <v>11959</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L85" t="n">
-        <v>12715.1</v>
+        <v>12762.1</v>
       </c>
       <c r="M85" t="n">
         <v>12715.1</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O85" t="n">
+        <v>14620</v>
+      </c>
+      <c r="P85" t="n">
         <v>14530</v>
       </c>
-      <c r="P85" t="n">
-        <v>14810</v>
-      </c>
       <c r="Q85" t="n">
-        <v>-1.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="86">
@@ -5286,13 +5286,13 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
+        <v>331000</v>
+      </c>
+      <c r="P86" t="n">
         <v>326000</v>
       </c>
-      <c r="P86" t="n">
-        <v>346000</v>
-      </c>
       <c r="Q86" t="n">
-        <v>-5.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="87">
@@ -5307,49 +5307,49 @@
         </is>
       </c>
       <c r="C87" t="n">
+        <v>3919</v>
+      </c>
+      <c r="D87" t="n">
         <v>3866</v>
       </c>
-      <c r="D87" t="n">
-        <v>3843</v>
-      </c>
       <c r="E87" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="F87" t="n">
+        <v>15120.1</v>
+      </c>
+      <c r="G87" t="n">
         <v>15108.4</v>
       </c>
-      <c r="G87" t="n">
-        <v>15067.6</v>
-      </c>
       <c r="H87" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I87" t="n">
+        <v>16261.1</v>
+      </c>
+      <c r="J87" t="n">
         <v>16302.5</v>
       </c>
-      <c r="J87" t="n">
-        <v>16299.9</v>
-      </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="L87" t="n">
+        <v>17211.8</v>
+      </c>
+      <c r="M87" t="n">
         <v>17252.5</v>
       </c>
-      <c r="M87" t="n">
-        <v>17227</v>
-      </c>
       <c r="N87" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="O87" t="n">
+        <v>179900</v>
+      </c>
+      <c r="P87" t="n">
         <v>174300</v>
       </c>
-      <c r="P87" t="n">
-        <v>184300</v>
-      </c>
       <c r="Q87" t="n">
-        <v>-5.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="88">
@@ -5364,25 +5364,25 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2659</v>
+        <v>2670</v>
       </c>
       <c r="D88" t="n">
         <v>2659</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F88" t="n">
-        <v>11195.5</v>
+        <v>11184.8</v>
       </c>
       <c r="G88" t="n">
         <v>11195.5</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I88" t="n">
-        <v>16045.1</v>
+        <v>16050.4</v>
       </c>
       <c r="J88" t="n">
         <v>16045.1</v>
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>21149.6</v>
+        <v>21153.6</v>
       </c>
       <c r="M88" t="n">
         <v>21149.6</v>
@@ -5400,13 +5400,13 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
+        <v>69700</v>
+      </c>
+      <c r="P88" t="n">
         <v>73200</v>
       </c>
-      <c r="P88" t="n">
-        <v>74000</v>
-      </c>
       <c r="Q88" t="n">
-        <v>-1.1</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="89">
@@ -5457,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
+        <v>10410</v>
+      </c>
+      <c r="P89" t="n">
         <v>10360</v>
       </c>
-      <c r="P89" t="n">
-        <v>11240</v>
-      </c>
       <c r="Q89" t="n">
-        <v>-7.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
@@ -5478,49 +5478,49 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="D90" t="n">
         <v>498</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F90" t="n">
-        <v>1856.2</v>
+        <v>1844.2</v>
       </c>
       <c r="G90" t="n">
         <v>1856.2</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="I90" t="n">
-        <v>2235.1</v>
+        <v>2244.1</v>
       </c>
       <c r="J90" t="n">
         <v>2235.1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L90" t="n">
-        <v>2456</v>
+        <v>2455.1</v>
       </c>
       <c r="M90" t="n">
         <v>2456</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O90" t="n">
+        <v>10190</v>
+      </c>
+      <c r="P90" t="n">
         <v>12550</v>
       </c>
-      <c r="P90" t="n">
-        <v>12920</v>
-      </c>
       <c r="Q90" t="n">
-        <v>-2.9</v>
+        <v>-18.8</v>
       </c>
     </row>
     <row r="91">
@@ -5571,13 +5571,13 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
+        <v>580000</v>
+      </c>
+      <c r="P91" t="n">
         <v>583000</v>
       </c>
-      <c r="P91" t="n">
-        <v>596000</v>
-      </c>
       <c r="Q91" t="n">
-        <v>-2.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="92">
@@ -5628,13 +5628,13 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
+        <v>14410</v>
+      </c>
+      <c r="P92" t="n">
         <v>14680</v>
       </c>
-      <c r="P92" t="n">
-        <v>14780</v>
-      </c>
       <c r="Q92" t="n">
-        <v>-0.7</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="93">
@@ -5649,49 +5649,49 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5693</v>
+        <v>5670</v>
       </c>
       <c r="D93" t="n">
         <v>5693</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F93" t="n">
+        <v>23891.1</v>
+      </c>
+      <c r="G93" t="n">
         <v>23973.6</v>
       </c>
-      <c r="G93" t="n">
-        <v>23970.7</v>
-      </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I93" t="n">
+        <v>27590</v>
+      </c>
+      <c r="J93" t="n">
         <v>27672</v>
       </c>
-      <c r="J93" t="n">
-        <v>27661</v>
-      </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="L93" t="n">
+        <v>31240.8</v>
+      </c>
+      <c r="M93" t="n">
         <v>31358.5</v>
       </c>
-      <c r="M93" t="n">
-        <v>31280.1</v>
-      </c>
       <c r="N93" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="O93" t="n">
+        <v>190000</v>
+      </c>
+      <c r="P93" t="n">
         <v>188000</v>
       </c>
-      <c r="P93" t="n">
-        <v>192700</v>
-      </c>
       <c r="Q93" t="n">
-        <v>-2.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="94">
@@ -5706,49 +5706,49 @@
         </is>
       </c>
       <c r="C94" t="n">
+        <v>2263</v>
+      </c>
+      <c r="D94" t="n">
         <v>2229</v>
       </c>
-      <c r="D94" t="n">
-        <v>2226</v>
-      </c>
       <c r="E94" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F94" t="n">
+        <v>9473.700000000001</v>
+      </c>
+      <c r="G94" t="n">
+        <v>9387.299999999999</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I94" t="n">
+        <v>10966.3</v>
+      </c>
+      <c r="J94" t="n">
+        <v>10959.7</v>
+      </c>
+      <c r="K94" t="n">
         <v>0.1</v>
       </c>
-      <c r="F94" t="n">
-        <v>9387.299999999999</v>
-      </c>
-      <c r="G94" t="n">
-        <v>9376.9</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I94" t="n">
-        <v>10959.7</v>
-      </c>
-      <c r="J94" t="n">
-        <v>10913.1</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0.4</v>
-      </c>
       <c r="L94" t="n">
+        <v>12514.8</v>
+      </c>
+      <c r="M94" t="n">
         <v>12671.7</v>
       </c>
-      <c r="M94" t="n">
-        <v>12611.7</v>
-      </c>
       <c r="N94" t="n">
-        <v>0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="O94" t="n">
+        <v>35900</v>
+      </c>
+      <c r="P94" t="n">
         <v>34750</v>
       </c>
-      <c r="P94" t="n">
-        <v>34650</v>
-      </c>
       <c r="Q94" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="95">
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
+        <v>32400</v>
+      </c>
+      <c r="P95" t="n">
         <v>32700</v>
       </c>
-      <c r="P95" t="n">
-        <v>33200</v>
-      </c>
       <c r="Q95" t="n">
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="96">
@@ -5820,49 +5820,49 @@
         </is>
       </c>
       <c r="C96" t="n">
+        <v>1284</v>
+      </c>
+      <c r="D96" t="n">
         <v>1270</v>
       </c>
-      <c r="D96" t="n">
-        <v>1266</v>
-      </c>
       <c r="E96" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>5019.9</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5026.8</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>5897.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5876.9</v>
+      </c>
+      <c r="K96" t="n">
         <v>0.3</v>
-      </c>
-      <c r="F96" t="n">
-        <v>5026.8</v>
-      </c>
-      <c r="G96" t="n">
-        <v>5021.2</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I96" t="n">
-        <v>5876.9</v>
-      </c>
-      <c r="J96" t="n">
-        <v>5888.8</v>
-      </c>
-      <c r="K96" t="n">
-        <v>-0.2</v>
       </c>
       <c r="L96" t="n">
         <v>5924.6</v>
       </c>
       <c r="M96" t="n">
-        <v>6011.7</v>
+        <v>5924.6</v>
       </c>
       <c r="N96" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
+        <v>223000</v>
+      </c>
+      <c r="P96" t="n">
         <v>240500</v>
       </c>
-      <c r="P96" t="n">
-        <v>258500</v>
-      </c>
       <c r="Q96" t="n">
-        <v>-7</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="97">
@@ -5877,49 +5877,49 @@
         </is>
       </c>
       <c r="C97" t="n">
+        <v>6522</v>
+      </c>
+      <c r="D97" t="n">
         <v>6375</v>
       </c>
-      <c r="D97" t="n">
-        <v>6257</v>
-      </c>
       <c r="E97" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F97" t="n">
+        <v>22059</v>
+      </c>
+      <c r="G97" t="n">
         <v>21921.9</v>
       </c>
-      <c r="G97" t="n">
-        <v>21724.8</v>
-      </c>
       <c r="H97" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I97" t="n">
+        <v>20561.6</v>
+      </c>
+      <c r="J97" t="n">
         <v>20426.9</v>
       </c>
-      <c r="J97" t="n">
-        <v>20349.5</v>
-      </c>
       <c r="K97" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L97" t="n">
-        <v>20600.4</v>
+        <v>20834.7</v>
       </c>
       <c r="M97" t="n">
         <v>20600.4</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O97" t="n">
+        <v>322000</v>
+      </c>
+      <c r="P97" t="n">
         <v>323500</v>
       </c>
-      <c r="P97" t="n">
-        <v>334500</v>
-      </c>
       <c r="Q97" t="n">
-        <v>-3.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="98">
@@ -5934,49 +5934,49 @@
         </is>
       </c>
       <c r="C98" t="n">
+        <v>5300</v>
+      </c>
+      <c r="D98" t="n">
         <v>5252</v>
       </c>
-      <c r="D98" t="n">
-        <v>5217</v>
-      </c>
       <c r="E98" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F98" t="n">
+        <v>19176.2</v>
+      </c>
+      <c r="G98" t="n">
         <v>19011.6</v>
       </c>
-      <c r="G98" t="n">
-        <v>18987.4</v>
-      </c>
       <c r="H98" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="I98" t="n">
+        <v>23327.3</v>
+      </c>
+      <c r="J98" t="n">
         <v>23489.7</v>
       </c>
-      <c r="J98" t="n">
-        <v>23507.6</v>
-      </c>
       <c r="K98" t="n">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="L98" t="n">
+        <v>27375.2</v>
+      </c>
+      <c r="M98" t="n">
         <v>27891.2</v>
       </c>
-      <c r="M98" t="n">
-        <v>27892.4</v>
-      </c>
       <c r="N98" t="n">
-        <v>-0</v>
+        <v>-1.9</v>
       </c>
       <c r="O98" t="n">
+        <v>86700</v>
+      </c>
+      <c r="P98" t="n">
         <v>78800</v>
       </c>
-      <c r="P98" t="n">
-        <v>82000</v>
-      </c>
       <c r="Q98" t="n">
-        <v>-3.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
@@ -5991,49 +5991,49 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1103</v>
+        <v>1210</v>
       </c>
       <c r="D99" t="n">
         <v>1103</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>3694</v>
+        <v>3822</v>
       </c>
       <c r="G99" t="n">
         <v>3694</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I99" t="n">
-        <v>5719</v>
+        <v>5617</v>
       </c>
       <c r="J99" t="n">
         <v>5719</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="L99" t="n">
-        <v>7297</v>
+        <v>6843</v>
       </c>
       <c r="M99" t="n">
         <v>7297</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>-6.2</v>
       </c>
       <c r="O99" t="n">
+        <v>242500</v>
+      </c>
+      <c r="P99" t="n">
         <v>205500</v>
       </c>
-      <c r="P99" t="n">
-        <v>199200</v>
-      </c>
       <c r="Q99" t="n">
-        <v>3.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100">
@@ -6048,49 +6048,49 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1508</v>
+        <v>1558</v>
       </c>
       <c r="D100" t="n">
         <v>1508</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="F100" t="n">
+        <v>7389.2</v>
+      </c>
+      <c r="G100" t="n">
         <v>7131.3</v>
       </c>
-      <c r="G100" t="n">
-        <v>6988.2</v>
-      </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="I100" t="n">
+        <v>7473.7</v>
+      </c>
+      <c r="J100" t="n">
         <v>7346.9</v>
       </c>
-      <c r="J100" t="n">
-        <v>7254.8</v>
-      </c>
       <c r="K100" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="L100" t="n">
+        <v>8753.799999999999</v>
+      </c>
+      <c r="M100" t="n">
         <v>8381.4</v>
       </c>
-      <c r="M100" t="n">
-        <v>8244.9</v>
-      </c>
       <c r="N100" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="O100" t="n">
+        <v>15150</v>
+      </c>
+      <c r="P100" t="n">
         <v>16010</v>
       </c>
-      <c r="P100" t="n">
-        <v>15830</v>
-      </c>
       <c r="Q100" t="n">
-        <v>1.1</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="101">
@@ -6105,49 +6105,49 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3517</v>
+        <v>3557</v>
       </c>
       <c r="D101" t="n">
         <v>3517</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F101" t="n">
-        <v>13940.8</v>
+        <v>13991.6</v>
       </c>
       <c r="G101" t="n">
         <v>13940.8</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I101" t="n">
-        <v>15092.4</v>
+        <v>15191</v>
       </c>
       <c r="J101" t="n">
         <v>15092.4</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L101" t="n">
-        <v>15771.5</v>
+        <v>15938.8</v>
       </c>
       <c r="M101" t="n">
         <v>15771.5</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O101" t="n">
+        <v>50900</v>
+      </c>
+      <c r="P101" t="n">
         <v>50600</v>
       </c>
-      <c r="P101" t="n">
-        <v>48750</v>
-      </c>
       <c r="Q101" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="102">
@@ -6162,49 +6162,49 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1002</v>
+        <v>951</v>
       </c>
       <c r="D102" t="n">
         <v>1002</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>-5.1</v>
       </c>
       <c r="F102" t="n">
-        <v>4679.8</v>
+        <v>4564.2</v>
       </c>
       <c r="G102" t="n">
         <v>4679.8</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="I102" t="n">
-        <v>6650.4</v>
+        <v>6612.7</v>
       </c>
       <c r="J102" t="n">
         <v>6650.4</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L102" t="n">
-        <v>8075.1</v>
+        <v>8049.8</v>
       </c>
       <c r="M102" t="n">
         <v>8075.1</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="O102" t="n">
+        <v>149200</v>
+      </c>
+      <c r="P102" t="n">
         <v>143500</v>
       </c>
-      <c r="P102" t="n">
-        <v>142000</v>
-      </c>
       <c r="Q102" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
+        <v>43550</v>
+      </c>
+      <c r="P103" t="n">
         <v>44050</v>
       </c>
-      <c r="P103" t="n">
-        <v>43900</v>
-      </c>
       <c r="Q103" t="n">
-        <v>0.3</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="104">
@@ -6276,49 +6276,49 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="D104" t="n">
         <v>751</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F104" t="n">
-        <v>3421.5</v>
+        <v>3443.6</v>
       </c>
       <c r="G104" t="n">
         <v>3421.5</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I104" t="n">
-        <v>3992.5</v>
+        <v>4017.5</v>
       </c>
       <c r="J104" t="n">
         <v>3992.5</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L104" t="n">
-        <v>4283.7</v>
+        <v>4314.5</v>
       </c>
       <c r="M104" t="n">
         <v>4283.7</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O104" t="n">
+        <v>246500</v>
+      </c>
+      <c r="P104" t="n">
         <v>248500</v>
       </c>
-      <c r="P104" t="n">
-        <v>256000</v>
-      </c>
       <c r="Q104" t="n">
-        <v>-2.9</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="105">
@@ -6372,10 +6372,10 @@
         <v>260500</v>
       </c>
       <c r="P105" t="n">
-        <v>255000</v>
+        <v>260500</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -6426,13 +6426,13 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
+        <v>92700</v>
+      </c>
+      <c r="P106" t="n">
         <v>97600</v>
       </c>
-      <c r="P106" t="n">
-        <v>94900</v>
-      </c>
       <c r="Q106" t="n">
-        <v>2.8</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="107">
@@ -6447,49 +6447,49 @@
         </is>
       </c>
       <c r="C107" t="n">
+        <v>22532</v>
+      </c>
+      <c r="D107" t="n">
         <v>22349</v>
       </c>
-      <c r="D107" t="n">
-        <v>22193</v>
-      </c>
       <c r="E107" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="F107" t="n">
+        <v>77226.7</v>
+      </c>
+      <c r="G107" t="n">
         <v>76926.5</v>
       </c>
-      <c r="G107" t="n">
-        <v>76844.60000000001</v>
-      </c>
       <c r="H107" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I107" t="n">
+        <v>81804.8</v>
+      </c>
+      <c r="J107" t="n">
+        <v>81714.5</v>
+      </c>
+      <c r="K107" t="n">
         <v>0.1</v>
       </c>
-      <c r="I107" t="n">
-        <v>81714.5</v>
-      </c>
-      <c r="J107" t="n">
-        <v>81715.8</v>
-      </c>
-      <c r="K107" t="n">
-        <v>-0</v>
-      </c>
       <c r="L107" t="n">
+        <v>85148.3</v>
+      </c>
+      <c r="M107" t="n">
         <v>85120.2</v>
       </c>
-      <c r="M107" t="n">
-        <v>85049.5</v>
-      </c>
       <c r="N107" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
+        <v>107900</v>
+      </c>
+      <c r="P107" t="n">
         <v>108600</v>
       </c>
-      <c r="P107" t="n">
-        <v>107300</v>
-      </c>
       <c r="Q107" t="n">
-        <v>1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="108">
@@ -6504,49 +6504,49 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D108" t="n">
         <v>603</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F108" t="n">
-        <v>2487.6</v>
+        <v>2483.1</v>
       </c>
       <c r="G108" t="n">
         <v>2487.6</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I108" t="n">
-        <v>3312.3</v>
+        <v>3333</v>
       </c>
       <c r="J108" t="n">
         <v>3312.3</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L108" t="n">
-        <v>4295.2</v>
+        <v>4265.2</v>
       </c>
       <c r="M108" t="n">
         <v>4295.2</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O108" t="n">
+        <v>170000</v>
+      </c>
+      <c r="P108" t="n">
         <v>169800</v>
       </c>
-      <c r="P108" t="n">
-        <v>178200</v>
-      </c>
       <c r="Q108" t="n">
-        <v>-4.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="109">
@@ -6561,49 +6561,49 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2768</v>
+        <v>2725</v>
       </c>
       <c r="D109" t="n">
         <v>2768</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="F109" t="n">
-        <v>11805.3</v>
+        <v>11569.8</v>
       </c>
       <c r="G109" t="n">
         <v>11805.3</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I109" t="n">
-        <v>15557.9</v>
+        <v>15181.7</v>
       </c>
       <c r="J109" t="n">
         <v>15557.9</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="L109" t="n">
-        <v>18626.1</v>
+        <v>18232.4</v>
       </c>
       <c r="M109" t="n">
         <v>18626.1</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="O109" t="n">
+        <v>159000</v>
+      </c>
+      <c r="P109" t="n">
         <v>170000</v>
       </c>
-      <c r="P109" t="n">
-        <v>169100</v>
-      </c>
       <c r="Q109" t="n">
-        <v>0.5</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="110">
@@ -6618,49 +6618,49 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1434</v>
+        <v>1409</v>
       </c>
       <c r="D110" t="n">
         <v>1434</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="F110" t="n">
-        <v>6162.8</v>
+        <v>6080.8</v>
       </c>
       <c r="G110" t="n">
         <v>6162.8</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="I110" t="n">
-        <v>7022.6</v>
+        <v>6954.7</v>
       </c>
       <c r="J110" t="n">
         <v>7022.6</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L110" t="n">
-        <v>7902.2</v>
+        <v>7875.6</v>
       </c>
       <c r="M110" t="n">
         <v>7902.2</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="O110" t="n">
+        <v>65000</v>
+      </c>
+      <c r="P110" t="n">
         <v>68200</v>
       </c>
-      <c r="P110" t="n">
-        <v>71200</v>
-      </c>
       <c r="Q110" t="n">
-        <v>-4.2</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="111">
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
+        <v>179000</v>
+      </c>
+      <c r="P111" t="n">
         <v>185600</v>
       </c>
-      <c r="P111" t="n">
-        <v>195800</v>
-      </c>
       <c r="Q111" t="n">
-        <v>-5.2</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="112">
@@ -6732,49 +6732,49 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="D112" t="n">
         <v>502</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="F112" t="n">
-        <v>2517.9</v>
+        <v>2488</v>
       </c>
       <c r="G112" t="n">
         <v>2517.9</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>2311</v>
+        <v>2330.9</v>
       </c>
       <c r="J112" t="n">
         <v>2311</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L112" t="n">
-        <v>3257.2</v>
+        <v>3311.8</v>
       </c>
       <c r="M112" t="n">
         <v>3257.2</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O112" t="n">
+        <v>92000</v>
+      </c>
+      <c r="P112" t="n">
         <v>101300</v>
       </c>
-      <c r="P112" t="n">
-        <v>91800</v>
-      </c>
       <c r="Q112" t="n">
-        <v>10.3</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6801,37 +6801,37 @@
         <v>17804.2</v>
       </c>
       <c r="G113" t="n">
-        <v>17705.6</v>
+        <v>17804.2</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>21031.7</v>
       </c>
       <c r="J113" t="n">
-        <v>21003.2</v>
+        <v>21031.7</v>
       </c>
       <c r="K113" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
         <v>24695.9</v>
       </c>
       <c r="M113" t="n">
-        <v>24637.2</v>
+        <v>24695.9</v>
       </c>
       <c r="N113" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
+        <v>175800</v>
+      </c>
+      <c r="P113" t="n">
         <v>175100</v>
       </c>
-      <c r="P113" t="n">
-        <v>176800</v>
-      </c>
       <c r="Q113" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="114">
@@ -6882,13 +6882,13 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
+        <v>15450</v>
+      </c>
+      <c r="P114" t="n">
         <v>15520</v>
       </c>
-      <c r="P114" t="n">
-        <v>15620</v>
-      </c>
       <c r="Q114" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="115">
@@ -6903,49 +6903,49 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="D115" t="n">
         <v>544</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F115" t="n">
-        <v>2065.2</v>
+        <v>2142.6</v>
       </c>
       <c r="G115" t="n">
         <v>2065.2</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I115" t="n">
-        <v>2402.6</v>
+        <v>2281</v>
       </c>
       <c r="J115" t="n">
         <v>2402.6</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>-5.1</v>
       </c>
       <c r="L115" t="n">
-        <v>3619.6</v>
+        <v>3611.6</v>
       </c>
       <c r="M115" t="n">
         <v>3619.6</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O115" t="n">
+        <v>121900</v>
+      </c>
+      <c r="P115" t="n">
         <v>132500</v>
       </c>
-      <c r="P115" t="n">
-        <v>134900</v>
-      </c>
       <c r="Q115" t="n">
-        <v>-1.8</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="116">
@@ -6960,16 +6960,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="D116" t="n">
         <v>858</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F116" t="n">
-        <v>4359.2</v>
+        <v>4359.6</v>
       </c>
       <c r="G116" t="n">
         <v>4359.2</v>
@@ -6978,31 +6978,31 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>5268.4</v>
+        <v>5281.8</v>
       </c>
       <c r="J116" t="n">
         <v>5268.4</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L116" t="n">
-        <v>5649.9</v>
+        <v>5667</v>
       </c>
       <c r="M116" t="n">
         <v>5649.9</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O116" t="n">
+        <v>157400</v>
+      </c>
+      <c r="P116" t="n">
         <v>157900</v>
       </c>
-      <c r="P116" t="n">
-        <v>168700</v>
-      </c>
       <c r="Q116" t="n">
-        <v>-6.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="117">
@@ -7017,49 +7017,49 @@
         </is>
       </c>
       <c r="C117" t="n">
+        <v>10519</v>
+      </c>
+      <c r="D117" t="n">
         <v>10415</v>
       </c>
-      <c r="D117" t="n">
-        <v>10145</v>
-      </c>
       <c r="E117" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
+        <v>35391.5</v>
+      </c>
+      <c r="G117" t="n">
         <v>35232.8</v>
-      </c>
-      <c r="G117" t="n">
-        <v>35060.4</v>
       </c>
       <c r="H117" t="n">
         <v>0.5</v>
       </c>
       <c r="I117" t="n">
+        <v>32503.9</v>
+      </c>
+      <c r="J117" t="n">
         <v>32313.2</v>
       </c>
-      <c r="J117" t="n">
-        <v>32190.9</v>
-      </c>
       <c r="K117" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L117" t="n">
-        <v>32379.5</v>
+        <v>32692.6</v>
       </c>
       <c r="M117" t="n">
         <v>32379.5</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
+        <v>229000</v>
+      </c>
+      <c r="P117" t="n">
         <v>237000</v>
       </c>
-      <c r="P117" t="n">
-        <v>233500</v>
-      </c>
       <c r="Q117" t="n">
-        <v>1.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="118">
@@ -7110,13 +7110,13 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
+        <v>64800</v>
+      </c>
+      <c r="P118" t="n">
         <v>66700</v>
       </c>
-      <c r="P118" t="n">
-        <v>67400</v>
-      </c>
       <c r="Q118" t="n">
-        <v>-1</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="119">
@@ -7131,49 +7131,49 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D119" t="n">
         <v>355</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F119" t="n">
-        <v>1522.5</v>
+        <v>1525.8</v>
       </c>
       <c r="G119" t="n">
         <v>1522.5</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I119" t="n">
-        <v>2035.3</v>
+        <v>2052.2</v>
       </c>
       <c r="J119" t="n">
         <v>2035.3</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L119" t="n">
-        <v>2477.5</v>
+        <v>2493.5</v>
       </c>
       <c r="M119" t="n">
         <v>2477.5</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O119" t="n">
+        <v>57600</v>
+      </c>
+      <c r="P119" t="n">
         <v>59600</v>
       </c>
-      <c r="P119" t="n">
-        <v>55900</v>
-      </c>
       <c r="Q119" t="n">
-        <v>6.6</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="120">
@@ -7188,49 +7188,49 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1455</v>
+        <v>1442</v>
       </c>
       <c r="D120" t="n">
         <v>1455</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="F120" t="n">
-        <v>5763.7</v>
+        <v>5747.7</v>
       </c>
       <c r="G120" t="n">
         <v>5763.7</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I120" t="n">
-        <v>5993.2</v>
+        <v>6118.2</v>
       </c>
       <c r="J120" t="n">
         <v>5993.2</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="L120" t="n">
-        <v>6656.3</v>
+        <v>6994.9</v>
       </c>
       <c r="M120" t="n">
         <v>6656.3</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O120" t="n">
+        <v>5850</v>
+      </c>
+      <c r="P120" t="n">
         <v>7160</v>
       </c>
-      <c r="P120" t="n">
-        <v>6400</v>
-      </c>
       <c r="Q120" t="n">
-        <v>11.9</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="121">
@@ -7281,13 +7281,13 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
+        <v>82800</v>
+      </c>
+      <c r="P121" t="n">
         <v>79500</v>
       </c>
-      <c r="P121" t="n">
-        <v>78600</v>
-      </c>
       <c r="Q121" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="122">
@@ -7302,49 +7302,49 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1049</v>
+        <v>1085</v>
       </c>
       <c r="D122" t="n">
         <v>1049</v>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="F122" t="n">
-        <v>4500.6</v>
+        <v>4545.4</v>
       </c>
       <c r="G122" t="n">
         <v>4500.6</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>6182.2</v>
+        <v>6272.3</v>
       </c>
       <c r="J122" t="n">
         <v>6182.2</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L122" t="n">
-        <v>8117.6</v>
+        <v>8198.4</v>
       </c>
       <c r="M122" t="n">
         <v>8117.6</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
+        <v>749000</v>
+      </c>
+      <c r="P122" t="n">
         <v>725000</v>
       </c>
-      <c r="P122" t="n">
-        <v>714000</v>
-      </c>
       <c r="Q122" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="123">
@@ -7359,49 +7359,49 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2121</v>
+        <v>2129</v>
       </c>
       <c r="D123" t="n">
         <v>2121</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F123" t="n">
-        <v>5637.1</v>
+        <v>5642.7</v>
       </c>
       <c r="G123" t="n">
         <v>5637.1</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I123" t="n">
-        <v>6005.9</v>
+        <v>6011.4</v>
       </c>
       <c r="J123" t="n">
         <v>6005.9</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L123" t="n">
-        <v>6231.9</v>
+        <v>6240.6</v>
       </c>
       <c r="M123" t="n">
         <v>6231.9</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O123" t="n">
+        <v>46950</v>
+      </c>
+      <c r="P123" t="n">
         <v>45150</v>
       </c>
-      <c r="P123" t="n">
-        <v>47850</v>
-      </c>
       <c r="Q123" t="n">
-        <v>-5.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
@@ -7416,49 +7416,49 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="D124" t="n">
         <v>595</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="F124" t="n">
-        <v>2407.6</v>
+        <v>2404.7</v>
       </c>
       <c r="G124" t="n">
         <v>2407.6</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I124" t="n">
-        <v>3687.6</v>
+        <v>3819.7</v>
       </c>
       <c r="J124" t="n">
         <v>3687.6</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L124" t="n">
-        <v>4521.6</v>
+        <v>4613</v>
       </c>
       <c r="M124" t="n">
         <v>4521.6</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O124" t="n">
+        <v>46900</v>
+      </c>
+      <c r="P124" t="n">
         <v>46200</v>
       </c>
-      <c r="P124" t="n">
-        <v>44750</v>
-      </c>
       <c r="Q124" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="125">
@@ -7473,49 +7473,49 @@
         </is>
       </c>
       <c r="C125" t="n">
+        <v>5133</v>
+      </c>
+      <c r="D125" t="n">
         <v>5168</v>
       </c>
-      <c r="D125" t="n">
-        <v>5218</v>
-      </c>
       <c r="E125" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="F125" t="n">
+        <v>21731.9</v>
+      </c>
+      <c r="G125" t="n">
         <v>21752.8</v>
-      </c>
-      <c r="G125" t="n">
-        <v>21784.2</v>
       </c>
       <c r="H125" t="n">
         <v>-0.1</v>
       </c>
       <c r="I125" t="n">
+        <v>23370.2</v>
+      </c>
+      <c r="J125" t="n">
         <v>23346</v>
-      </c>
-      <c r="J125" t="n">
-        <v>23322.1</v>
       </c>
       <c r="K125" t="n">
         <v>0.1</v>
       </c>
       <c r="L125" t="n">
+        <v>24535.4</v>
+      </c>
+      <c r="M125" t="n">
         <v>24506.1</v>
-      </c>
-      <c r="M125" t="n">
-        <v>24482.1</v>
       </c>
       <c r="N125" t="n">
         <v>0.1</v>
       </c>
       <c r="O125" t="n">
+        <v>188600</v>
+      </c>
+      <c r="P125" t="n">
         <v>187800</v>
       </c>
-      <c r="P125" t="n">
-        <v>190400</v>
-      </c>
       <c r="Q125" t="n">
-        <v>-1.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="126">
@@ -7530,49 +7530,49 @@
         </is>
       </c>
       <c r="C126" t="n">
+        <v>16580</v>
+      </c>
+      <c r="D126" t="n">
         <v>16571</v>
       </c>
-      <c r="D126" t="n">
-        <v>16577</v>
-      </c>
       <c r="E126" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="F126" t="n">
+        <v>60544.8</v>
+      </c>
+      <c r="G126" t="n">
         <v>60434.6</v>
       </c>
-      <c r="G126" t="n">
-        <v>60367.7</v>
-      </c>
       <c r="H126" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I126" t="n">
+        <v>63280</v>
+      </c>
+      <c r="J126" t="n">
         <v>63113.2</v>
       </c>
-      <c r="J126" t="n">
-        <v>63117.4</v>
-      </c>
       <c r="K126" t="n">
-        <v>-0</v>
+        <v>0.3</v>
       </c>
       <c r="L126" t="n">
+        <v>66171.10000000001</v>
+      </c>
+      <c r="M126" t="n">
         <v>65920.60000000001</v>
       </c>
-      <c r="M126" t="n">
-        <v>65992.2</v>
-      </c>
       <c r="N126" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="O126" t="n">
+        <v>136800</v>
+      </c>
+      <c r="P126" t="n">
         <v>132600</v>
       </c>
-      <c r="P126" t="n">
-        <v>122300</v>
-      </c>
       <c r="Q126" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="127">
@@ -7587,40 +7587,40 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>8132.5</v>
+        <v>8267.299999999999</v>
       </c>
       <c r="G127" t="n">
         <v>8132.5</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I127" t="n">
-        <v>9055.200000000001</v>
+        <v>9144.799999999999</v>
       </c>
       <c r="J127" t="n">
         <v>9055.200000000001</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
-        <v>8905.200000000001</v>
+        <v>9030.9</v>
       </c>
       <c r="M127" t="n">
         <v>8905.200000000001</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O127" t="n">
+        <v>4540</v>
+      </c>
+      <c r="P127" t="n">
         <v>4355</v>
       </c>
-      <c r="P127" t="n">
-        <v>4335</v>
-      </c>
       <c r="Q127" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="128">
@@ -7635,49 +7635,49 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D128" t="n">
         <v>984</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="F128" t="n">
-        <v>4637.6</v>
+        <v>4633.1</v>
       </c>
       <c r="G128" t="n">
         <v>4637.6</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I128" t="n">
-        <v>5278.1</v>
+        <v>5273.7</v>
       </c>
       <c r="J128" t="n">
         <v>5278.1</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L128" t="n">
-        <v>5882.1</v>
+        <v>5877.4</v>
       </c>
       <c r="M128" t="n">
         <v>5882.1</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O128" t="n">
+        <v>124400</v>
+      </c>
+      <c r="P128" t="n">
         <v>121600</v>
       </c>
-      <c r="P128" t="n">
-        <v>124300</v>
-      </c>
       <c r="Q128" t="n">
-        <v>-2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="129">
@@ -7701,13 +7701,13 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
+        <v>11690</v>
+      </c>
+      <c r="P129" t="n">
         <v>12340</v>
       </c>
-      <c r="P129" t="n">
-        <v>10740</v>
-      </c>
       <c r="Q129" t="n">
-        <v>14.9</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="130">
@@ -7722,49 +7722,49 @@
         </is>
       </c>
       <c r="C130" t="n">
+        <v>14936</v>
+      </c>
+      <c r="D130" t="n">
         <v>14123</v>
       </c>
-      <c r="D130" t="n">
-        <v>13980</v>
-      </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="F130" t="n">
-        <v>50950.2</v>
+        <v>52816.8</v>
       </c>
       <c r="G130" t="n">
         <v>50950.2</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I130" t="n">
-        <v>31187.9</v>
+        <v>31630.4</v>
       </c>
       <c r="J130" t="n">
         <v>31187.9</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="L130" t="n">
-        <v>36712.4</v>
+        <v>37398.4</v>
       </c>
       <c r="M130" t="n">
         <v>36712.4</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O130" t="n">
+        <v>121400</v>
+      </c>
+      <c r="P130" t="n">
         <v>110200</v>
       </c>
-      <c r="P130" t="n">
-        <v>99800</v>
-      </c>
       <c r="Q130" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="131">
@@ -7779,49 +7779,49 @@
         </is>
       </c>
       <c r="C131" t="n">
+        <v>2779</v>
+      </c>
+      <c r="D131" t="n">
         <v>2773</v>
       </c>
-      <c r="D131" t="n">
-        <v>2787</v>
-      </c>
       <c r="E131" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F131" t="n">
+        <v>12844.8</v>
+      </c>
+      <c r="G131" t="n">
         <v>12855.1</v>
       </c>
-      <c r="G131" t="n">
-        <v>12921.1</v>
-      </c>
       <c r="H131" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="I131" t="n">
+        <v>14582.7</v>
+      </c>
+      <c r="J131" t="n">
         <v>14545.4</v>
       </c>
-      <c r="J131" t="n">
-        <v>14542.5</v>
-      </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L131" t="n">
+        <v>16091</v>
+      </c>
+      <c r="M131" t="n">
         <v>15955.2</v>
-      </c>
-      <c r="M131" t="n">
-        <v>15806</v>
       </c>
       <c r="N131" t="n">
         <v>0.9</v>
       </c>
       <c r="O131" t="n">
+        <v>184800</v>
+      </c>
+      <c r="P131" t="n">
         <v>191900</v>
       </c>
-      <c r="P131" t="n">
-        <v>198200</v>
-      </c>
       <c r="Q131" t="n">
-        <v>-3.2</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="132">
@@ -7836,49 +7836,49 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>831</v>
+        <v>848</v>
       </c>
       <c r="D132" t="n">
         <v>831</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>3617.8</v>
+        <v>3654.7</v>
       </c>
       <c r="G132" t="n">
         <v>3617.8</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>3606.6</v>
+        <v>3583.9</v>
       </c>
       <c r="J132" t="n">
         <v>3606.6</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L132" t="n">
-        <v>3982.7</v>
+        <v>3961.3</v>
       </c>
       <c r="M132" t="n">
         <v>3982.7</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O132" t="n">
+        <v>62100</v>
+      </c>
+      <c r="P132" t="n">
         <v>62800</v>
       </c>
-      <c r="P132" t="n">
-        <v>62500</v>
-      </c>
       <c r="Q132" t="n">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="133">
@@ -7893,49 +7893,49 @@
         </is>
       </c>
       <c r="C133" t="n">
+        <v>26142</v>
+      </c>
+      <c r="D133" t="n">
         <v>25959</v>
       </c>
-      <c r="D133" t="n">
-        <v>25740</v>
-      </c>
       <c r="E133" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F133" t="n">
+        <v>93654.60000000001</v>
+      </c>
+      <c r="G133" t="n">
+        <v>92995.5</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I133" t="n">
+        <v>95238.60000000001</v>
+      </c>
+      <c r="J133" t="n">
+        <v>94516.7</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L133" t="n">
+        <v>98084.8</v>
+      </c>
+      <c r="M133" t="n">
+        <v>97229.5</v>
+      </c>
+      <c r="N133" t="n">
         <v>0.9</v>
       </c>
-      <c r="F133" t="n">
-        <v>92995.5</v>
-      </c>
-      <c r="G133" t="n">
-        <v>92733.10000000001</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I133" t="n">
-        <v>94516.7</v>
-      </c>
-      <c r="J133" t="n">
-        <v>94340.8</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L133" t="n">
-        <v>97229.5</v>
-      </c>
-      <c r="M133" t="n">
-        <v>97139.5</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0.1</v>
-      </c>
       <c r="O133" t="n">
+        <v>181100</v>
+      </c>
+      <c r="P133" t="n">
         <v>186200</v>
       </c>
-      <c r="P133" t="n">
-        <v>171000</v>
-      </c>
       <c r="Q133" t="n">
-        <v>8.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="134">
@@ -7950,49 +7950,49 @@
         </is>
       </c>
       <c r="C134" t="n">
+        <v>1837</v>
+      </c>
+      <c r="D134" t="n">
         <v>1828</v>
       </c>
-      <c r="D134" t="n">
-        <v>1826</v>
-      </c>
       <c r="E134" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F134" t="n">
-        <v>6361.3</v>
+        <v>6372.3</v>
       </c>
       <c r="G134" t="n">
         <v>6361.3</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I134" t="n">
+        <v>7034.4</v>
+      </c>
+      <c r="J134" t="n">
         <v>6985.6</v>
       </c>
-      <c r="J134" t="n">
-        <v>6986.7</v>
-      </c>
       <c r="K134" t="n">
-        <v>-0</v>
+        <v>0.7</v>
       </c>
       <c r="L134" t="n">
+        <v>7585.7</v>
+      </c>
+      <c r="M134" t="n">
         <v>7521.4</v>
       </c>
-      <c r="M134" t="n">
-        <v>7460</v>
-      </c>
       <c r="N134" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O134" t="n">
+        <v>86900</v>
+      </c>
+      <c r="P134" t="n">
         <v>84600</v>
       </c>
-      <c r="P134" t="n">
-        <v>85400</v>
-      </c>
       <c r="Q134" t="n">
-        <v>-0.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="135">
@@ -8043,13 +8043,13 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
+        <v>39850</v>
+      </c>
+      <c r="P135" t="n">
         <v>41400</v>
       </c>
-      <c r="P135" t="n">
-        <v>39050</v>
-      </c>
       <c r="Q135" t="n">
-        <v>6</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="136">
@@ -8091,22 +8091,22 @@
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>2981.2</v>
+        <v>2980.4</v>
       </c>
       <c r="M136" t="n">
         <v>2981.2</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O136" t="n">
+        <v>53600</v>
+      </c>
+      <c r="P136" t="n">
         <v>53400</v>
       </c>
-      <c r="P136" t="n">
-        <v>56100</v>
-      </c>
       <c r="Q136" t="n">
-        <v>-4.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137">
@@ -8121,49 +8121,49 @@
         </is>
       </c>
       <c r="C137" t="n">
+        <v>1042</v>
+      </c>
+      <c r="D137" t="n">
         <v>866</v>
       </c>
-      <c r="D137" t="n">
-        <v>632</v>
-      </c>
       <c r="E137" t="n">
-        <v>37</v>
+        <v>20.3</v>
       </c>
       <c r="F137" t="n">
+        <v>3105.6</v>
+      </c>
+      <c r="G137" t="n">
         <v>2961.1</v>
       </c>
-      <c r="G137" t="n">
-        <v>2803.7</v>
-      </c>
       <c r="H137" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="I137" t="n">
+        <v>3147.9</v>
+      </c>
+      <c r="J137" t="n">
         <v>3106.5</v>
       </c>
-      <c r="J137" t="n">
-        <v>3114.5</v>
-      </c>
       <c r="K137" t="n">
-        <v>-0.3</v>
+        <v>1.3</v>
       </c>
       <c r="L137" t="n">
+        <v>3403.1</v>
+      </c>
+      <c r="M137" t="n">
         <v>3328.3</v>
       </c>
-      <c r="M137" t="n">
-        <v>3340.5</v>
-      </c>
       <c r="N137" t="n">
-        <v>-0.4</v>
+        <v>2.2</v>
       </c>
       <c r="O137" t="n">
+        <v>386000</v>
+      </c>
+      <c r="P137" t="n">
         <v>381500</v>
       </c>
-      <c r="P137" t="n">
-        <v>409000</v>
-      </c>
       <c r="Q137" t="n">
-        <v>-6.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="138">
@@ -8214,13 +8214,13 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
+        <v>118300</v>
+      </c>
+      <c r="P138" t="n">
         <v>117000</v>
       </c>
-      <c r="P138" t="n">
-        <v>113700</v>
-      </c>
       <c r="Q138" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="139">
@@ -8235,49 +8235,49 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3328</v>
+        <v>3241</v>
       </c>
       <c r="D139" t="n">
         <v>3328</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="F139" t="n">
-        <v>11090.9</v>
+        <v>10990.9</v>
       </c>
       <c r="G139" t="n">
         <v>11090.9</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="I139" t="n">
-        <v>11963.5</v>
+        <v>11876.1</v>
       </c>
       <c r="J139" t="n">
         <v>11963.5</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="L139" t="n">
-        <v>12679.9</v>
+        <v>12628.4</v>
       </c>
       <c r="M139" t="n">
         <v>12679.9</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O139" t="n">
+        <v>18330</v>
+      </c>
+      <c r="P139" t="n">
         <v>18160</v>
       </c>
-      <c r="P139" t="n">
-        <v>17930</v>
-      </c>
       <c r="Q139" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="140">
@@ -8292,49 +8292,49 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2101</v>
+        <v>2054</v>
       </c>
       <c r="D140" t="n">
         <v>2101</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="F140" t="n">
+        <v>6565.1</v>
+      </c>
+      <c r="G140" t="n">
         <v>6606.6</v>
-      </c>
-      <c r="G140" t="n">
-        <v>6646.1</v>
       </c>
       <c r="H140" t="n">
         <v>-0.6</v>
       </c>
       <c r="I140" t="n">
+        <v>7114.6</v>
+      </c>
+      <c r="J140" t="n">
         <v>7148.2</v>
       </c>
-      <c r="J140" t="n">
-        <v>7169.7</v>
-      </c>
       <c r="K140" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="L140" t="n">
+        <v>7534.6</v>
+      </c>
+      <c r="M140" t="n">
         <v>7563.8</v>
       </c>
-      <c r="M140" t="n">
-        <v>7576.4</v>
-      </c>
       <c r="N140" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="O140" t="n">
+        <v>18410</v>
+      </c>
+      <c r="P140" t="n">
         <v>18220</v>
       </c>
-      <c r="P140" t="n">
-        <v>18090</v>
-      </c>
       <c r="Q140" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -8349,49 +8349,49 @@
         </is>
       </c>
       <c r="C141" t="n">
+        <v>563</v>
+      </c>
+      <c r="D141" t="n">
         <v>611</v>
       </c>
-      <c r="D141" t="n">
-        <v>672</v>
-      </c>
       <c r="E141" t="n">
-        <v>-9.1</v>
+        <v>-7.9</v>
       </c>
       <c r="F141" t="n">
+        <v>5405.5</v>
+      </c>
+      <c r="G141" t="n">
         <v>5488.2</v>
       </c>
-      <c r="G141" t="n">
-        <v>5599.1</v>
-      </c>
       <c r="H141" t="n">
-        <v>-2</v>
+        <v>-1.5</v>
       </c>
       <c r="I141" t="n">
+        <v>6438.3</v>
+      </c>
+      <c r="J141" t="n">
         <v>6514.8</v>
       </c>
-      <c r="J141" t="n">
-        <v>6533.8</v>
-      </c>
       <c r="K141" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
       <c r="L141" t="n">
+        <v>7146</v>
+      </c>
+      <c r="M141" t="n">
         <v>7220.6</v>
       </c>
-      <c r="M141" t="n">
-        <v>7229.4</v>
-      </c>
       <c r="N141" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="O141" t="n">
+        <v>79700</v>
+      </c>
+      <c r="P141" t="n">
         <v>82300</v>
       </c>
-      <c r="P141" t="n">
-        <v>81100</v>
-      </c>
       <c r="Q141" t="n">
-        <v>1.5</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="142">
@@ -8406,49 +8406,49 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5313</v>
+        <v>5317</v>
       </c>
       <c r="D142" t="n">
         <v>5313</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F142" t="n">
-        <v>21431.1</v>
+        <v>21470.8</v>
       </c>
       <c r="G142" t="n">
         <v>21431.1</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I142" t="n">
-        <v>23669.5</v>
+        <v>23784.1</v>
       </c>
       <c r="J142" t="n">
         <v>23669.5</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L142" t="n">
-        <v>25886.4</v>
+        <v>25761.1</v>
       </c>
       <c r="M142" t="n">
         <v>25886.4</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O142" t="n">
+        <v>73600</v>
+      </c>
+      <c r="P142" t="n">
         <v>69700</v>
       </c>
-      <c r="P142" t="n">
-        <v>73000</v>
-      </c>
       <c r="Q142" t="n">
-        <v>-4.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="143">
@@ -8463,49 +8463,49 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="D143" t="n">
         <v>953</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F143" t="n">
-        <v>3148.2</v>
+        <v>3146.1</v>
       </c>
       <c r="G143" t="n">
         <v>3148.2</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I143" t="n">
-        <v>3633</v>
+        <v>3638.5</v>
       </c>
       <c r="J143" t="n">
         <v>3633</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L143" t="n">
-        <v>4096.7</v>
+        <v>4102.8</v>
       </c>
       <c r="M143" t="n">
         <v>4096.7</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O143" t="n">
+        <v>107600</v>
+      </c>
+      <c r="P143" t="n">
         <v>115800</v>
       </c>
-      <c r="P143" t="n">
-        <v>112100</v>
-      </c>
       <c r="Q143" t="n">
-        <v>3.3</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="144">
@@ -8520,49 +8520,49 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2872</v>
+        <v>2886</v>
       </c>
       <c r="D144" t="n">
         <v>2872</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F144" t="n">
-        <v>10076.6</v>
+        <v>10057.9</v>
       </c>
       <c r="G144" t="n">
         <v>10076.6</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I144" t="n">
-        <v>10814.8</v>
+        <v>10827.5</v>
       </c>
       <c r="J144" t="n">
         <v>10814.8</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L144" t="n">
-        <v>11377.3</v>
+        <v>11410.1</v>
       </c>
       <c r="M144" t="n">
         <v>11377.3</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O144" t="n">
+        <v>27400</v>
+      </c>
+      <c r="P144" t="n">
         <v>28000</v>
       </c>
-      <c r="P144" t="n">
-        <v>26000</v>
-      </c>
       <c r="Q144" t="n">
-        <v>7.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="145">
@@ -8586,40 +8586,40 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>804.6</v>
+        <v>783.8</v>
       </c>
       <c r="G145" t="n">
         <v>804.6</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="I145" t="n">
-        <v>937.8</v>
+        <v>903.5</v>
       </c>
       <c r="J145" t="n">
         <v>937.8</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="L145" t="n">
-        <v>1023.2</v>
+        <v>988.5</v>
       </c>
       <c r="M145" t="n">
         <v>1023.2</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>-3.4</v>
       </c>
       <c r="O145" t="n">
+        <v>68300</v>
+      </c>
+      <c r="P145" t="n">
         <v>70400</v>
       </c>
-      <c r="P145" t="n">
-        <v>69600</v>
-      </c>
       <c r="Q145" t="n">
-        <v>1.1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="146">
@@ -8634,49 +8634,49 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D146" t="n">
         <v>704</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="F146" t="n">
-        <v>2852.6</v>
+        <v>2839.1</v>
       </c>
       <c r="G146" t="n">
         <v>2852.6</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="I146" t="n">
-        <v>3117.2</v>
+        <v>3105</v>
       </c>
       <c r="J146" t="n">
         <v>3117.2</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="L146" t="n">
-        <v>3347.5</v>
+        <v>3342.3</v>
       </c>
       <c r="M146" t="n">
         <v>3347.5</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O146" t="n">
+        <v>61600</v>
+      </c>
+      <c r="P146" t="n">
         <v>61100</v>
       </c>
-      <c r="P146" t="n">
-        <v>64500</v>
-      </c>
       <c r="Q146" t="n">
-        <v>-5.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="147">
@@ -8700,40 +8700,40 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>2327.5</v>
+        <v>2334.6</v>
       </c>
       <c r="G147" t="n">
         <v>2327.5</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I147" t="n">
-        <v>2766.5</v>
+        <v>2777.6</v>
       </c>
       <c r="J147" t="n">
         <v>2766.5</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L147" t="n">
-        <v>3194</v>
+        <v>3207.5</v>
       </c>
       <c r="M147" t="n">
         <v>3194</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O147" t="n">
+        <v>181100</v>
+      </c>
+      <c r="P147" t="n">
         <v>184300</v>
       </c>
-      <c r="P147" t="n">
-        <v>179600</v>
-      </c>
       <c r="Q147" t="n">
-        <v>2.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="148">
@@ -8748,49 +8748,49 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="D148" t="n">
         <v>1037</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F148" t="n">
-        <v>4028.2</v>
+        <v>4032.2</v>
       </c>
       <c r="G148" t="n">
         <v>4028.2</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I148" t="n">
-        <v>4685.9</v>
+        <v>4689.4</v>
       </c>
       <c r="J148" t="n">
         <v>4685.9</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L148" t="n">
-        <v>5234.6</v>
+        <v>5201.8</v>
       </c>
       <c r="M148" t="n">
         <v>5234.6</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="O148" t="n">
+        <v>44800</v>
+      </c>
+      <c r="P148" t="n">
         <v>47600</v>
       </c>
-      <c r="P148" t="n">
-        <v>48700</v>
-      </c>
       <c r="Q148" t="n">
-        <v>-2.3</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="149">
@@ -8841,13 +8841,13 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
+        <v>1396000</v>
+      </c>
+      <c r="P149" t="n">
         <v>1400000</v>
       </c>
-      <c r="P149" t="n">
-        <v>1363000</v>
-      </c>
       <c r="Q149" t="n">
-        <v>2.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="150">
@@ -8898,13 +8898,13 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
+        <v>64300</v>
+      </c>
+      <c r="P150" t="n">
         <v>61600</v>
       </c>
-      <c r="P150" t="n">
-        <v>61400</v>
-      </c>
       <c r="Q150" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="151">
@@ -8919,49 +8919,49 @@
         </is>
       </c>
       <c r="C151" t="n">
+        <v>901</v>
+      </c>
+      <c r="D151" t="n">
         <v>964</v>
       </c>
-      <c r="D151" t="n">
-        <v>1023</v>
-      </c>
       <c r="E151" t="n">
-        <v>-5.8</v>
+        <v>-6.5</v>
       </c>
       <c r="F151" t="n">
+        <v>3636.6</v>
+      </c>
+      <c r="G151" t="n">
         <v>3714.5</v>
       </c>
-      <c r="G151" t="n">
-        <v>3834.4</v>
-      </c>
       <c r="H151" t="n">
-        <v>-3.1</v>
+        <v>-2.1</v>
       </c>
       <c r="I151" t="n">
+        <v>4301.9</v>
+      </c>
+      <c r="J151" t="n">
         <v>4314.8</v>
       </c>
-      <c r="J151" t="n">
-        <v>4403.6</v>
-      </c>
       <c r="K151" t="n">
-        <v>-2</v>
+        <v>-0.3</v>
       </c>
       <c r="L151" t="n">
+        <v>4457.2</v>
+      </c>
+      <c r="M151" t="n">
         <v>4476</v>
       </c>
-      <c r="M151" t="n">
-        <v>4553.1</v>
-      </c>
       <c r="N151" t="n">
-        <v>-1.7</v>
+        <v>-0.4</v>
       </c>
       <c r="O151" t="n">
+        <v>36300</v>
+      </c>
+      <c r="P151" t="n">
         <v>38150</v>
       </c>
-      <c r="P151" t="n">
-        <v>38800</v>
-      </c>
       <c r="Q151" t="n">
-        <v>-1.7</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="152">
@@ -9012,13 +9012,13 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
+        <v>240500</v>
+      </c>
+      <c r="P152" t="n">
         <v>238000</v>
       </c>
-      <c r="P152" t="n">
-        <v>245000</v>
-      </c>
       <c r="Q152" t="n">
-        <v>-2.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="153">
@@ -9069,13 +9069,13 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
+        <v>204500</v>
+      </c>
+      <c r="P153" t="n">
         <v>198000</v>
       </c>
-      <c r="P153" t="n">
-        <v>193700</v>
-      </c>
       <c r="Q153" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="154">
@@ -9090,49 +9090,49 @@
         </is>
       </c>
       <c r="C154" t="n">
+        <v>2851</v>
+      </c>
+      <c r="D154" t="n">
         <v>2811</v>
       </c>
-      <c r="D154" t="n">
-        <v>2842</v>
-      </c>
       <c r="E154" t="n">
-        <v>-1.1</v>
+        <v>1.4</v>
       </c>
       <c r="F154" t="n">
+        <v>12398.9</v>
+      </c>
+      <c r="G154" t="n">
         <v>12375.1</v>
       </c>
-      <c r="G154" t="n">
-        <v>12432</v>
-      </c>
       <c r="H154" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I154" t="n">
+        <v>15481.2</v>
+      </c>
+      <c r="J154" t="n">
         <v>15394.8</v>
       </c>
-      <c r="J154" t="n">
-        <v>15390.2</v>
-      </c>
       <c r="K154" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L154" t="n">
+        <v>19010</v>
+      </c>
+      <c r="M154" t="n">
         <v>18919</v>
       </c>
-      <c r="M154" t="n">
-        <v>18811.5</v>
-      </c>
       <c r="N154" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O154" t="n">
+        <v>797000</v>
+      </c>
+      <c r="P154" t="n">
         <v>788000</v>
       </c>
-      <c r="P154" t="n">
-        <v>814000</v>
-      </c>
       <c r="Q154" t="n">
-        <v>-3.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="155">
@@ -9150,46 +9150,46 @@
         <v>1987</v>
       </c>
       <c r="D155" t="n">
-        <v>1945</v>
+        <v>1987</v>
       </c>
       <c r="E155" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
+        <v>7089.3</v>
+      </c>
+      <c r="G155" t="n">
         <v>6959.4</v>
       </c>
-      <c r="G155" t="n">
-        <v>6812.6</v>
-      </c>
       <c r="H155" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="I155" t="n">
         <v>8809.700000000001</v>
       </c>
       <c r="J155" t="n">
-        <v>8492.700000000001</v>
+        <v>8809.700000000001</v>
       </c>
       <c r="K155" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L155" t="n">
         <v>10474.8</v>
       </c>
       <c r="M155" t="n">
-        <v>10354.5</v>
+        <v>10474.8</v>
       </c>
       <c r="N155" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
+        <v>130300</v>
+      </c>
+      <c r="P155" t="n">
         <v>127000</v>
       </c>
-      <c r="P155" t="n">
-        <v>125300</v>
-      </c>
       <c r="Q155" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="156">
@@ -9204,49 +9204,49 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="D156" t="n">
         <v>1376</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F156" t="n">
-        <v>6507.6</v>
+        <v>6482.2</v>
       </c>
       <c r="G156" t="n">
         <v>6507.6</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="I156" t="n">
-        <v>7041.8</v>
+        <v>7020.5</v>
       </c>
       <c r="J156" t="n">
         <v>7041.8</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="L156" t="n">
-        <v>7619.4</v>
+        <v>7523.1</v>
       </c>
       <c r="M156" t="n">
         <v>7619.4</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="O156" t="n">
+        <v>128400</v>
+      </c>
+      <c r="P156" t="n">
         <v>133700</v>
       </c>
-      <c r="P156" t="n">
-        <v>140300</v>
-      </c>
       <c r="Q156" t="n">
-        <v>-4.7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="157">
@@ -9261,49 +9261,49 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="D157" t="n">
         <v>604</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="F157" t="n">
-        <v>2744.2</v>
+        <v>2664.2</v>
       </c>
       <c r="G157" t="n">
         <v>2744.2</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="I157" t="n">
-        <v>4888.5</v>
+        <v>4853.8</v>
       </c>
       <c r="J157" t="n">
         <v>4888.5</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="L157" t="n">
-        <v>6189.8</v>
+        <v>6138.2</v>
       </c>
       <c r="M157" t="n">
         <v>6189.8</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="O157" t="n">
+        <v>65500</v>
+      </c>
+      <c r="P157" t="n">
         <v>66500</v>
       </c>
-      <c r="P157" t="n">
-        <v>64900</v>
-      </c>
       <c r="Q157" t="n">
-        <v>2.5</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="158">
@@ -9318,49 +9318,49 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1735</v>
+        <v>1781</v>
       </c>
       <c r="D158" t="n">
         <v>1735</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="F158" t="n">
-        <v>7140.1</v>
+        <v>7313.5</v>
       </c>
       <c r="G158" t="n">
         <v>7140.1</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I158" t="n">
-        <v>9637.700000000001</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="J158" t="n">
         <v>9637.700000000001</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="L158" t="n">
-        <v>12055.9</v>
+        <v>12427.3</v>
       </c>
       <c r="M158" t="n">
         <v>12055.9</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O158" t="n">
+        <v>393000</v>
+      </c>
+      <c r="P158" t="n">
         <v>380000</v>
       </c>
-      <c r="P158" t="n">
-        <v>385500</v>
-      </c>
       <c r="Q158" t="n">
-        <v>-1.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="159">
@@ -9375,49 +9375,49 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D159" t="n">
         <v>461</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F159" t="n">
-        <v>1888.8</v>
+        <v>1892.3</v>
       </c>
       <c r="G159" t="n">
         <v>1888.8</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I159" t="n">
-        <v>2153.5</v>
+        <v>2159.4</v>
       </c>
       <c r="J159" t="n">
         <v>2153.5</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L159" t="n">
-        <v>2409.9</v>
+        <v>2398.1</v>
       </c>
       <c r="M159" t="n">
         <v>2409.9</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O159" t="n">
+        <v>101000</v>
+      </c>
+      <c r="P159" t="n">
         <v>107800</v>
       </c>
-      <c r="P159" t="n">
-        <v>105600</v>
-      </c>
       <c r="Q159" t="n">
-        <v>2.1</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="160">
@@ -9432,49 +9432,49 @@
         </is>
       </c>
       <c r="C160" t="n">
+        <v>760</v>
+      </c>
+      <c r="D160" t="n">
         <v>759</v>
       </c>
-      <c r="D160" t="n">
-        <v>747</v>
-      </c>
       <c r="E160" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="F160" t="n">
+        <v>2960.7</v>
+      </c>
+      <c r="G160" t="n">
         <v>2941.1</v>
       </c>
-      <c r="G160" t="n">
-        <v>2910.9</v>
-      </c>
       <c r="H160" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="I160" t="n">
+        <v>3258</v>
+      </c>
+      <c r="J160" t="n">
         <v>3228.1</v>
       </c>
-      <c r="J160" t="n">
-        <v>3201.2</v>
-      </c>
       <c r="K160" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L160" t="n">
+        <v>3518.2</v>
+      </c>
+      <c r="M160" t="n">
         <v>3473.8</v>
       </c>
-      <c r="M160" t="n">
-        <v>3447.5</v>
-      </c>
       <c r="N160" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="O160" t="n">
+        <v>126400</v>
+      </c>
+      <c r="P160" t="n">
         <v>127800</v>
       </c>
-      <c r="P160" t="n">
-        <v>125400</v>
-      </c>
       <c r="Q160" t="n">
-        <v>1.9</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="161">
@@ -9525,13 +9525,13 @@
         <v>0</v>
       </c>
       <c r="O161" t="n">
+        <v>39250</v>
+      </c>
+      <c r="P161" t="n">
         <v>39850</v>
       </c>
-      <c r="P161" t="n">
-        <v>40600</v>
-      </c>
       <c r="Q161" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
@@ -9582,13 +9582,13 @@
         <v>0</v>
       </c>
       <c r="O162" t="n">
+        <v>278000</v>
+      </c>
+      <c r="P162" t="n">
         <v>272000</v>
       </c>
-      <c r="P162" t="n">
-        <v>268000</v>
-      </c>
       <c r="Q162" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="163">
@@ -9603,49 +9603,49 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2845</v>
+        <v>2806</v>
       </c>
       <c r="D163" t="n">
         <v>2845</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="F163" t="n">
-        <v>10942.1</v>
+        <v>10879.9</v>
       </c>
       <c r="G163" t="n">
         <v>10942.1</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="I163" t="n">
-        <v>15477.6</v>
+        <v>15397.1</v>
       </c>
       <c r="J163" t="n">
         <v>15477.6</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L163" t="n">
-        <v>19558.8</v>
+        <v>19657.9</v>
       </c>
       <c r="M163" t="n">
         <v>19558.8</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O163" t="n">
+        <v>2789000</v>
+      </c>
+      <c r="P163" t="n">
         <v>2666000</v>
       </c>
-      <c r="P163" t="n">
-        <v>2689000</v>
-      </c>
       <c r="Q163" t="n">
-        <v>-0.9</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="164">
@@ -9696,13 +9696,13 @@
         <v>0</v>
       </c>
       <c r="O164" t="n">
+        <v>150500</v>
+      </c>
+      <c r="P164" t="n">
         <v>145000</v>
       </c>
-      <c r="P164" t="n">
-        <v>150200</v>
-      </c>
       <c r="Q164" t="n">
-        <v>-3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="165">
@@ -9753,13 +9753,13 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
+        <v>13990</v>
+      </c>
+      <c r="P165" t="n">
         <v>14310</v>
       </c>
-      <c r="P165" t="n">
-        <v>14470</v>
-      </c>
       <c r="Q165" t="n">
-        <v>-1.1</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="166">
@@ -9810,13 +9810,13 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
+        <v>35450</v>
+      </c>
+      <c r="P166" t="n">
         <v>36300</v>
       </c>
-      <c r="P166" t="n">
-        <v>37950</v>
-      </c>
       <c r="Q166" t="n">
-        <v>-4.3</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="167">
@@ -9831,49 +9831,49 @@
         </is>
       </c>
       <c r="C167" t="n">
+        <v>770</v>
+      </c>
+      <c r="D167" t="n">
         <v>785</v>
       </c>
-      <c r="D167" t="n">
-        <v>798</v>
-      </c>
       <c r="E167" t="n">
-        <v>-1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="F167" t="n">
+        <v>2741.8</v>
+      </c>
+      <c r="G167" t="n">
         <v>2766.1</v>
       </c>
-      <c r="G167" t="n">
-        <v>2774.2</v>
-      </c>
       <c r="H167" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="I167" t="n">
+        <v>3662.2</v>
+      </c>
+      <c r="J167" t="n">
         <v>3678.5</v>
-      </c>
-      <c r="J167" t="n">
-        <v>3692.2</v>
       </c>
       <c r="K167" t="n">
         <v>-0.4</v>
       </c>
       <c r="L167" t="n">
+        <v>4615.7</v>
+      </c>
+      <c r="M167" t="n">
         <v>4633.6</v>
       </c>
-      <c r="M167" t="n">
-        <v>4669.3</v>
-      </c>
       <c r="N167" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="O167" t="n">
+        <v>393000</v>
+      </c>
+      <c r="P167" t="n">
         <v>438000</v>
       </c>
-      <c r="P167" t="n">
-        <v>441500</v>
-      </c>
       <c r="Q167" t="n">
-        <v>-0.8</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="168">
@@ -9888,49 +9888,49 @@
         </is>
       </c>
       <c r="C168" t="n">
+        <v>12920</v>
+      </c>
+      <c r="D168" t="n">
         <v>12900</v>
       </c>
-      <c r="D168" t="n">
-        <v>12888</v>
-      </c>
       <c r="E168" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F168" t="n">
+        <v>43434.9</v>
+      </c>
+      <c r="G168" t="n">
         <v>43417.7</v>
       </c>
-      <c r="G168" t="n">
-        <v>43419.9</v>
-      </c>
       <c r="H168" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
+        <v>47616.6</v>
+      </c>
+      <c r="J168" t="n">
         <v>47710.4</v>
       </c>
-      <c r="J168" t="n">
-        <v>47767.7</v>
-      </c>
       <c r="K168" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="L168" t="n">
+        <v>50303.6</v>
+      </c>
+      <c r="M168" t="n">
         <v>50412.4</v>
       </c>
-      <c r="M168" t="n">
-        <v>50466.5</v>
-      </c>
       <c r="N168" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="O168" t="n">
+        <v>31500</v>
+      </c>
+      <c r="P168" t="n">
         <v>31200</v>
       </c>
-      <c r="P168" t="n">
-        <v>30700</v>
-      </c>
       <c r="Q168" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -9945,49 +9945,49 @@
         </is>
       </c>
       <c r="C169" t="n">
+        <v>1822</v>
+      </c>
+      <c r="D169" t="n">
         <v>1833</v>
       </c>
-      <c r="D169" t="n">
-        <v>1829</v>
-      </c>
       <c r="E169" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="F169" t="n">
+        <v>7099.5</v>
+      </c>
+      <c r="G169" t="n">
         <v>7101.1</v>
       </c>
-      <c r="G169" t="n">
-        <v>7092.9</v>
-      </c>
       <c r="H169" t="n">
-        <v>0.1</v>
+        <v>-0</v>
       </c>
       <c r="I169" t="n">
+        <v>8219.5</v>
+      </c>
+      <c r="J169" t="n">
         <v>8165.4</v>
       </c>
-      <c r="J169" t="n">
-        <v>8168.1</v>
-      </c>
       <c r="K169" t="n">
-        <v>-0</v>
+        <v>0.7</v>
       </c>
       <c r="L169" t="n">
+        <v>8952.200000000001</v>
+      </c>
+      <c r="M169" t="n">
         <v>8919.4</v>
       </c>
-      <c r="M169" t="n">
-        <v>8940.6</v>
-      </c>
       <c r="N169" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="O169" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P169" t="n">
         <v>23300</v>
       </c>
-      <c r="P169" t="n">
-        <v>22000</v>
-      </c>
       <c r="Q169" t="n">
-        <v>5.9</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="170">
@@ -10005,16 +10005,16 @@
         <v>845</v>
       </c>
       <c r="D170" t="n">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
         <v>3377.3</v>
       </c>
       <c r="G170" t="n">
-        <v>3376.7</v>
+        <v>3377.3</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -10023,28 +10023,28 @@
         <v>4511.6</v>
       </c>
       <c r="J170" t="n">
-        <v>4497.3</v>
+        <v>4511.6</v>
       </c>
       <c r="K170" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
         <v>5545</v>
       </c>
       <c r="M170" t="n">
-        <v>5597.5</v>
+        <v>5545</v>
       </c>
       <c r="N170" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
+        <v>79400</v>
+      </c>
+      <c r="P170" t="n">
         <v>79300</v>
       </c>
-      <c r="P170" t="n">
-        <v>82100</v>
-      </c>
       <c r="Q170" t="n">
-        <v>-3.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="171">
@@ -10059,49 +10059,49 @@
         </is>
       </c>
       <c r="C171" t="n">
+        <v>9925</v>
+      </c>
+      <c r="D171" t="n">
         <v>9902</v>
       </c>
-      <c r="D171" t="n">
-        <v>10003</v>
-      </c>
       <c r="E171" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="F171" t="n">
+        <v>38979</v>
+      </c>
+      <c r="G171" t="n">
         <v>38897.6</v>
       </c>
-      <c r="G171" t="n">
-        <v>39168.8</v>
-      </c>
       <c r="H171" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I171" t="n">
+        <v>45775.8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>45686.3</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L171" t="n">
+        <v>52641.7</v>
+      </c>
+      <c r="M171" t="n">
+        <v>51979.2</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O171" t="n">
+        <v>484000</v>
+      </c>
+      <c r="P171" t="n">
+        <v>487500</v>
+      </c>
+      <c r="Q171" t="n">
         <v>-0.7</v>
-      </c>
-      <c r="I171" t="n">
-        <v>45686.3</v>
-      </c>
-      <c r="J171" t="n">
-        <v>46037.2</v>
-      </c>
-      <c r="K171" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="L171" t="n">
-        <v>51979.2</v>
-      </c>
-      <c r="M171" t="n">
-        <v>52136.8</v>
-      </c>
-      <c r="N171" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="O171" t="n">
-        <v>487500</v>
-      </c>
-      <c r="P171" t="n">
-        <v>517000</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>-5.7</v>
       </c>
     </row>
     <row r="172">
@@ -10116,49 +10116,49 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1499</v>
+        <v>1528</v>
       </c>
       <c r="D172" t="n">
         <v>1499</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F172" t="n">
-        <v>2659.2</v>
+        <v>2697</v>
       </c>
       <c r="G172" t="n">
         <v>2659.2</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I172" t="n">
-        <v>4935</v>
+        <v>4904.1</v>
       </c>
       <c r="J172" t="n">
         <v>4935</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L172" t="n">
-        <v>5511.5</v>
+        <v>5526.9</v>
       </c>
       <c r="M172" t="n">
         <v>5511.5</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O172" t="n">
+        <v>208500</v>
+      </c>
+      <c r="P172" t="n">
         <v>213000</v>
       </c>
-      <c r="P172" t="n">
-        <v>230000</v>
-      </c>
       <c r="Q172" t="n">
-        <v>-7.4</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="173">
@@ -10209,13 +10209,13 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
+        <v>14260</v>
+      </c>
+      <c r="P173" t="n">
         <v>14460</v>
       </c>
-      <c r="P173" t="n">
-        <v>14400</v>
-      </c>
       <c r="Q173" t="n">
-        <v>0.4</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="174">
@@ -10239,40 +10239,40 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>11444.5</v>
+        <v>11337.5</v>
       </c>
       <c r="G174" t="n">
         <v>11444.5</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="I174" t="n">
-        <v>39869.5</v>
+        <v>39777.8</v>
       </c>
       <c r="J174" t="n">
         <v>39869.5</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L174" t="n">
-        <v>61536.8</v>
+        <v>61996.8</v>
       </c>
       <c r="M174" t="n">
         <v>61536.8</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O174" t="n">
+        <v>334000</v>
+      </c>
+      <c r="P174" t="n">
         <v>328500</v>
       </c>
-      <c r="P174" t="n">
-        <v>315500</v>
-      </c>
       <c r="Q174" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="175">
@@ -10287,49 +10287,49 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1199</v>
+        <v>1222</v>
       </c>
       <c r="D175" t="n">
         <v>1199</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F175" t="n">
+        <v>5218.5</v>
+      </c>
+      <c r="G175" t="n">
         <v>5129.8</v>
       </c>
-      <c r="G175" t="n">
-        <v>5086.1</v>
-      </c>
       <c r="H175" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="I175" t="n">
+        <v>5621.3</v>
+      </c>
+      <c r="J175" t="n">
         <v>5671.2</v>
       </c>
-      <c r="J175" t="n">
-        <v>5624.8</v>
-      </c>
       <c r="K175" t="n">
-        <v>0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="L175" t="n">
+        <v>6108.3</v>
+      </c>
+      <c r="M175" t="n">
         <v>6198.3</v>
       </c>
-      <c r="M175" t="n">
-        <v>6159</v>
-      </c>
       <c r="N175" t="n">
-        <v>0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="O175" t="n">
+        <v>60200</v>
+      </c>
+      <c r="P175" t="n">
         <v>60300</v>
       </c>
-      <c r="P175" t="n">
-        <v>59700</v>
-      </c>
       <c r="Q175" t="n">
-        <v>1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="176">
@@ -10380,13 +10380,13 @@
         <v>0</v>
       </c>
       <c r="O176" t="n">
+        <v>40900</v>
+      </c>
+      <c r="P176" t="n">
         <v>39750</v>
       </c>
-      <c r="P176" t="n">
-        <v>38150</v>
-      </c>
       <c r="Q176" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="177">
@@ -10410,40 +10410,40 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>5294.5</v>
+        <v>5307.8</v>
       </c>
       <c r="G177" t="n">
         <v>5294.5</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I177" t="n">
-        <v>5592.8</v>
+        <v>5622.7</v>
       </c>
       <c r="J177" t="n">
         <v>5592.8</v>
       </c>
       <c r="K177" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L177" t="n">
-        <v>5983.8</v>
+        <v>6051.2</v>
       </c>
       <c r="M177" t="n">
         <v>5983.8</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O177" t="n">
+        <v>79000</v>
+      </c>
+      <c r="P177" t="n">
         <v>79900</v>
       </c>
-      <c r="P177" t="n">
-        <v>80200</v>
-      </c>
       <c r="Q177" t="n">
-        <v>-0.4</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="178">
@@ -10467,40 +10467,40 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>430391.9</v>
+        <v>434130.4</v>
       </c>
       <c r="G178" t="n">
         <v>430391.9</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I178" t="n">
-        <v>541747.7</v>
+        <v>547499.1</v>
       </c>
       <c r="J178" t="n">
         <v>541747.7</v>
       </c>
       <c r="K178" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L178" t="n">
-        <v>583359</v>
+        <v>587557.6</v>
       </c>
       <c r="M178" t="n">
         <v>583359</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O178" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="P178" t="n">
         <v>1161000</v>
       </c>
-      <c r="P178" t="n">
-        <v>1270000</v>
-      </c>
       <c r="Q178" t="n">
-        <v>-8.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="179">
@@ -10515,49 +10515,49 @@
         </is>
       </c>
       <c r="C179" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D179" t="n">
         <v>1055</v>
       </c>
-      <c r="D179" t="n">
-        <v>1077</v>
-      </c>
       <c r="E179" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="F179" t="n">
+        <v>4310.1</v>
+      </c>
+      <c r="G179" t="n">
         <v>4346.1</v>
       </c>
-      <c r="G179" t="n">
-        <v>4394.7</v>
-      </c>
       <c r="H179" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="I179" t="n">
+        <v>5454.2</v>
+      </c>
+      <c r="J179" t="n">
         <v>5498.2</v>
       </c>
-      <c r="J179" t="n">
-        <v>5562.8</v>
-      </c>
       <c r="K179" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="L179" t="n">
+        <v>6620.5</v>
+      </c>
+      <c r="M179" t="n">
         <v>6666.5</v>
       </c>
-      <c r="M179" t="n">
-        <v>6650.8</v>
-      </c>
       <c r="N179" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="O179" t="n">
+        <v>201000</v>
+      </c>
+      <c r="P179" t="n">
         <v>193600</v>
       </c>
-      <c r="P179" t="n">
-        <v>197600</v>
-      </c>
       <c r="Q179" t="n">
-        <v>-2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="180">
@@ -10575,46 +10575,46 @@
         <v>462</v>
       </c>
       <c r="D180" t="n">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="E180" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
         <v>1669.7</v>
       </c>
       <c r="G180" t="n">
-        <v>1698.3</v>
+        <v>1669.7</v>
       </c>
       <c r="H180" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="I180" t="n">
         <v>1943.7</v>
       </c>
       <c r="J180" t="n">
-        <v>2071.3</v>
+        <v>1943.7</v>
       </c>
       <c r="K180" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
         <v>2033.3</v>
       </c>
       <c r="M180" t="n">
-        <v>2153.3</v>
+        <v>2033.3</v>
       </c>
       <c r="N180" t="n">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
+        <v>89800</v>
+      </c>
+      <c r="P180" t="n">
         <v>92100</v>
       </c>
-      <c r="P180" t="n">
-        <v>83700</v>
-      </c>
       <c r="Q180" t="n">
-        <v>10</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="181">
@@ -10629,49 +10629,49 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D181" t="n">
         <v>414</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F181" t="n">
-        <v>1606.1</v>
+        <v>1607.4</v>
       </c>
       <c r="G181" t="n">
         <v>1606.1</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I181" t="n">
-        <v>2195.5</v>
+        <v>2200.8</v>
       </c>
       <c r="J181" t="n">
         <v>2195.5</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L181" t="n">
-        <v>2769.4</v>
+        <v>2775.9</v>
       </c>
       <c r="M181" t="n">
         <v>2769.4</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O181" t="n">
+        <v>208500</v>
+      </c>
+      <c r="P181" t="n">
         <v>199500</v>
       </c>
-      <c r="P181" t="n">
-        <v>217500</v>
-      </c>
       <c r="Q181" t="n">
-        <v>-8.300000000000001</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-16 · 전주 2026-07-13</t>
+          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-17 · 전주 2026-07-13</t>
         </is>
       </c>
     </row>
@@ -669,40 +669,40 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1140</v>
+        <v>1132</v>
       </c>
       <c r="D5" t="n">
         <v>1140</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>5163</v>
+        <v>5126.3</v>
       </c>
       <c r="G5" t="n">
         <v>5163</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5718.2</v>
+        <v>5683.2</v>
       </c>
       <c r="J5" t="n">
         <v>5718.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L5" t="n">
-        <v>6160.5</v>
+        <v>6123.2</v>
       </c>
       <c r="M5" t="n">
         <v>6160.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="O5" t="n">
         <v>72500</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4571</v>
+        <v>4572</v>
       </c>
       <c r="D6" t="n">
         <v>4571</v>
@@ -735,22 +735,22 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>17063.8</v>
+        <v>17032.2</v>
       </c>
       <c r="G6" t="n">
         <v>17063.8</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>23491.7</v>
+        <v>23515</v>
       </c>
       <c r="J6" t="n">
         <v>23491.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L6" t="n">
         <v>29523.5</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27946</v>
+        <v>27935</v>
       </c>
       <c r="D9" t="n">
         <v>27920</v>
@@ -906,31 +906,31 @@
         <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>102821.2</v>
+        <v>102889.3</v>
       </c>
       <c r="G9" t="n">
         <v>102466.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I9" t="n">
-        <v>113657.1</v>
+        <v>113580.6</v>
       </c>
       <c r="J9" t="n">
         <v>113527.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>119510.4</v>
+        <v>119352.9</v>
       </c>
       <c r="M9" t="n">
         <v>120853.9</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="O9" t="n">
         <v>149700</v>
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2005</v>
+        <v>2026</v>
       </c>
       <c r="D11" t="n">
         <v>2005</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>8244.4</v>
+        <v>8280.6</v>
       </c>
       <c r="G11" t="n">
         <v>8244.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I11" t="n">
-        <v>11142.2</v>
+        <v>11114.9</v>
       </c>
       <c r="J11" t="n">
         <v>11142.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L11" t="n">
-        <v>13878.5</v>
+        <v>13860.7</v>
       </c>
       <c r="M11" t="n">
         <v>13845.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O11" t="n">
         <v>99000</v>
@@ -1068,40 +1068,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8669</v>
+        <v>8815</v>
       </c>
       <c r="D12" t="n">
         <v>8312</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="F12" t="n">
-        <v>30745.2</v>
+        <v>30870.2</v>
       </c>
       <c r="G12" t="n">
         <v>30345.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I12" t="n">
-        <v>33631.5</v>
+        <v>33681.5</v>
       </c>
       <c r="J12" t="n">
         <v>32907.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="L12" t="n">
-        <v>34054.8</v>
+        <v>34114</v>
       </c>
       <c r="M12" t="n">
         <v>33721.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O12" t="n">
         <v>701000</v>
@@ -1152,13 +1152,13 @@
         <v>-1.8</v>
       </c>
       <c r="L13" t="n">
-        <v>72135</v>
+        <v>72448</v>
       </c>
       <c r="M13" t="n">
         <v>72135</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O13" t="n">
         <v>93200</v>
@@ -1296,40 +1296,40 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="D16" t="n">
         <v>508</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1504</v>
+        <v>1517.9</v>
       </c>
       <c r="G16" t="n">
         <v>1464.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2024.1</v>
+        <v>1976.6</v>
       </c>
       <c r="J16" t="n">
         <v>2038.9</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7</v>
+        <v>-3.1</v>
       </c>
       <c r="L16" t="n">
-        <v>2335.4</v>
+        <v>2211.6</v>
       </c>
       <c r="M16" t="n">
         <v>2062.4</v>
       </c>
       <c r="N16" t="n">
-        <v>13.2</v>
+        <v>7.2</v>
       </c>
       <c r="O16" t="n">
         <v>32500</v>
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10521.3</v>
+        <v>10625.3</v>
       </c>
       <c r="G18" t="n">
         <v>10434.4</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="I18" t="n">
         <v>12179.5</v>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="D23" t="n">
         <v>1790</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="F23" t="n">
-        <v>7296.7</v>
+        <v>7309.6</v>
       </c>
       <c r="G23" t="n">
         <v>7298.4</v>
       </c>
       <c r="H23" t="n">
-        <v>-0</v>
+        <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>8769.6</v>
+        <v>8786.1</v>
       </c>
       <c r="J23" t="n">
         <v>8765.200000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L23" t="n">
         <v>10286.4</v>
@@ -2067,31 +2067,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D30" t="n">
         <v>485</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="F30" t="n">
-        <v>2144</v>
+        <v>2150.9</v>
       </c>
       <c r="G30" t="n">
         <v>2133.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>2321.7</v>
+        <v>2328.6</v>
       </c>
       <c r="J30" t="n">
         <v>2307.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="L30" t="n">
         <v>2454.5</v>
@@ -2181,31 +2181,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="D32" t="n">
         <v>651</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="F32" t="n">
-        <v>2131.6</v>
+        <v>2123.5</v>
       </c>
       <c r="G32" t="n">
         <v>2138.2</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="I32" t="n">
-        <v>2351.1</v>
+        <v>2342</v>
       </c>
       <c r="J32" t="n">
         <v>2364.6</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="L32" t="n">
         <v>2484.3</v>
@@ -2238,40 +2238,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>30293</v>
+        <v>30232</v>
       </c>
       <c r="D33" t="n">
         <v>31086</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="F33" t="n">
-        <v>117983.4</v>
+        <v>117500.2</v>
       </c>
       <c r="G33" t="n">
         <v>118721.8</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="I33" t="n">
-        <v>132991</v>
+        <v>132780.2</v>
       </c>
       <c r="J33" t="n">
         <v>133560</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="L33" t="n">
-        <v>145128.6</v>
+        <v>144868.6</v>
       </c>
       <c r="M33" t="n">
         <v>146466.8</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="O33" t="n">
         <v>425000</v>
@@ -2295,40 +2295,40 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7241</v>
+        <v>7299</v>
       </c>
       <c r="D34" t="n">
         <v>7419</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.4</v>
+        <v>-1.6</v>
       </c>
       <c r="F34" t="n">
-        <v>30676.6</v>
+        <v>30875.7</v>
       </c>
       <c r="G34" t="n">
         <v>31078.4</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="I34" t="n">
-        <v>38245.5</v>
+        <v>38602.4</v>
       </c>
       <c r="J34" t="n">
         <v>38922.9</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.7</v>
+        <v>-0.8</v>
       </c>
       <c r="L34" t="n">
-        <v>44284.7</v>
+        <v>44763.8</v>
       </c>
       <c r="M34" t="n">
         <v>44719.4</v>
       </c>
       <c r="N34" t="n">
-        <v>-1</v>
+        <v>0.1</v>
       </c>
       <c r="O34" t="n">
         <v>311500</v>
@@ -2361,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>21293.7</v>
+        <v>21330.6</v>
       </c>
       <c r="G35" t="n">
         <v>21132.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I35" t="n">
         <v>23130.1</v>
@@ -3198,40 +3198,40 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4015</v>
+        <v>4043</v>
       </c>
       <c r="D50" t="n">
         <v>4015</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F50" t="n">
-        <v>16524.3</v>
+        <v>16599.1</v>
       </c>
       <c r="G50" t="n">
         <v>16524.3</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I50" t="n">
-        <v>31390.1</v>
+        <v>31750.1</v>
       </c>
       <c r="J50" t="n">
         <v>31390.1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L50" t="n">
-        <v>49657.5</v>
+        <v>50852.8</v>
       </c>
       <c r="M50" t="n">
         <v>49657.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O50" t="n">
         <v>1277000</v>
@@ -3654,31 +3654,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3735</v>
+        <v>3744</v>
       </c>
       <c r="D58" t="n">
         <v>3902</v>
       </c>
       <c r="E58" t="n">
-        <v>-4.3</v>
+        <v>-4</v>
       </c>
       <c r="F58" t="n">
-        <v>14605.2</v>
+        <v>14649.6</v>
       </c>
       <c r="G58" t="n">
         <v>14956.6</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="I58" t="n">
-        <v>20139.2</v>
+        <v>20222.6</v>
       </c>
       <c r="J58" t="n">
         <v>20358</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="L58" t="n">
         <v>23690.3</v>
@@ -3768,22 +3768,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1803</v>
+        <v>1823</v>
       </c>
       <c r="D60" t="n">
         <v>1803</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F60" t="n">
-        <v>11679.8</v>
+        <v>11828.4</v>
       </c>
       <c r="G60" t="n">
         <v>11679.8</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I60" t="n">
         <v>13870.9</v>
@@ -3882,40 +3882,40 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3275</v>
+        <v>3463</v>
       </c>
       <c r="D62" t="n">
         <v>3182</v>
       </c>
       <c r="E62" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>11807.9</v>
+        <v>12211.1</v>
       </c>
       <c r="G62" t="n">
         <v>11608</v>
       </c>
       <c r="H62" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="I62" t="n">
-        <v>8617.9</v>
+        <v>8944.6</v>
       </c>
       <c r="J62" t="n">
         <v>8554.9</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="L62" t="n">
-        <v>9030.200000000001</v>
+        <v>9046.9</v>
       </c>
       <c r="M62" t="n">
         <v>9030.200000000001</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O62" t="n">
         <v>20050</v>
@@ -4110,16 +4110,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9096</v>
+        <v>9075</v>
       </c>
       <c r="D66" t="n">
         <v>9088</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="F66" t="n">
-        <v>37335.7</v>
+        <v>37334.3</v>
       </c>
       <c r="G66" t="n">
         <v>37234.8</v>
@@ -4128,16 +4128,16 @@
         <v>0.3</v>
       </c>
       <c r="I66" t="n">
-        <v>42530.4</v>
+        <v>42519.2</v>
       </c>
       <c r="J66" t="n">
         <v>42459</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L66" t="n">
-        <v>46497.8</v>
+        <v>46485</v>
       </c>
       <c r="M66" t="n">
         <v>46500.8</v>
@@ -4167,40 +4167,40 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10025</v>
+        <v>9962</v>
       </c>
       <c r="D67" t="n">
         <v>10136</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.1</v>
+        <v>-1.7</v>
       </c>
       <c r="F67" t="n">
-        <v>42746.8</v>
+        <v>42796.2</v>
       </c>
       <c r="G67" t="n">
         <v>42647.9</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I67" t="n">
-        <v>55240.3</v>
+        <v>54920.9</v>
       </c>
       <c r="J67" t="n">
         <v>55103.9</v>
       </c>
       <c r="K67" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="L67" t="n">
-        <v>61947.8</v>
+        <v>61626.3</v>
       </c>
       <c r="M67" t="n">
         <v>62256.4</v>
       </c>
       <c r="N67" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="O67" t="n">
         <v>943000</v>
@@ -4290,31 +4290,31 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1889.2</v>
+        <v>1886.8</v>
       </c>
       <c r="G69" t="n">
         <v>1879.9</v>
       </c>
       <c r="H69" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I69" t="n">
-        <v>2374</v>
+        <v>2361</v>
       </c>
       <c r="J69" t="n">
         <v>2386.1</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="L69" t="n">
-        <v>2982.6</v>
+        <v>2994.7</v>
       </c>
       <c r="M69" t="n">
         <v>3072.4</v>
       </c>
       <c r="N69" t="n">
-        <v>-2.9</v>
+        <v>-2.5</v>
       </c>
       <c r="O69" t="n">
         <v>244500</v>
@@ -4338,40 +4338,40 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>19553</v>
+        <v>20041</v>
       </c>
       <c r="D70" t="n">
         <v>19122</v>
       </c>
       <c r="E70" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="F70" t="n">
-        <v>98532.2</v>
+        <v>100192.7</v>
       </c>
       <c r="G70" t="n">
         <v>97617.5</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="I70" t="n">
-        <v>136740.3</v>
+        <v>139318.5</v>
       </c>
       <c r="J70" t="n">
         <v>134651.3</v>
       </c>
       <c r="K70" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="L70" t="n">
-        <v>149138.7</v>
+        <v>152635.4</v>
       </c>
       <c r="M70" t="n">
         <v>148583.9</v>
       </c>
       <c r="N70" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>34050</v>
@@ -4452,40 +4452,40 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5425</v>
+        <v>5446</v>
       </c>
       <c r="D72" t="n">
         <v>5307</v>
       </c>
       <c r="E72" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="F72" t="n">
-        <v>19372.4</v>
+        <v>19444.4</v>
       </c>
       <c r="G72" t="n">
         <v>19164.7</v>
       </c>
       <c r="H72" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="I72" t="n">
-        <v>20475.3</v>
+        <v>20548.8</v>
       </c>
       <c r="J72" t="n">
         <v>20300.4</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="L72" t="n">
-        <v>21634.8</v>
+        <v>21669.4</v>
       </c>
       <c r="M72" t="n">
         <v>21507.9</v>
       </c>
       <c r="N72" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="O72" t="n">
         <v>89700</v>
@@ -4623,40 +4623,40 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D75" t="n">
         <v>1095</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F75" t="n">
-        <v>4287.6</v>
+        <v>4307</v>
       </c>
       <c r="G75" t="n">
         <v>4279.2</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I75" t="n">
-        <v>5039.6</v>
+        <v>5064.6</v>
       </c>
       <c r="J75" t="n">
         <v>4997.4</v>
       </c>
       <c r="K75" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="L75" t="n">
-        <v>5833.9</v>
+        <v>5878.2</v>
       </c>
       <c r="M75" t="n">
         <v>5789.7</v>
       </c>
       <c r="N75" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O75" t="n">
         <v>3490</v>
@@ -4965,34 +4965,34 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="D81" t="n">
         <v>1503</v>
       </c>
       <c r="E81" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="F81" t="n">
-        <v>5936.6</v>
+        <v>5923</v>
       </c>
       <c r="G81" t="n">
         <v>5854.9</v>
       </c>
       <c r="H81" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I81" t="n">
-        <v>6133.7</v>
+        <v>6114.9</v>
       </c>
       <c r="J81" t="n">
         <v>6091.5</v>
       </c>
       <c r="K81" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="L81" t="n">
-        <v>6369.3</v>
+        <v>6369.4</v>
       </c>
       <c r="M81" t="n">
         <v>6368.1</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6038</v>
+        <v>6037</v>
       </c>
       <c r="D84" t="n">
         <v>6081</v>
@@ -5145,31 +5145,31 @@
         <v>-0.7</v>
       </c>
       <c r="F84" t="n">
-        <v>20519.3</v>
+        <v>20554.3</v>
       </c>
       <c r="G84" t="n">
         <v>20653.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="I84" t="n">
-        <v>22467.7</v>
+        <v>22489.1</v>
       </c>
       <c r="J84" t="n">
         <v>22502.9</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="L84" t="n">
-        <v>23804.6</v>
+        <v>23864.3</v>
       </c>
       <c r="M84" t="n">
         <v>23821.8</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="O84" t="n">
         <v>52400</v>
@@ -5193,25 +5193,25 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3072</v>
+        <v>3087</v>
       </c>
       <c r="D85" t="n">
         <v>3062</v>
       </c>
       <c r="E85" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F85" t="n">
-        <v>11105.5</v>
+        <v>11108.8</v>
       </c>
       <c r="G85" t="n">
         <v>11111.1</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="I85" t="n">
-        <v>11996.9</v>
+        <v>11988.9</v>
       </c>
       <c r="J85" t="n">
         <v>11959</v>
@@ -5220,7 +5220,7 @@
         <v>0.3</v>
       </c>
       <c r="L85" t="n">
-        <v>12762.1</v>
+        <v>12761.4</v>
       </c>
       <c r="M85" t="n">
         <v>12715.1</v>
@@ -5250,22 +5250,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10237</v>
+        <v>10171</v>
       </c>
       <c r="D86" t="n">
         <v>10237</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="F86" t="n">
-        <v>33019.2</v>
+        <v>33448.1</v>
       </c>
       <c r="G86" t="n">
         <v>33019.2</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I86" t="n">
         <v>52718.3</v>
@@ -5307,31 +5307,31 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3919</v>
+        <v>3937</v>
       </c>
       <c r="D87" t="n">
         <v>3866</v>
       </c>
       <c r="E87" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F87" t="n">
-        <v>15120.1</v>
+        <v>15140.1</v>
       </c>
       <c r="G87" t="n">
         <v>15108.4</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I87" t="n">
-        <v>16261.1</v>
+        <v>16276.8</v>
       </c>
       <c r="J87" t="n">
         <v>16302.5</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="L87" t="n">
         <v>17211.8</v>
@@ -5478,40 +5478,40 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="D90" t="n">
         <v>498</v>
       </c>
       <c r="E90" t="n">
-        <v>-2</v>
+        <v>-5.2</v>
       </c>
       <c r="F90" t="n">
-        <v>1844.2</v>
+        <v>1773.4</v>
       </c>
       <c r="G90" t="n">
         <v>1856.2</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.6</v>
+        <v>-4.5</v>
       </c>
       <c r="I90" t="n">
-        <v>2244.1</v>
+        <v>2147.9</v>
       </c>
       <c r="J90" t="n">
         <v>2235.1</v>
       </c>
       <c r="K90" t="n">
-        <v>0.4</v>
+        <v>-3.9</v>
       </c>
       <c r="L90" t="n">
-        <v>2455.1</v>
+        <v>2443.3</v>
       </c>
       <c r="M90" t="n">
         <v>2456</v>
       </c>
       <c r="N90" t="n">
-        <v>-0</v>
+        <v>-0.5</v>
       </c>
       <c r="O90" t="n">
         <v>10190</v>
@@ -5592,40 +5592,40 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D92" t="n">
         <v>489</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F92" t="n">
-        <v>2212.7</v>
+        <v>2231.8</v>
       </c>
       <c r="G92" t="n">
         <v>2212.7</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I92" t="n">
-        <v>2287.4</v>
+        <v>2312.7</v>
       </c>
       <c r="J92" t="n">
         <v>2287.4</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L92" t="n">
-        <v>2883.4</v>
+        <v>2882</v>
       </c>
       <c r="M92" t="n">
         <v>2883.4</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O92" t="n">
         <v>14410</v>
@@ -5667,22 +5667,22 @@
         <v>-0.3</v>
       </c>
       <c r="I93" t="n">
-        <v>27590</v>
+        <v>27632</v>
       </c>
       <c r="J93" t="n">
         <v>27672</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="L93" t="n">
-        <v>31240.8</v>
+        <v>31373.3</v>
       </c>
       <c r="M93" t="n">
         <v>31358.5</v>
       </c>
       <c r="N93" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>190000</v>
@@ -5820,40 +5820,40 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="D96" t="n">
         <v>1270</v>
       </c>
       <c r="E96" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="F96" t="n">
-        <v>5019.9</v>
+        <v>5051.7</v>
       </c>
       <c r="G96" t="n">
         <v>5026.8</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
       <c r="I96" t="n">
-        <v>5897.3</v>
+        <v>5877.6</v>
       </c>
       <c r="J96" t="n">
         <v>5876.9</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>5924.6</v>
+        <v>5885.7</v>
       </c>
       <c r="M96" t="n">
         <v>5924.6</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O96" t="n">
         <v>223000</v>
@@ -5934,31 +5934,31 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5300</v>
+        <v>5335</v>
       </c>
       <c r="D98" t="n">
         <v>5252</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F98" t="n">
-        <v>19176.2</v>
+        <v>19239.6</v>
       </c>
       <c r="G98" t="n">
         <v>19011.6</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>23327.3</v>
+        <v>23307.3</v>
       </c>
       <c r="J98" t="n">
         <v>23489.7</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="L98" t="n">
         <v>27375.2</v>
@@ -6105,25 +6105,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3557</v>
+        <v>3601</v>
       </c>
       <c r="D101" t="n">
         <v>3517</v>
       </c>
       <c r="E101" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="F101" t="n">
-        <v>13991.6</v>
+        <v>14034.5</v>
       </c>
       <c r="G101" t="n">
         <v>13940.8</v>
       </c>
       <c r="H101" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I101" t="n">
-        <v>15191</v>
+        <v>15201.9</v>
       </c>
       <c r="J101" t="n">
         <v>15092.4</v>
@@ -6132,13 +6132,13 @@
         <v>0.7</v>
       </c>
       <c r="L101" t="n">
-        <v>15938.8</v>
+        <v>15932.4</v>
       </c>
       <c r="M101" t="n">
         <v>15771.5</v>
       </c>
       <c r="N101" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
         <v>50900</v>
@@ -6162,40 +6162,40 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="D102" t="n">
         <v>1002</v>
       </c>
       <c r="E102" t="n">
-        <v>-5.1</v>
+        <v>-7.1</v>
       </c>
       <c r="F102" t="n">
-        <v>4564.2</v>
+        <v>4546.9</v>
       </c>
       <c r="G102" t="n">
         <v>4679.8</v>
       </c>
       <c r="H102" t="n">
-        <v>-2.5</v>
+        <v>-2.8</v>
       </c>
       <c r="I102" t="n">
-        <v>6612.7</v>
+        <v>6570.8</v>
       </c>
       <c r="J102" t="n">
         <v>6650.4</v>
       </c>
       <c r="K102" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="L102" t="n">
-        <v>8049.8</v>
+        <v>8017.4</v>
       </c>
       <c r="M102" t="n">
         <v>8075.1</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="O102" t="n">
         <v>149200</v>
@@ -6561,40 +6561,40 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2725</v>
+        <v>2706</v>
       </c>
       <c r="D109" t="n">
         <v>2768</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="F109" t="n">
-        <v>11569.8</v>
+        <v>11551.8</v>
       </c>
       <c r="G109" t="n">
         <v>11805.3</v>
       </c>
       <c r="H109" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="I109" t="n">
-        <v>15181.7</v>
+        <v>15008.9</v>
       </c>
       <c r="J109" t="n">
         <v>15557.9</v>
       </c>
       <c r="K109" t="n">
-        <v>-2.4</v>
+        <v>-3.5</v>
       </c>
       <c r="L109" t="n">
-        <v>18232.4</v>
+        <v>18246.1</v>
       </c>
       <c r="M109" t="n">
         <v>18626.1</v>
       </c>
       <c r="N109" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="O109" t="n">
         <v>159000</v>
@@ -6732,40 +6732,40 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="D112" t="n">
         <v>502</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.2</v>
+        <v>-3.6</v>
       </c>
       <c r="F112" t="n">
-        <v>2488</v>
+        <v>2479.7</v>
       </c>
       <c r="G112" t="n">
         <v>2517.9</v>
       </c>
       <c r="H112" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="I112" t="n">
-        <v>2330.9</v>
+        <v>2351.1</v>
       </c>
       <c r="J112" t="n">
         <v>2311</v>
       </c>
       <c r="K112" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="L112" t="n">
-        <v>3311.8</v>
+        <v>3364.5</v>
       </c>
       <c r="M112" t="n">
         <v>3257.2</v>
       </c>
       <c r="N112" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="O112" t="n">
         <v>92000</v>
@@ -7416,40 +7416,40 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D124" t="n">
         <v>595</v>
       </c>
       <c r="E124" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="F124" t="n">
-        <v>2404.7</v>
+        <v>2416.7</v>
       </c>
       <c r="G124" t="n">
         <v>2407.6</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I124" t="n">
-        <v>3819.7</v>
+        <v>3854</v>
       </c>
       <c r="J124" t="n">
         <v>3687.6</v>
       </c>
       <c r="K124" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="L124" t="n">
-        <v>4613</v>
+        <v>4707.3</v>
       </c>
       <c r="M124" t="n">
         <v>4521.6</v>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="O124" t="n">
         <v>46900</v>
@@ -7587,13 +7587,13 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>8267.299999999999</v>
+        <v>8338.200000000001</v>
       </c>
       <c r="G127" t="n">
         <v>8132.5</v>
       </c>
       <c r="H127" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I127" t="n">
         <v>9144.799999999999</v>
@@ -7722,40 +7722,40 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>14936</v>
+        <v>15727</v>
       </c>
       <c r="D130" t="n">
         <v>14123</v>
       </c>
       <c r="E130" t="n">
-        <v>5.8</v>
+        <v>11.4</v>
       </c>
       <c r="F130" t="n">
-        <v>52816.8</v>
+        <v>54903.6</v>
       </c>
       <c r="G130" t="n">
         <v>50950.2</v>
       </c>
       <c r="H130" t="n">
-        <v>3.7</v>
+        <v>7.8</v>
       </c>
       <c r="I130" t="n">
-        <v>31630.4</v>
+        <v>33584.2</v>
       </c>
       <c r="J130" t="n">
         <v>31187.9</v>
       </c>
       <c r="K130" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="L130" t="n">
-        <v>37398.4</v>
+        <v>38301.9</v>
       </c>
       <c r="M130" t="n">
         <v>36712.4</v>
       </c>
       <c r="N130" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="O130" t="n">
         <v>121400</v>
@@ -7779,31 +7779,31 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2779</v>
+        <v>2777</v>
       </c>
       <c r="D131" t="n">
         <v>2773</v>
       </c>
       <c r="E131" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F131" t="n">
-        <v>12844.8</v>
+        <v>12832.5</v>
       </c>
       <c r="G131" t="n">
         <v>12855.1</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="I131" t="n">
-        <v>14582.7</v>
+        <v>14554.2</v>
       </c>
       <c r="J131" t="n">
         <v>14545.4</v>
       </c>
       <c r="K131" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L131" t="n">
         <v>16091</v>
@@ -7836,40 +7836,40 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>848</v>
+        <v>819</v>
       </c>
       <c r="D132" t="n">
         <v>831</v>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>-1.4</v>
       </c>
       <c r="F132" t="n">
-        <v>3654.7</v>
+        <v>3630.2</v>
       </c>
       <c r="G132" t="n">
         <v>3617.8</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I132" t="n">
-        <v>3583.9</v>
+        <v>3537.3</v>
       </c>
       <c r="J132" t="n">
         <v>3606.6</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="L132" t="n">
-        <v>3961.3</v>
+        <v>3903.7</v>
       </c>
       <c r="M132" t="n">
         <v>3982.7</v>
       </c>
       <c r="N132" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="O132" t="n">
         <v>62100</v>
@@ -8064,40 +8064,40 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="D136" t="n">
         <v>712</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F136" t="n">
-        <v>2243.2</v>
+        <v>2328.2</v>
       </c>
       <c r="G136" t="n">
         <v>2243.2</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I136" t="n">
-        <v>2576.2</v>
+        <v>2607.6</v>
       </c>
       <c r="J136" t="n">
         <v>2576.2</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L136" t="n">
-        <v>2980.4</v>
+        <v>3037.5</v>
       </c>
       <c r="M136" t="n">
         <v>2981.2</v>
       </c>
       <c r="N136" t="n">
-        <v>-0</v>
+        <v>1.9</v>
       </c>
       <c r="O136" t="n">
         <v>53600</v>
@@ -8121,40 +8121,40 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="D137" t="n">
         <v>866</v>
       </c>
       <c r="E137" t="n">
-        <v>20.3</v>
+        <v>21.9</v>
       </c>
       <c r="F137" t="n">
-        <v>3105.6</v>
+        <v>3103.2</v>
       </c>
       <c r="G137" t="n">
         <v>2961.1</v>
       </c>
       <c r="H137" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I137" t="n">
-        <v>3147.9</v>
+        <v>3164.5</v>
       </c>
       <c r="J137" t="n">
         <v>3106.5</v>
       </c>
       <c r="K137" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="L137" t="n">
-        <v>3403.1</v>
+        <v>3447.3</v>
       </c>
       <c r="M137" t="n">
         <v>3328.3</v>
       </c>
       <c r="N137" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="O137" t="n">
         <v>386000</v>
@@ -8463,40 +8463,40 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D143" t="n">
         <v>953</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="F143" t="n">
-        <v>3146.1</v>
+        <v>3152.6</v>
       </c>
       <c r="G143" t="n">
         <v>3148.2</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="I143" t="n">
-        <v>3638.5</v>
+        <v>3650.9</v>
       </c>
       <c r="J143" t="n">
         <v>3633</v>
       </c>
       <c r="K143" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L143" t="n">
-        <v>4102.8</v>
+        <v>4118.9</v>
       </c>
       <c r="M143" t="n">
         <v>4096.7</v>
       </c>
       <c r="N143" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="O143" t="n">
         <v>107600</v>
@@ -8577,40 +8577,40 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D145" t="n">
         <v>210</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>-3.8</v>
       </c>
       <c r="F145" t="n">
-        <v>783.8</v>
+        <v>785.8</v>
       </c>
       <c r="G145" t="n">
         <v>804.6</v>
       </c>
       <c r="H145" t="n">
-        <v>-2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="I145" t="n">
-        <v>903.5</v>
+        <v>901.4</v>
       </c>
       <c r="J145" t="n">
         <v>937.8</v>
       </c>
       <c r="K145" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="L145" t="n">
-        <v>988.5</v>
+        <v>984.8</v>
       </c>
       <c r="M145" t="n">
         <v>1023.2</v>
       </c>
       <c r="N145" t="n">
-        <v>-3.4</v>
+        <v>-3.8</v>
       </c>
       <c r="O145" t="n">
         <v>68300</v>
@@ -8691,34 +8691,34 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D147" t="n">
         <v>695</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="F147" t="n">
-        <v>2334.6</v>
+        <v>2331.9</v>
       </c>
       <c r="G147" t="n">
         <v>2327.5</v>
       </c>
       <c r="H147" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I147" t="n">
-        <v>2777.6</v>
+        <v>2774.9</v>
       </c>
       <c r="J147" t="n">
         <v>2766.5</v>
       </c>
       <c r="K147" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L147" t="n">
-        <v>3207.5</v>
+        <v>3206.8</v>
       </c>
       <c r="M147" t="n">
         <v>3194</v>
@@ -8748,25 +8748,25 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="D148" t="n">
         <v>1037</v>
       </c>
       <c r="E148" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="F148" t="n">
-        <v>4032.2</v>
+        <v>4022.1</v>
       </c>
       <c r="G148" t="n">
         <v>4028.2</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="I148" t="n">
-        <v>4689.4</v>
+        <v>4688.9</v>
       </c>
       <c r="J148" t="n">
         <v>4685.9</v>
@@ -8775,13 +8775,13 @@
         <v>0.1</v>
       </c>
       <c r="L148" t="n">
-        <v>5201.8</v>
+        <v>5231.2</v>
       </c>
       <c r="M148" t="n">
         <v>5234.6</v>
       </c>
       <c r="N148" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="O148" t="n">
         <v>44800</v>
@@ -9204,31 +9204,31 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="D156" t="n">
         <v>1376</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F156" t="n">
-        <v>6482.2</v>
+        <v>6487.6</v>
       </c>
       <c r="G156" t="n">
         <v>6507.6</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>7020.5</v>
+        <v>7029.8</v>
       </c>
       <c r="J156" t="n">
         <v>7041.8</v>
       </c>
       <c r="K156" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="L156" t="n">
         <v>7523.1</v>
@@ -9375,31 +9375,31 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D159" t="n">
         <v>461</v>
       </c>
       <c r="E159" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="F159" t="n">
-        <v>1892.3</v>
+        <v>1902.3</v>
       </c>
       <c r="G159" t="n">
         <v>1888.8</v>
       </c>
       <c r="H159" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="I159" t="n">
-        <v>2159.4</v>
+        <v>2170.4</v>
       </c>
       <c r="J159" t="n">
         <v>2153.5</v>
       </c>
       <c r="K159" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="L159" t="n">
         <v>2398.1</v>
@@ -9546,40 +9546,40 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1279</v>
+        <v>1305</v>
       </c>
       <c r="D162" t="n">
         <v>1279</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F162" t="n">
-        <v>4462.8</v>
+        <v>4538.8</v>
       </c>
       <c r="G162" t="n">
         <v>4462.8</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>5285.2</v>
+        <v>5431.5</v>
       </c>
       <c r="J162" t="n">
         <v>5285.2</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="L162" t="n">
-        <v>5652.6</v>
+        <v>5773.2</v>
       </c>
       <c r="M162" t="n">
         <v>5652.6</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O162" t="n">
         <v>278000</v>
@@ -9603,40 +9603,40 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2806</v>
+        <v>2812</v>
       </c>
       <c r="D163" t="n">
         <v>2845</v>
       </c>
       <c r="E163" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="F163" t="n">
-        <v>10879.9</v>
+        <v>10910.6</v>
       </c>
       <c r="G163" t="n">
         <v>10942.1</v>
       </c>
       <c r="H163" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="I163" t="n">
-        <v>15397.1</v>
+        <v>15413.5</v>
       </c>
       <c r="J163" t="n">
         <v>15477.6</v>
       </c>
       <c r="K163" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="L163" t="n">
-        <v>19657.9</v>
+        <v>20226.6</v>
       </c>
       <c r="M163" t="n">
         <v>19558.8</v>
       </c>
       <c r="N163" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="O163" t="n">
         <v>2789000</v>
@@ -10059,31 +10059,31 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>9925</v>
+        <v>9910</v>
       </c>
       <c r="D171" t="n">
         <v>9902</v>
       </c>
       <c r="E171" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F171" t="n">
-        <v>38979</v>
+        <v>38876</v>
       </c>
       <c r="G171" t="n">
         <v>38897.6</v>
       </c>
       <c r="H171" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I171" t="n">
-        <v>45775.8</v>
+        <v>45739.8</v>
       </c>
       <c r="J171" t="n">
         <v>45686.3</v>
       </c>
       <c r="K171" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L171" t="n">
         <v>52641.7</v>
@@ -10287,25 +10287,25 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="D175" t="n">
         <v>1199</v>
       </c>
       <c r="E175" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F175" t="n">
-        <v>5218.5</v>
+        <v>5259.8</v>
       </c>
       <c r="G175" t="n">
         <v>5129.8</v>
       </c>
       <c r="H175" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I175" t="n">
-        <v>5621.3</v>
+        <v>5620.8</v>
       </c>
       <c r="J175" t="n">
         <v>5671.2</v>
@@ -10314,13 +10314,13 @@
         <v>-0.9</v>
       </c>
       <c r="L175" t="n">
-        <v>6108.3</v>
+        <v>6112.2</v>
       </c>
       <c r="M175" t="n">
         <v>6198.3</v>
       </c>
       <c r="N175" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="O175" t="n">
         <v>60200</v>
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D176" t="n">
         <v>323</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="F176" t="n">
         <v>1388.2</v>
@@ -10401,16 +10401,16 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D177" t="n">
         <v>969</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F177" t="n">
-        <v>5307.8</v>
+        <v>5308.8</v>
       </c>
       <c r="G177" t="n">
         <v>5294.5</v>
@@ -10419,22 +10419,22 @@
         <v>0.3</v>
       </c>
       <c r="I177" t="n">
-        <v>5622.7</v>
+        <v>5626.7</v>
       </c>
       <c r="J177" t="n">
         <v>5592.8</v>
       </c>
       <c r="K177" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L177" t="n">
-        <v>6051.2</v>
+        <v>6061.2</v>
       </c>
       <c r="M177" t="n">
         <v>5983.8</v>
       </c>
       <c r="N177" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="O177" t="n">
         <v>79000</v>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-17 · 전주 2026-07-13</t>
+          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-21 · 전주 2026-07-17</t>
         </is>
       </c>
     </row>
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="D3" t="n">
         <v>615</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1958.2</v>
+        <v>1949.2</v>
       </c>
       <c r="G3" t="n">
         <v>1958.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2060.6</v>
+        <v>2049.7</v>
       </c>
       <c r="J3" t="n">
         <v>2060.6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L3" t="n">
         <v>2183</v>
@@ -591,13 +591,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>14790</v>
+      </c>
+      <c r="P3" t="n">
         <v>14910</v>
       </c>
-      <c r="P3" t="n">
-        <v>14960</v>
-      </c>
       <c r="Q3" t="n">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="4">
@@ -615,46 +615,46 @@
         <v>571</v>
       </c>
       <c r="D4" t="n">
-        <v>612</v>
+        <v>571</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.7</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1311.3</v>
       </c>
       <c r="G4" t="n">
-        <v>1321.9</v>
+        <v>1311.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>2224.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2176.3</v>
+        <v>2224.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>2994</v>
       </c>
       <c r="M4" t="n">
-        <v>2997.6</v>
+        <v>2994</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>69500</v>
+      </c>
+      <c r="P4" t="n">
         <v>70800</v>
       </c>
-      <c r="P4" t="n">
-        <v>68100</v>
-      </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -669,49 +669,49 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>1122</v>
+      </c>
+      <c r="D5" t="n">
         <v>1132</v>
       </c>
-      <c r="D5" t="n">
-        <v>1140</v>
-      </c>
       <c r="E5" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="F5" t="n">
+        <v>5083.3</v>
+      </c>
+      <c r="G5" t="n">
         <v>5126.3</v>
       </c>
-      <c r="G5" t="n">
-        <v>5163</v>
-      </c>
       <c r="H5" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I5" t="n">
+        <v>5652.6</v>
+      </c>
+      <c r="J5" t="n">
         <v>5683.2</v>
       </c>
-      <c r="J5" t="n">
-        <v>5718.2</v>
-      </c>
       <c r="K5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6095.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6123.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>72100</v>
+      </c>
+      <c r="P5" t="n">
+        <v>72500</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.6</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6123.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6160.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>72500</v>
-      </c>
-      <c r="P5" t="n">
-        <v>73600</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="6">
@@ -729,7 +729,7 @@
         <v>4572</v>
       </c>
       <c r="D6" t="n">
-        <v>4571</v>
+        <v>4572</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
         <v>17032.2</v>
       </c>
       <c r="G6" t="n">
-        <v>17063.8</v>
+        <v>17032.2</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>23515</v>
       </c>
       <c r="J6" t="n">
-        <v>23491.7</v>
+        <v>23515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>29523.5</v>
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>1107000</v>
+      </c>
+      <c r="P6" t="n">
         <v>1202000</v>
       </c>
-      <c r="P6" t="n">
-        <v>1238000</v>
-      </c>
       <c r="Q6" t="n">
-        <v>-2.9</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="7">
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>44750</v>
+      </c>
+      <c r="P7" t="n">
         <v>46450</v>
       </c>
-      <c r="P7" t="n">
-        <v>45550</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="8">
@@ -876,13 +876,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
+        <v>25450</v>
+      </c>
+      <c r="P8" t="n">
         <v>25250</v>
       </c>
-      <c r="P8" t="n">
-        <v>24650</v>
-      </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -900,25 +900,25 @@
         <v>27935</v>
       </c>
       <c r="D9" t="n">
-        <v>27920</v>
+        <v>27935</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>102889.3</v>
       </c>
       <c r="G9" t="n">
-        <v>102466.9</v>
+        <v>102889.3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>113580.6</v>
       </c>
       <c r="J9" t="n">
-        <v>113527.7</v>
+        <v>113580.6</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -927,19 +927,19 @@
         <v>119352.9</v>
       </c>
       <c r="M9" t="n">
-        <v>120853.9</v>
+        <v>119352.9</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>142500</v>
+      </c>
+      <c r="P9" t="n">
         <v>149700</v>
       </c>
-      <c r="P9" t="n">
-        <v>143500</v>
-      </c>
       <c r="Q9" t="n">
-        <v>4.3</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="10">
@@ -957,46 +957,46 @@
         <v>641632</v>
       </c>
       <c r="D10" t="n">
-        <v>650541</v>
+        <v>641632</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>2728835.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2767812.5</v>
+        <v>2728835.8</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>3981826.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4043634.6</v>
+        <v>3981826.7</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>3871437.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3939915.6</v>
+        <v>3871437.2</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
+        <v>1823000</v>
+      </c>
+      <c r="P10" t="n">
         <v>1842000</v>
       </c>
-      <c r="P10" t="n">
-        <v>1845000</v>
-      </c>
       <c r="Q10" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D11" t="n">
         <v>2026</v>
       </c>
-      <c r="D11" t="n">
-        <v>2005</v>
-      </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="F11" t="n">
+        <v>8315.799999999999</v>
+      </c>
+      <c r="G11" t="n">
         <v>8280.6</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8244.4</v>
       </c>
       <c r="H11" t="n">
         <v>0.4</v>
       </c>
       <c r="I11" t="n">
+        <v>11067.6</v>
+      </c>
+      <c r="J11" t="n">
         <v>11114.9</v>
       </c>
-      <c r="J11" t="n">
-        <v>11142.2</v>
-      </c>
       <c r="K11" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="L11" t="n">
+        <v>13657.2</v>
+      </c>
+      <c r="M11" t="n">
         <v>13860.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>13845.2</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.1</v>
+        <v>-1.5</v>
       </c>
       <c r="O11" t="n">
+        <v>92700</v>
+      </c>
+      <c r="P11" t="n">
         <v>99000</v>
       </c>
-      <c r="P11" t="n">
-        <v>101500</v>
-      </c>
       <c r="Q11" t="n">
-        <v>-2.5</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="12">
@@ -1071,46 +1071,46 @@
         <v>8815</v>
       </c>
       <c r="D12" t="n">
-        <v>8312</v>
+        <v>8815</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>30870.2</v>
       </c>
       <c r="G12" t="n">
-        <v>30345.1</v>
+        <v>30870.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>33681.5</v>
       </c>
       <c r="J12" t="n">
-        <v>32907.2</v>
+        <v>33681.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>34114</v>
       </c>
       <c r="M12" t="n">
-        <v>33721.5</v>
+        <v>34114</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
+        <v>612000</v>
+      </c>
+      <c r="P12" t="n">
         <v>701000</v>
       </c>
-      <c r="P12" t="n">
-        <v>639000</v>
-      </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>-12.7</v>
       </c>
     </row>
     <row r="13">
@@ -1137,37 +1137,37 @@
         <v>55718.1</v>
       </c>
       <c r="G13" t="n">
-        <v>56369.3</v>
+        <v>55718.1</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>67947</v>
       </c>
       <c r="J13" t="n">
-        <v>69187.3</v>
+        <v>67947</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>72448</v>
       </c>
       <c r="M13" t="n">
-        <v>72135</v>
+        <v>72448</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
+        <v>86900</v>
+      </c>
+      <c r="P13" t="n">
         <v>93200</v>
       </c>
-      <c r="P13" t="n">
-        <v>92300</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="14">
@@ -1218,13 +1218,13 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
+        <v>102900</v>
+      </c>
+      <c r="P14" t="n">
         <v>109600</v>
       </c>
-      <c r="P14" t="n">
-        <v>110700</v>
-      </c>
       <c r="Q14" t="n">
-        <v>-1</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,13 +1275,13 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
+        <v>130700</v>
+      </c>
+      <c r="P15" t="n">
         <v>135700</v>
       </c>
-      <c r="P15" t="n">
-        <v>142600</v>
-      </c>
       <c r="Q15" t="n">
-        <v>-4.8</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="16">
@@ -1299,46 +1299,46 @@
         <v>529</v>
       </c>
       <c r="D16" t="n">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>1517.9</v>
       </c>
       <c r="G16" t="n">
-        <v>1464.4</v>
+        <v>1517.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>1976.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2038.9</v>
+        <v>1976.6</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2211.6</v>
       </c>
       <c r="M16" t="n">
-        <v>2062.4</v>
+        <v>2211.6</v>
       </c>
       <c r="N16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
+        <v>31250</v>
+      </c>
+      <c r="P16" t="n">
         <v>32500</v>
       </c>
-      <c r="P16" t="n">
-        <v>30250</v>
-      </c>
       <c r="Q16" t="n">
-        <v>7.4</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="17">
@@ -1356,46 +1356,46 @@
         <v>423</v>
       </c>
       <c r="D17" t="n">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>1995.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1963.7</v>
+        <v>1995.6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>2252.9</v>
       </c>
       <c r="J17" t="n">
-        <v>2356.2</v>
+        <v>2252.9</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.4</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2899.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3058</v>
+        <v>2899.4</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
+        <v>25450</v>
+      </c>
+      <c r="P17" t="n">
         <v>27700</v>
       </c>
-      <c r="P17" t="n">
-        <v>28300</v>
-      </c>
       <c r="Q17" t="n">
-        <v>-2.1</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="18">
@@ -1410,40 +1410,40 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>10748.6</v>
+      </c>
+      <c r="G18" t="n">
         <v>10625.3</v>
       </c>
-      <c r="G18" t="n">
-        <v>10434.4</v>
-      </c>
       <c r="H18" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="I18" t="n">
+        <v>12188.1</v>
+      </c>
+      <c r="J18" t="n">
         <v>12179.5</v>
       </c>
-      <c r="J18" t="n">
-        <v>12149.2</v>
-      </c>
       <c r="K18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L18" t="n">
+        <v>13346.7</v>
+      </c>
+      <c r="M18" t="n">
         <v>13329</v>
       </c>
-      <c r="M18" t="n">
-        <v>13426.9</v>
-      </c>
       <c r="N18" t="n">
-        <v>-0.7</v>
+        <v>0.1</v>
       </c>
       <c r="O18" t="n">
+        <v>37550</v>
+      </c>
+      <c r="P18" t="n">
         <v>38300</v>
       </c>
-      <c r="P18" t="n">
-        <v>38550</v>
-      </c>
       <c r="Q18" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="19">
@@ -1494,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
+        <v>17370</v>
+      </c>
+      <c r="P19" t="n">
         <v>17260</v>
       </c>
-      <c r="P19" t="n">
-        <v>17500</v>
-      </c>
       <c r="Q19" t="n">
-        <v>-1.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
@@ -1533,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
+        <v>25400</v>
+      </c>
+      <c r="P20" t="n">
         <v>26050</v>
       </c>
-      <c r="P20" t="n">
-        <v>26800</v>
-      </c>
       <c r="Q20" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="21">
@@ -1554,49 +1554,49 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1051</v>
+        <v>1075</v>
       </c>
       <c r="D21" t="n">
         <v>1051</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="F21" t="n">
-        <v>4153.2</v>
+        <v>4245.5</v>
       </c>
       <c r="G21" t="n">
         <v>4153.2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4725</v>
+        <v>4841.8</v>
       </c>
       <c r="J21" t="n">
         <v>4725</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L21" t="n">
-        <v>5072.2</v>
+        <v>5176.8</v>
       </c>
       <c r="M21" t="n">
         <v>5072.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
+        <v>401500</v>
+      </c>
+      <c r="P21" t="n">
         <v>420000</v>
       </c>
-      <c r="P21" t="n">
-        <v>434000</v>
-      </c>
       <c r="Q21" t="n">
-        <v>-3.2</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="22">
@@ -1647,13 +1647,13 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>95200</v>
+      </c>
+      <c r="P22" t="n">
         <v>99600</v>
       </c>
-      <c r="P22" t="n">
-        <v>103700</v>
-      </c>
       <c r="Q22" t="n">
-        <v>-4</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="23">
@@ -1668,49 +1668,49 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1785</v>
+      </c>
+      <c r="D23" t="n">
         <v>1781</v>
       </c>
-      <c r="D23" t="n">
-        <v>1790</v>
-      </c>
       <c r="E23" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F23" t="n">
+        <v>7316.2</v>
+      </c>
+      <c r="G23" t="n">
         <v>7309.6</v>
       </c>
-      <c r="G23" t="n">
-        <v>7298.4</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I23" t="n">
+        <v>8826.9</v>
+      </c>
+      <c r="J23" t="n">
         <v>8786.1</v>
       </c>
-      <c r="J23" t="n">
-        <v>8765.200000000001</v>
-      </c>
       <c r="K23" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L23" t="n">
+        <v>10322.7</v>
+      </c>
+      <c r="M23" t="n">
         <v>10286.4</v>
       </c>
-      <c r="M23" t="n">
-        <v>10284.3</v>
-      </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O23" t="n">
+        <v>1118000</v>
+      </c>
+      <c r="P23" t="n">
         <v>1069000</v>
       </c>
-      <c r="P23" t="n">
-        <v>1110000</v>
-      </c>
       <c r="Q23" t="n">
-        <v>-3.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="24">
@@ -1728,46 +1728,46 @@
         <v>-2377</v>
       </c>
       <c r="D24" t="n">
-        <v>-2207</v>
+        <v>-2377</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.7</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>11051.5</v>
       </c>
       <c r="G24" t="n">
-        <v>8666.299999999999</v>
+        <v>11051.5</v>
       </c>
       <c r="H24" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>22324.6</v>
       </c>
       <c r="J24" t="n">
-        <v>20882.1</v>
+        <v>22324.6</v>
       </c>
       <c r="K24" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>26471.7</v>
       </c>
       <c r="M24" t="n">
-        <v>25171.4</v>
+        <v>26471.7</v>
       </c>
       <c r="N24" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
+        <v>25700</v>
+      </c>
+      <c r="P24" t="n">
         <v>26500</v>
       </c>
-      <c r="P24" t="n">
-        <v>25850</v>
-      </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="25">
@@ -1791,40 +1791,40 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>16182.7</v>
+        <v>16315.8</v>
       </c>
       <c r="G25" t="n">
         <v>16182.7</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I25" t="n">
-        <v>20528.9</v>
+        <v>20997.3</v>
       </c>
       <c r="J25" t="n">
         <v>20528.9</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="L25" t="n">
-        <v>21051.1</v>
+        <v>22184.8</v>
       </c>
       <c r="M25" t="n">
         <v>21051.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O25" t="n">
+        <v>96700</v>
+      </c>
+      <c r="P25" t="n">
         <v>98800</v>
       </c>
-      <c r="P25" t="n">
-        <v>99300</v>
-      </c>
       <c r="Q25" t="n">
-        <v>-0.5</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="26">
@@ -1842,46 +1842,46 @@
         <v>292</v>
       </c>
       <c r="D26" t="n">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>997.3</v>
       </c>
       <c r="G26" t="n">
-        <v>952.8</v>
+        <v>997.3</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>1648.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1606.5</v>
+        <v>1648.4</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>2856.9</v>
       </c>
       <c r="M26" t="n">
-        <v>2814.7</v>
+        <v>2856.9</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
+        <v>135800</v>
+      </c>
+      <c r="P26" t="n">
         <v>147600</v>
       </c>
-      <c r="P26" t="n">
-        <v>150700</v>
-      </c>
       <c r="Q26" t="n">
-        <v>-2.1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="27">
@@ -1896,49 +1896,49 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="D27" t="n">
         <v>357</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="F27" t="n">
-        <v>1388</v>
+        <v>1440</v>
       </c>
       <c r="G27" t="n">
         <v>1388</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1592.5</v>
+        <v>1628.4</v>
       </c>
       <c r="J27" t="n">
         <v>1592.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1730</v>
+        <v>1748.7</v>
       </c>
       <c r="M27" t="n">
         <v>1730</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
+        <v>45850</v>
+      </c>
+      <c r="P27" t="n">
         <v>45650</v>
       </c>
-      <c r="P27" t="n">
-        <v>46000</v>
-      </c>
       <c r="Q27" t="n">
-        <v>-0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28">
@@ -1953,49 +1953,49 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>833</v>
+      </c>
+      <c r="D28" t="n">
         <v>866</v>
       </c>
-      <c r="D28" t="n">
-        <v>1027</v>
-      </c>
       <c r="E28" t="n">
-        <v>-15.7</v>
+        <v>-3.8</v>
       </c>
       <c r="F28" t="n">
+        <v>3982.2</v>
+      </c>
+      <c r="G28" t="n">
         <v>4077.3</v>
       </c>
-      <c r="G28" t="n">
-        <v>4371.2</v>
-      </c>
       <c r="H28" t="n">
-        <v>-6.7</v>
+        <v>-2.3</v>
       </c>
       <c r="I28" t="n">
+        <v>7071.2</v>
+      </c>
+      <c r="J28" t="n">
         <v>7113.6</v>
       </c>
-      <c r="J28" t="n">
-        <v>7567</v>
-      </c>
       <c r="K28" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
       <c r="L28" t="n">
+        <v>7982.9</v>
+      </c>
+      <c r="M28" t="n">
         <v>8048.5</v>
       </c>
-      <c r="M28" t="n">
-        <v>8315.4</v>
-      </c>
       <c r="N28" t="n">
-        <v>-3.2</v>
+        <v>-0.8</v>
       </c>
       <c r="O28" t="n">
+        <v>25200</v>
+      </c>
+      <c r="P28" t="n">
         <v>26550</v>
       </c>
-      <c r="P28" t="n">
-        <v>26800</v>
-      </c>
       <c r="Q28" t="n">
-        <v>-0.9</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="29">
@@ -2010,49 +2010,49 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>1528</v>
+      </c>
+      <c r="D29" t="n">
         <v>1526</v>
       </c>
-      <c r="D29" t="n">
-        <v>1502</v>
-      </c>
       <c r="E29" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="F29" t="n">
+        <v>7676</v>
+      </c>
+      <c r="G29" t="n">
         <v>7675.2</v>
       </c>
-      <c r="G29" t="n">
-        <v>7610.5</v>
-      </c>
       <c r="H29" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
+        <v>8596.4</v>
+      </c>
+      <c r="J29" t="n">
         <v>8596.9</v>
       </c>
-      <c r="J29" t="n">
-        <v>8508.299999999999</v>
-      </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="L29" t="n">
+        <v>9080.6</v>
+      </c>
+      <c r="M29" t="n">
         <v>9078.200000000001</v>
       </c>
-      <c r="M29" t="n">
-        <v>8956</v>
-      </c>
       <c r="N29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
+        <v>555000</v>
+      </c>
+      <c r="P29" t="n">
         <v>589000</v>
       </c>
-      <c r="P29" t="n">
-        <v>591000</v>
-      </c>
       <c r="Q29" t="n">
-        <v>-0.3</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="30">
@@ -2070,46 +2070,46 @@
         <v>497</v>
       </c>
       <c r="D30" t="n">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="E30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>2150.9</v>
       </c>
       <c r="G30" t="n">
-        <v>2133.8</v>
+        <v>2150.9</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>2328.6</v>
       </c>
       <c r="J30" t="n">
-        <v>2307.4</v>
+        <v>2328.6</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>2454.5</v>
       </c>
       <c r="M30" t="n">
-        <v>2449.6</v>
+        <v>2454.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
+        <v>351000</v>
+      </c>
+      <c r="P30" t="n">
         <v>349500</v>
       </c>
-      <c r="P30" t="n">
-        <v>356000</v>
-      </c>
       <c r="Q30" t="n">
-        <v>-1.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31">
@@ -2160,13 +2160,13 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
+        <v>22450</v>
+      </c>
+      <c r="P31" t="n">
         <v>22800</v>
       </c>
-      <c r="P31" t="n">
-        <v>23050</v>
-      </c>
       <c r="Q31" t="n">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="32">
@@ -2184,46 +2184,46 @@
         <v>639</v>
       </c>
       <c r="D32" t="n">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>2123.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2138.2</v>
+        <v>2123.5</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>2342</v>
       </c>
       <c r="J32" t="n">
-        <v>2364.6</v>
+        <v>2342</v>
       </c>
       <c r="K32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>2484.3</v>
       </c>
       <c r="M32" t="n">
-        <v>2497</v>
+        <v>2484.3</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
+        <v>97400</v>
+      </c>
+      <c r="P32" t="n">
         <v>99400</v>
       </c>
-      <c r="P32" t="n">
-        <v>101600</v>
-      </c>
       <c r="Q32" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="33">
@@ -2238,49 +2238,49 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>30059</v>
+      </c>
+      <c r="D33" t="n">
         <v>30232</v>
       </c>
-      <c r="D33" t="n">
-        <v>31086</v>
-      </c>
       <c r="E33" t="n">
-        <v>-2.7</v>
+        <v>-0.6</v>
       </c>
       <c r="F33" t="n">
+        <v>117411.4</v>
+      </c>
+      <c r="G33" t="n">
         <v>117500.2</v>
       </c>
-      <c r="G33" t="n">
-        <v>118721.8</v>
-      </c>
       <c r="H33" t="n">
-        <v>-1</v>
+        <v>-0.1</v>
       </c>
       <c r="I33" t="n">
+        <v>132691</v>
+      </c>
+      <c r="J33" t="n">
         <v>132780.2</v>
       </c>
-      <c r="J33" t="n">
-        <v>133560</v>
-      </c>
       <c r="K33" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="L33" t="n">
         <v>144868.6</v>
       </c>
       <c r="M33" t="n">
-        <v>146466.8</v>
+        <v>144868.6</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
+        <v>393500</v>
+      </c>
+      <c r="P33" t="n">
         <v>425000</v>
       </c>
-      <c r="P33" t="n">
-        <v>444000</v>
-      </c>
       <c r="Q33" t="n">
-        <v>-4.3</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="34">
@@ -2298,46 +2298,46 @@
         <v>7299</v>
       </c>
       <c r="D34" t="n">
-        <v>7419</v>
+        <v>7299</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>30875.7</v>
       </c>
       <c r="G34" t="n">
-        <v>31078.4</v>
+        <v>30875.7</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>38602.4</v>
       </c>
       <c r="J34" t="n">
-        <v>38922.9</v>
+        <v>38602.4</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>44763.8</v>
       </c>
       <c r="M34" t="n">
-        <v>44719.4</v>
+        <v>44763.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
+        <v>298000</v>
+      </c>
+      <c r="P34" t="n">
         <v>311500</v>
       </c>
-      <c r="P34" t="n">
-        <v>308000</v>
-      </c>
       <c r="Q34" t="n">
-        <v>1.1</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="35">
@@ -2364,37 +2364,37 @@
         <v>21330.6</v>
       </c>
       <c r="G35" t="n">
-        <v>21132.5</v>
+        <v>21330.6</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>23130.1</v>
       </c>
       <c r="J35" t="n">
-        <v>23517.5</v>
+        <v>23130.1</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>24397.6</v>
       </c>
       <c r="M35" t="n">
-        <v>25037.6</v>
+        <v>24397.6</v>
       </c>
       <c r="N35" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
+        <v>163800</v>
+      </c>
+      <c r="P35" t="n">
         <v>163000</v>
       </c>
-      <c r="P35" t="n">
-        <v>159100</v>
-      </c>
       <c r="Q35" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -2445,13 +2445,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
+        <v>52400</v>
+      </c>
+      <c r="P36" t="n">
         <v>54400</v>
       </c>
-      <c r="P36" t="n">
-        <v>54200</v>
-      </c>
       <c r="Q36" t="n">
-        <v>0.4</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="37">
@@ -2478,7 +2478,7 @@
         <v>3832403.6</v>
       </c>
       <c r="G37" t="n">
-        <v>3832403.5</v>
+        <v>3832403.6</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2487,10 +2487,10 @@
         <v>5422607.3</v>
       </c>
       <c r="J37" t="n">
-        <v>5422607.5</v>
+        <v>5422607.3</v>
       </c>
       <c r="K37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>5327749.5</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
+        <v>257000</v>
+      </c>
+      <c r="P37" t="n">
         <v>255000</v>
       </c>
-      <c r="P37" t="n">
-        <v>254500</v>
-      </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="38">
@@ -2559,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
+        <v>29800</v>
+      </c>
+      <c r="P38" t="n">
         <v>31000</v>
       </c>
-      <c r="P38" t="n">
-        <v>31150</v>
-      </c>
       <c r="Q38" t="n">
-        <v>-0.5</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="39">
@@ -2580,31 +2580,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1265</v>
+        <v>1253</v>
       </c>
       <c r="D39" t="n">
         <v>1265</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="F39" t="n">
-        <v>5524</v>
+        <v>5511.8</v>
       </c>
       <c r="G39" t="n">
         <v>5524</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I39" t="n">
-        <v>5847.8</v>
+        <v>5853.2</v>
       </c>
       <c r="J39" t="n">
         <v>5847.8</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
         <v>6013</v>
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
+        <v>33550</v>
+      </c>
+      <c r="P39" t="n">
         <v>33350</v>
       </c>
-      <c r="P39" t="n">
-        <v>34500</v>
-      </c>
       <c r="Q39" t="n">
-        <v>-3.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40">
@@ -2649,37 +2649,37 @@
         <v>16923.6</v>
       </c>
       <c r="G40" t="n">
-        <v>16669</v>
+        <v>16923.6</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>19159.2</v>
       </c>
       <c r="J40" t="n">
-        <v>18990.1</v>
+        <v>19159.2</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>21845.4</v>
       </c>
       <c r="M40" t="n">
-        <v>21819.9</v>
+        <v>21845.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
+        <v>268000</v>
+      </c>
+      <c r="P40" t="n">
         <v>288000</v>
       </c>
-      <c r="P40" t="n">
-        <v>303500</v>
-      </c>
       <c r="Q40" t="n">
-        <v>-5.1</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="41">
@@ -2694,49 +2694,49 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D41" t="n">
         <v>210</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="F41" t="n">
-        <v>747.3</v>
+        <v>741.5</v>
       </c>
       <c r="G41" t="n">
         <v>747.3</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="I41" t="n">
-        <v>972.3</v>
+        <v>984.8</v>
       </c>
       <c r="J41" t="n">
         <v>972.3</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1352.6</v>
+        <v>1401.4</v>
       </c>
       <c r="M41" t="n">
         <v>1352.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
+        <v>119700</v>
+      </c>
+      <c r="P41" t="n">
         <v>122800</v>
       </c>
-      <c r="P41" t="n">
-        <v>120500</v>
-      </c>
       <c r="Q41" t="n">
-        <v>1.9</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="42">
@@ -2751,49 +2751,49 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>-396</v>
+      </c>
+      <c r="D42" t="n">
         <v>-449</v>
       </c>
-      <c r="D42" t="n">
-        <v>-523</v>
-      </c>
       <c r="E42" t="n">
-        <v>14.1</v>
+        <v>11.8</v>
       </c>
       <c r="F42" t="n">
+        <v>415</v>
+      </c>
+      <c r="G42" t="n">
         <v>217.5</v>
       </c>
-      <c r="G42" t="n">
-        <v>82.7</v>
-      </c>
       <c r="H42" t="n">
-        <v>163</v>
+        <v>90.8</v>
       </c>
       <c r="I42" t="n">
-        <v>14829.6</v>
+        <v>14944.3</v>
       </c>
       <c r="J42" t="n">
         <v>14829.6</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L42" t="n">
-        <v>25291.6</v>
+        <v>25529.8</v>
       </c>
       <c r="M42" t="n">
         <v>25291.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O42" t="n">
+        <v>400000</v>
+      </c>
+      <c r="P42" t="n">
         <v>434500</v>
       </c>
-      <c r="P42" t="n">
-        <v>440000</v>
-      </c>
       <c r="Q42" t="n">
-        <v>-1.2</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="43">
@@ -2808,49 +2808,49 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>675</v>
+        <v>419</v>
       </c>
       <c r="D43" t="n">
         <v>675</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>-37.9</v>
       </c>
       <c r="F43" t="n">
-        <v>2274.3</v>
+        <v>1977.2</v>
       </c>
       <c r="G43" t="n">
         <v>2274.3</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-13.1</v>
       </c>
       <c r="I43" t="n">
-        <v>2417.5</v>
+        <v>2195.3</v>
       </c>
       <c r="J43" t="n">
         <v>2417.5</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>2694</v>
+        <v>2467.5</v>
       </c>
       <c r="M43" t="n">
         <v>2694</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>-8.4</v>
       </c>
       <c r="O43" t="n">
+        <v>96700</v>
+      </c>
+      <c r="P43" t="n">
         <v>105400</v>
       </c>
-      <c r="P43" t="n">
-        <v>105600</v>
-      </c>
       <c r="Q43" t="n">
-        <v>-0.2</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -2868,46 +2868,46 @@
         <v>19098</v>
       </c>
       <c r="D44" t="n">
-        <v>19019</v>
+        <v>19098</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>42131.5</v>
       </c>
       <c r="G44" t="n">
-        <v>41655.9</v>
+        <v>42131.5</v>
       </c>
       <c r="H44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>27027.3</v>
       </c>
       <c r="J44" t="n">
-        <v>26985.4</v>
+        <v>27027.3</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>27637.9</v>
       </c>
       <c r="M44" t="n">
-        <v>27554.5</v>
+        <v>27637.9</v>
       </c>
       <c r="N44" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
+        <v>36700</v>
+      </c>
+      <c r="P44" t="n">
         <v>40050</v>
       </c>
-      <c r="P44" t="n">
-        <v>40000</v>
-      </c>
       <c r="Q44" t="n">
-        <v>0.1</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="45">
@@ -2925,46 +2925,46 @@
         <v>1022</v>
       </c>
       <c r="D45" t="n">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>3481.6</v>
       </c>
       <c r="G45" t="n">
-        <v>3470.8</v>
+        <v>3481.6</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
+        <v>3743.2</v>
+      </c>
+      <c r="J45" t="n">
         <v>3743.9</v>
       </c>
-      <c r="J45" t="n">
-        <v>3736.8</v>
-      </c>
       <c r="K45" t="n">
-        <v>0.2</v>
+        <v>-0</v>
       </c>
       <c r="L45" t="n">
+        <v>3883.9</v>
+      </c>
+      <c r="M45" t="n">
         <v>3883</v>
       </c>
-      <c r="M45" t="n">
-        <v>3886.5</v>
-      </c>
       <c r="N45" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
+        <v>25850</v>
+      </c>
+      <c r="P45" t="n">
         <v>26400</v>
       </c>
-      <c r="P45" t="n">
-        <v>26600</v>
-      </c>
       <c r="Q45" t="n">
-        <v>-0.8</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="46">
@@ -2982,46 +2982,46 @@
         <v>1461</v>
       </c>
       <c r="D46" t="n">
-        <v>1401</v>
+        <v>1461</v>
       </c>
       <c r="E46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>5836.5</v>
       </c>
       <c r="G46" t="n">
-        <v>5719.5</v>
+        <v>5836.5</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>6604.5</v>
       </c>
       <c r="J46" t="n">
-        <v>6499.5</v>
+        <v>6604.5</v>
       </c>
       <c r="K46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>7196.5</v>
       </c>
       <c r="M46" t="n">
-        <v>7120</v>
+        <v>7196.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
+        <v>36750</v>
+      </c>
+      <c r="P46" t="n">
         <v>40800</v>
       </c>
-      <c r="P46" t="n">
-        <v>37900</v>
-      </c>
       <c r="Q46" t="n">
-        <v>7.7</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="47">
@@ -3039,46 +3039,46 @@
         <v>751</v>
       </c>
       <c r="D47" t="n">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>3272.1</v>
       </c>
       <c r="G47" t="n">
-        <v>3259</v>
+        <v>3272.1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>4603.5</v>
       </c>
       <c r="J47" t="n">
-        <v>4554.5</v>
+        <v>4603.5</v>
       </c>
       <c r="K47" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>5890.1</v>
       </c>
       <c r="M47" t="n">
-        <v>5798.5</v>
+        <v>5890.1</v>
       </c>
       <c r="N47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
+        <v>86100</v>
+      </c>
+      <c r="P47" t="n">
         <v>92000</v>
       </c>
-      <c r="P47" t="n">
-        <v>99600</v>
-      </c>
       <c r="Q47" t="n">
-        <v>-7.6</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="48">
@@ -3120,13 +3120,13 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
+        <v>12750</v>
+      </c>
+      <c r="P48" t="n">
         <v>13480</v>
       </c>
-      <c r="P48" t="n">
-        <v>13970</v>
-      </c>
       <c r="Q48" t="n">
-        <v>-3.5</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="49">
@@ -3141,31 +3141,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="D49" t="n">
         <v>531</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="F49" t="n">
-        <v>1805.1</v>
+        <v>1833.6</v>
       </c>
       <c r="G49" t="n">
         <v>1805.1</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I49" t="n">
-        <v>2301.7</v>
+        <v>2305.4</v>
       </c>
       <c r="J49" t="n">
         <v>2301.7</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L49" t="n">
         <v>2678.5</v>
@@ -3177,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
+        <v>46150</v>
+      </c>
+      <c r="P49" t="n">
         <v>47800</v>
       </c>
-      <c r="P49" t="n">
-        <v>49750</v>
-      </c>
       <c r="Q49" t="n">
-        <v>-3.9</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="50">
@@ -3201,46 +3201,46 @@
         <v>4043</v>
       </c>
       <c r="D50" t="n">
-        <v>4015</v>
+        <v>4043</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>16599.1</v>
       </c>
       <c r="G50" t="n">
-        <v>16524.3</v>
+        <v>16599.1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>31750.1</v>
       </c>
       <c r="J50" t="n">
-        <v>31390.1</v>
+        <v>31750.1</v>
       </c>
       <c r="K50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>50852.8</v>
       </c>
       <c r="M50" t="n">
-        <v>49657.5</v>
+        <v>50852.8</v>
       </c>
       <c r="N50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
+        <v>1276000</v>
+      </c>
+      <c r="P50" t="n">
         <v>1277000</v>
       </c>
-      <c r="P50" t="n">
-        <v>1289000</v>
-      </c>
       <c r="Q50" t="n">
-        <v>-0.9</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="51">
@@ -3291,13 +3291,13 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
+        <v>35600</v>
+      </c>
+      <c r="P51" t="n">
         <v>35400</v>
       </c>
-      <c r="P51" t="n">
-        <v>34800</v>
-      </c>
       <c r="Q51" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="52">
@@ -3321,40 +3321,40 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>16.6</v>
+        <v>19.3</v>
       </c>
       <c r="G52" t="n">
         <v>16.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="I52" t="n">
-        <v>88.3</v>
+        <v>104</v>
       </c>
       <c r="J52" t="n">
         <v>88.3</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="L52" t="n">
-        <v>229.2</v>
+        <v>264</v>
       </c>
       <c r="M52" t="n">
         <v>229.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="O52" t="n">
+        <v>48150</v>
+      </c>
+      <c r="P52" t="n">
         <v>52800</v>
       </c>
-      <c r="P52" t="n">
-        <v>55200</v>
-      </c>
       <c r="Q52" t="n">
-        <v>-4.3</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3372,46 +3372,46 @@
         <v>14693</v>
       </c>
       <c r="D53" t="n">
-        <v>14211</v>
+        <v>14693</v>
       </c>
       <c r="E53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>57969.2</v>
       </c>
       <c r="G53" t="n">
-        <v>56417.8</v>
+        <v>57969.2</v>
       </c>
       <c r="H53" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>69012.2</v>
       </c>
       <c r="J53" t="n">
-        <v>67968.8</v>
+        <v>69012.2</v>
       </c>
       <c r="K53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>80641.10000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>78474.8</v>
+        <v>80641.10000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
+        <v>339000</v>
+      </c>
+      <c r="P53" t="n">
         <v>354000</v>
       </c>
-      <c r="P53" t="n">
-        <v>341500</v>
-      </c>
       <c r="Q53" t="n">
-        <v>3.7</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="54">
@@ -3462,13 +3462,13 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
+        <v>26200</v>
+      </c>
+      <c r="P54" t="n">
         <v>27600</v>
       </c>
-      <c r="P54" t="n">
-        <v>32000</v>
-      </c>
       <c r="Q54" t="n">
-        <v>-13.8</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="55">
@@ -3486,46 +3486,46 @@
         <v>1218</v>
       </c>
       <c r="D55" t="n">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>3787.1</v>
       </c>
       <c r="G55" t="n">
-        <v>3751.4</v>
+        <v>3787.1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>5418.3</v>
       </c>
       <c r="J55" t="n">
-        <v>5370.1</v>
+        <v>5418.3</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>6630.9</v>
       </c>
       <c r="M55" t="n">
-        <v>6603.2</v>
+        <v>6630.9</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
+        <v>192500</v>
+      </c>
+      <c r="P55" t="n">
         <v>194300</v>
       </c>
-      <c r="P55" t="n">
-        <v>204500</v>
-      </c>
       <c r="Q55" t="n">
-        <v>-5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="56">
@@ -3540,49 +3540,49 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>1612</v>
+      </c>
+      <c r="D56" t="n">
         <v>1607</v>
       </c>
-      <c r="D56" t="n">
-        <v>1590</v>
-      </c>
       <c r="E56" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="F56" t="n">
+        <v>6645.8</v>
+      </c>
+      <c r="G56" t="n">
         <v>6627.8</v>
       </c>
-      <c r="G56" t="n">
-        <v>6602.2</v>
-      </c>
       <c r="H56" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I56" t="n">
+        <v>9313.5</v>
+      </c>
+      <c r="J56" t="n">
         <v>9288.200000000001</v>
       </c>
-      <c r="J56" t="n">
-        <v>9331.700000000001</v>
-      </c>
       <c r="K56" t="n">
-        <v>-0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L56" t="n">
+        <v>12075.4</v>
+      </c>
+      <c r="M56" t="n">
         <v>12036.9</v>
       </c>
-      <c r="M56" t="n">
-        <v>12279.5</v>
-      </c>
       <c r="N56" t="n">
-        <v>-2</v>
+        <v>0.3</v>
       </c>
       <c r="O56" t="n">
+        <v>183800</v>
+      </c>
+      <c r="P56" t="n">
         <v>190000</v>
       </c>
-      <c r="P56" t="n">
-        <v>184500</v>
-      </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="57">
@@ -3633,13 +3633,13 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
+        <v>952000</v>
+      </c>
+      <c r="P57" t="n">
         <v>1029000</v>
       </c>
-      <c r="P57" t="n">
-        <v>1025000</v>
-      </c>
       <c r="Q57" t="n">
-        <v>0.4</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="58">
@@ -3657,46 +3657,46 @@
         <v>3744</v>
       </c>
       <c r="D58" t="n">
-        <v>3902</v>
+        <v>3744</v>
       </c>
       <c r="E58" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>14649.6</v>
       </c>
       <c r="G58" t="n">
-        <v>14956.6</v>
+        <v>14649.6</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>20222.6</v>
       </c>
       <c r="J58" t="n">
-        <v>20358</v>
+        <v>20222.6</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>23690.3</v>
       </c>
       <c r="M58" t="n">
-        <v>23869.4</v>
+        <v>23690.3</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
+        <v>20950</v>
+      </c>
+      <c r="P58" t="n">
         <v>22300</v>
       </c>
-      <c r="P58" t="n">
-        <v>22050</v>
-      </c>
       <c r="Q58" t="n">
-        <v>1.1</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="59">
@@ -3711,49 +3711,49 @@
         </is>
       </c>
       <c r="C59" t="n">
+        <v>9551</v>
+      </c>
+      <c r="D59" t="n">
         <v>9592</v>
       </c>
-      <c r="D59" t="n">
-        <v>9415</v>
-      </c>
       <c r="E59" t="n">
-        <v>1.9</v>
+        <v>-0.4</v>
       </c>
       <c r="F59" t="n">
+        <v>35904.7</v>
+      </c>
+      <c r="G59" t="n">
         <v>35895.3</v>
       </c>
-      <c r="G59" t="n">
-        <v>35619.5</v>
-      </c>
       <c r="H59" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
+        <v>27021.4</v>
+      </c>
+      <c r="J59" t="n">
         <v>26366.1</v>
       </c>
-      <c r="J59" t="n">
-        <v>24566.4</v>
-      </c>
       <c r="K59" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="L59" t="n">
+        <v>24226.4</v>
+      </c>
+      <c r="M59" t="n">
         <v>23703.9</v>
       </c>
-      <c r="M59" t="n">
-        <v>22576.3</v>
-      </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="O59" t="n">
+        <v>141850</v>
+      </c>
+      <c r="P59" t="n">
         <v>144900</v>
       </c>
-      <c r="P59" t="n">
-        <v>139500</v>
-      </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="60">
@@ -3771,19 +3771,19 @@
         <v>1823</v>
       </c>
       <c r="D60" t="n">
-        <v>1803</v>
+        <v>1823</v>
       </c>
       <c r="E60" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>11828.4</v>
       </c>
       <c r="G60" t="n">
-        <v>11679.8</v>
+        <v>11828.4</v>
       </c>
       <c r="H60" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>13870.9</v>
@@ -3804,13 +3804,13 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
+        <v>606000</v>
+      </c>
+      <c r="P60" t="n">
         <v>668000</v>
       </c>
-      <c r="P60" t="n">
-        <v>661000</v>
-      </c>
       <c r="Q60" t="n">
-        <v>1.1</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -3825,49 +3825,49 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1380</v>
+        <v>1356</v>
       </c>
       <c r="D61" t="n">
         <v>1380</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="F61" t="n">
-        <v>1671</v>
+        <v>1778.8</v>
       </c>
       <c r="G61" t="n">
         <v>1671</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I61" t="n">
-        <v>2610.4</v>
+        <v>2605.7</v>
       </c>
       <c r="J61" t="n">
         <v>2610.4</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L61" t="n">
-        <v>4783.5</v>
+        <v>4707.1</v>
       </c>
       <c r="M61" t="n">
         <v>4783.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="O61" t="n">
+        <v>56600</v>
+      </c>
+      <c r="P61" t="n">
         <v>61000</v>
       </c>
-      <c r="P61" t="n">
-        <v>60600</v>
-      </c>
       <c r="Q61" t="n">
-        <v>0.7</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="62">
@@ -3885,46 +3885,46 @@
         <v>3463</v>
       </c>
       <c r="D62" t="n">
-        <v>3182</v>
+        <v>3463</v>
       </c>
       <c r="E62" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>12211.1</v>
       </c>
       <c r="G62" t="n">
-        <v>11608</v>
+        <v>12211.1</v>
       </c>
       <c r="H62" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>8944.6</v>
       </c>
       <c r="J62" t="n">
-        <v>8554.9</v>
+        <v>8944.6</v>
       </c>
       <c r="K62" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>9046.9</v>
       </c>
       <c r="M62" t="n">
-        <v>9030.200000000001</v>
+        <v>9046.9</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
+        <v>20350</v>
+      </c>
+      <c r="P62" t="n">
         <v>20050</v>
       </c>
-      <c r="P62" t="n">
-        <v>19550</v>
-      </c>
       <c r="Q62" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="63">
@@ -3942,46 +3942,46 @@
         <v>530</v>
       </c>
       <c r="D63" t="n">
-        <v>576</v>
+        <v>530</v>
       </c>
       <c r="E63" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>2256.9</v>
       </c>
       <c r="G63" t="n">
-        <v>2314.2</v>
+        <v>2256.9</v>
       </c>
       <c r="H63" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>2802.8</v>
       </c>
       <c r="J63" t="n">
-        <v>2836.9</v>
+        <v>2802.8</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>3111.2</v>
       </c>
       <c r="M63" t="n">
-        <v>3126.8</v>
+        <v>3111.2</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
+        <v>55600</v>
+      </c>
+      <c r="P63" t="n">
         <v>57600</v>
       </c>
-      <c r="P63" t="n">
-        <v>59900</v>
-      </c>
       <c r="Q63" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="64">
@@ -3996,49 +3996,49 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>1470</v>
+      </c>
+      <c r="D64" t="n">
         <v>1437</v>
       </c>
-      <c r="D64" t="n">
-        <v>1401</v>
-      </c>
       <c r="E64" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="F64" t="n">
+        <v>4006</v>
+      </c>
+      <c r="G64" t="n">
         <v>3948.2</v>
       </c>
-      <c r="G64" t="n">
-        <v>3904.6</v>
-      </c>
       <c r="H64" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="I64" t="n">
+        <v>4560</v>
+      </c>
+      <c r="J64" t="n">
         <v>4448.1</v>
       </c>
-      <c r="J64" t="n">
-        <v>4430.3</v>
-      </c>
       <c r="K64" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="L64" t="n">
+        <v>4858.5</v>
+      </c>
+      <c r="M64" t="n">
         <v>4909.2</v>
       </c>
-      <c r="M64" t="n">
-        <v>4902.9</v>
-      </c>
       <c r="N64" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="O64" t="n">
+        <v>116700</v>
+      </c>
+      <c r="P64" t="n">
         <v>123500</v>
       </c>
-      <c r="P64" t="n">
-        <v>117400</v>
-      </c>
       <c r="Q64" t="n">
-        <v>5.2</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="65">
@@ -4089,13 +4089,13 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
+        <v>78100</v>
+      </c>
+      <c r="P65" t="n">
         <v>85200</v>
       </c>
-      <c r="P65" t="n">
-        <v>88000</v>
-      </c>
       <c r="Q65" t="n">
-        <v>-3.2</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4113,46 +4113,46 @@
         <v>9075</v>
       </c>
       <c r="D66" t="n">
-        <v>9088</v>
+        <v>9075</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>37334.3</v>
       </c>
       <c r="G66" t="n">
-        <v>37234.8</v>
+        <v>37334.3</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
         <v>42519.2</v>
       </c>
       <c r="J66" t="n">
-        <v>42459</v>
+        <v>42519.2</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>46485</v>
       </c>
       <c r="M66" t="n">
-        <v>46500.8</v>
+        <v>46485</v>
       </c>
       <c r="N66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
+        <v>475500</v>
+      </c>
+      <c r="P66" t="n">
         <v>482000</v>
       </c>
-      <c r="P66" t="n">
-        <v>487500</v>
-      </c>
       <c r="Q66" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="67">
@@ -4167,49 +4167,49 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>9970</v>
+      </c>
+      <c r="D67" t="n">
         <v>9962</v>
       </c>
-      <c r="D67" t="n">
-        <v>10136</v>
-      </c>
       <c r="E67" t="n">
-        <v>-1.7</v>
+        <v>0.1</v>
       </c>
       <c r="F67" t="n">
+        <v>42852.8</v>
+      </c>
+      <c r="G67" t="n">
         <v>42796.2</v>
       </c>
-      <c r="G67" t="n">
-        <v>42647.9</v>
-      </c>
       <c r="H67" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I67" t="n">
+        <v>54780.9</v>
+      </c>
+      <c r="J67" t="n">
         <v>54920.9</v>
-      </c>
-      <c r="J67" t="n">
-        <v>55103.9</v>
       </c>
       <c r="K67" t="n">
         <v>-0.3</v>
       </c>
       <c r="L67" t="n">
+        <v>61398</v>
+      </c>
+      <c r="M67" t="n">
         <v>61626.3</v>
       </c>
-      <c r="M67" t="n">
-        <v>62256.4</v>
-      </c>
       <c r="N67" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="O67" t="n">
+        <v>900000</v>
+      </c>
+      <c r="P67" t="n">
         <v>943000</v>
       </c>
-      <c r="P67" t="n">
-        <v>936000</v>
-      </c>
       <c r="Q67" t="n">
-        <v>0.7</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="68">
@@ -4260,13 +4260,13 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
+        <v>71000</v>
+      </c>
+      <c r="P68" t="n">
         <v>72100</v>
       </c>
-      <c r="P68" t="n">
-        <v>71700</v>
-      </c>
       <c r="Q68" t="n">
-        <v>0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="69">
@@ -4284,46 +4284,46 @@
         <v>507</v>
       </c>
       <c r="D69" t="n">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>1886.8</v>
       </c>
       <c r="G69" t="n">
-        <v>1879.9</v>
+        <v>1886.8</v>
       </c>
       <c r="H69" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>2361</v>
       </c>
       <c r="J69" t="n">
-        <v>2386.1</v>
+        <v>2361</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>2994.7</v>
       </c>
       <c r="M69" t="n">
-        <v>3072.4</v>
+        <v>2994.7</v>
       </c>
       <c r="N69" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
+        <v>230000</v>
+      </c>
+      <c r="P69" t="n">
         <v>244500</v>
       </c>
-      <c r="P69" t="n">
-        <v>260000</v>
-      </c>
       <c r="Q69" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="70">
@@ -4341,46 +4341,46 @@
         <v>20041</v>
       </c>
       <c r="D70" t="n">
-        <v>19122</v>
+        <v>20041</v>
       </c>
       <c r="E70" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
         <v>100192.7</v>
       </c>
       <c r="G70" t="n">
-        <v>97617.5</v>
+        <v>100192.7</v>
       </c>
       <c r="H70" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>139318.5</v>
       </c>
       <c r="J70" t="n">
-        <v>134651.3</v>
+        <v>139318.5</v>
       </c>
       <c r="K70" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>152635.4</v>
       </c>
       <c r="M70" t="n">
-        <v>148583.9</v>
+        <v>152635.4</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
+        <v>33650</v>
+      </c>
+      <c r="P70" t="n">
         <v>34050</v>
       </c>
-      <c r="P70" t="n">
-        <v>34250</v>
-      </c>
       <c r="Q70" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="71">
@@ -4398,46 +4398,46 @@
         <v>6617</v>
       </c>
       <c r="D71" t="n">
-        <v>6435</v>
+        <v>6617</v>
       </c>
       <c r="E71" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>23027.4</v>
       </c>
       <c r="G71" t="n">
-        <v>22640.4</v>
+        <v>23027.4</v>
       </c>
       <c r="H71" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>21231.4</v>
       </c>
       <c r="J71" t="n">
-        <v>20996.1</v>
+        <v>21231.4</v>
       </c>
       <c r="K71" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>21175.6</v>
       </c>
       <c r="M71" t="n">
-        <v>20937.6</v>
+        <v>21175.6</v>
       </c>
       <c r="N71" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
+        <v>102600</v>
+      </c>
+      <c r="P71" t="n">
         <v>107700</v>
       </c>
-      <c r="P71" t="n">
-        <v>108800</v>
-      </c>
       <c r="Q71" t="n">
-        <v>-1</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="72">
@@ -4455,46 +4455,46 @@
         <v>5446</v>
       </c>
       <c r="D72" t="n">
-        <v>5307</v>
+        <v>5446</v>
       </c>
       <c r="E72" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>19444.4</v>
       </c>
       <c r="G72" t="n">
-        <v>19164.7</v>
+        <v>19444.4</v>
       </c>
       <c r="H72" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>20548.8</v>
       </c>
       <c r="J72" t="n">
-        <v>20300.4</v>
+        <v>20548.8</v>
       </c>
       <c r="K72" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>21669.4</v>
       </c>
       <c r="M72" t="n">
-        <v>21507.9</v>
+        <v>21669.4</v>
       </c>
       <c r="N72" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
+        <v>84300</v>
+      </c>
+      <c r="P72" t="n">
         <v>89700</v>
       </c>
-      <c r="P72" t="n">
-        <v>85700</v>
-      </c>
       <c r="Q72" t="n">
-        <v>4.7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="73">
@@ -4512,46 +4512,46 @@
         <v>483</v>
       </c>
       <c r="D73" t="n">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="E73" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>1818.3</v>
       </c>
       <c r="G73" t="n">
-        <v>1798.3</v>
+        <v>1818.3</v>
       </c>
       <c r="H73" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>1997.7</v>
       </c>
       <c r="J73" t="n">
-        <v>1964.3</v>
+        <v>1997.7</v>
       </c>
       <c r="K73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>2141.5</v>
       </c>
       <c r="M73" t="n">
-        <v>1946.5</v>
+        <v>2141.5</v>
       </c>
       <c r="N73" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
+        <v>21800</v>
+      </c>
+      <c r="P73" t="n">
         <v>23450</v>
       </c>
-      <c r="P73" t="n">
-        <v>24600</v>
-      </c>
       <c r="Q73" t="n">
-        <v>-4.7</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="74">
@@ -4569,46 +4569,46 @@
         <v>2368</v>
       </c>
       <c r="D74" t="n">
-        <v>2349</v>
+        <v>2368</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>8360.799999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>8342.200000000001</v>
+        <v>8360.799999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>10668.7</v>
       </c>
       <c r="J74" t="n">
-        <v>10645.7</v>
+        <v>10668.7</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>12020.2</v>
       </c>
       <c r="M74" t="n">
-        <v>11844.7</v>
+        <v>12020.2</v>
       </c>
       <c r="N74" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
+        <v>188900</v>
+      </c>
+      <c r="P74" t="n">
         <v>199300</v>
       </c>
-      <c r="P74" t="n">
-        <v>190200</v>
-      </c>
       <c r="Q74" t="n">
-        <v>4.8</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="75">
@@ -4623,49 +4623,49 @@
         </is>
       </c>
       <c r="C75" t="n">
+        <v>1116</v>
+      </c>
+      <c r="D75" t="n">
         <v>1102</v>
       </c>
-      <c r="D75" t="n">
-        <v>1095</v>
-      </c>
       <c r="E75" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F75" t="n">
+        <v>4305.3</v>
+      </c>
+      <c r="G75" t="n">
         <v>4307</v>
       </c>
-      <c r="G75" t="n">
-        <v>4279.2</v>
-      </c>
       <c r="H75" t="n">
-        <v>0.6</v>
+        <v>-0</v>
       </c>
       <c r="I75" t="n">
+        <v>5077.9</v>
+      </c>
+      <c r="J75" t="n">
         <v>5064.6</v>
       </c>
-      <c r="J75" t="n">
-        <v>4997.4</v>
-      </c>
       <c r="K75" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="L75" t="n">
         <v>5878.2</v>
       </c>
       <c r="M75" t="n">
-        <v>5789.7</v>
+        <v>5878.2</v>
       </c>
       <c r="N75" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
+        <v>3370</v>
+      </c>
+      <c r="P75" t="n">
         <v>3490</v>
       </c>
-      <c r="P75" t="n">
-        <v>3440</v>
-      </c>
       <c r="Q75" t="n">
-        <v>1.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="76">
@@ -4683,16 +4683,16 @@
         <v>2675</v>
       </c>
       <c r="D76" t="n">
-        <v>2682</v>
+        <v>2675</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>10139.2</v>
       </c>
       <c r="G76" t="n">
-        <v>10136.5</v>
+        <v>10139.2</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -4701,10 +4701,10 @@
         <v>11678.2</v>
       </c>
       <c r="J76" t="n">
-        <v>11688.8</v>
+        <v>11678.2</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>12472.5</v>
@@ -4716,13 +4716,13 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
+        <v>94300</v>
+      </c>
+      <c r="P76" t="n">
         <v>96700</v>
       </c>
-      <c r="P76" t="n">
-        <v>91700</v>
-      </c>
       <c r="Q76" t="n">
-        <v>5.5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="77">
@@ -4737,49 +4737,49 @@
         </is>
       </c>
       <c r="C77" t="n">
+        <v>1140</v>
+      </c>
+      <c r="D77" t="n">
         <v>1129</v>
       </c>
-      <c r="D77" t="n">
-        <v>1104</v>
-      </c>
       <c r="E77" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
+        <v>8128.7</v>
+      </c>
+      <c r="G77" t="n">
         <v>8112.6</v>
       </c>
-      <c r="G77" t="n">
-        <v>8034.7</v>
-      </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="I77" t="n">
+        <v>8729.5</v>
+      </c>
+      <c r="J77" t="n">
         <v>8722.4</v>
       </c>
-      <c r="J77" t="n">
-        <v>8618.5</v>
-      </c>
       <c r="K77" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="L77" t="n">
+        <v>9365.6</v>
+      </c>
+      <c r="M77" t="n">
         <v>9228.4</v>
       </c>
-      <c r="M77" t="n">
-        <v>9113.799999999999</v>
-      </c>
       <c r="N77" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="O77" t="n">
+        <v>131100</v>
+      </c>
+      <c r="P77" t="n">
         <v>140800</v>
       </c>
-      <c r="P77" t="n">
-        <v>154300</v>
-      </c>
       <c r="Q77" t="n">
-        <v>-8.699999999999999</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="78">
@@ -4797,46 +4797,46 @@
         <v>9260</v>
       </c>
       <c r="D78" t="n">
-        <v>9431</v>
+        <v>9260</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>36894.8</v>
       </c>
       <c r="G78" t="n">
-        <v>37016.5</v>
+        <v>36894.8</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>39631.1</v>
       </c>
       <c r="J78" t="n">
-        <v>39830.2</v>
+        <v>39631.1</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>42250.5</v>
       </c>
       <c r="M78" t="n">
-        <v>42552.4</v>
+        <v>42250.5</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
+        <v>20800</v>
+      </c>
+      <c r="P78" t="n">
         <v>21600</v>
       </c>
-      <c r="P78" t="n">
-        <v>21150</v>
-      </c>
       <c r="Q78" t="n">
-        <v>2.1</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="79">
@@ -4851,49 +4851,49 @@
         </is>
       </c>
       <c r="C79" t="n">
+        <v>2191</v>
+      </c>
+      <c r="D79" t="n">
         <v>2188</v>
       </c>
-      <c r="D79" t="n">
-        <v>2179</v>
-      </c>
       <c r="E79" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F79" t="n">
+        <v>8849.5</v>
+      </c>
+      <c r="G79" t="n">
         <v>8845.299999999999</v>
       </c>
-      <c r="G79" t="n">
-        <v>8839.6</v>
-      </c>
       <c r="H79" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
+        <v>10315.2</v>
+      </c>
+      <c r="J79" t="n">
         <v>10313.1</v>
       </c>
-      <c r="J79" t="n">
-        <v>10306.5</v>
-      </c>
       <c r="K79" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>11551.5</v>
       </c>
       <c r="M79" t="n">
-        <v>11529.4</v>
+        <v>11551.5</v>
       </c>
       <c r="N79" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
+        <v>40650</v>
+      </c>
+      <c r="P79" t="n">
         <v>40850</v>
       </c>
-      <c r="P79" t="n">
-        <v>41100</v>
-      </c>
       <c r="Q79" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="80">
@@ -4944,13 +4944,13 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
+        <v>339000</v>
+      </c>
+      <c r="P80" t="n">
         <v>346000</v>
       </c>
-      <c r="P80" t="n">
-        <v>361000</v>
-      </c>
       <c r="Q80" t="n">
-        <v>-4.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="81">
@@ -4968,46 +4968,46 @@
         <v>1544</v>
       </c>
       <c r="D81" t="n">
-        <v>1503</v>
+        <v>1544</v>
       </c>
       <c r="E81" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
         <v>5923</v>
       </c>
       <c r="G81" t="n">
-        <v>5854.9</v>
+        <v>5923</v>
       </c>
       <c r="H81" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>6114.9</v>
       </c>
       <c r="J81" t="n">
-        <v>6091.5</v>
+        <v>6114.9</v>
       </c>
       <c r="K81" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>6369.4</v>
       </c>
       <c r="M81" t="n">
-        <v>6368.1</v>
+        <v>6369.4</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
       </c>
       <c r="O81" t="n">
+        <v>5040</v>
+      </c>
+      <c r="P81" t="n">
         <v>5160</v>
       </c>
-      <c r="P81" t="n">
-        <v>5240</v>
-      </c>
       <c r="Q81" t="n">
-        <v>-1.5</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="82">
@@ -5025,46 +5025,46 @@
         <v>2144</v>
       </c>
       <c r="D82" t="n">
-        <v>2131</v>
+        <v>2144</v>
       </c>
       <c r="E82" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>8315</v>
       </c>
       <c r="G82" t="n">
-        <v>8470</v>
+        <v>8315</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>8912.5</v>
       </c>
       <c r="J82" t="n">
-        <v>9226.700000000001</v>
+        <v>8912.5</v>
       </c>
       <c r="K82" t="n">
-        <v>-3.4</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>9062.5</v>
       </c>
       <c r="M82" t="n">
-        <v>9336.700000000001</v>
+        <v>9062.5</v>
       </c>
       <c r="N82" t="n">
-        <v>-2.9</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
+        <v>48050</v>
+      </c>
+      <c r="P82" t="n">
         <v>47050</v>
       </c>
-      <c r="P82" t="n">
-        <v>47800</v>
-      </c>
       <c r="Q82" t="n">
-        <v>-1.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="83">
@@ -5079,49 +5079,49 @@
         </is>
       </c>
       <c r="C83" t="n">
+        <v>937</v>
+      </c>
+      <c r="D83" t="n">
         <v>940</v>
       </c>
-      <c r="D83" t="n">
-        <v>942</v>
-      </c>
       <c r="E83" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F83" t="n">
+        <v>3333.2</v>
+      </c>
+      <c r="G83" t="n">
         <v>3331.9</v>
       </c>
-      <c r="G83" t="n">
-        <v>3339.9</v>
-      </c>
       <c r="H83" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
+        <v>3626.4</v>
+      </c>
+      <c r="J83" t="n">
         <v>3627.7</v>
       </c>
-      <c r="J83" t="n">
-        <v>3636.7</v>
-      </c>
       <c r="K83" t="n">
-        <v>-0.2</v>
+        <v>-0</v>
       </c>
       <c r="L83" t="n">
+        <v>3679.2</v>
+      </c>
+      <c r="M83" t="n">
         <v>3685.9</v>
-      </c>
-      <c r="M83" t="n">
-        <v>3692.6</v>
       </c>
       <c r="N83" t="n">
         <v>-0.2</v>
       </c>
       <c r="O83" t="n">
+        <v>18620</v>
+      </c>
+      <c r="P83" t="n">
         <v>18610</v>
       </c>
-      <c r="P83" t="n">
-        <v>18760</v>
-      </c>
       <c r="Q83" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="84">
@@ -5139,46 +5139,46 @@
         <v>6037</v>
       </c>
       <c r="D84" t="n">
-        <v>6081</v>
+        <v>6037</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
         <v>20554.3</v>
       </c>
       <c r="G84" t="n">
-        <v>20653.3</v>
+        <v>20554.3</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>22489.1</v>
       </c>
       <c r="J84" t="n">
-        <v>22502.9</v>
+        <v>22489.1</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>23864.3</v>
       </c>
       <c r="M84" t="n">
-        <v>23821.8</v>
+        <v>23864.3</v>
       </c>
       <c r="N84" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
+        <v>53500</v>
+      </c>
+      <c r="P84" t="n">
         <v>52400</v>
       </c>
-      <c r="P84" t="n">
-        <v>52700</v>
-      </c>
       <c r="Q84" t="n">
-        <v>-0.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="85">
@@ -5196,46 +5196,46 @@
         <v>3087</v>
       </c>
       <c r="D85" t="n">
-        <v>3062</v>
+        <v>3087</v>
       </c>
       <c r="E85" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>11108.8</v>
       </c>
       <c r="G85" t="n">
-        <v>11111.1</v>
+        <v>11108.8</v>
       </c>
       <c r="H85" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>11988.9</v>
       </c>
       <c r="J85" t="n">
-        <v>11959</v>
+        <v>11988.9</v>
       </c>
       <c r="K85" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>12761.4</v>
       </c>
       <c r="M85" t="n">
-        <v>12715.1</v>
+        <v>12761.4</v>
       </c>
       <c r="N85" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
+        <v>14580</v>
+      </c>
+      <c r="P85" t="n">
         <v>14620</v>
       </c>
-      <c r="P85" t="n">
-        <v>14530</v>
-      </c>
       <c r="Q85" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="86">
@@ -5253,19 +5253,19 @@
         <v>10171</v>
       </c>
       <c r="D86" t="n">
-        <v>10237</v>
+        <v>10171</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>33448.1</v>
       </c>
       <c r="G86" t="n">
-        <v>33019.2</v>
+        <v>33448.1</v>
       </c>
       <c r="H86" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>52718.3</v>
@@ -5286,13 +5286,13 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
+        <v>307000</v>
+      </c>
+      <c r="P86" t="n">
         <v>331000</v>
       </c>
-      <c r="P86" t="n">
-        <v>326000</v>
-      </c>
       <c r="Q86" t="n">
-        <v>1.5</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="87">
@@ -5307,49 +5307,49 @@
         </is>
       </c>
       <c r="C87" t="n">
+        <v>3949</v>
+      </c>
+      <c r="D87" t="n">
         <v>3937</v>
       </c>
-      <c r="D87" t="n">
-        <v>3866</v>
-      </c>
       <c r="E87" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="F87" t="n">
+        <v>15137</v>
+      </c>
+      <c r="G87" t="n">
         <v>15140.1</v>
       </c>
-      <c r="G87" t="n">
-        <v>15108.4</v>
-      </c>
       <c r="H87" t="n">
-        <v>0.2</v>
+        <v>-0</v>
       </c>
       <c r="I87" t="n">
+        <v>16291.6</v>
+      </c>
+      <c r="J87" t="n">
         <v>16276.8</v>
       </c>
-      <c r="J87" t="n">
-        <v>16302.5</v>
-      </c>
       <c r="K87" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L87" t="n">
         <v>17211.8</v>
       </c>
       <c r="M87" t="n">
-        <v>17252.5</v>
+        <v>17211.8</v>
       </c>
       <c r="N87" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
+        <v>180300</v>
+      </c>
+      <c r="P87" t="n">
         <v>179900</v>
       </c>
-      <c r="P87" t="n">
-        <v>174300</v>
-      </c>
       <c r="Q87" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="88">
@@ -5367,25 +5367,25 @@
         <v>2670</v>
       </c>
       <c r="D88" t="n">
-        <v>2659</v>
+        <v>2670</v>
       </c>
       <c r="E88" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>11184.8</v>
       </c>
       <c r="G88" t="n">
-        <v>11195.5</v>
+        <v>11184.8</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>16050.4</v>
       </c>
       <c r="J88" t="n">
-        <v>16045.1</v>
+        <v>16050.4</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -5394,19 +5394,19 @@
         <v>21153.6</v>
       </c>
       <c r="M88" t="n">
-        <v>21149.6</v>
+        <v>21153.6</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
       </c>
       <c r="O88" t="n">
+        <v>65400</v>
+      </c>
+      <c r="P88" t="n">
         <v>69700</v>
       </c>
-      <c r="P88" t="n">
-        <v>73200</v>
-      </c>
       <c r="Q88" t="n">
-        <v>-4.8</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="89">
@@ -5457,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
+        <v>9720</v>
+      </c>
+      <c r="P89" t="n">
         <v>10410</v>
       </c>
-      <c r="P89" t="n">
-        <v>10360</v>
-      </c>
       <c r="Q89" t="n">
-        <v>0.5</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="90">
@@ -5481,46 +5481,46 @@
         <v>472</v>
       </c>
       <c r="D90" t="n">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="E90" t="n">
-        <v>-5.2</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
         <v>1773.4</v>
       </c>
       <c r="G90" t="n">
-        <v>1856.2</v>
+        <v>1773.4</v>
       </c>
       <c r="H90" t="n">
-        <v>-4.5</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
         <v>2147.9</v>
       </c>
       <c r="J90" t="n">
-        <v>2235.1</v>
+        <v>2147.9</v>
       </c>
       <c r="K90" t="n">
-        <v>-3.9</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>2443.3</v>
       </c>
       <c r="M90" t="n">
-        <v>2456</v>
+        <v>2443.3</v>
       </c>
       <c r="N90" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
+        <v>9610</v>
+      </c>
+      <c r="P90" t="n">
         <v>10190</v>
       </c>
-      <c r="P90" t="n">
-        <v>12550</v>
-      </c>
       <c r="Q90" t="n">
-        <v>-18.8</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="91">
@@ -5571,13 +5571,13 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
+        <v>583000</v>
+      </c>
+      <c r="P91" t="n">
         <v>580000</v>
       </c>
-      <c r="P91" t="n">
-        <v>583000</v>
-      </c>
       <c r="Q91" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92">
@@ -5595,46 +5595,46 @@
         <v>491</v>
       </c>
       <c r="D92" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E92" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>2231.8</v>
       </c>
       <c r="G92" t="n">
-        <v>2212.7</v>
+        <v>2231.8</v>
       </c>
       <c r="H92" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
         <v>2312.7</v>
       </c>
       <c r="J92" t="n">
-        <v>2287.4</v>
+        <v>2312.7</v>
       </c>
       <c r="K92" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>2882</v>
       </c>
       <c r="M92" t="n">
-        <v>2883.4</v>
+        <v>2882</v>
       </c>
       <c r="N92" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
+        <v>14290</v>
+      </c>
+      <c r="P92" t="n">
         <v>14410</v>
       </c>
-      <c r="P92" t="n">
-        <v>14680</v>
-      </c>
       <c r="Q92" t="n">
-        <v>-1.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="93">
@@ -5649,49 +5649,49 @@
         </is>
       </c>
       <c r="C93" t="n">
+        <v>5660</v>
+      </c>
+      <c r="D93" t="n">
         <v>5670</v>
       </c>
-      <c r="D93" t="n">
-        <v>5693</v>
-      </c>
       <c r="E93" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="F93" t="n">
+        <v>23882.1</v>
+      </c>
+      <c r="G93" t="n">
         <v>23891.1</v>
       </c>
-      <c r="G93" t="n">
-        <v>23973.6</v>
-      </c>
       <c r="H93" t="n">
-        <v>-0.3</v>
+        <v>-0</v>
       </c>
       <c r="I93" t="n">
+        <v>27685.9</v>
+      </c>
+      <c r="J93" t="n">
         <v>27632</v>
       </c>
-      <c r="J93" t="n">
-        <v>27672</v>
-      </c>
       <c r="K93" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L93" t="n">
+        <v>31542.1</v>
+      </c>
+      <c r="M93" t="n">
         <v>31373.3</v>
       </c>
-      <c r="M93" t="n">
-        <v>31358.5</v>
-      </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O93" t="n">
+        <v>192400</v>
+      </c>
+      <c r="P93" t="n">
         <v>190000</v>
       </c>
-      <c r="P93" t="n">
-        <v>188000</v>
-      </c>
       <c r="Q93" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="94">
@@ -5709,46 +5709,46 @@
         <v>2263</v>
       </c>
       <c r="D94" t="n">
-        <v>2229</v>
+        <v>2263</v>
       </c>
       <c r="E94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
         <v>9473.700000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>9387.299999999999</v>
+        <v>9473.700000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>10966.3</v>
       </c>
       <c r="J94" t="n">
-        <v>10959.7</v>
+        <v>10966.3</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>12514.8</v>
       </c>
       <c r="M94" t="n">
-        <v>12671.7</v>
+        <v>12514.8</v>
       </c>
       <c r="N94" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
+        <v>35425</v>
+      </c>
+      <c r="P94" t="n">
         <v>35900</v>
       </c>
-      <c r="P94" t="n">
-        <v>34750</v>
-      </c>
       <c r="Q94" t="n">
-        <v>3.3</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="95">
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
+        <v>32200</v>
+      </c>
+      <c r="P95" t="n">
         <v>32400</v>
       </c>
-      <c r="P95" t="n">
-        <v>32700</v>
-      </c>
       <c r="Q95" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="96">
@@ -5823,25 +5823,25 @@
         <v>1294</v>
       </c>
       <c r="D96" t="n">
-        <v>1270</v>
+        <v>1294</v>
       </c>
       <c r="E96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>5051.7</v>
       </c>
       <c r="G96" t="n">
-        <v>5026.8</v>
+        <v>5051.7</v>
       </c>
       <c r="H96" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>5877.6</v>
       </c>
       <c r="J96" t="n">
-        <v>5876.9</v>
+        <v>5877.6</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -5850,19 +5850,19 @@
         <v>5885.7</v>
       </c>
       <c r="M96" t="n">
-        <v>5924.6</v>
+        <v>5885.7</v>
       </c>
       <c r="N96" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
+        <v>210000</v>
+      </c>
+      <c r="P96" t="n">
         <v>223000</v>
       </c>
-      <c r="P96" t="n">
-        <v>240500</v>
-      </c>
       <c r="Q96" t="n">
-        <v>-7.3</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="97">
@@ -5880,46 +5880,46 @@
         <v>6522</v>
       </c>
       <c r="D97" t="n">
-        <v>6375</v>
+        <v>6522</v>
       </c>
       <c r="E97" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
         <v>22059</v>
       </c>
       <c r="G97" t="n">
-        <v>21921.9</v>
+        <v>22059</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
         <v>20561.6</v>
       </c>
       <c r="J97" t="n">
-        <v>20426.9</v>
+        <v>20561.6</v>
       </c>
       <c r="K97" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>20834.7</v>
       </c>
       <c r="M97" t="n">
-        <v>20600.4</v>
+        <v>20834.7</v>
       </c>
       <c r="N97" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
+        <v>307000</v>
+      </c>
+      <c r="P97" t="n">
         <v>322000</v>
       </c>
-      <c r="P97" t="n">
-        <v>323500</v>
-      </c>
       <c r="Q97" t="n">
-        <v>-0.5</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="98">
@@ -5937,46 +5937,46 @@
         <v>5335</v>
       </c>
       <c r="D98" t="n">
-        <v>5252</v>
+        <v>5335</v>
       </c>
       <c r="E98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
         <v>19239.6</v>
       </c>
       <c r="G98" t="n">
-        <v>19011.6</v>
+        <v>19239.6</v>
       </c>
       <c r="H98" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
         <v>23307.3</v>
       </c>
       <c r="J98" t="n">
-        <v>23489.7</v>
+        <v>23307.3</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>27375.2</v>
       </c>
       <c r="M98" t="n">
-        <v>27891.2</v>
+        <v>27375.2</v>
       </c>
       <c r="N98" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
+        <v>81500</v>
+      </c>
+      <c r="P98" t="n">
         <v>86700</v>
       </c>
-      <c r="P98" t="n">
-        <v>78800</v>
-      </c>
       <c r="Q98" t="n">
-        <v>10</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="99">
@@ -5994,46 +5994,46 @@
         <v>1210</v>
       </c>
       <c r="D99" t="n">
-        <v>1103</v>
+        <v>1210</v>
       </c>
       <c r="E99" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
         <v>3822</v>
       </c>
       <c r="G99" t="n">
-        <v>3694</v>
+        <v>3822</v>
       </c>
       <c r="H99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
         <v>5617</v>
       </c>
       <c r="J99" t="n">
-        <v>5719</v>
+        <v>5617</v>
       </c>
       <c r="K99" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>6843</v>
       </c>
       <c r="M99" t="n">
-        <v>7297</v>
+        <v>6843</v>
       </c>
       <c r="N99" t="n">
-        <v>-6.2</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
+        <v>222750</v>
+      </c>
+      <c r="P99" t="n">
         <v>242500</v>
       </c>
-      <c r="P99" t="n">
-        <v>205500</v>
-      </c>
       <c r="Q99" t="n">
-        <v>18</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="100">
@@ -6048,49 +6048,49 @@
         </is>
       </c>
       <c r="C100" t="n">
+        <v>1601</v>
+      </c>
+      <c r="D100" t="n">
         <v>1558</v>
       </c>
-      <c r="D100" t="n">
-        <v>1508</v>
-      </c>
       <c r="E100" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="F100" t="n">
+        <v>7516.8</v>
+      </c>
+      <c r="G100" t="n">
         <v>7389.2</v>
       </c>
-      <c r="G100" t="n">
-        <v>7131.3</v>
-      </c>
       <c r="H100" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="I100" t="n">
+        <v>7562.6</v>
+      </c>
+      <c r="J100" t="n">
         <v>7473.7</v>
       </c>
-      <c r="J100" t="n">
-        <v>7346.9</v>
-      </c>
       <c r="K100" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="L100" t="n">
+        <v>8844.200000000001</v>
+      </c>
+      <c r="M100" t="n">
         <v>8753.799999999999</v>
       </c>
-      <c r="M100" t="n">
-        <v>8381.4</v>
-      </c>
       <c r="N100" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
+        <v>14380</v>
+      </c>
+      <c r="P100" t="n">
         <v>15150</v>
       </c>
-      <c r="P100" t="n">
-        <v>16010</v>
-      </c>
       <c r="Q100" t="n">
-        <v>-5.4</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="101">
@@ -6108,46 +6108,46 @@
         <v>3601</v>
       </c>
       <c r="D101" t="n">
-        <v>3517</v>
+        <v>3601</v>
       </c>
       <c r="E101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
         <v>14034.5</v>
       </c>
       <c r="G101" t="n">
-        <v>13940.8</v>
+        <v>14034.5</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
         <v>15201.9</v>
       </c>
       <c r="J101" t="n">
-        <v>15092.4</v>
+        <v>15201.9</v>
       </c>
       <c r="K101" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>15932.4</v>
       </c>
       <c r="M101" t="n">
-        <v>15771.5</v>
+        <v>15932.4</v>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
+        <v>51100</v>
+      </c>
+      <c r="P101" t="n">
         <v>50900</v>
       </c>
-      <c r="P101" t="n">
-        <v>50600</v>
-      </c>
       <c r="Q101" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="102">
@@ -6165,46 +6165,46 @@
         <v>931</v>
       </c>
       <c r="D102" t="n">
-        <v>1002</v>
+        <v>931</v>
       </c>
       <c r="E102" t="n">
-        <v>-7.1</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
         <v>4546.9</v>
       </c>
       <c r="G102" t="n">
-        <v>4679.8</v>
+        <v>4546.9</v>
       </c>
       <c r="H102" t="n">
-        <v>-2.8</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
         <v>6570.8</v>
       </c>
       <c r="J102" t="n">
-        <v>6650.4</v>
+        <v>6570.8</v>
       </c>
       <c r="K102" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>8017.4</v>
       </c>
       <c r="M102" t="n">
-        <v>8075.1</v>
+        <v>8017.4</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
+        <v>146500</v>
+      </c>
+      <c r="P102" t="n">
         <v>149200</v>
       </c>
-      <c r="P102" t="n">
-        <v>143500</v>
-      </c>
       <c r="Q102" t="n">
-        <v>4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="103">
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
+        <v>42650</v>
+      </c>
+      <c r="P103" t="n">
         <v>43550</v>
       </c>
-      <c r="P103" t="n">
-        <v>44050</v>
-      </c>
       <c r="Q103" t="n">
-        <v>-1.1</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="104">
@@ -6276,49 +6276,49 @@
         </is>
       </c>
       <c r="C104" t="n">
+        <v>752</v>
+      </c>
+      <c r="D104" t="n">
         <v>760</v>
       </c>
-      <c r="D104" t="n">
-        <v>751</v>
-      </c>
       <c r="E104" t="n">
-        <v>1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="F104" t="n">
         <v>3443.6</v>
       </c>
       <c r="G104" t="n">
-        <v>3421.5</v>
+        <v>3443.6</v>
       </c>
       <c r="H104" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
         <v>4017.5</v>
       </c>
       <c r="J104" t="n">
-        <v>3992.5</v>
+        <v>4017.5</v>
       </c>
       <c r="K104" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
         <v>4314.5</v>
       </c>
       <c r="M104" t="n">
-        <v>4283.7</v>
+        <v>4314.5</v>
       </c>
       <c r="N104" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
+        <v>247000</v>
+      </c>
+      <c r="P104" t="n">
         <v>246500</v>
       </c>
-      <c r="P104" t="n">
-        <v>248500</v>
-      </c>
       <c r="Q104" t="n">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="105">
@@ -6333,49 +6333,49 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3808</v>
+        <v>3820</v>
       </c>
       <c r="D105" t="n">
         <v>3808</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F105" t="n">
-        <v>15532.2</v>
+        <v>15588.5</v>
       </c>
       <c r="G105" t="n">
         <v>15532.2</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I105" t="n">
-        <v>42457.5</v>
+        <v>42389.9</v>
       </c>
       <c r="J105" t="n">
         <v>42457.5</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L105" t="n">
-        <v>59569.1</v>
+        <v>58181.9</v>
       </c>
       <c r="M105" t="n">
         <v>59569.1</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="O105" t="n">
-        <v>260500</v>
+        <v>250500</v>
       </c>
       <c r="P105" t="n">
         <v>260500</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="106">
@@ -6426,13 +6426,13 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
+        <v>87800</v>
+      </c>
+      <c r="P106" t="n">
         <v>92700</v>
       </c>
-      <c r="P106" t="n">
-        <v>97600</v>
-      </c>
       <c r="Q106" t="n">
-        <v>-5</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="107">
@@ -6450,46 +6450,46 @@
         <v>22532</v>
       </c>
       <c r="D107" t="n">
-        <v>22349</v>
+        <v>22532</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
         <v>77226.7</v>
       </c>
       <c r="G107" t="n">
-        <v>76926.5</v>
+        <v>77226.7</v>
       </c>
       <c r="H107" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
         <v>81804.8</v>
       </c>
       <c r="J107" t="n">
-        <v>81714.5</v>
+        <v>81804.8</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L107" t="n">
         <v>85148.3</v>
       </c>
       <c r="M107" t="n">
-        <v>85120.2</v>
+        <v>85148.3</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
       </c>
       <c r="O107" t="n">
+        <v>103600</v>
+      </c>
+      <c r="P107" t="n">
         <v>107900</v>
       </c>
-      <c r="P107" t="n">
-        <v>108600</v>
-      </c>
       <c r="Q107" t="n">
-        <v>-0.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="108">
@@ -6507,46 +6507,46 @@
         <v>602</v>
       </c>
       <c r="D108" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
         <v>2483.1</v>
       </c>
       <c r="G108" t="n">
-        <v>2487.6</v>
+        <v>2483.1</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
         <v>3333</v>
       </c>
       <c r="J108" t="n">
-        <v>3312.3</v>
+        <v>3333</v>
       </c>
       <c r="K108" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>4265.2</v>
       </c>
       <c r="M108" t="n">
-        <v>4295.2</v>
+        <v>4265.2</v>
       </c>
       <c r="N108" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
+        <v>160500</v>
+      </c>
+      <c r="P108" t="n">
         <v>170000</v>
       </c>
-      <c r="P108" t="n">
-        <v>169800</v>
-      </c>
       <c r="Q108" t="n">
-        <v>0.1</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="109">
@@ -6564,46 +6564,46 @@
         <v>2706</v>
       </c>
       <c r="D109" t="n">
-        <v>2768</v>
+        <v>2706</v>
       </c>
       <c r="E109" t="n">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
         <v>11551.8</v>
       </c>
       <c r="G109" t="n">
-        <v>11805.3</v>
+        <v>11551.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-2.1</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
         <v>15008.9</v>
       </c>
       <c r="J109" t="n">
-        <v>15557.9</v>
+        <v>15008.9</v>
       </c>
       <c r="K109" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="L109" t="n">
         <v>18246.1</v>
       </c>
       <c r="M109" t="n">
-        <v>18626.1</v>
+        <v>18246.1</v>
       </c>
       <c r="N109" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
+        <v>151800</v>
+      </c>
+      <c r="P109" t="n">
         <v>159000</v>
       </c>
-      <c r="P109" t="n">
-        <v>170000</v>
-      </c>
       <c r="Q109" t="n">
-        <v>-6.5</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="110">
@@ -6618,49 +6618,49 @@
         </is>
       </c>
       <c r="C110" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D110" t="n">
         <v>1409</v>
       </c>
-      <c r="D110" t="n">
-        <v>1434</v>
-      </c>
       <c r="E110" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="F110" t="n">
+        <v>6058.6</v>
+      </c>
+      <c r="G110" t="n">
         <v>6080.8</v>
       </c>
-      <c r="G110" t="n">
-        <v>6162.8</v>
-      </c>
       <c r="H110" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
       <c r="I110" t="n">
+        <v>6916.7</v>
+      </c>
+      <c r="J110" t="n">
         <v>6954.7</v>
       </c>
-      <c r="J110" t="n">
-        <v>7022.6</v>
-      </c>
       <c r="K110" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="L110" t="n">
+        <v>7816.8</v>
+      </c>
+      <c r="M110" t="n">
         <v>7875.6</v>
       </c>
-      <c r="M110" t="n">
-        <v>7902.2</v>
-      </c>
       <c r="N110" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="O110" t="n">
+        <v>62050</v>
+      </c>
+      <c r="P110" t="n">
         <v>65000</v>
       </c>
-      <c r="P110" t="n">
-        <v>68200</v>
-      </c>
       <c r="Q110" t="n">
-        <v>-4.7</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="111">
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
+        <v>169400</v>
+      </c>
+      <c r="P111" t="n">
         <v>179000</v>
       </c>
-      <c r="P111" t="n">
-        <v>185600</v>
-      </c>
       <c r="Q111" t="n">
-        <v>-3.6</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="112">
@@ -6732,49 +6732,49 @@
         </is>
       </c>
       <c r="C112" t="n">
+        <v>468</v>
+      </c>
+      <c r="D112" t="n">
         <v>484</v>
       </c>
-      <c r="D112" t="n">
-        <v>502</v>
-      </c>
       <c r="E112" t="n">
-        <v>-3.6</v>
+        <v>-3.3</v>
       </c>
       <c r="F112" t="n">
+        <v>2491.8</v>
+      </c>
+      <c r="G112" t="n">
         <v>2479.7</v>
       </c>
-      <c r="G112" t="n">
-        <v>2517.9</v>
-      </c>
       <c r="H112" t="n">
-        <v>-1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I112" t="n">
+        <v>2392.7</v>
+      </c>
+      <c r="J112" t="n">
         <v>2351.1</v>
       </c>
-      <c r="J112" t="n">
-        <v>2311</v>
-      </c>
       <c r="K112" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L112" t="n">
+        <v>3357.4</v>
+      </c>
+      <c r="M112" t="n">
         <v>3364.5</v>
       </c>
-      <c r="M112" t="n">
-        <v>3257.2</v>
-      </c>
       <c r="N112" t="n">
-        <v>3.3</v>
+        <v>-0.2</v>
       </c>
       <c r="O112" t="n">
+        <v>81800</v>
+      </c>
+      <c r="P112" t="n">
         <v>92000</v>
       </c>
-      <c r="P112" t="n">
-        <v>101300</v>
-      </c>
       <c r="Q112" t="n">
-        <v>-9.199999999999999</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="113">
@@ -6825,13 +6825,13 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
+        <v>174000</v>
+      </c>
+      <c r="P113" t="n">
         <v>175800</v>
       </c>
-      <c r="P113" t="n">
-        <v>175100</v>
-      </c>
       <c r="Q113" t="n">
-        <v>0.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="114">
@@ -6882,13 +6882,13 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
+        <v>15160</v>
+      </c>
+      <c r="P114" t="n">
         <v>15450</v>
       </c>
-      <c r="P114" t="n">
-        <v>15520</v>
-      </c>
       <c r="Q114" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="115">
@@ -6906,46 +6906,46 @@
         <v>594</v>
       </c>
       <c r="D115" t="n">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="E115" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
         <v>2142.6</v>
       </c>
       <c r="G115" t="n">
-        <v>2065.2</v>
+        <v>2142.6</v>
       </c>
       <c r="H115" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>2281</v>
       </c>
       <c r="J115" t="n">
-        <v>2402.6</v>
+        <v>2281</v>
       </c>
       <c r="K115" t="n">
-        <v>-5.1</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>3611.6</v>
       </c>
       <c r="M115" t="n">
-        <v>3619.6</v>
+        <v>3611.6</v>
       </c>
       <c r="N115" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
+        <v>121000</v>
+      </c>
+      <c r="P115" t="n">
         <v>121900</v>
       </c>
-      <c r="P115" t="n">
-        <v>132500</v>
-      </c>
       <c r="Q115" t="n">
-        <v>-8</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="116">
@@ -6960,49 +6960,49 @@
         </is>
       </c>
       <c r="C116" t="n">
+        <v>858</v>
+      </c>
+      <c r="D116" t="n">
         <v>853</v>
       </c>
-      <c r="D116" t="n">
-        <v>858</v>
-      </c>
       <c r="E116" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="F116" t="n">
+        <v>4364.8</v>
+      </c>
+      <c r="G116" t="n">
         <v>4359.6</v>
       </c>
-      <c r="G116" t="n">
-        <v>4359.2</v>
-      </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I116" t="n">
+        <v>5274.4</v>
+      </c>
+      <c r="J116" t="n">
         <v>5281.8</v>
       </c>
-      <c r="J116" t="n">
-        <v>5268.4</v>
-      </c>
       <c r="K116" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="L116" t="n">
         <v>5667</v>
       </c>
       <c r="M116" t="n">
-        <v>5649.9</v>
+        <v>5667</v>
       </c>
       <c r="N116" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
+        <v>137600</v>
+      </c>
+      <c r="P116" t="n">
         <v>157400</v>
       </c>
-      <c r="P116" t="n">
-        <v>157900</v>
-      </c>
       <c r="Q116" t="n">
-        <v>-0.3</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="117">
@@ -7020,46 +7020,46 @@
         <v>10519</v>
       </c>
       <c r="D117" t="n">
-        <v>10415</v>
+        <v>10519</v>
       </c>
       <c r="E117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" t="n">
         <v>35391.5</v>
       </c>
       <c r="G117" t="n">
-        <v>35232.8</v>
+        <v>35391.5</v>
       </c>
       <c r="H117" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>32503.9</v>
       </c>
       <c r="J117" t="n">
-        <v>32313.2</v>
+        <v>32503.9</v>
       </c>
       <c r="K117" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>32692.6</v>
       </c>
       <c r="M117" t="n">
-        <v>32379.5</v>
+        <v>32692.6</v>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
+        <v>218500</v>
+      </c>
+      <c r="P117" t="n">
         <v>229000</v>
       </c>
-      <c r="P117" t="n">
-        <v>237000</v>
-      </c>
       <c r="Q117" t="n">
-        <v>-3.4</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="118">
@@ -7110,13 +7110,13 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
+        <v>64000</v>
+      </c>
+      <c r="P118" t="n">
         <v>64800</v>
       </c>
-      <c r="P118" t="n">
-        <v>66700</v>
-      </c>
       <c r="Q118" t="n">
-        <v>-2.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="119">
@@ -7134,46 +7134,46 @@
         <v>353</v>
       </c>
       <c r="D119" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
         <v>1525.8</v>
       </c>
       <c r="G119" t="n">
-        <v>1522.5</v>
+        <v>1525.8</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
         <v>2052.2</v>
       </c>
       <c r="J119" t="n">
-        <v>2035.3</v>
+        <v>2052.2</v>
       </c>
       <c r="K119" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
         <v>2493.5</v>
       </c>
       <c r="M119" t="n">
-        <v>2477.5</v>
+        <v>2493.5</v>
       </c>
       <c r="N119" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
+        <v>54300</v>
+      </c>
+      <c r="P119" t="n">
         <v>57600</v>
       </c>
-      <c r="P119" t="n">
-        <v>59600</v>
-      </c>
       <c r="Q119" t="n">
-        <v>-3.4</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="120">
@@ -7188,49 +7188,49 @@
         </is>
       </c>
       <c r="C120" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D120" t="n">
         <v>1442</v>
       </c>
-      <c r="D120" t="n">
-        <v>1455</v>
-      </c>
       <c r="E120" t="n">
-        <v>-0.9</v>
+        <v>2.7</v>
       </c>
       <c r="F120" t="n">
+        <v>5891.4</v>
+      </c>
+      <c r="G120" t="n">
         <v>5747.7</v>
       </c>
-      <c r="G120" t="n">
-        <v>5763.7</v>
-      </c>
       <c r="H120" t="n">
-        <v>-0.3</v>
+        <v>2.5</v>
       </c>
       <c r="I120" t="n">
+        <v>6323.3</v>
+      </c>
+      <c r="J120" t="n">
         <v>6118.2</v>
       </c>
-      <c r="J120" t="n">
-        <v>5993.2</v>
-      </c>
       <c r="K120" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="L120" t="n">
+        <v>7160.8</v>
+      </c>
+      <c r="M120" t="n">
         <v>6994.9</v>
       </c>
-      <c r="M120" t="n">
-        <v>6656.3</v>
-      </c>
       <c r="N120" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="O120" t="n">
+        <v>6060</v>
+      </c>
+      <c r="P120" t="n">
         <v>5850</v>
       </c>
-      <c r="P120" t="n">
-        <v>7160</v>
-      </c>
       <c r="Q120" t="n">
-        <v>-18.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="121">
@@ -7245,49 +7245,49 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>11636</v>
+        <v>11204</v>
       </c>
       <c r="D121" t="n">
         <v>11636</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="F121" t="n">
-        <v>41969.8</v>
+        <v>41295.8</v>
       </c>
       <c r="G121" t="n">
         <v>41969.8</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="I121" t="n">
-        <v>33273.2</v>
+        <v>34665.2</v>
       </c>
       <c r="J121" t="n">
         <v>33273.2</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L121" t="n">
-        <v>34176</v>
+        <v>35612</v>
       </c>
       <c r="M121" t="n">
         <v>34176</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O121" t="n">
         <v>82800</v>
       </c>
       <c r="P121" t="n">
-        <v>79500</v>
+        <v>82800</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7302,49 +7302,49 @@
         </is>
       </c>
       <c r="C122" t="n">
+        <v>1096</v>
+      </c>
+      <c r="D122" t="n">
         <v>1085</v>
       </c>
-      <c r="D122" t="n">
-        <v>1049</v>
-      </c>
       <c r="E122" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
+        <v>4559.3</v>
+      </c>
+      <c r="G122" t="n">
         <v>4545.4</v>
       </c>
-      <c r="G122" t="n">
-        <v>4500.6</v>
-      </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I122" t="n">
+        <v>6306.6</v>
+      </c>
+      <c r="J122" t="n">
         <v>6272.3</v>
       </c>
-      <c r="J122" t="n">
-        <v>6182.2</v>
-      </c>
       <c r="K122" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L122" t="n">
+        <v>8190.3</v>
+      </c>
+      <c r="M122" t="n">
         <v>8198.4</v>
       </c>
-      <c r="M122" t="n">
-        <v>8117.6</v>
-      </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>-0.1</v>
       </c>
       <c r="O122" t="n">
+        <v>676000</v>
+      </c>
+      <c r="P122" t="n">
         <v>749000</v>
       </c>
-      <c r="P122" t="n">
-        <v>725000</v>
-      </c>
       <c r="Q122" t="n">
-        <v>3.3</v>
+        <v>-9.699999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7362,46 +7362,46 @@
         <v>2129</v>
       </c>
       <c r="D123" t="n">
-        <v>2121</v>
+        <v>2129</v>
       </c>
       <c r="E123" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
         <v>5642.7</v>
       </c>
       <c r="G123" t="n">
-        <v>5637.1</v>
+        <v>5642.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
         <v>6011.4</v>
       </c>
       <c r="J123" t="n">
-        <v>6005.9</v>
+        <v>6011.4</v>
       </c>
       <c r="K123" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
         <v>6240.6</v>
       </c>
       <c r="M123" t="n">
-        <v>6231.9</v>
+        <v>6240.6</v>
       </c>
       <c r="N123" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
+        <v>46250</v>
+      </c>
+      <c r="P123" t="n">
         <v>46950</v>
       </c>
-      <c r="P123" t="n">
-        <v>45150</v>
-      </c>
       <c r="Q123" t="n">
-        <v>4</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="124">
@@ -7419,46 +7419,46 @@
         <v>580</v>
       </c>
       <c r="D124" t="n">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="E124" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
         <v>2416.7</v>
       </c>
       <c r="G124" t="n">
-        <v>2407.6</v>
+        <v>2416.7</v>
       </c>
       <c r="H124" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
         <v>3854</v>
       </c>
       <c r="J124" t="n">
-        <v>3687.6</v>
+        <v>3854</v>
       </c>
       <c r="K124" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>4707.3</v>
       </c>
       <c r="M124" t="n">
-        <v>4521.6</v>
+        <v>4707.3</v>
       </c>
       <c r="N124" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
+        <v>43500</v>
+      </c>
+      <c r="P124" t="n">
         <v>46900</v>
       </c>
-      <c r="P124" t="n">
-        <v>46200</v>
-      </c>
       <c r="Q124" t="n">
-        <v>1.5</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="125">
@@ -7476,46 +7476,46 @@
         <v>5133</v>
       </c>
       <c r="D125" t="n">
-        <v>5168</v>
+        <v>5133</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
         <v>21731.9</v>
       </c>
       <c r="G125" t="n">
-        <v>21752.8</v>
+        <v>21731.9</v>
       </c>
       <c r="H125" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I125" t="n">
         <v>23370.2</v>
       </c>
       <c r="J125" t="n">
-        <v>23346</v>
+        <v>23370.2</v>
       </c>
       <c r="K125" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
         <v>24535.4</v>
       </c>
       <c r="M125" t="n">
-        <v>24506.1</v>
+        <v>24535.4</v>
       </c>
       <c r="N125" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
+        <v>190900</v>
+      </c>
+      <c r="P125" t="n">
         <v>188600</v>
       </c>
-      <c r="P125" t="n">
-        <v>187800</v>
-      </c>
       <c r="Q125" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="126">
@@ -7533,46 +7533,46 @@
         <v>16580</v>
       </c>
       <c r="D126" t="n">
-        <v>16571</v>
+        <v>16580</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
         <v>60544.8</v>
       </c>
       <c r="G126" t="n">
-        <v>60434.6</v>
+        <v>60544.8</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
         <v>63280</v>
       </c>
       <c r="J126" t="n">
-        <v>63113.2</v>
+        <v>63280</v>
       </c>
       <c r="K126" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
         <v>66171.10000000001</v>
       </c>
       <c r="M126" t="n">
-        <v>65920.60000000001</v>
+        <v>66171.10000000001</v>
       </c>
       <c r="N126" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
+        <v>133100</v>
+      </c>
+      <c r="P126" t="n">
         <v>136800</v>
       </c>
-      <c r="P126" t="n">
-        <v>132600</v>
-      </c>
       <c r="Q126" t="n">
-        <v>3.2</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="127">
@@ -7587,40 +7587,40 @@
         </is>
       </c>
       <c r="F127" t="n">
+        <v>8471.799999999999</v>
+      </c>
+      <c r="G127" t="n">
         <v>8338.200000000001</v>
       </c>
-      <c r="G127" t="n">
-        <v>8132.5</v>
-      </c>
       <c r="H127" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="I127" t="n">
+        <v>9407.5</v>
+      </c>
+      <c r="J127" t="n">
         <v>9144.799999999999</v>
       </c>
-      <c r="J127" t="n">
-        <v>9055.200000000001</v>
-      </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="L127" t="n">
+        <v>9398.4</v>
+      </c>
+      <c r="M127" t="n">
         <v>9030.9</v>
       </c>
-      <c r="M127" t="n">
-        <v>8905.200000000001</v>
-      </c>
       <c r="N127" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="O127" t="n">
+        <v>4350</v>
+      </c>
+      <c r="P127" t="n">
         <v>4540</v>
       </c>
-      <c r="P127" t="n">
-        <v>4355</v>
-      </c>
       <c r="Q127" t="n">
-        <v>4.2</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="128">
@@ -7638,46 +7638,46 @@
         <v>983</v>
       </c>
       <c r="D128" t="n">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
+        <v>4647</v>
+      </c>
+      <c r="G128" t="n">
         <v>4633.1</v>
       </c>
-      <c r="G128" t="n">
-        <v>4637.6</v>
-      </c>
       <c r="H128" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I128" t="n">
+        <v>5283.7</v>
+      </c>
+      <c r="J128" t="n">
         <v>5273.7</v>
       </c>
-      <c r="J128" t="n">
-        <v>5278.1</v>
-      </c>
       <c r="K128" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L128" t="n">
+        <v>5883.9</v>
+      </c>
+      <c r="M128" t="n">
         <v>5877.4</v>
       </c>
-      <c r="M128" t="n">
-        <v>5882.1</v>
-      </c>
       <c r="N128" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="O128" t="n">
+        <v>121100</v>
+      </c>
+      <c r="P128" t="n">
         <v>124400</v>
       </c>
-      <c r="P128" t="n">
-        <v>121600</v>
-      </c>
       <c r="Q128" t="n">
-        <v>2.3</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="129">
@@ -7701,13 +7701,13 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
+        <v>10120</v>
+      </c>
+      <c r="P129" t="n">
         <v>11690</v>
       </c>
-      <c r="P129" t="n">
-        <v>12340</v>
-      </c>
       <c r="Q129" t="n">
-        <v>-5.3</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="130">
@@ -7722,49 +7722,49 @@
         </is>
       </c>
       <c r="C130" t="n">
+        <v>15582</v>
+      </c>
+      <c r="D130" t="n">
         <v>15727</v>
       </c>
-      <c r="D130" t="n">
-        <v>14123</v>
-      </c>
       <c r="E130" t="n">
-        <v>11.4</v>
+        <v>-0.9</v>
       </c>
       <c r="F130" t="n">
+        <v>54601.8</v>
+      </c>
+      <c r="G130" t="n">
         <v>54903.6</v>
       </c>
-      <c r="G130" t="n">
-        <v>50950.2</v>
-      </c>
       <c r="H130" t="n">
-        <v>7.8</v>
+        <v>-0.5</v>
       </c>
       <c r="I130" t="n">
+        <v>34598.5</v>
+      </c>
+      <c r="J130" t="n">
         <v>33584.2</v>
       </c>
-      <c r="J130" t="n">
-        <v>31187.9</v>
-      </c>
       <c r="K130" t="n">
-        <v>7.7</v>
+        <v>3</v>
       </c>
       <c r="L130" t="n">
+        <v>40044.5</v>
+      </c>
+      <c r="M130" t="n">
         <v>38301.9</v>
       </c>
-      <c r="M130" t="n">
-        <v>36712.4</v>
-      </c>
       <c r="N130" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O130" t="n">
+        <v>114200</v>
+      </c>
+      <c r="P130" t="n">
         <v>121400</v>
       </c>
-      <c r="P130" t="n">
-        <v>110200</v>
-      </c>
       <c r="Q130" t="n">
-        <v>10.2</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="131">
@@ -7779,49 +7779,49 @@
         </is>
       </c>
       <c r="C131" t="n">
+        <v>2769</v>
+      </c>
+      <c r="D131" t="n">
         <v>2777</v>
       </c>
-      <c r="D131" t="n">
-        <v>2773</v>
-      </c>
       <c r="E131" t="n">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="F131" t="n">
+        <v>12835.6</v>
+      </c>
+      <c r="G131" t="n">
         <v>12832.5</v>
       </c>
-      <c r="G131" t="n">
-        <v>12855.1</v>
-      </c>
       <c r="H131" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
+        <v>14512.8</v>
+      </c>
+      <c r="J131" t="n">
         <v>14554.2</v>
       </c>
-      <c r="J131" t="n">
-        <v>14545.4</v>
-      </c>
       <c r="K131" t="n">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="L131" t="n">
+        <v>15986.6</v>
+      </c>
+      <c r="M131" t="n">
         <v>16091</v>
       </c>
-      <c r="M131" t="n">
-        <v>15955.2</v>
-      </c>
       <c r="N131" t="n">
-        <v>0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="O131" t="n">
+        <v>188000</v>
+      </c>
+      <c r="P131" t="n">
         <v>184800</v>
       </c>
-      <c r="P131" t="n">
-        <v>191900</v>
-      </c>
       <c r="Q131" t="n">
-        <v>-3.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="132">
@@ -7836,49 +7836,49 @@
         </is>
       </c>
       <c r="C132" t="n">
+        <v>825</v>
+      </c>
+      <c r="D132" t="n">
         <v>819</v>
       </c>
-      <c r="D132" t="n">
-        <v>831</v>
-      </c>
       <c r="E132" t="n">
-        <v>-1.4</v>
+        <v>0.7</v>
       </c>
       <c r="F132" t="n">
+        <v>3600.1</v>
+      </c>
+      <c r="G132" t="n">
         <v>3630.2</v>
       </c>
-      <c r="G132" t="n">
-        <v>3617.8</v>
-      </c>
       <c r="H132" t="n">
-        <v>0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="I132" t="n">
+        <v>3530.3</v>
+      </c>
+      <c r="J132" t="n">
         <v>3537.3</v>
       </c>
-      <c r="J132" t="n">
-        <v>3606.6</v>
-      </c>
       <c r="K132" t="n">
-        <v>-1.9</v>
+        <v>-0.2</v>
       </c>
       <c r="L132" t="n">
+        <v>3913</v>
+      </c>
+      <c r="M132" t="n">
         <v>3903.7</v>
       </c>
-      <c r="M132" t="n">
-        <v>3982.7</v>
-      </c>
       <c r="N132" t="n">
-        <v>-2</v>
+        <v>0.2</v>
       </c>
       <c r="O132" t="n">
+        <v>60200</v>
+      </c>
+      <c r="P132" t="n">
         <v>62100</v>
       </c>
-      <c r="P132" t="n">
-        <v>62800</v>
-      </c>
       <c r="Q132" t="n">
-        <v>-1.1</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="133">
@@ -7896,46 +7896,46 @@
         <v>26142</v>
       </c>
       <c r="D133" t="n">
-        <v>25959</v>
+        <v>26142</v>
       </c>
       <c r="E133" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
         <v>93654.60000000001</v>
       </c>
       <c r="G133" t="n">
-        <v>92995.5</v>
+        <v>93654.60000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
         <v>95238.60000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>94516.7</v>
+        <v>95238.60000000001</v>
       </c>
       <c r="K133" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
         <v>98084.8</v>
       </c>
       <c r="M133" t="n">
-        <v>97229.5</v>
+        <v>98084.8</v>
       </c>
       <c r="N133" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
+        <v>169900</v>
+      </c>
+      <c r="P133" t="n">
         <v>181100</v>
       </c>
-      <c r="P133" t="n">
-        <v>186200</v>
-      </c>
       <c r="Q133" t="n">
-        <v>-2.7</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="134">
@@ -7953,46 +7953,46 @@
         <v>1837</v>
       </c>
       <c r="D134" t="n">
-        <v>1828</v>
+        <v>1837</v>
       </c>
       <c r="E134" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
         <v>6372.3</v>
       </c>
       <c r="G134" t="n">
-        <v>6361.3</v>
+        <v>6372.3</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
         <v>7034.4</v>
       </c>
       <c r="J134" t="n">
-        <v>6985.6</v>
+        <v>7034.4</v>
       </c>
       <c r="K134" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
         <v>7585.7</v>
       </c>
       <c r="M134" t="n">
-        <v>7521.4</v>
+        <v>7585.7</v>
       </c>
       <c r="N134" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>86900</v>
       </c>
       <c r="P134" t="n">
-        <v>84600</v>
+        <v>86900</v>
       </c>
       <c r="Q134" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -8043,13 +8043,13 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
+        <v>38850</v>
+      </c>
+      <c r="P135" t="n">
         <v>39850</v>
       </c>
-      <c r="P135" t="n">
-        <v>41400</v>
-      </c>
       <c r="Q135" t="n">
-        <v>-3.7</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="136">
@@ -8064,49 +8064,49 @@
         </is>
       </c>
       <c r="C136" t="n">
+        <v>741</v>
+      </c>
+      <c r="D136" t="n">
         <v>726</v>
       </c>
-      <c r="D136" t="n">
-        <v>712</v>
-      </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F136" t="n">
+        <v>2385.2</v>
+      </c>
+      <c r="G136" t="n">
         <v>2328.2</v>
       </c>
-      <c r="G136" t="n">
-        <v>2243.2</v>
-      </c>
       <c r="H136" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="I136" t="n">
+        <v>2689</v>
+      </c>
+      <c r="J136" t="n">
         <v>2607.6</v>
       </c>
-      <c r="J136" t="n">
-        <v>2576.2</v>
-      </c>
       <c r="K136" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="L136" t="n">
+        <v>3139.5</v>
+      </c>
+      <c r="M136" t="n">
         <v>3037.5</v>
       </c>
-      <c r="M136" t="n">
-        <v>2981.2</v>
-      </c>
       <c r="N136" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="O136" t="n">
+        <v>50100</v>
+      </c>
+      <c r="P136" t="n">
         <v>53600</v>
       </c>
-      <c r="P136" t="n">
-        <v>53400</v>
-      </c>
       <c r="Q136" t="n">
-        <v>0.4</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="137">
@@ -8124,46 +8124,46 @@
         <v>1056</v>
       </c>
       <c r="D137" t="n">
-        <v>866</v>
+        <v>1056</v>
       </c>
       <c r="E137" t="n">
-        <v>21.9</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
         <v>3103.2</v>
       </c>
       <c r="G137" t="n">
-        <v>2961.1</v>
+        <v>3103.2</v>
       </c>
       <c r="H137" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
         <v>3164.5</v>
       </c>
       <c r="J137" t="n">
-        <v>3106.5</v>
+        <v>3164.5</v>
       </c>
       <c r="K137" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>3447.3</v>
       </c>
       <c r="M137" t="n">
-        <v>3328.3</v>
+        <v>3447.3</v>
       </c>
       <c r="N137" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
+        <v>373000</v>
+      </c>
+      <c r="P137" t="n">
         <v>386000</v>
       </c>
-      <c r="P137" t="n">
-        <v>381500</v>
-      </c>
       <c r="Q137" t="n">
-        <v>1.2</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="138">
@@ -8214,13 +8214,13 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
+        <v>115800</v>
+      </c>
+      <c r="P138" t="n">
         <v>118300</v>
       </c>
-      <c r="P138" t="n">
-        <v>117000</v>
-      </c>
       <c r="Q138" t="n">
-        <v>1.1</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="139">
@@ -8238,46 +8238,46 @@
         <v>3241</v>
       </c>
       <c r="D139" t="n">
-        <v>3328</v>
+        <v>3241</v>
       </c>
       <c r="E139" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
         <v>10990.9</v>
       </c>
       <c r="G139" t="n">
-        <v>11090.9</v>
+        <v>10990.9</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>11876.1</v>
       </c>
       <c r="J139" t="n">
-        <v>11963.5</v>
+        <v>11876.1</v>
       </c>
       <c r="K139" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>12628.4</v>
       </c>
       <c r="M139" t="n">
-        <v>12679.9</v>
+        <v>12628.4</v>
       </c>
       <c r="N139" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
+        <v>18350</v>
+      </c>
+      <c r="P139" t="n">
         <v>18330</v>
       </c>
-      <c r="P139" t="n">
-        <v>18160</v>
-      </c>
       <c r="Q139" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="140">
@@ -8295,46 +8295,46 @@
         <v>2054</v>
       </c>
       <c r="D140" t="n">
-        <v>2101</v>
+        <v>2054</v>
       </c>
       <c r="E140" t="n">
-        <v>-2.2</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
         <v>6565.1</v>
       </c>
       <c r="G140" t="n">
-        <v>6606.6</v>
+        <v>6565.1</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
         <v>7114.6</v>
       </c>
       <c r="J140" t="n">
-        <v>7148.2</v>
+        <v>7114.6</v>
       </c>
       <c r="K140" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
         <v>7534.6</v>
       </c>
       <c r="M140" t="n">
-        <v>7563.8</v>
+        <v>7534.6</v>
       </c>
       <c r="N140" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
+        <v>18180</v>
+      </c>
+      <c r="P140" t="n">
         <v>18410</v>
       </c>
-      <c r="P140" t="n">
-        <v>18220</v>
-      </c>
       <c r="Q140" t="n">
-        <v>1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="141">
@@ -8352,46 +8352,46 @@
         <v>563</v>
       </c>
       <c r="D141" t="n">
-        <v>611</v>
+        <v>563</v>
       </c>
       <c r="E141" t="n">
-        <v>-7.9</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
         <v>5405.5</v>
       </c>
       <c r="G141" t="n">
-        <v>5488.2</v>
+        <v>5405.5</v>
       </c>
       <c r="H141" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
         <v>6438.3</v>
       </c>
       <c r="J141" t="n">
-        <v>6514.8</v>
+        <v>6438.3</v>
       </c>
       <c r="K141" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
         <v>7146</v>
       </c>
       <c r="M141" t="n">
-        <v>7220.6</v>
+        <v>7146</v>
       </c>
       <c r="N141" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
+        <v>81300</v>
+      </c>
+      <c r="P141" t="n">
         <v>79700</v>
       </c>
-      <c r="P141" t="n">
-        <v>82300</v>
-      </c>
       <c r="Q141" t="n">
-        <v>-3.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -8406,49 +8406,49 @@
         </is>
       </c>
       <c r="C142" t="n">
+        <v>5323</v>
+      </c>
+      <c r="D142" t="n">
         <v>5317</v>
-      </c>
-      <c r="D142" t="n">
-        <v>5313</v>
       </c>
       <c r="E142" t="n">
         <v>0.1</v>
       </c>
       <c r="F142" t="n">
+        <v>21470.9</v>
+      </c>
+      <c r="G142" t="n">
         <v>21470.8</v>
       </c>
-      <c r="G142" t="n">
-        <v>21431.1</v>
-      </c>
       <c r="H142" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
+        <v>23959.6</v>
+      </c>
+      <c r="J142" t="n">
         <v>23784.1</v>
       </c>
-      <c r="J142" t="n">
-        <v>23669.5</v>
-      </c>
       <c r="K142" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L142" t="n">
+        <v>25943.3</v>
+      </c>
+      <c r="M142" t="n">
         <v>25761.1</v>
       </c>
-      <c r="M142" t="n">
-        <v>25886.4</v>
-      </c>
       <c r="N142" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O142" t="n">
+        <v>72800</v>
+      </c>
+      <c r="P142" t="n">
         <v>73600</v>
       </c>
-      <c r="P142" t="n">
-        <v>69700</v>
-      </c>
       <c r="Q142" t="n">
-        <v>5.6</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="143">
@@ -8466,46 +8466,46 @@
         <v>951</v>
       </c>
       <c r="D143" t="n">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
         <v>3152.6</v>
       </c>
       <c r="G143" t="n">
-        <v>3148.2</v>
+        <v>3152.6</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
         <v>3650.9</v>
       </c>
       <c r="J143" t="n">
-        <v>3633</v>
+        <v>3650.9</v>
       </c>
       <c r="K143" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
         <v>4118.9</v>
       </c>
       <c r="M143" t="n">
-        <v>4096.7</v>
+        <v>4118.9</v>
       </c>
       <c r="N143" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
+        <v>101500</v>
+      </c>
+      <c r="P143" t="n">
         <v>107600</v>
       </c>
-      <c r="P143" t="n">
-        <v>115800</v>
-      </c>
       <c r="Q143" t="n">
-        <v>-7.1</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="144">
@@ -8523,46 +8523,46 @@
         <v>2886</v>
       </c>
       <c r="D144" t="n">
-        <v>2872</v>
+        <v>2886</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
         <v>10057.9</v>
       </c>
       <c r="G144" t="n">
-        <v>10076.6</v>
+        <v>10057.9</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
         <v>10827.5</v>
       </c>
       <c r="J144" t="n">
-        <v>10814.8</v>
+        <v>10827.5</v>
       </c>
       <c r="K144" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>11410.1</v>
       </c>
       <c r="M144" t="n">
-        <v>11377.3</v>
+        <v>11410.1</v>
       </c>
       <c r="N144" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
+        <v>26350</v>
+      </c>
+      <c r="P144" t="n">
         <v>27400</v>
       </c>
-      <c r="P144" t="n">
-        <v>28000</v>
-      </c>
       <c r="Q144" t="n">
-        <v>-2.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="145">
@@ -8580,46 +8580,46 @@
         <v>202</v>
       </c>
       <c r="D145" t="n">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E145" t="n">
-        <v>-3.8</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
         <v>785.8</v>
       </c>
       <c r="G145" t="n">
-        <v>804.6</v>
+        <v>785.8</v>
       </c>
       <c r="H145" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
         <v>901.4</v>
       </c>
       <c r="J145" t="n">
-        <v>937.8</v>
+        <v>901.4</v>
       </c>
       <c r="K145" t="n">
-        <v>-3.9</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
         <v>984.8</v>
       </c>
       <c r="M145" t="n">
-        <v>1023.2</v>
+        <v>984.8</v>
       </c>
       <c r="N145" t="n">
-        <v>-3.8</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
+        <v>66000</v>
+      </c>
+      <c r="P145" t="n">
         <v>68300</v>
       </c>
-      <c r="P145" t="n">
-        <v>70400</v>
-      </c>
       <c r="Q145" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="146">
@@ -8634,49 +8634,49 @@
         </is>
       </c>
       <c r="C146" t="n">
+        <v>701</v>
+      </c>
+      <c r="D146" t="n">
         <v>698</v>
       </c>
-      <c r="D146" t="n">
-        <v>704</v>
-      </c>
       <c r="E146" t="n">
-        <v>-0.9</v>
+        <v>0.4</v>
       </c>
       <c r="F146" t="n">
+        <v>2856.2</v>
+      </c>
+      <c r="G146" t="n">
         <v>2839.1</v>
       </c>
-      <c r="G146" t="n">
-        <v>2852.6</v>
-      </c>
       <c r="H146" t="n">
-        <v>-0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I146" t="n">
+        <v>3132.9</v>
+      </c>
+      <c r="J146" t="n">
         <v>3105</v>
       </c>
-      <c r="J146" t="n">
-        <v>3117.2</v>
-      </c>
       <c r="K146" t="n">
-        <v>-0.4</v>
+        <v>0.9</v>
       </c>
       <c r="L146" t="n">
+        <v>3390.5</v>
+      </c>
+      <c r="M146" t="n">
         <v>3342.3</v>
       </c>
-      <c r="M146" t="n">
-        <v>3347.5</v>
-      </c>
       <c r="N146" t="n">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
       <c r="O146" t="n">
+        <v>59600</v>
+      </c>
+      <c r="P146" t="n">
         <v>61600</v>
       </c>
-      <c r="P146" t="n">
-        <v>61100</v>
-      </c>
       <c r="Q146" t="n">
-        <v>0.8</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="147">
@@ -8694,46 +8694,46 @@
         <v>694</v>
       </c>
       <c r="D147" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
         <v>2331.9</v>
       </c>
       <c r="G147" t="n">
-        <v>2327.5</v>
+        <v>2331.9</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
         <v>2774.9</v>
       </c>
       <c r="J147" t="n">
-        <v>2766.5</v>
+        <v>2774.9</v>
       </c>
       <c r="K147" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>3206.8</v>
       </c>
       <c r="M147" t="n">
-        <v>3194</v>
+        <v>3206.8</v>
       </c>
       <c r="N147" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
+        <v>173800</v>
+      </c>
+      <c r="P147" t="n">
         <v>181100</v>
       </c>
-      <c r="P147" t="n">
-        <v>184300</v>
-      </c>
       <c r="Q147" t="n">
-        <v>-1.7</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="148">
@@ -8751,46 +8751,46 @@
         <v>1022</v>
       </c>
       <c r="D148" t="n">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="E148" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
         <v>4022.1</v>
       </c>
       <c r="G148" t="n">
-        <v>4028.2</v>
+        <v>4022.1</v>
       </c>
       <c r="H148" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I148" t="n">
         <v>4688.9</v>
       </c>
       <c r="J148" t="n">
-        <v>4685.9</v>
+        <v>4688.9</v>
       </c>
       <c r="K148" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
         <v>5231.2</v>
       </c>
       <c r="M148" t="n">
-        <v>5234.6</v>
+        <v>5231.2</v>
       </c>
       <c r="N148" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
+        <v>43050</v>
+      </c>
+      <c r="P148" t="n">
         <v>44800</v>
       </c>
-      <c r="P148" t="n">
-        <v>47600</v>
-      </c>
       <c r="Q148" t="n">
-        <v>-5.9</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="149">
@@ -8841,13 +8841,13 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
+        <v>1404000</v>
+      </c>
+      <c r="P149" t="n">
         <v>1396000</v>
       </c>
-      <c r="P149" t="n">
-        <v>1400000</v>
-      </c>
       <c r="Q149" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="150">
@@ -8898,13 +8898,13 @@
         <v>0</v>
       </c>
       <c r="O150" t="n">
+        <v>60900</v>
+      </c>
+      <c r="P150" t="n">
         <v>64300</v>
       </c>
-      <c r="P150" t="n">
-        <v>61600</v>
-      </c>
       <c r="Q150" t="n">
-        <v>4.4</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="151">
@@ -8919,49 +8919,49 @@
         </is>
       </c>
       <c r="C151" t="n">
+        <v>893</v>
+      </c>
+      <c r="D151" t="n">
         <v>901</v>
       </c>
-      <c r="D151" t="n">
-        <v>964</v>
-      </c>
       <c r="E151" t="n">
-        <v>-6.5</v>
+        <v>-0.9</v>
       </c>
       <c r="F151" t="n">
+        <v>3624.2</v>
+      </c>
+      <c r="G151" t="n">
         <v>3636.6</v>
       </c>
-      <c r="G151" t="n">
-        <v>3714.5</v>
-      </c>
       <c r="H151" t="n">
-        <v>-2.1</v>
+        <v>-0.3</v>
       </c>
       <c r="I151" t="n">
+        <v>4271.6</v>
+      </c>
+      <c r="J151" t="n">
         <v>4301.9</v>
       </c>
-      <c r="J151" t="n">
-        <v>4314.8</v>
-      </c>
       <c r="K151" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="L151" t="n">
         <v>4457.2</v>
       </c>
       <c r="M151" t="n">
-        <v>4476</v>
+        <v>4457.2</v>
       </c>
       <c r="N151" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
+        <v>35250</v>
+      </c>
+      <c r="P151" t="n">
         <v>36300</v>
       </c>
-      <c r="P151" t="n">
-        <v>38150</v>
-      </c>
       <c r="Q151" t="n">
-        <v>-4.8</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="152">
@@ -9012,13 +9012,13 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
+        <v>238000</v>
+      </c>
+      <c r="P152" t="n">
         <v>240500</v>
       </c>
-      <c r="P152" t="n">
-        <v>238000</v>
-      </c>
       <c r="Q152" t="n">
-        <v>1.1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="153">
@@ -9069,13 +9069,13 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
+        <v>197000</v>
+      </c>
+      <c r="P153" t="n">
         <v>204500</v>
       </c>
-      <c r="P153" t="n">
-        <v>198000</v>
-      </c>
       <c r="Q153" t="n">
-        <v>3.3</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="154">
@@ -9093,46 +9093,46 @@
         <v>2851</v>
       </c>
       <c r="D154" t="n">
-        <v>2811</v>
+        <v>2851</v>
       </c>
       <c r="E154" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
         <v>12398.9</v>
       </c>
       <c r="G154" t="n">
-        <v>12375.1</v>
+        <v>12398.9</v>
       </c>
       <c r="H154" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
         <v>15481.2</v>
       </c>
       <c r="J154" t="n">
-        <v>15394.8</v>
+        <v>15481.2</v>
       </c>
       <c r="K154" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
         <v>19010</v>
       </c>
       <c r="M154" t="n">
-        <v>18919</v>
+        <v>19010</v>
       </c>
       <c r="N154" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
+        <v>763000</v>
+      </c>
+      <c r="P154" t="n">
         <v>797000</v>
       </c>
-      <c r="P154" t="n">
-        <v>788000</v>
-      </c>
       <c r="Q154" t="n">
-        <v>1.1</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="155">
@@ -9159,10 +9159,10 @@
         <v>7089.3</v>
       </c>
       <c r="G155" t="n">
-        <v>6959.4</v>
+        <v>7089.3</v>
       </c>
       <c r="H155" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
         <v>8809.700000000001</v>
@@ -9183,13 +9183,13 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
+        <v>120400</v>
+      </c>
+      <c r="P155" t="n">
         <v>130300</v>
       </c>
-      <c r="P155" t="n">
-        <v>127000</v>
-      </c>
       <c r="Q155" t="n">
-        <v>2.6</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="156">
@@ -9204,49 +9204,49 @@
         </is>
       </c>
       <c r="C156" t="n">
+        <v>1369</v>
+      </c>
+      <c r="D156" t="n">
         <v>1370</v>
       </c>
-      <c r="D156" t="n">
-        <v>1376</v>
-      </c>
       <c r="E156" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="F156" t="n">
+        <v>6491</v>
+      </c>
+      <c r="G156" t="n">
         <v>6487.6</v>
       </c>
-      <c r="G156" t="n">
-        <v>6507.6</v>
-      </c>
       <c r="H156" t="n">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I156" t="n">
+        <v>7053.8</v>
+      </c>
+      <c r="J156" t="n">
         <v>7029.8</v>
       </c>
-      <c r="J156" t="n">
-        <v>7041.8</v>
-      </c>
       <c r="K156" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L156" t="n">
         <v>7523.1</v>
       </c>
       <c r="M156" t="n">
-        <v>7619.4</v>
+        <v>7523.1</v>
       </c>
       <c r="N156" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
+        <v>128900</v>
+      </c>
+      <c r="P156" t="n">
         <v>128400</v>
       </c>
-      <c r="P156" t="n">
-        <v>133700</v>
-      </c>
       <c r="Q156" t="n">
-        <v>-4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="157">
@@ -9264,46 +9264,46 @@
         <v>588</v>
       </c>
       <c r="D157" t="n">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
+        <v>2645.5</v>
+      </c>
+      <c r="G157" t="n">
         <v>2664.2</v>
       </c>
-      <c r="G157" t="n">
-        <v>2744.2</v>
-      </c>
       <c r="H157" t="n">
-        <v>-2.9</v>
+        <v>-0.7</v>
       </c>
       <c r="I157" t="n">
+        <v>4803</v>
+      </c>
+      <c r="J157" t="n">
         <v>4853.8</v>
       </c>
-      <c r="J157" t="n">
-        <v>4888.5</v>
-      </c>
       <c r="K157" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="L157" t="n">
+        <v>6107.8</v>
+      </c>
+      <c r="M157" t="n">
         <v>6138.2</v>
       </c>
-      <c r="M157" t="n">
-        <v>6189.8</v>
-      </c>
       <c r="N157" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="O157" t="n">
+        <v>60700</v>
+      </c>
+      <c r="P157" t="n">
         <v>65500</v>
       </c>
-      <c r="P157" t="n">
-        <v>66500</v>
-      </c>
       <c r="Q157" t="n">
-        <v>-1.5</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="158">
@@ -9321,46 +9321,46 @@
         <v>1781</v>
       </c>
       <c r="D158" t="n">
-        <v>1735</v>
+        <v>1781</v>
       </c>
       <c r="E158" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
         <v>7313.5</v>
       </c>
       <c r="G158" t="n">
-        <v>7140.1</v>
+        <v>7313.5</v>
       </c>
       <c r="H158" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
         <v>9915.700000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>9637.700000000001</v>
+        <v>9915.700000000001</v>
       </c>
       <c r="K158" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>12427.3</v>
       </c>
       <c r="M158" t="n">
-        <v>12055.9</v>
+        <v>12427.3</v>
       </c>
       <c r="N158" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
+        <v>368500</v>
+      </c>
+      <c r="P158" t="n">
         <v>393000</v>
       </c>
-      <c r="P158" t="n">
-        <v>380000</v>
-      </c>
       <c r="Q158" t="n">
-        <v>3.4</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="159">
@@ -9378,46 +9378,46 @@
         <v>472</v>
       </c>
       <c r="D159" t="n">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="E159" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
         <v>1902.3</v>
       </c>
       <c r="G159" t="n">
-        <v>1888.8</v>
+        <v>1902.3</v>
       </c>
       <c r="H159" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
         <v>2170.4</v>
       </c>
       <c r="J159" t="n">
-        <v>2153.5</v>
+        <v>2170.4</v>
       </c>
       <c r="K159" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L159" t="n">
         <v>2398.1</v>
       </c>
       <c r="M159" t="n">
-        <v>2409.9</v>
+        <v>2398.1</v>
       </c>
       <c r="N159" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
+        <v>101200</v>
+      </c>
+      <c r="P159" t="n">
         <v>101000</v>
       </c>
-      <c r="P159" t="n">
-        <v>107800</v>
-      </c>
       <c r="Q159" t="n">
-        <v>-6.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="160">
@@ -9435,46 +9435,46 @@
         <v>760</v>
       </c>
       <c r="D160" t="n">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E160" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
         <v>2960.7</v>
       </c>
       <c r="G160" t="n">
-        <v>2941.1</v>
+        <v>2960.7</v>
       </c>
       <c r="H160" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
         <v>3258</v>
       </c>
       <c r="J160" t="n">
-        <v>3228.1</v>
+        <v>3258</v>
       </c>
       <c r="K160" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>3518.2</v>
       </c>
       <c r="M160" t="n">
-        <v>3473.8</v>
+        <v>3518.2</v>
       </c>
       <c r="N160" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
+        <v>125200</v>
+      </c>
+      <c r="P160" t="n">
         <v>126400</v>
       </c>
-      <c r="P160" t="n">
-        <v>127800</v>
-      </c>
       <c r="Q160" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="161">
@@ -9489,49 +9489,49 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="D161" t="n">
         <v>-15</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="F161" t="n">
-        <v>69</v>
+        <v>78.5</v>
       </c>
       <c r="G161" t="n">
         <v>69</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="I161" t="n">
-        <v>1050.5</v>
+        <v>1154</v>
       </c>
       <c r="J161" t="n">
         <v>1050.5</v>
       </c>
       <c r="K161" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="L161" t="n">
-        <v>1660</v>
+        <v>1770</v>
       </c>
       <c r="M161" t="n">
         <v>1660</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O161" t="n">
+        <v>37750</v>
+      </c>
+      <c r="P161" t="n">
         <v>39250</v>
       </c>
-      <c r="P161" t="n">
-        <v>39850</v>
-      </c>
       <c r="Q161" t="n">
-        <v>-1.5</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="162">
@@ -9546,49 +9546,49 @@
         </is>
       </c>
       <c r="C162" t="n">
+        <v>1431</v>
+      </c>
+      <c r="D162" t="n">
         <v>1305</v>
       </c>
-      <c r="D162" t="n">
-        <v>1279</v>
-      </c>
       <c r="E162" t="n">
-        <v>2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F162" t="n">
+        <v>4800.8</v>
+      </c>
+      <c r="G162" t="n">
         <v>4538.8</v>
       </c>
-      <c r="G162" t="n">
-        <v>4462.8</v>
-      </c>
       <c r="H162" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="I162" t="n">
+        <v>5760.2</v>
+      </c>
+      <c r="J162" t="n">
         <v>5431.5</v>
       </c>
-      <c r="J162" t="n">
-        <v>5285.2</v>
-      </c>
       <c r="K162" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="L162" t="n">
+        <v>6113.8</v>
+      </c>
+      <c r="M162" t="n">
         <v>5773.2</v>
       </c>
-      <c r="M162" t="n">
-        <v>5652.6</v>
-      </c>
       <c r="N162" t="n">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="O162" t="n">
+        <v>316000</v>
+      </c>
+      <c r="P162" t="n">
         <v>278000</v>
       </c>
-      <c r="P162" t="n">
-        <v>272000</v>
-      </c>
       <c r="Q162" t="n">
-        <v>2.2</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="163">
@@ -9606,46 +9606,46 @@
         <v>2812</v>
       </c>
       <c r="D163" t="n">
-        <v>2845</v>
+        <v>2812</v>
       </c>
       <c r="E163" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
         <v>10910.6</v>
       </c>
       <c r="G163" t="n">
-        <v>10942.1</v>
+        <v>10910.6</v>
       </c>
       <c r="H163" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="I163" t="n">
         <v>15413.5</v>
       </c>
       <c r="J163" t="n">
-        <v>15477.6</v>
+        <v>15413.5</v>
       </c>
       <c r="K163" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
+        <v>20085.3</v>
+      </c>
+      <c r="M163" t="n">
         <v>20226.6</v>
       </c>
-      <c r="M163" t="n">
-        <v>19558.8</v>
-      </c>
       <c r="N163" t="n">
-        <v>3.4</v>
+        <v>-0.7</v>
       </c>
       <c r="O163" t="n">
+        <v>2554000</v>
+      </c>
+      <c r="P163" t="n">
         <v>2789000</v>
       </c>
-      <c r="P163" t="n">
-        <v>2666000</v>
-      </c>
       <c r="Q163" t="n">
-        <v>4.6</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="164">
@@ -9660,49 +9660,49 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="D164" t="n">
         <v>552</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="F164" t="n">
-        <v>2071.2</v>
+        <v>2200.4</v>
       </c>
       <c r="G164" t="n">
         <v>2071.2</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I164" t="n">
-        <v>2550.6</v>
+        <v>2696.6</v>
       </c>
       <c r="J164" t="n">
         <v>2550.6</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="L164" t="n">
-        <v>2729.6</v>
+        <v>2854.4</v>
       </c>
       <c r="M164" t="n">
         <v>2729.6</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O164" t="n">
+        <v>142800</v>
+      </c>
+      <c r="P164" t="n">
         <v>150500</v>
       </c>
-      <c r="P164" t="n">
-        <v>145000</v>
-      </c>
       <c r="Q164" t="n">
-        <v>3.8</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="165">
@@ -9753,13 +9753,13 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
+        <v>13850</v>
+      </c>
+      <c r="P165" t="n">
         <v>13990</v>
       </c>
-      <c r="P165" t="n">
-        <v>14310</v>
-      </c>
       <c r="Q165" t="n">
-        <v>-2.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="166">
@@ -9810,13 +9810,13 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
+        <v>33750</v>
+      </c>
+      <c r="P166" t="n">
         <v>35450</v>
       </c>
-      <c r="P166" t="n">
-        <v>36300</v>
-      </c>
       <c r="Q166" t="n">
-        <v>-2.3</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="167">
@@ -9834,46 +9834,46 @@
         <v>770</v>
       </c>
       <c r="D167" t="n">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="E167" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
         <v>2741.8</v>
       </c>
       <c r="G167" t="n">
-        <v>2766.1</v>
+        <v>2741.8</v>
       </c>
       <c r="H167" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
         <v>3662.2</v>
       </c>
       <c r="J167" t="n">
-        <v>3678.5</v>
+        <v>3662.2</v>
       </c>
       <c r="K167" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
         <v>4615.7</v>
       </c>
       <c r="M167" t="n">
-        <v>4633.6</v>
+        <v>4615.7</v>
       </c>
       <c r="N167" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
+        <v>364000</v>
+      </c>
+      <c r="P167" t="n">
         <v>393000</v>
       </c>
-      <c r="P167" t="n">
-        <v>438000</v>
-      </c>
       <c r="Q167" t="n">
-        <v>-10.3</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="168">
@@ -9891,16 +9891,16 @@
         <v>12920</v>
       </c>
       <c r="D168" t="n">
-        <v>12900</v>
+        <v>12920</v>
       </c>
       <c r="E168" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
         <v>43434.9</v>
       </c>
       <c r="G168" t="n">
-        <v>43417.7</v>
+        <v>43434.9</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -9909,28 +9909,28 @@
         <v>47616.6</v>
       </c>
       <c r="J168" t="n">
-        <v>47710.4</v>
+        <v>47616.6</v>
       </c>
       <c r="K168" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="L168" t="n">
         <v>50303.6</v>
       </c>
       <c r="M168" t="n">
-        <v>50412.4</v>
+        <v>50303.6</v>
       </c>
       <c r="N168" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
+        <v>30600</v>
+      </c>
+      <c r="P168" t="n">
         <v>31500</v>
       </c>
-      <c r="P168" t="n">
-        <v>31200</v>
-      </c>
       <c r="Q168" t="n">
-        <v>1</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="169">
@@ -9948,46 +9948,46 @@
         <v>1822</v>
       </c>
       <c r="D169" t="n">
-        <v>1833</v>
+        <v>1822</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
         <v>7099.5</v>
       </c>
       <c r="G169" t="n">
-        <v>7101.1</v>
+        <v>7099.5</v>
       </c>
       <c r="H169" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
         <v>8219.5</v>
       </c>
       <c r="J169" t="n">
-        <v>8165.4</v>
+        <v>8219.5</v>
       </c>
       <c r="K169" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L169" t="n">
         <v>8952.200000000001</v>
       </c>
       <c r="M169" t="n">
-        <v>8919.4</v>
+        <v>8952.200000000001</v>
       </c>
       <c r="N169" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
+        <v>22500</v>
+      </c>
+      <c r="P169" t="n">
         <v>23000</v>
       </c>
-      <c r="P169" t="n">
-        <v>23300</v>
-      </c>
       <c r="Q169" t="n">
-        <v>-1.3</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="170">
@@ -10038,13 +10038,13 @@
         <v>0</v>
       </c>
       <c r="O170" t="n">
+        <v>78300</v>
+      </c>
+      <c r="P170" t="n">
         <v>79400</v>
       </c>
-      <c r="P170" t="n">
-        <v>79300</v>
-      </c>
       <c r="Q170" t="n">
-        <v>0.1</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="171">
@@ -10062,46 +10062,46 @@
         <v>9910</v>
       </c>
       <c r="D171" t="n">
-        <v>9902</v>
+        <v>9910</v>
       </c>
       <c r="E171" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
         <v>38876</v>
       </c>
       <c r="G171" t="n">
-        <v>38897.6</v>
+        <v>38876</v>
       </c>
       <c r="H171" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I171" t="n">
         <v>45739.8</v>
       </c>
       <c r="J171" t="n">
-        <v>45686.3</v>
+        <v>45739.8</v>
       </c>
       <c r="K171" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
         <v>52641.7</v>
       </c>
       <c r="M171" t="n">
-        <v>51979.2</v>
+        <v>52641.7</v>
       </c>
       <c r="N171" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
+        <v>442500</v>
+      </c>
+      <c r="P171" t="n">
         <v>484000</v>
       </c>
-      <c r="P171" t="n">
-        <v>487500</v>
-      </c>
       <c r="Q171" t="n">
-        <v>-0.7</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="172">
@@ -10116,49 +10116,49 @@
         </is>
       </c>
       <c r="C172" t="n">
+        <v>1536</v>
+      </c>
+      <c r="D172" t="n">
         <v>1528</v>
       </c>
-      <c r="D172" t="n">
-        <v>1499</v>
-      </c>
       <c r="E172" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F172" t="n">
+        <v>2708</v>
+      </c>
+      <c r="G172" t="n">
         <v>2697</v>
       </c>
-      <c r="G172" t="n">
-        <v>2659.2</v>
-      </c>
       <c r="H172" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="I172" t="n">
+        <v>4881.3</v>
+      </c>
+      <c r="J172" t="n">
         <v>4904.1</v>
       </c>
-      <c r="J172" t="n">
-        <v>4935</v>
-      </c>
       <c r="K172" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="L172" t="n">
+        <v>5489.9</v>
+      </c>
+      <c r="M172" t="n">
         <v>5526.9</v>
       </c>
-      <c r="M172" t="n">
-        <v>5511.5</v>
-      </c>
       <c r="N172" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="O172" t="n">
+        <v>199900</v>
+      </c>
+      <c r="P172" t="n">
         <v>208500</v>
       </c>
-      <c r="P172" t="n">
-        <v>213000</v>
-      </c>
       <c r="Q172" t="n">
-        <v>-2.1</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="173">
@@ -10209,13 +10209,13 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
+        <v>13310</v>
+      </c>
+      <c r="P173" t="n">
         <v>14260</v>
       </c>
-      <c r="P173" t="n">
-        <v>14460</v>
-      </c>
       <c r="Q173" t="n">
-        <v>-1.4</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="174">
@@ -10242,37 +10242,37 @@
         <v>11337.5</v>
       </c>
       <c r="G174" t="n">
-        <v>11444.5</v>
+        <v>11337.5</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="I174" t="n">
         <v>39777.8</v>
       </c>
       <c r="J174" t="n">
-        <v>39869.5</v>
+        <v>39777.8</v>
       </c>
       <c r="K174" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
         <v>61996.8</v>
       </c>
       <c r="M174" t="n">
-        <v>61536.8</v>
+        <v>61996.8</v>
       </c>
       <c r="N174" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
+        <v>314000</v>
+      </c>
+      <c r="P174" t="n">
         <v>334000</v>
       </c>
-      <c r="P174" t="n">
-        <v>328500</v>
-      </c>
       <c r="Q174" t="n">
-        <v>1.7</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="175">
@@ -10287,49 +10287,49 @@
         </is>
       </c>
       <c r="C175" t="n">
+        <v>1238</v>
+      </c>
+      <c r="D175" t="n">
         <v>1227</v>
       </c>
-      <c r="D175" t="n">
-        <v>1199</v>
-      </c>
       <c r="E175" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="F175" t="n">
+        <v>5272.2</v>
+      </c>
+      <c r="G175" t="n">
         <v>5259.8</v>
       </c>
-      <c r="G175" t="n">
-        <v>5129.8</v>
-      </c>
       <c r="H175" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="I175" t="n">
+        <v>5624.7</v>
+      </c>
+      <c r="J175" t="n">
         <v>5620.8</v>
       </c>
-      <c r="J175" t="n">
-        <v>5671.2</v>
-      </c>
       <c r="K175" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="L175" t="n">
+        <v>6119.8</v>
+      </c>
+      <c r="M175" t="n">
         <v>6112.2</v>
       </c>
-      <c r="M175" t="n">
-        <v>6198.3</v>
-      </c>
       <c r="N175" t="n">
-        <v>-1.4</v>
+        <v>0.1</v>
       </c>
       <c r="O175" t="n">
+        <v>58500</v>
+      </c>
+      <c r="P175" t="n">
         <v>60200</v>
       </c>
-      <c r="P175" t="n">
-        <v>60300</v>
-      </c>
       <c r="Q175" t="n">
-        <v>-0.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="176">
@@ -10344,49 +10344,49 @@
         </is>
       </c>
       <c r="C176" t="n">
+        <v>341</v>
+      </c>
+      <c r="D176" t="n">
         <v>332</v>
       </c>
-      <c r="D176" t="n">
-        <v>323</v>
-      </c>
       <c r="E176" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F176" t="n">
-        <v>1388.2</v>
+        <v>1389.8</v>
       </c>
       <c r="G176" t="n">
         <v>1388.2</v>
       </c>
       <c r="H176" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I176" t="n">
-        <v>1925.5</v>
+        <v>1928.8</v>
       </c>
       <c r="J176" t="n">
         <v>1925.5</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L176" t="n">
-        <v>2719</v>
+        <v>2724</v>
       </c>
       <c r="M176" t="n">
         <v>2719</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O176" t="n">
+        <v>40950</v>
+      </c>
+      <c r="P176" t="n">
         <v>40900</v>
       </c>
-      <c r="P176" t="n">
-        <v>39750</v>
-      </c>
       <c r="Q176" t="n">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="177">
@@ -10404,46 +10404,46 @@
         <v>970</v>
       </c>
       <c r="D177" t="n">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E177" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
         <v>5308.8</v>
       </c>
       <c r="G177" t="n">
-        <v>5294.5</v>
+        <v>5308.8</v>
       </c>
       <c r="H177" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I177" t="n">
         <v>5626.7</v>
       </c>
       <c r="J177" t="n">
-        <v>5592.8</v>
+        <v>5626.7</v>
       </c>
       <c r="K177" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>6061.2</v>
       </c>
       <c r="M177" t="n">
-        <v>5983.8</v>
+        <v>6061.2</v>
       </c>
       <c r="N177" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
+        <v>75700</v>
+      </c>
+      <c r="P177" t="n">
         <v>79000</v>
       </c>
-      <c r="P177" t="n">
-        <v>79900</v>
-      </c>
       <c r="Q177" t="n">
-        <v>-1.1</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="178">
@@ -10470,37 +10470,37 @@
         <v>434130.4</v>
       </c>
       <c r="G178" t="n">
-        <v>430391.9</v>
+        <v>434130.4</v>
       </c>
       <c r="H178" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I178" t="n">
         <v>547499.1</v>
       </c>
       <c r="J178" t="n">
-        <v>541747.7</v>
+        <v>547499.1</v>
       </c>
       <c r="K178" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
         <v>587557.6</v>
       </c>
       <c r="M178" t="n">
-        <v>583359</v>
+        <v>587557.6</v>
       </c>
       <c r="N178" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
+        <v>1217000</v>
+      </c>
+      <c r="P178" t="n">
         <v>1212000</v>
       </c>
-      <c r="P178" t="n">
-        <v>1161000</v>
-      </c>
       <c r="Q178" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="179">
@@ -10518,46 +10518,46 @@
         <v>1035</v>
       </c>
       <c r="D179" t="n">
-        <v>1055</v>
+        <v>1035</v>
       </c>
       <c r="E179" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
         <v>4310.1</v>
       </c>
       <c r="G179" t="n">
-        <v>4346.1</v>
+        <v>4310.1</v>
       </c>
       <c r="H179" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="I179" t="n">
         <v>5454.2</v>
       </c>
       <c r="J179" t="n">
-        <v>5498.2</v>
+        <v>5454.2</v>
       </c>
       <c r="K179" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="L179" t="n">
         <v>6620.5</v>
       </c>
       <c r="M179" t="n">
-        <v>6666.5</v>
+        <v>6620.5</v>
       </c>
       <c r="N179" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
+        <v>186400</v>
+      </c>
+      <c r="P179" t="n">
         <v>201000</v>
       </c>
-      <c r="P179" t="n">
-        <v>193600</v>
-      </c>
       <c r="Q179" t="n">
-        <v>3.8</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="180">
@@ -10608,13 +10608,13 @@
         <v>0</v>
       </c>
       <c r="O180" t="n">
+        <v>84500</v>
+      </c>
+      <c r="P180" t="n">
         <v>89800</v>
       </c>
-      <c r="P180" t="n">
-        <v>92100</v>
-      </c>
       <c r="Q180" t="n">
-        <v>-2.5</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="181">
@@ -10629,49 +10629,49 @@
         </is>
       </c>
       <c r="C181" t="n">
+        <v>408</v>
+      </c>
+      <c r="D181" t="n">
         <v>410</v>
       </c>
-      <c r="D181" t="n">
-        <v>414</v>
-      </c>
       <c r="E181" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="F181" t="n">
+        <v>1613.9</v>
+      </c>
+      <c r="G181" t="n">
         <v>1607.4</v>
       </c>
-      <c r="G181" t="n">
-        <v>1606.1</v>
-      </c>
       <c r="H181" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I181" t="n">
+        <v>2210.9</v>
+      </c>
+      <c r="J181" t="n">
         <v>2200.8</v>
       </c>
-      <c r="J181" t="n">
-        <v>2195.5</v>
-      </c>
       <c r="K181" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L181" t="n">
+        <v>2791.2</v>
+      </c>
+      <c r="M181" t="n">
         <v>2775.9</v>
       </c>
-      <c r="M181" t="n">
-        <v>2769.4</v>
-      </c>
       <c r="N181" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="O181" t="n">
+        <v>238000</v>
+      </c>
+      <c r="P181" t="n">
         <v>208500</v>
       </c>
-      <c r="P181" t="n">
-        <v>199500</v>
-      </c>
       <c r="Q181" t="n">
-        <v>4.5</v>
+        <v>14.1</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -452,7 +452,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-21 · 전주 2026-07-17</t>
+          <t>KOSPI200 영업이익 컨센 · 기준일 2026-07-23 · 전주 2026-07-17</t>
         </is>
       </c>
     </row>
@@ -555,49 +555,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="D3" t="n">
         <v>615</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.8</v>
+        <v>-0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1949.2</v>
+        <v>1941.4</v>
       </c>
       <c r="G3" t="n">
         <v>1958.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>2049.7</v>
+        <v>2047</v>
       </c>
       <c r="J3" t="n">
         <v>2060.6</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="L3" t="n">
-        <v>2183</v>
+        <v>2178.8</v>
       </c>
       <c r="M3" t="n">
         <v>2183</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O3" t="n">
-        <v>14790</v>
+        <v>14990</v>
       </c>
       <c r="P3" t="n">
         <v>14910</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -612,49 +612,49 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="D4" t="n">
         <v>571</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F4" t="n">
-        <v>1311.3</v>
+        <v>1302.1</v>
       </c>
       <c r="G4" t="n">
         <v>1311.3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2224.1</v>
+        <v>2221.5</v>
       </c>
       <c r="J4" t="n">
         <v>2224.1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L4" t="n">
-        <v>2994</v>
+        <v>3051.5</v>
       </c>
       <c r="M4" t="n">
         <v>2994</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>69500</v>
+        <v>71700</v>
       </c>
       <c r="P4" t="n">
         <v>70800</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
@@ -669,49 +669,49 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1122</v>
+        <v>1104</v>
       </c>
       <c r="D5" t="n">
         <v>1132</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9</v>
+        <v>-2.5</v>
       </c>
       <c r="F5" t="n">
-        <v>5083.3</v>
+        <v>5010.4</v>
       </c>
       <c r="G5" t="n">
         <v>5126.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="I5" t="n">
-        <v>5652.6</v>
+        <v>5615.6</v>
       </c>
       <c r="J5" t="n">
         <v>5683.2</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="L5" t="n">
-        <v>6095.5</v>
+        <v>6144.3</v>
       </c>
       <c r="M5" t="n">
         <v>6123.2</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O5" t="n">
-        <v>72100</v>
+        <v>73900</v>
       </c>
       <c r="P5" t="n">
         <v>72500</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1107000</v>
+        <v>1255000</v>
       </c>
       <c r="P6" t="n">
         <v>1202000</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="7">
@@ -819,3682 +819,3658 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>44750</v>
+        <v>49200</v>
       </c>
       <c r="P7" t="n">
         <v>46450</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>000240</t>
+          <t>000270</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한국앤컴퍼니</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1365</v>
+        <v>27935</v>
       </c>
       <c r="D8" t="n">
-        <v>1365</v>
+        <v>27935</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4574</v>
+        <v>102889.3</v>
       </c>
       <c r="G8" t="n">
-        <v>4574</v>
+        <v>102889.3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4536</v>
+        <v>113580.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4536</v>
+        <v>113580.6</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5420</v>
+        <v>119352.9</v>
       </c>
       <c r="M8" t="n">
-        <v>5420</v>
+        <v>119352.9</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>25450</v>
+        <v>149100</v>
       </c>
       <c r="P8" t="n">
-        <v>25250</v>
+        <v>149700</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>000270</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27935</v>
+        <v>642327</v>
       </c>
       <c r="D9" t="n">
-        <v>27935</v>
+        <v>641632</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>102889.3</v>
+        <v>2723113.3</v>
       </c>
       <c r="G9" t="n">
-        <v>102889.3</v>
+        <v>2728835.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>113580.6</v>
+        <v>3993188</v>
       </c>
       <c r="J9" t="n">
-        <v>113580.6</v>
+        <v>3981826.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L9" t="n">
-        <v>119352.9</v>
+        <v>3871437.2</v>
       </c>
       <c r="M9" t="n">
-        <v>119352.9</v>
+        <v>3871437.2</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>142500</v>
+        <v>1906000</v>
       </c>
       <c r="P9" t="n">
-        <v>149700</v>
+        <v>1842000</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>641632</v>
+        <v>2105</v>
       </c>
       <c r="D10" t="n">
-        <v>641632</v>
+        <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="F10" t="n">
-        <v>2728835.8</v>
+        <v>8335.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2728835.8</v>
+        <v>8280.6</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>3981826.7</v>
+        <v>11041</v>
       </c>
       <c r="J10" t="n">
-        <v>3981826.7</v>
+        <v>11114.9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="L10" t="n">
-        <v>3871437.2</v>
+        <v>13616.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3871437.2</v>
+        <v>13860.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1823000</v>
+        <v>103300</v>
       </c>
       <c r="P10" t="n">
-        <v>1842000</v>
+        <v>99000</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2120</v>
+        <v>8815</v>
       </c>
       <c r="D11" t="n">
-        <v>2026</v>
+        <v>8815</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8315.799999999999</v>
+        <v>30870.2</v>
       </c>
       <c r="G11" t="n">
-        <v>8280.6</v>
+        <v>30870.2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>11067.6</v>
+        <v>33681.5</v>
       </c>
       <c r="J11" t="n">
-        <v>11114.9</v>
+        <v>33681.5</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13657.2</v>
+        <v>34114</v>
       </c>
       <c r="M11" t="n">
-        <v>13860.7</v>
+        <v>34114</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>92700</v>
+        <v>642000</v>
       </c>
       <c r="P11" t="n">
-        <v>99000</v>
+        <v>701000</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.4</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>000880</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8815</v>
+        <v>14592</v>
       </c>
       <c r="D12" t="n">
-        <v>8815</v>
+        <v>14500</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="n">
-        <v>30870.2</v>
+        <v>55739.2</v>
       </c>
       <c r="G12" t="n">
-        <v>30870.2</v>
+        <v>55718.1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>33681.5</v>
+        <v>68427</v>
       </c>
       <c r="J12" t="n">
-        <v>33681.5</v>
+        <v>67947</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L12" t="n">
-        <v>34114</v>
+        <v>73590</v>
       </c>
       <c r="M12" t="n">
-        <v>34114</v>
+        <v>72448</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>612000</v>
+        <v>93000</v>
       </c>
       <c r="P12" t="n">
-        <v>701000</v>
+        <v>93200</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.7</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>000880</t>
+          <t>000990</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>DB하이텍</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14500</v>
+        <v>886</v>
       </c>
       <c r="D13" t="n">
-        <v>14500</v>
+        <v>886</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>55718.1</v>
+        <v>3667.7</v>
       </c>
       <c r="G13" t="n">
-        <v>55718.1</v>
+        <v>3667.7</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>67947</v>
+        <v>4733.7</v>
       </c>
       <c r="J13" t="n">
-        <v>67947</v>
+        <v>4733.7</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>72448</v>
+        <v>5485.5</v>
       </c>
       <c r="M13" t="n">
-        <v>72448</v>
+        <v>5485.5</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>86900</v>
+        <v>107600</v>
       </c>
       <c r="P13" t="n">
-        <v>93200</v>
+        <v>109600</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.8</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>000990</t>
+          <t>001040</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DB하이텍</t>
+          <t>CJ</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>886</v>
+        <v>7075</v>
       </c>
       <c r="D14" t="n">
-        <v>886</v>
+        <v>7075</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3667.7</v>
+        <v>27186.7</v>
       </c>
       <c r="G14" t="n">
-        <v>3667.7</v>
+        <v>27186.7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4733.7</v>
+        <v>30305.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4733.7</v>
+        <v>30305.6</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5485.5</v>
+        <v>31530.4</v>
       </c>
       <c r="M14" t="n">
-        <v>5485.5</v>
+        <v>31530.4</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>102900</v>
+        <v>132400</v>
       </c>
       <c r="P14" t="n">
-        <v>109600</v>
+        <v>135700</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.1</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>001040</t>
+          <t>001430</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CJ</t>
+          <t>세아베스틸지주</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7075</v>
+        <v>535</v>
       </c>
       <c r="D15" t="n">
-        <v>7075</v>
+        <v>529</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F15" t="n">
-        <v>27186.7</v>
+        <v>1553.8</v>
       </c>
       <c r="G15" t="n">
-        <v>27186.7</v>
+        <v>1517.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I15" t="n">
-        <v>30305.6</v>
+        <v>2003</v>
       </c>
       <c r="J15" t="n">
-        <v>30305.6</v>
+        <v>1976.6</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L15" t="n">
-        <v>31530.4</v>
+        <v>2264.1</v>
       </c>
       <c r="M15" t="n">
-        <v>31530.4</v>
+        <v>2211.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>130700</v>
+        <v>35300</v>
       </c>
       <c r="P15" t="n">
-        <v>135700</v>
+        <v>32500</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>001430</t>
+          <t>001440</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>세아베스틸지주</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>529</v>
+        <v>423</v>
       </c>
       <c r="D16" t="n">
-        <v>529</v>
+        <v>423</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1517.9</v>
+        <v>1995.6</v>
       </c>
       <c r="G16" t="n">
-        <v>1517.9</v>
+        <v>1995.6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1976.6</v>
+        <v>2252.9</v>
       </c>
       <c r="J16" t="n">
-        <v>1976.6</v>
+        <v>2252.9</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2211.6</v>
+        <v>2899.4</v>
       </c>
       <c r="M16" t="n">
-        <v>2211.6</v>
+        <v>2899.4</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>31250</v>
+        <v>29050</v>
       </c>
       <c r="P16" t="n">
-        <v>32500</v>
+        <v>27700</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>대한전선</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>423</v>
-      </c>
-      <c r="D17" t="n">
-        <v>423</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
+          <t>현대해상</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>1995.6</v>
+        <v>10748.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1995.6</v>
+        <v>10625.3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2252.9</v>
+        <v>12188.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2252.9</v>
+        <v>12179.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L17" t="n">
-        <v>2899.4</v>
+        <v>13346.7</v>
       </c>
       <c r="M17" t="n">
-        <v>2899.4</v>
+        <v>13329</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O17" t="n">
-        <v>25450</v>
+        <v>38850</v>
       </c>
       <c r="P17" t="n">
-        <v>27700</v>
+        <v>38300</v>
       </c>
       <c r="Q17" t="n">
-        <v>-8.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>001680</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>현대해상</t>
-        </is>
+          <t>대상</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>396</v>
+      </c>
+      <c r="D18" t="n">
+        <v>396</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>10748.6</v>
+        <v>1830.5</v>
       </c>
       <c r="G18" t="n">
-        <v>10625.3</v>
+        <v>1830.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>12188.1</v>
+        <v>2044</v>
       </c>
       <c r="J18" t="n">
-        <v>12179.5</v>
+        <v>2044</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>13346.7</v>
+        <v>2060</v>
       </c>
       <c r="M18" t="n">
-        <v>13329</v>
+        <v>2060</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>37550</v>
+        <v>17370</v>
       </c>
       <c r="P18" t="n">
-        <v>38300</v>
+        <v>17260</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>001680</t>
+          <t>001800</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>대상</t>
+          <t>오리온홀딩스</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>396</v>
+        <v>1224</v>
       </c>
       <c r="D19" t="n">
-        <v>396</v>
+        <v>1224</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1830.5</v>
+        <v>6028</v>
       </c>
       <c r="G19" t="n">
-        <v>1830.5</v>
+        <v>6028</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="n">
-        <v>2044</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2044</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2060</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2060</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
-        <v>17370</v>
+        <v>25600</v>
       </c>
       <c r="P19" t="n">
-        <v>17260</v>
+        <v>26050</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>001800</t>
+          <t>002380</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>오리온홀딩스</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1224</v>
+        <v>1112</v>
       </c>
       <c r="D20" t="n">
-        <v>1224</v>
+        <v>1051</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F20" t="n">
-        <v>6028</v>
+        <v>4296.4</v>
       </c>
       <c r="G20" t="n">
-        <v>6028</v>
+        <v>4153.2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4870.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4725</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5210.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5072.2</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>25400</v>
+        <v>439000</v>
       </c>
       <c r="P20" t="n">
-        <v>26050</v>
+        <v>420000</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>002380</t>
+          <t>003030</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KCC</t>
+          <t>세아제강지주</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1075</v>
+        <v>422</v>
       </c>
       <c r="D21" t="n">
-        <v>1051</v>
+        <v>422</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>4245.5</v>
+        <v>1767.5</v>
       </c>
       <c r="G21" t="n">
-        <v>4153.2</v>
+        <v>1767.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4841.8</v>
+        <v>2913</v>
       </c>
       <c r="J21" t="n">
-        <v>4725</v>
+        <v>2913</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5176.8</v>
+        <v>4827</v>
       </c>
       <c r="M21" t="n">
-        <v>5072.2</v>
+        <v>4827</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>401500</v>
+        <v>106300</v>
       </c>
       <c r="P21" t="n">
-        <v>420000</v>
+        <v>99600</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>003030</t>
+          <t>003230</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>세아제강지주</t>
+          <t>삼양식품</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>422</v>
+        <v>1776</v>
       </c>
       <c r="D22" t="n">
-        <v>422</v>
+        <v>1781</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F22" t="n">
-        <v>1767.5</v>
+        <v>7333.1</v>
       </c>
       <c r="G22" t="n">
-        <v>1767.5</v>
+        <v>7309.6</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2913</v>
+        <v>8848.799999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>2913</v>
+        <v>8786.1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L22" t="n">
-        <v>4827</v>
+        <v>10353.1</v>
       </c>
       <c r="M22" t="n">
-        <v>4827</v>
+        <v>10286.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O22" t="n">
-        <v>95200</v>
+        <v>1110000</v>
       </c>
       <c r="P22" t="n">
-        <v>99600</v>
+        <v>1069000</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>003230</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼양식품</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1785</v>
+        <v>-2377</v>
       </c>
       <c r="D23" t="n">
-        <v>1781</v>
+        <v>-2377</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>7316.2</v>
+        <v>11051.5</v>
       </c>
       <c r="G23" t="n">
-        <v>7309.6</v>
+        <v>11051.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>8826.9</v>
+        <v>22324.6</v>
       </c>
       <c r="J23" t="n">
-        <v>8786.1</v>
+        <v>22324.6</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>10322.7</v>
+        <v>26471.7</v>
       </c>
       <c r="M23" t="n">
-        <v>10286.4</v>
+        <v>26471.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1118000</v>
+        <v>25525</v>
       </c>
       <c r="P23" t="n">
-        <v>1069000</v>
+        <v>26500</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.6</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003550</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-2377</v>
+        <v>4161</v>
       </c>
       <c r="D24" t="n">
-        <v>-2377</v>
+        <v>4161</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>11051.5</v>
+        <v>16315.8</v>
       </c>
       <c r="G24" t="n">
-        <v>11051.5</v>
+        <v>16182.7</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I24" t="n">
-        <v>22324.6</v>
+        <v>20997.3</v>
       </c>
       <c r="J24" t="n">
-        <v>22324.6</v>
+        <v>20528.9</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="L24" t="n">
-        <v>26471.7</v>
+        <v>22184.8</v>
       </c>
       <c r="M24" t="n">
-        <v>26471.7</v>
+        <v>21051.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O24" t="n">
-        <v>25700</v>
+        <v>100600</v>
       </c>
       <c r="P24" t="n">
-        <v>26500</v>
+        <v>98800</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>003550</t>
+          <t>003670</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>포스코퓨처엠</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4161</v>
+        <v>292</v>
       </c>
       <c r="D25" t="n">
-        <v>4161</v>
+        <v>292</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>16315.8</v>
+        <v>997.3</v>
       </c>
       <c r="G25" t="n">
-        <v>16182.7</v>
+        <v>997.3</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>20997.3</v>
+        <v>1648.4</v>
       </c>
       <c r="J25" t="n">
-        <v>20528.9</v>
+        <v>1648.4</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>22184.8</v>
+        <v>2856.9</v>
       </c>
       <c r="M25" t="n">
-        <v>21051.1</v>
+        <v>2856.9</v>
       </c>
       <c r="N25" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>96700</v>
+        <v>144900</v>
       </c>
       <c r="P25" t="n">
-        <v>98800</v>
+        <v>147600</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>003670</t>
+          <t>004000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>포스코퓨처엠</t>
+          <t>롯데정밀화학</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>292</v>
+        <v>397</v>
       </c>
       <c r="D26" t="n">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="F26" t="n">
-        <v>997.3</v>
+        <v>1440</v>
       </c>
       <c r="G26" t="n">
-        <v>997.3</v>
+        <v>1388</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1648.4</v>
+        <v>1628.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1648.4</v>
+        <v>1592.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="L26" t="n">
-        <v>2856.9</v>
+        <v>1748.7</v>
       </c>
       <c r="M26" t="n">
-        <v>2856.9</v>
+        <v>1730</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>135800</v>
+        <v>46250</v>
       </c>
       <c r="P26" t="n">
-        <v>147600</v>
+        <v>45650</v>
       </c>
       <c r="Q26" t="n">
-        <v>-8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>004000</t>
+          <t>004020</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>롯데정밀화학</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>397</v>
+        <v>833</v>
       </c>
       <c r="D27" t="n">
-        <v>357</v>
+        <v>866</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2</v>
+        <v>-3.8</v>
       </c>
       <c r="F27" t="n">
-        <v>1440</v>
+        <v>3982.2</v>
       </c>
       <c r="G27" t="n">
-        <v>1388</v>
+        <v>4077.3</v>
       </c>
       <c r="H27" t="n">
-        <v>3.7</v>
+        <v>-2.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1628.4</v>
+        <v>7071.2</v>
       </c>
       <c r="J27" t="n">
-        <v>1592.5</v>
+        <v>7113.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>-0.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1748.7</v>
+        <v>7982.9</v>
       </c>
       <c r="M27" t="n">
-        <v>1730</v>
+        <v>8048.5</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="O27" t="n">
-        <v>45850</v>
+        <v>27200</v>
       </c>
       <c r="P27" t="n">
-        <v>45650</v>
+        <v>26550</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>004170</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>신세계</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>833</v>
+        <v>1528</v>
       </c>
       <c r="D28" t="n">
-        <v>866</v>
+        <v>1526</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.8</v>
+        <v>0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>3982.2</v>
+        <v>7676</v>
       </c>
       <c r="G28" t="n">
-        <v>4077.3</v>
+        <v>7675.2</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>7071.2</v>
+        <v>8596.4</v>
       </c>
       <c r="J28" t="n">
-        <v>7113.6</v>
+        <v>8596.9</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.6</v>
+        <v>-0</v>
       </c>
       <c r="L28" t="n">
-        <v>7982.9</v>
+        <v>9080.6</v>
       </c>
       <c r="M28" t="n">
-        <v>8048.5</v>
+        <v>9078.200000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>25200</v>
+        <v>545000</v>
       </c>
       <c r="P28" t="n">
-        <v>26550</v>
+        <v>589000</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5.1</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>004170</t>
+          <t>004370</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>신세계</t>
+          <t>농심</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1528</v>
+        <v>502</v>
       </c>
       <c r="D29" t="n">
-        <v>1526</v>
+        <v>497</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>7676</v>
+        <v>2161.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7675.2</v>
+        <v>2150.9</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I29" t="n">
-        <v>8596.4</v>
+        <v>2341.6</v>
       </c>
       <c r="J29" t="n">
-        <v>8596.9</v>
+        <v>2328.6</v>
       </c>
       <c r="K29" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="L29" t="n">
-        <v>9080.6</v>
+        <v>2481.5</v>
       </c>
       <c r="M29" t="n">
-        <v>9078.200000000001</v>
+        <v>2454.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>555000</v>
+        <v>359500</v>
       </c>
       <c r="P29" t="n">
-        <v>589000</v>
+        <v>349500</v>
       </c>
       <c r="Q29" t="n">
-        <v>-5.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>004370</t>
+          <t>004990</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>농심</t>
+          <t>롯데지주</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>497</v>
+        <v>1613</v>
       </c>
       <c r="D30" t="n">
-        <v>497</v>
+        <v>1613</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>2150.9</v>
+        <v>3797</v>
       </c>
       <c r="G30" t="n">
-        <v>2150.9</v>
+        <v>3797</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2328.6</v>
+        <v>4472.5</v>
       </c>
       <c r="J30" t="n">
-        <v>2328.6</v>
+        <v>4472.5</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2454.5</v>
+        <v>7397.5</v>
       </c>
       <c r="M30" t="n">
-        <v>2454.5</v>
+        <v>7397.5</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>351000</v>
+        <v>23250</v>
       </c>
       <c r="P30" t="n">
-        <v>349500</v>
+        <v>22800</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>004990</t>
+          <t>005300</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>롯데지주</t>
+          <t>롯데칠성</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1613</v>
+        <v>631</v>
       </c>
       <c r="D31" t="n">
-        <v>1613</v>
+        <v>639</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="F31" t="n">
-        <v>3797</v>
+        <v>2118.2</v>
       </c>
       <c r="G31" t="n">
-        <v>3797</v>
+        <v>2123.5</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I31" t="n">
-        <v>4472.5</v>
+        <v>2340.8</v>
       </c>
       <c r="J31" t="n">
-        <v>4472.5</v>
+        <v>2342</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L31" t="n">
-        <v>7397.5</v>
+        <v>2485.3</v>
       </c>
       <c r="M31" t="n">
-        <v>7397.5</v>
+        <v>2484.3</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>22450</v>
+        <v>98800</v>
       </c>
       <c r="P31" t="n">
-        <v>22800</v>
+        <v>99400</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.5</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>005300</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>롯데칠성</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>639</v>
+        <v>29940</v>
       </c>
       <c r="D32" t="n">
-        <v>639</v>
+        <v>30232</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F32" t="n">
-        <v>2123.5</v>
+        <v>117320.6</v>
       </c>
       <c r="G32" t="n">
-        <v>2123.5</v>
+        <v>117500.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I32" t="n">
-        <v>2342</v>
+        <v>132763</v>
       </c>
       <c r="J32" t="n">
-        <v>2342</v>
+        <v>132780.2</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L32" t="n">
-        <v>2484.3</v>
+        <v>145088.2</v>
       </c>
       <c r="M32" t="n">
-        <v>2484.3</v>
+        <v>144868.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O32" t="n">
-        <v>97400</v>
+        <v>429000</v>
       </c>
       <c r="P32" t="n">
-        <v>99400</v>
+        <v>425000</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>005490</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>30059</v>
+        <v>7299</v>
       </c>
       <c r="D33" t="n">
-        <v>30232</v>
+        <v>7299</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>117411.4</v>
+        <v>30875.7</v>
       </c>
       <c r="G33" t="n">
-        <v>117500.2</v>
+        <v>30875.7</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>132691</v>
+        <v>38602.4</v>
       </c>
       <c r="J33" t="n">
-        <v>132780.2</v>
+        <v>38602.4</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>144868.6</v>
+        <v>44763.8</v>
       </c>
       <c r="M33" t="n">
-        <v>144868.6</v>
+        <v>44763.8</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>393500</v>
+        <v>314000</v>
       </c>
       <c r="P33" t="n">
-        <v>425000</v>
+        <v>311500</v>
       </c>
       <c r="Q33" t="n">
-        <v>-7.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>005490</t>
+          <t>005830</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>DB손해보험</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7299</v>
+        <v>5604</v>
       </c>
       <c r="D34" t="n">
-        <v>7299</v>
+        <v>5604</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>30875.7</v>
+        <v>21369.8</v>
       </c>
       <c r="G34" t="n">
-        <v>30875.7</v>
+        <v>21330.6</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I34" t="n">
-        <v>38602.4</v>
+        <v>23187</v>
       </c>
       <c r="J34" t="n">
-        <v>38602.4</v>
+        <v>23130.1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L34" t="n">
-        <v>44763.8</v>
+        <v>24471.6</v>
       </c>
       <c r="M34" t="n">
-        <v>44763.8</v>
+        <v>24397.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O34" t="n">
-        <v>298000</v>
+        <v>168800</v>
       </c>
       <c r="P34" t="n">
-        <v>311500</v>
+        <v>163000</v>
       </c>
       <c r="Q34" t="n">
-        <v>-4.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>005830</t>
+          <t>005850</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DB손해보험</t>
+          <t>에스엘</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5604</v>
+        <v>1344</v>
       </c>
       <c r="D35" t="n">
-        <v>5604</v>
+        <v>1344</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>21330.6</v>
+        <v>4617</v>
       </c>
       <c r="G35" t="n">
-        <v>21330.6</v>
+        <v>4617</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>23130.1</v>
+        <v>5073.1</v>
       </c>
       <c r="J35" t="n">
-        <v>23130.1</v>
+        <v>5073.1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>24397.6</v>
+        <v>5900.8</v>
       </c>
       <c r="M35" t="n">
-        <v>24397.6</v>
+        <v>5900.8</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>163800</v>
+        <v>57100</v>
       </c>
       <c r="P35" t="n">
-        <v>163000</v>
+        <v>54400</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>005850</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>에스엘</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1344</v>
+        <v>850494</v>
       </c>
       <c r="D36" t="n">
-        <v>1344</v>
+        <v>850494</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>4617</v>
+        <v>3832403.6</v>
       </c>
       <c r="G36" t="n">
-        <v>4617</v>
+        <v>3832403.6</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>5073.1</v>
+        <v>5422607.3</v>
       </c>
       <c r="J36" t="n">
-        <v>5073.1</v>
+        <v>5422607.3</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>5900.8</v>
+        <v>5327749.5</v>
       </c>
       <c r="M36" t="n">
-        <v>5900.8</v>
+        <v>5327749.5</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>52400</v>
+        <v>269750</v>
       </c>
       <c r="P36" t="n">
-        <v>54400</v>
+        <v>255000</v>
       </c>
       <c r="Q36" t="n">
-        <v>-3.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005940</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>850494</v>
+        <v>6194</v>
       </c>
       <c r="D37" t="n">
-        <v>850494</v>
+        <v>6194</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>3832403.6</v>
+        <v>22124.5</v>
       </c>
       <c r="G37" t="n">
-        <v>3832403.6</v>
+        <v>21770.4</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I37" t="n">
-        <v>5422607.3</v>
+        <v>19912.6</v>
       </c>
       <c r="J37" t="n">
-        <v>5422607.3</v>
+        <v>19816.4</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L37" t="n">
-        <v>5327749.5</v>
+        <v>19928.7</v>
       </c>
       <c r="M37" t="n">
-        <v>5327749.5</v>
+        <v>19922.1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>257000</v>
+        <v>30250</v>
       </c>
       <c r="P37" t="n">
-        <v>255000</v>
+        <v>31000</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.8</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>005940</t>
+          <t>006040</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>동원산업</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6194</v>
+        <v>1253</v>
       </c>
       <c r="D38" t="n">
-        <v>6194</v>
+        <v>1265</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="F38" t="n">
-        <v>21770.4</v>
+        <v>5511.8</v>
       </c>
       <c r="G38" t="n">
-        <v>21770.4</v>
+        <v>5524</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I38" t="n">
-        <v>19816.4</v>
+        <v>5853.2</v>
       </c>
       <c r="J38" t="n">
-        <v>19816.4</v>
+        <v>5847.8</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L38" t="n">
-        <v>19922.1</v>
+        <v>6013</v>
       </c>
       <c r="M38" t="n">
-        <v>19922.1</v>
+        <v>6013</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>29800</v>
+        <v>33900</v>
       </c>
       <c r="P38" t="n">
-        <v>31000</v>
+        <v>33350</v>
       </c>
       <c r="Q38" t="n">
-        <v>-3.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>006040</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>동원산업</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1253</v>
+        <v>4406</v>
       </c>
       <c r="D39" t="n">
-        <v>1265</v>
+        <v>4406</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>5511.8</v>
+        <v>16923.6</v>
       </c>
       <c r="G39" t="n">
-        <v>5524</v>
+        <v>16923.6</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>5853.2</v>
+        <v>19159.2</v>
       </c>
       <c r="J39" t="n">
-        <v>5847.8</v>
+        <v>19159.2</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>6013</v>
+        <v>21845.4</v>
       </c>
       <c r="M39" t="n">
-        <v>6013</v>
+        <v>21845.4</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>33550</v>
+        <v>307000</v>
       </c>
       <c r="P39" t="n">
-        <v>33350</v>
+        <v>288000</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>006280</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>녹십자</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4406</v>
+        <v>88</v>
       </c>
       <c r="D40" t="n">
-        <v>4406</v>
+        <v>210</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>-58.1</v>
       </c>
       <c r="F40" t="n">
-        <v>16923.6</v>
+        <v>737.8</v>
       </c>
       <c r="G40" t="n">
-        <v>16923.6</v>
+        <v>747.3</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="I40" t="n">
-        <v>19159.2</v>
+        <v>973.6</v>
       </c>
       <c r="J40" t="n">
-        <v>19159.2</v>
+        <v>972.3</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L40" t="n">
-        <v>21845.4</v>
+        <v>1402.3</v>
       </c>
       <c r="M40" t="n">
-        <v>21845.4</v>
+        <v>1352.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
-        <v>268000</v>
+        <v>122700</v>
       </c>
       <c r="P40" t="n">
-        <v>288000</v>
+        <v>122800</v>
       </c>
       <c r="Q40" t="n">
-        <v>-6.9</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>006280</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>205</v>
+        <v>-356</v>
       </c>
       <c r="D41" t="n">
-        <v>210</v>
+        <v>-449</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4</v>
+        <v>20.7</v>
       </c>
       <c r="F41" t="n">
-        <v>741.5</v>
+        <v>509.1</v>
       </c>
       <c r="G41" t="n">
-        <v>747.3</v>
+        <v>217.5</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8</v>
+        <v>134.1</v>
       </c>
       <c r="I41" t="n">
-        <v>984.8</v>
+        <v>14952.3</v>
       </c>
       <c r="J41" t="n">
-        <v>972.3</v>
+        <v>14829.6</v>
       </c>
       <c r="K41" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="L41" t="n">
-        <v>1401.4</v>
+        <v>25566.4</v>
       </c>
       <c r="M41" t="n">
-        <v>1352.6</v>
+        <v>25291.6</v>
       </c>
       <c r="N41" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="O41" t="n">
-        <v>119700</v>
+        <v>432500</v>
       </c>
       <c r="P41" t="n">
-        <v>122800</v>
+        <v>434500</v>
       </c>
       <c r="Q41" t="n">
-        <v>-2.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-396</v>
+        <v>361</v>
       </c>
       <c r="D42" t="n">
-        <v>-449</v>
+        <v>675</v>
       </c>
       <c r="E42" t="n">
-        <v>11.8</v>
+        <v>-46.5</v>
       </c>
       <c r="F42" t="n">
-        <v>415</v>
+        <v>1925</v>
       </c>
       <c r="G42" t="n">
-        <v>217.5</v>
+        <v>2274.3</v>
       </c>
       <c r="H42" t="n">
-        <v>90.8</v>
+        <v>-15.4</v>
       </c>
       <c r="I42" t="n">
-        <v>14944.3</v>
+        <v>2254.8</v>
       </c>
       <c r="J42" t="n">
-        <v>14829.6</v>
+        <v>2417.5</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8</v>
+        <v>-6.7</v>
       </c>
       <c r="L42" t="n">
-        <v>25529.8</v>
+        <v>2472.6</v>
       </c>
       <c r="M42" t="n">
-        <v>25291.6</v>
+        <v>2694</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>400000</v>
+        <v>101300</v>
       </c>
       <c r="P42" t="n">
-        <v>434500</v>
+        <v>105400</v>
       </c>
       <c r="Q42" t="n">
-        <v>-7.9</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>006800</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>419</v>
+        <v>19098</v>
       </c>
       <c r="D43" t="n">
-        <v>675</v>
+        <v>19098</v>
       </c>
       <c r="E43" t="n">
-        <v>-37.9</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1977.2</v>
+        <v>42637.8</v>
       </c>
       <c r="G43" t="n">
-        <v>2274.3</v>
+        <v>42131.5</v>
       </c>
       <c r="H43" t="n">
-        <v>-13.1</v>
+        <v>1.2</v>
       </c>
       <c r="I43" t="n">
-        <v>2195.3</v>
+        <v>26349.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2417.5</v>
+        <v>27027.3</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.199999999999999</v>
+        <v>-2.5</v>
       </c>
       <c r="L43" t="n">
-        <v>2467.5</v>
+        <v>27155.9</v>
       </c>
       <c r="M43" t="n">
-        <v>2694</v>
+        <v>27637.9</v>
       </c>
       <c r="N43" t="n">
-        <v>-8.4</v>
+        <v>-1.7</v>
       </c>
       <c r="O43" t="n">
-        <v>96700</v>
+        <v>38050</v>
       </c>
       <c r="P43" t="n">
-        <v>105400</v>
+        <v>40050</v>
       </c>
       <c r="Q43" t="n">
-        <v>-8.300000000000001</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>006800</t>
+          <t>007070</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>GS리테일</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>19098</v>
+        <v>1013</v>
       </c>
       <c r="D44" t="n">
-        <v>19098</v>
+        <v>1022</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="F44" t="n">
-        <v>42131.5</v>
+        <v>3477.7</v>
       </c>
       <c r="G44" t="n">
-        <v>42131.5</v>
+        <v>3481.6</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I44" t="n">
-        <v>27027.3</v>
+        <v>3738.5</v>
       </c>
       <c r="J44" t="n">
-        <v>27027.3</v>
+        <v>3743.9</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L44" t="n">
-        <v>27637.9</v>
+        <v>3875.7</v>
       </c>
       <c r="M44" t="n">
-        <v>27637.9</v>
+        <v>3883</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O44" t="n">
-        <v>36700</v>
+        <v>25750</v>
       </c>
       <c r="P44" t="n">
-        <v>40050</v>
+        <v>26400</v>
       </c>
       <c r="Q44" t="n">
-        <v>-8.4</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>007070</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GS리테일</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1022</v>
+        <v>1610</v>
       </c>
       <c r="D45" t="n">
-        <v>1022</v>
+        <v>1461</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="F45" t="n">
-        <v>3481.6</v>
+        <v>6230</v>
       </c>
       <c r="G45" t="n">
-        <v>3481.6</v>
+        <v>5836.5</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I45" t="n">
-        <v>3743.2</v>
+        <v>6558</v>
       </c>
       <c r="J45" t="n">
-        <v>3743.9</v>
+        <v>6604.5</v>
       </c>
       <c r="K45" t="n">
-        <v>-0</v>
+        <v>-0.7</v>
       </c>
       <c r="L45" t="n">
-        <v>3883.9</v>
+        <v>6878</v>
       </c>
       <c r="M45" t="n">
-        <v>3883</v>
+        <v>7196.5</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="O45" t="n">
-        <v>25850</v>
+        <v>40400</v>
       </c>
       <c r="P45" t="n">
-        <v>26400</v>
+        <v>40800</v>
       </c>
       <c r="Q45" t="n">
-        <v>-2.1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>007660</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1461</v>
+        <v>751</v>
       </c>
       <c r="D46" t="n">
-        <v>1461</v>
+        <v>751</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>5836.5</v>
+        <v>3272.1</v>
       </c>
       <c r="G46" t="n">
-        <v>5836.5</v>
+        <v>3272.1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>6604.5</v>
+        <v>4603.5</v>
       </c>
       <c r="J46" t="n">
-        <v>6604.5</v>
+        <v>4603.5</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>7196.5</v>
+        <v>5890.1</v>
       </c>
       <c r="M46" t="n">
-        <v>7196.5</v>
+        <v>5890.1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>36750</v>
+        <v>92900</v>
       </c>
       <c r="P46" t="n">
-        <v>40800</v>
+        <v>92000</v>
       </c>
       <c r="Q46" t="n">
-        <v>-9.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>007660</t>
+          <t>008730</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>율촌화학</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>751</v>
+        <v>13</v>
       </c>
       <c r="D47" t="n">
-        <v>751</v>
+        <v>13</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>3272.1</v>
+        <v>131</v>
       </c>
       <c r="G47" t="n">
-        <v>3272.1</v>
+        <v>131</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>4603.5</v>
+        <v>454</v>
       </c>
       <c r="J47" t="n">
-        <v>4603.5</v>
+        <v>454</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
-      <c r="L47" t="n">
-        <v>5890.1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>5890.1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
       <c r="O47" t="n">
-        <v>86100</v>
+        <v>13150</v>
       </c>
       <c r="P47" t="n">
-        <v>92000</v>
+        <v>13480</v>
       </c>
       <c r="Q47" t="n">
-        <v>-6.4</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>008730</t>
+          <t>008770</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>율촌화학</t>
+          <t>호텔신라</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>544</v>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>531</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="F48" t="n">
-        <v>131</v>
+        <v>1833.6</v>
       </c>
       <c r="G48" t="n">
-        <v>131</v>
+        <v>1805.1</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I48" t="n">
-        <v>454</v>
+        <v>2305.4</v>
       </c>
       <c r="J48" t="n">
-        <v>454</v>
+        <v>2301.7</v>
       </c>
       <c r="K48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2678.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2678.5</v>
+      </c>
+      <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>12750</v>
+        <v>47400</v>
       </c>
       <c r="P48" t="n">
-        <v>13480</v>
+        <v>47800</v>
       </c>
       <c r="Q48" t="n">
-        <v>-5.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>008770</t>
+          <t>009150</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>호텔신라</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>544</v>
+        <v>4043</v>
       </c>
       <c r="D49" t="n">
-        <v>531</v>
+        <v>4043</v>
       </c>
       <c r="E49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1833.6</v>
+        <v>16599.1</v>
       </c>
       <c r="G49" t="n">
-        <v>1805.1</v>
+        <v>16599.1</v>
       </c>
       <c r="H49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>2305.4</v>
+        <v>31750.1</v>
       </c>
       <c r="J49" t="n">
-        <v>2301.7</v>
+        <v>31750.1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2678.5</v>
+        <v>50852.8</v>
       </c>
       <c r="M49" t="n">
-        <v>2678.5</v>
+        <v>50852.8</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>46150</v>
+        <v>1441000</v>
       </c>
       <c r="P49" t="n">
-        <v>47800</v>
+        <v>1277000</v>
       </c>
       <c r="Q49" t="n">
-        <v>-3.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>009150</t>
+          <t>009240</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>한샘</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4043</v>
+        <v>122</v>
       </c>
       <c r="D50" t="n">
-        <v>4043</v>
+        <v>122</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>16599.1</v>
+        <v>379.5</v>
       </c>
       <c r="G50" t="n">
-        <v>16599.1</v>
+        <v>379.5</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>31750.1</v>
+        <v>441.7</v>
       </c>
       <c r="J50" t="n">
-        <v>31750.1</v>
+        <v>441.7</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>50852.8</v>
+        <v>581.3</v>
       </c>
       <c r="M50" t="n">
-        <v>50852.8</v>
+        <v>581.3</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1276000</v>
+        <v>37400</v>
       </c>
       <c r="P50" t="n">
-        <v>1277000</v>
+        <v>35400</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>009240</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>한샘</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>379.5</v>
+        <v>19.3</v>
       </c>
       <c r="G51" t="n">
-        <v>379.5</v>
+        <v>16.6</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="I51" t="n">
-        <v>441.7</v>
+        <v>104</v>
       </c>
       <c r="J51" t="n">
-        <v>441.7</v>
+        <v>88.3</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="L51" t="n">
-        <v>581.3</v>
+        <v>264</v>
       </c>
       <c r="M51" t="n">
-        <v>581.3</v>
+        <v>229.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="O51" t="n">
-        <v>35600</v>
+        <v>49150</v>
       </c>
       <c r="P51" t="n">
-        <v>35400</v>
+        <v>52800</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.6</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>009540</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>HD한국조선해양</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>14693</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>14693</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>19.3</v>
+        <v>57969.2</v>
       </c>
       <c r="G52" t="n">
-        <v>16.6</v>
+        <v>57969.2</v>
       </c>
       <c r="H52" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>104</v>
+        <v>69012.2</v>
       </c>
       <c r="J52" t="n">
-        <v>88.3</v>
+        <v>69012.2</v>
       </c>
       <c r="K52" t="n">
-        <v>17.8</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>264</v>
+        <v>80641.10000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>229.2</v>
+        <v>80641.10000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>48150</v>
+        <v>369500</v>
       </c>
       <c r="P52" t="n">
-        <v>52800</v>
+        <v>354000</v>
       </c>
       <c r="Q52" t="n">
-        <v>-8.800000000000001</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>009540</t>
+          <t>009830</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HD한국조선해양</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>14693</v>
+        <v>1839</v>
       </c>
       <c r="D53" t="n">
-        <v>14693</v>
+        <v>1804</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F53" t="n">
-        <v>57969.2</v>
+        <v>7641.5</v>
       </c>
       <c r="G53" t="n">
-        <v>57969.2</v>
+        <v>7641.5</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>69012.2</v>
+        <v>12300.9</v>
       </c>
       <c r="J53" t="n">
-        <v>69012.2</v>
+        <v>12300.9</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>80641.10000000001</v>
+        <v>15192.5</v>
       </c>
       <c r="M53" t="n">
-        <v>80641.10000000001</v>
+        <v>15192.5</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>339000</v>
+        <v>28800</v>
       </c>
       <c r="P53" t="n">
-        <v>354000</v>
+        <v>27600</v>
       </c>
       <c r="Q53" t="n">
-        <v>-4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>010060</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>OCI홀딩스</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1804</v>
+        <v>1218</v>
       </c>
       <c r="D54" t="n">
-        <v>1804</v>
+        <v>1218</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>7641.5</v>
+        <v>3787.1</v>
       </c>
       <c r="G54" t="n">
-        <v>7641.5</v>
+        <v>3787.1</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>12300.9</v>
+        <v>5418.3</v>
       </c>
       <c r="J54" t="n">
-        <v>12300.9</v>
+        <v>5418.3</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>15192.5</v>
+        <v>6630.9</v>
       </c>
       <c r="M54" t="n">
-        <v>15192.5</v>
+        <v>6630.9</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>26200</v>
+        <v>207500</v>
       </c>
       <c r="P54" t="n">
-        <v>27600</v>
+        <v>194300</v>
       </c>
       <c r="Q54" t="n">
-        <v>-5.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>010060</t>
+          <t>010120</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OCI홀딩스</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1218</v>
+        <v>1640</v>
       </c>
       <c r="D55" t="n">
-        <v>1218</v>
+        <v>1607</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="F55" t="n">
-        <v>3787.1</v>
+        <v>6797.4</v>
       </c>
       <c r="G55" t="n">
-        <v>3787.1</v>
+        <v>6627.8</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I55" t="n">
-        <v>5418.3</v>
+        <v>9823.200000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>5418.3</v>
+        <v>9288.200000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L55" t="n">
-        <v>6630.9</v>
+        <v>12637.2</v>
       </c>
       <c r="M55" t="n">
-        <v>6630.9</v>
+        <v>12036.9</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>192500</v>
+        <v>207500</v>
       </c>
       <c r="P55" t="n">
-        <v>194300</v>
+        <v>190000</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>010120</t>
+          <t>010130</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LS ELECTRIC</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1612</v>
+        <v>5918</v>
       </c>
       <c r="D56" t="n">
-        <v>1607</v>
+        <v>5918</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>6645.8</v>
+        <v>23854.4</v>
       </c>
       <c r="G56" t="n">
-        <v>6627.8</v>
+        <v>23854.4</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>9313.5</v>
+        <v>21792.2</v>
       </c>
       <c r="J56" t="n">
-        <v>9288.200000000001</v>
+        <v>21792.2</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>12075.4</v>
+        <v>23102.8</v>
       </c>
       <c r="M56" t="n">
-        <v>12036.9</v>
+        <v>23102.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>183800</v>
+        <v>1025000</v>
       </c>
       <c r="P56" t="n">
-        <v>190000</v>
+        <v>1029000</v>
       </c>
       <c r="Q56" t="n">
-        <v>-3.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>010130</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>고려아연</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5918</v>
+        <v>3744</v>
       </c>
       <c r="D57" t="n">
-        <v>5918</v>
+        <v>3744</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>23854.4</v>
+        <v>14649.6</v>
       </c>
       <c r="G57" t="n">
-        <v>23854.4</v>
+        <v>14649.6</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>21792.2</v>
+        <v>20222.6</v>
       </c>
       <c r="J57" t="n">
-        <v>21792.2</v>
+        <v>20222.6</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>23102.8</v>
+        <v>23690.3</v>
       </c>
       <c r="M57" t="n">
-        <v>23102.8</v>
+        <v>23690.3</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>952000</v>
+        <v>22450</v>
       </c>
       <c r="P57" t="n">
-        <v>1029000</v>
+        <v>22300</v>
       </c>
       <c r="Q57" t="n">
-        <v>-7.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3744</v>
+        <v>9551</v>
       </c>
       <c r="D58" t="n">
-        <v>3744</v>
+        <v>9592</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F58" t="n">
-        <v>14649.6</v>
+        <v>35904.7</v>
       </c>
       <c r="G58" t="n">
-        <v>14649.6</v>
+        <v>35895.3</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>20222.6</v>
+        <v>27021.4</v>
       </c>
       <c r="J58" t="n">
-        <v>20222.6</v>
+        <v>26366.1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L58" t="n">
-        <v>23690.3</v>
+        <v>24226.4</v>
       </c>
       <c r="M58" t="n">
-        <v>23690.3</v>
+        <v>23703.9</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O58" t="n">
-        <v>20950</v>
+        <v>146900</v>
       </c>
       <c r="P58" t="n">
-        <v>22300</v>
+        <v>144900</v>
       </c>
       <c r="Q58" t="n">
-        <v>-6.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>011070</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LG이노텍</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9551</v>
+        <v>1823</v>
       </c>
       <c r="D59" t="n">
-        <v>9592</v>
+        <v>1823</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>35904.7</v>
+        <v>11828.4</v>
       </c>
       <c r="G59" t="n">
-        <v>35895.3</v>
+        <v>11828.4</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>27021.4</v>
+        <v>13870.9</v>
       </c>
       <c r="J59" t="n">
-        <v>26366.1</v>
+        <v>13870.9</v>
       </c>
       <c r="K59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>24226.4</v>
+        <v>15782.4</v>
       </c>
       <c r="M59" t="n">
-        <v>23703.9</v>
+        <v>15782.4</v>
       </c>
       <c r="N59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>141850</v>
+        <v>676000</v>
       </c>
       <c r="P59" t="n">
-        <v>144900</v>
+        <v>668000</v>
       </c>
       <c r="Q59" t="n">
-        <v>-2.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>011070</t>
+          <t>011170</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LG이노텍</t>
+          <t>롯데케미칼</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1823</v>
+        <v>1356</v>
       </c>
       <c r="D60" t="n">
-        <v>1823</v>
+        <v>1380</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="F60" t="n">
-        <v>11828.4</v>
+        <v>1778.8</v>
       </c>
       <c r="G60" t="n">
-        <v>11828.4</v>
+        <v>1671</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I60" t="n">
-        <v>13870.9</v>
+        <v>2605.7</v>
       </c>
       <c r="J60" t="n">
-        <v>13870.9</v>
+        <v>2610.4</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L60" t="n">
-        <v>15782.4</v>
+        <v>4707.1</v>
       </c>
       <c r="M60" t="n">
-        <v>15782.4</v>
+        <v>4783.5</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="O60" t="n">
-        <v>606000</v>
+        <v>61600</v>
       </c>
       <c r="P60" t="n">
-        <v>668000</v>
+        <v>61000</v>
       </c>
       <c r="Q60" t="n">
-        <v>-9.300000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>011170</t>
+          <t>011200</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>롯데케미칼</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1356</v>
+        <v>3692</v>
       </c>
       <c r="D61" t="n">
-        <v>1380</v>
+        <v>3463</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.7</v>
+        <v>6.6</v>
       </c>
       <c r="F61" t="n">
-        <v>1778.8</v>
+        <v>13260.6</v>
       </c>
       <c r="G61" t="n">
-        <v>1671</v>
+        <v>12211.1</v>
       </c>
       <c r="H61" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="I61" t="n">
-        <v>2605.7</v>
+        <v>9400.200000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>2610.4</v>
+        <v>8944.6</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.2</v>
+        <v>5.1</v>
       </c>
       <c r="L61" t="n">
-        <v>4707.1</v>
+        <v>9351.4</v>
       </c>
       <c r="M61" t="n">
-        <v>4783.5</v>
+        <v>9046.9</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.6</v>
+        <v>3.4</v>
       </c>
       <c r="O61" t="n">
-        <v>56600</v>
+        <v>20900</v>
       </c>
       <c r="P61" t="n">
-        <v>61000</v>
+        <v>20050</v>
       </c>
       <c r="Q61" t="n">
-        <v>-7.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>011200</t>
+          <t>011210</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>현대위아</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3463</v>
+        <v>530</v>
       </c>
       <c r="D62" t="n">
-        <v>3463</v>
+        <v>530</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>12211.1</v>
+        <v>2256.9</v>
       </c>
       <c r="G62" t="n">
-        <v>12211.1</v>
+        <v>2256.9</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>8944.6</v>
+        <v>2802.8</v>
       </c>
       <c r="J62" t="n">
-        <v>8944.6</v>
+        <v>2802.8</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>9046.9</v>
+        <v>3111.2</v>
       </c>
       <c r="M62" t="n">
-        <v>9046.9</v>
+        <v>3111.2</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>20350</v>
+        <v>59600</v>
       </c>
       <c r="P62" t="n">
-        <v>20050</v>
+        <v>57600</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>011210</t>
+          <t>011780</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>현대위아</t>
+          <t>금호석유화학</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>530</v>
+        <v>1470</v>
       </c>
       <c r="D63" t="n">
-        <v>530</v>
+        <v>1437</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="F63" t="n">
-        <v>2256.9</v>
+        <v>4006</v>
       </c>
       <c r="G63" t="n">
-        <v>2256.9</v>
+        <v>3948.2</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I63" t="n">
-        <v>2802.8</v>
+        <v>4560</v>
       </c>
       <c r="J63" t="n">
-        <v>2802.8</v>
+        <v>4448.1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L63" t="n">
-        <v>3111.2</v>
+        <v>4858.5</v>
       </c>
       <c r="M63" t="n">
-        <v>3111.2</v>
+        <v>4909.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O63" t="n">
-        <v>55600</v>
+        <v>123800</v>
       </c>
       <c r="P63" t="n">
-        <v>57600</v>
+        <v>123500</v>
       </c>
       <c r="Q63" t="n">
-        <v>-3.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>011780</t>
+          <t>011790</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>금호석유화학</t>
+          <t>SKC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1470</v>
+        <v>-187</v>
       </c>
       <c r="D64" t="n">
-        <v>1437</v>
+        <v>-187</v>
       </c>
       <c r="E64" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>4006</v>
+        <v>-604.5</v>
       </c>
       <c r="G64" t="n">
-        <v>3948.2</v>
+        <v>-604.5</v>
       </c>
       <c r="H64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>4560</v>
+        <v>844.5</v>
       </c>
       <c r="J64" t="n">
-        <v>4448.1</v>
+        <v>844.5</v>
       </c>
       <c r="K64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>4858.5</v>
+        <v>2398.8</v>
       </c>
       <c r="M64" t="n">
-        <v>4909.2</v>
+        <v>2398.8</v>
       </c>
       <c r="N64" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>116700</v>
+        <v>84500</v>
       </c>
       <c r="P64" t="n">
-        <v>123500</v>
+        <v>85200</v>
       </c>
       <c r="Q64" t="n">
-        <v>-5.5</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>011790</t>
+          <t>012330</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SKC</t>
+          <t>현대모비스</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-187</v>
+        <v>9075</v>
       </c>
       <c r="D65" t="n">
-        <v>-187</v>
+        <v>9075</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>-604.5</v>
+        <v>37334.3</v>
       </c>
       <c r="G65" t="n">
-        <v>-604.5</v>
+        <v>37334.3</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>844.5</v>
+        <v>42519.2</v>
       </c>
       <c r="J65" t="n">
-        <v>844.5</v>
+        <v>42519.2</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2398.8</v>
+        <v>46485</v>
       </c>
       <c r="M65" t="n">
-        <v>2398.8</v>
+        <v>46485</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>78100</v>
+        <v>521000</v>
       </c>
       <c r="P65" t="n">
-        <v>85200</v>
+        <v>482000</v>
       </c>
       <c r="Q65" t="n">
-        <v>-8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>012330</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>9075</v>
+        <v>9970</v>
       </c>
       <c r="D66" t="n">
-        <v>9075</v>
+        <v>9962</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F66" t="n">
-        <v>37334.3</v>
+        <v>42852.8</v>
       </c>
       <c r="G66" t="n">
-        <v>37334.3</v>
+        <v>42796.2</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I66" t="n">
-        <v>42519.2</v>
+        <v>54780.9</v>
       </c>
       <c r="J66" t="n">
-        <v>42519.2</v>
+        <v>54920.9</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="L66" t="n">
-        <v>46485</v>
+        <v>61398</v>
       </c>
       <c r="M66" t="n">
-        <v>46485</v>
+        <v>61626.3</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O66" t="n">
-        <v>475500</v>
+        <v>920000</v>
       </c>
       <c r="P66" t="n">
-        <v>482000</v>
+        <v>943000</v>
       </c>
       <c r="Q66" t="n">
-        <v>-1.3</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>012750</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>에스원</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9970</v>
+        <v>563</v>
       </c>
       <c r="D67" t="n">
-        <v>9962</v>
+        <v>563</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>42852.8</v>
+        <v>1961</v>
       </c>
       <c r="G67" t="n">
-        <v>42796.2</v>
+        <v>1961</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>54780.9</v>
+        <v>2539.8</v>
       </c>
       <c r="J67" t="n">
-        <v>54920.9</v>
+        <v>2539.8</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>61398</v>
+        <v>2681</v>
       </c>
       <c r="M67" t="n">
-        <v>61626.3</v>
+        <v>2681</v>
       </c>
       <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>71800</v>
+      </c>
+      <c r="P67" t="n">
+        <v>72100</v>
+      </c>
+      <c r="Q67" t="n">
         <v>-0.4</v>
-      </c>
-      <c r="O67" t="n">
-        <v>900000</v>
-      </c>
-      <c r="P67" t="n">
-        <v>943000</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>-4.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>012750</t>
+          <t>014680</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에스원</t>
+          <t>한솔케미칼</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>563</v>
+        <v>499</v>
       </c>
       <c r="D68" t="n">
-        <v>563</v>
+        <v>507</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="F68" t="n">
-        <v>1961</v>
+        <v>1879.4</v>
       </c>
       <c r="G68" t="n">
-        <v>1961</v>
+        <v>1886.8</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="I68" t="n">
-        <v>2539.8</v>
+        <v>2389</v>
       </c>
       <c r="J68" t="n">
-        <v>2539.8</v>
+        <v>2361</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L68" t="n">
-        <v>2681</v>
+        <v>3090.2</v>
       </c>
       <c r="M68" t="n">
-        <v>2681</v>
+        <v>2994.7</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O68" t="n">
-        <v>71000</v>
+        <v>232500</v>
       </c>
       <c r="P68" t="n">
-        <v>72100</v>
+        <v>244500</v>
       </c>
       <c r="Q68" t="n">
-        <v>-1.5</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>014680</t>
+          <t>015760</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>507</v>
+        <v>19612</v>
       </c>
       <c r="D69" t="n">
-        <v>507</v>
+        <v>20041</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="F69" t="n">
-        <v>1886.8</v>
+        <v>98395.8</v>
       </c>
       <c r="G69" t="n">
-        <v>1886.8</v>
+        <v>100192.7</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="I69" t="n">
-        <v>2361</v>
+        <v>140220.6</v>
       </c>
       <c r="J69" t="n">
-        <v>2361</v>
+        <v>139318.5</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L69" t="n">
-        <v>2994.7</v>
+        <v>152635.4</v>
       </c>
       <c r="M69" t="n">
-        <v>2994.7</v>
+        <v>152635.4</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>230000</v>
+        <v>35100</v>
       </c>
       <c r="P69" t="n">
-        <v>244500</v>
+        <v>34050</v>
       </c>
       <c r="Q69" t="n">
-        <v>-5.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>015760</t>
+          <t>016360</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한국전력</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>20041</v>
+        <v>6617</v>
       </c>
       <c r="D70" t="n">
-        <v>20041</v>
+        <v>6617</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>100192.7</v>
+        <v>23119.8</v>
       </c>
       <c r="G70" t="n">
-        <v>100192.7</v>
+        <v>23027.4</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I70" t="n">
-        <v>139318.5</v>
+        <v>21245.5</v>
       </c>
       <c r="J70" t="n">
-        <v>139318.5</v>
+        <v>21231.4</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L70" t="n">
-        <v>152635.4</v>
+        <v>21146.3</v>
       </c>
       <c r="M70" t="n">
-        <v>152635.4</v>
+        <v>21175.6</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O70" t="n">
-        <v>33650</v>
+        <v>104200</v>
       </c>
       <c r="P70" t="n">
-        <v>34050</v>
+        <v>107700</v>
       </c>
       <c r="Q70" t="n">
-        <v>-1.2</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>016360</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6617</v>
+        <v>5470</v>
       </c>
       <c r="D71" t="n">
-        <v>6617</v>
+        <v>5446</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F71" t="n">
-        <v>23027.4</v>
+        <v>19415.2</v>
       </c>
       <c r="G71" t="n">
-        <v>23027.4</v>
+        <v>19444.4</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="I71" t="n">
-        <v>21231.4</v>
+        <v>20700.4</v>
       </c>
       <c r="J71" t="n">
-        <v>21231.4</v>
+        <v>20548.8</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L71" t="n">
-        <v>21175.6</v>
+        <v>21814.2</v>
       </c>
       <c r="M71" t="n">
-        <v>21175.6</v>
+        <v>21669.4</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O71" t="n">
-        <v>102600</v>
+        <v>96500</v>
       </c>
       <c r="P71" t="n">
-        <v>107700</v>
+        <v>89700</v>
       </c>
       <c r="Q71" t="n">
-        <v>-4.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>017800</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>현대엘리베이터</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5446</v>
-      </c>
-      <c r="D72" t="n">
-        <v>5446</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="F72" t="n">
-        <v>19444.4</v>
-      </c>
-      <c r="G72" t="n">
-        <v>19444.4</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="I72" t="n">
-        <v>20548.8</v>
-      </c>
-      <c r="J72" t="n">
-        <v>20548.8</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+        <v>2190</v>
       </c>
       <c r="L72" t="n">
-        <v>21669.4</v>
-      </c>
-      <c r="M72" t="n">
-        <v>21669.4</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="O72" t="n">
-        <v>84300</v>
+        <v>69700</v>
       </c>
       <c r="P72" t="n">
-        <v>89700</v>
+        <v>68900</v>
       </c>
       <c r="Q72" t="n">
-        <v>-6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="73">
@@ -4545,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>21800</v>
+        <v>23200</v>
       </c>
       <c r="P73" t="n">
         <v>23450</v>
       </c>
       <c r="Q73" t="n">
-        <v>-7</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="74">
@@ -4602,13 +4578,13 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>188900</v>
+        <v>204000</v>
       </c>
       <c r="P74" t="n">
         <v>199300</v>
       </c>
       <c r="Q74" t="n">
-        <v>-5.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="75">
@@ -4659,13 +4635,13 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>3370</v>
+        <v>3720</v>
       </c>
       <c r="P75" t="n">
         <v>3490</v>
       </c>
       <c r="Q75" t="n">
-        <v>-3.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="76">
@@ -4716,13 +4692,13 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>94300</v>
+        <v>92000</v>
       </c>
       <c r="P76" t="n">
         <v>96700</v>
       </c>
       <c r="Q76" t="n">
-        <v>-2.5</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="77">
@@ -4773,13 +4749,13 @@
         <v>1.5</v>
       </c>
       <c r="O77" t="n">
-        <v>131100</v>
+        <v>124700</v>
       </c>
       <c r="P77" t="n">
         <v>140800</v>
       </c>
       <c r="Q77" t="n">
-        <v>-6.9</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="78">
@@ -4830,13 +4806,13 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>20800</v>
+        <v>21150</v>
       </c>
       <c r="P78" t="n">
         <v>21600</v>
       </c>
       <c r="Q78" t="n">
-        <v>-3.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="79">
@@ -4851,49 +4827,49 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="D79" t="n">
         <v>2188</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>8849.5</v>
+        <v>8821.6</v>
       </c>
       <c r="G79" t="n">
         <v>8845.299999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I79" t="n">
-        <v>10315.2</v>
+        <v>10256.4</v>
       </c>
       <c r="J79" t="n">
         <v>10313.1</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L79" t="n">
-        <v>11551.5</v>
+        <v>11353.1</v>
       </c>
       <c r="M79" t="n">
         <v>11551.5</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="O79" t="n">
-        <v>40650</v>
+        <v>43000</v>
       </c>
       <c r="P79" t="n">
         <v>40850</v>
       </c>
       <c r="Q79" t="n">
-        <v>-0.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="80">
@@ -4944,13 +4920,13 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>339000</v>
+        <v>361500</v>
       </c>
       <c r="P80" t="n">
         <v>346000</v>
       </c>
       <c r="Q80" t="n">
-        <v>-2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="81">
@@ -4965,49 +4941,49 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1544</v>
+        <v>1557</v>
       </c>
       <c r="D81" t="n">
         <v>1544</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F81" t="n">
-        <v>5923</v>
+        <v>5946.1</v>
       </c>
       <c r="G81" t="n">
         <v>5923</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>6114.9</v>
+        <v>6131.1</v>
       </c>
       <c r="J81" t="n">
         <v>6114.9</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L81" t="n">
-        <v>6369.4</v>
+        <v>6384.8</v>
       </c>
       <c r="M81" t="n">
         <v>6369.4</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O81" t="n">
-        <v>5040</v>
+        <v>5310</v>
       </c>
       <c r="P81" t="n">
         <v>5160</v>
       </c>
       <c r="Q81" t="n">
-        <v>-2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="82">
@@ -5058,13 +5034,13 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>48050</v>
+        <v>48350</v>
       </c>
       <c r="P82" t="n">
         <v>47050</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="83">
@@ -5079,31 +5055,31 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D83" t="n">
         <v>940</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F83" t="n">
-        <v>3333.2</v>
+        <v>3331.5</v>
       </c>
       <c r="G83" t="n">
         <v>3331.9</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I83" t="n">
-        <v>3626.4</v>
+        <v>3629.6</v>
       </c>
       <c r="J83" t="n">
         <v>3627.7</v>
       </c>
       <c r="K83" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="L83" t="n">
         <v>3679.2</v>
@@ -5115,13 +5091,13 @@
         <v>-0.2</v>
       </c>
       <c r="O83" t="n">
-        <v>18620</v>
+        <v>18840</v>
       </c>
       <c r="P83" t="n">
         <v>18610</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="84">
@@ -5136,34 +5112,34 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6037</v>
+        <v>6035</v>
       </c>
       <c r="D84" t="n">
         <v>6037</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F84" t="n">
-        <v>20554.3</v>
+        <v>20602.1</v>
       </c>
       <c r="G84" t="n">
         <v>20554.3</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I84" t="n">
-        <v>22489.1</v>
+        <v>22575.2</v>
       </c>
       <c r="J84" t="n">
         <v>22489.1</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L84" t="n">
-        <v>23864.3</v>
+        <v>23873.2</v>
       </c>
       <c r="M84" t="n">
         <v>23864.3</v>
@@ -5172,13 +5148,13 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>53500</v>
+        <v>53400</v>
       </c>
       <c r="P84" t="n">
         <v>52400</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="85">
@@ -5193,49 +5169,49 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3087</v>
+        <v>3103</v>
       </c>
       <c r="D85" t="n">
         <v>3087</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F85" t="n">
-        <v>11108.8</v>
+        <v>11131.6</v>
       </c>
       <c r="G85" t="n">
         <v>11108.8</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I85" t="n">
-        <v>11988.9</v>
+        <v>12037.3</v>
       </c>
       <c r="J85" t="n">
         <v>11988.9</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L85" t="n">
-        <v>12761.4</v>
+        <v>12907.9</v>
       </c>
       <c r="M85" t="n">
         <v>12761.4</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O85" t="n">
-        <v>14580</v>
+        <v>14830</v>
       </c>
       <c r="P85" t="n">
         <v>14620</v>
       </c>
       <c r="Q85" t="n">
-        <v>-0.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="86">
@@ -5286,13 +5262,13 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>307000</v>
+        <v>332500</v>
       </c>
       <c r="P86" t="n">
         <v>331000</v>
       </c>
       <c r="Q86" t="n">
-        <v>-7.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
@@ -5307,49 +5283,49 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3949</v>
+        <v>3967</v>
       </c>
       <c r="D87" t="n">
         <v>3937</v>
       </c>
       <c r="E87" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F87" t="n">
-        <v>15137</v>
+        <v>15141.4</v>
       </c>
       <c r="G87" t="n">
         <v>15140.1</v>
       </c>
       <c r="H87" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>16291.6</v>
+        <v>16278.4</v>
       </c>
       <c r="J87" t="n">
         <v>16276.8</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>17211.8</v>
+        <v>17201.8</v>
       </c>
       <c r="M87" t="n">
         <v>17211.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O87" t="n">
-        <v>180300</v>
+        <v>179100</v>
       </c>
       <c r="P87" t="n">
         <v>179900</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="88">
@@ -5400,13 +5376,13 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>65400</v>
+        <v>71400</v>
       </c>
       <c r="P88" t="n">
         <v>69700</v>
       </c>
       <c r="Q88" t="n">
-        <v>-6.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="89">
@@ -5457,13 +5433,13 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>9720</v>
+        <v>10370</v>
       </c>
       <c r="P89" t="n">
         <v>10410</v>
       </c>
       <c r="Q89" t="n">
-        <v>-6.6</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="90">
@@ -5487,40 +5463,40 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1773.4</v>
+        <v>1735.9</v>
       </c>
       <c r="G90" t="n">
         <v>1773.4</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="I90" t="n">
-        <v>2147.9</v>
+        <v>2120.8</v>
       </c>
       <c r="J90" t="n">
         <v>2147.9</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="L90" t="n">
-        <v>2443.3</v>
+        <v>2430.6</v>
       </c>
       <c r="M90" t="n">
         <v>2443.3</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O90" t="n">
-        <v>9610</v>
+        <v>9960</v>
       </c>
       <c r="P90" t="n">
         <v>10190</v>
       </c>
       <c r="Q90" t="n">
-        <v>-5.7</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="91">
@@ -5571,13 +5547,13 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>583000</v>
+        <v>662000</v>
       </c>
       <c r="P91" t="n">
         <v>580000</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.5</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="92">
@@ -5628,13 +5604,13 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>14290</v>
+        <v>14430</v>
       </c>
       <c r="P92" t="n">
         <v>14410</v>
       </c>
       <c r="Q92" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="93">
@@ -5685,13 +5661,13 @@
         <v>0.5</v>
       </c>
       <c r="O93" t="n">
-        <v>192400</v>
+        <v>212500</v>
       </c>
       <c r="P93" t="n">
         <v>190000</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="94">
@@ -5742,13 +5718,13 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>35425</v>
+        <v>36450</v>
       </c>
       <c r="P94" t="n">
         <v>35900</v>
       </c>
       <c r="Q94" t="n">
-        <v>-1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="95">
@@ -5799,13 +5775,13 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>32200</v>
+        <v>33650</v>
       </c>
       <c r="P95" t="n">
         <v>32400</v>
       </c>
       <c r="Q95" t="n">
-        <v>-0.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="96">
@@ -5820,49 +5796,49 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1294</v>
+        <v>1319</v>
       </c>
       <c r="D96" t="n">
         <v>1294</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="F96" t="n">
-        <v>5051.7</v>
+        <v>5000.1</v>
       </c>
       <c r="G96" t="n">
         <v>5051.7</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I96" t="n">
-        <v>5877.6</v>
+        <v>5900.9</v>
       </c>
       <c r="J96" t="n">
         <v>5877.6</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L96" t="n">
-        <v>5885.7</v>
+        <v>5846.8</v>
       </c>
       <c r="M96" t="n">
         <v>5885.7</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="O96" t="n">
-        <v>210000</v>
+        <v>222500</v>
       </c>
       <c r="P96" t="n">
         <v>223000</v>
       </c>
       <c r="Q96" t="n">
-        <v>-5.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="97">
@@ -5913,13 +5889,13 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>307000</v>
+        <v>312000</v>
       </c>
       <c r="P97" t="n">
         <v>322000</v>
       </c>
       <c r="Q97" t="n">
-        <v>-4.7</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="98">
@@ -5970,13 +5946,13 @@
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>81500</v>
+        <v>85500</v>
       </c>
       <c r="P98" t="n">
         <v>86700</v>
       </c>
       <c r="Q98" t="n">
-        <v>-6</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="99">
@@ -6027,13 +6003,13 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>222750</v>
+        <v>212500</v>
       </c>
       <c r="P99" t="n">
         <v>242500</v>
       </c>
       <c r="Q99" t="n">
-        <v>-8.1</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="100">
@@ -6084,13 +6060,13 @@
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>14380</v>
+        <v>15580</v>
       </c>
       <c r="P100" t="n">
         <v>15150</v>
       </c>
       <c r="Q100" t="n">
-        <v>-5.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="101">
@@ -6141,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>51100</v>
+        <v>53800</v>
       </c>
       <c r="P101" t="n">
         <v>50900</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="102">
@@ -6162,49 +6138,49 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>931</v>
+        <v>901</v>
       </c>
       <c r="D102" t="n">
         <v>931</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="F102" t="n">
-        <v>4546.9</v>
+        <v>4498.1</v>
       </c>
       <c r="G102" t="n">
         <v>4546.9</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>6570.8</v>
+        <v>6528.2</v>
       </c>
       <c r="J102" t="n">
         <v>6570.8</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L102" t="n">
-        <v>8017.4</v>
+        <v>8004.2</v>
       </c>
       <c r="M102" t="n">
         <v>8017.4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O102" t="n">
-        <v>146500</v>
+        <v>156300</v>
       </c>
       <c r="P102" t="n">
         <v>149200</v>
       </c>
       <c r="Q102" t="n">
-        <v>-1.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="103">
@@ -6255,13 +6231,13 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>42650</v>
+        <v>45550</v>
       </c>
       <c r="P103" t="n">
         <v>43550</v>
       </c>
       <c r="Q103" t="n">
-        <v>-2.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="104">
@@ -6312,13 +6288,13 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>247000</v>
+        <v>246000</v>
       </c>
       <c r="P104" t="n">
         <v>246500</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="105">
@@ -6369,13 +6345,13 @@
         <v>-2.3</v>
       </c>
       <c r="O105" t="n">
-        <v>250500</v>
+        <v>262000</v>
       </c>
       <c r="P105" t="n">
         <v>260500</v>
       </c>
       <c r="Q105" t="n">
-        <v>-3.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="106">
@@ -6426,13 +6402,13 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>87800</v>
+        <v>94200</v>
       </c>
       <c r="P106" t="n">
         <v>92700</v>
       </c>
       <c r="Q106" t="n">
-        <v>-5.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="107">
@@ -6540,13 +6516,13 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>160500</v>
+        <v>174800</v>
       </c>
       <c r="P108" t="n">
         <v>170000</v>
       </c>
       <c r="Q108" t="n">
-        <v>-5.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="109">
@@ -6597,13 +6573,13 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>151800</v>
+        <v>162200</v>
       </c>
       <c r="P109" t="n">
         <v>159000</v>
       </c>
       <c r="Q109" t="n">
-        <v>-4.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -6618,49 +6594,49 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1387</v>
+        <v>1377</v>
       </c>
       <c r="D110" t="n">
         <v>1409</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.6</v>
+        <v>-2.3</v>
       </c>
       <c r="F110" t="n">
-        <v>6058.6</v>
+        <v>6025.6</v>
       </c>
       <c r="G110" t="n">
         <v>6080.8</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="I110" t="n">
-        <v>6916.7</v>
+        <v>6868.2</v>
       </c>
       <c r="J110" t="n">
         <v>6954.7</v>
       </c>
       <c r="K110" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="L110" t="n">
-        <v>7816.8</v>
+        <v>7723.9</v>
       </c>
       <c r="M110" t="n">
         <v>7875.6</v>
       </c>
       <c r="N110" t="n">
-        <v>-0.7</v>
+        <v>-1.9</v>
       </c>
       <c r="O110" t="n">
-        <v>62050</v>
+        <v>68000</v>
       </c>
       <c r="P110" t="n">
         <v>65000</v>
       </c>
       <c r="Q110" t="n">
-        <v>-4.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="111">
@@ -6711,13 +6687,13 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>169400</v>
+        <v>183900</v>
       </c>
       <c r="P111" t="n">
         <v>179000</v>
       </c>
       <c r="Q111" t="n">
-        <v>-5.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="112">
@@ -6768,13 +6744,13 @@
         <v>-0.2</v>
       </c>
       <c r="O112" t="n">
-        <v>81800</v>
+        <v>85800</v>
       </c>
       <c r="P112" t="n">
         <v>92000</v>
       </c>
       <c r="Q112" t="n">
-        <v>-11.1</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="113">
@@ -6798,40 +6774,40 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>17804.2</v>
+        <v>17841.8</v>
       </c>
       <c r="G113" t="n">
         <v>17804.2</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I113" t="n">
-        <v>21031.7</v>
+        <v>21006.4</v>
       </c>
       <c r="J113" t="n">
         <v>21031.7</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L113" t="n">
-        <v>24695.9</v>
+        <v>24598.1</v>
       </c>
       <c r="M113" t="n">
         <v>24695.9</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O113" t="n">
-        <v>174000</v>
+        <v>173200</v>
       </c>
       <c r="P113" t="n">
         <v>175800</v>
       </c>
       <c r="Q113" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="114">
@@ -6882,13 +6858,13 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>15160</v>
+        <v>15180</v>
       </c>
       <c r="P114" t="n">
         <v>15450</v>
       </c>
       <c r="Q114" t="n">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="115">
@@ -6903,49 +6879,49 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>594</v>
+        <v>631</v>
       </c>
       <c r="D115" t="n">
         <v>594</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="F115" t="n">
-        <v>2142.6</v>
+        <v>2202</v>
       </c>
       <c r="G115" t="n">
         <v>2142.6</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I115" t="n">
-        <v>2281</v>
+        <v>2377</v>
       </c>
       <c r="J115" t="n">
         <v>2281</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L115" t="n">
-        <v>3611.6</v>
+        <v>3578.8</v>
       </c>
       <c r="M115" t="n">
         <v>3611.6</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="O115" t="n">
-        <v>121000</v>
+        <v>122300</v>
       </c>
       <c r="P115" t="n">
         <v>121900</v>
       </c>
       <c r="Q115" t="n">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="116">
@@ -6960,16 +6936,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="D116" t="n">
         <v>853</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F116" t="n">
-        <v>4364.8</v>
+        <v>4362</v>
       </c>
       <c r="G116" t="n">
         <v>4359.6</v>
@@ -6978,22 +6954,22 @@
         <v>0.1</v>
       </c>
       <c r="I116" t="n">
-        <v>5274.4</v>
+        <v>5260.5</v>
       </c>
       <c r="J116" t="n">
         <v>5281.8</v>
       </c>
       <c r="K116" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L116" t="n">
-        <v>5667</v>
+        <v>5636</v>
       </c>
       <c r="M116" t="n">
         <v>5667</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O116" t="n">
         <v>137600</v>
@@ -7053,13 +7029,13 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>218500</v>
+        <v>219500</v>
       </c>
       <c r="P117" t="n">
         <v>229000</v>
       </c>
       <c r="Q117" t="n">
-        <v>-4.6</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="118">
@@ -7110,13 +7086,13 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>64000</v>
+        <v>64500</v>
       </c>
       <c r="P118" t="n">
         <v>64800</v>
       </c>
       <c r="Q118" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="119">
@@ -7140,40 +7116,40 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>1525.8</v>
+        <v>1526.7</v>
       </c>
       <c r="G119" t="n">
         <v>1525.8</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I119" t="n">
-        <v>2052.2</v>
+        <v>2054.3</v>
       </c>
       <c r="J119" t="n">
         <v>2052.2</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L119" t="n">
-        <v>2493.5</v>
+        <v>2545</v>
       </c>
       <c r="M119" t="n">
         <v>2493.5</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O119" t="n">
-        <v>54300</v>
+        <v>65500</v>
       </c>
       <c r="P119" t="n">
         <v>57600</v>
       </c>
       <c r="Q119" t="n">
-        <v>-5.7</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="120">
@@ -7224,13 +7200,13 @@
         <v>2.4</v>
       </c>
       <c r="O120" t="n">
-        <v>6060</v>
+        <v>6240</v>
       </c>
       <c r="P120" t="n">
         <v>5850</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="121">
@@ -7281,13 +7257,13 @@
         <v>4.2</v>
       </c>
       <c r="O121" t="n">
-        <v>82800</v>
+        <v>89600</v>
       </c>
       <c r="P121" t="n">
         <v>82800</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7302,49 +7278,49 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="D122" t="n">
         <v>1085</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F122" t="n">
-        <v>4559.3</v>
+        <v>4575.6</v>
       </c>
       <c r="G122" t="n">
         <v>4545.4</v>
       </c>
       <c r="H122" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I122" t="n">
-        <v>6306.6</v>
+        <v>6266.7</v>
       </c>
       <c r="J122" t="n">
         <v>6272.3</v>
       </c>
       <c r="K122" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="L122" t="n">
-        <v>8190.3</v>
+        <v>8243.799999999999</v>
       </c>
       <c r="M122" t="n">
         <v>8198.4</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.1</v>
+        <v>0.6</v>
       </c>
       <c r="O122" t="n">
-        <v>676000</v>
+        <v>714000</v>
       </c>
       <c r="P122" t="n">
         <v>749000</v>
       </c>
       <c r="Q122" t="n">
-        <v>-9.699999999999999</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="123">
@@ -7359,31 +7335,31 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2129</v>
+        <v>2136</v>
       </c>
       <c r="D123" t="n">
         <v>2129</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F123" t="n">
-        <v>5642.7</v>
+        <v>5648.2</v>
       </c>
       <c r="G123" t="n">
         <v>5642.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I123" t="n">
-        <v>6011.4</v>
+        <v>6023.7</v>
       </c>
       <c r="J123" t="n">
         <v>6011.4</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L123" t="n">
         <v>6240.6</v>
@@ -7395,13 +7371,13 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>46250</v>
+        <v>46000</v>
       </c>
       <c r="P123" t="n">
         <v>46950</v>
       </c>
       <c r="Q123" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="124">
@@ -7416,49 +7392,49 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="D124" t="n">
         <v>580</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="F124" t="n">
-        <v>2416.7</v>
+        <v>2384.3</v>
       </c>
       <c r="G124" t="n">
         <v>2416.7</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="I124" t="n">
-        <v>3854</v>
+        <v>3696.7</v>
       </c>
       <c r="J124" t="n">
         <v>3854</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>-4.1</v>
       </c>
       <c r="L124" t="n">
-        <v>4707.3</v>
+        <v>4688.5</v>
       </c>
       <c r="M124" t="n">
         <v>4707.3</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O124" t="n">
-        <v>43500</v>
+        <v>48350</v>
       </c>
       <c r="P124" t="n">
         <v>46900</v>
       </c>
       <c r="Q124" t="n">
-        <v>-7.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="125">
@@ -7473,49 +7449,49 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5133</v>
+        <v>5079</v>
       </c>
       <c r="D125" t="n">
         <v>5133</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="F125" t="n">
-        <v>21731.9</v>
+        <v>21713.1</v>
       </c>
       <c r="G125" t="n">
         <v>21731.9</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I125" t="n">
-        <v>23370.2</v>
+        <v>23422.5</v>
       </c>
       <c r="J125" t="n">
         <v>23370.2</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L125" t="n">
-        <v>24535.4</v>
+        <v>24596.7</v>
       </c>
       <c r="M125" t="n">
         <v>24535.4</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O125" t="n">
-        <v>190900</v>
+        <v>204500</v>
       </c>
       <c r="P125" t="n">
         <v>188600</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="126">
@@ -7566,13 +7542,13 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>133100</v>
+        <v>132500</v>
       </c>
       <c r="P126" t="n">
         <v>136800</v>
       </c>
       <c r="Q126" t="n">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="127">
@@ -7614,13 +7590,13 @@
         <v>4.1</v>
       </c>
       <c r="O127" t="n">
-        <v>4350</v>
+        <v>4580</v>
       </c>
       <c r="P127" t="n">
         <v>4540</v>
       </c>
       <c r="Q127" t="n">
-        <v>-4.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="128">
@@ -7671,13 +7647,13 @@
         <v>0.1</v>
       </c>
       <c r="O128" t="n">
-        <v>121100</v>
+        <v>117300</v>
       </c>
       <c r="P128" t="n">
         <v>124400</v>
       </c>
       <c r="Q128" t="n">
-        <v>-2.7</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="129">
@@ -7701,13 +7677,13 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>10120</v>
+        <v>11170</v>
       </c>
       <c r="P129" t="n">
         <v>11690</v>
       </c>
       <c r="Q129" t="n">
-        <v>-13.4</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="130">
@@ -7758,13 +7734,13 @@
         <v>4.5</v>
       </c>
       <c r="O130" t="n">
-        <v>114200</v>
+        <v>125900</v>
       </c>
       <c r="P130" t="n">
         <v>121400</v>
       </c>
       <c r="Q130" t="n">
-        <v>-5.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="131">
@@ -7779,49 +7755,49 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2769</v>
+        <v>2751</v>
       </c>
       <c r="D131" t="n">
         <v>2777</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="F131" t="n">
-        <v>12835.6</v>
+        <v>12823.8</v>
       </c>
       <c r="G131" t="n">
         <v>12832.5</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I131" t="n">
-        <v>14512.8</v>
+        <v>14428.2</v>
       </c>
       <c r="J131" t="n">
         <v>14554.2</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="L131" t="n">
-        <v>15986.6</v>
+        <v>15800.5</v>
       </c>
       <c r="M131" t="n">
         <v>16091</v>
       </c>
       <c r="N131" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="O131" t="n">
-        <v>188000</v>
+        <v>188100</v>
       </c>
       <c r="P131" t="n">
         <v>184800</v>
       </c>
       <c r="Q131" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="132">
@@ -7836,31 +7812,31 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="D132" t="n">
         <v>819</v>
       </c>
       <c r="E132" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F132" t="n">
-        <v>3600.1</v>
+        <v>3594.6</v>
       </c>
       <c r="G132" t="n">
         <v>3630.2</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="I132" t="n">
-        <v>3530.3</v>
+        <v>3524.8</v>
       </c>
       <c r="J132" t="n">
         <v>3537.3</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="L132" t="n">
         <v>3913</v>
@@ -7872,13 +7848,13 @@
         <v>0.2</v>
       </c>
       <c r="O132" t="n">
-        <v>60200</v>
+        <v>62900</v>
       </c>
       <c r="P132" t="n">
         <v>62100</v>
       </c>
       <c r="Q132" t="n">
-        <v>-3.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="133">
@@ -7929,13 +7905,13 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>169900</v>
+        <v>178300</v>
       </c>
       <c r="P133" t="n">
         <v>181100</v>
       </c>
       <c r="Q133" t="n">
-        <v>-6.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="134">
@@ -7986,13 +7962,13 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>86900</v>
+        <v>87900</v>
       </c>
       <c r="P134" t="n">
         <v>86900</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="135">
@@ -8043,13 +8019,13 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>38850</v>
+        <v>42100</v>
       </c>
       <c r="P135" t="n">
         <v>39850</v>
       </c>
       <c r="Q135" t="n">
-        <v>-2.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="136">
@@ -8100,13 +8076,13 @@
         <v>3.4</v>
       </c>
       <c r="O136" t="n">
-        <v>50100</v>
+        <v>52700</v>
       </c>
       <c r="P136" t="n">
         <v>53600</v>
       </c>
       <c r="Q136" t="n">
-        <v>-6.5</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="137">
@@ -8121,49 +8097,49 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1056</v>
+        <v>1107</v>
       </c>
       <c r="D137" t="n">
         <v>1056</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="F137" t="n">
-        <v>3103.2</v>
+        <v>3142.8</v>
       </c>
       <c r="G137" t="n">
         <v>3103.2</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I137" t="n">
-        <v>3164.5</v>
+        <v>3140.6</v>
       </c>
       <c r="J137" t="n">
         <v>3164.5</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="L137" t="n">
-        <v>3447.3</v>
+        <v>3435.4</v>
       </c>
       <c r="M137" t="n">
         <v>3447.3</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="O137" t="n">
-        <v>373000</v>
+        <v>381000</v>
       </c>
       <c r="P137" t="n">
         <v>386000</v>
       </c>
       <c r="Q137" t="n">
-        <v>-3.4</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="138">
@@ -8178,49 +8154,49 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>9092</v>
+        <v>8696</v>
       </c>
       <c r="D138" t="n">
         <v>9092</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>-4.4</v>
       </c>
       <c r="F138" t="n">
-        <v>32058</v>
+        <v>31480.7</v>
       </c>
       <c r="G138" t="n">
         <v>32058</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="I138" t="n">
-        <v>34091.5</v>
+        <v>33722</v>
       </c>
       <c r="J138" t="n">
         <v>34091.5</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="L138" t="n">
-        <v>35486.3</v>
+        <v>35539.5</v>
       </c>
       <c r="M138" t="n">
         <v>35486.3</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O138" t="n">
-        <v>115800</v>
+        <v>117200</v>
       </c>
       <c r="P138" t="n">
         <v>118300</v>
       </c>
       <c r="Q138" t="n">
-        <v>-2.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="139">
@@ -8271,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>18350</v>
+        <v>17810</v>
       </c>
       <c r="P139" t="n">
         <v>18330</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.1</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="140">
@@ -8328,13 +8304,13 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>18180</v>
+        <v>17880</v>
       </c>
       <c r="P140" t="n">
         <v>18410</v>
       </c>
       <c r="Q140" t="n">
-        <v>-1.2</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="141">
@@ -8385,13 +8361,13 @@
         <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>81300</v>
+        <v>84300</v>
       </c>
       <c r="P141" t="n">
         <v>79700</v>
       </c>
       <c r="Q141" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="142">
@@ -8442,13 +8418,13 @@
         <v>0.7</v>
       </c>
       <c r="O142" t="n">
-        <v>72800</v>
+        <v>76800</v>
       </c>
       <c r="P142" t="n">
         <v>73600</v>
       </c>
       <c r="Q142" t="n">
-        <v>-1.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="143">
@@ -8499,13 +8475,13 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>101500</v>
+        <v>102100</v>
       </c>
       <c r="P143" t="n">
         <v>107600</v>
       </c>
       <c r="Q143" t="n">
-        <v>-5.7</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="144">
@@ -8556,13 +8532,13 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>26350</v>
+        <v>26300</v>
       </c>
       <c r="P144" t="n">
         <v>27400</v>
       </c>
       <c r="Q144" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="145">
@@ -8586,40 +8562,40 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>785.8</v>
+        <v>787.1</v>
       </c>
       <c r="G145" t="n">
         <v>785.8</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I145" t="n">
-        <v>901.4</v>
+        <v>900.7</v>
       </c>
       <c r="J145" t="n">
         <v>901.4</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L145" t="n">
-        <v>984.8</v>
+        <v>1019</v>
       </c>
       <c r="M145" t="n">
         <v>984.8</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O145" t="n">
-        <v>66000</v>
+        <v>67100</v>
       </c>
       <c r="P145" t="n">
         <v>68300</v>
       </c>
       <c r="Q145" t="n">
-        <v>-3.4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="146">
@@ -8634,16 +8610,16 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D146" t="n">
         <v>698</v>
       </c>
       <c r="E146" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F146" t="n">
-        <v>2856.2</v>
+        <v>2857.4</v>
       </c>
       <c r="G146" t="n">
         <v>2839.1</v>
@@ -8652,7 +8628,7 @@
         <v>0.6</v>
       </c>
       <c r="I146" t="n">
-        <v>3132.9</v>
+        <v>3131.4</v>
       </c>
       <c r="J146" t="n">
         <v>3105</v>
@@ -8661,22 +8637,22 @@
         <v>0.9</v>
       </c>
       <c r="L146" t="n">
-        <v>3390.5</v>
+        <v>3397.4</v>
       </c>
       <c r="M146" t="n">
         <v>3342.3</v>
       </c>
       <c r="N146" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="O146" t="n">
-        <v>59600</v>
+        <v>61000</v>
       </c>
       <c r="P146" t="n">
         <v>61600</v>
       </c>
       <c r="Q146" t="n">
-        <v>-3.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="147">
@@ -8727,13 +8703,13 @@
         <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>173800</v>
+        <v>175900</v>
       </c>
       <c r="P147" t="n">
         <v>181100</v>
       </c>
       <c r="Q147" t="n">
-        <v>-4</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="148">
@@ -8784,13 +8760,13 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>43050</v>
+        <v>46800</v>
       </c>
       <c r="P148" t="n">
         <v>44800</v>
       </c>
       <c r="Q148" t="n">
-        <v>-3.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="149">
@@ -8841,13 +8817,13 @@
         <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>1404000</v>
+        <v>1403000</v>
       </c>
       <c r="P149" t="n">
         <v>1396000</v>
       </c>
       <c r="Q149" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
@@ -8862,49 +8838,49 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1941</v>
+        <v>2053</v>
       </c>
       <c r="D150" t="n">
         <v>1941</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="F150" t="n">
-        <v>7591.4</v>
+        <v>7747.4</v>
       </c>
       <c r="G150" t="n">
         <v>7591.4</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I150" t="n">
-        <v>9204.1</v>
+        <v>9347</v>
       </c>
       <c r="J150" t="n">
         <v>9204.1</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="L150" t="n">
-        <v>10163</v>
+        <v>10405.3</v>
       </c>
       <c r="M150" t="n">
         <v>10163</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O150" t="n">
-        <v>60900</v>
+        <v>67100</v>
       </c>
       <c r="P150" t="n">
         <v>64300</v>
       </c>
       <c r="Q150" t="n">
-        <v>-5.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="151">
@@ -8919,49 +8895,49 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D151" t="n">
         <v>901</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
       <c r="F151" t="n">
-        <v>3624.2</v>
+        <v>3601.2</v>
       </c>
       <c r="G151" t="n">
         <v>3636.6</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.3</v>
+        <v>-1</v>
       </c>
       <c r="I151" t="n">
-        <v>4271.6</v>
+        <v>4239.1</v>
       </c>
       <c r="J151" t="n">
         <v>4301.9</v>
       </c>
       <c r="K151" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="L151" t="n">
-        <v>4457.2</v>
+        <v>4385.8</v>
       </c>
       <c r="M151" t="n">
         <v>4457.2</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="O151" t="n">
-        <v>35250</v>
+        <v>36700</v>
       </c>
       <c r="P151" t="n">
         <v>36300</v>
       </c>
       <c r="Q151" t="n">
-        <v>-2.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="152">
@@ -8976,49 +8952,49 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3671</v>
+        <v>3750</v>
       </c>
       <c r="D152" t="n">
         <v>3671</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="F152" t="n">
-        <v>14812.8</v>
+        <v>14855.6</v>
       </c>
       <c r="G152" t="n">
         <v>14812.8</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I152" t="n">
-        <v>15832.8</v>
+        <v>15923.4</v>
       </c>
       <c r="J152" t="n">
         <v>15832.8</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L152" t="n">
-        <v>17211.9</v>
+        <v>17431.9</v>
       </c>
       <c r="M152" t="n">
         <v>17211.9</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O152" t="n">
-        <v>238000</v>
+        <v>235500</v>
       </c>
       <c r="P152" t="n">
         <v>240500</v>
       </c>
       <c r="Q152" t="n">
-        <v>-1</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="153">
@@ -9069,13 +9045,13 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>197000</v>
+        <v>225000</v>
       </c>
       <c r="P153" t="n">
         <v>204500</v>
       </c>
       <c r="Q153" t="n">
-        <v>-3.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154">
@@ -9126,13 +9102,13 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>763000</v>
+        <v>845000</v>
       </c>
       <c r="P154" t="n">
         <v>797000</v>
       </c>
       <c r="Q154" t="n">
-        <v>-4.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
@@ -9183,13 +9159,13 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>120400</v>
+        <v>139000</v>
       </c>
       <c r="P155" t="n">
         <v>130300</v>
       </c>
       <c r="Q155" t="n">
-        <v>-7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="156">
@@ -9204,25 +9180,25 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1369</v>
+        <v>1359</v>
       </c>
       <c r="D156" t="n">
         <v>1370</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="F156" t="n">
-        <v>6491</v>
+        <v>6453.1</v>
       </c>
       <c r="G156" t="n">
         <v>6487.6</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="I156" t="n">
-        <v>7053.8</v>
+        <v>7047.8</v>
       </c>
       <c r="J156" t="n">
         <v>7029.8</v>
@@ -9231,22 +9207,22 @@
         <v>0.3</v>
       </c>
       <c r="L156" t="n">
-        <v>7523.1</v>
+        <v>7564.6</v>
       </c>
       <c r="M156" t="n">
         <v>7523.1</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O156" t="n">
-        <v>128900</v>
+        <v>129500</v>
       </c>
       <c r="P156" t="n">
         <v>128400</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="157">
@@ -9297,13 +9273,13 @@
         <v>-0.5</v>
       </c>
       <c r="O157" t="n">
-        <v>60700</v>
+        <v>64700</v>
       </c>
       <c r="P157" t="n">
         <v>65500</v>
       </c>
       <c r="Q157" t="n">
-        <v>-7.3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="158">
@@ -9354,13 +9330,13 @@
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>368500</v>
+        <v>371000</v>
       </c>
       <c r="P158" t="n">
         <v>393000</v>
       </c>
       <c r="Q158" t="n">
-        <v>-6.2</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="159">
@@ -9375,49 +9351,49 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D159" t="n">
         <v>472</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="F159" t="n">
-        <v>1902.3</v>
+        <v>1914.3</v>
       </c>
       <c r="G159" t="n">
         <v>1902.3</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I159" t="n">
-        <v>2170.4</v>
+        <v>2189.7</v>
       </c>
       <c r="J159" t="n">
         <v>2170.4</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L159" t="n">
-        <v>2398.1</v>
+        <v>2417.3</v>
       </c>
       <c r="M159" t="n">
         <v>2398.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O159" t="n">
-        <v>101200</v>
+        <v>100800</v>
       </c>
       <c r="P159" t="n">
         <v>101000</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="160">
@@ -9468,13 +9444,13 @@
         <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>125200</v>
+        <v>118200</v>
       </c>
       <c r="P160" t="n">
         <v>126400</v>
       </c>
       <c r="Q160" t="n">
-        <v>-0.9</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="161">
@@ -9525,13 +9501,13 @@
         <v>6.6</v>
       </c>
       <c r="O161" t="n">
-        <v>37750</v>
+        <v>39000</v>
       </c>
       <c r="P161" t="n">
         <v>39250</v>
       </c>
       <c r="Q161" t="n">
-        <v>-3.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="162">
@@ -9582,13 +9558,13 @@
         <v>5.9</v>
       </c>
       <c r="O162" t="n">
-        <v>316000</v>
+        <v>320500</v>
       </c>
       <c r="P162" t="n">
         <v>278000</v>
       </c>
       <c r="Q162" t="n">
-        <v>13.7</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="163">
@@ -9639,13 +9615,13 @@
         <v>-0.7</v>
       </c>
       <c r="O163" t="n">
-        <v>2554000</v>
+        <v>2770000</v>
       </c>
       <c r="P163" t="n">
         <v>2789000</v>
       </c>
       <c r="Q163" t="n">
-        <v>-8.4</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="164">
@@ -9696,13 +9672,13 @@
         <v>4.6</v>
       </c>
       <c r="O164" t="n">
-        <v>142800</v>
+        <v>152500</v>
       </c>
       <c r="P164" t="n">
         <v>150500</v>
       </c>
       <c r="Q164" t="n">
-        <v>-5.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="165">
@@ -9753,13 +9729,13 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>13850</v>
+        <v>14050</v>
       </c>
       <c r="P165" t="n">
         <v>13990</v>
       </c>
       <c r="Q165" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="166">
@@ -9810,13 +9786,13 @@
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>33750</v>
+        <v>33200</v>
       </c>
       <c r="P166" t="n">
         <v>35450</v>
       </c>
       <c r="Q166" t="n">
-        <v>-4.8</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="167">
@@ -9831,49 +9807,49 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="D167" t="n">
         <v>770</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F167" t="n">
-        <v>2741.8</v>
+        <v>2738</v>
       </c>
       <c r="G167" t="n">
         <v>2741.8</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I167" t="n">
-        <v>3662.2</v>
+        <v>3653.6</v>
       </c>
       <c r="J167" t="n">
         <v>3662.2</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="L167" t="n">
-        <v>4615.7</v>
+        <v>4585.7</v>
       </c>
       <c r="M167" t="n">
         <v>4615.7</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="O167" t="n">
-        <v>364000</v>
+        <v>408500</v>
       </c>
       <c r="P167" t="n">
         <v>393000</v>
       </c>
       <c r="Q167" t="n">
-        <v>-7.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="168">
@@ -9924,13 +9900,13 @@
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>30600</v>
+        <v>30850</v>
       </c>
       <c r="P168" t="n">
         <v>31500</v>
       </c>
       <c r="Q168" t="n">
-        <v>-2.9</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="169">
@@ -9945,49 +9921,49 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="D169" t="n">
         <v>1822</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F169" t="n">
-        <v>7099.5</v>
+        <v>7127</v>
       </c>
       <c r="G169" t="n">
         <v>7099.5</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I169" t="n">
-        <v>8219.5</v>
+        <v>8312.1</v>
       </c>
       <c r="J169" t="n">
         <v>8219.5</v>
       </c>
       <c r="K169" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L169" t="n">
-        <v>8952.200000000001</v>
+        <v>9149</v>
       </c>
       <c r="M169" t="n">
         <v>8952.200000000001</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O169" t="n">
-        <v>22500</v>
+        <v>22000</v>
       </c>
       <c r="P169" t="n">
         <v>23000</v>
       </c>
       <c r="Q169" t="n">
-        <v>-2.2</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="170">
@@ -10002,49 +9978,49 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D170" t="n">
         <v>845</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F170" t="n">
-        <v>3377.3</v>
+        <v>3438.6</v>
       </c>
       <c r="G170" t="n">
         <v>3377.3</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I170" t="n">
-        <v>4511.6</v>
+        <v>4564.2</v>
       </c>
       <c r="J170" t="n">
         <v>4511.6</v>
       </c>
       <c r="K170" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L170" t="n">
-        <v>5545</v>
+        <v>5651.6</v>
       </c>
       <c r="M170" t="n">
         <v>5545</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O170" t="n">
-        <v>78300</v>
+        <v>79400</v>
       </c>
       <c r="P170" t="n">
         <v>79400</v>
       </c>
       <c r="Q170" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -10095,13 +10071,13 @@
         <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>442500</v>
+        <v>483000</v>
       </c>
       <c r="P171" t="n">
         <v>484000</v>
       </c>
       <c r="Q171" t="n">
-        <v>-8.6</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="172">
@@ -10116,49 +10092,49 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1536</v>
+        <v>1551</v>
       </c>
       <c r="D172" t="n">
         <v>1528</v>
       </c>
       <c r="E172" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F172" t="n">
-        <v>2708</v>
+        <v>2750.3</v>
       </c>
       <c r="G172" t="n">
         <v>2697</v>
       </c>
       <c r="H172" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="I172" t="n">
-        <v>4881.3</v>
+        <v>4937.1</v>
       </c>
       <c r="J172" t="n">
         <v>4904.1</v>
       </c>
       <c r="K172" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L172" t="n">
-        <v>5489.9</v>
+        <v>5399.4</v>
       </c>
       <c r="M172" t="n">
         <v>5526.9</v>
       </c>
       <c r="N172" t="n">
-        <v>-0.7</v>
+        <v>-2.3</v>
       </c>
       <c r="O172" t="n">
-        <v>199900</v>
+        <v>203000</v>
       </c>
       <c r="P172" t="n">
         <v>208500</v>
       </c>
       <c r="Q172" t="n">
-        <v>-4.1</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="173">
@@ -10209,13 +10185,13 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>13310</v>
+        <v>14030</v>
       </c>
       <c r="P173" t="n">
         <v>14260</v>
       </c>
       <c r="Q173" t="n">
-        <v>-6.7</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="174">
@@ -10266,13 +10242,13 @@
         <v>0</v>
       </c>
       <c r="O174" t="n">
-        <v>314000</v>
+        <v>330500</v>
       </c>
       <c r="P174" t="n">
         <v>334000</v>
       </c>
       <c r="Q174" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="175">
@@ -10323,13 +10299,13 @@
         <v>0.1</v>
       </c>
       <c r="O175" t="n">
-        <v>58500</v>
+        <v>63800</v>
       </c>
       <c r="P175" t="n">
         <v>60200</v>
       </c>
       <c r="Q175" t="n">
-        <v>-2.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176">
@@ -10344,49 +10320,49 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D176" t="n">
         <v>332</v>
       </c>
       <c r="E176" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="F176" t="n">
-        <v>1389.8</v>
+        <v>1432.4</v>
       </c>
       <c r="G176" t="n">
         <v>1388.2</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="I176" t="n">
-        <v>1928.8</v>
+        <v>1977.4</v>
       </c>
       <c r="J176" t="n">
         <v>1925.5</v>
       </c>
       <c r="K176" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="L176" t="n">
-        <v>2724</v>
+        <v>2824.8</v>
       </c>
       <c r="M176" t="n">
         <v>2719</v>
       </c>
       <c r="N176" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="O176" t="n">
-        <v>40950</v>
+        <v>43350</v>
       </c>
       <c r="P176" t="n">
         <v>40900</v>
       </c>
       <c r="Q176" t="n">
-        <v>0.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177">
@@ -10401,49 +10377,49 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>970</v>
+        <v>979</v>
       </c>
       <c r="D177" t="n">
         <v>970</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F177" t="n">
-        <v>5308.8</v>
+        <v>5333.8</v>
       </c>
       <c r="G177" t="n">
         <v>5308.8</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I177" t="n">
-        <v>5626.7</v>
+        <v>5651.7</v>
       </c>
       <c r="J177" t="n">
         <v>5626.7</v>
       </c>
       <c r="K177" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L177" t="n">
-        <v>6061.2</v>
+        <v>6086.2</v>
       </c>
       <c r="M177" t="n">
         <v>6061.2</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O177" t="n">
-        <v>75700</v>
+        <v>75400</v>
       </c>
       <c r="P177" t="n">
         <v>79000</v>
       </c>
       <c r="Q177" t="n">
-        <v>-4.2</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="178">
@@ -10494,13 +10470,13 @@
         <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>1217000</v>
+        <v>1244000</v>
       </c>
       <c r="P178" t="n">
         <v>1212000</v>
       </c>
       <c r="Q178" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="179">
@@ -10551,13 +10527,13 @@
         <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>186400</v>
+        <v>206500</v>
       </c>
       <c r="P179" t="n">
         <v>201000</v>
       </c>
       <c r="Q179" t="n">
-        <v>-7.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="180">
@@ -10608,13 +10584,13 @@
         <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>84500</v>
+        <v>83200</v>
       </c>
       <c r="P180" t="n">
         <v>89800</v>
       </c>
       <c r="Q180" t="n">
-        <v>-5.9</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="181">
@@ -10665,13 +10641,13 @@
         <v>0.6</v>
       </c>
       <c r="O181" t="n">
-        <v>238000</v>
+        <v>241500</v>
       </c>
       <c r="P181" t="n">
         <v>208500</v>
       </c>
       <c r="Q181" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>화장품·생활용품</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>화장품·생활용품</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>화장품·생활용품</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>화장품·생활용품</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>화장품·생활용품</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>화장품·생활용품</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>반도체 소부장</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -17022,7 +17022,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>화장품·생활용품</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>유통·면세</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>IT서비스·SW</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>레저·카지노</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>레저·카지노</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>인터넷</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>인터넷</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>IT서비스·SW</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>레저·카지노</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>IT서비스·SW</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>전기전자</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>금융-보험</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>금융-보험</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>금융-보험</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>증권</t>
+          <t>금융-증권</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>증권</t>
+          <t>금융-증권</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>증권</t>
+          <t>금융-증권</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>카드·기타금융</t>
+          <t>금융-카드기타</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>금융-보험</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>증권</t>
+          <t>금융-증권</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>증권</t>
+          <t>금융-증권</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>금융-보험</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>은행·금융지주</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>카드·기타금융</t>
+          <t>금융-카드기타</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>전기전자</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>음식료</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>방산·항공우주</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>방산·항공우주</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>미디어·광고</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>운송·물류</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>철강·비철</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>철강·비철</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>방산·항공우주</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -11544,7 +11544,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -455,7 +455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-07-31 · 전주 2026-07-26</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-02 · 전주 2026-07-26</t>
         </is>
       </c>
     </row>
@@ -669,31 +669,31 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1302.1</v>
+        <v>1276.2</v>
       </c>
       <c r="J4" t="n">
         <v>1302.1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L4" t="n">
-        <v>2221.5</v>
+        <v>2057.1</v>
       </c>
       <c r="M4" t="n">
         <v>2221.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-7.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3051.5</v>
+        <v>2988.6</v>
       </c>
       <c r="P4" t="n">
         <v>3051.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="R4" t="n">
         <v>73500</v>
@@ -813,31 +813,31 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>17753.8</v>
+        <v>18124.9</v>
       </c>
       <c r="J6" t="n">
         <v>17032.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="L6" t="n">
-        <v>24731.6</v>
+        <v>24845.8</v>
       </c>
       <c r="M6" t="n">
         <v>23515</v>
       </c>
       <c r="N6" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="O6" t="n">
-        <v>30543</v>
+        <v>30674</v>
       </c>
       <c r="P6" t="n">
         <v>29523.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
         <v>1170000</v>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2664928.5</v>
+        <v>2660324.5</v>
       </c>
       <c r="J10" t="n">
         <v>2715863.3</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="L10" t="n">
-        <v>3924061.4</v>
+        <v>3923981.9</v>
       </c>
       <c r="M10" t="n">
         <v>3981021.3</v>
@@ -1119,7 +1119,7 @@
         <v>-1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4018350</v>
+        <v>4018476.8</v>
       </c>
       <c r="P10" t="n">
         <v>3964740.9</v>
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2140</v>
+        <v>2119</v>
       </c>
       <c r="G11" t="n">
         <v>2119</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>8321.4</v>
@@ -1533,31 +1533,31 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1564.9</v>
+        <v>1625.7</v>
       </c>
       <c r="J16" t="n">
         <v>1564.9</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>2069.4</v>
+        <v>2130.2</v>
       </c>
       <c r="M16" t="n">
         <v>2069.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2404.4</v>
+        <v>2410.9</v>
       </c>
       <c r="P16" t="n">
         <v>2404.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R16" t="n">
         <v>33300</v>
@@ -1605,31 +1605,31 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1995.6</v>
+        <v>2285.9</v>
       </c>
       <c r="J17" t="n">
         <v>1995.6</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="L17" t="n">
-        <v>2252.9</v>
+        <v>2555.4</v>
       </c>
       <c r="M17" t="n">
         <v>2252.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2899.4</v>
+        <v>3230</v>
       </c>
       <c r="P17" t="n">
         <v>2899.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="R17" t="n">
         <v>23200</v>
@@ -1866,31 +1866,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1747.6</v>
+        <v>1776.7</v>
       </c>
       <c r="J21" t="n">
         <v>1949.2</v>
       </c>
       <c r="K21" t="n">
-        <v>-10.3</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>2102.3</v>
+        <v>2139.9</v>
       </c>
       <c r="M21" t="n">
         <v>2228</v>
       </c>
       <c r="N21" t="n">
-        <v>-5.6</v>
+        <v>-4</v>
       </c>
       <c r="O21" t="n">
-        <v>2430.5</v>
+        <v>2437.2</v>
       </c>
       <c r="P21" t="n">
         <v>2513.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.3</v>
+        <v>-3</v>
       </c>
       <c r="R21" t="n">
         <v>6180</v>
@@ -2361,40 +2361,40 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-2377</v>
+        <v>-1901</v>
       </c>
       <c r="G28" t="n">
         <v>-2377</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I28" t="n">
-        <v>11051.5</v>
+        <v>11586.2</v>
       </c>
       <c r="J28" t="n">
         <v>11051.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L28" t="n">
-        <v>22324.6</v>
+        <v>22110.5</v>
       </c>
       <c r="M28" t="n">
         <v>22324.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O28" t="n">
-        <v>26471.7</v>
+        <v>26041.9</v>
       </c>
       <c r="P28" t="n">
         <v>26471.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="R28" t="n">
         <v>25900</v>
@@ -2514,31 +2514,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>997.3</v>
+        <v>994.8</v>
       </c>
       <c r="J30" t="n">
         <v>997.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1648.4</v>
+        <v>1786.1</v>
       </c>
       <c r="M30" t="n">
         <v>1648.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="O30" t="n">
-        <v>2856.9</v>
+        <v>3034.8</v>
       </c>
       <c r="P30" t="n">
         <v>2856.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R30" t="n">
         <v>137700</v>
@@ -2586,31 +2586,31 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1478.8</v>
+        <v>1558.2</v>
       </c>
       <c r="J31" t="n">
         <v>1440</v>
       </c>
       <c r="K31" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>1655.8</v>
+        <v>1610.8</v>
       </c>
       <c r="M31" t="n">
         <v>1628.4</v>
       </c>
       <c r="N31" t="n">
-        <v>1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1728.5</v>
+        <v>1734</v>
       </c>
       <c r="P31" t="n">
         <v>1748.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="R31" t="n">
         <v>44650</v>
@@ -3090,31 +3090,31 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>30875.7</v>
+        <v>31198.5</v>
       </c>
       <c r="J38" t="n">
         <v>30875.7</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>38602.4</v>
+        <v>38184.4</v>
       </c>
       <c r="M38" t="n">
         <v>38602.4</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="O38" t="n">
-        <v>44763.8</v>
+        <v>43978.5</v>
       </c>
       <c r="P38" t="n">
         <v>44763.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="R38" t="n">
         <v>312500</v>
@@ -3306,31 +3306,31 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3829987</v>
+        <v>3911296.2</v>
       </c>
       <c r="J41" t="n">
         <v>3832416.1</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.1</v>
+        <v>2.1</v>
       </c>
       <c r="L41" t="n">
-        <v>5414963.6</v>
+        <v>5490913</v>
       </c>
       <c r="M41" t="n">
         <v>5422608.6</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.1</v>
+        <v>1.3</v>
       </c>
       <c r="O41" t="n">
-        <v>5340609.5</v>
+        <v>5563316.4</v>
       </c>
       <c r="P41" t="n">
         <v>5327749.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="R41" t="n">
         <v>262500</v>
@@ -3738,31 +3738,31 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>855.3</v>
+        <v>3062.9</v>
       </c>
       <c r="J47" t="n">
         <v>509.1</v>
       </c>
       <c r="K47" t="n">
-        <v>68</v>
+        <v>501.6</v>
       </c>
       <c r="L47" t="n">
-        <v>15162.5</v>
+        <v>13976.6</v>
       </c>
       <c r="M47" t="n">
         <v>14952.3</v>
       </c>
       <c r="N47" t="n">
-        <v>1.4</v>
+        <v>-6.5</v>
       </c>
       <c r="O47" t="n">
-        <v>24694.9</v>
+        <v>24303.4</v>
       </c>
       <c r="P47" t="n">
         <v>25566.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>-3.4</v>
+        <v>-4.9</v>
       </c>
       <c r="R47" t="n">
         <v>397000</v>
@@ -3810,31 +3810,31 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1925</v>
+        <v>1843.8</v>
       </c>
       <c r="J48" t="n">
         <v>1925</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>-4.2</v>
       </c>
       <c r="L48" t="n">
-        <v>2254.8</v>
+        <v>2363.5</v>
       </c>
       <c r="M48" t="n">
         <v>2254.8</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O48" t="n">
-        <v>2472.6</v>
+        <v>2625.8</v>
       </c>
       <c r="P48" t="n">
         <v>2472.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R48" t="n">
         <v>85500</v>
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="G55" t="n">
         <v>544</v>
       </c>
       <c r="H55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>1884.9</v>
@@ -4377,31 +4377,31 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>16675.9</v>
+        <v>19263.6</v>
       </c>
       <c r="J56" t="n">
         <v>16675.9</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="L56" t="n">
-        <v>31927.6</v>
+        <v>37014.1</v>
       </c>
       <c r="M56" t="n">
         <v>31927.6</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="O56" t="n">
-        <v>51440.2</v>
+        <v>58301.1</v>
       </c>
       <c r="P56" t="n">
         <v>51440.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="R56" t="n">
         <v>1142000</v>
@@ -4593,16 +4593,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>59868.3</v>
+        <v>60493.2</v>
       </c>
       <c r="J59" t="n">
         <v>57969.2</v>
       </c>
       <c r="K59" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="L59" t="n">
-        <v>71478.7</v>
+        <v>71518.3</v>
       </c>
       <c r="M59" t="n">
         <v>69012.2</v>
@@ -4611,13 +4611,13 @@
         <v>3.6</v>
       </c>
       <c r="O59" t="n">
-        <v>83723.10000000001</v>
+        <v>83788</v>
       </c>
       <c r="P59" t="n">
         <v>80641.10000000001</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
         <v>384500</v>
@@ -4665,31 +4665,31 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>8261.799999999999</v>
+        <v>8068.5</v>
       </c>
       <c r="J60" t="n">
         <v>7641.5</v>
       </c>
       <c r="K60" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="L60" t="n">
-        <v>11941.1</v>
+        <v>11562.8</v>
       </c>
       <c r="M60" t="n">
         <v>12300.9</v>
       </c>
       <c r="N60" t="n">
-        <v>-2.9</v>
+        <v>-6</v>
       </c>
       <c r="O60" t="n">
-        <v>13974.7</v>
+        <v>13668.4</v>
       </c>
       <c r="P60" t="n">
         <v>15192.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="R60" t="n">
         <v>25500</v>
@@ -5304,40 +5304,40 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3797</v>
+        <v>3962</v>
       </c>
       <c r="G69" t="n">
         <v>3788</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2</v>
+        <v>4.6</v>
       </c>
       <c r="I69" t="n">
-        <v>13739.3</v>
+        <v>14632.7</v>
       </c>
       <c r="J69" t="n">
         <v>13678.5</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="L69" t="n">
-        <v>9780.200000000001</v>
+        <v>10103.5</v>
       </c>
       <c r="M69" t="n">
         <v>9774.299999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="O69" t="n">
-        <v>9794.200000000001</v>
+        <v>10048.4</v>
       </c>
       <c r="P69" t="n">
         <v>9789.200000000001</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="R69" t="n">
         <v>20950</v>
@@ -5673,31 +5673,31 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>37812.3</v>
+        <v>37830.2</v>
       </c>
       <c r="J74" t="n">
         <v>37353.9</v>
       </c>
       <c r="K74" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L74" t="n">
-        <v>42599.5</v>
+        <v>42606.3</v>
       </c>
       <c r="M74" t="n">
         <v>42626.4</v>
       </c>
       <c r="N74" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="O74" t="n">
-        <v>46098.4</v>
+        <v>46132.5</v>
       </c>
       <c r="P74" t="n">
         <v>46322.8</v>
       </c>
       <c r="Q74" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="R74" t="n">
         <v>476000</v>
@@ -5736,40 +5736,40 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>9962</v>
+        <v>9970</v>
       </c>
       <c r="G75" t="n">
         <v>9970</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>42863.6</v>
+        <v>42800.5</v>
       </c>
       <c r="J75" t="n">
         <v>42852.8</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="L75" t="n">
-        <v>55046.6</v>
+        <v>55094.4</v>
       </c>
       <c r="M75" t="n">
         <v>54780.9</v>
       </c>
       <c r="N75" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O75" t="n">
-        <v>61839.9</v>
+        <v>61471.3</v>
       </c>
       <c r="P75" t="n">
         <v>61398</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="R75" t="n">
         <v>917000</v>
@@ -6528,31 +6528,31 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>8327.9</v>
+        <v>8304.200000000001</v>
       </c>
       <c r="J86" t="n">
         <v>8379.5</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="L86" t="n">
-        <v>10685.2</v>
+        <v>10724.8</v>
       </c>
       <c r="M86" t="n">
         <v>10717.4</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="O86" t="n">
-        <v>12003.7</v>
+        <v>11914</v>
       </c>
       <c r="P86" t="n">
         <v>12125.8</v>
       </c>
       <c r="Q86" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
       <c r="R86" t="n">
         <v>206000</v>
@@ -6600,31 +6600,31 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>4350.9</v>
+        <v>4325.1</v>
       </c>
       <c r="J87" t="n">
         <v>4350.9</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L87" t="n">
-        <v>5147.3</v>
+        <v>5038.9</v>
       </c>
       <c r="M87" t="n">
         <v>5147.3</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="O87" t="n">
-        <v>5926.1</v>
+        <v>5851.9</v>
       </c>
       <c r="P87" t="n">
         <v>5926.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="R87" t="n">
         <v>3305</v>
@@ -6888,31 +6888,31 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>36858.3</v>
+        <v>37009.7</v>
       </c>
       <c r="J91" t="n">
         <v>36894.8</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L91" t="n">
-        <v>39741</v>
+        <v>39989.8</v>
       </c>
       <c r="M91" t="n">
         <v>39631.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="O91" t="n">
-        <v>42158.7</v>
+        <v>42270.6</v>
       </c>
       <c r="P91" t="n">
         <v>42250.5</v>
       </c>
       <c r="Q91" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>20650</v>
@@ -7032,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>37926.9</v>
+        <v>37916.4</v>
       </c>
       <c r="J93" t="n">
         <v>36427</v>
@@ -7041,22 +7041,22 @@
         <v>4.1</v>
       </c>
       <c r="L93" t="n">
-        <v>43783.1</v>
+        <v>43710</v>
       </c>
       <c r="M93" t="n">
         <v>41311</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O93" t="n">
-        <v>47509.5</v>
+        <v>47320.3</v>
       </c>
       <c r="P93" t="n">
         <v>45429.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R93" t="n">
         <v>351500</v>
@@ -7095,13 +7095,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="G94" t="n">
         <v>1557</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
         <v>5949.2</v>
@@ -7860,31 +7860,31 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>10077.8</v>
+        <v>9648.9</v>
       </c>
       <c r="J105" t="n">
         <v>10077.8</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="L105" t="n">
-        <v>14137.8</v>
+        <v>14046</v>
       </c>
       <c r="M105" t="n">
         <v>14137.8</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="O105" t="n">
-        <v>17103.4</v>
+        <v>17013.4</v>
       </c>
       <c r="P105" t="n">
         <v>17103.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R105" t="n">
         <v>9210</v>
@@ -8868,31 +8868,31 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>22291.9</v>
+        <v>22902.4</v>
       </c>
       <c r="J119" t="n">
         <v>22166.6</v>
       </c>
       <c r="K119" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="L119" t="n">
-        <v>20515.7</v>
+        <v>19494.5</v>
       </c>
       <c r="M119" t="n">
         <v>20465.1</v>
       </c>
       <c r="N119" t="n">
-        <v>0.2</v>
+        <v>-4.7</v>
       </c>
       <c r="O119" t="n">
-        <v>20865.4</v>
+        <v>19779.6</v>
       </c>
       <c r="P119" t="n">
         <v>20751.9</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.5</v>
+        <v>-4.7</v>
       </c>
       <c r="R119" t="n">
         <v>293500</v>
@@ -9300,31 +9300,31 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>14079.3</v>
+        <v>14688.2</v>
       </c>
       <c r="J125" t="n">
         <v>14079.3</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L125" t="n">
-        <v>15235.2</v>
+        <v>15554.8</v>
       </c>
       <c r="M125" t="n">
         <v>15235.2</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O125" t="n">
-        <v>15977.1</v>
+        <v>16386.5</v>
       </c>
       <c r="P125" t="n">
         <v>15977.1</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R125" t="n">
         <v>52200</v>
@@ -9372,31 +9372,31 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>3939.3</v>
+        <v>3834.8</v>
       </c>
       <c r="J126" t="n">
         <v>4474.9</v>
       </c>
       <c r="K126" t="n">
-        <v>-12</v>
+        <v>-14.3</v>
       </c>
       <c r="L126" t="n">
-        <v>6195.9</v>
+        <v>6089.3</v>
       </c>
       <c r="M126" t="n">
         <v>6539.1</v>
       </c>
       <c r="N126" t="n">
-        <v>-5.2</v>
+        <v>-6.9</v>
       </c>
       <c r="O126" t="n">
-        <v>7649.1</v>
+        <v>7599.1</v>
       </c>
       <c r="P126" t="n">
         <v>8019.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>-4.6</v>
+        <v>-5.2</v>
       </c>
       <c r="R126" t="n">
         <v>127300</v>
@@ -9660,31 +9660,31 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>15563.6</v>
+        <v>15130.3</v>
       </c>
       <c r="J130" t="n">
         <v>15563.6</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>-2.8</v>
       </c>
       <c r="L130" t="n">
-        <v>42293.6</v>
+        <v>42094.5</v>
       </c>
       <c r="M130" t="n">
         <v>42293.6</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O130" t="n">
-        <v>57794.5</v>
+        <v>57719.8</v>
       </c>
       <c r="P130" t="n">
         <v>57794.5</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R130" t="n">
         <v>258000</v>
@@ -10164,31 +10164,31 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>11021.2</v>
+        <v>10960.4</v>
       </c>
       <c r="J137" t="n">
         <v>11584.5</v>
       </c>
       <c r="K137" t="n">
-        <v>-4.9</v>
+        <v>-5.4</v>
       </c>
       <c r="L137" t="n">
-        <v>13777.4</v>
+        <v>13689.7</v>
       </c>
       <c r="M137" t="n">
         <v>15208.9</v>
       </c>
       <c r="N137" t="n">
-        <v>-9.4</v>
+        <v>-10</v>
       </c>
       <c r="O137" t="n">
-        <v>17340.5</v>
+        <v>17272.6</v>
       </c>
       <c r="P137" t="n">
         <v>18796.5</v>
       </c>
       <c r="Q137" t="n">
-        <v>-7.7</v>
+        <v>-8.1</v>
       </c>
       <c r="R137" t="n">
         <v>133700</v>
@@ -10227,40 +10227,40 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>1370</v>
+        <v>1377</v>
       </c>
       <c r="G138" t="n">
         <v>1377</v>
       </c>
       <c r="H138" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>6015.2</v>
+        <v>5976.9</v>
       </c>
       <c r="J138" t="n">
         <v>6025.6</v>
       </c>
       <c r="K138" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="L138" t="n">
-        <v>6838.7</v>
+        <v>6767.4</v>
       </c>
       <c r="M138" t="n">
         <v>6868.2</v>
       </c>
       <c r="N138" t="n">
-        <v>-0.4</v>
+        <v>-1.5</v>
       </c>
       <c r="O138" t="n">
-        <v>7643</v>
+        <v>7569.7</v>
       </c>
       <c r="P138" t="n">
         <v>7723.9</v>
       </c>
       <c r="Q138" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R138" t="n">
         <v>62500</v>
@@ -10326,13 +10326,13 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>2029.8</v>
+        <v>2036.2</v>
       </c>
       <c r="P139" t="n">
         <v>2029.8</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R139" t="n">
         <v>165500</v>
@@ -10380,31 +10380,31 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>1092.8</v>
+        <v>1093.4</v>
       </c>
       <c r="J140" t="n">
         <v>1092.8</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L140" t="n">
-        <v>1215.6</v>
+        <v>1214.2</v>
       </c>
       <c r="M140" t="n">
         <v>1215.6</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O140" t="n">
-        <v>1439.6</v>
+        <v>1437.6</v>
       </c>
       <c r="P140" t="n">
         <v>1439.6</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="R140" t="n">
         <v>26500</v>
@@ -10452,31 +10452,31 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>42384.2</v>
+        <v>45778.1</v>
       </c>
       <c r="J141" t="n">
         <v>42384.2</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L141" t="n">
-        <v>45628.6</v>
+        <v>47920.8</v>
       </c>
       <c r="M141" t="n">
         <v>45628.6</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O141" t="n">
-        <v>55174.1</v>
+        <v>57864.5</v>
       </c>
       <c r="P141" t="n">
         <v>55174.1</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R141" t="n">
         <v>162100</v>
@@ -10740,7 +10740,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>18478.3</v>
+        <v>18488.3</v>
       </c>
       <c r="J145" t="n">
         <v>17841.8</v>
@@ -10749,22 +10749,22 @@
         <v>3.6</v>
       </c>
       <c r="L145" t="n">
-        <v>21856.8</v>
+        <v>21876.8</v>
       </c>
       <c r="M145" t="n">
         <v>21006.4</v>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O145" t="n">
-        <v>25471</v>
+        <v>25498.6</v>
       </c>
       <c r="P145" t="n">
         <v>24598.1</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R145" t="n">
         <v>186700</v>
@@ -10884,31 +10884,31 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>2335</v>
+        <v>2311</v>
       </c>
       <c r="J147" t="n">
         <v>2202</v>
       </c>
       <c r="K147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L147" t="n">
-        <v>2506.3</v>
+        <v>2420.3</v>
       </c>
       <c r="M147" t="n">
         <v>2377</v>
       </c>
       <c r="N147" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="O147" t="n">
-        <v>2967.4</v>
+        <v>2825.8</v>
       </c>
       <c r="P147" t="n">
         <v>3578.8</v>
       </c>
       <c r="Q147" t="n">
-        <v>-17.1</v>
+        <v>-21</v>
       </c>
       <c r="R147" t="n">
         <v>113800</v>
@@ -11172,31 +11172,31 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>1517.2</v>
+        <v>1516.5</v>
       </c>
       <c r="J151" t="n">
         <v>1526.7</v>
       </c>
       <c r="K151" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="L151" t="n">
-        <v>2058.2</v>
+        <v>2056.3</v>
       </c>
       <c r="M151" t="n">
         <v>2054.3</v>
       </c>
       <c r="N151" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O151" t="n">
-        <v>2546.3</v>
+        <v>2542.2</v>
       </c>
       <c r="P151" t="n">
         <v>2545</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="R151" t="n">
         <v>49450</v>
@@ -11244,31 +11244,31 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>5922.1</v>
+        <v>6217.2</v>
       </c>
       <c r="J152" t="n">
         <v>5891.4</v>
       </c>
       <c r="K152" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="L152" t="n">
-        <v>6584.1</v>
+        <v>6596.8</v>
       </c>
       <c r="M152" t="n">
         <v>6323.3</v>
       </c>
       <c r="N152" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O152" t="n">
-        <v>7258</v>
+        <v>7427.8</v>
       </c>
       <c r="P152" t="n">
         <v>7160.8</v>
       </c>
       <c r="Q152" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="R152" t="n">
         <v>7290</v>
@@ -11685,13 +11685,13 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="G159" t="n">
         <v>561</v>
       </c>
       <c r="H159" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I159" t="n">
         <v>2389.6</v>
@@ -12234,31 +12234,31 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>4650.4</v>
+        <v>4810.5</v>
       </c>
       <c r="J167" t="n">
         <v>4647</v>
       </c>
       <c r="K167" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
       <c r="L167" t="n">
-        <v>5283.9</v>
+        <v>5542.3</v>
       </c>
       <c r="M167" t="n">
         <v>5283.7</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O167" t="n">
-        <v>5871</v>
+        <v>6265.4</v>
       </c>
       <c r="P167" t="n">
         <v>5883.9</v>
       </c>
       <c r="Q167" t="n">
-        <v>-0.2</v>
+        <v>6.5</v>
       </c>
       <c r="R167" t="n">
         <v>130000</v>
@@ -12639,31 +12639,31 @@
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>54601.8</v>
+        <v>80836</v>
       </c>
       <c r="J173" t="n">
         <v>54601.8</v>
       </c>
       <c r="K173" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L173" t="n">
-        <v>34598.5</v>
+        <v>41223.6</v>
       </c>
       <c r="M173" t="n">
         <v>34598.5</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="O173" t="n">
-        <v>40044.5</v>
+        <v>44949.8</v>
       </c>
       <c r="P173" t="n">
         <v>40044.5</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="R173" t="n">
         <v>110500</v>
@@ -12972,31 +12972,31 @@
         <v>0</v>
       </c>
       <c r="I178" t="n">
-        <v>3594.6</v>
+        <v>3573.2</v>
       </c>
       <c r="J178" t="n">
         <v>3594.6</v>
       </c>
       <c r="K178" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L178" t="n">
-        <v>3524.8</v>
+        <v>3455.3</v>
       </c>
       <c r="M178" t="n">
         <v>3524.8</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="O178" t="n">
-        <v>3913</v>
+        <v>3744.2</v>
       </c>
       <c r="P178" t="n">
         <v>3913</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="R178" t="n">
         <v>71200</v>
@@ -13737,31 +13737,31 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>10318.9</v>
+        <v>10183.5</v>
       </c>
       <c r="J189" t="n">
         <v>10990.9</v>
       </c>
       <c r="K189" t="n">
-        <v>-6.1</v>
+        <v>-7.3</v>
       </c>
       <c r="L189" t="n">
-        <v>11341.3</v>
+        <v>11267.5</v>
       </c>
       <c r="M189" t="n">
         <v>11876.1</v>
       </c>
       <c r="N189" t="n">
-        <v>-4.5</v>
+        <v>-5.1</v>
       </c>
       <c r="O189" t="n">
-        <v>11964.7</v>
+        <v>11910</v>
       </c>
       <c r="P189" t="n">
         <v>12628.4</v>
       </c>
       <c r="Q189" t="n">
-        <v>-5.3</v>
+        <v>-5.7</v>
       </c>
       <c r="R189" t="n">
         <v>15170</v>
@@ -13809,31 +13809,31 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>6264</v>
+        <v>6291.4</v>
       </c>
       <c r="J190" t="n">
         <v>6565.1</v>
       </c>
       <c r="K190" t="n">
-        <v>-4.6</v>
+        <v>-4.2</v>
       </c>
       <c r="L190" t="n">
-        <v>6842.7</v>
+        <v>6860.1</v>
       </c>
       <c r="M190" t="n">
         <v>7114.6</v>
       </c>
       <c r="N190" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="O190" t="n">
-        <v>7201.9</v>
+        <v>7226.9</v>
       </c>
       <c r="P190" t="n">
         <v>7534.6</v>
       </c>
       <c r="Q190" t="n">
-        <v>-4.4</v>
+        <v>-4.1</v>
       </c>
       <c r="R190" t="n">
         <v>16950</v>
@@ -14637,31 +14637,31 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>787.1</v>
+        <v>759</v>
       </c>
       <c r="J202" t="n">
         <v>787.1</v>
       </c>
       <c r="K202" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="L202" t="n">
-        <v>900.7</v>
+        <v>874</v>
       </c>
       <c r="M202" t="n">
         <v>900.7</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O202" t="n">
-        <v>1019</v>
+        <v>995</v>
       </c>
       <c r="P202" t="n">
         <v>1019</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="R202" t="n">
         <v>66900</v>
@@ -14700,40 +14700,40 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G203" t="n">
         <v>80</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I203" t="n">
-        <v>384.3</v>
+        <v>389.9</v>
       </c>
       <c r="J203" t="n">
         <v>384.3</v>
       </c>
       <c r="K203" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L203" t="n">
-        <v>595.9</v>
+        <v>598.4</v>
       </c>
       <c r="M203" t="n">
         <v>595.9</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O203" t="n">
-        <v>882.5</v>
+        <v>887.5</v>
       </c>
       <c r="P203" t="n">
         <v>882.5</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R203" t="n">
         <v>58200</v>
@@ -14925,31 +14925,31 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>1305.5</v>
+        <v>1303.4</v>
       </c>
       <c r="J206" t="n">
         <v>1307.8</v>
       </c>
       <c r="K206" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="L206" t="n">
-        <v>1480.4</v>
+        <v>1477.5</v>
       </c>
       <c r="M206" t="n">
         <v>1471.7</v>
       </c>
       <c r="N206" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="O206" t="n">
-        <v>1670.2</v>
+        <v>1681</v>
       </c>
       <c r="P206" t="n">
         <v>1623.6</v>
       </c>
       <c r="Q206" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="R206" t="n">
         <v>36100</v>
@@ -15069,31 +15069,31 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>4022.1</v>
+        <v>4107.2</v>
       </c>
       <c r="J208" t="n">
         <v>4022.1</v>
       </c>
       <c r="K208" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="L208" t="n">
-        <v>4688.9</v>
+        <v>4696.1</v>
       </c>
       <c r="M208" t="n">
         <v>4688.9</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O208" t="n">
-        <v>5231.2</v>
+        <v>5287.3</v>
       </c>
       <c r="P208" t="n">
         <v>5231.2</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="R208" t="n">
         <v>44700</v>
@@ -15141,31 +15141,31 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>24193.1</v>
+        <v>24162.2</v>
       </c>
       <c r="J209" t="n">
         <v>24196.8</v>
       </c>
       <c r="K209" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="L209" t="n">
-        <v>28135.5</v>
+        <v>28197.6</v>
       </c>
       <c r="M209" t="n">
         <v>28253.4</v>
       </c>
       <c r="N209" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="O209" t="n">
-        <v>31109.9</v>
+        <v>30980.9</v>
       </c>
       <c r="P209" t="n">
         <v>30972.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>1485000</v>
@@ -15204,40 +15204,40 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="G210" t="n">
         <v>510</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="I210" t="n">
-        <v>2117.3</v>
+        <v>2107.1</v>
       </c>
       <c r="J210" t="n">
         <v>2117.3</v>
       </c>
       <c r="K210" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L210" t="n">
-        <v>2826.9</v>
+        <v>2814</v>
       </c>
       <c r="M210" t="n">
         <v>2826.9</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O210" t="n">
-        <v>3490.6</v>
+        <v>3480.9</v>
       </c>
       <c r="P210" t="n">
         <v>3490.6</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="R210" t="n">
         <v>41150</v>
@@ -15501,22 +15501,22 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>755.4</v>
+        <v>753.9</v>
       </c>
       <c r="J214" t="n">
         <v>789.7</v>
       </c>
       <c r="K214" t="n">
-        <v>-4.3</v>
+        <v>-4.5</v>
       </c>
       <c r="L214" t="n">
-        <v>1028.3</v>
+        <v>1027.6</v>
       </c>
       <c r="M214" t="n">
         <v>1065</v>
       </c>
       <c r="N214" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="O214" t="n">
         <v>1343.7</v>
@@ -15780,40 +15780,40 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G218" t="n">
         <v>239</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>1130.3</v>
+        <v>1085.9</v>
       </c>
       <c r="J218" t="n">
         <v>1136.3</v>
       </c>
       <c r="K218" t="n">
-        <v>-0.5</v>
+        <v>-4.4</v>
       </c>
       <c r="L218" t="n">
-        <v>2136.7</v>
+        <v>1947.2</v>
       </c>
       <c r="M218" t="n">
         <v>2111.3</v>
       </c>
       <c r="N218" t="n">
-        <v>1.2</v>
+        <v>-7.8</v>
       </c>
       <c r="O218" t="n">
-        <v>3558.3</v>
+        <v>3429.6</v>
       </c>
       <c r="P218" t="n">
         <v>3469</v>
       </c>
       <c r="Q218" t="n">
-        <v>2.6</v>
+        <v>-1.1</v>
       </c>
       <c r="R218" t="n">
         <v>103500</v>
@@ -15852,40 +15852,40 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>884</v>
+        <v>861</v>
       </c>
       <c r="G219" t="n">
         <v>889</v>
       </c>
       <c r="H219" t="n">
-        <v>-0.6</v>
+        <v>-3.1</v>
       </c>
       <c r="I219" t="n">
-        <v>3517.8</v>
+        <v>3508.1</v>
       </c>
       <c r="J219" t="n">
         <v>3601.2</v>
       </c>
       <c r="K219" t="n">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
       <c r="L219" t="n">
-        <v>4126.4</v>
+        <v>4192</v>
       </c>
       <c r="M219" t="n">
         <v>4239.1</v>
       </c>
       <c r="N219" t="n">
-        <v>-2.7</v>
+        <v>-1.1</v>
       </c>
       <c r="O219" t="n">
-        <v>4303.6</v>
+        <v>4414</v>
       </c>
       <c r="P219" t="n">
         <v>4385.8</v>
       </c>
       <c r="Q219" t="n">
-        <v>-1.9</v>
+        <v>0.6</v>
       </c>
       <c r="R219" t="n">
         <v>38300</v>
@@ -16149,31 +16149,31 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>14488.1</v>
+        <v>14592.8</v>
       </c>
       <c r="J223" t="n">
         <v>14855.6</v>
       </c>
       <c r="K223" t="n">
-        <v>-2.5</v>
+        <v>-1.8</v>
       </c>
       <c r="L223" t="n">
-        <v>15738.2</v>
+        <v>15949.3</v>
       </c>
       <c r="M223" t="n">
         <v>15923.4</v>
       </c>
       <c r="N223" t="n">
-        <v>-1.2</v>
+        <v>0.2</v>
       </c>
       <c r="O223" t="n">
-        <v>16836.6</v>
+        <v>16935.4</v>
       </c>
       <c r="P223" t="n">
         <v>17431.9</v>
       </c>
       <c r="Q223" t="n">
-        <v>-3.4</v>
+        <v>-2.8</v>
       </c>
       <c r="R223" t="n">
         <v>243000</v>
@@ -16284,13 +16284,13 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>22197</v>
+        <v>20915</v>
       </c>
       <c r="G225" t="n">
         <v>20915</v>
       </c>
       <c r="H225" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I225" t="n">
         <v>91376.2</v>
@@ -16527,13 +16527,13 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>7564.6</v>
+        <v>7562.3</v>
       </c>
       <c r="P228" t="n">
         <v>7564.6</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R228" t="n">
         <v>131800</v>
@@ -16644,40 +16644,40 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>-707</v>
+        <v>-655</v>
       </c>
       <c r="G230" t="n">
         <v>-707</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I230" t="n">
-        <v>-344.5</v>
+        <v>-297</v>
       </c>
       <c r="J230" t="n">
         <v>-344.5</v>
       </c>
       <c r="K230" t="n">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="L230" t="n">
-        <v>835.2</v>
+        <v>799</v>
       </c>
       <c r="M230" t="n">
         <v>835.2</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>-4.3</v>
       </c>
       <c r="O230" t="n">
-        <v>1157.4</v>
+        <v>1236</v>
       </c>
       <c r="P230" t="n">
         <v>1157.4</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="R230" t="n">
         <v>5200</v>
@@ -17211,13 +17211,13 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>2907</v>
+        <v>2812</v>
       </c>
       <c r="G238" t="n">
         <v>2812</v>
       </c>
       <c r="H238" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I238" t="n">
         <v>10928</v>
@@ -17292,31 +17292,31 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>2160.7</v>
+        <v>2341.8</v>
       </c>
       <c r="J239" t="n">
         <v>2200.4</v>
       </c>
       <c r="K239" t="n">
-        <v>-1.8</v>
+        <v>6.4</v>
       </c>
       <c r="L239" t="n">
-        <v>2614.3</v>
+        <v>2688.2</v>
       </c>
       <c r="M239" t="n">
         <v>2696.6</v>
       </c>
       <c r="N239" t="n">
-        <v>-3.1</v>
+        <v>-0.3</v>
       </c>
       <c r="O239" t="n">
-        <v>2810.7</v>
+        <v>2873</v>
       </c>
       <c r="P239" t="n">
         <v>2854.4</v>
       </c>
       <c r="Q239" t="n">
-        <v>-1.5</v>
+        <v>0.7</v>
       </c>
       <c r="R239" t="n">
         <v>160800</v>
@@ -17643,31 +17643,31 @@
         <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>2808.3</v>
+        <v>2805.4</v>
       </c>
       <c r="J244" t="n">
         <v>2738</v>
       </c>
       <c r="K244" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="L244" t="n">
-        <v>3555.2</v>
+        <v>3500.2</v>
       </c>
       <c r="M244" t="n">
         <v>3653.6</v>
       </c>
       <c r="N244" t="n">
-        <v>-2.7</v>
+        <v>-4.2</v>
       </c>
       <c r="O244" t="n">
-        <v>4469.2</v>
+        <v>4478.6</v>
       </c>
       <c r="P244" t="n">
         <v>4585.7</v>
       </c>
       <c r="Q244" t="n">
-        <v>-2.5</v>
+        <v>-2.3</v>
       </c>
       <c r="R244" t="n">
         <v>364500</v>
@@ -18066,31 +18066,31 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>40062</v>
+        <v>40238.8</v>
       </c>
       <c r="J250" t="n">
         <v>38876</v>
       </c>
       <c r="K250" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="L250" t="n">
-        <v>46975.6</v>
+        <v>46858.8</v>
       </c>
       <c r="M250" t="n">
         <v>45739.8</v>
       </c>
       <c r="N250" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="O250" t="n">
-        <v>54196.9</v>
+        <v>54155.1</v>
       </c>
       <c r="P250" t="n">
         <v>52641.7</v>
       </c>
       <c r="Q250" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R250" t="n">
         <v>481000</v>
@@ -18138,31 +18138,31 @@
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>2934.4</v>
+        <v>2864.8</v>
       </c>
       <c r="J251" t="n">
         <v>2750.3</v>
       </c>
       <c r="K251" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="L251" t="n">
-        <v>4920.5</v>
+        <v>4903.3</v>
       </c>
       <c r="M251" t="n">
         <v>4937.1</v>
       </c>
       <c r="N251" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="O251" t="n">
-        <v>5606.9</v>
+        <v>5518.4</v>
       </c>
       <c r="P251" t="n">
         <v>5399.4</v>
       </c>
       <c r="Q251" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="R251" t="n">
         <v>168800</v>
@@ -18210,31 +18210,31 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>2550.6</v>
+        <v>2584.8</v>
       </c>
       <c r="J252" t="n">
         <v>2550.6</v>
       </c>
       <c r="K252" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L252" t="n">
-        <v>3642.6</v>
+        <v>3713.6</v>
       </c>
       <c r="M252" t="n">
         <v>3642.6</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O252" t="n">
-        <v>4513.6</v>
+        <v>4621.8</v>
       </c>
       <c r="P252" t="n">
         <v>4513.6</v>
       </c>
       <c r="Q252" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R252" t="n">
         <v>96800</v>
@@ -18354,31 +18354,31 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>-2448.4</v>
+        <v>-2511.6</v>
       </c>
       <c r="J254" t="n">
         <v>-2448.4</v>
       </c>
       <c r="K254" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="L254" t="n">
-        <v>-938</v>
+        <v>-981.6</v>
       </c>
       <c r="M254" t="n">
         <v>-938</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="O254" t="n">
-        <v>203.6</v>
+        <v>178.5</v>
       </c>
       <c r="P254" t="n">
         <v>203.6</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>-12.3</v>
       </c>
       <c r="R254" t="n">
         <v>13260</v>
@@ -18426,31 +18426,31 @@
         <v>0</v>
       </c>
       <c r="I255" t="n">
-        <v>11337.5</v>
+        <v>9459.6</v>
       </c>
       <c r="J255" t="n">
         <v>11337.5</v>
       </c>
       <c r="K255" t="n">
-        <v>0</v>
+        <v>-16.6</v>
       </c>
       <c r="L255" t="n">
-        <v>39777.8</v>
+        <v>39260.5</v>
       </c>
       <c r="M255" t="n">
         <v>39777.8</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="O255" t="n">
-        <v>61996.8</v>
+        <v>61218.4</v>
       </c>
       <c r="P255" t="n">
         <v>61996.8</v>
       </c>
       <c r="Q255" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="R255" t="n">
         <v>328000</v>
@@ -18498,31 +18498,31 @@
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>5272.2</v>
+        <v>5744.6</v>
       </c>
       <c r="J256" t="n">
         <v>5272.2</v>
       </c>
       <c r="K256" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L256" t="n">
-        <v>5624.7</v>
+        <v>5756.8</v>
       </c>
       <c r="M256" t="n">
         <v>5624.7</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O256" t="n">
-        <v>6119.8</v>
+        <v>6461.5</v>
       </c>
       <c r="P256" t="n">
         <v>6119.8</v>
       </c>
       <c r="Q256" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R256" t="n">
         <v>58500</v>
@@ -18984,40 +18984,40 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G264" t="n">
         <v>49</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I264" t="n">
-        <v>291.8</v>
+        <v>297.4</v>
       </c>
       <c r="J264" t="n">
         <v>291.8</v>
       </c>
       <c r="K264" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="L264" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="M264" t="n">
         <v>833</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O264" t="n">
-        <v>764</v>
+        <v>798</v>
       </c>
       <c r="P264" t="n">
         <v>764</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R264" t="n">
         <v>103500</v>
@@ -19065,31 +19065,31 @@
         <v>0</v>
       </c>
       <c r="I265" t="n">
-        <v>3666.2</v>
+        <v>3646.8</v>
       </c>
       <c r="J265" t="n">
         <v>3670.6</v>
       </c>
       <c r="K265" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="L265" t="n">
-        <v>3728.8</v>
+        <v>3739.2</v>
       </c>
       <c r="M265" t="n">
         <v>3828.1</v>
       </c>
       <c r="N265" t="n">
-        <v>-2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="O265" t="n">
-        <v>4268.8</v>
+        <v>4253.5</v>
       </c>
       <c r="P265" t="n">
         <v>4209</v>
       </c>
       <c r="Q265" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="R265" t="n">
         <v>50100</v>
@@ -19227,13 +19227,13 @@
         <v>-1.6</v>
       </c>
       <c r="O267" t="n">
-        <v>6638.8</v>
+        <v>6713.7</v>
       </c>
       <c r="P267" t="n">
         <v>6676.8</v>
       </c>
       <c r="Q267" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="R267" t="n">
         <v>184000</v>
@@ -19353,31 +19353,31 @@
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>1167</v>
+        <v>1234.7</v>
       </c>
       <c r="J269" t="n">
         <v>1015.3</v>
       </c>
       <c r="K269" t="n">
-        <v>14.9</v>
+        <v>21.6</v>
       </c>
       <c r="L269" t="n">
-        <v>1477.5</v>
+        <v>1485</v>
       </c>
       <c r="M269" t="n">
         <v>1305.3</v>
       </c>
       <c r="N269" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="O269" t="n">
-        <v>1637.5</v>
+        <v>1601.7</v>
       </c>
       <c r="P269" t="n">
         <v>1408.7</v>
       </c>
       <c r="Q269" t="n">
-        <v>16.2</v>
+        <v>13.7</v>
       </c>
       <c r="R269" t="n">
         <v>9010</v>
@@ -19641,31 +19641,31 @@
         <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>1854</v>
+        <v>1924</v>
       </c>
       <c r="J273" t="n">
         <v>1854</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="L273" t="n">
-        <v>2817</v>
+        <v>2897</v>
       </c>
       <c r="M273" t="n">
         <v>2817</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O273" t="n">
-        <v>3774</v>
+        <v>3880.7</v>
       </c>
       <c r="P273" t="n">
         <v>3774</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R273" t="n">
         <v>42000</v>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T275"/>
+  <dimension ref="A1:T276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -624,13 +624,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>15720</v>
+        <v>15970</v>
       </c>
       <c r="S3" t="n">
         <v>15400</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
@@ -696,13 +696,13 @@
         <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>78700</v>
+        <v>80600</v>
       </c>
       <c r="S4" t="n">
         <v>73500</v>
       </c>
       <c r="T4" t="n">
-        <v>7.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>78200</v>
+        <v>79000</v>
       </c>
       <c r="S5" t="n">
         <v>74500</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -840,13 +840,13 @@
         <v>1.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1164000</v>
+        <v>1191000</v>
       </c>
       <c r="S6" t="n">
         <v>1170000</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -912,13 +912,13 @@
         <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>49450</v>
+        <v>50900</v>
       </c>
       <c r="S7" t="n">
         <v>42950</v>
       </c>
       <c r="T7" t="n">
-        <v>15.1</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="8">
@@ -984,13 +984,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>133700</v>
+        <v>134900</v>
       </c>
       <c r="S8" t="n">
         <v>131900</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -1056,13 +1056,13 @@
         <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>87900</v>
+        <v>89000</v>
       </c>
       <c r="S9" t="n">
         <v>88200</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -1128,13 +1128,13 @@
         <v>0.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1433000</v>
+        <v>1422000</v>
       </c>
       <c r="S10" t="n">
         <v>1718000</v>
       </c>
       <c r="T10" t="n">
-        <v>-16.6</v>
+        <v>-17.2</v>
       </c>
     </row>
     <row r="11">
@@ -1200,13 +1200,13 @@
         <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>106000</v>
+        <v>109900</v>
       </c>
       <c r="S11" t="n">
         <v>94600</v>
       </c>
       <c r="T11" t="n">
-        <v>12.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="12">
@@ -1272,13 +1272,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>646000</v>
+        <v>645000</v>
       </c>
       <c r="S12" t="n">
         <v>632000</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>83000</v>
+        <v>84100</v>
       </c>
       <c r="S14" t="n">
         <v>83100</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
@@ -1488,13 +1488,13 @@
         <v>0.1</v>
       </c>
       <c r="R15" t="n">
-        <v>143800</v>
+        <v>145700</v>
       </c>
       <c r="S15" t="n">
         <v>129400</v>
       </c>
       <c r="T15" t="n">
-        <v>11.1</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="16">
@@ -1560,13 +1560,13 @@
         <v>6.3</v>
       </c>
       <c r="R16" t="n">
-        <v>40550</v>
+        <v>41600</v>
       </c>
       <c r="S16" t="n">
         <v>33300</v>
       </c>
       <c r="T16" t="n">
-        <v>21.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="17">
@@ -1632,13 +1632,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>26550</v>
+        <v>27100</v>
       </c>
       <c r="S17" t="n">
         <v>23200</v>
       </c>
       <c r="T17" t="n">
-        <v>14.4</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="18">
@@ -1695,13 +1695,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>38400</v>
+        <v>39300</v>
       </c>
       <c r="S18" t="n">
         <v>38450</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -1767,13 +1767,13 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>18300</v>
+        <v>18550</v>
       </c>
       <c r="S19" t="n">
         <v>17720</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="20">
@@ -1821,13 +1821,13 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>27450</v>
+        <v>27750</v>
       </c>
       <c r="S20" t="n">
         <v>25500</v>
       </c>
       <c r="T20" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1893,13 +1893,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6540</v>
+        <v>6550</v>
       </c>
       <c r="S21" t="n">
         <v>6180</v>
       </c>
       <c r="T21" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1965,13 +1965,13 @@
         <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>427000</v>
+        <v>442000</v>
       </c>
       <c r="S22" t="n">
         <v>388000</v>
       </c>
       <c r="T22" t="n">
-        <v>10.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="23">
@@ -2037,13 +2037,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>9220</v>
+        <v>9770</v>
       </c>
       <c r="S23" t="n">
         <v>9110</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="24">
@@ -2109,13 +2109,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>111000</v>
+        <v>114500</v>
       </c>
       <c r="S24" t="n">
         <v>104600</v>
       </c>
       <c r="T24" t="n">
-        <v>6.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="25">
@@ -2181,13 +2181,13 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8880</v>
+        <v>8950</v>
       </c>
       <c r="S25" t="n">
         <v>8350</v>
       </c>
       <c r="T25" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="26">
@@ -2253,13 +2253,13 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7950</v>
+        <v>8160</v>
       </c>
       <c r="S26" t="n">
         <v>7390</v>
       </c>
       <c r="T26" t="n">
-        <v>7.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="27">
@@ -2325,13 +2325,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1272000</v>
+        <v>1306000</v>
       </c>
       <c r="S27" t="n">
         <v>1168000</v>
       </c>
       <c r="T27" t="n">
-        <v>8.9</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="28">
@@ -2397,13 +2397,13 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>27050</v>
+        <v>27150</v>
       </c>
       <c r="S28" t="n">
         <v>25900</v>
       </c>
       <c r="T28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="29">
@@ -2469,13 +2469,13 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>105700</v>
+        <v>108100</v>
       </c>
       <c r="S29" t="n">
         <v>101100</v>
       </c>
       <c r="T29" t="n">
-        <v>4.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="30">
@@ -2541,13 +2541,13 @@
         <v>-6.1</v>
       </c>
       <c r="R30" t="n">
-        <v>153100</v>
+        <v>155800</v>
       </c>
       <c r="S30" t="n">
         <v>137700</v>
       </c>
       <c r="T30" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="31">
@@ -2613,13 +2613,13 @@
         <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>47700</v>
+        <v>48550</v>
       </c>
       <c r="S31" t="n">
         <v>44650</v>
       </c>
       <c r="T31" t="n">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2685,13 +2685,13 @@
         <v>-5.6</v>
       </c>
       <c r="R32" t="n">
-        <v>27300</v>
+        <v>28300</v>
       </c>
       <c r="S32" t="n">
         <v>26350</v>
       </c>
       <c r="T32" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="33">
@@ -2757,13 +2757,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>403500</v>
+        <v>420000</v>
       </c>
       <c r="S33" t="n">
         <v>423000</v>
       </c>
       <c r="T33" t="n">
-        <v>-4.6</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="34">
@@ -2829,13 +2829,13 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>401000</v>
+        <v>405000</v>
       </c>
       <c r="S34" t="n">
         <v>383000</v>
       </c>
       <c r="T34" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="35">
@@ -2901,13 +2901,13 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>23100</v>
+        <v>23700</v>
       </c>
       <c r="S35" t="n">
         <v>22600</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="36">
@@ -2973,13 +2973,13 @@
         <v>-0.1</v>
       </c>
       <c r="R36" t="n">
-        <v>100600</v>
+        <v>102600</v>
       </c>
       <c r="S36" t="n">
         <v>101000</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="37">
@@ -3045,13 +3045,13 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>390000</v>
+        <v>395500</v>
       </c>
       <c r="S37" t="n">
         <v>388000</v>
       </c>
       <c r="T37" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="38">
@@ -3117,13 +3117,13 @@
         <v>0.1</v>
       </c>
       <c r="R38" t="n">
-        <v>321500</v>
+        <v>331000</v>
       </c>
       <c r="S38" t="n">
         <v>312500</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="39">
@@ -3189,13 +3189,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>163900</v>
+        <v>165900</v>
       </c>
       <c r="S39" t="n">
         <v>157000</v>
       </c>
       <c r="T39" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="40">
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>54000</v>
+        <v>55200</v>
       </c>
       <c r="S40" t="n">
         <v>52900</v>
       </c>
       <c r="T40" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="41">
@@ -3333,13 +3333,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>233000</v>
+        <v>231000</v>
       </c>
       <c r="S41" t="n">
         <v>262500</v>
       </c>
       <c r="T41" t="n">
-        <v>-11.2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="42">
@@ -3405,13 +3405,13 @@
         <v>-0.3</v>
       </c>
       <c r="R42" t="n">
-        <v>27600</v>
+        <v>27800</v>
       </c>
       <c r="S42" t="n">
         <v>28500</v>
       </c>
       <c r="T42" t="n">
-        <v>-3.2</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="43">
@@ -3477,13 +3477,13 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>37450</v>
+        <v>37750</v>
       </c>
       <c r="S43" t="n">
         <v>35400</v>
       </c>
       <c r="T43" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="44">
@@ -3549,13 +3549,13 @@
         <v>0.9</v>
       </c>
       <c r="R44" t="n">
-        <v>312500</v>
+        <v>317000</v>
       </c>
       <c r="S44" t="n">
         <v>267000</v>
       </c>
       <c r="T44" t="n">
-        <v>17</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="45">
@@ -3621,13 +3621,13 @@
         <v>-5.5</v>
       </c>
       <c r="R45" t="n">
-        <v>127200</v>
+        <v>129900</v>
       </c>
       <c r="S45" t="n">
         <v>115900</v>
       </c>
       <c r="T45" t="n">
-        <v>9.699999999999999</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="46">
@@ -3693,13 +3693,13 @@
         <v>0.3</v>
       </c>
       <c r="R46" t="n">
-        <v>31950</v>
+        <v>31650</v>
       </c>
       <c r="S46" t="n">
         <v>23450</v>
       </c>
       <c r="T46" t="n">
-        <v>36.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47">
@@ -3765,13 +3765,13 @@
         <v>-1.9</v>
       </c>
       <c r="R47" t="n">
-        <v>446500</v>
+        <v>459000</v>
       </c>
       <c r="S47" t="n">
         <v>397000</v>
       </c>
       <c r="T47" t="n">
-        <v>12.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="48">
@@ -3837,13 +3837,13 @@
         <v>-7.3</v>
       </c>
       <c r="R48" t="n">
-        <v>91600</v>
+        <v>93700</v>
       </c>
       <c r="S48" t="n">
         <v>85500</v>
       </c>
       <c r="T48" t="n">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="49">
@@ -3909,13 +3909,13 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>33500</v>
+        <v>33900</v>
       </c>
       <c r="S49" t="n">
         <v>34550</v>
       </c>
       <c r="T49" t="n">
-        <v>-3</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="50">
@@ -3981,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>28000</v>
+        <v>28350</v>
       </c>
       <c r="S50" t="n">
         <v>24750</v>
       </c>
       <c r="T50" t="n">
-        <v>13.1</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="51">
@@ -4053,13 +4053,13 @@
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>48200</v>
+        <v>47600</v>
       </c>
       <c r="S51" t="n">
         <v>40350</v>
       </c>
       <c r="T51" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -4125,13 +4125,13 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>81300</v>
+        <v>82300</v>
       </c>
       <c r="S52" t="n">
         <v>74500</v>
       </c>
       <c r="T52" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="53">
@@ -4197,13 +4197,13 @@
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>54300</v>
+        <v>55700</v>
       </c>
       <c r="S53" t="n">
         <v>46450</v>
       </c>
       <c r="T53" t="n">
-        <v>16.9</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="54">
@@ -4260,13 +4260,13 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>14570</v>
+        <v>14840</v>
       </c>
       <c r="S54" t="n">
         <v>13560</v>
       </c>
       <c r="T54" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="55">
@@ -4332,13 +4332,13 @@
         <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>42050</v>
+        <v>42700</v>
       </c>
       <c r="S55" t="n">
         <v>43550</v>
       </c>
       <c r="T55" t="n">
-        <v>-3.4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="56">
@@ -4404,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1263000</v>
+        <v>1278000</v>
       </c>
       <c r="S56" t="n">
         <v>1142000</v>
       </c>
       <c r="T56" t="n">
-        <v>10.6</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="57">
@@ -4476,13 +4476,13 @@
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>40250</v>
+        <v>40850</v>
       </c>
       <c r="S57" t="n">
         <v>38900</v>
       </c>
       <c r="T57" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -4548,13 +4548,13 @@
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>52500</v>
+        <v>54100</v>
       </c>
       <c r="S58" t="n">
         <v>43400</v>
       </c>
       <c r="T58" t="n">
-        <v>21</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="59">
@@ -4620,13 +4620,13 @@
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>392500</v>
+        <v>398500</v>
       </c>
       <c r="S59" t="n">
         <v>384500</v>
       </c>
       <c r="T59" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="60">
@@ -4692,13 +4692,13 @@
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>32200</v>
+        <v>33900</v>
       </c>
       <c r="S60" t="n">
         <v>25500</v>
       </c>
       <c r="T60" t="n">
-        <v>26.3</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="61">
@@ -4764,13 +4764,13 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>247500</v>
+        <v>272500</v>
       </c>
       <c r="S61" t="n">
         <v>190300</v>
       </c>
       <c r="T61" t="n">
-        <v>30.1</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="62">
@@ -4836,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>194300</v>
+        <v>201000</v>
       </c>
       <c r="S62" t="n">
         <v>184800</v>
       </c>
       <c r="T62" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4908,13 +4908,13 @@
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1099000</v>
+        <v>1106000</v>
       </c>
       <c r="S63" t="n">
         <v>999000</v>
       </c>
       <c r="T63" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="64">
@@ -4980,13 +4980,13 @@
         <v>-0.1</v>
       </c>
       <c r="R64" t="n">
-        <v>21900</v>
+        <v>22050</v>
       </c>
       <c r="S64" t="n">
         <v>21350</v>
       </c>
       <c r="T64" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="65">
@@ -5052,13 +5052,13 @@
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>18980</v>
+        <v>19230</v>
       </c>
       <c r="S65" t="n">
         <v>18030</v>
       </c>
       <c r="T65" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="66">
@@ -5124,13 +5124,13 @@
         <v>14.1</v>
       </c>
       <c r="R66" t="n">
-        <v>134200</v>
+        <v>137600</v>
       </c>
       <c r="S66" t="n">
         <v>127300</v>
       </c>
       <c r="T66" t="n">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="67">
@@ -5196,13 +5196,13 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>548000</v>
+        <v>552000</v>
       </c>
       <c r="S67" t="n">
         <v>514000</v>
       </c>
       <c r="T67" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="68">
@@ -5268,13 +5268,13 @@
         <v>-5.9</v>
       </c>
       <c r="R68" t="n">
-        <v>58600</v>
+        <v>61000</v>
       </c>
       <c r="S68" t="n">
         <v>56500</v>
       </c>
       <c r="T68" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
@@ -5340,13 +5340,13 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>21550</v>
+        <v>21800</v>
       </c>
       <c r="S69" t="n">
         <v>20950</v>
       </c>
       <c r="T69" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="70">
@@ -5412,13 +5412,13 @@
         <v>-0.8</v>
       </c>
       <c r="R70" t="n">
-        <v>61500</v>
+        <v>62500</v>
       </c>
       <c r="S70" t="n">
         <v>58200</v>
       </c>
       <c r="T70" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="71">
@@ -5484,13 +5484,13 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>121300</v>
+        <v>129600</v>
       </c>
       <c r="S71" t="n">
         <v>114400</v>
       </c>
       <c r="T71" t="n">
-        <v>6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="72">
@@ -5556,13 +5556,13 @@
         <v>-10.7</v>
       </c>
       <c r="R72" t="n">
-        <v>78500</v>
+        <v>81200</v>
       </c>
       <c r="S72" t="n">
         <v>72200</v>
       </c>
       <c r="T72" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="73">
@@ -5628,13 +5628,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>15630</v>
+        <v>15140</v>
       </c>
       <c r="S73" t="n">
         <v>14100</v>
       </c>
       <c r="T73" t="n">
-        <v>10.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="74">
@@ -5700,13 +5700,13 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>490500</v>
+        <v>496500</v>
       </c>
       <c r="S74" t="n">
         <v>476000</v>
       </c>
       <c r="T74" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="75">
@@ -5772,13 +5772,13 @@
         <v>2.7</v>
       </c>
       <c r="R75" t="n">
-        <v>1071000</v>
+        <v>1097000</v>
       </c>
       <c r="S75" t="n">
         <v>917000</v>
       </c>
       <c r="T75" t="n">
-        <v>16.8</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="76">
@@ -5844,13 +5844,13 @@
         <v>0.3</v>
       </c>
       <c r="R76" t="n">
-        <v>75800</v>
+        <v>76600</v>
       </c>
       <c r="S76" t="n">
         <v>71200</v>
       </c>
       <c r="T76" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="77">
@@ -5907,13 +5907,13 @@
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>19830</v>
+        <v>19940</v>
       </c>
       <c r="S77" t="n">
         <v>18350</v>
       </c>
       <c r="T77" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5979,13 +5979,13 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>26150</v>
+        <v>26650</v>
       </c>
       <c r="S78" t="n">
         <v>26750</v>
       </c>
       <c r="T78" t="n">
-        <v>-2.2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="79">
@@ -6051,13 +6051,13 @@
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>216000</v>
+        <v>222500</v>
       </c>
       <c r="S79" t="n">
         <v>208000</v>
       </c>
       <c r="T79" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -6123,13 +6123,13 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2470</v>
+        <v>2480</v>
       </c>
       <c r="S80" t="n">
         <v>2310</v>
       </c>
       <c r="T80" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="81">
@@ -6195,13 +6195,13 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>35000</v>
+        <v>35600</v>
       </c>
       <c r="S81" t="n">
         <v>34800</v>
       </c>
       <c r="T81" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="82">
@@ -6267,13 +6267,13 @@
         <v>0.6</v>
       </c>
       <c r="R82" t="n">
-        <v>90600</v>
+        <v>91000</v>
       </c>
       <c r="S82" t="n">
         <v>99800</v>
       </c>
       <c r="T82" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -6339,13 +6339,13 @@
         <v>-0.1</v>
       </c>
       <c r="R83" t="n">
-        <v>89400</v>
+        <v>88200</v>
       </c>
       <c r="S83" t="n">
         <v>81400</v>
       </c>
       <c r="T83" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="84">
@@ -6411,13 +6411,13 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>72200</v>
+        <v>72500</v>
       </c>
       <c r="S84" t="n">
         <v>67900</v>
       </c>
       <c r="T84" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="85">
@@ -6483,13 +6483,13 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>22350</v>
+        <v>23100</v>
       </c>
       <c r="S85" t="n">
         <v>21350</v>
       </c>
       <c r="T85" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -6555,13 +6555,13 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>220500</v>
+        <v>221500</v>
       </c>
       <c r="S86" t="n">
         <v>206000</v>
       </c>
       <c r="T86" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="87">
@@ -6627,13 +6627,13 @@
         <v>-4.3</v>
       </c>
       <c r="R87" t="n">
-        <v>3525</v>
+        <v>3625</v>
       </c>
       <c r="S87" t="n">
         <v>3305</v>
       </c>
       <c r="T87" t="n">
-        <v>6.7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -6699,13 +6699,13 @@
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>93900</v>
+        <v>95700</v>
       </c>
       <c r="S88" t="n">
         <v>91500</v>
       </c>
       <c r="T88" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="89">
@@ -6771,13 +6771,13 @@
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>23100</v>
+        <v>23150</v>
       </c>
       <c r="S89" t="n">
         <v>21800</v>
       </c>
       <c r="T89" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="90">
@@ -6843,13 +6843,13 @@
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>96000</v>
+        <v>99700</v>
       </c>
       <c r="S90" t="n">
         <v>117300</v>
       </c>
       <c r="T90" t="n">
-        <v>-18.2</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="91">
@@ -6915,13 +6915,13 @@
         <v>-0.1</v>
       </c>
       <c r="R91" t="n">
-        <v>20600</v>
+        <v>20750</v>
       </c>
       <c r="S91" t="n">
         <v>20650</v>
       </c>
       <c r="T91" t="n">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92">
@@ -6987,13 +6987,13 @@
         <v>-0</v>
       </c>
       <c r="R92" t="n">
-        <v>47800</v>
+        <v>48100</v>
       </c>
       <c r="S92" t="n">
         <v>43800</v>
       </c>
       <c r="T92" t="n">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -7059,13 +7059,13 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>325500</v>
+        <v>336500</v>
       </c>
       <c r="S93" t="n">
         <v>351500</v>
       </c>
       <c r="T93" t="n">
-        <v>-7.4</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="94">
@@ -7131,13 +7131,13 @@
         <v>9.6</v>
       </c>
       <c r="R94" t="n">
-        <v>5980</v>
+        <v>6040</v>
       </c>
       <c r="S94" t="n">
         <v>5470</v>
       </c>
       <c r="T94" t="n">
-        <v>9.300000000000001</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="95">
@@ -7203,13 +7203,13 @@
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>47650</v>
+        <v>47850</v>
       </c>
       <c r="S95" t="n">
         <v>47000</v>
       </c>
       <c r="T95" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="96">
@@ -7275,13 +7275,13 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>19130</v>
+        <v>19170</v>
       </c>
       <c r="S96" t="n">
         <v>18930</v>
       </c>
       <c r="T96" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="97">
@@ -7419,13 +7419,13 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>91900</v>
+        <v>94000</v>
       </c>
       <c r="S98" t="n">
         <v>97800</v>
       </c>
       <c r="T98" t="n">
-        <v>-6</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="99">
@@ -7464,13 +7464,13 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>12620</v>
+        <v>13030</v>
       </c>
       <c r="S99" t="n">
         <v>11620</v>
       </c>
       <c r="T99" t="n">
-        <v>8.6</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="100">
@@ -7608,13 +7608,13 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>272000</v>
+        <v>275500</v>
       </c>
       <c r="S101" t="n">
         <v>311500</v>
       </c>
       <c r="T101" t="n">
-        <v>-12.7</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="102">
@@ -7671,13 +7671,13 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>16620</v>
+        <v>17000</v>
       </c>
       <c r="S102" t="n">
         <v>15690</v>
       </c>
       <c r="T102" t="n">
-        <v>5.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7743,13 +7743,13 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>185700</v>
+        <v>188800</v>
       </c>
       <c r="S103" t="n">
         <v>179100</v>
       </c>
       <c r="T103" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="104">
@@ -7815,13 +7815,13 @@
         <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>75100</v>
+        <v>77100</v>
       </c>
       <c r="S104" t="n">
         <v>67100</v>
       </c>
       <c r="T104" t="n">
-        <v>11.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="105">
@@ -7887,13 +7887,13 @@
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>9675</v>
+        <v>9770</v>
       </c>
       <c r="S105" t="n">
         <v>9210</v>
       </c>
       <c r="T105" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="106">
@@ -7959,13 +7959,13 @@
         <v>0.7</v>
       </c>
       <c r="R106" t="n">
-        <v>9830</v>
+        <v>10100</v>
       </c>
       <c r="S106" t="n">
         <v>9700</v>
       </c>
       <c r="T106" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="107">
@@ -8031,13 +8031,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>499500</v>
+        <v>508000</v>
       </c>
       <c r="S107" t="n">
         <v>557000</v>
       </c>
       <c r="T107" t="n">
-        <v>-10.3</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -8103,13 +8103,13 @@
         <v>-10.9</v>
       </c>
       <c r="R108" t="n">
-        <v>14500</v>
+        <v>14690</v>
       </c>
       <c r="S108" t="n">
         <v>14700</v>
       </c>
       <c r="T108" t="n">
-        <v>-1.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="109">
@@ -8175,13 +8175,13 @@
         <v>0.5</v>
       </c>
       <c r="R109" t="n">
-        <v>210500</v>
+        <v>210000</v>
       </c>
       <c r="S109" t="n">
         <v>208000</v>
       </c>
       <c r="T109" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -8247,13 +8247,13 @@
         <v>-1.1</v>
       </c>
       <c r="R110" t="n">
-        <v>39650</v>
+        <v>39900</v>
       </c>
       <c r="S110" t="n">
         <v>37400</v>
       </c>
       <c r="T110" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="111">
@@ -8319,13 +8319,13 @@
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>34800</v>
+        <v>35450</v>
       </c>
       <c r="S111" t="n">
         <v>31350</v>
       </c>
       <c r="T111" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="112">
@@ -8391,13 +8391,13 @@
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>45950</v>
+        <v>46800</v>
       </c>
       <c r="S112" t="n">
         <v>43200</v>
       </c>
       <c r="T112" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -8439,13 +8439,13 @@
         <v>502</v>
       </c>
       <c r="R113" t="n">
-        <v>7410</v>
+        <v>7510</v>
       </c>
       <c r="S113" t="n">
         <v>7490</v>
       </c>
       <c r="T113" t="n">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="114">
@@ -8511,13 +8511,13 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>34475</v>
+        <v>35750</v>
       </c>
       <c r="S114" t="n">
         <v>34450</v>
       </c>
       <c r="T114" t="n">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="115">
@@ -8583,13 +8583,13 @@
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>243000</v>
+        <v>248500</v>
       </c>
       <c r="S115" t="n">
         <v>234500</v>
       </c>
       <c r="T115" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -8655,13 +8655,13 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>126300</v>
+        <v>127800</v>
       </c>
       <c r="S116" t="n">
         <v>124500</v>
       </c>
       <c r="T116" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="117">
@@ -8727,13 +8727,13 @@
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>314500</v>
+        <v>324500</v>
       </c>
       <c r="S117" t="n">
         <v>296000</v>
       </c>
       <c r="T117" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="118">
@@ -8799,13 +8799,13 @@
         <v>-0.3</v>
       </c>
       <c r="R118" t="n">
-        <v>31250</v>
+        <v>31500</v>
       </c>
       <c r="S118" t="n">
         <v>30650</v>
       </c>
       <c r="T118" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="119">
@@ -8871,13 +8871,13 @@
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>20850</v>
+        <v>21150</v>
       </c>
       <c r="S119" t="n">
         <v>21950</v>
       </c>
       <c r="T119" t="n">
-        <v>-5</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="120">
@@ -8943,13 +8943,13 @@
         <v>-1</v>
       </c>
       <c r="R120" t="n">
-        <v>276000</v>
+        <v>277500</v>
       </c>
       <c r="S120" t="n">
         <v>293500</v>
       </c>
       <c r="T120" t="n">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="121">
@@ -9015,13 +9015,13 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>12390</v>
+        <v>12570</v>
       </c>
       <c r="S121" t="n">
         <v>12150</v>
       </c>
       <c r="T121" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="122">
@@ -9087,13 +9087,13 @@
         <v>0.4</v>
       </c>
       <c r="R122" t="n">
-        <v>74200</v>
+        <v>75600</v>
       </c>
       <c r="S122" t="n">
         <v>68400</v>
       </c>
       <c r="T122" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="123">
@@ -9159,13 +9159,13 @@
         <v>0.5</v>
       </c>
       <c r="R123" t="n">
-        <v>87900</v>
+        <v>89400</v>
       </c>
       <c r="S123" t="n">
         <v>85200</v>
       </c>
       <c r="T123" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="124">
@@ -9231,13 +9231,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>191100</v>
+        <v>192300</v>
       </c>
       <c r="S124" t="n">
         <v>214500</v>
       </c>
       <c r="T124" t="n">
-        <v>-10.9</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="125">
@@ -9303,13 +9303,13 @@
         <v>4.6</v>
       </c>
       <c r="R125" t="n">
-        <v>15730</v>
+        <v>16410</v>
       </c>
       <c r="S125" t="n">
         <v>12780</v>
       </c>
       <c r="T125" t="n">
-        <v>23.1</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="126">
@@ -9375,13 +9375,13 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>56800</v>
+        <v>58000</v>
       </c>
       <c r="S126" t="n">
         <v>52200</v>
       </c>
       <c r="T126" t="n">
-        <v>8.800000000000001</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="127">
@@ -9447,13 +9447,13 @@
         <v>-0.4</v>
       </c>
       <c r="R127" t="n">
-        <v>155300</v>
+        <v>154200</v>
       </c>
       <c r="S127" t="n">
         <v>127300</v>
       </c>
       <c r="T127" t="n">
-        <v>22</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="128">
@@ -9519,13 +9519,13 @@
         <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>23250</v>
+        <v>23450</v>
       </c>
       <c r="S128" t="n">
         <v>22550</v>
       </c>
       <c r="T128" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129">
@@ -9591,13 +9591,13 @@
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>46450</v>
+        <v>47250</v>
       </c>
       <c r="S129" t="n">
         <v>44950</v>
       </c>
       <c r="T129" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="130">
@@ -9663,13 +9663,13 @@
         <v>1.4</v>
       </c>
       <c r="R130" t="n">
-        <v>327000</v>
+        <v>333500</v>
       </c>
       <c r="S130" t="n">
         <v>287000</v>
       </c>
       <c r="T130" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="131">
@@ -9735,13 +9735,13 @@
         <v>-3.5</v>
       </c>
       <c r="R131" t="n">
-        <v>264000</v>
+        <v>276000</v>
       </c>
       <c r="S131" t="n">
         <v>258000</v>
       </c>
       <c r="T131" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
@@ -9807,13 +9807,13 @@
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>99300</v>
+        <v>101900</v>
       </c>
       <c r="S132" t="n">
         <v>89000</v>
       </c>
       <c r="T132" t="n">
-        <v>11.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="133">
@@ -9879,13 +9879,13 @@
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>109300</v>
+        <v>110000</v>
       </c>
       <c r="S133" t="n">
         <v>100700</v>
       </c>
       <c r="T133" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -9951,13 +9951,13 @@
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>64700</v>
+        <v>65700</v>
       </c>
       <c r="S134" t="n">
         <v>64100</v>
       </c>
       <c r="T134" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="135">
@@ -10023,13 +10023,13 @@
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>100500</v>
+        <v>101700</v>
       </c>
       <c r="S135" t="n">
         <v>94600</v>
       </c>
       <c r="T135" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="136">
@@ -10095,13 +10095,13 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>38800</v>
+        <v>39100</v>
       </c>
       <c r="S136" t="n">
         <v>37600</v>
       </c>
       <c r="T136" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
@@ -10167,13 +10167,13 @@
         <v>1.6</v>
       </c>
       <c r="R137" t="n">
-        <v>157000</v>
+        <v>157300</v>
       </c>
       <c r="S137" t="n">
         <v>143200</v>
       </c>
       <c r="T137" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="138">
@@ -10239,13 +10239,13 @@
         <v>-0.8</v>
       </c>
       <c r="R138" t="n">
-        <v>143000</v>
+        <v>146900</v>
       </c>
       <c r="S138" t="n">
         <v>133700</v>
       </c>
       <c r="T138" t="n">
-        <v>7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="139">
@@ -10311,13 +10311,13 @@
         <v>-2.2</v>
       </c>
       <c r="R139" t="n">
-        <v>71500</v>
+        <v>72600</v>
       </c>
       <c r="S139" t="n">
         <v>62500</v>
       </c>
       <c r="T139" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="140">
@@ -10383,13 +10383,13 @@
         <v>0.3</v>
       </c>
       <c r="R140" t="n">
-        <v>172700</v>
+        <v>167300</v>
       </c>
       <c r="S140" t="n">
         <v>165500</v>
       </c>
       <c r="T140" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="141">
@@ -10455,13 +10455,13 @@
         <v>-1.8</v>
       </c>
       <c r="R141" t="n">
-        <v>27150</v>
+        <v>27350</v>
       </c>
       <c r="S141" t="n">
         <v>26500</v>
       </c>
       <c r="T141" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="142">
@@ -10527,13 +10527,13 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>181800</v>
+        <v>185000</v>
       </c>
       <c r="S142" t="n">
         <v>162100</v>
       </c>
       <c r="T142" t="n">
-        <v>12.2</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="143">
@@ -10599,13 +10599,13 @@
         <v>0.7</v>
       </c>
       <c r="R143" t="n">
-        <v>85800</v>
+        <v>90200</v>
       </c>
       <c r="S143" t="n">
         <v>73300</v>
       </c>
       <c r="T143" t="n">
-        <v>17.1</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="144">
@@ -10671,13 +10671,13 @@
         <v>-11.8</v>
       </c>
       <c r="R144" t="n">
-        <v>42700</v>
+        <v>43300</v>
       </c>
       <c r="S144" t="n">
         <v>48000</v>
       </c>
       <c r="T144" t="n">
-        <v>-11</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -10743,13 +10743,13 @@
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>29850</v>
+        <v>30000</v>
       </c>
       <c r="S145" t="n">
         <v>29700</v>
       </c>
       <c r="T145" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -10815,13 +10815,13 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>197600</v>
+        <v>199300</v>
       </c>
       <c r="S146" t="n">
         <v>186700</v>
       </c>
       <c r="T146" t="n">
-        <v>5.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="147">
@@ -10887,13 +10887,13 @@
         <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>15800</v>
+        <v>16450</v>
       </c>
       <c r="S147" t="n">
         <v>14890</v>
       </c>
       <c r="T147" t="n">
-        <v>6.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="148">
@@ -10959,13 +10959,13 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>125900</v>
+        <v>129000</v>
       </c>
       <c r="S148" t="n">
         <v>113800</v>
       </c>
       <c r="T148" t="n">
-        <v>10.6</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="149">
@@ -11031,13 +11031,13 @@
         <v>-1.8</v>
       </c>
       <c r="R149" t="n">
-        <v>100600</v>
+        <v>101800</v>
       </c>
       <c r="S149" t="n">
         <v>118800</v>
       </c>
       <c r="T149" t="n">
-        <v>-15.3</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="150">
@@ -11103,13 +11103,13 @@
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>188100</v>
+        <v>188000</v>
       </c>
       <c r="S150" t="n">
         <v>206500</v>
       </c>
       <c r="T150" t="n">
-        <v>-8.9</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="151">
@@ -11175,13 +11175,13 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>63300</v>
+        <v>64500</v>
       </c>
       <c r="S151" t="n">
         <v>67100</v>
       </c>
       <c r="T151" t="n">
-        <v>-5.7</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="152">
@@ -11247,13 +11247,13 @@
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>53600</v>
+        <v>55200</v>
       </c>
       <c r="S152" t="n">
         <v>49450</v>
       </c>
       <c r="T152" t="n">
-        <v>8.4</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="153">
@@ -11319,13 +11319,13 @@
         <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>7720</v>
+        <v>7810</v>
       </c>
       <c r="S153" t="n">
         <v>7290</v>
       </c>
       <c r="T153" t="n">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="154">
@@ -11364,13 +11364,13 @@
         <v>4.7</v>
       </c>
       <c r="R154" t="n">
-        <v>9100</v>
+        <v>9260</v>
       </c>
       <c r="S154" t="n">
         <v>8760</v>
       </c>
       <c r="T154" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="155">
@@ -11436,13 +11436,13 @@
         <v>4</v>
       </c>
       <c r="R155" t="n">
-        <v>26400</v>
+        <v>27050</v>
       </c>
       <c r="S155" t="n">
         <v>23050</v>
       </c>
       <c r="T155" t="n">
-        <v>14.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="156">
@@ -11508,13 +11508,13 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>97550</v>
+        <v>98900</v>
       </c>
       <c r="S156" t="n">
         <v>89000</v>
       </c>
       <c r="T156" t="n">
-        <v>9.6</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="157">
@@ -11580,13 +11580,13 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>703000</v>
+        <v>741000</v>
       </c>
       <c r="S157" t="n">
         <v>699000</v>
       </c>
       <c r="T157" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
@@ -11625,13 +11625,13 @@
         <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>8850</v>
+        <v>8920</v>
       </c>
       <c r="S158" t="n">
         <v>8470</v>
       </c>
       <c r="T158" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="159">
@@ -11697,13 +11697,13 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>46450</v>
+        <v>46600</v>
       </c>
       <c r="S159" t="n">
         <v>45150</v>
       </c>
       <c r="T159" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="160">
@@ -11769,13 +11769,13 @@
         <v>-2.5</v>
       </c>
       <c r="R160" t="n">
-        <v>41250</v>
+        <v>42500</v>
       </c>
       <c r="S160" t="n">
         <v>39050</v>
       </c>
       <c r="T160" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>108000</v>
+        <v>111200</v>
       </c>
       <c r="S161" t="n">
         <v>112300</v>
       </c>
       <c r="T161" t="n">
-        <v>-3.8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="162">
@@ -11913,13 +11913,13 @@
         <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>203500</v>
+        <v>207500</v>
       </c>
       <c r="S162" t="n">
         <v>200000</v>
       </c>
       <c r="T162" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="163">
@@ -11985,13 +11985,13 @@
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>132800</v>
+        <v>134700</v>
       </c>
       <c r="S163" t="n">
         <v>125400</v>
       </c>
       <c r="T163" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="164">
@@ -12048,13 +12048,13 @@
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>4480</v>
+        <v>4555</v>
       </c>
       <c r="S164" t="n">
         <v>4420</v>
       </c>
       <c r="T164" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="165">
@@ -12068,21 +12068,12 @@
           <t>테크윙</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>반도체소부장</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>KOSDAQ50</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="n">
         <v>133</v>
       </c>
@@ -12165,13 +12156,13 @@
         <v>0.2</v>
       </c>
       <c r="R166" t="n">
-        <v>40500</v>
+        <v>40400</v>
       </c>
       <c r="S166" t="n">
         <v>39350</v>
       </c>
       <c r="T166" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="167">
@@ -12237,13 +12228,13 @@
         <v>4.8</v>
       </c>
       <c r="R167" t="n">
-        <v>59600</v>
+        <v>60500</v>
       </c>
       <c r="S167" t="n">
         <v>65500</v>
       </c>
       <c r="T167" t="n">
-        <v>-9</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="168">
@@ -12309,13 +12300,13 @@
         <v>0.2</v>
       </c>
       <c r="R168" t="n">
-        <v>138700</v>
+        <v>141800</v>
       </c>
       <c r="S168" t="n">
         <v>130000</v>
       </c>
       <c r="T168" t="n">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="169">
@@ -12354,13 +12345,13 @@
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>9470</v>
+        <v>9940</v>
       </c>
       <c r="S169" t="n">
         <v>9000</v>
       </c>
       <c r="T169" t="n">
-        <v>5.2</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="170">
@@ -12426,13 +12417,13 @@
         <v>-5.9</v>
       </c>
       <c r="R170" t="n">
-        <v>129800</v>
+        <v>131000</v>
       </c>
       <c r="S170" t="n">
         <v>129600</v>
       </c>
       <c r="T170" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="171">
@@ -12498,13 +12489,13 @@
         <v>-0.3</v>
       </c>
       <c r="R171" t="n">
-        <v>124100</v>
+        <v>124600</v>
       </c>
       <c r="S171" t="n">
         <v>130000</v>
       </c>
       <c r="T171" t="n">
-        <v>-4.5</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="172">
@@ -12570,13 +12561,13 @@
         <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>19060</v>
+        <v>19280</v>
       </c>
       <c r="S172" t="n">
         <v>18270</v>
       </c>
       <c r="T172" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="173">
@@ -12642,13 +12633,13 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>28000</v>
+        <v>28900</v>
       </c>
       <c r="S173" t="n">
         <v>26900</v>
       </c>
       <c r="T173" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="174">
@@ -12714,13 +12705,13 @@
         <v>-2</v>
       </c>
       <c r="R174" t="n">
-        <v>114600</v>
+        <v>120300</v>
       </c>
       <c r="S174" t="n">
         <v>110500</v>
       </c>
       <c r="T174" t="n">
-        <v>3.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="175">
@@ -12786,13 +12777,13 @@
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>203000</v>
+        <v>204500</v>
       </c>
       <c r="S175" t="n">
         <v>191400</v>
       </c>
       <c r="T175" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="176">
@@ -12831,13 +12822,13 @@
         <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>29400</v>
+        <v>29600</v>
       </c>
       <c r="S176" t="n">
         <v>27250</v>
       </c>
       <c r="T176" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="177">
@@ -12903,13 +12894,13 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>18250</v>
+        <v>18400</v>
       </c>
       <c r="S177" t="n">
         <v>16750</v>
       </c>
       <c r="T177" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="178">
@@ -12975,13 +12966,13 @@
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>74600</v>
+        <v>74800</v>
       </c>
       <c r="S178" t="n">
         <v>64300</v>
       </c>
       <c r="T178" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="179">
@@ -13047,13 +13038,13 @@
         <v>10.7</v>
       </c>
       <c r="R179" t="n">
-        <v>83000</v>
+        <v>83600</v>
       </c>
       <c r="S179" t="n">
         <v>71200</v>
       </c>
       <c r="T179" t="n">
-        <v>16.6</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="180">
@@ -13119,13 +13110,13 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>174700</v>
+        <v>175800</v>
       </c>
       <c r="S180" t="n">
         <v>168500</v>
       </c>
       <c r="T180" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="181">
@@ -13191,13 +13182,13 @@
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>223000</v>
+        <v>229500</v>
       </c>
       <c r="S181" t="n">
         <v>183800</v>
       </c>
       <c r="T181" t="n">
-        <v>21.3</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="182">
@@ -13263,13 +13254,13 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>91900</v>
+        <v>93400</v>
       </c>
       <c r="S182" t="n">
         <v>89400</v>
       </c>
       <c r="T182" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="183">
@@ -13335,13 +13326,13 @@
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>42650</v>
+        <v>43850</v>
       </c>
       <c r="S183" t="n">
         <v>37300</v>
       </c>
       <c r="T183" t="n">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="184">
@@ -13380,13 +13371,13 @@
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>9380</v>
+        <v>9500</v>
       </c>
       <c r="S184" t="n">
         <v>9380</v>
       </c>
       <c r="T184" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="185">
@@ -13452,13 +13443,13 @@
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>54100</v>
+        <v>58600</v>
       </c>
       <c r="S185" t="n">
         <v>48050</v>
       </c>
       <c r="T185" t="n">
-        <v>12.6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="186">
@@ -13524,13 +13515,13 @@
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>40850</v>
+        <v>41550</v>
       </c>
       <c r="S186" t="n">
         <v>38150</v>
       </c>
       <c r="T186" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="187">
@@ -13596,13 +13587,13 @@
         <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>388000</v>
+        <v>392500</v>
       </c>
       <c r="S187" t="n">
         <v>333500</v>
       </c>
       <c r="T187" t="n">
-        <v>16.3</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="188">
@@ -13668,13 +13659,13 @@
         <v>0.3</v>
       </c>
       <c r="R188" t="n">
-        <v>206500</v>
+        <v>207000</v>
       </c>
       <c r="S188" t="n">
         <v>186600</v>
       </c>
       <c r="T188" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="189">
@@ -13740,13 +13731,13 @@
         <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>126100</v>
+        <v>126300</v>
       </c>
       <c r="S189" t="n">
         <v>124000</v>
       </c>
       <c r="T189" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="190">
@@ -13812,13 +13803,13 @@
         <v>-1.5</v>
       </c>
       <c r="R190" t="n">
-        <v>14950</v>
+        <v>15150</v>
       </c>
       <c r="S190" t="n">
         <v>15170</v>
       </c>
       <c r="T190" t="n">
-        <v>-1.5</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="191">
@@ -13884,13 +13875,13 @@
         <v>0.3</v>
       </c>
       <c r="R191" t="n">
-        <v>17760</v>
+        <v>17870</v>
       </c>
       <c r="S191" t="n">
         <v>16950</v>
       </c>
       <c r="T191" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="192">
@@ -13956,13 +13947,13 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>81300</v>
+        <v>81600</v>
       </c>
       <c r="S192" t="n">
         <v>79800</v>
       </c>
       <c r="T192" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="193">
@@ -14028,13 +14019,13 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>248000</v>
+        <v>250500</v>
       </c>
       <c r="S193" t="n">
         <v>255000</v>
       </c>
       <c r="T193" t="n">
-        <v>-2.7</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="194">
@@ -14091,13 +14082,13 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="R194" t="n">
-        <v>108400</v>
+        <v>113200</v>
       </c>
       <c r="S194" t="n">
         <v>87500</v>
       </c>
       <c r="T194" t="n">
-        <v>23.9</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="195">
@@ -14163,13 +14154,13 @@
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>266000</v>
+        <v>273500</v>
       </c>
       <c r="S195" t="n">
         <v>232500</v>
       </c>
       <c r="T195" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="196">
@@ -14235,13 +14226,13 @@
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>40550</v>
+        <v>41400</v>
       </c>
       <c r="S196" t="n">
         <v>38300</v>
       </c>
       <c r="T196" t="n">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="197">
@@ -14280,13 +14271,13 @@
         <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>9600</v>
+        <v>9680</v>
       </c>
       <c r="S197" t="n">
         <v>8560</v>
       </c>
       <c r="T197" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="198">
@@ -14352,13 +14343,13 @@
         <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>69700</v>
+        <v>70500</v>
       </c>
       <c r="S198" t="n">
         <v>67600</v>
       </c>
       <c r="T198" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="199">
@@ -14424,13 +14415,13 @@
         <v>0.1</v>
       </c>
       <c r="R199" t="n">
-        <v>105300</v>
+        <v>106700</v>
       </c>
       <c r="S199" t="n">
         <v>95200</v>
       </c>
       <c r="T199" t="n">
-        <v>10.6</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="200">
@@ -14496,13 +14487,13 @@
         <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>37700</v>
+        <v>38250</v>
       </c>
       <c r="S200" t="n">
         <v>34450</v>
       </c>
       <c r="T200" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201">
@@ -14568,13 +14559,13 @@
         <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>28550</v>
+        <v>28850</v>
       </c>
       <c r="S201" t="n">
         <v>26450</v>
       </c>
       <c r="T201" t="n">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="202">
@@ -14640,13 +14631,13 @@
         <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>33150</v>
+        <v>34100</v>
       </c>
       <c r="S202" t="n">
         <v>33000</v>
       </c>
       <c r="T202" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="203">
@@ -14712,13 +14703,13 @@
         <v>-2.5</v>
       </c>
       <c r="R203" t="n">
-        <v>69900</v>
+        <v>70500</v>
       </c>
       <c r="S203" t="n">
         <v>66900</v>
       </c>
       <c r="T203" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="204">
@@ -14784,13 +14775,13 @@
         <v>-1.6</v>
       </c>
       <c r="R204" t="n">
-        <v>69900</v>
+        <v>70600</v>
       </c>
       <c r="S204" t="n">
         <v>58200</v>
       </c>
       <c r="T204" t="n">
-        <v>20.1</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="205">
@@ -14856,13 +14847,13 @@
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>61500</v>
+        <v>62300</v>
       </c>
       <c r="S205" t="n">
         <v>60100</v>
       </c>
       <c r="T205" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="206">
@@ -14928,13 +14919,13 @@
         <v>-0.2</v>
       </c>
       <c r="R206" t="n">
-        <v>201000</v>
+        <v>205500</v>
       </c>
       <c r="S206" t="n">
         <v>184700</v>
       </c>
       <c r="T206" t="n">
-        <v>8.800000000000001</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="207">
@@ -15000,13 +14991,13 @@
         <v>0.2</v>
       </c>
       <c r="R207" t="n">
-        <v>41050</v>
+        <v>41600</v>
       </c>
       <c r="S207" t="n">
         <v>36100</v>
       </c>
       <c r="T207" t="n">
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="208">
@@ -15072,13 +15063,13 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="R208" t="n">
-        <v>287500</v>
+        <v>305000</v>
       </c>
       <c r="S208" t="n">
         <v>308500</v>
       </c>
       <c r="T208" t="n">
-        <v>-6.8</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="209">
@@ -15144,13 +15135,13 @@
         <v>0.7</v>
       </c>
       <c r="R209" t="n">
-        <v>50400</v>
+        <v>50800</v>
       </c>
       <c r="S209" t="n">
         <v>44700</v>
       </c>
       <c r="T209" t="n">
-        <v>12.8</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="210">
@@ -15216,13 +15207,13 @@
         <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>1523000</v>
+        <v>1556000</v>
       </c>
       <c r="S210" t="n">
         <v>1485000</v>
       </c>
       <c r="T210" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="211">
@@ -15288,13 +15279,13 @@
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>44650</v>
+        <v>45900</v>
       </c>
       <c r="S211" t="n">
         <v>41150</v>
       </c>
       <c r="T211" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="212">
@@ -15360,13 +15351,13 @@
         <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>354500</v>
+        <v>378500</v>
       </c>
       <c r="S212" t="n">
         <v>338500</v>
       </c>
       <c r="T212" t="n">
-        <v>4.7</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="213">
@@ -15432,13 +15423,13 @@
         <v>-8.1</v>
       </c>
       <c r="R213" t="n">
-        <v>47400</v>
+        <v>48450</v>
       </c>
       <c r="S213" t="n">
         <v>42700</v>
       </c>
       <c r="T213" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="214">
@@ -15504,13 +15495,13 @@
         <v>22.7</v>
       </c>
       <c r="R214" t="n">
-        <v>107500</v>
+        <v>110000</v>
       </c>
       <c r="S214" t="n">
         <v>82900</v>
       </c>
       <c r="T214" t="n">
-        <v>29.7</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="215">
@@ -15576,13 +15567,13 @@
         <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>97900</v>
+        <v>100100</v>
       </c>
       <c r="S215" t="n">
         <v>88500</v>
       </c>
       <c r="T215" t="n">
-        <v>10.6</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="216">
@@ -15648,13 +15639,13 @@
         <v>4.8</v>
       </c>
       <c r="R216" t="n">
-        <v>86300</v>
+        <v>88300</v>
       </c>
       <c r="S216" t="n">
         <v>97600</v>
       </c>
       <c r="T216" t="n">
-        <v>-11.6</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="217">
@@ -15720,13 +15711,13 @@
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>62700</v>
+        <v>63600</v>
       </c>
       <c r="S217" t="n">
         <v>59800</v>
       </c>
       <c r="T217" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="218">
@@ -15792,13 +15783,13 @@
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>94200</v>
+        <v>95900</v>
       </c>
       <c r="S218" t="n">
         <v>78800</v>
       </c>
       <c r="T218" t="n">
-        <v>19.5</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="219">
@@ -15864,13 +15855,13 @@
         <v>-10.9</v>
       </c>
       <c r="R219" t="n">
-        <v>101700</v>
+        <v>107000</v>
       </c>
       <c r="S219" t="n">
         <v>103500</v>
       </c>
       <c r="T219" t="n">
-        <v>-1.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="220">
@@ -15936,13 +15927,13 @@
         <v>-3.3</v>
       </c>
       <c r="R220" t="n">
-        <v>40050</v>
+        <v>40900</v>
       </c>
       <c r="S220" t="n">
         <v>38300</v>
       </c>
       <c r="T220" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="221">
@@ -16008,13 +15999,13 @@
         <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>48050</v>
+        <v>49500</v>
       </c>
       <c r="S221" t="n">
         <v>46100</v>
       </c>
       <c r="T221" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="222">
@@ -16080,13 +16071,13 @@
         <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>25100</v>
+        <v>25200</v>
       </c>
       <c r="S222" t="n">
         <v>21600</v>
       </c>
       <c r="T222" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="223">
@@ -16152,13 +16143,13 @@
         <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>37650</v>
+        <v>39300</v>
       </c>
       <c r="S223" t="n">
         <v>33950</v>
       </c>
       <c r="T223" t="n">
-        <v>10.9</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="224">
@@ -16224,13 +16215,13 @@
         <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>235000</v>
+        <v>241500</v>
       </c>
       <c r="S224" t="n">
         <v>243000</v>
       </c>
       <c r="T224" t="n">
-        <v>-3.3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="225">
@@ -16296,13 +16287,13 @@
         <v>0</v>
       </c>
       <c r="R225" t="n">
-        <v>34700</v>
+        <v>35600</v>
       </c>
       <c r="S225" t="n">
         <v>33200</v>
       </c>
       <c r="T225" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="226">
@@ -16368,13 +16359,13 @@
         <v>13.4</v>
       </c>
       <c r="R226" t="n">
-        <v>222500</v>
+        <v>225000</v>
       </c>
       <c r="S226" t="n">
         <v>199600</v>
       </c>
       <c r="T226" t="n">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="227">
@@ -16440,13 +16431,13 @@
         <v>-0.9</v>
       </c>
       <c r="R227" t="n">
-        <v>750000</v>
+        <v>762000</v>
       </c>
       <c r="S227" t="n">
         <v>684000</v>
       </c>
       <c r="T227" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="228">
@@ -16512,13 +16503,13 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>137800</v>
+        <v>138100</v>
       </c>
       <c r="S228" t="n">
         <v>124900</v>
       </c>
       <c r="T228" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="229">
@@ -16584,13 +16575,13 @@
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>136000</v>
+        <v>137600</v>
       </c>
       <c r="S229" t="n">
         <v>131800</v>
       </c>
       <c r="T229" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="230">
@@ -16656,13 +16647,13 @@
         <v>-0.7</v>
       </c>
       <c r="R230" t="n">
-        <v>68400</v>
+        <v>70700</v>
       </c>
       <c r="S230" t="n">
         <v>62500</v>
       </c>
       <c r="T230" t="n">
-        <v>9.4</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="231">
@@ -16728,13 +16719,13 @@
         <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>5360</v>
+        <v>5380</v>
       </c>
       <c r="S231" t="n">
         <v>5200</v>
       </c>
       <c r="T231" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="232">
@@ -16791,13 +16782,13 @@
         <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>450000</v>
+        <v>465000</v>
       </c>
       <c r="S232" t="n">
         <v>433000</v>
       </c>
       <c r="T232" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="233">
@@ -16863,13 +16854,13 @@
         <v>6</v>
       </c>
       <c r="R233" t="n">
-        <v>372000</v>
+        <v>384500</v>
       </c>
       <c r="S233" t="n">
         <v>320000</v>
       </c>
       <c r="T233" t="n">
-        <v>16.2</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="234">
@@ -16935,13 +16926,13 @@
         <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>106000</v>
+        <v>116900</v>
       </c>
       <c r="S234" t="n">
         <v>103000</v>
       </c>
       <c r="T234" t="n">
-        <v>2.9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="235">
@@ -17007,13 +16998,13 @@
         <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>152600</v>
+        <v>153100</v>
       </c>
       <c r="S235" t="n">
         <v>125000</v>
       </c>
       <c r="T235" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="236">
@@ -17079,96 +17070,66 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>42950</v>
+        <v>43650</v>
       </c>
       <c r="S236" t="n">
         <v>39350</v>
       </c>
       <c r="T236" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>294870</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>IPARK현대산업개발</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>1215</v>
-      </c>
-      <c r="G237" t="n">
-        <v>1215</v>
-      </c>
-      <c r="H237" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I237" t="n">
-        <v>5213.7</v>
-      </c>
-      <c r="J237" t="n">
-        <v>5213.7</v>
-      </c>
-      <c r="K237" t="n">
-        <v>0</v>
+        <v>370.4</v>
       </c>
       <c r="L237" t="n">
-        <v>7042.4</v>
-      </c>
-      <c r="M237" t="n">
-        <v>7042.4</v>
-      </c>
-      <c r="N237" t="n">
-        <v>0</v>
+        <v>626.8</v>
       </c>
       <c r="O237" t="n">
-        <v>6523.9</v>
-      </c>
-      <c r="P237" t="n">
-        <v>6523.9</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>0</v>
+        <v>968.5</v>
       </c>
       <c r="R237" t="n">
-        <v>22250</v>
-      </c>
-      <c r="S237" t="n">
-        <v>19850</v>
-      </c>
-      <c r="T237" t="n">
-        <v>12.1</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>298020</t>
+          <t>294870</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>효성티앤씨</t>
+          <t>IPARK현대산업개발</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -17178,69 +17139,69 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>정유·화학</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>1469</v>
+        <v>1215</v>
       </c>
       <c r="G238" t="n">
-        <v>1546</v>
+        <v>1215</v>
       </c>
       <c r="H238" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>5571.2</v>
+        <v>5213.7</v>
       </c>
       <c r="J238" t="n">
-        <v>5006</v>
+        <v>5213.7</v>
       </c>
       <c r="K238" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>6144.7</v>
+        <v>7042.4</v>
       </c>
       <c r="M238" t="n">
-        <v>5962.8</v>
+        <v>7042.4</v>
       </c>
       <c r="N238" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
-        <v>6563.5</v>
+        <v>6523.9</v>
       </c>
       <c r="P238" t="n">
-        <v>6376.2</v>
+        <v>6523.9</v>
       </c>
       <c r="Q238" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>328000</v>
+        <v>22650</v>
       </c>
       <c r="S238" t="n">
-        <v>308000</v>
+        <v>19850</v>
       </c>
       <c r="T238" t="n">
-        <v>6.5</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>298020</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>효성티앤씨</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -17250,69 +17211,69 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>그린인프라</t>
+          <t>정유·화학</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>2812</v>
+        <v>1469</v>
       </c>
       <c r="G239" t="n">
-        <v>2812</v>
+        <v>1546</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I239" t="n">
-        <v>11174.7</v>
+        <v>5571.2</v>
       </c>
       <c r="J239" t="n">
-        <v>10928</v>
+        <v>5006</v>
       </c>
       <c r="K239" t="n">
-        <v>2.3</v>
+        <v>11.3</v>
       </c>
       <c r="L239" t="n">
-        <v>15584.5</v>
+        <v>6144.7</v>
       </c>
       <c r="M239" t="n">
-        <v>15627.4</v>
+        <v>5962.8</v>
       </c>
       <c r="N239" t="n">
-        <v>-0.3</v>
+        <v>3.1</v>
       </c>
       <c r="O239" t="n">
-        <v>20718.5</v>
+        <v>6563.5</v>
       </c>
       <c r="P239" t="n">
-        <v>20992.1</v>
+        <v>6376.2</v>
       </c>
       <c r="Q239" t="n">
-        <v>-1.3</v>
+        <v>2.9</v>
       </c>
       <c r="R239" t="n">
-        <v>2829000</v>
+        <v>339000</v>
       </c>
       <c r="S239" t="n">
-        <v>2417000</v>
+        <v>308000</v>
       </c>
       <c r="T239" t="n">
-        <v>17</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>298050</t>
+          <t>298040</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HS효성첨단소재</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -17322,204 +17283,204 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>정유·화학</t>
+          <t>그린인프라</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>605</v>
+        <v>2812</v>
       </c>
       <c r="G240" t="n">
-        <v>605</v>
+        <v>2812</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
       </c>
       <c r="I240" t="n">
-        <v>2363.8</v>
+        <v>11174.7</v>
       </c>
       <c r="J240" t="n">
-        <v>2341.8</v>
+        <v>10928</v>
       </c>
       <c r="K240" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="L240" t="n">
-        <v>2787.4</v>
+        <v>15584.5</v>
       </c>
       <c r="M240" t="n">
-        <v>2688.2</v>
+        <v>15627.4</v>
       </c>
       <c r="N240" t="n">
-        <v>3.7</v>
+        <v>-0.3</v>
       </c>
       <c r="O240" t="n">
-        <v>3003.6</v>
+        <v>20718.5</v>
       </c>
       <c r="P240" t="n">
-        <v>2873</v>
+        <v>20992.1</v>
       </c>
       <c r="Q240" t="n">
-        <v>4.5</v>
+        <v>-1.3</v>
       </c>
       <c r="R240" t="n">
-        <v>174500</v>
+        <v>2832000</v>
       </c>
       <c r="S240" t="n">
-        <v>160800</v>
+        <v>2417000</v>
       </c>
       <c r="T240" t="n">
-        <v>8.5</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>298380</t>
+          <t>298050</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HS효성첨단소재</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>제약·바이오</t>
+          <t>정유·화학</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>KOSDAQ50,커버리지</t>
-        </is>
+          <t>KOSPI200</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>605</v>
+      </c>
+      <c r="G241" t="n">
+        <v>605</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
       </c>
       <c r="I241" t="n">
-        <v>-750</v>
+        <v>2363.8</v>
       </c>
       <c r="J241" t="n">
-        <v>-750</v>
+        <v>2341.8</v>
       </c>
       <c r="K241" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L241" t="n">
-        <v>-509.5</v>
+        <v>2787.4</v>
       </c>
       <c r="M241" t="n">
-        <v>-509.5</v>
+        <v>2688.2</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O241" t="n">
-        <v>-138</v>
+        <v>3003.6</v>
       </c>
       <c r="P241" t="n">
-        <v>-138</v>
+        <v>2873</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R241" t="n">
-        <v>81900</v>
+        <v>183200</v>
       </c>
       <c r="S241" t="n">
-        <v>66800</v>
+        <v>160800</v>
       </c>
       <c r="T241" t="n">
-        <v>22.6</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>300720</t>
+          <t>298380</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>한일시멘트</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
-        </is>
-      </c>
-      <c r="F242" t="n">
-        <v>400</v>
-      </c>
-      <c r="G242" t="n">
-        <v>400</v>
-      </c>
-      <c r="H242" t="n">
-        <v>0</v>
+          <t>KOSDAQ50,커버리지</t>
+        </is>
       </c>
       <c r="I242" t="n">
-        <v>1150</v>
+        <v>-750</v>
       </c>
       <c r="J242" t="n">
-        <v>1150</v>
+        <v>-750</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>1480</v>
+        <v>-509.5</v>
       </c>
       <c r="M242" t="n">
-        <v>1480</v>
+        <v>-509.5</v>
       </c>
       <c r="N242" t="n">
         <v>0</v>
       </c>
       <c r="O242" t="n">
-        <v>1630</v>
+        <v>-138</v>
       </c>
       <c r="P242" t="n">
-        <v>1630</v>
+        <v>-138</v>
       </c>
       <c r="Q242" t="n">
         <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>14690</v>
+        <v>86600</v>
       </c>
       <c r="S242" t="n">
-        <v>13900</v>
+        <v>66800</v>
       </c>
       <c r="T242" t="n">
-        <v>5.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>302440</t>
+          <t>300720</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SK바이오사이언스</t>
+          <t>한일시멘트</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -17529,69 +17490,69 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>제약·바이오</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>-399</v>
+        <v>400</v>
       </c>
       <c r="G243" t="n">
-        <v>-399</v>
+        <v>400</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>-1294.7</v>
+        <v>1150</v>
       </c>
       <c r="J243" t="n">
-        <v>-1294.7</v>
+        <v>1150</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>-953.7</v>
+        <v>1480</v>
       </c>
       <c r="M243" t="n">
-        <v>-953.7</v>
+        <v>1480</v>
       </c>
       <c r="N243" t="n">
         <v>0</v>
       </c>
       <c r="O243" t="n">
-        <v>-66.7</v>
+        <v>1630</v>
       </c>
       <c r="P243" t="n">
-        <v>-66.7</v>
+        <v>1630</v>
       </c>
       <c r="Q243" t="n">
         <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>35900</v>
+        <v>14830</v>
       </c>
       <c r="S243" t="n">
-        <v>33850</v>
+        <v>13900</v>
       </c>
       <c r="T243" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>302440</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>SK바이오사이언스</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -17601,69 +17562,69 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>철강·비철</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>282</v>
+        <v>-399</v>
       </c>
       <c r="G244" t="n">
-        <v>282</v>
+        <v>-399</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>987</v>
+        <v>-1294.7</v>
       </c>
       <c r="J244" t="n">
-        <v>987</v>
+        <v>-1294.7</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
       </c>
       <c r="L244" t="n">
-        <v>1165</v>
+        <v>-953.7</v>
       </c>
       <c r="M244" t="n">
-        <v>1165</v>
+        <v>-953.7</v>
       </c>
       <c r="N244" t="n">
         <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>1412.7</v>
+        <v>-66.7</v>
       </c>
       <c r="P244" t="n">
-        <v>1412.7</v>
+        <v>-66.7</v>
       </c>
       <c r="Q244" t="n">
         <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>130800</v>
+        <v>36850</v>
       </c>
       <c r="S244" t="n">
-        <v>126400</v>
+        <v>33850</v>
       </c>
       <c r="T244" t="n">
-        <v>3.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>307950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>현대오토에버</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -17673,69 +17634,69 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>인터넷/AI</t>
+          <t>철강·비철</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>764</v>
+        <v>282</v>
       </c>
       <c r="G245" t="n">
-        <v>764</v>
+        <v>282</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>2813.8</v>
+        <v>987</v>
       </c>
       <c r="J245" t="n">
-        <v>2805.4</v>
+        <v>987</v>
       </c>
       <c r="K245" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>3525.4</v>
+        <v>1165</v>
       </c>
       <c r="M245" t="n">
-        <v>3500.2</v>
+        <v>1165</v>
       </c>
       <c r="N245" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>4478.6</v>
+        <v>1412.7</v>
       </c>
       <c r="P245" t="n">
-        <v>4478.6</v>
+        <v>1412.7</v>
       </c>
       <c r="Q245" t="n">
         <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>401000</v>
+        <v>132000</v>
       </c>
       <c r="S245" t="n">
-        <v>364500</v>
+        <v>126400</v>
       </c>
       <c r="T245" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>307950</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>현대오토에버</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -17745,7 +17706,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>금융-은행지주</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -17754,60 +17715,60 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>12920</v>
+        <v>764</v>
       </c>
       <c r="G246" t="n">
-        <v>12920</v>
+        <v>764</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>43798.2</v>
+        <v>2813.8</v>
       </c>
       <c r="J246" t="n">
-        <v>43798.2</v>
+        <v>2805.4</v>
       </c>
       <c r="K246" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L246" t="n">
-        <v>47992.2</v>
+        <v>3525.4</v>
       </c>
       <c r="M246" t="n">
-        <v>47992.2</v>
+        <v>3500.2</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O246" t="n">
-        <v>50426.3</v>
+        <v>4478.6</v>
       </c>
       <c r="P246" t="n">
-        <v>50426.3</v>
+        <v>4478.6</v>
       </c>
       <c r="Q246" t="n">
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>34300</v>
+        <v>412000</v>
       </c>
       <c r="S246" t="n">
-        <v>33600</v>
+        <v>364500</v>
       </c>
       <c r="T246" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -17817,204 +17778,204 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>90</v>
+        <v>12920</v>
       </c>
       <c r="G247" t="n">
-        <v>90</v>
+        <v>12920</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>570</v>
+        <v>43798.2</v>
       </c>
       <c r="J247" t="n">
-        <v>640</v>
+        <v>43798.2</v>
       </c>
       <c r="K247" t="n">
-        <v>-10.9</v>
+        <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>1170</v>
+        <v>47992.2</v>
       </c>
       <c r="M247" t="n">
-        <v>1060</v>
+        <v>47992.2</v>
       </c>
       <c r="N247" t="n">
-        <v>10.4</v>
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>50426.3</v>
+      </c>
+      <c r="P247" t="n">
+        <v>50426.3</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>8750</v>
+        <v>34800</v>
       </c>
       <c r="S247" t="n">
-        <v>6400</v>
+        <v>33600</v>
       </c>
       <c r="T247" t="n">
-        <v>36.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>319660</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>459</v>
+        <v>90</v>
       </c>
       <c r="G248" t="n">
-        <v>459</v>
+        <v>90</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>1791.6</v>
+        <v>570</v>
       </c>
       <c r="J248" t="n">
-        <v>1791.6</v>
+        <v>640</v>
       </c>
       <c r="K248" t="n">
-        <v>0</v>
+        <v>-10.9</v>
       </c>
       <c r="L248" t="n">
-        <v>2256</v>
+        <v>1170</v>
       </c>
       <c r="M248" t="n">
-        <v>2256</v>
+        <v>1060</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
-      </c>
-      <c r="O248" t="n">
-        <v>2675.4</v>
-      </c>
-      <c r="P248" t="n">
-        <v>2675.4</v>
-      </c>
-      <c r="Q248" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="R248" t="n">
-        <v>115900</v>
+        <v>8320</v>
       </c>
       <c r="S248" t="n">
-        <v>129600</v>
+        <v>6400</v>
       </c>
       <c r="T248" t="n">
-        <v>-10.6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>323410</t>
+          <t>319660</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>카카오뱅크</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>금융-은행지주</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>1823</v>
+        <v>459</v>
       </c>
       <c r="G249" t="n">
-        <v>1823</v>
+        <v>459</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>7379.8</v>
+        <v>1791.6</v>
       </c>
       <c r="J249" t="n">
-        <v>7127</v>
+        <v>1791.6</v>
       </c>
       <c r="K249" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>8847.5</v>
+        <v>2256</v>
       </c>
       <c r="M249" t="n">
-        <v>8312.1</v>
+        <v>2256</v>
       </c>
       <c r="N249" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>9776</v>
+        <v>2675.4</v>
       </c>
       <c r="P249" t="n">
-        <v>9149</v>
+        <v>2675.4</v>
       </c>
       <c r="Q249" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>21750</v>
+        <v>118400</v>
       </c>
       <c r="S249" t="n">
-        <v>22100</v>
+        <v>129600</v>
       </c>
       <c r="T249" t="n">
-        <v>-1.6</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>323410</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>카카오뱅크</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -18024,7 +17985,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>제약·바이오</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -18033,60 +17994,60 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>854</v>
+        <v>1823</v>
       </c>
       <c r="G250" t="n">
-        <v>854</v>
+        <v>1823</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>3525.8</v>
+        <v>7379.8</v>
       </c>
       <c r="J250" t="n">
-        <v>3432.6</v>
+        <v>7127</v>
       </c>
       <c r="K250" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="L250" t="n">
-        <v>4714.4</v>
+        <v>8847.5</v>
       </c>
       <c r="M250" t="n">
-        <v>4577.6</v>
+        <v>8312.1</v>
       </c>
       <c r="N250" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="O250" t="n">
-        <v>5789</v>
+        <v>9776</v>
       </c>
       <c r="P250" t="n">
-        <v>5637.4</v>
+        <v>9149</v>
       </c>
       <c r="Q250" t="n">
-        <v>2.7</v>
+        <v>6.9</v>
       </c>
       <c r="R250" t="n">
-        <v>83200</v>
+        <v>22000</v>
       </c>
       <c r="S250" t="n">
-        <v>79000</v>
+        <v>22100</v>
       </c>
       <c r="T250" t="n">
-        <v>5.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>329180</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -18096,7 +18057,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>제약·바이오</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -18105,60 +18066,60 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>9910</v>
+        <v>854</v>
       </c>
       <c r="G251" t="n">
-        <v>9910</v>
+        <v>854</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>40238.8</v>
+        <v>3525.8</v>
       </c>
       <c r="J251" t="n">
-        <v>40238.8</v>
+        <v>3432.6</v>
       </c>
       <c r="K251" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L251" t="n">
-        <v>46858.8</v>
+        <v>4714.4</v>
       </c>
       <c r="M251" t="n">
-        <v>46858.8</v>
+        <v>4577.6</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O251" t="n">
-        <v>54155.1</v>
+        <v>5789</v>
       </c>
       <c r="P251" t="n">
-        <v>54155.1</v>
+        <v>5637.4</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R251" t="n">
-        <v>495000</v>
+        <v>85400</v>
       </c>
       <c r="S251" t="n">
-        <v>481000</v>
+        <v>79000</v>
       </c>
       <c r="T251" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>352820</t>
+          <t>329180</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -18168,7 +18129,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -18177,60 +18138,60 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>1551</v>
+        <v>9910</v>
       </c>
       <c r="G252" t="n">
-        <v>1551</v>
+        <v>9910</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>2850</v>
+        <v>40238.8</v>
       </c>
       <c r="J252" t="n">
-        <v>2864.8</v>
+        <v>40238.8</v>
       </c>
       <c r="K252" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>4902.5</v>
+        <v>46858.8</v>
       </c>
       <c r="M252" t="n">
-        <v>4903.3</v>
+        <v>46858.8</v>
       </c>
       <c r="N252" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>5471.9</v>
+        <v>54155.1</v>
       </c>
       <c r="P252" t="n">
-        <v>5518.4</v>
+        <v>54155.1</v>
       </c>
       <c r="Q252" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>180500</v>
+        <v>506000</v>
       </c>
       <c r="S252" t="n">
-        <v>168800</v>
+        <v>481000</v>
       </c>
       <c r="T252" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>352820</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -18240,213 +18201,213 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>전기전자</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>640</v>
+        <v>1551</v>
       </c>
       <c r="G253" t="n">
-        <v>640</v>
+        <v>1551</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
       </c>
       <c r="I253" t="n">
-        <v>2759</v>
+        <v>2850</v>
       </c>
       <c r="J253" t="n">
-        <v>2584.8</v>
+        <v>2864.8</v>
       </c>
       <c r="K253" t="n">
-        <v>6.7</v>
+        <v>-0.5</v>
       </c>
       <c r="L253" t="n">
-        <v>4080.7</v>
+        <v>4902.5</v>
       </c>
       <c r="M253" t="n">
-        <v>3713.6</v>
+        <v>4903.3</v>
       </c>
       <c r="N253" t="n">
-        <v>9.9</v>
+        <v>-0</v>
       </c>
       <c r="O253" t="n">
-        <v>5068.4</v>
+        <v>5471.9</v>
       </c>
       <c r="P253" t="n">
-        <v>4621.8</v>
+        <v>5518.4</v>
       </c>
       <c r="Q253" t="n">
-        <v>9.699999999999999</v>
+        <v>-0.8</v>
       </c>
       <c r="R253" t="n">
-        <v>102900</v>
+        <v>185000</v>
       </c>
       <c r="S253" t="n">
-        <v>96800</v>
+        <v>168800</v>
       </c>
       <c r="T253" t="n">
-        <v>6.3</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>357780</t>
+          <t>353200</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>전기전자</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>443</v>
+        <v>640</v>
       </c>
       <c r="G254" t="n">
-        <v>443</v>
+        <v>640</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>1933.3</v>
+        <v>2759</v>
       </c>
       <c r="J254" t="n">
-        <v>1933.3</v>
+        <v>2584.8</v>
       </c>
       <c r="K254" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="L254" t="n">
-        <v>2584.6</v>
+        <v>4080.7</v>
       </c>
       <c r="M254" t="n">
-        <v>2584.6</v>
+        <v>3713.6</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="O254" t="n">
-        <v>3333.4</v>
+        <v>5068.4</v>
       </c>
       <c r="P254" t="n">
-        <v>3333.4</v>
+        <v>4621.8</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R254" t="n">
-        <v>290500</v>
+        <v>103800</v>
       </c>
       <c r="S254" t="n">
-        <v>252500</v>
+        <v>96800</v>
       </c>
       <c r="T254" t="n">
-        <v>15</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>361610</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SK아이이테크놀로지</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2차전지</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>-664</v>
+        <v>443</v>
       </c>
       <c r="G255" t="n">
-        <v>-664</v>
+        <v>443</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
       </c>
       <c r="I255" t="n">
-        <v>-2433.7</v>
+        <v>1933.3</v>
       </c>
       <c r="J255" t="n">
-        <v>-2511.6</v>
+        <v>1933.3</v>
       </c>
       <c r="K255" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>-990.8</v>
+        <v>2584.6</v>
       </c>
       <c r="M255" t="n">
-        <v>-981.6</v>
+        <v>2584.6</v>
       </c>
       <c r="N255" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
-        <v>69.7</v>
+        <v>3333.4</v>
       </c>
       <c r="P255" t="n">
-        <v>178.5</v>
+        <v>3333.4</v>
       </c>
       <c r="Q255" t="n">
-        <v>-61</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>14210</v>
+        <v>295000</v>
       </c>
       <c r="S255" t="n">
-        <v>13260</v>
+        <v>252500</v>
       </c>
       <c r="T255" t="n">
-        <v>7.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>373220</t>
+          <t>361610</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>SK아이이테크놀로지</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -18461,64 +18422,64 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>2034</v>
+        <v>-664</v>
       </c>
       <c r="G256" t="n">
-        <v>2034</v>
+        <v>-664</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>8254.1</v>
+        <v>-2433.7</v>
       </c>
       <c r="J256" t="n">
-        <v>9459.6</v>
+        <v>-2511.6</v>
       </c>
       <c r="K256" t="n">
-        <v>-12.7</v>
+        <v>3.1</v>
       </c>
       <c r="L256" t="n">
-        <v>38513.5</v>
+        <v>-990.8</v>
       </c>
       <c r="M256" t="n">
-        <v>39260.5</v>
+        <v>-981.6</v>
       </c>
       <c r="N256" t="n">
-        <v>-1.9</v>
+        <v>-0.9</v>
       </c>
       <c r="O256" t="n">
-        <v>61264.2</v>
+        <v>69.7</v>
       </c>
       <c r="P256" t="n">
-        <v>61218.4</v>
+        <v>178.5</v>
       </c>
       <c r="Q256" t="n">
-        <v>0.1</v>
+        <v>-61</v>
       </c>
       <c r="R256" t="n">
-        <v>352500</v>
+        <v>14980</v>
       </c>
       <c r="S256" t="n">
-        <v>328000</v>
+        <v>13260</v>
       </c>
       <c r="T256" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>373220</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -18528,7 +18489,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>2차전지</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -18537,204 +18498,204 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>1238</v>
+        <v>2034</v>
       </c>
       <c r="G257" t="n">
-        <v>1238</v>
+        <v>2034</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>5744.6</v>
+        <v>8254.1</v>
       </c>
       <c r="J257" t="n">
-        <v>5744.6</v>
+        <v>9459.6</v>
       </c>
       <c r="K257" t="n">
-        <v>0</v>
+        <v>-12.7</v>
       </c>
       <c r="L257" t="n">
-        <v>5756.8</v>
+        <v>38513.5</v>
       </c>
       <c r="M257" t="n">
-        <v>5756.8</v>
+        <v>39260.5</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="O257" t="n">
-        <v>6461.5</v>
+        <v>61264.2</v>
       </c>
       <c r="P257" t="n">
-        <v>6461.5</v>
+        <v>61218.4</v>
       </c>
       <c r="Q257" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R257" t="n">
-        <v>70700</v>
+        <v>360000</v>
       </c>
       <c r="S257" t="n">
-        <v>58500</v>
+        <v>328000</v>
       </c>
       <c r="T257" t="n">
-        <v>20.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>376300</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>디어유</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>102</v>
+        <v>1238</v>
       </c>
       <c r="G258" t="n">
-        <v>102</v>
+        <v>1238</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
       </c>
       <c r="I258" t="n">
-        <v>389.7</v>
+        <v>5744.6</v>
       </c>
       <c r="J258" t="n">
-        <v>416.1</v>
+        <v>5744.6</v>
       </c>
       <c r="K258" t="n">
-        <v>-6.3</v>
+        <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>463.1</v>
+        <v>5756.8</v>
       </c>
       <c r="M258" t="n">
-        <v>519.5</v>
+        <v>5756.8</v>
       </c>
       <c r="N258" t="n">
-        <v>-10.9</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>536.6</v>
+        <v>6461.5</v>
       </c>
       <c r="P258" t="n">
-        <v>583.6</v>
+        <v>6461.5</v>
       </c>
       <c r="Q258" t="n">
-        <v>-8.1</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>19540</v>
+        <v>72000</v>
       </c>
       <c r="S258" t="n">
-        <v>19840</v>
+        <v>58500</v>
       </c>
       <c r="T258" t="n">
-        <v>-1.5</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>377300</t>
+          <t>376300</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>카카오페이</t>
+          <t>디어유</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>금융-카드기타</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="G259" t="n">
-        <v>360</v>
+        <v>102</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>1618</v>
+        <v>389.7</v>
       </c>
       <c r="J259" t="n">
-        <v>1423.8</v>
+        <v>416.1</v>
       </c>
       <c r="K259" t="n">
-        <v>13.6</v>
+        <v>-6.3</v>
       </c>
       <c r="L259" t="n">
-        <v>2086.2</v>
+        <v>463.1</v>
       </c>
       <c r="M259" t="n">
-        <v>1930.7</v>
+        <v>519.5</v>
       </c>
       <c r="N259" t="n">
-        <v>8.1</v>
+        <v>-10.9</v>
       </c>
       <c r="O259" t="n">
-        <v>2755.2</v>
+        <v>536.6</v>
       </c>
       <c r="P259" t="n">
-        <v>2725.7</v>
+        <v>583.6</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.1</v>
+        <v>-8.1</v>
       </c>
       <c r="R259" t="n">
-        <v>41550</v>
+        <v>19660</v>
       </c>
       <c r="S259" t="n">
-        <v>42600</v>
+        <v>19840</v>
       </c>
       <c r="T259" t="n">
-        <v>-2.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>383220</t>
+          <t>377300</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>F&amp;F</t>
+          <t>카카오페이</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -18744,7 +18705,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>섬유·의류</t>
+          <t>금융-카드기타</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -18753,105 +18714,132 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>983</v>
+        <v>360</v>
       </c>
       <c r="G260" t="n">
-        <v>983</v>
+        <v>360</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
       </c>
       <c r="I260" t="n">
-        <v>5358.4</v>
+        <v>1618</v>
       </c>
       <c r="J260" t="n">
-        <v>5370.7</v>
+        <v>1423.8</v>
       </c>
       <c r="K260" t="n">
-        <v>-0.2</v>
+        <v>13.6</v>
       </c>
       <c r="L260" t="n">
-        <v>5739.4</v>
+        <v>2086.2</v>
       </c>
       <c r="M260" t="n">
-        <v>5709.5</v>
+        <v>1930.7</v>
       </c>
       <c r="N260" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="O260" t="n">
-        <v>6274.3</v>
+        <v>2755.2</v>
       </c>
       <c r="P260" t="n">
-        <v>6184.4</v>
+        <v>2725.7</v>
       </c>
       <c r="Q260" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="R260" t="n">
-        <v>66300</v>
+        <v>42000</v>
       </c>
       <c r="S260" t="n">
-        <v>80500</v>
+        <v>42600</v>
       </c>
       <c r="T260" t="n">
-        <v>-17.6</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>389500</t>
+          <t>383220</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>에스비비테크</t>
+          <t>F&amp;F</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>섬유·의류</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>-12</v>
+        <v>983</v>
       </c>
       <c r="G261" t="n">
-        <v>-12</v>
+        <v>983</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
       </c>
+      <c r="I261" t="n">
+        <v>5358.4</v>
+      </c>
+      <c r="J261" t="n">
+        <v>5370.7</v>
+      </c>
+      <c r="K261" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L261" t="n">
+        <v>5739.4</v>
+      </c>
+      <c r="M261" t="n">
+        <v>5709.5</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O261" t="n">
+        <v>6274.3</v>
+      </c>
+      <c r="P261" t="n">
+        <v>6184.4</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>1.5</v>
+      </c>
       <c r="R261" t="n">
-        <v>32900</v>
+        <v>67000</v>
       </c>
       <c r="S261" t="n">
-        <v>30350</v>
+        <v>80500</v>
       </c>
       <c r="T261" t="n">
-        <v>8.4</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>389650</t>
+          <t>389500</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>넥스트바이오메디컬</t>
+          <t>에스비비테크</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -18861,7 +18849,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -18879,141 +18867,141 @@
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>39400</v>
+        <v>33500</v>
       </c>
       <c r="S262" t="n">
-        <v>34650</v>
+        <v>30350</v>
       </c>
       <c r="T262" t="n">
-        <v>13.7</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>402340</t>
+          <t>389650</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>넥스트바이오메디컬</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>지주회사</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>99084</v>
+        <v>-12</v>
       </c>
       <c r="G263" t="n">
-        <v>99084</v>
+        <v>-12</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
       </c>
-      <c r="I263" t="n">
-        <v>434130.4</v>
-      </c>
-      <c r="J263" t="n">
-        <v>434130.4</v>
-      </c>
-      <c r="K263" t="n">
-        <v>0</v>
-      </c>
-      <c r="L263" t="n">
-        <v>547499.1</v>
-      </c>
-      <c r="M263" t="n">
-        <v>547499.1</v>
-      </c>
-      <c r="N263" t="n">
-        <v>0</v>
-      </c>
-      <c r="O263" t="n">
-        <v>587557.6</v>
-      </c>
-      <c r="P263" t="n">
-        <v>587557.6</v>
-      </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
-        <v>941000</v>
+        <v>40050</v>
       </c>
       <c r="S263" t="n">
-        <v>1038000</v>
+        <v>34650</v>
       </c>
       <c r="T263" t="n">
-        <v>-9.300000000000001</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>403870</t>
+          <t>402340</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>지주회사</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>227</v>
+        <v>99084</v>
       </c>
       <c r="G264" t="n">
-        <v>227</v>
+        <v>99084</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
       </c>
+      <c r="I264" t="n">
+        <v>434130.4</v>
+      </c>
+      <c r="J264" t="n">
+        <v>434130.4</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>547499.1</v>
+      </c>
+      <c r="M264" t="n">
+        <v>547499.1</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>587557.6</v>
+      </c>
+      <c r="P264" t="n">
+        <v>587557.6</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>0</v>
+      </c>
       <c r="R264" t="n">
-        <v>33800</v>
+        <v>939000</v>
       </c>
       <c r="S264" t="n">
-        <v>34600</v>
+        <v>1038000</v>
       </c>
       <c r="T264" t="n">
-        <v>-2.3</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>403870</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -19023,79 +19011,52 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>전기전자</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="G265" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
       </c>
-      <c r="I265" t="n">
-        <v>297.4</v>
-      </c>
-      <c r="J265" t="n">
-        <v>297.4</v>
-      </c>
-      <c r="K265" t="n">
-        <v>0</v>
-      </c>
-      <c r="L265" t="n">
-        <v>836</v>
-      </c>
-      <c r="M265" t="n">
-        <v>836</v>
-      </c>
-      <c r="N265" t="n">
-        <v>0</v>
-      </c>
-      <c r="O265" t="n">
-        <v>798</v>
-      </c>
-      <c r="P265" t="n">
-        <v>798</v>
-      </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
-        <v>107100</v>
+        <v>34400</v>
       </c>
       <c r="S265" t="n">
-        <v>103500</v>
+        <v>34600</v>
       </c>
       <c r="T265" t="n">
-        <v>3.5</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>전기전자</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -19104,204 +19065,204 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>966</v>
+        <v>55</v>
       </c>
       <c r="G266" t="n">
-        <v>966</v>
+        <v>55</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
       </c>
       <c r="I266" t="n">
-        <v>3646.8</v>
+        <v>297.4</v>
       </c>
       <c r="J266" t="n">
-        <v>3646.8</v>
+        <v>297.4</v>
       </c>
       <c r="K266" t="n">
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>3749.2</v>
+        <v>836</v>
       </c>
       <c r="M266" t="n">
-        <v>3739.2</v>
+        <v>836</v>
       </c>
       <c r="N266" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>4301.8</v>
+        <v>798</v>
       </c>
       <c r="P266" t="n">
-        <v>4253.5</v>
+        <v>798</v>
       </c>
       <c r="Q266" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>48600</v>
+        <v>110300</v>
       </c>
       <c r="S266" t="n">
-        <v>50100</v>
+        <v>103500</v>
       </c>
       <c r="T266" t="n">
-        <v>-3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>86</v>
+        <v>966</v>
       </c>
       <c r="G267" t="n">
-        <v>86</v>
+        <v>966</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>859</v>
+        <v>3646.8</v>
       </c>
       <c r="J267" t="n">
-        <v>859</v>
+        <v>3646.8</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>2158</v>
+        <v>3749.2</v>
       </c>
       <c r="M267" t="n">
-        <v>2158</v>
+        <v>3739.2</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O267" t="n">
-        <v>2618</v>
+        <v>4301.8</v>
       </c>
       <c r="P267" t="n">
-        <v>2618</v>
+        <v>4253.5</v>
       </c>
       <c r="Q267" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="R267" t="n">
-        <v>55800</v>
+        <v>49150</v>
       </c>
       <c r="S267" t="n">
-        <v>63400</v>
+        <v>50100</v>
       </c>
       <c r="T267" t="n">
-        <v>-12</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>443060</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>1027</v>
+        <v>86</v>
       </c>
       <c r="G268" t="n">
-        <v>1027</v>
+        <v>86</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>4204.2</v>
+        <v>859</v>
       </c>
       <c r="J268" t="n">
-        <v>4204.2</v>
+        <v>859</v>
       </c>
       <c r="K268" t="n">
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>5358.1</v>
+        <v>2158</v>
       </c>
       <c r="M268" t="n">
-        <v>5358.1</v>
+        <v>2158</v>
       </c>
       <c r="N268" t="n">
         <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>6713.7</v>
+        <v>2618</v>
       </c>
       <c r="P268" t="n">
-        <v>6713.7</v>
+        <v>2618</v>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>190800</v>
+        <v>57100</v>
       </c>
       <c r="S268" t="n">
-        <v>184000</v>
+        <v>63400</v>
       </c>
       <c r="T268" t="n">
-        <v>3.7</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>456040</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>OCI</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -19311,69 +19272,69 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>그린인프라</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>462</v>
+        <v>1027</v>
       </c>
       <c r="G269" t="n">
-        <v>462</v>
+        <v>1027</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>1648</v>
+        <v>4204.2</v>
       </c>
       <c r="J269" t="n">
-        <v>1648</v>
+        <v>4204.2</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>1880.7</v>
+        <v>5358.1</v>
       </c>
       <c r="M269" t="n">
-        <v>1880.7</v>
+        <v>5358.1</v>
       </c>
       <c r="N269" t="n">
         <v>0</v>
       </c>
       <c r="O269" t="n">
-        <v>1966.7</v>
+        <v>6713.7</v>
       </c>
       <c r="P269" t="n">
-        <v>1966.7</v>
+        <v>6713.7</v>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>75800</v>
+        <v>196400</v>
       </c>
       <c r="S269" t="n">
-        <v>68900</v>
+        <v>184000</v>
       </c>
       <c r="T269" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>460860</t>
+          <t>456040</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>동국제강</t>
+          <t>OCI</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -19383,69 +19344,69 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>철강·비철</t>
+          <t>그린인프라</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>337</v>
+        <v>462</v>
       </c>
       <c r="G270" t="n">
-        <v>337</v>
+        <v>462</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
       </c>
       <c r="I270" t="n">
-        <v>1234.7</v>
+        <v>1648</v>
       </c>
       <c r="J270" t="n">
-        <v>1234.7</v>
+        <v>1648</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>1485</v>
+        <v>1880.7</v>
       </c>
       <c r="M270" t="n">
-        <v>1485</v>
+        <v>1880.7</v>
       </c>
       <c r="N270" t="n">
         <v>0</v>
       </c>
       <c r="O270" t="n">
-        <v>1601.7</v>
+        <v>1966.7</v>
       </c>
       <c r="P270" t="n">
-        <v>1601.7</v>
+        <v>1966.7</v>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>9650</v>
+        <v>77400</v>
       </c>
       <c r="S270" t="n">
-        <v>9010</v>
+        <v>68900</v>
       </c>
       <c r="T270" t="n">
-        <v>7.1</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>462870</t>
+          <t>460860</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>시프트업</t>
+          <t>동국제강</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -19455,7 +19416,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>철강·비철</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -19464,60 +19425,60 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="G271" t="n">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
       </c>
       <c r="I271" t="n">
-        <v>1068</v>
+        <v>1234.7</v>
       </c>
       <c r="J271" t="n">
-        <v>1068</v>
+        <v>1234.7</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>1036.3</v>
+        <v>1485</v>
       </c>
       <c r="M271" t="n">
-        <v>1036.3</v>
+        <v>1485</v>
       </c>
       <c r="N271" t="n">
         <v>0</v>
       </c>
       <c r="O271" t="n">
-        <v>2596.5</v>
+        <v>1601.7</v>
       </c>
       <c r="P271" t="n">
-        <v>2596.5</v>
+        <v>1601.7</v>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>32550</v>
+        <v>9800</v>
       </c>
       <c r="S271" t="n">
-        <v>31600</v>
+        <v>9010</v>
       </c>
       <c r="T271" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>462870</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>시프트업</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -19527,69 +19488,69 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>412</v>
+        <v>280</v>
       </c>
       <c r="G272" t="n">
-        <v>412</v>
+        <v>280</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>1615.7</v>
+        <v>1068</v>
       </c>
       <c r="J272" t="n">
-        <v>1614</v>
+        <v>1068</v>
       </c>
       <c r="K272" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>2185.1</v>
+        <v>1036.3</v>
       </c>
       <c r="M272" t="n">
-        <v>2182.9</v>
+        <v>1036.3</v>
       </c>
       <c r="N272" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
-        <v>2752.9</v>
+        <v>2596.5</v>
       </c>
       <c r="P272" t="n">
-        <v>2764.6</v>
+        <v>2596.5</v>
       </c>
       <c r="Q272" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>241500</v>
+        <v>32750</v>
       </c>
       <c r="S272" t="n">
-        <v>221000</v>
+        <v>31600</v>
       </c>
       <c r="T272" t="n">
-        <v>9.300000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>484870</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>엠앤씨솔루션</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -19599,69 +19560,69 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>방산·항공우주</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>135</v>
+        <v>412</v>
       </c>
       <c r="G273" t="n">
-        <v>135</v>
+        <v>412</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>636</v>
+        <v>1615.7</v>
       </c>
       <c r="J273" t="n">
-        <v>636</v>
+        <v>1614</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L273" t="n">
-        <v>847</v>
+        <v>2185.1</v>
       </c>
       <c r="M273" t="n">
-        <v>847</v>
+        <v>2182.9</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O273" t="n">
-        <v>1111</v>
+        <v>2752.9</v>
       </c>
       <c r="P273" t="n">
-        <v>1111</v>
+        <v>2764.6</v>
       </c>
       <c r="Q273" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="R273" t="n">
-        <v>15620</v>
+        <v>246000</v>
       </c>
       <c r="S273" t="n">
-        <v>15020</v>
+        <v>221000</v>
       </c>
       <c r="T273" t="n">
-        <v>4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>484870</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>엠앤씨솔루션</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -19671,7 +19632,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>방산·항공우주</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -19680,94 +19641,166 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>489</v>
+        <v>135</v>
       </c>
       <c r="G274" t="n">
-        <v>489</v>
+        <v>135</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>2031.3</v>
+        <v>636</v>
       </c>
       <c r="J274" t="n">
-        <v>1924</v>
+        <v>636</v>
       </c>
       <c r="K274" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>2996.7</v>
+        <v>847</v>
       </c>
       <c r="M274" t="n">
-        <v>2897</v>
+        <v>847</v>
       </c>
       <c r="N274" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
-        <v>3767.3</v>
+        <v>1111</v>
       </c>
       <c r="P274" t="n">
-        <v>3880.7</v>
+        <v>1111</v>
       </c>
       <c r="Q274" t="n">
-        <v>-2.9</v>
+        <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>48450</v>
+        <v>16000</v>
       </c>
       <c r="S274" t="n">
-        <v>42000</v>
+        <v>15020</v>
       </c>
       <c r="T274" t="n">
-        <v>15.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
+          <t>489790</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>한화비전</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>반도체소부장</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>커버리지</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>489</v>
+      </c>
+      <c r="G275" t="n">
+        <v>489</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="n">
+        <v>2031.3</v>
+      </c>
+      <c r="J275" t="n">
+        <v>1924</v>
+      </c>
+      <c r="K275" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L275" t="n">
+        <v>2996.7</v>
+      </c>
+      <c r="M275" t="n">
+        <v>2897</v>
+      </c>
+      <c r="N275" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O275" t="n">
+        <v>3767.3</v>
+      </c>
+      <c r="P275" t="n">
+        <v>3880.7</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="R275" t="n">
+        <v>48900</v>
+      </c>
+      <c r="S275" t="n">
+        <v>42000</v>
+      </c>
+      <c r="T275" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
           <t>491000</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>리브스메드</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D276" t="inlineStr">
         <is>
           <t>의료기기</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="E276" t="inlineStr">
         <is>
           <t>커버리지</t>
         </is>
       </c>
-      <c r="F275" t="n">
+      <c r="F276" t="n">
         <v>-71</v>
       </c>
-      <c r="G275" t="n">
+      <c r="G276" t="n">
         <v>-71</v>
       </c>
-      <c r="H275" t="n">
-        <v>0</v>
-      </c>
-      <c r="R275" t="n">
-        <v>45050</v>
-      </c>
-      <c r="S275" t="n">
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="R276" t="n">
+        <v>46200</v>
+      </c>
+      <c r="S276" t="n">
         <v>37450</v>
       </c>
-      <c r="T275" t="n">
-        <v>20.3</v>
+      <c r="T276" t="n">
+        <v>23.4</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="컨센" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="컨센" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -696,13 +696,13 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>83100</v>
+        <v>83700</v>
       </c>
       <c r="S4" t="n">
         <v>80600</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="5">
@@ -768,13 +768,13 @@
         <v>-2</v>
       </c>
       <c r="R5" t="n">
-        <v>75700</v>
+        <v>77200</v>
       </c>
       <c r="S5" t="n">
         <v>79000</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.2</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="6">
@@ -840,13 +840,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1227000</v>
+        <v>1276000</v>
       </c>
       <c r="S6" t="n">
         <v>1191000</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
@@ -912,13 +912,13 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>51500</v>
+        <v>51900</v>
       </c>
       <c r="S7" t="n">
         <v>50900</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -957,13 +957,13 @@
         <v>5340</v>
       </c>
       <c r="R8" t="n">
-        <v>25750</v>
+        <v>26250</v>
       </c>
       <c r="S8" t="n">
         <v>25850</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>140100</v>
+        <v>141700</v>
       </c>
       <c r="S9" t="n">
         <v>134900</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1101,13 +1101,13 @@
         <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>92000</v>
+        <v>93000</v>
       </c>
       <c r="S10" t="n">
         <v>89000</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11">
@@ -1245,13 +1245,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>113300</v>
+        <v>115800</v>
       </c>
       <c r="S12" t="n">
         <v>109900</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="13">
@@ -1317,13 +1317,13 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>618000</v>
+        <v>615000</v>
       </c>
       <c r="S13" t="n">
         <v>645000</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.2</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="14">
@@ -1461,13 +1461,13 @@
         <v>0.5</v>
       </c>
       <c r="R15" t="n">
-        <v>100300</v>
+        <v>102800</v>
       </c>
       <c r="S15" t="n">
         <v>84100</v>
       </c>
       <c r="T15" t="n">
-        <v>19.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="16">
@@ -1533,13 +1533,13 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>134300</v>
+        <v>138100</v>
       </c>
       <c r="S16" t="n">
         <v>145700</v>
       </c>
       <c r="T16" t="n">
-        <v>-7.8</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="17">
@@ -1605,13 +1605,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>44200</v>
+        <v>45000</v>
       </c>
       <c r="S17" t="n">
         <v>41600</v>
       </c>
       <c r="T17" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1677,13 +1677,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>29050</v>
+        <v>29950</v>
       </c>
       <c r="S18" t="n">
         <v>27100</v>
       </c>
       <c r="T18" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="19">
@@ -1740,13 +1740,13 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>44900</v>
+        <v>45350</v>
       </c>
       <c r="S19" t="n">
         <v>39300</v>
       </c>
       <c r="T19" t="n">
-        <v>14.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="20">
@@ -1812,13 +1812,13 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>18130</v>
+        <v>18370</v>
       </c>
       <c r="S20" t="n">
         <v>18550</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21">
@@ -1938,13 +1938,13 @@
         <v>-1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>6580</v>
+        <v>6730</v>
       </c>
       <c r="S22" t="n">
         <v>6550</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -2010,13 +2010,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>451000</v>
+        <v>465500</v>
       </c>
       <c r="S23" t="n">
         <v>442000</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="24">
@@ -2082,13 +2082,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>13310</v>
+        <v>13400</v>
       </c>
       <c r="S24" t="n">
         <v>9770</v>
       </c>
       <c r="T24" t="n">
-        <v>36.2</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="25">
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>109100</v>
+        <v>108000</v>
       </c>
       <c r="S25" t="n">
         <v>114500</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.7</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="26">
@@ -2226,13 +2226,13 @@
         <v>-4.3</v>
       </c>
       <c r="R26" t="n">
-        <v>10340</v>
+        <v>10240</v>
       </c>
       <c r="S26" t="n">
         <v>8950</v>
       </c>
       <c r="T26" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="27">
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>7940</v>
+        <v>7960</v>
       </c>
       <c r="S27" t="n">
         <v>8160</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="28">
@@ -2361,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1273000</v>
+        <v>1270000</v>
       </c>
       <c r="S28" t="n">
         <v>1306000</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.5</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="29">
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>26250</v>
+        <v>26300</v>
       </c>
       <c r="S29" t="n">
         <v>27150</v>
       </c>
       <c r="T29" t="n">
-        <v>-3.3</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="30">
@@ -2505,13 +2505,13 @@
         <v>-8</v>
       </c>
       <c r="R30" t="n">
-        <v>116900</v>
+        <v>120000</v>
       </c>
       <c r="S30" t="n">
         <v>108100</v>
       </c>
       <c r="T30" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -2577,13 +2577,13 @@
         <v>-0.6</v>
       </c>
       <c r="R31" t="n">
-        <v>163200</v>
+        <v>170500</v>
       </c>
       <c r="S31" t="n">
         <v>155800</v>
       </c>
       <c r="T31" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="32">
@@ -2649,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>46600</v>
+        <v>47100</v>
       </c>
       <c r="S32" t="n">
         <v>48550</v>
       </c>
       <c r="T32" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="33">
@@ -2721,13 +2721,13 @@
         <v>0.9</v>
       </c>
       <c r="R33" t="n">
-        <v>29150</v>
+        <v>29900</v>
       </c>
       <c r="S33" t="n">
         <v>28300</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="34">
@@ -2793,13 +2793,13 @@
         <v>1.8</v>
       </c>
       <c r="R34" t="n">
-        <v>419500</v>
+        <v>427000</v>
       </c>
       <c r="S34" t="n">
         <v>420000</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="35">
@@ -2865,13 +2865,13 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>431000</v>
+        <v>437500</v>
       </c>
       <c r="S35" t="n">
         <v>405000</v>
       </c>
       <c r="T35" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>24050</v>
+        <v>24300</v>
       </c>
       <c r="S36" t="n">
         <v>23700</v>
       </c>
       <c r="T36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="37">
@@ -3009,13 +3009,13 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>101400</v>
+        <v>101700</v>
       </c>
       <c r="S37" t="n">
         <v>102600</v>
       </c>
       <c r="T37" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="38">
@@ -3081,13 +3081,13 @@
         <v>-0.1</v>
       </c>
       <c r="R38" t="n">
-        <v>443500</v>
+        <v>453000</v>
       </c>
       <c r="S38" t="n">
         <v>395500</v>
       </c>
       <c r="T38" t="n">
-        <v>12.1</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="39">
@@ -3153,13 +3153,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>328500</v>
+        <v>334000</v>
       </c>
       <c r="S39" t="n">
         <v>331000</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="40">
@@ -3225,13 +3225,13 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>172100</v>
+        <v>176800</v>
       </c>
       <c r="S40" t="n">
         <v>165900</v>
       </c>
       <c r="T40" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="41">
@@ -3297,13 +3297,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>60000</v>
+        <v>61600</v>
       </c>
       <c r="S41" t="n">
         <v>55200</v>
       </c>
       <c r="T41" t="n">
-        <v>8.699999999999999</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="42">
@@ -3369,13 +3369,13 @@
         <v>-2.2</v>
       </c>
       <c r="R42" t="n">
-        <v>267500</v>
+        <v>274500</v>
       </c>
       <c r="S42" t="n">
         <v>231000</v>
       </c>
       <c r="T42" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="43">
@@ -3441,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>28400</v>
+        <v>28750</v>
       </c>
       <c r="S43" t="n">
         <v>27800</v>
       </c>
       <c r="T43" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="44">
@@ -3513,13 +3513,13 @@
         <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>37650</v>
+        <v>37550</v>
       </c>
       <c r="S44" t="n">
         <v>37750</v>
       </c>
       <c r="T44" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="45">
@@ -3585,13 +3585,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>307500</v>
+        <v>323500</v>
       </c>
       <c r="S45" t="n">
         <v>317000</v>
       </c>
       <c r="T45" t="n">
-        <v>-3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="46">
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>128600</v>
+        <v>129200</v>
       </c>
       <c r="S46" t="n">
         <v>129900</v>
       </c>
       <c r="T46" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="47">
@@ -3729,13 +3729,13 @@
         <v>0.3</v>
       </c>
       <c r="R47" t="n">
-        <v>34300</v>
+        <v>35350</v>
       </c>
       <c r="S47" t="n">
         <v>31650</v>
       </c>
       <c r="T47" t="n">
-        <v>8.4</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="48">
@@ -3801,13 +3801,13 @@
         <v>-0</v>
       </c>
       <c r="R48" t="n">
-        <v>495000</v>
+        <v>516000</v>
       </c>
       <c r="S48" t="n">
         <v>459000</v>
       </c>
       <c r="T48" t="n">
-        <v>7.8</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="49">
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>90400</v>
+        <v>91400</v>
       </c>
       <c r="S49" t="n">
         <v>93700</v>
       </c>
       <c r="T49" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="50">
@@ -3945,13 +3945,13 @@
         <v>-0.5</v>
       </c>
       <c r="R50" t="n">
-        <v>37000</v>
+        <v>37650</v>
       </c>
       <c r="S50" t="n">
         <v>33900</v>
       </c>
       <c r="T50" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="51">
@@ -4017,13 +4017,13 @@
         <v>6.9</v>
       </c>
       <c r="R51" t="n">
-        <v>27750</v>
+        <v>27700</v>
       </c>
       <c r="S51" t="n">
         <v>28350</v>
       </c>
       <c r="T51" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="52">
@@ -4089,13 +4089,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="R52" t="n">
-        <v>50300</v>
+        <v>58900</v>
       </c>
       <c r="S52" t="n">
         <v>47600</v>
       </c>
       <c r="T52" t="n">
-        <v>5.7</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="53">
@@ -4161,13 +4161,13 @@
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>90100</v>
+        <v>95600</v>
       </c>
       <c r="S53" t="n">
         <v>82300</v>
       </c>
       <c r="T53" t="n">
-        <v>9.5</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="54">
@@ -4233,13 +4233,13 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>64200</v>
+        <v>63100</v>
       </c>
       <c r="S54" t="n">
         <v>55700</v>
       </c>
       <c r="T54" t="n">
-        <v>15.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="55">
@@ -4296,13 +4296,13 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>14640</v>
+        <v>15090</v>
       </c>
       <c r="S55" t="n">
         <v>14840</v>
       </c>
       <c r="T55" t="n">
-        <v>-1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="56">
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>44800</v>
+        <v>45400</v>
       </c>
       <c r="S56" t="n">
         <v>42700</v>
       </c>
       <c r="T56" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="57">
@@ -4440,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1531000</v>
+        <v>1558000</v>
       </c>
       <c r="S57" t="n">
         <v>1278000</v>
       </c>
       <c r="T57" t="n">
-        <v>19.8</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="58">
@@ -4512,13 +4512,13 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="R58" t="n">
-        <v>39700</v>
+        <v>40500</v>
       </c>
       <c r="S58" t="n">
         <v>40850</v>
       </c>
       <c r="T58" t="n">
-        <v>-2.8</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="59">
@@ -4584,13 +4584,13 @@
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>58200</v>
+        <v>59700</v>
       </c>
       <c r="S59" t="n">
         <v>54100</v>
       </c>
       <c r="T59" t="n">
-        <v>7.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="60">
@@ -4656,13 +4656,13 @@
         <v>-1.8</v>
       </c>
       <c r="R60" t="n">
-        <v>384500</v>
+        <v>386000</v>
       </c>
       <c r="S60" t="n">
         <v>398500</v>
       </c>
       <c r="T60" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="61">
@@ -4728,13 +4728,13 @@
         <v>1.3</v>
       </c>
       <c r="R61" t="n">
-        <v>34950</v>
+        <v>35400</v>
       </c>
       <c r="S61" t="n">
         <v>33900</v>
       </c>
       <c r="T61" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="62">
@@ -4800,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>267000</v>
+        <v>279000</v>
       </c>
       <c r="S62" t="n">
         <v>272500</v>
       </c>
       <c r="T62" t="n">
-        <v>-2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="63">
@@ -4872,13 +4872,13 @@
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>203500</v>
+        <v>206500</v>
       </c>
       <c r="S63" t="n">
         <v>201000</v>
       </c>
       <c r="T63" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="64">
@@ -4944,13 +4944,13 @@
         <v>-10</v>
       </c>
       <c r="R64" t="n">
-        <v>1184000</v>
+        <v>1196000</v>
       </c>
       <c r="S64" t="n">
         <v>1106000</v>
       </c>
       <c r="T64" t="n">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="65">
@@ -5016,13 +5016,13 @@
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>22350</v>
+        <v>22300</v>
       </c>
       <c r="S65" t="n">
         <v>22050</v>
       </c>
       <c r="T65" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="66">
@@ -5088,13 +5088,13 @@
         <v>-2.5</v>
       </c>
       <c r="R66" t="n">
-        <v>16090</v>
+        <v>16730</v>
       </c>
       <c r="S66" t="n">
         <v>19230</v>
       </c>
       <c r="T66" t="n">
-        <v>-16.3</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="67">
@@ -5160,13 +5160,13 @@
         <v>0.7</v>
       </c>
       <c r="R67" t="n">
-        <v>143400</v>
+        <v>147600</v>
       </c>
       <c r="S67" t="n">
         <v>137600</v>
       </c>
       <c r="T67" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="68">
@@ -5232,13 +5232,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>625000</v>
+        <v>654000</v>
       </c>
       <c r="S68" t="n">
         <v>552000</v>
       </c>
       <c r="T68" t="n">
-        <v>13.2</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="69">
@@ -5304,13 +5304,13 @@
         <v>-18.9</v>
       </c>
       <c r="R69" t="n">
-        <v>56900</v>
+        <v>57200</v>
       </c>
       <c r="S69" t="n">
         <v>61000</v>
       </c>
       <c r="T69" t="n">
-        <v>-6.7</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="70">
@@ -5376,13 +5376,13 @@
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>21050</v>
+        <v>21250</v>
       </c>
       <c r="S70" t="n">
         <v>21800</v>
       </c>
       <c r="T70" t="n">
-        <v>-3.4</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="71">
@@ -5448,13 +5448,13 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>66800</v>
+        <v>67800</v>
       </c>
       <c r="S71" t="n">
         <v>62500</v>
       </c>
       <c r="T71" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="72">
@@ -5520,13 +5520,13 @@
         <v>-1</v>
       </c>
       <c r="R72" t="n">
-        <v>130000</v>
+        <v>130600</v>
       </c>
       <c r="S72" t="n">
         <v>129600</v>
       </c>
       <c r="T72" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="73">
@@ -5592,13 +5592,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>87200</v>
+        <v>89800</v>
       </c>
       <c r="S73" t="n">
         <v>81200</v>
       </c>
       <c r="T73" t="n">
-        <v>7.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="74">
@@ -5664,13 +5664,13 @@
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>16520</v>
+        <v>16890</v>
       </c>
       <c r="S74" t="n">
         <v>15140</v>
       </c>
       <c r="T74" t="n">
-        <v>9.1</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="75">
@@ -5736,13 +5736,13 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>532000</v>
+        <v>547000</v>
       </c>
       <c r="S75" t="n">
         <v>496500</v>
       </c>
       <c r="T75" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="76">
@@ -5808,13 +5808,13 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1148000</v>
+        <v>1160000</v>
       </c>
       <c r="S76" t="n">
         <v>1097000</v>
       </c>
       <c r="T76" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="77">
@@ -5880,13 +5880,13 @@
         <v>0.2</v>
       </c>
       <c r="R77" t="n">
-        <v>77200</v>
+        <v>77700</v>
       </c>
       <c r="S77" t="n">
         <v>76600</v>
       </c>
       <c r="T77" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="78">
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>20900</v>
+        <v>21600</v>
       </c>
       <c r="S78" t="n">
         <v>19940</v>
       </c>
       <c r="T78" t="n">
-        <v>4.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -6015,13 +6015,13 @@
         <v>5.1</v>
       </c>
       <c r="R79" t="n">
-        <v>26450</v>
+        <v>26050</v>
       </c>
       <c r="S79" t="n">
         <v>26650</v>
       </c>
       <c r="T79" t="n">
-        <v>-0.8</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="80">
@@ -6087,13 +6087,13 @@
         <v>0.8</v>
       </c>
       <c r="R80" t="n">
-        <v>212000</v>
+        <v>218500</v>
       </c>
       <c r="S80" t="n">
         <v>222500</v>
       </c>
       <c r="T80" t="n">
-        <v>-4.7</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="81">
@@ -6159,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2505</v>
+        <v>2575</v>
       </c>
       <c r="S81" t="n">
         <v>2480</v>
       </c>
       <c r="T81" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="82">
@@ -6231,13 +6231,13 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="R82" t="n">
-        <v>32850</v>
+        <v>33250</v>
       </c>
       <c r="S82" t="n">
         <v>35600</v>
       </c>
       <c r="T82" t="n">
-        <v>-7.7</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="83">
@@ -6303,13 +6303,13 @@
         <v>-0.5</v>
       </c>
       <c r="R83" t="n">
-        <v>92100</v>
+        <v>93000</v>
       </c>
       <c r="S83" t="n">
         <v>91000</v>
       </c>
       <c r="T83" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="84">
@@ -6375,13 +6375,13 @@
         <v>0.5</v>
       </c>
       <c r="R84" t="n">
-        <v>100000</v>
+        <v>100500</v>
       </c>
       <c r="S84" t="n">
         <v>88200</v>
       </c>
       <c r="T84" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="85">
@@ -6519,13 +6519,13 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>24500</v>
+        <v>25150</v>
       </c>
       <c r="S86" t="n">
         <v>23100</v>
       </c>
       <c r="T86" t="n">
-        <v>6.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="87">
@@ -6591,13 +6591,13 @@
         <v>-0.5</v>
       </c>
       <c r="R87" t="n">
-        <v>234500</v>
+        <v>243500</v>
       </c>
       <c r="S87" t="n">
         <v>221500</v>
       </c>
       <c r="T87" t="n">
-        <v>5.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="88">
@@ -6663,13 +6663,13 @@
         <v>-0.5</v>
       </c>
       <c r="R88" t="n">
-        <v>3785</v>
+        <v>3820</v>
       </c>
       <c r="S88" t="n">
         <v>3625</v>
       </c>
       <c r="T88" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="89">
@@ -6735,13 +6735,13 @@
         <v>3.9</v>
       </c>
       <c r="R89" t="n">
-        <v>98700</v>
+        <v>98200</v>
       </c>
       <c r="S89" t="n">
         <v>95700</v>
       </c>
       <c r="T89" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="90">
@@ -6807,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>23250</v>
+        <v>23200</v>
       </c>
       <c r="S90" t="n">
         <v>23150</v>
       </c>
       <c r="T90" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91">
@@ -6879,13 +6879,13 @@
         <v>-1</v>
       </c>
       <c r="R91" t="n">
-        <v>102000</v>
+        <v>102900</v>
       </c>
       <c r="S91" t="n">
         <v>99700</v>
       </c>
       <c r="T91" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="92">
@@ -6951,13 +6951,13 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>20250</v>
+        <v>20400</v>
       </c>
       <c r="S92" t="n">
         <v>20750</v>
       </c>
       <c r="T92" t="n">
-        <v>-2.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="93">
@@ -7023,13 +7023,13 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>48900</v>
+        <v>49800</v>
       </c>
       <c r="S93" t="n">
         <v>48100</v>
       </c>
       <c r="T93" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="94">
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>362500</v>
+        <v>369000</v>
       </c>
       <c r="S94" t="n">
         <v>336500</v>
       </c>
       <c r="T94" t="n">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -7167,13 +7167,13 @@
         <v>0.4</v>
       </c>
       <c r="R95" t="n">
-        <v>5690</v>
+        <v>5790</v>
       </c>
       <c r="S95" t="n">
         <v>6040</v>
       </c>
       <c r="T95" t="n">
-        <v>-5.8</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="96">
@@ -7239,13 +7239,13 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>47950</v>
+        <v>48550</v>
       </c>
       <c r="S96" t="n">
         <v>47850</v>
       </c>
       <c r="T96" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="97">
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>18970</v>
+        <v>18980</v>
       </c>
       <c r="S97" t="n">
         <v>19170</v>
@@ -7383,13 +7383,13 @@
         <v>-1.4</v>
       </c>
       <c r="R98" t="n">
-        <v>53800</v>
+        <v>53400</v>
       </c>
       <c r="S98" t="n">
         <v>53300</v>
       </c>
       <c r="T98" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="99">
@@ -7455,13 +7455,13 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>100800</v>
+        <v>111200</v>
       </c>
       <c r="S99" t="n">
         <v>94000</v>
       </c>
       <c r="T99" t="n">
-        <v>7.2</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="100">
@@ -7500,13 +7500,13 @@
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>13780</v>
+        <v>13760</v>
       </c>
       <c r="S100" t="n">
         <v>13030</v>
       </c>
       <c r="T100" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="101">
@@ -7572,13 +7572,13 @@
         <v>2</v>
       </c>
       <c r="R101" t="n">
-        <v>14890</v>
+        <v>15060</v>
       </c>
       <c r="S101" t="n">
         <v>14960</v>
       </c>
       <c r="T101" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="102">
@@ -7644,13 +7644,13 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>298000</v>
+        <v>301000</v>
       </c>
       <c r="S102" t="n">
         <v>275500</v>
       </c>
       <c r="T102" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>17170</v>
+        <v>17350</v>
       </c>
       <c r="S103" t="n">
         <v>17000</v>
       </c>
       <c r="T103" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="104">
@@ -7779,13 +7779,13 @@
         <v>1.7</v>
       </c>
       <c r="R104" t="n">
-        <v>176700</v>
+        <v>176000</v>
       </c>
       <c r="S104" t="n">
         <v>188800</v>
       </c>
       <c r="T104" t="n">
-        <v>-6.4</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="105">
@@ -7851,13 +7851,13 @@
         <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>81400</v>
+        <v>82600</v>
       </c>
       <c r="S105" t="n">
         <v>77100</v>
       </c>
       <c r="T105" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="106">
@@ -7923,13 +7923,13 @@
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>9970</v>
+        <v>10270</v>
       </c>
       <c r="S106" t="n">
         <v>9770</v>
       </c>
       <c r="T106" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="107">
@@ -7995,13 +7995,13 @@
         <v>0.3</v>
       </c>
       <c r="R107" t="n">
-        <v>9780</v>
+        <v>9890</v>
       </c>
       <c r="S107" t="n">
         <v>10100</v>
       </c>
       <c r="T107" t="n">
-        <v>-3.2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="108">
@@ -8067,13 +8067,13 @@
         <v>7.1</v>
       </c>
       <c r="R108" t="n">
-        <v>566000</v>
+        <v>585000</v>
       </c>
       <c r="S108" t="n">
         <v>508000</v>
       </c>
       <c r="T108" t="n">
-        <v>11.4</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="109">
@@ -8139,13 +8139,13 @@
         <v>-0</v>
       </c>
       <c r="R109" t="n">
-        <v>14720</v>
+        <v>14590</v>
       </c>
       <c r="S109" t="n">
         <v>14690</v>
       </c>
       <c r="T109" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="110">
@@ -8211,13 +8211,13 @@
         <v>-5.1</v>
       </c>
       <c r="R110" t="n">
-        <v>225500</v>
+        <v>228000</v>
       </c>
       <c r="S110" t="n">
         <v>210000</v>
       </c>
       <c r="T110" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="111">
@@ -8283,13 +8283,13 @@
         <v>7</v>
       </c>
       <c r="R111" t="n">
-        <v>39700</v>
+        <v>40000</v>
       </c>
       <c r="S111" t="n">
         <v>39900</v>
       </c>
       <c r="T111" t="n">
-        <v>-0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="112">
@@ -8355,13 +8355,13 @@
         <v>2.3</v>
       </c>
       <c r="R112" t="n">
-        <v>34750</v>
+        <v>34400</v>
       </c>
       <c r="S112" t="n">
         <v>35450</v>
       </c>
       <c r="T112" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="113">
@@ -8499,13 +8499,13 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>8590</v>
+        <v>8760</v>
       </c>
       <c r="S114" t="n">
         <v>7510</v>
       </c>
       <c r="T114" t="n">
-        <v>14.4</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="115">
@@ -8571,13 +8571,13 @@
         <v>10</v>
       </c>
       <c r="R115" t="n">
-        <v>36450</v>
+        <v>36600</v>
       </c>
       <c r="S115" t="n">
         <v>35750</v>
       </c>
       <c r="T115" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="116">
@@ -8643,13 +8643,13 @@
         <v>6.3</v>
       </c>
       <c r="R116" t="n">
-        <v>242500</v>
+        <v>247500</v>
       </c>
       <c r="S116" t="n">
         <v>248500</v>
       </c>
       <c r="T116" t="n">
-        <v>-2.4</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="117">
@@ -8715,13 +8715,13 @@
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>173500</v>
+        <v>177800</v>
       </c>
       <c r="S117" t="n">
         <v>127800</v>
       </c>
       <c r="T117" t="n">
-        <v>35.8</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="118">
@@ -8787,13 +8787,13 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>390000</v>
+        <v>404000</v>
       </c>
       <c r="S118" t="n">
         <v>324500</v>
       </c>
       <c r="T118" t="n">
-        <v>20.2</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="119">
@@ -8859,13 +8859,13 @@
         <v>-1.3</v>
       </c>
       <c r="R119" t="n">
-        <v>32450</v>
+        <v>32700</v>
       </c>
       <c r="S119" t="n">
         <v>31500</v>
       </c>
       <c r="T119" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="120">
@@ -8931,13 +8931,13 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>23450</v>
+        <v>23700</v>
       </c>
       <c r="S120" t="n">
         <v>21150</v>
       </c>
       <c r="T120" t="n">
-        <v>10.9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="121">
@@ -9003,13 +9003,13 @@
         <v>-0.3</v>
       </c>
       <c r="R121" t="n">
-        <v>296000</v>
+        <v>300500</v>
       </c>
       <c r="S121" t="n">
         <v>277500</v>
       </c>
       <c r="T121" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -9057,13 +9057,13 @@
         <v>-2.2</v>
       </c>
       <c r="R122" t="n">
-        <v>12230</v>
+        <v>12290</v>
       </c>
       <c r="S122" t="n">
         <v>12570</v>
       </c>
       <c r="T122" t="n">
-        <v>-2.7</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="123">
@@ -9129,13 +9129,13 @@
         <v>1.4</v>
       </c>
       <c r="R123" t="n">
-        <v>72800</v>
+        <v>73400</v>
       </c>
       <c r="S123" t="n">
         <v>75600</v>
       </c>
       <c r="T123" t="n">
-        <v>-3.7</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="124">
@@ -9201,13 +9201,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>94000</v>
+        <v>95800</v>
       </c>
       <c r="S124" t="n">
         <v>89400</v>
       </c>
       <c r="T124" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="125">
@@ -9273,13 +9273,13 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>224500</v>
+        <v>229000</v>
       </c>
       <c r="S125" t="n">
         <v>192300</v>
       </c>
       <c r="T125" t="n">
-        <v>16.7</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="126">
@@ -9345,13 +9345,13 @@
         <v>-0.3</v>
       </c>
       <c r="R126" t="n">
-        <v>17570</v>
+        <v>18010</v>
       </c>
       <c r="S126" t="n">
         <v>16410</v>
       </c>
       <c r="T126" t="n">
-        <v>7.1</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -9417,13 +9417,13 @@
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>53100</v>
+        <v>53300</v>
       </c>
       <c r="S127" t="n">
         <v>58000</v>
       </c>
       <c r="T127" t="n">
-        <v>-8.4</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="128">
@@ -9489,13 +9489,13 @@
         <v>-1.2</v>
       </c>
       <c r="R128" t="n">
-        <v>146800</v>
+        <v>146400</v>
       </c>
       <c r="S128" t="n">
         <v>154200</v>
       </c>
       <c r="T128" t="n">
-        <v>-4.8</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="129">
@@ -9561,13 +9561,13 @@
         <v>-0.4</v>
       </c>
       <c r="R129" t="n">
-        <v>24600</v>
+        <v>24850</v>
       </c>
       <c r="S129" t="n">
         <v>23450</v>
       </c>
       <c r="T129" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130">
@@ -9633,13 +9633,13 @@
         <v>-2.7</v>
       </c>
       <c r="R130" t="n">
-        <v>46050</v>
+        <v>46350</v>
       </c>
       <c r="S130" t="n">
         <v>47250</v>
       </c>
       <c r="T130" t="n">
-        <v>-2.5</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="131">
@@ -9777,13 +9777,13 @@
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>274500</v>
+        <v>280500</v>
       </c>
       <c r="S132" t="n">
         <v>276000</v>
       </c>
       <c r="T132" t="n">
-        <v>-0.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="133">
@@ -9849,13 +9849,13 @@
         <v>-10.3</v>
       </c>
       <c r="R133" t="n">
-        <v>100300</v>
+        <v>101000</v>
       </c>
       <c r="S133" t="n">
         <v>101900</v>
       </c>
       <c r="T133" t="n">
-        <v>-1.6</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="134">
@@ -9921,13 +9921,13 @@
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>107300</v>
+        <v>107400</v>
       </c>
       <c r="S134" t="n">
         <v>110000</v>
       </c>
       <c r="T134" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="135">
@@ -9993,13 +9993,13 @@
         <v>2</v>
       </c>
       <c r="R135" t="n">
-        <v>71000</v>
+        <v>70800</v>
       </c>
       <c r="S135" t="n">
         <v>65700</v>
       </c>
       <c r="T135" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="136">
@@ -10065,13 +10065,13 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>120000</v>
+        <v>118600</v>
       </c>
       <c r="S136" t="n">
         <v>101700</v>
       </c>
       <c r="T136" t="n">
-        <v>18</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="137">
@@ -10137,13 +10137,13 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>41200</v>
+        <v>41100</v>
       </c>
       <c r="S137" t="n">
         <v>39100</v>
       </c>
       <c r="T137" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="138">
@@ -10209,13 +10209,13 @@
         <v>1</v>
       </c>
       <c r="R138" t="n">
-        <v>175200</v>
+        <v>182500</v>
       </c>
       <c r="S138" t="n">
         <v>157300</v>
       </c>
       <c r="T138" t="n">
-        <v>11.4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139">
@@ -10281,13 +10281,13 @@
         <v>-1.9</v>
       </c>
       <c r="R139" t="n">
-        <v>144800</v>
+        <v>146900</v>
       </c>
       <c r="S139" t="n">
         <v>146900</v>
       </c>
       <c r="T139" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -10353,13 +10353,13 @@
         <v>-0.6</v>
       </c>
       <c r="R140" t="n">
-        <v>77600</v>
+        <v>79900</v>
       </c>
       <c r="S140" t="n">
         <v>72600</v>
       </c>
       <c r="T140" t="n">
-        <v>6.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="141">
@@ -10425,13 +10425,13 @@
         <v>1.8</v>
       </c>
       <c r="R141" t="n">
-        <v>232000</v>
+        <v>244000</v>
       </c>
       <c r="S141" t="n">
         <v>167300</v>
       </c>
       <c r="T141" t="n">
-        <v>38.7</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="142">
@@ -10488,13 +10488,13 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>28700</v>
+        <v>28450</v>
       </c>
       <c r="S142" t="n">
         <v>27350</v>
       </c>
       <c r="T142" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
@@ -10560,13 +10560,13 @@
         <v>0.9</v>
       </c>
       <c r="R143" t="n">
-        <v>207000</v>
+        <v>215000</v>
       </c>
       <c r="S143" t="n">
         <v>185000</v>
       </c>
       <c r="T143" t="n">
-        <v>11.9</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="144">
@@ -10632,13 +10632,13 @@
         <v>-2</v>
       </c>
       <c r="R144" t="n">
-        <v>103700</v>
+        <v>109700</v>
       </c>
       <c r="S144" t="n">
         <v>90200</v>
       </c>
       <c r="T144" t="n">
-        <v>15</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="145">
@@ -10704,13 +10704,13 @@
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>42050</v>
+        <v>41500</v>
       </c>
       <c r="S145" t="n">
         <v>43300</v>
       </c>
       <c r="T145" t="n">
-        <v>-2.9</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="146">
@@ -10776,13 +10776,13 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>35750</v>
+        <v>36600</v>
       </c>
       <c r="S146" t="n">
         <v>30000</v>
       </c>
       <c r="T146" t="n">
-        <v>19.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147">
@@ -10848,13 +10848,13 @@
         <v>0.8</v>
       </c>
       <c r="R147" t="n">
-        <v>200500</v>
+        <v>201000</v>
       </c>
       <c r="S147" t="n">
         <v>199300</v>
       </c>
       <c r="T147" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="148">
@@ -10920,13 +10920,13 @@
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>16260</v>
+        <v>16350</v>
       </c>
       <c r="S148" t="n">
         <v>16450</v>
       </c>
       <c r="T148" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="149">
@@ -11064,13 +11064,13 @@
         <v>-0.5</v>
       </c>
       <c r="R150" t="n">
-        <v>101800</v>
+        <v>102200</v>
       </c>
       <c r="S150" t="n">
         <v>101800</v>
       </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="151">
@@ -11136,13 +11136,13 @@
         <v>2.1</v>
       </c>
       <c r="R151" t="n">
-        <v>200500</v>
+        <v>204000</v>
       </c>
       <c r="S151" t="n">
         <v>188000</v>
       </c>
       <c r="T151" t="n">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="152">
@@ -11208,13 +11208,13 @@
         <v>-7.4</v>
       </c>
       <c r="R152" t="n">
-        <v>74800</v>
+        <v>76400</v>
       </c>
       <c r="S152" t="n">
         <v>64500</v>
       </c>
       <c r="T152" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="153">
@@ -11280,13 +11280,13 @@
         <v>2.4</v>
       </c>
       <c r="R153" t="n">
-        <v>57500</v>
+        <v>58200</v>
       </c>
       <c r="S153" t="n">
         <v>55200</v>
       </c>
       <c r="T153" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="154">
@@ -11352,13 +11352,13 @@
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>8030</v>
+        <v>8140</v>
       </c>
       <c r="S154" t="n">
         <v>7810</v>
       </c>
       <c r="T154" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="155">
@@ -11469,13 +11469,13 @@
         <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>28450</v>
+        <v>28400</v>
       </c>
       <c r="S156" t="n">
         <v>27050</v>
       </c>
       <c r="T156" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
@@ -11541,13 +11541,13 @@
         <v>2.4</v>
       </c>
       <c r="R157" t="n">
-        <v>114900</v>
+        <v>117000</v>
       </c>
       <c r="S157" t="n">
         <v>98900</v>
       </c>
       <c r="T157" t="n">
-        <v>16.2</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="158">
@@ -11613,13 +11613,13 @@
         <v>2.4</v>
       </c>
       <c r="R158" t="n">
-        <v>811000</v>
+        <v>815000</v>
       </c>
       <c r="S158" t="n">
         <v>741000</v>
       </c>
       <c r="T158" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159">
@@ -11658,13 +11658,13 @@
         <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>9110</v>
+        <v>9200</v>
       </c>
       <c r="S159" t="n">
         <v>8920</v>
       </c>
       <c r="T159" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="160">
@@ -11730,13 +11730,13 @@
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>42900</v>
+        <v>42500</v>
       </c>
       <c r="S160" t="n">
         <v>46600</v>
       </c>
       <c r="T160" t="n">
-        <v>-7.9</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -11802,13 +11802,13 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>47750</v>
+        <v>49050</v>
       </c>
       <c r="S161" t="n">
         <v>42500</v>
       </c>
       <c r="T161" t="n">
-        <v>12.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="162">
@@ -11850,7 +11850,7 @@
         <v>1928.3</v>
       </c>
       <c r="R162" t="n">
-        <v>57600</v>
+        <v>61300</v>
       </c>
     </row>
     <row r="163">
@@ -11916,13 +11916,13 @@
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>124900</v>
+        <v>131100</v>
       </c>
       <c r="S163" t="n">
         <v>111200</v>
       </c>
       <c r="T163" t="n">
-        <v>12.3</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="164">
@@ -11988,13 +11988,13 @@
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>206500</v>
+        <v>211000</v>
       </c>
       <c r="S164" t="n">
         <v>207500</v>
       </c>
       <c r="T164" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="165">
@@ -12060,13 +12060,13 @@
         <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>133200</v>
+        <v>133000</v>
       </c>
       <c r="S165" t="n">
         <v>134700</v>
       </c>
       <c r="T165" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="166">
@@ -12123,13 +12123,13 @@
         <v>14.6</v>
       </c>
       <c r="R166" t="n">
-        <v>5365</v>
+        <v>5630</v>
       </c>
       <c r="S166" t="n">
         <v>4555</v>
       </c>
       <c r="T166" t="n">
-        <v>17.8</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="167">
@@ -12168,13 +12168,13 @@
         <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>48300</v>
+        <v>49250</v>
       </c>
       <c r="S167" t="n">
         <v>43350</v>
       </c>
       <c r="T167" t="n">
-        <v>11.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="168">
@@ -12240,13 +12240,13 @@
         <v>-1.1</v>
       </c>
       <c r="R168" t="n">
-        <v>43300</v>
+        <v>45000</v>
       </c>
       <c r="S168" t="n">
         <v>40400</v>
       </c>
       <c r="T168" t="n">
-        <v>7.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="169">
@@ -12312,13 +12312,13 @@
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>65200</v>
+        <v>68200</v>
       </c>
       <c r="S169" t="n">
         <v>60500</v>
       </c>
       <c r="T169" t="n">
-        <v>7.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="170">
@@ -12384,13 +12384,13 @@
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>135600</v>
+        <v>135700</v>
       </c>
       <c r="S170" t="n">
         <v>141800</v>
       </c>
       <c r="T170" t="n">
-        <v>-4.4</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="171">
@@ -12429,13 +12429,13 @@
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>12370</v>
+        <v>12400</v>
       </c>
       <c r="S171" t="n">
         <v>9940</v>
       </c>
       <c r="T171" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="172">
@@ -12501,13 +12501,13 @@
         <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>158900</v>
+        <v>161300</v>
       </c>
       <c r="S172" t="n">
         <v>131000</v>
       </c>
       <c r="T172" t="n">
-        <v>21.3</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="173">
@@ -12573,13 +12573,13 @@
         <v>0.3</v>
       </c>
       <c r="R173" t="n">
-        <v>140700</v>
+        <v>147500</v>
       </c>
       <c r="S173" t="n">
         <v>124600</v>
       </c>
       <c r="T173" t="n">
-        <v>12.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="174">
@@ -12645,13 +12645,13 @@
         <v>-30</v>
       </c>
       <c r="R174" t="n">
-        <v>18870</v>
+        <v>19100</v>
       </c>
       <c r="S174" t="n">
         <v>19280</v>
       </c>
       <c r="T174" t="n">
-        <v>-2.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="175">
@@ -12717,13 +12717,13 @@
         <v>-1.2</v>
       </c>
       <c r="R175" t="n">
-        <v>32500</v>
+        <v>32150</v>
       </c>
       <c r="S175" t="n">
         <v>28900</v>
       </c>
       <c r="T175" t="n">
-        <v>12.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="176">
@@ -12789,13 +12789,13 @@
         <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>126800</v>
+        <v>128700</v>
       </c>
       <c r="S176" t="n">
         <v>120300</v>
       </c>
       <c r="T176" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -12861,13 +12861,13 @@
         <v>-2</v>
       </c>
       <c r="R177" t="n">
-        <v>186700</v>
+        <v>185400</v>
       </c>
       <c r="S177" t="n">
         <v>204500</v>
       </c>
       <c r="T177" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="178">
@@ -12906,13 +12906,13 @@
         <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>31400</v>
+        <v>32350</v>
       </c>
       <c r="S178" t="n">
         <v>29600</v>
       </c>
       <c r="T178" t="n">
-        <v>6.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="179">
@@ -12978,13 +12978,13 @@
         <v>0</v>
       </c>
       <c r="R179" t="n">
-        <v>18220</v>
+        <v>18460</v>
       </c>
       <c r="S179" t="n">
         <v>18400</v>
       </c>
       <c r="T179" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="180">
@@ -13050,13 +13050,13 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>80700</v>
+        <v>81400</v>
       </c>
       <c r="S180" t="n">
         <v>74800</v>
       </c>
       <c r="T180" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="181">
@@ -13122,13 +13122,13 @@
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>81400</v>
+        <v>82000</v>
       </c>
       <c r="S181" t="n">
         <v>83600</v>
       </c>
       <c r="T181" t="n">
-        <v>-2.6</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="182">
@@ -13194,13 +13194,13 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>168800</v>
+        <v>168500</v>
       </c>
       <c r="S182" t="n">
         <v>175800</v>
       </c>
       <c r="T182" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="183">
@@ -13266,13 +13266,13 @@
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>272000</v>
+        <v>280000</v>
       </c>
       <c r="S183" t="n">
         <v>229500</v>
       </c>
       <c r="T183" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="184">
@@ -13338,13 +13338,13 @@
         <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>85800</v>
+        <v>85900</v>
       </c>
       <c r="S184" t="n">
         <v>93400</v>
       </c>
       <c r="T184" t="n">
-        <v>-8.1</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="185">
@@ -13410,13 +13410,13 @@
         <v>-19</v>
       </c>
       <c r="R185" t="n">
-        <v>45450</v>
+        <v>46850</v>
       </c>
       <c r="S185" t="n">
         <v>43850</v>
       </c>
       <c r="T185" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="186">
@@ -13455,13 +13455,13 @@
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>9450</v>
+        <v>9400</v>
       </c>
       <c r="S186" t="n">
         <v>9500</v>
       </c>
       <c r="T186" t="n">
-        <v>-0.5</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="187">
@@ -13527,13 +13527,13 @@
         <v>5</v>
       </c>
       <c r="R187" t="n">
-        <v>55900</v>
+        <v>55300</v>
       </c>
       <c r="S187" t="n">
         <v>58600</v>
       </c>
       <c r="T187" t="n">
-        <v>-4.6</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="188">
@@ -13599,13 +13599,13 @@
         <v>4.1</v>
       </c>
       <c r="R188" t="n">
-        <v>40650</v>
+        <v>41050</v>
       </c>
       <c r="S188" t="n">
         <v>41550</v>
       </c>
       <c r="T188" t="n">
-        <v>-2.2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="189">
@@ -13671,13 +13671,13 @@
         <v>-3.2</v>
       </c>
       <c r="R189" t="n">
-        <v>392500</v>
+        <v>398500</v>
       </c>
       <c r="S189" t="n">
         <v>392500</v>
       </c>
       <c r="T189" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="190">
@@ -13743,13 +13743,13 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>257500</v>
+        <v>260000</v>
       </c>
       <c r="S190" t="n">
         <v>207000</v>
       </c>
       <c r="T190" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="191">
@@ -13815,13 +13815,13 @@
         <v>-0.4</v>
       </c>
       <c r="R191" t="n">
-        <v>116100</v>
+        <v>116700</v>
       </c>
       <c r="S191" t="n">
         <v>126300</v>
       </c>
       <c r="T191" t="n">
-        <v>-8.1</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="192">
@@ -13887,13 +13887,13 @@
         <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>15050</v>
+        <v>15130</v>
       </c>
       <c r="S192" t="n">
         <v>15150</v>
       </c>
       <c r="T192" t="n">
-        <v>-0.7</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="193">
@@ -13959,13 +13959,13 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>17280</v>
+        <v>17470</v>
       </c>
       <c r="S193" t="n">
         <v>17870</v>
       </c>
       <c r="T193" t="n">
-        <v>-3.3</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="194">
@@ -14031,13 +14031,13 @@
         <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>77900</v>
+        <v>78900</v>
       </c>
       <c r="S194" t="n">
         <v>81600</v>
       </c>
       <c r="T194" t="n">
-        <v>-4.5</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="195">
@@ -14166,13 +14166,13 @@
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>112900</v>
+        <v>113900</v>
       </c>
       <c r="S196" t="n">
         <v>113200</v>
       </c>
       <c r="T196" t="n">
-        <v>-0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="197">
@@ -14238,13 +14238,13 @@
         <v>1.1</v>
       </c>
       <c r="R197" t="n">
-        <v>254500</v>
+        <v>256000</v>
       </c>
       <c r="S197" t="n">
         <v>273500</v>
       </c>
       <c r="T197" t="n">
-        <v>-6.9</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="198">
@@ -14310,13 +14310,13 @@
         <v>-21.6</v>
       </c>
       <c r="R198" t="n">
-        <v>40300</v>
+        <v>40700</v>
       </c>
       <c r="S198" t="n">
         <v>41400</v>
       </c>
       <c r="T198" t="n">
-        <v>-2.7</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="199">
@@ -14355,13 +14355,13 @@
         <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>10160</v>
+        <v>10180</v>
       </c>
       <c r="S199" t="n">
         <v>9680</v>
       </c>
       <c r="T199" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="200">
@@ -14427,13 +14427,13 @@
         <v>1.1</v>
       </c>
       <c r="R200" t="n">
-        <v>70700</v>
+        <v>71600</v>
       </c>
       <c r="S200" t="n">
         <v>70500</v>
       </c>
       <c r="T200" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="201">
@@ -14499,13 +14499,13 @@
         <v>12.6</v>
       </c>
       <c r="R201" t="n">
-        <v>137300</v>
+        <v>136700</v>
       </c>
       <c r="S201" t="n">
         <v>106700</v>
       </c>
       <c r="T201" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="202">
@@ -14571,13 +14571,13 @@
         <v>1.4</v>
       </c>
       <c r="R202" t="n">
-        <v>38450</v>
+        <v>38500</v>
       </c>
       <c r="S202" t="n">
         <v>38250</v>
       </c>
       <c r="T202" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="203">
@@ -14643,13 +14643,13 @@
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>28150</v>
+        <v>28000</v>
       </c>
       <c r="S203" t="n">
         <v>28850</v>
       </c>
       <c r="T203" t="n">
-        <v>-2.4</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="204">
@@ -14706,13 +14706,13 @@
         <v>26.8</v>
       </c>
       <c r="R204" t="n">
-        <v>36350</v>
+        <v>36950</v>
       </c>
       <c r="S204" t="n">
         <v>34100</v>
       </c>
       <c r="T204" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="205">
@@ -14778,13 +14778,13 @@
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>68200</v>
+        <v>68300</v>
       </c>
       <c r="S205" t="n">
         <v>70500</v>
       </c>
       <c r="T205" t="n">
-        <v>-3.3</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="206">
@@ -14850,13 +14850,13 @@
         <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>77300</v>
+        <v>79000</v>
       </c>
       <c r="S206" t="n">
         <v>70600</v>
       </c>
       <c r="T206" t="n">
-        <v>9.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="207">
@@ -14922,13 +14922,13 @@
         <v>-3.1</v>
       </c>
       <c r="R207" t="n">
-        <v>61800</v>
+        <v>61600</v>
       </c>
       <c r="S207" t="n">
         <v>62300</v>
       </c>
       <c r="T207" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="208">
@@ -14994,13 +14994,13 @@
         <v>15.4</v>
       </c>
       <c r="R208" t="n">
-        <v>249000</v>
+        <v>247500</v>
       </c>
       <c r="S208" t="n">
         <v>205500</v>
       </c>
       <c r="T208" t="n">
-        <v>21.2</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="209">
@@ -15066,13 +15066,13 @@
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>41400</v>
+        <v>41650</v>
       </c>
       <c r="S209" t="n">
         <v>41600</v>
       </c>
       <c r="T209" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="210">
@@ -15138,13 +15138,13 @@
         <v>-2.4</v>
       </c>
       <c r="R210" t="n">
-        <v>313000</v>
+        <v>314000</v>
       </c>
       <c r="S210" t="n">
         <v>305000</v>
       </c>
       <c r="T210" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
@@ -15210,13 +15210,13 @@
         <v>0.3</v>
       </c>
       <c r="R211" t="n">
-        <v>55300</v>
+        <v>57100</v>
       </c>
       <c r="S211" t="n">
         <v>50800</v>
       </c>
       <c r="T211" t="n">
-        <v>8.9</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="212">
@@ -15282,13 +15282,13 @@
         <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>1547000</v>
+        <v>1548000</v>
       </c>
       <c r="S212" t="n">
         <v>1556000</v>
       </c>
       <c r="T212" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="213">
@@ -15354,13 +15354,13 @@
         <v>-5.3</v>
       </c>
       <c r="R213" t="n">
-        <v>38150</v>
+        <v>37500</v>
       </c>
       <c r="S213" t="n">
         <v>45900</v>
       </c>
       <c r="T213" t="n">
-        <v>-16.9</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="214">
@@ -15426,13 +15426,13 @@
         <v>-0.8</v>
       </c>
       <c r="R214" t="n">
-        <v>401000</v>
+        <v>398000</v>
       </c>
       <c r="S214" t="n">
         <v>378500</v>
       </c>
       <c r="T214" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="215">
@@ -15498,13 +15498,13 @@
         <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>52100</v>
+        <v>53200</v>
       </c>
       <c r="S215" t="n">
         <v>48450</v>
       </c>
       <c r="T215" t="n">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -15570,13 +15570,13 @@
         <v>2.7</v>
       </c>
       <c r="R216" t="n">
-        <v>104500</v>
+        <v>108700</v>
       </c>
       <c r="S216" t="n">
         <v>110000</v>
       </c>
       <c r="T216" t="n">
-        <v>-5</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="217">
@@ -15642,13 +15642,13 @@
         <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>105700</v>
+        <v>106400</v>
       </c>
       <c r="S217" t="n">
         <v>100100</v>
       </c>
       <c r="T217" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="218">
@@ -15714,13 +15714,13 @@
         <v>-2.4</v>
       </c>
       <c r="R218" t="n">
-        <v>111100</v>
+        <v>116600</v>
       </c>
       <c r="S218" t="n">
         <v>88300</v>
       </c>
       <c r="T218" t="n">
-        <v>25.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="219">
@@ -15786,13 +15786,13 @@
         <v>2.9</v>
       </c>
       <c r="R219" t="n">
-        <v>65100</v>
+        <v>66100</v>
       </c>
       <c r="S219" t="n">
         <v>63600</v>
       </c>
       <c r="T219" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="220">
@@ -15858,13 +15858,13 @@
         <v>10.9</v>
       </c>
       <c r="R220" t="n">
-        <v>129000</v>
+        <v>127200</v>
       </c>
       <c r="S220" t="n">
         <v>95900</v>
       </c>
       <c r="T220" t="n">
-        <v>34.5</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="221">
@@ -15930,13 +15930,13 @@
         <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>114000</v>
+        <v>116700</v>
       </c>
       <c r="S221" t="n">
         <v>107000</v>
       </c>
       <c r="T221" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="222">
@@ -16002,13 +16002,13 @@
         <v>-1.4</v>
       </c>
       <c r="R222" t="n">
-        <v>38850</v>
+        <v>39100</v>
       </c>
       <c r="S222" t="n">
         <v>40900</v>
       </c>
       <c r="T222" t="n">
-        <v>-5</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="223">
@@ -16074,13 +16074,13 @@
         <v>20.1</v>
       </c>
       <c r="R223" t="n">
-        <v>53100</v>
+        <v>53000</v>
       </c>
       <c r="S223" t="n">
         <v>49500</v>
       </c>
       <c r="T223" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="224">
@@ -16146,13 +16146,13 @@
         <v>1.3</v>
       </c>
       <c r="R224" t="n">
-        <v>23550</v>
+        <v>23600</v>
       </c>
       <c r="S224" t="n">
         <v>25200</v>
       </c>
       <c r="T224" t="n">
-        <v>-6.5</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="225">
@@ -16218,13 +16218,13 @@
         <v>0.3</v>
       </c>
       <c r="R225" t="n">
-        <v>43950</v>
+        <v>42850</v>
       </c>
       <c r="S225" t="n">
         <v>39300</v>
       </c>
       <c r="T225" t="n">
-        <v>11.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="226">
@@ -16290,13 +16290,13 @@
         <v>-0.2</v>
       </c>
       <c r="R226" t="n">
-        <v>237000</v>
+        <v>238000</v>
       </c>
       <c r="S226" t="n">
         <v>241500</v>
       </c>
       <c r="T226" t="n">
-        <v>-1.9</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="227">
@@ -16362,13 +16362,13 @@
         <v>-15.3</v>
       </c>
       <c r="R227" t="n">
-        <v>31400</v>
+        <v>31250</v>
       </c>
       <c r="S227" t="n">
         <v>35600</v>
       </c>
       <c r="T227" t="n">
-        <v>-11.8</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="228">
@@ -16434,13 +16434,13 @@
         <v>3.6</v>
       </c>
       <c r="R228" t="n">
-        <v>236500</v>
+        <v>235500</v>
       </c>
       <c r="S228" t="n">
         <v>225000</v>
       </c>
       <c r="T228" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="229">
@@ -16506,13 +16506,13 @@
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>774000</v>
+        <v>803000</v>
       </c>
       <c r="S229" t="n">
         <v>762000</v>
       </c>
       <c r="T229" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="230">
@@ -16578,13 +16578,13 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>135900</v>
+        <v>138600</v>
       </c>
       <c r="S230" t="n">
         <v>138100</v>
       </c>
       <c r="T230" t="n">
-        <v>-1.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="231">
@@ -16650,13 +16650,13 @@
         <v>0.1</v>
       </c>
       <c r="R231" t="n">
-        <v>135500</v>
+        <v>134000</v>
       </c>
       <c r="S231" t="n">
         <v>137600</v>
       </c>
       <c r="T231" t="n">
-        <v>-1.5</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="232">
@@ -16794,13 +16794,13 @@
         <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>5260</v>
+        <v>5320</v>
       </c>
       <c r="S233" t="n">
         <v>5380</v>
       </c>
       <c r="T233" t="n">
-        <v>-2.2</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="234">
@@ -16857,13 +16857,13 @@
         <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>496500</v>
+        <v>501000</v>
       </c>
       <c r="S234" t="n">
         <v>465000</v>
       </c>
       <c r="T234" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="235">
@@ -16929,13 +16929,13 @@
         <v>0.8</v>
       </c>
       <c r="R235" t="n">
-        <v>393000</v>
+        <v>390500</v>
       </c>
       <c r="S235" t="n">
         <v>384500</v>
       </c>
       <c r="T235" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="236">
@@ -17001,13 +17001,13 @@
         <v>9.300000000000001</v>
       </c>
       <c r="R236" t="n">
-        <v>127500</v>
+        <v>129300</v>
       </c>
       <c r="S236" t="n">
         <v>116900</v>
       </c>
       <c r="T236" t="n">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="237">
@@ -17073,13 +17073,13 @@
         <v>4.6</v>
       </c>
       <c r="R237" t="n">
-        <v>147000</v>
+        <v>145200</v>
       </c>
       <c r="S237" t="n">
         <v>153100</v>
       </c>
       <c r="T237" t="n">
-        <v>-4</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="238">
@@ -17145,13 +17145,13 @@
         <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>50100</v>
+        <v>50000</v>
       </c>
       <c r="S238" t="n">
         <v>43650</v>
       </c>
       <c r="T238" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="239">
@@ -17217,13 +17217,13 @@
         <v>0</v>
       </c>
       <c r="R239" t="n">
-        <v>22000</v>
+        <v>22100</v>
       </c>
       <c r="S239" t="n">
         <v>22650</v>
       </c>
       <c r="T239" t="n">
-        <v>-2.9</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="240">
@@ -17289,13 +17289,13 @@
         <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>323000</v>
+        <v>330500</v>
       </c>
       <c r="S240" t="n">
         <v>339000</v>
       </c>
       <c r="T240" t="n">
-        <v>-4.7</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="241">
@@ -17361,13 +17361,13 @@
         <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>2865000</v>
+        <v>2954000</v>
       </c>
       <c r="S241" t="n">
         <v>2832000</v>
       </c>
       <c r="T241" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="242">
@@ -17433,13 +17433,13 @@
         <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>174700</v>
+        <v>177700</v>
       </c>
       <c r="S242" t="n">
         <v>183200</v>
       </c>
       <c r="T242" t="n">
-        <v>-4.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="243">
@@ -17496,13 +17496,13 @@
         <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>83500</v>
+        <v>84100</v>
       </c>
       <c r="S243" t="n">
         <v>86600</v>
       </c>
       <c r="T243" t="n">
-        <v>-3.6</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="244">
@@ -17568,13 +17568,13 @@
         <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>14770</v>
+        <v>14900</v>
       </c>
       <c r="S244" t="n">
         <v>14830</v>
       </c>
       <c r="T244" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="245">
@@ -17631,13 +17631,13 @@
         <v>-184.9</v>
       </c>
       <c r="R245" t="n">
-        <v>37300</v>
+        <v>37650</v>
       </c>
       <c r="S245" t="n">
         <v>36850</v>
       </c>
       <c r="T245" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="246">
@@ -17703,13 +17703,13 @@
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>131100</v>
+        <v>132800</v>
       </c>
       <c r="S246" t="n">
         <v>132000</v>
       </c>
       <c r="T246" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="247">
@@ -17775,13 +17775,13 @@
         <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>473500</v>
+        <v>489500</v>
       </c>
       <c r="S247" t="n">
         <v>412000</v>
       </c>
       <c r="T247" t="n">
-        <v>14.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="248">
@@ -17847,13 +17847,13 @@
         <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>33350</v>
+        <v>33700</v>
       </c>
       <c r="S248" t="n">
         <v>34800</v>
       </c>
       <c r="T248" t="n">
-        <v>-4.2</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="249">
@@ -17913,13 +17913,13 @@
         <v>1043</v>
       </c>
       <c r="R249" t="n">
-        <v>9590</v>
+        <v>10030</v>
       </c>
       <c r="S249" t="n">
         <v>8320</v>
       </c>
       <c r="T249" t="n">
-        <v>15.3</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="250">
@@ -17985,13 +17985,13 @@
         <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>128000</v>
+        <v>134100</v>
       </c>
       <c r="S250" t="n">
         <v>118400</v>
       </c>
       <c r="T250" t="n">
-        <v>8.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="251">
@@ -18057,13 +18057,13 @@
         <v>-0.5</v>
       </c>
       <c r="R251" t="n">
-        <v>22150</v>
+        <v>22200</v>
       </c>
       <c r="S251" t="n">
         <v>22000</v>
       </c>
       <c r="T251" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="252">
@@ -18129,13 +18129,13 @@
         <v>0.1</v>
       </c>
       <c r="R252" t="n">
-        <v>86800</v>
+        <v>87300</v>
       </c>
       <c r="S252" t="n">
         <v>85400</v>
       </c>
       <c r="T252" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="253">
@@ -18201,13 +18201,13 @@
         <v>-0.9</v>
       </c>
       <c r="R253" t="n">
-        <v>507000</v>
+        <v>510000</v>
       </c>
       <c r="S253" t="n">
         <v>506000</v>
       </c>
       <c r="T253" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="254">
@@ -18273,13 +18273,13 @@
         <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>177600</v>
+        <v>179400</v>
       </c>
       <c r="S254" t="n">
         <v>185000</v>
       </c>
       <c r="T254" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="255">
@@ -18345,13 +18345,13 @@
         <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>116200</v>
+        <v>119100</v>
       </c>
       <c r="S255" t="n">
         <v>103800</v>
       </c>
       <c r="T255" t="n">
-        <v>11.9</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="256">
@@ -18417,13 +18417,13 @@
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>306000</v>
+        <v>322000</v>
       </c>
       <c r="S256" t="n">
         <v>295000</v>
       </c>
       <c r="T256" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -18489,13 +18489,13 @@
         <v>-40.6</v>
       </c>
       <c r="R257" t="n">
-        <v>15260</v>
+        <v>15550</v>
       </c>
       <c r="S257" t="n">
         <v>14980</v>
       </c>
       <c r="T257" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="258">
@@ -18561,13 +18561,13 @@
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>361000</v>
+        <v>369500</v>
       </c>
       <c r="S258" t="n">
         <v>360000</v>
       </c>
       <c r="T258" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="259">
@@ -18633,13 +18633,13 @@
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>73400</v>
+        <v>73800</v>
       </c>
       <c r="S259" t="n">
         <v>72000</v>
       </c>
       <c r="T259" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="260">
@@ -18705,13 +18705,13 @@
         <v>-2.1</v>
       </c>
       <c r="R260" t="n">
-        <v>19750</v>
+        <v>19800</v>
       </c>
       <c r="S260" t="n">
         <v>19660</v>
       </c>
       <c r="T260" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="261">
@@ -18777,13 +18777,13 @@
         <v>-15.5</v>
       </c>
       <c r="R261" t="n">
-        <v>45450</v>
+        <v>45150</v>
       </c>
       <c r="S261" t="n">
         <v>42000</v>
       </c>
       <c r="T261" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="262">
@@ -18849,13 +18849,13 @@
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>67500</v>
+        <v>67000</v>
       </c>
       <c r="S262" t="n">
         <v>67000</v>
       </c>
       <c r="T262" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -18894,13 +18894,13 @@
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>41550</v>
+        <v>41100</v>
       </c>
       <c r="S263" t="n">
         <v>33500</v>
       </c>
       <c r="T263" t="n">
-        <v>24</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="264">
@@ -18966,13 +18966,13 @@
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>1143000</v>
+        <v>1154000</v>
       </c>
       <c r="S264" t="n">
         <v>939000</v>
       </c>
       <c r="T264" t="n">
-        <v>21.7</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="265">
@@ -19011,13 +19011,13 @@
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>39550</v>
+        <v>40400</v>
       </c>
       <c r="S265" t="n">
         <v>34400</v>
       </c>
       <c r="T265" t="n">
-        <v>15</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="266">
@@ -19083,13 +19083,13 @@
         <v>0.9</v>
       </c>
       <c r="R266" t="n">
-        <v>116100</v>
+        <v>120100</v>
       </c>
       <c r="S266" t="n">
         <v>110300</v>
       </c>
       <c r="T266" t="n">
-        <v>5.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="267">
@@ -19155,13 +19155,13 @@
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>55500</v>
+        <v>54700</v>
       </c>
       <c r="S267" t="n">
         <v>49150</v>
       </c>
       <c r="T267" t="n">
-        <v>12.9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="268">
@@ -19227,13 +19227,13 @@
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>65400</v>
+        <v>65500</v>
       </c>
       <c r="S268" t="n">
         <v>57100</v>
       </c>
       <c r="T268" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="269">
@@ -19299,13 +19299,13 @@
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>200500</v>
+        <v>196800</v>
       </c>
       <c r="S269" t="n">
         <v>196400</v>
       </c>
       <c r="T269" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="270">
@@ -19371,13 +19371,13 @@
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>79300</v>
+        <v>80900</v>
       </c>
       <c r="S270" t="n">
         <v>77400</v>
       </c>
       <c r="T270" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="271">
@@ -19443,13 +19443,13 @@
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>9800</v>
+        <v>9860</v>
       </c>
       <c r="S271" t="n">
         <v>9800</v>
       </c>
       <c r="T271" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="272">
@@ -19515,13 +19515,13 @@
         <v>-5.5</v>
       </c>
       <c r="R272" t="n">
-        <v>31200</v>
+        <v>31700</v>
       </c>
       <c r="S272" t="n">
         <v>32750</v>
       </c>
       <c r="T272" t="n">
-        <v>-4.7</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="273">
@@ -19587,13 +19587,13 @@
         <v>1.1</v>
       </c>
       <c r="R273" t="n">
-        <v>228000</v>
+        <v>228500</v>
       </c>
       <c r="S273" t="n">
         <v>246000</v>
       </c>
       <c r="T273" t="n">
-        <v>-7.3</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="274">
@@ -19659,13 +19659,13 @@
         <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>18030</v>
+        <v>17820</v>
       </c>
       <c r="S274" t="n">
         <v>16000</v>
       </c>
       <c r="T274" t="n">
-        <v>12.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="275">
@@ -19731,13 +19731,13 @@
         <v>-1</v>
       </c>
       <c r="R275" t="n">
-        <v>53200</v>
+        <v>53300</v>
       </c>
       <c r="S275" t="n">
         <v>48900</v>
       </c>
       <c r="T275" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276">
@@ -19776,13 +19776,13 @@
         <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>45400</v>
+        <v>45900</v>
       </c>
       <c r="S276" t="n">
         <v>46200</v>
       </c>
       <c r="T276" t="n">
-        <v>-1.7</v>
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -455,7 +455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-14 · 전주 2026-08-07</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-15 · 전주 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -597,31 +597,31 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1913.1</v>
+        <v>1912.4</v>
       </c>
       <c r="J3" t="n">
         <v>1913.1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>2014.5</v>
+        <v>2027</v>
       </c>
       <c r="M3" t="n">
         <v>2014.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2156.6</v>
+        <v>2164.2</v>
       </c>
       <c r="P3" t="n">
         <v>2156.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R3" t="n">
         <v>15850</v>
@@ -1290,31 +1290,31 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>30987.2</v>
+        <v>31281.5</v>
       </c>
       <c r="J13" t="n">
         <v>30987.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L13" t="n">
-        <v>33793.2</v>
+        <v>36815.2</v>
       </c>
       <c r="M13" t="n">
         <v>33793.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="O13" t="n">
-        <v>34047.1</v>
+        <v>37033.8</v>
       </c>
       <c r="P13" t="n">
         <v>34047.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>615000</v>
@@ -1713,31 +1713,31 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10874.9</v>
+        <v>10934.2</v>
       </c>
       <c r="J19" t="n">
         <v>10874.9</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>12172.3</v>
+        <v>12243.7</v>
       </c>
       <c r="M19" t="n">
         <v>12172.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>13312.2</v>
+        <v>13359.8</v>
       </c>
       <c r="P19" t="n">
         <v>13312.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R19" t="n">
         <v>45350</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1772.2</v>
+        <v>1771.6</v>
       </c>
       <c r="J22" t="n">
         <v>1776.7</v>
@@ -1920,7 +1920,7 @@
         <v>-0.3</v>
       </c>
       <c r="L22" t="n">
-        <v>2130.3</v>
+        <v>2132.2</v>
       </c>
       <c r="M22" t="n">
         <v>2139.9</v>
@@ -1929,7 +1929,7 @@
         <v>-0.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2401.6</v>
+        <v>2400.2</v>
       </c>
       <c r="P22" t="n">
         <v>2437.2</v>
@@ -2478,31 +2478,31 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>15660.6</v>
+        <v>16363.9</v>
       </c>
       <c r="J30" t="n">
         <v>16388.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.4</v>
+        <v>-0.2</v>
       </c>
       <c r="L30" t="n">
-        <v>18708.9</v>
+        <v>20311.2</v>
       </c>
       <c r="M30" t="n">
         <v>20712.2</v>
       </c>
       <c r="N30" t="n">
-        <v>-9.699999999999999</v>
+        <v>-1.9</v>
       </c>
       <c r="O30" t="n">
-        <v>20155.3</v>
+        <v>22126.9</v>
       </c>
       <c r="P30" t="n">
         <v>21913.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>120000</v>
@@ -3198,31 +3198,31 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>21369.8</v>
+        <v>23213.5</v>
       </c>
       <c r="J40" t="n">
         <v>21369.8</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="L40" t="n">
-        <v>23187</v>
+        <v>23939.7</v>
       </c>
       <c r="M40" t="n">
         <v>23187</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O40" t="n">
-        <v>24471.6</v>
+        <v>25246.5</v>
       </c>
       <c r="P40" t="n">
         <v>24471.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
         <v>176800</v>
@@ -3486,31 +3486,31 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>5543</v>
+        <v>5742</v>
       </c>
       <c r="J44" t="n">
         <v>5491.8</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="L44" t="n">
-        <v>5933</v>
+        <v>6005.3</v>
       </c>
       <c r="M44" t="n">
         <v>5863.2</v>
       </c>
       <c r="N44" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
-        <v>6040</v>
+        <v>6140</v>
       </c>
       <c r="P44" t="n">
         <v>6013</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="R44" t="n">
         <v>37550</v>
@@ -3918,31 +3918,31 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>47527.2</v>
+        <v>47797.9</v>
       </c>
       <c r="J50" t="n">
         <v>42637.8</v>
       </c>
       <c r="K50" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="L50" t="n">
-        <v>26108.4</v>
+        <v>26153.7</v>
       </c>
       <c r="M50" t="n">
         <v>26349.2</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="O50" t="n">
-        <v>27025.7</v>
+        <v>27203.7</v>
       </c>
       <c r="P50" t="n">
         <v>27155.9</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R50" t="n">
         <v>37650</v>
@@ -4485,31 +4485,31 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>383.2</v>
+        <v>389.2</v>
       </c>
       <c r="J58" t="n">
         <v>378.1</v>
       </c>
       <c r="K58" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="L58" t="n">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="M58" t="n">
         <v>447.1</v>
       </c>
       <c r="N58" t="n">
-        <v>-3.8</v>
+        <v>-4.7</v>
       </c>
       <c r="O58" t="n">
-        <v>537.5</v>
+        <v>524.2</v>
       </c>
       <c r="P58" t="n">
         <v>585.4</v>
       </c>
       <c r="Q58" t="n">
-        <v>-8.199999999999999</v>
+        <v>-10.5</v>
       </c>
       <c r="R58" t="n">
         <v>40500</v>
@@ -5061,31 +5061,31 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1950.4</v>
+        <v>1768.2</v>
       </c>
       <c r="J66" t="n">
         <v>1998</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.4</v>
+        <v>-11.5</v>
       </c>
       <c r="L66" t="n">
-        <v>2052</v>
+        <v>1935.2</v>
       </c>
       <c r="M66" t="n">
         <v>2174.8</v>
       </c>
       <c r="N66" t="n">
-        <v>-5.6</v>
+        <v>-11</v>
       </c>
       <c r="O66" t="n">
-        <v>3472.8</v>
+        <v>3376.5</v>
       </c>
       <c r="P66" t="n">
         <v>3560.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>-2.5</v>
+        <v>-5.2</v>
       </c>
       <c r="R66" t="n">
         <v>16730</v>
@@ -5349,31 +5349,31 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>14632.7</v>
+        <v>15670.8</v>
       </c>
       <c r="J70" t="n">
         <v>14632.7</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="L70" t="n">
-        <v>10103.5</v>
+        <v>10170.2</v>
       </c>
       <c r="M70" t="n">
         <v>10103.5</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O70" t="n">
-        <v>10048.4</v>
+        <v>8860.5</v>
       </c>
       <c r="P70" t="n">
         <v>10048.4</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>-11.8</v>
       </c>
       <c r="R70" t="n">
         <v>21250</v>
@@ -6060,31 +6060,31 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1880</v>
+        <v>1880.4</v>
       </c>
       <c r="J80" t="n">
         <v>1879.4</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L80" t="n">
-        <v>2387.1</v>
+        <v>2382.7</v>
       </c>
       <c r="M80" t="n">
         <v>2389</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="O80" t="n">
-        <v>3114.2</v>
+        <v>3075</v>
       </c>
       <c r="P80" t="n">
         <v>3090.2</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="R80" t="n">
         <v>218500</v>
@@ -6204,31 +6204,31 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>84649.3</v>
+        <v>81516.39999999999</v>
       </c>
       <c r="J82" t="n">
         <v>97891.39999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-13.5</v>
+        <v>-16.7</v>
       </c>
       <c r="L82" t="n">
-        <v>121459.2</v>
+        <v>118344.1</v>
       </c>
       <c r="M82" t="n">
         <v>137111.9</v>
       </c>
       <c r="N82" t="n">
-        <v>-11.4</v>
+        <v>-13.7</v>
       </c>
       <c r="O82" t="n">
-        <v>139310.8</v>
+        <v>139037.8</v>
       </c>
       <c r="P82" t="n">
         <v>152635.4</v>
       </c>
       <c r="Q82" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="R82" t="n">
         <v>33250</v>
@@ -6780,31 +6780,31 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>482</v>
+        <v>467.8</v>
       </c>
       <c r="J90" t="n">
         <v>482</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="L90" t="n">
-        <v>820</v>
+        <v>765.2</v>
       </c>
       <c r="M90" t="n">
         <v>820</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>-6.7</v>
       </c>
       <c r="O90" t="n">
-        <v>740.3</v>
+        <v>746.8</v>
       </c>
       <c r="P90" t="n">
         <v>740.3</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="R90" t="n">
         <v>23200</v>
@@ -7130,15 +7130,6 @@
           <t>KOSPI200,커버리지</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>1557</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1557</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
       <c r="I95" t="n">
         <v>6781</v>
       </c>
@@ -7617,31 +7608,31 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>33560.4</v>
+        <v>32159.5</v>
       </c>
       <c r="J102" t="n">
         <v>33471.6</v>
       </c>
       <c r="K102" t="n">
-        <v>0.3</v>
+        <v>-3.9</v>
       </c>
       <c r="L102" t="n">
-        <v>55259.8</v>
+        <v>68894.5</v>
       </c>
       <c r="M102" t="n">
         <v>55410.6</v>
       </c>
       <c r="N102" t="n">
-        <v>-0.3</v>
+        <v>24.3</v>
       </c>
       <c r="O102" t="n">
-        <v>33270.9</v>
+        <v>45521.6</v>
       </c>
       <c r="P102" t="n">
         <v>33270.9</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>36.8</v>
       </c>
       <c r="R102" t="n">
         <v>301000</v>
@@ -8184,31 +8175,31 @@
         <v>-0.1</v>
       </c>
       <c r="I110" t="n">
-        <v>22425.2</v>
+        <v>22171.3</v>
       </c>
       <c r="J110" t="n">
         <v>23801.6</v>
       </c>
       <c r="K110" t="n">
-        <v>-5.8</v>
+        <v>-6.8</v>
       </c>
       <c r="L110" t="n">
-        <v>26076.1</v>
+        <v>25835.1</v>
       </c>
       <c r="M110" t="n">
         <v>27787.1</v>
       </c>
       <c r="N110" t="n">
-        <v>-6.2</v>
+        <v>-7</v>
       </c>
       <c r="O110" t="n">
-        <v>30354.1</v>
+        <v>30038.4</v>
       </c>
       <c r="P110" t="n">
         <v>31999.8</v>
       </c>
       <c r="Q110" t="n">
-        <v>-5.1</v>
+        <v>-6.1</v>
       </c>
       <c r="R110" t="n">
         <v>228000</v>
@@ -8400,31 +8391,31 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>1541.9</v>
+        <v>1529.1</v>
       </c>
       <c r="J113" t="n">
         <v>1676.8</v>
       </c>
       <c r="K113" t="n">
-        <v>-8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L113" t="n">
-        <v>1702.5</v>
+        <v>1681.4</v>
       </c>
       <c r="M113" t="n">
         <v>1888.7</v>
       </c>
       <c r="N113" t="n">
-        <v>-9.9</v>
+        <v>-11</v>
       </c>
       <c r="O113" t="n">
-        <v>1734.1</v>
+        <v>1702.3</v>
       </c>
       <c r="P113" t="n">
         <v>1924.5</v>
       </c>
       <c r="Q113" t="n">
-        <v>-9.9</v>
+        <v>-11.5</v>
       </c>
       <c r="R113" t="n">
         <v>41050</v>
@@ -8562,13 +8553,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O115" t="n">
-        <v>24280.4</v>
+        <v>24366.8</v>
       </c>
       <c r="P115" t="n">
         <v>22082.9</v>
       </c>
       <c r="Q115" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="R115" t="n">
         <v>36600</v>
@@ -8832,31 +8823,31 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>519.4</v>
+        <v>507.8</v>
       </c>
       <c r="J119" t="n">
         <v>525.4</v>
       </c>
       <c r="K119" t="n">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="L119" t="n">
-        <v>678.8</v>
+        <v>651.2</v>
       </c>
       <c r="M119" t="n">
         <v>678.8</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>-4.1</v>
       </c>
       <c r="O119" t="n">
-        <v>756.8</v>
+        <v>723.5</v>
       </c>
       <c r="P119" t="n">
         <v>766.8</v>
       </c>
       <c r="Q119" t="n">
-        <v>-1.3</v>
+        <v>-5.6</v>
       </c>
       <c r="R119" t="n">
         <v>32700</v>
@@ -9164,15 +9155,6 @@
           <t>KOSPI200,커버리지</t>
         </is>
       </c>
-      <c r="F124" t="n">
-        <v>5335</v>
-      </c>
-      <c r="G124" t="n">
-        <v>5335</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
       <c r="I124" t="n">
         <v>22530</v>
       </c>
@@ -9462,31 +9444,31 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>3712.8</v>
+        <v>3653.6</v>
       </c>
       <c r="J128" t="n">
         <v>3849.6</v>
       </c>
       <c r="K128" t="n">
-        <v>-3.6</v>
+        <v>-5.1</v>
       </c>
       <c r="L128" t="n">
-        <v>5996.2</v>
+        <v>5956.6</v>
       </c>
       <c r="M128" t="n">
         <v>6069.3</v>
       </c>
       <c r="N128" t="n">
-        <v>-1.2</v>
+        <v>-1.9</v>
       </c>
       <c r="O128" t="n">
-        <v>7480.7</v>
+        <v>7433.4</v>
       </c>
       <c r="P128" t="n">
         <v>7572.3</v>
       </c>
       <c r="Q128" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="R128" t="n">
         <v>146400</v>
@@ -11880,40 +11862,40 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G163" t="n">
         <v>249</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I163" t="n">
-        <v>1027.3</v>
+        <v>1055.5</v>
       </c>
       <c r="J163" t="n">
         <v>1027.3</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L163" t="n">
-        <v>1319</v>
+        <v>1382</v>
       </c>
       <c r="M163" t="n">
         <v>1319</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O163" t="n">
-        <v>1390</v>
+        <v>1350</v>
       </c>
       <c r="P163" t="n">
         <v>1390</v>
       </c>
       <c r="Q163" t="n">
-        <v>0</v>
+        <v>-2.9</v>
       </c>
       <c r="R163" t="n">
         <v>131100</v>
@@ -12546,31 +12528,31 @@
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>1018.8</v>
+        <v>1031.3</v>
       </c>
       <c r="J173" t="n">
         <v>1015.8</v>
       </c>
       <c r="K173" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="L173" t="n">
-        <v>1375</v>
+        <v>1441</v>
       </c>
       <c r="M173" t="n">
         <v>1356.6</v>
       </c>
       <c r="N173" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="O173" t="n">
-        <v>1823.4</v>
+        <v>1927.3</v>
       </c>
       <c r="P173" t="n">
         <v>1817.3</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.3</v>
+        <v>6.1</v>
       </c>
       <c r="R173" t="n">
         <v>147500</v>
@@ -12618,22 +12600,22 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="J174" t="n">
         <v>366.5</v>
       </c>
       <c r="K174" t="n">
-        <v>-4.5</v>
+        <v>-5.9</v>
       </c>
       <c r="L174" t="n">
-        <v>485.8</v>
+        <v>493.2</v>
       </c>
       <c r="M174" t="n">
         <v>473.4</v>
       </c>
       <c r="N174" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O174" t="n">
         <v>598.2</v>
@@ -12762,31 +12744,31 @@
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>80330.10000000001</v>
+        <v>84273.89999999999</v>
       </c>
       <c r="J176" t="n">
         <v>80330.10000000001</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L176" t="n">
-        <v>40678.1</v>
+        <v>41287.8</v>
       </c>
       <c r="M176" t="n">
         <v>40678.1</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O176" t="n">
-        <v>44043.8</v>
+        <v>43216.7</v>
       </c>
       <c r="P176" t="n">
         <v>44043.8</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>-1.9</v>
       </c>
       <c r="R176" t="n">
         <v>128700</v>
@@ -13788,31 +13770,31 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>32341.8</v>
+        <v>32423.4</v>
       </c>
       <c r="J191" t="n">
         <v>31480.7</v>
       </c>
       <c r="K191" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="L191" t="n">
-        <v>34098.8</v>
+        <v>34399</v>
       </c>
       <c r="M191" t="n">
         <v>33722</v>
       </c>
       <c r="N191" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="O191" t="n">
-        <v>35395.8</v>
+        <v>35646.6</v>
       </c>
       <c r="P191" t="n">
         <v>35539.5</v>
       </c>
       <c r="Q191" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R191" t="n">
         <v>116700</v>
@@ -14004,31 +13986,31 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>5200.8</v>
+        <v>4188.1</v>
       </c>
       <c r="J194" t="n">
         <v>5200.8</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>-19.5</v>
       </c>
       <c r="L194" t="n">
-        <v>6201.1</v>
+        <v>5619.9</v>
       </c>
       <c r="M194" t="n">
         <v>6201.1</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>-9.4</v>
       </c>
       <c r="O194" t="n">
-        <v>6784.5</v>
+        <v>6077.9</v>
       </c>
       <c r="P194" t="n">
         <v>6784.5</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>-10.4</v>
       </c>
       <c r="R194" t="n">
         <v>78900</v>
@@ -14283,31 +14265,31 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>783.3</v>
+        <v>768.8</v>
       </c>
       <c r="J198" t="n">
         <v>862.2</v>
       </c>
       <c r="K198" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.8</v>
       </c>
       <c r="L198" t="n">
-        <v>938</v>
+        <v>911</v>
       </c>
       <c r="M198" t="n">
         <v>1060.2</v>
       </c>
       <c r="N198" t="n">
-        <v>-11.5</v>
+        <v>-14.1</v>
       </c>
       <c r="O198" t="n">
-        <v>1175</v>
+        <v>1130</v>
       </c>
       <c r="P198" t="n">
         <v>1499</v>
       </c>
       <c r="Q198" t="n">
-        <v>-21.6</v>
+        <v>-24.6</v>
       </c>
       <c r="R198" t="n">
         <v>40700</v>
@@ -14895,16 +14877,16 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>2836.8</v>
+        <v>2831</v>
       </c>
       <c r="J207" t="n">
         <v>2857.4</v>
       </c>
       <c r="K207" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="L207" t="n">
-        <v>3094.6</v>
+        <v>3094.2</v>
       </c>
       <c r="M207" t="n">
         <v>3131.4</v>
@@ -15111,13 +15093,13 @@
         <v>5.2</v>
       </c>
       <c r="I210" t="n">
-        <v>2588.5</v>
+        <v>2641.5</v>
       </c>
       <c r="J210" t="n">
         <v>2573.5</v>
       </c>
       <c r="K210" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="L210" t="n">
         <v>4463</v>
@@ -15327,31 +15309,31 @@
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>2006.2</v>
+        <v>1944.1</v>
       </c>
       <c r="J213" t="n">
         <v>2107.1</v>
       </c>
       <c r="K213" t="n">
-        <v>-4.8</v>
+        <v>-7.7</v>
       </c>
       <c r="L213" t="n">
-        <v>2665.9</v>
+        <v>2569.5</v>
       </c>
       <c r="M213" t="n">
         <v>2814</v>
       </c>
       <c r="N213" t="n">
-        <v>-5.3</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="O213" t="n">
-        <v>3295.3</v>
+        <v>3234</v>
       </c>
       <c r="P213" t="n">
         <v>3480.9</v>
       </c>
       <c r="Q213" t="n">
-        <v>-5.3</v>
+        <v>-7.1</v>
       </c>
       <c r="R213" t="n">
         <v>37500</v>
@@ -15399,31 +15381,31 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>2709.2</v>
+        <v>2706.6</v>
       </c>
       <c r="J214" t="n">
         <v>2704.3</v>
       </c>
       <c r="K214" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L214" t="n">
-        <v>3369.9</v>
+        <v>3364.9</v>
       </c>
       <c r="M214" t="n">
         <v>3377.6</v>
       </c>
       <c r="N214" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="O214" t="n">
-        <v>4047.7</v>
+        <v>4032.5</v>
       </c>
       <c r="P214" t="n">
         <v>4080.3</v>
       </c>
       <c r="Q214" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="R214" t="n">
         <v>398000</v>
@@ -15543,31 +15525,31 @@
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>2381.4</v>
+        <v>2453.7</v>
       </c>
       <c r="J216" t="n">
         <v>2310.6</v>
       </c>
       <c r="K216" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="L216" t="n">
-        <v>3986.6</v>
+        <v>4074.3</v>
       </c>
       <c r="M216" t="n">
         <v>3869.9</v>
       </c>
       <c r="N216" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="O216" t="n">
-        <v>5005.4</v>
+        <v>5154.1</v>
       </c>
       <c r="P216" t="n">
         <v>4872.6</v>
       </c>
       <c r="Q216" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="R216" t="n">
         <v>108700</v>
@@ -16191,31 +16173,31 @@
         <v>0</v>
       </c>
       <c r="I225" t="n">
-        <v>2784.7</v>
+        <v>2928.9</v>
       </c>
       <c r="J225" t="n">
         <v>2766.7</v>
       </c>
       <c r="K225" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="L225" t="n">
-        <v>3498.9</v>
+        <v>3725</v>
       </c>
       <c r="M225" t="n">
         <v>3488.9</v>
       </c>
       <c r="N225" t="n">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="O225" t="n">
-        <v>4209.2</v>
+        <v>4538.8</v>
       </c>
       <c r="P225" t="n">
         <v>4195.5</v>
       </c>
       <c r="Q225" t="n">
-        <v>0.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R225" t="n">
         <v>42850</v>
@@ -16767,31 +16749,31 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>-297</v>
+        <v>-302.4</v>
       </c>
       <c r="J233" t="n">
         <v>-297</v>
       </c>
       <c r="K233" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="L233" t="n">
-        <v>799</v>
+        <v>790.1</v>
       </c>
       <c r="M233" t="n">
         <v>799</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="O233" t="n">
-        <v>1236</v>
+        <v>1297.8</v>
       </c>
       <c r="P233" t="n">
         <v>1236</v>
       </c>
       <c r="Q233" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R233" t="n">
         <v>5320</v>
@@ -17118,31 +17100,31 @@
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>78.5</v>
+        <v>587</v>
       </c>
       <c r="J238" t="n">
         <v>78.5</v>
       </c>
       <c r="K238" t="n">
-        <v>0</v>
+        <v>647.8</v>
       </c>
       <c r="L238" t="n">
-        <v>1154</v>
+        <v>1592</v>
       </c>
       <c r="M238" t="n">
         <v>1154</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O238" t="n">
-        <v>1770</v>
+        <v>2230</v>
       </c>
       <c r="P238" t="n">
         <v>1770</v>
       </c>
       <c r="Q238" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R238" t="n">
         <v>50000</v>
@@ -18462,31 +18444,31 @@
         <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>-2424.1</v>
+        <v>-2480.9</v>
       </c>
       <c r="J257" t="n">
         <v>-2433.7</v>
       </c>
       <c r="K257" t="n">
-        <v>0.4</v>
+        <v>-1.9</v>
       </c>
       <c r="L257" t="n">
-        <v>-1037.2</v>
+        <v>-1153.1</v>
       </c>
       <c r="M257" t="n">
         <v>-990.8</v>
       </c>
       <c r="N257" t="n">
-        <v>-4.7</v>
+        <v>-16.4</v>
       </c>
       <c r="O257" t="n">
-        <v>41.4</v>
+        <v>3</v>
       </c>
       <c r="P257" t="n">
         <v>69.7</v>
       </c>
       <c r="Q257" t="n">
-        <v>-40.6</v>
+        <v>-95.7</v>
       </c>
       <c r="R257" t="n">
         <v>15550</v>
@@ -19560,31 +19542,31 @@
         <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>1614.8</v>
+        <v>1628.2</v>
       </c>
       <c r="J273" t="n">
         <v>1615.7</v>
       </c>
       <c r="K273" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="L273" t="n">
-        <v>2195.4</v>
+        <v>2207.5</v>
       </c>
       <c r="M273" t="n">
         <v>2185.1</v>
       </c>
       <c r="N273" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O273" t="n">
-        <v>2782.4</v>
+        <v>2796</v>
       </c>
       <c r="P273" t="n">
         <v>2752.9</v>
       </c>
       <c r="Q273" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="R273" t="n">
         <v>228500</v>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -455,7 +455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-15 · 전주 2026-08-07</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-16 · 전주 2026-08-07</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -455,7 +455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-22 · 전주 2026-08-16</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-24 · 전주 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -615,13 +615,13 @@
         <v>-0.2</v>
       </c>
       <c r="R3" t="n">
-        <v>15240</v>
+        <v>15470</v>
       </c>
       <c r="S3" t="n">
         <v>15850</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.8</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="4">
@@ -678,13 +678,13 @@
         <v>-2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>82300</v>
+        <v>84500</v>
       </c>
       <c r="S4" t="n">
         <v>83700</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -813,13 +813,13 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1078000</v>
+        <v>1084000</v>
       </c>
       <c r="S6" t="n">
         <v>1276000</v>
       </c>
       <c r="T6" t="n">
-        <v>-15.5</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="7">
@@ -885,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>46700</v>
+        <v>46600</v>
       </c>
       <c r="S7" t="n">
         <v>51900</v>
       </c>
       <c r="T7" t="n">
-        <v>-10</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="8">
@@ -948,13 +948,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>23250</v>
+        <v>23775</v>
       </c>
       <c r="S8" t="n">
         <v>26250</v>
       </c>
       <c r="T8" t="n">
-        <v>-11.4</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="9">
@@ -1020,13 +1020,13 @@
         <v>0.7</v>
       </c>
       <c r="R9" t="n">
-        <v>130900</v>
+        <v>130800</v>
       </c>
       <c r="S9" t="n">
         <v>141700</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.6</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="10">
@@ -1092,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>90000</v>
+        <v>92100</v>
       </c>
       <c r="S10" t="n">
         <v>93000</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1730000</v>
+        <v>1679000</v>
       </c>
       <c r="S11" t="n">
         <v>1645000</v>
       </c>
       <c r="T11" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -1227,13 +1227,13 @@
         <v>-0.3</v>
       </c>
       <c r="R12" t="n">
-        <v>105600</v>
+        <v>104500</v>
       </c>
       <c r="S12" t="n">
         <v>115800</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1299,13 +1299,13 @@
         <v>-1.2</v>
       </c>
       <c r="R13" t="n">
-        <v>661000</v>
+        <v>633000</v>
       </c>
       <c r="S13" t="n">
         <v>615000</v>
       </c>
       <c r="T13" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1434,13 +1434,13 @@
         <v>5.9</v>
       </c>
       <c r="R15" t="n">
-        <v>89700</v>
+        <v>87000</v>
       </c>
       <c r="S15" t="n">
         <v>102800</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.7</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="16">
@@ -1506,13 +1506,13 @@
         <v>1.1</v>
       </c>
       <c r="R16" t="n">
-        <v>121300</v>
+        <v>127200</v>
       </c>
       <c r="S16" t="n">
         <v>138100</v>
       </c>
       <c r="T16" t="n">
-        <v>-12.2</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="17">
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>39350</v>
+        <v>41900</v>
       </c>
       <c r="S17" t="n">
         <v>45000</v>
       </c>
       <c r="T17" t="n">
-        <v>-12.6</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="18">
@@ -1650,13 +1650,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>26650</v>
+        <v>26600</v>
       </c>
       <c r="S18" t="n">
         <v>29950</v>
       </c>
       <c r="T18" t="n">
-        <v>-11</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="19">
@@ -1713,13 +1713,13 @@
         <v>17.9</v>
       </c>
       <c r="R19" t="n">
-        <v>49750</v>
+        <v>50200</v>
       </c>
       <c r="S19" t="n">
         <v>45350</v>
       </c>
       <c r="T19" t="n">
-        <v>9.699999999999999</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="20">
@@ -1785,13 +1785,13 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>17320</v>
+        <v>17990</v>
       </c>
       <c r="S20" t="n">
         <v>18370</v>
       </c>
       <c r="T20" t="n">
-        <v>-5.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="21">
@@ -1848,13 +1848,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6400</v>
+        <v>6550</v>
       </c>
       <c r="S21" t="n">
         <v>6730</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="22">
@@ -1920,13 +1920,13 @@
         <v>-0.1</v>
       </c>
       <c r="R22" t="n">
-        <v>484000</v>
+        <v>450500</v>
       </c>
       <c r="S22" t="n">
         <v>465500</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="23">
@@ -1983,13 +1983,13 @@
         <v>17.4</v>
       </c>
       <c r="R23" t="n">
-        <v>14750</v>
+        <v>14880</v>
       </c>
       <c r="S23" t="n">
         <v>13400</v>
       </c>
       <c r="T23" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -2055,13 +2055,13 @@
         <v>-21.5</v>
       </c>
       <c r="R24" t="n">
-        <v>100300</v>
+        <v>100500</v>
       </c>
       <c r="S24" t="n">
         <v>108000</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.1</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="25">
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>9700</v>
+        <v>9690</v>
       </c>
       <c r="S25" t="n">
         <v>10240</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.3</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="26">
@@ -2190,13 +2190,13 @@
         <v>-30</v>
       </c>
       <c r="R26" t="n">
-        <v>7710</v>
+        <v>7810</v>
       </c>
       <c r="S26" t="n">
         <v>7960</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="27">
@@ -2253,13 +2253,13 @@
         <v>1.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1366000</v>
+        <v>1402000</v>
       </c>
       <c r="S27" t="n">
         <v>1270000</v>
       </c>
       <c r="T27" t="n">
-        <v>7.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="28">
@@ -2325,13 +2325,13 @@
         <v>-0.3</v>
       </c>
       <c r="R28" t="n">
-        <v>25800</v>
+        <v>26050</v>
       </c>
       <c r="S28" t="n">
         <v>26300</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
@@ -2397,13 +2397,13 @@
         <v>0.9</v>
       </c>
       <c r="R29" t="n">
-        <v>107700</v>
+        <v>112300</v>
       </c>
       <c r="S29" t="n">
         <v>120000</v>
       </c>
       <c r="T29" t="n">
-        <v>-10.2</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="30">
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>154900</v>
+        <v>170700</v>
       </c>
       <c r="S30" t="n">
         <v>170500</v>
       </c>
       <c r="T30" t="n">
-        <v>-9.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="31">
@@ -2523,13 +2523,13 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>44150</v>
+        <v>45500</v>
       </c>
       <c r="S31" t="n">
         <v>47100</v>
       </c>
       <c r="T31" t="n">
-        <v>-6.3</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="32">
@@ -2595,13 +2595,13 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>27000</v>
+        <v>27800</v>
       </c>
       <c r="S32" t="n">
         <v>29900</v>
       </c>
       <c r="T32" t="n">
-        <v>-9.699999999999999</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="33">
@@ -2658,13 +2658,13 @@
         <v>-0.7</v>
       </c>
       <c r="R33" t="n">
-        <v>400500</v>
+        <v>397500</v>
       </c>
       <c r="S33" t="n">
         <v>427000</v>
       </c>
       <c r="T33" t="n">
-        <v>-6.2</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="34">
@@ -2721,13 +2721,13 @@
         <v>5.8</v>
       </c>
       <c r="R34" t="n">
-        <v>432500</v>
+        <v>454500</v>
       </c>
       <c r="S34" t="n">
         <v>437500</v>
       </c>
       <c r="T34" t="n">
-        <v>-1.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="35">
@@ -2793,13 +2793,13 @@
         <v>0.8</v>
       </c>
       <c r="R35" t="n">
-        <v>22800</v>
+        <v>23050</v>
       </c>
       <c r="S35" t="n">
         <v>24300</v>
       </c>
       <c r="T35" t="n">
-        <v>-6.2</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="36">
@@ -2856,13 +2856,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>96600</v>
+        <v>97700</v>
       </c>
       <c r="S36" t="n">
         <v>101700</v>
       </c>
       <c r="T36" t="n">
-        <v>-5</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="37">
@@ -2919,13 +2919,13 @@
         <v>0.1</v>
       </c>
       <c r="R37" t="n">
-        <v>415000</v>
+        <v>410500</v>
       </c>
       <c r="S37" t="n">
         <v>453000</v>
       </c>
       <c r="T37" t="n">
-        <v>-8.4</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="38">
@@ -2982,13 +2982,13 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>310000</v>
+        <v>326500</v>
       </c>
       <c r="S38" t="n">
         <v>334000</v>
       </c>
       <c r="T38" t="n">
-        <v>-7.2</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="39">
@@ -3054,13 +3054,13 @@
         <v>-0.8</v>
       </c>
       <c r="R39" t="n">
-        <v>177800</v>
+        <v>180400</v>
       </c>
       <c r="S39" t="n">
         <v>176800</v>
       </c>
       <c r="T39" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3126,13 +3126,13 @@
         <v>0.8</v>
       </c>
       <c r="R40" t="n">
-        <v>52400</v>
+        <v>53500</v>
       </c>
       <c r="S40" t="n">
         <v>61600</v>
       </c>
       <c r="T40" t="n">
-        <v>-14.9</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="41">
@@ -3189,13 +3189,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>281500</v>
+        <v>256750</v>
       </c>
       <c r="S41" t="n">
         <v>274500</v>
       </c>
       <c r="T41" t="n">
-        <v>2.6</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="42">
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>26100</v>
+        <v>25900</v>
       </c>
       <c r="S42" t="n">
         <v>28750</v>
       </c>
       <c r="T42" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="43">
@@ -3324,13 +3324,13 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>37750</v>
+        <v>38000</v>
       </c>
       <c r="S43" t="n">
         <v>37550</v>
       </c>
       <c r="T43" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="44">
@@ -3387,13 +3387,13 @@
         <v>11.7</v>
       </c>
       <c r="R44" t="n">
-        <v>293500</v>
+        <v>286000</v>
       </c>
       <c r="S44" t="n">
         <v>323500</v>
       </c>
       <c r="T44" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="45">
@@ -3459,13 +3459,13 @@
         <v>-0.6</v>
       </c>
       <c r="R45" t="n">
-        <v>122100</v>
+        <v>130600</v>
       </c>
       <c r="S45" t="n">
         <v>129200</v>
       </c>
       <c r="T45" t="n">
-        <v>-5.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="46">
@@ -3522,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>33250</v>
+        <v>34150</v>
       </c>
       <c r="S46" t="n">
         <v>35350</v>
       </c>
       <c r="T46" t="n">
-        <v>-5.9</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="47">
@@ -3594,13 +3594,13 @@
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>478000</v>
+        <v>514000</v>
       </c>
       <c r="S47" t="n">
         <v>516000</v>
       </c>
       <c r="T47" t="n">
-        <v>-7.4</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="48">
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>80300</v>
+        <v>82700</v>
       </c>
       <c r="S48" t="n">
         <v>91400</v>
       </c>
       <c r="T48" t="n">
-        <v>-12.1</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="49">
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>34500</v>
+        <v>34550</v>
       </c>
       <c r="S49" t="n">
         <v>37650</v>
       </c>
       <c r="T49" t="n">
-        <v>-8.4</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3792,13 +3792,13 @@
         <v>-0.6</v>
       </c>
       <c r="R50" t="n">
-        <v>25800</v>
+        <v>26800</v>
       </c>
       <c r="S50" t="n">
         <v>27700</v>
       </c>
       <c r="T50" t="n">
-        <v>-6.9</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="51">
@@ -3855,13 +3855,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="R51" t="n">
-        <v>44200</v>
+        <v>47950</v>
       </c>
       <c r="S51" t="n">
         <v>58900</v>
       </c>
       <c r="T51" t="n">
-        <v>-25</v>
+        <v>-18.6</v>
       </c>
     </row>
     <row r="52">
@@ -3927,13 +3927,13 @@
         <v>5.8</v>
       </c>
       <c r="R52" t="n">
-        <v>99300</v>
+        <v>101300</v>
       </c>
       <c r="S52" t="n">
         <v>95600</v>
       </c>
       <c r="T52" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -3990,13 +3990,13 @@
         <v>-0.3</v>
       </c>
       <c r="R53" t="n">
-        <v>54600</v>
+        <v>55200</v>
       </c>
       <c r="S53" t="n">
         <v>63100</v>
       </c>
       <c r="T53" t="n">
-        <v>-13.5</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="54">
@@ -4053,13 +4053,13 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>14860</v>
+        <v>15120</v>
       </c>
       <c r="S54" t="n">
         <v>15090</v>
       </c>
       <c r="T54" t="n">
-        <v>-1.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="55">
@@ -4116,13 +4116,13 @@
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>42300</v>
+        <v>42100</v>
       </c>
       <c r="S55" t="n">
         <v>45400</v>
       </c>
       <c r="T55" t="n">
-        <v>-6.8</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="56">
@@ -4179,13 +4179,13 @@
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1316000</v>
+        <v>1318000</v>
       </c>
       <c r="S56" t="n">
         <v>1558000</v>
       </c>
       <c r="T56" t="n">
-        <v>-15.5</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="57">
@@ -4242,13 +4242,13 @@
         <v>-3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>38050</v>
+        <v>39050</v>
       </c>
       <c r="S57" t="n">
         <v>40500</v>
       </c>
       <c r="T57" t="n">
-        <v>-6</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="58">
@@ -4287,13 +4287,13 @@
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>56500</v>
+        <v>60200</v>
       </c>
       <c r="S58" t="n">
         <v>59700</v>
       </c>
       <c r="T58" t="n">
-        <v>-5.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="59">
@@ -4350,13 +4350,13 @@
         <v>1.7</v>
       </c>
       <c r="R59" t="n">
-        <v>348500</v>
+        <v>351500</v>
       </c>
       <c r="S59" t="n">
         <v>386000</v>
       </c>
       <c r="T59" t="n">
-        <v>-9.699999999999999</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="60">
@@ -4413,13 +4413,13 @@
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>32050</v>
+        <v>31800</v>
       </c>
       <c r="S60" t="n">
         <v>35400</v>
       </c>
       <c r="T60" t="n">
-        <v>-9.5</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="61">
@@ -4476,13 +4476,13 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>265000</v>
+        <v>268000</v>
       </c>
       <c r="S61" t="n">
         <v>279000</v>
       </c>
       <c r="T61" t="n">
-        <v>-5</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="62">
@@ -4548,13 +4548,13 @@
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>187000</v>
+        <v>191300</v>
       </c>
       <c r="S62" t="n">
         <v>206500</v>
       </c>
       <c r="T62" t="n">
-        <v>-9.4</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="63">
@@ -4611,13 +4611,13 @@
         <v>5.3</v>
       </c>
       <c r="R63" t="n">
-        <v>1237000</v>
+        <v>1347000</v>
       </c>
       <c r="S63" t="n">
         <v>1196000</v>
       </c>
       <c r="T63" t="n">
-        <v>3.4</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="64">
@@ -4683,13 +4683,13 @@
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>20200</v>
+        <v>20050</v>
       </c>
       <c r="S64" t="n">
         <v>22300</v>
       </c>
       <c r="T64" t="n">
-        <v>-9.4</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="65">
@@ -4746,13 +4746,13 @@
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>15060</v>
+        <v>16010</v>
       </c>
       <c r="S65" t="n">
         <v>16730</v>
       </c>
       <c r="T65" t="n">
-        <v>-10</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="66">
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>141100</v>
+        <v>141200</v>
       </c>
       <c r="S66" t="n">
         <v>147600</v>
       </c>
       <c r="T66" t="n">
-        <v>-4.4</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="67">
@@ -4872,13 +4872,13 @@
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>550000</v>
+        <v>571000</v>
       </c>
       <c r="S67" t="n">
         <v>654000</v>
       </c>
       <c r="T67" t="n">
-        <v>-15.9</v>
+        <v>-12.7</v>
       </c>
     </row>
     <row r="68">
@@ -4944,13 +4944,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>54300</v>
+        <v>55000</v>
       </c>
       <c r="S68" t="n">
         <v>57200</v>
       </c>
       <c r="T68" t="n">
-        <v>-5.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="69">
@@ -5007,13 +5007,13 @@
         <v>-1.5</v>
       </c>
       <c r="R69" t="n">
-        <v>21600</v>
+        <v>22800</v>
       </c>
       <c r="S69" t="n">
         <v>21250</v>
       </c>
       <c r="T69" t="n">
-        <v>1.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="70">
@@ -5079,13 +5079,13 @@
         <v>-0.1</v>
       </c>
       <c r="R70" t="n">
-        <v>59400</v>
+        <v>60200</v>
       </c>
       <c r="S70" t="n">
         <v>67800</v>
       </c>
       <c r="T70" t="n">
-        <v>-12.4</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="71">
@@ -5142,13 +5142,13 @@
         <v>-1.5</v>
       </c>
       <c r="R71" t="n">
-        <v>117200</v>
+        <v>119500</v>
       </c>
       <c r="S71" t="n">
         <v>130600</v>
       </c>
       <c r="T71" t="n">
-        <v>-10.3</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="72">
@@ -5205,13 +5205,13 @@
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>83400</v>
+        <v>84500</v>
       </c>
       <c r="S72" t="n">
         <v>89800</v>
       </c>
       <c r="T72" t="n">
-        <v>-7.1</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="73">
@@ -5268,13 +5268,13 @@
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>496000</v>
+        <v>495500</v>
       </c>
       <c r="S73" t="n">
         <v>547000</v>
       </c>
       <c r="T73" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="74">
@@ -5331,13 +5331,13 @@
         <v>0.3</v>
       </c>
       <c r="R74" t="n">
-        <v>1085000</v>
+        <v>1107000</v>
       </c>
       <c r="S74" t="n">
         <v>1160000</v>
       </c>
       <c r="T74" t="n">
-        <v>-6.5</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="75">
@@ -5403,13 +5403,13 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>76800</v>
+        <v>78900</v>
       </c>
       <c r="S75" t="n">
         <v>77700</v>
       </c>
       <c r="T75" t="n">
-        <v>-1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="76">
@@ -5466,13 +5466,13 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>22200</v>
+        <v>22000</v>
       </c>
       <c r="S76" t="n">
         <v>21600</v>
       </c>
       <c r="T76" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="77">
@@ -5538,13 +5538,13 @@
         <v>1.2</v>
       </c>
       <c r="R77" t="n">
-        <v>22950</v>
+        <v>24100</v>
       </c>
       <c r="S77" t="n">
         <v>26050</v>
       </c>
       <c r="T77" t="n">
-        <v>-11.9</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="78">
@@ -5601,13 +5601,13 @@
         <v>-3.3</v>
       </c>
       <c r="R78" t="n">
-        <v>201000</v>
+        <v>203000</v>
       </c>
       <c r="S78" t="n">
         <v>218500</v>
       </c>
       <c r="T78" t="n">
-        <v>-8</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="79">
@@ -5736,13 +5736,13 @@
         <v>-3.7</v>
       </c>
       <c r="R80" t="n">
-        <v>31750</v>
+        <v>31300</v>
       </c>
       <c r="S80" t="n">
         <v>33250</v>
       </c>
       <c r="T80" t="n">
-        <v>-4.5</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="81">
@@ -5808,13 +5808,13 @@
         <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>92000</v>
+        <v>86200</v>
       </c>
       <c r="S81" t="n">
         <v>93000</v>
       </c>
       <c r="T81" t="n">
-        <v>-1.1</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="82">
@@ -5871,13 +5871,13 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>102200</v>
+        <v>103300</v>
       </c>
       <c r="S82" t="n">
         <v>100500</v>
       </c>
       <c r="T82" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="83">
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>72200</v>
+        <v>73900</v>
       </c>
       <c r="S83" t="n">
         <v>72500</v>
       </c>
       <c r="T83" t="n">
-        <v>-0.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="84">
@@ -6006,13 +6006,13 @@
         <v>-0.2</v>
       </c>
       <c r="R84" t="n">
-        <v>22550</v>
+        <v>22700</v>
       </c>
       <c r="S84" t="n">
         <v>25150</v>
       </c>
       <c r="T84" t="n">
-        <v>-10.3</v>
+        <v>-9.699999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -6069,13 +6069,13 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>228000</v>
+        <v>226000</v>
       </c>
       <c r="S85" t="n">
         <v>243500</v>
       </c>
       <c r="T85" t="n">
-        <v>-6.4</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="86">
@@ -6132,13 +6132,13 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3400</v>
+        <v>3515</v>
       </c>
       <c r="S86" t="n">
         <v>3820</v>
       </c>
       <c r="T86" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="87">
@@ -6195,13 +6195,13 @@
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>95900</v>
+        <v>97000</v>
       </c>
       <c r="S87" t="n">
         <v>98200</v>
       </c>
       <c r="T87" t="n">
-        <v>-2.3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="88">
@@ -6267,13 +6267,13 @@
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>20150</v>
+        <v>21250</v>
       </c>
       <c r="S88" t="n">
         <v>23200</v>
       </c>
       <c r="T88" t="n">
-        <v>-13.1</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="89">
@@ -6330,13 +6330,13 @@
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>96700</v>
+        <v>95400</v>
       </c>
       <c r="S89" t="n">
         <v>102900</v>
       </c>
       <c r="T89" t="n">
-        <v>-6</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="90">
@@ -6402,13 +6402,13 @@
         <v>0.3</v>
       </c>
       <c r="R90" t="n">
-        <v>20000</v>
+        <v>20200</v>
       </c>
       <c r="S90" t="n">
         <v>20400</v>
       </c>
       <c r="T90" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="91">
@@ -6474,13 +6474,13 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>45150</v>
+        <v>44650</v>
       </c>
       <c r="S91" t="n">
         <v>49800</v>
       </c>
       <c r="T91" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="92">
@@ -6537,13 +6537,13 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>395500</v>
+        <v>361500</v>
       </c>
       <c r="S92" t="n">
         <v>369000</v>
       </c>
       <c r="T92" t="n">
-        <v>7.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="93">
@@ -6600,13 +6600,13 @@
         <v>-0.4</v>
       </c>
       <c r="R93" t="n">
-        <v>5850</v>
+        <v>6380</v>
       </c>
       <c r="S93" t="n">
         <v>5790</v>
       </c>
       <c r="T93" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="94">
@@ -6672,13 +6672,13 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>46150</v>
+        <v>46250</v>
       </c>
       <c r="S94" t="n">
         <v>48550</v>
       </c>
       <c r="T94" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="95">
@@ -6735,13 +6735,13 @@
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>18900</v>
+        <v>19090</v>
       </c>
       <c r="S95" t="n">
         <v>18980</v>
       </c>
       <c r="T95" t="n">
-        <v>-0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="96">
@@ -6807,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>52400</v>
+        <v>52600</v>
       </c>
       <c r="S96" t="n">
         <v>53400</v>
       </c>
       <c r="T96" t="n">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="97">
@@ -6879,13 +6879,13 @@
         <v>0.2</v>
       </c>
       <c r="R97" t="n">
-        <v>107500</v>
+        <v>110800</v>
       </c>
       <c r="S97" t="n">
         <v>111200</v>
       </c>
       <c r="T97" t="n">
-        <v>-3.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="98">
@@ -7014,13 +7014,13 @@
         <v>0.5</v>
       </c>
       <c r="R99" t="n">
-        <v>328500</v>
+        <v>287000</v>
       </c>
       <c r="S99" t="n">
         <v>301000</v>
       </c>
       <c r="T99" t="n">
-        <v>9.1</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="100">
@@ -7077,13 +7077,13 @@
         <v>7.3</v>
       </c>
       <c r="R100" t="n">
-        <v>16700</v>
+        <v>17040</v>
       </c>
       <c r="S100" t="n">
         <v>17350</v>
       </c>
       <c r="T100" t="n">
-        <v>-3.7</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="101">
@@ -7149,13 +7149,13 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>172300</v>
+        <v>172600</v>
       </c>
       <c r="S101" t="n">
         <v>176000</v>
       </c>
       <c r="T101" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="102">
@@ -7221,13 +7221,13 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>73300</v>
+        <v>72300</v>
       </c>
       <c r="S102" t="n">
         <v>82600</v>
       </c>
       <c r="T102" t="n">
-        <v>-11.3</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="103">
@@ -7284,13 +7284,13 @@
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>9500</v>
+        <v>9580</v>
       </c>
       <c r="S103" t="n">
         <v>10270</v>
       </c>
       <c r="T103" t="n">
-        <v>-7.5</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="104">
@@ -7347,13 +7347,13 @@
         <v>0.2</v>
       </c>
       <c r="R104" t="n">
-        <v>9260</v>
+        <v>9430</v>
       </c>
       <c r="S104" t="n">
         <v>9890</v>
       </c>
       <c r="T104" t="n">
-        <v>-6.4</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="105">
@@ -7419,13 +7419,13 @@
         <v>-1</v>
       </c>
       <c r="R105" t="n">
-        <v>586000</v>
+        <v>544000</v>
       </c>
       <c r="S105" t="n">
         <v>585000</v>
       </c>
       <c r="T105" t="n">
-        <v>0.2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="106">
@@ -7491,13 +7491,13 @@
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>14310</v>
+        <v>14460</v>
       </c>
       <c r="S106" t="n">
         <v>14590</v>
       </c>
       <c r="T106" t="n">
-        <v>-1.9</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="107">
@@ -7554,13 +7554,13 @@
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>222000</v>
+        <v>223500</v>
       </c>
       <c r="S107" t="n">
         <v>228000</v>
       </c>
       <c r="T107" t="n">
-        <v>-2.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="108">
@@ -7626,13 +7626,13 @@
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>35800</v>
+        <v>35750</v>
       </c>
       <c r="S108" t="n">
         <v>40000</v>
       </c>
       <c r="T108" t="n">
-        <v>-10.5</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="109">
@@ -7698,13 +7698,13 @@
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>31800</v>
+        <v>32850</v>
       </c>
       <c r="S109" t="n">
         <v>34400</v>
       </c>
       <c r="T109" t="n">
-        <v>-7.6</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="110">
@@ -7770,13 +7770,13 @@
         <v>-1.4</v>
       </c>
       <c r="R110" t="n">
-        <v>38800</v>
+        <v>39550</v>
       </c>
       <c r="S110" t="n">
         <v>41050</v>
       </c>
       <c r="T110" t="n">
-        <v>-5.5</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="111">
@@ -7842,13 +7842,13 @@
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>9020</v>
+        <v>8830</v>
       </c>
       <c r="S111" t="n">
         <v>8760</v>
       </c>
       <c r="T111" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="112">
@@ -7905,13 +7905,13 @@
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>35650</v>
+        <v>36350</v>
       </c>
       <c r="S112" t="n">
         <v>36600</v>
       </c>
       <c r="T112" t="n">
-        <v>-2.6</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="113">
@@ -7977,13 +7977,13 @@
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>224500</v>
+        <v>225500</v>
       </c>
       <c r="S113" t="n">
         <v>247500</v>
       </c>
       <c r="T113" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="114">
@@ -8049,13 +8049,13 @@
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>168600</v>
+        <v>167100</v>
       </c>
       <c r="S114" t="n">
         <v>177800</v>
       </c>
       <c r="T114" t="n">
-        <v>-5.2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="115">
@@ -8121,13 +8121,13 @@
         <v>10.6</v>
       </c>
       <c r="R115" t="n">
-        <v>404500</v>
+        <v>388500</v>
       </c>
       <c r="S115" t="n">
         <v>404000</v>
       </c>
       <c r="T115" t="n">
-        <v>0.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="116">
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>31200</v>
+        <v>32000</v>
       </c>
       <c r="S116" t="n">
         <v>32700</v>
       </c>
       <c r="T116" t="n">
-        <v>-4.6</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="117">
@@ -8229,13 +8229,13 @@
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>19900</v>
+        <v>19290</v>
       </c>
       <c r="S117" t="n">
         <v>23700</v>
       </c>
       <c r="T117" t="n">
-        <v>-16</v>
+        <v>-18.6</v>
       </c>
     </row>
     <row r="118">
@@ -8301,13 +8301,13 @@
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>268000</v>
+        <v>266000</v>
       </c>
       <c r="S118" t="n">
         <v>300500</v>
       </c>
       <c r="T118" t="n">
-        <v>-10.8</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="119">
@@ -8352,13 +8352,13 @@
         <v>350</v>
       </c>
       <c r="R119" t="n">
-        <v>11620</v>
+        <v>11200</v>
       </c>
       <c r="S119" t="n">
         <v>12290</v>
       </c>
       <c r="T119" t="n">
-        <v>-5.5</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="120">
@@ -8424,13 +8424,13 @@
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>71300</v>
+        <v>72000</v>
       </c>
       <c r="S120" t="n">
         <v>73400</v>
       </c>
       <c r="T120" t="n">
-        <v>-2.9</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="121">
@@ -8487,13 +8487,13 @@
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>84200</v>
+        <v>83000</v>
       </c>
       <c r="S121" t="n">
         <v>95800</v>
       </c>
       <c r="T121" t="n">
-        <v>-12.1</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="122">
@@ -8550,13 +8550,13 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>213500</v>
+        <v>209500</v>
       </c>
       <c r="S122" t="n">
         <v>229000</v>
       </c>
       <c r="T122" t="n">
-        <v>-6.8</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="123">
@@ -8613,13 +8613,13 @@
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>15930</v>
+        <v>15640</v>
       </c>
       <c r="S123" t="n">
         <v>18010</v>
       </c>
       <c r="T123" t="n">
-        <v>-11.5</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="124">
@@ -8676,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>50600</v>
+        <v>53400</v>
       </c>
       <c r="S124" t="n">
         <v>53300</v>
       </c>
       <c r="T124" t="n">
-        <v>-5.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="125">
@@ -8739,13 +8739,13 @@
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>130000</v>
+        <v>129600</v>
       </c>
       <c r="S125" t="n">
         <v>146400</v>
       </c>
       <c r="T125" t="n">
-        <v>-11.2</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="126">
@@ -8811,13 +8811,13 @@
         <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>23350</v>
+        <v>24000</v>
       </c>
       <c r="S126" t="n">
         <v>24850</v>
       </c>
       <c r="T126" t="n">
-        <v>-6</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="127">
@@ -8874,13 +8874,13 @@
         <v>-0.4</v>
       </c>
       <c r="R127" t="n">
-        <v>43800</v>
+        <v>43900</v>
       </c>
       <c r="S127" t="n">
         <v>46350</v>
       </c>
       <c r="T127" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="128">
@@ -8946,13 +8946,13 @@
         <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>313000</v>
+        <v>317000</v>
       </c>
       <c r="S128" t="n">
         <v>307500</v>
       </c>
       <c r="T128" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="129">
@@ -9018,13 +9018,13 @@
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>252500</v>
+        <v>270000</v>
       </c>
       <c r="S129" t="n">
         <v>280500</v>
       </c>
       <c r="T129" t="n">
-        <v>-10</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="130">
@@ -9081,13 +9081,13 @@
         <v>0.8</v>
       </c>
       <c r="R130" t="n">
-        <v>91500</v>
+        <v>89700</v>
       </c>
       <c r="S130" t="n">
         <v>101000</v>
       </c>
       <c r="T130" t="n">
-        <v>-9.4</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="131">
@@ -9153,13 +9153,13 @@
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>104100</v>
+        <v>103600</v>
       </c>
       <c r="S131" t="n">
         <v>107400</v>
       </c>
       <c r="T131" t="n">
-        <v>-3.1</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="132">
@@ -9216,13 +9216,13 @@
         <v>-4.3</v>
       </c>
       <c r="R132" t="n">
-        <v>65700</v>
+        <v>64700</v>
       </c>
       <c r="S132" t="n">
         <v>70800</v>
       </c>
       <c r="T132" t="n">
-        <v>-7.2</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="133">
@@ -9288,13 +9288,13 @@
         <v>16.6</v>
       </c>
       <c r="R133" t="n">
-        <v>95500</v>
+        <v>93700</v>
       </c>
       <c r="S133" t="n">
         <v>118600</v>
       </c>
       <c r="T133" t="n">
-        <v>-19.5</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="134">
@@ -9360,13 +9360,13 @@
         <v>25</v>
       </c>
       <c r="R134" t="n">
-        <v>38650</v>
+        <v>39500</v>
       </c>
       <c r="S134" t="n">
         <v>41100</v>
       </c>
       <c r="T134" t="n">
-        <v>-6</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="135">
@@ -9432,13 +9432,13 @@
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>164800</v>
+        <v>164900</v>
       </c>
       <c r="S135" t="n">
         <v>182500</v>
       </c>
       <c r="T135" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="136">
@@ -9495,13 +9495,13 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>130100</v>
+        <v>133400</v>
       </c>
       <c r="S136" t="n">
         <v>146900</v>
       </c>
       <c r="T136" t="n">
-        <v>-11.4</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -9558,13 +9558,13 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>71600</v>
+        <v>71900</v>
       </c>
       <c r="S137" t="n">
         <v>79900</v>
       </c>
       <c r="T137" t="n">
-        <v>-10.4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="138">
@@ -9630,13 +9630,13 @@
         <v>1.4</v>
       </c>
       <c r="R138" t="n">
-        <v>225500</v>
+        <v>227500</v>
       </c>
       <c r="S138" t="n">
         <v>244000</v>
       </c>
       <c r="T138" t="n">
-        <v>-7.6</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="139">
@@ -9693,13 +9693,13 @@
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>26100</v>
+        <v>26450</v>
       </c>
       <c r="S139" t="n">
         <v>28450</v>
       </c>
       <c r="T139" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="140">
@@ -9756,13 +9756,13 @@
         <v>3.1</v>
       </c>
       <c r="R140" t="n">
-        <v>194500</v>
+        <v>199100</v>
       </c>
       <c r="S140" t="n">
         <v>215000</v>
       </c>
       <c r="T140" t="n">
-        <v>-9.5</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="141">
@@ -9819,13 +9819,13 @@
         <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>104500</v>
+        <v>122500</v>
       </c>
       <c r="S141" t="n">
         <v>109700</v>
       </c>
       <c r="T141" t="n">
-        <v>-4.7</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="142">
@@ -9891,13 +9891,13 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>37650</v>
+        <v>38100</v>
       </c>
       <c r="S142" t="n">
         <v>41500</v>
       </c>
       <c r="T142" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="143">
@@ -9963,13 +9963,13 @@
         <v>5.3</v>
       </c>
       <c r="R143" t="n">
-        <v>35000</v>
+        <v>34350</v>
       </c>
       <c r="S143" t="n">
         <v>36600</v>
       </c>
       <c r="T143" t="n">
-        <v>-4.4</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="144">
@@ -10035,13 +10035,13 @@
         <v>-0.3</v>
       </c>
       <c r="R144" t="n">
-        <v>192300</v>
+        <v>193700</v>
       </c>
       <c r="S144" t="n">
         <v>201000</v>
       </c>
       <c r="T144" t="n">
-        <v>-4.3</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="145">
@@ -10098,13 +10098,13 @@
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>15730</v>
+        <v>15940</v>
       </c>
       <c r="S145" t="n">
         <v>16350</v>
       </c>
       <c r="T145" t="n">
-        <v>-3.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="146">
@@ -10161,13 +10161,13 @@
         <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>119500</v>
+        <v>124500</v>
       </c>
       <c r="S146" t="n">
         <v>124600</v>
       </c>
       <c r="T146" t="n">
-        <v>-4.1</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="147">
@@ -10224,13 +10224,13 @@
         <v>-0.6</v>
       </c>
       <c r="R147" t="n">
-        <v>93400</v>
+        <v>93500</v>
       </c>
       <c r="S147" t="n">
         <v>102200</v>
       </c>
       <c r="T147" t="n">
-        <v>-8.6</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="148">
@@ -10296,13 +10296,13 @@
         <v>0.5</v>
       </c>
       <c r="R148" t="n">
-        <v>184500</v>
+        <v>183100</v>
       </c>
       <c r="S148" t="n">
         <v>204000</v>
       </c>
       <c r="T148" t="n">
-        <v>-9.6</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="149">
@@ -10359,13 +10359,13 @@
         <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>72500</v>
+        <v>72600</v>
       </c>
       <c r="S149" t="n">
         <v>76400</v>
       </c>
       <c r="T149" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="150">
@@ -10422,13 +10422,13 @@
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>49700</v>
+        <v>50100</v>
       </c>
       <c r="S150" t="n">
         <v>58200</v>
       </c>
       <c r="T150" t="n">
-        <v>-14.6</v>
+        <v>-13.9</v>
       </c>
     </row>
     <row r="151">
@@ -10485,13 +10485,13 @@
         <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>7250</v>
+        <v>7160</v>
       </c>
       <c r="S151" t="n">
         <v>8140</v>
       </c>
       <c r="T151" t="n">
-        <v>-10.9</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="152">
@@ -10548,13 +10548,13 @@
         <v>-0.1</v>
       </c>
       <c r="R152" t="n">
-        <v>23450</v>
+        <v>23400</v>
       </c>
       <c r="S152" t="n">
         <v>28400</v>
       </c>
       <c r="T152" t="n">
-        <v>-17.4</v>
+        <v>-17.6</v>
       </c>
     </row>
     <row r="153">
@@ -10611,13 +10611,13 @@
         <v>1.5</v>
       </c>
       <c r="R153" t="n">
-        <v>116200</v>
+        <v>114600</v>
       </c>
       <c r="S153" t="n">
         <v>117000</v>
       </c>
       <c r="T153" t="n">
-        <v>-0.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="154">
@@ -10683,13 +10683,13 @@
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>695000</v>
+        <v>712000</v>
       </c>
       <c r="S154" t="n">
         <v>815000</v>
       </c>
       <c r="T154" t="n">
-        <v>-14.7</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="155">
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>8730</v>
+        <v>8970</v>
       </c>
       <c r="S155" t="n">
         <v>9200</v>
       </c>
       <c r="T155" t="n">
-        <v>-5.1</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="156">
@@ -10791,13 +10791,13 @@
         <v>1.8</v>
       </c>
       <c r="R156" t="n">
-        <v>41750</v>
+        <v>42150</v>
       </c>
       <c r="S156" t="n">
         <v>42500</v>
       </c>
       <c r="T156" t="n">
-        <v>-1.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="157">
@@ -10863,13 +10863,13 @@
         <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>44100</v>
+        <v>45050</v>
       </c>
       <c r="S157" t="n">
         <v>49050</v>
       </c>
       <c r="T157" t="n">
-        <v>-10.1</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -10935,13 +10935,13 @@
         <v>15.3</v>
       </c>
       <c r="R158" t="n">
-        <v>56500</v>
+        <v>55900</v>
       </c>
       <c r="S158" t="n">
         <v>61300</v>
       </c>
       <c r="T158" t="n">
-        <v>-7.8</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -11007,13 +11007,13 @@
         <v>33.3</v>
       </c>
       <c r="R159" t="n">
-        <v>128500</v>
+        <v>136300</v>
       </c>
       <c r="S159" t="n">
         <v>131100</v>
       </c>
       <c r="T159" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
@@ -11070,13 +11070,13 @@
         <v>-0.8</v>
       </c>
       <c r="R160" t="n">
-        <v>196700</v>
+        <v>198600</v>
       </c>
       <c r="S160" t="n">
         <v>211000</v>
       </c>
       <c r="T160" t="n">
-        <v>-6.8</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="161">
@@ -11142,13 +11142,13 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>128800</v>
+        <v>127900</v>
       </c>
       <c r="S161" t="n">
         <v>133000</v>
       </c>
       <c r="T161" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="162">
@@ -11205,13 +11205,13 @@
         <v>-0.6</v>
       </c>
       <c r="R162" t="n">
-        <v>5470</v>
+        <v>5230</v>
       </c>
       <c r="S162" t="n">
         <v>5630</v>
       </c>
       <c r="T162" t="n">
-        <v>-2.8</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="163">
@@ -11250,13 +11250,13 @@
         <v>0</v>
       </c>
       <c r="R163" t="n">
-        <v>48400</v>
+        <v>46650</v>
       </c>
       <c r="S163" t="n">
         <v>49250</v>
       </c>
       <c r="T163" t="n">
-        <v>-1.7</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="164">
@@ -11322,13 +11322,13 @@
         <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>45900</v>
+        <v>46100</v>
       </c>
       <c r="S164" t="n">
         <v>45000</v>
       </c>
       <c r="T164" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="165">
@@ -11385,13 +11385,13 @@
         <v>0.6</v>
       </c>
       <c r="R165" t="n">
-        <v>58100</v>
+        <v>58400</v>
       </c>
       <c r="S165" t="n">
         <v>68200</v>
       </c>
       <c r="T165" t="n">
-        <v>-14.8</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="166">
@@ -11457,13 +11457,13 @@
         <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>138000</v>
+        <v>139100</v>
       </c>
       <c r="S166" t="n">
         <v>135700</v>
       </c>
       <c r="T166" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="167">
@@ -11529,13 +11529,13 @@
         <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>154300</v>
+        <v>153400</v>
       </c>
       <c r="S167" t="n">
         <v>161300</v>
       </c>
       <c r="T167" t="n">
-        <v>-4.3</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="168">
@@ -11592,13 +11592,13 @@
         <v>-2.9</v>
       </c>
       <c r="R168" t="n">
-        <v>132900</v>
+        <v>133500</v>
       </c>
       <c r="S168" t="n">
         <v>147500</v>
       </c>
       <c r="T168" t="n">
-        <v>-9.9</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="169">
@@ -11664,13 +11664,13 @@
         <v>2.4</v>
       </c>
       <c r="R169" t="n">
-        <v>17790</v>
+        <v>18200</v>
       </c>
       <c r="S169" t="n">
         <v>19100</v>
       </c>
       <c r="T169" t="n">
-        <v>-6.9</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="170">
@@ -11736,13 +11736,13 @@
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>30500</v>
+        <v>32050</v>
       </c>
       <c r="S170" t="n">
         <v>32150</v>
       </c>
       <c r="T170" t="n">
-        <v>-5.1</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="171">
@@ -11808,13 +11808,13 @@
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>124800</v>
+        <v>129100</v>
       </c>
       <c r="S171" t="n">
         <v>128700</v>
       </c>
       <c r="T171" t="n">
-        <v>-3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="172">
@@ -11871,13 +11871,13 @@
         <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>184000</v>
+        <v>189800</v>
       </c>
       <c r="S172" t="n">
         <v>185400</v>
       </c>
       <c r="T172" t="n">
-        <v>-0.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="173">
@@ -11916,13 +11916,13 @@
         <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>28300</v>
+        <v>27200</v>
       </c>
       <c r="S173" t="n">
         <v>32350</v>
       </c>
       <c r="T173" t="n">
-        <v>-12.5</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="174">
@@ -11988,13 +11988,13 @@
         <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>17500</v>
+        <v>17900</v>
       </c>
       <c r="S174" t="n">
         <v>18460</v>
       </c>
       <c r="T174" t="n">
-        <v>-5.2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="175">
@@ -12051,13 +12051,13 @@
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>69400</v>
+        <v>70500</v>
       </c>
       <c r="S175" t="n">
         <v>81400</v>
       </c>
       <c r="T175" t="n">
-        <v>-14.7</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="176">
@@ -12123,13 +12123,13 @@
         <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>77800</v>
+        <v>81900</v>
       </c>
       <c r="S176" t="n">
         <v>82000</v>
       </c>
       <c r="T176" t="n">
-        <v>-5.1</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="177">
@@ -12195,13 +12195,13 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>164300</v>
+        <v>162500</v>
       </c>
       <c r="S177" t="n">
         <v>168500</v>
       </c>
       <c r="T177" t="n">
-        <v>-2.5</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="178">
@@ -12267,13 +12267,13 @@
         <v>-7</v>
       </c>
       <c r="R178" t="n">
-        <v>254000</v>
+        <v>245500</v>
       </c>
       <c r="S178" t="n">
         <v>280000</v>
       </c>
       <c r="T178" t="n">
-        <v>-9.300000000000001</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="179">
@@ -12339,13 +12339,13 @@
         <v>-0.1</v>
       </c>
       <c r="R179" t="n">
-        <v>74700</v>
+        <v>75400</v>
       </c>
       <c r="S179" t="n">
         <v>85900</v>
       </c>
       <c r="T179" t="n">
-        <v>-13</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="180">
@@ -12402,13 +12402,13 @@
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>46550</v>
+        <v>46900</v>
       </c>
       <c r="S180" t="n">
         <v>46850</v>
       </c>
       <c r="T180" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="181">
@@ -12465,13 +12465,13 @@
         <v>3.4</v>
       </c>
       <c r="R181" t="n">
-        <v>49650</v>
+        <v>50000</v>
       </c>
       <c r="S181" t="n">
         <v>55300</v>
       </c>
       <c r="T181" t="n">
-        <v>-10.2</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="182">
@@ -12537,13 +12537,13 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>39100</v>
+        <v>39350</v>
       </c>
       <c r="S182" t="n">
         <v>41050</v>
       </c>
       <c r="T182" t="n">
-        <v>-4.8</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="183">
@@ -12609,13 +12609,13 @@
         <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>415500</v>
+        <v>540000</v>
       </c>
       <c r="S183" t="n">
         <v>398500</v>
       </c>
       <c r="T183" t="n">
-        <v>4.3</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="184">
@@ -12681,13 +12681,13 @@
         <v>15.1</v>
       </c>
       <c r="R184" t="n">
-        <v>222000</v>
+        <v>245500</v>
       </c>
       <c r="S184" t="n">
         <v>260000</v>
       </c>
       <c r="T184" t="n">
-        <v>-14.6</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="185">
@@ -12753,13 +12753,13 @@
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>115400</v>
+        <v>114800</v>
       </c>
       <c r="S185" t="n">
         <v>116700</v>
       </c>
       <c r="T185" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="186">
@@ -12825,13 +12825,13 @@
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>14310</v>
+        <v>14300</v>
       </c>
       <c r="S186" t="n">
         <v>15130</v>
       </c>
       <c r="T186" t="n">
-        <v>-5.4</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="187">
@@ -12897,13 +12897,13 @@
         <v>0.5</v>
       </c>
       <c r="R187" t="n">
-        <v>17180</v>
+        <v>17100</v>
       </c>
       <c r="S187" t="n">
         <v>17470</v>
       </c>
       <c r="T187" t="n">
-        <v>-1.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="188">
@@ -12969,13 +12969,13 @@
         <v>-0.4</v>
       </c>
       <c r="R188" t="n">
-        <v>71900</v>
+        <v>72600</v>
       </c>
       <c r="S188" t="n">
         <v>78900</v>
       </c>
       <c r="T188" t="n">
-        <v>-8.9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="189">
@@ -13041,13 +13041,13 @@
         <v>-8</v>
       </c>
       <c r="R189" t="n">
-        <v>259500</v>
+        <v>265500</v>
       </c>
       <c r="S189" t="n">
         <v>279500</v>
       </c>
       <c r="T189" t="n">
-        <v>-7.2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="190">
@@ -13104,13 +13104,13 @@
         <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>100000</v>
+        <v>102500</v>
       </c>
       <c r="S190" t="n">
         <v>113900</v>
       </c>
       <c r="T190" t="n">
-        <v>-12.2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="191">
@@ -13176,13 +13176,13 @@
         <v>-0</v>
       </c>
       <c r="R191" t="n">
-        <v>245000</v>
+        <v>252000</v>
       </c>
       <c r="S191" t="n">
         <v>256000</v>
       </c>
       <c r="T191" t="n">
-        <v>-4.3</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="192">
@@ -13239,13 +13239,13 @@
         <v>-6.2</v>
       </c>
       <c r="R192" t="n">
-        <v>36350</v>
+        <v>36850</v>
       </c>
       <c r="S192" t="n">
         <v>40700</v>
       </c>
       <c r="T192" t="n">
-        <v>-10.7</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="193">
@@ -13284,13 +13284,13 @@
         <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>9680</v>
+        <v>9620</v>
       </c>
       <c r="S193" t="n">
         <v>10180</v>
       </c>
       <c r="T193" t="n">
-        <v>-4.9</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="194">
@@ -13347,13 +13347,13 @@
         <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>66000</v>
+        <v>66400</v>
       </c>
       <c r="S194" t="n">
         <v>71600</v>
       </c>
       <c r="T194" t="n">
-        <v>-7.8</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="195">
@@ -13419,13 +13419,13 @@
         <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>136700</v>
+        <v>143300</v>
       </c>
       <c r="S195" t="n">
         <v>136700</v>
       </c>
       <c r="T195" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="196">
@@ -13491,13 +13491,13 @@
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>37050</v>
+        <v>37750</v>
       </c>
       <c r="S196" t="n">
         <v>38500</v>
       </c>
       <c r="T196" t="n">
-        <v>-3.8</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="197">
@@ -13563,13 +13563,13 @@
         <v>0.1</v>
       </c>
       <c r="R197" t="n">
-        <v>26600</v>
+        <v>27250</v>
       </c>
       <c r="S197" t="n">
         <v>28000</v>
       </c>
       <c r="T197" t="n">
-        <v>-5</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="198">
@@ -13629,13 +13629,13 @@
         <v>4450</v>
       </c>
       <c r="R198" t="n">
-        <v>36250</v>
+        <v>38200</v>
       </c>
       <c r="S198" t="n">
         <v>36950</v>
       </c>
       <c r="T198" t="n">
-        <v>-1.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="199">
@@ -13701,13 +13701,13 @@
         <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>66900</v>
+        <v>68800</v>
       </c>
       <c r="S199" t="n">
         <v>68300</v>
       </c>
       <c r="T199" t="n">
-        <v>-2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="200">
@@ -13773,13 +13773,13 @@
         <v>3.9</v>
       </c>
       <c r="R200" t="n">
-        <v>62900</v>
+        <v>65600</v>
       </c>
       <c r="S200" t="n">
         <v>79000</v>
       </c>
       <c r="T200" t="n">
-        <v>-20.4</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="201">
@@ -13836,13 +13836,13 @@
         <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>59400</v>
+        <v>58700</v>
       </c>
       <c r="S201" t="n">
         <v>61600</v>
       </c>
       <c r="T201" t="n">
-        <v>-3.6</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="202">
@@ -13899,13 +13899,13 @@
         <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>271000</v>
+        <v>287000</v>
       </c>
       <c r="S202" t="n">
         <v>247500</v>
       </c>
       <c r="T202" t="n">
-        <v>9.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203">
@@ -13971,13 +13971,13 @@
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>41000</v>
+        <v>44150</v>
       </c>
       <c r="S203" t="n">
         <v>41650</v>
       </c>
       <c r="T203" t="n">
-        <v>-1.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204">
@@ -14043,13 +14043,13 @@
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>320000</v>
+        <v>320500</v>
       </c>
       <c r="S204" t="n">
         <v>314000</v>
       </c>
       <c r="T204" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="205">
@@ -14106,13 +14106,13 @@
         <v>0</v>
       </c>
       <c r="R205" t="n">
-        <v>51500</v>
+        <v>50900</v>
       </c>
       <c r="S205" t="n">
         <v>57100</v>
       </c>
       <c r="T205" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="206">
@@ -14169,13 +14169,13 @@
         <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>1551000</v>
+        <v>1567000</v>
       </c>
       <c r="S206" t="n">
         <v>1548000</v>
       </c>
       <c r="T206" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="207">
@@ -14241,13 +14241,13 @@
         <v>-1.2</v>
       </c>
       <c r="R207" t="n">
-        <v>32150</v>
+        <v>33300</v>
       </c>
       <c r="S207" t="n">
         <v>37500</v>
       </c>
       <c r="T207" t="n">
-        <v>-14.3</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="208">
@@ -14313,13 +14313,13 @@
         <v>0.7</v>
       </c>
       <c r="R208" t="n">
-        <v>400500</v>
+        <v>416000</v>
       </c>
       <c r="S208" t="n">
         <v>398000</v>
       </c>
       <c r="T208" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="209">
@@ -14376,13 +14376,13 @@
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>47150</v>
+        <v>46350</v>
       </c>
       <c r="S209" t="n">
         <v>53200</v>
       </c>
       <c r="T209" t="n">
-        <v>-11.4</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="210">
@@ -14439,13 +14439,13 @@
         <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>99700</v>
+        <v>105500</v>
       </c>
       <c r="S210" t="n">
         <v>108700</v>
       </c>
       <c r="T210" t="n">
-        <v>-8.300000000000001</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="211">
@@ -14511,13 +14511,13 @@
         <v>-0.6</v>
       </c>
       <c r="R211" t="n">
-        <v>99700</v>
+        <v>110700</v>
       </c>
       <c r="S211" t="n">
         <v>106400</v>
       </c>
       <c r="T211" t="n">
-        <v>-6.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -14583,13 +14583,13 @@
         <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>107900</v>
+        <v>106800</v>
       </c>
       <c r="S212" t="n">
         <v>116600</v>
       </c>
       <c r="T212" t="n">
-        <v>-7.5</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="213">
@@ -14646,13 +14646,13 @@
         <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>57900</v>
+        <v>60000</v>
       </c>
       <c r="S213" t="n">
         <v>66100</v>
       </c>
       <c r="T213" t="n">
-        <v>-12.4</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -14718,13 +14718,13 @@
         <v>1.8</v>
       </c>
       <c r="R214" t="n">
-        <v>137300</v>
+        <v>139900</v>
       </c>
       <c r="S214" t="n">
         <v>127200</v>
       </c>
       <c r="T214" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215">
@@ -14790,13 +14790,13 @@
         <v>-10.6</v>
       </c>
       <c r="R215" t="n">
-        <v>105600</v>
+        <v>117000</v>
       </c>
       <c r="S215" t="n">
         <v>116700</v>
       </c>
       <c r="T215" t="n">
-        <v>-9.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="216">
@@ -14862,13 +14862,13 @@
         <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>37050</v>
+        <v>37750</v>
       </c>
       <c r="S216" t="n">
         <v>39100</v>
       </c>
       <c r="T216" t="n">
-        <v>-5.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="217">
@@ -14934,13 +14934,13 @@
         <v>0.5</v>
       </c>
       <c r="R217" t="n">
-        <v>59800</v>
+        <v>63000</v>
       </c>
       <c r="S217" t="n">
         <v>53000</v>
       </c>
       <c r="T217" t="n">
-        <v>12.8</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="218">
@@ -15006,13 +15006,13 @@
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>21150</v>
+        <v>21450</v>
       </c>
       <c r="S218" t="n">
         <v>23600</v>
       </c>
       <c r="T218" t="n">
-        <v>-10.4</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="219">
@@ -15078,13 +15078,13 @@
         <v>0.4</v>
       </c>
       <c r="R219" t="n">
-        <v>47650</v>
+        <v>49450</v>
       </c>
       <c r="S219" t="n">
         <v>42850</v>
       </c>
       <c r="T219" t="n">
-        <v>11.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="220">
@@ -15150,13 +15150,13 @@
         <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>222000</v>
+        <v>223500</v>
       </c>
       <c r="S220" t="n">
         <v>238000</v>
       </c>
       <c r="T220" t="n">
-        <v>-6.7</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="221">
@@ -15222,13 +15222,13 @@
         <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>32200</v>
+        <v>32050</v>
       </c>
       <c r="S221" t="n">
         <v>31250</v>
       </c>
       <c r="T221" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="222">
@@ -15294,13 +15294,13 @@
         <v>2.2</v>
       </c>
       <c r="R222" t="n">
-        <v>213000</v>
+        <v>210500</v>
       </c>
       <c r="S222" t="n">
         <v>235500</v>
       </c>
       <c r="T222" t="n">
-        <v>-9.6</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="223">
@@ -15357,13 +15357,13 @@
         <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>718000</v>
+        <v>716000</v>
       </c>
       <c r="S223" t="n">
         <v>803000</v>
       </c>
       <c r="T223" t="n">
-        <v>-10.6</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="224">
@@ -15420,13 +15420,13 @@
         <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>115500</v>
+        <v>126900</v>
       </c>
       <c r="S224" t="n">
         <v>138600</v>
       </c>
       <c r="T224" t="n">
-        <v>-16.7</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="225">
@@ -15483,13 +15483,13 @@
         <v>-0.2</v>
       </c>
       <c r="R225" t="n">
-        <v>125400</v>
+        <v>128000</v>
       </c>
       <c r="S225" t="n">
         <v>134000</v>
       </c>
       <c r="T225" t="n">
-        <v>-6.4</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="226">
@@ -15546,13 +15546,13 @@
         <v>-1.6</v>
       </c>
       <c r="R226" t="n">
-        <v>70300</v>
+        <v>69300</v>
       </c>
       <c r="S226" t="n">
         <v>80300</v>
       </c>
       <c r="T226" t="n">
-        <v>-12.5</v>
+        <v>-13.7</v>
       </c>
     </row>
     <row r="227">
@@ -15609,13 +15609,13 @@
         <v>-1.9</v>
       </c>
       <c r="R227" t="n">
-        <v>5170</v>
+        <v>5720</v>
       </c>
       <c r="S227" t="n">
         <v>5320</v>
       </c>
       <c r="T227" t="n">
-        <v>-2.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="228">
@@ -15672,13 +15672,13 @@
         <v>254.1</v>
       </c>
       <c r="R228" t="n">
-        <v>454000</v>
+        <v>443000</v>
       </c>
       <c r="S228" t="n">
         <v>501000</v>
       </c>
       <c r="T228" t="n">
-        <v>-9.4</v>
+        <v>-11.6</v>
       </c>
     </row>
     <row r="229">
@@ -15744,13 +15744,13 @@
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>385000</v>
+        <v>407000</v>
       </c>
       <c r="S229" t="n">
         <v>390500</v>
       </c>
       <c r="T229" t="n">
-        <v>-1.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="230">
@@ -15807,13 +15807,13 @@
         <v>0.2</v>
       </c>
       <c r="R230" t="n">
-        <v>128300</v>
+        <v>130700</v>
       </c>
       <c r="S230" t="n">
         <v>129300</v>
       </c>
       <c r="T230" t="n">
-        <v>-0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="231">
@@ -15870,13 +15870,13 @@
         <v>-0.2</v>
       </c>
       <c r="R231" t="n">
-        <v>141400</v>
+        <v>145600</v>
       </c>
       <c r="S231" t="n">
         <v>145200</v>
       </c>
       <c r="T231" t="n">
-        <v>-2.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="232">
@@ -15933,13 +15933,13 @@
         <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>49600</v>
+        <v>50000</v>
       </c>
       <c r="S232" t="n">
         <v>50000</v>
       </c>
       <c r="T232" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -16005,13 +16005,13 @@
         <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>21600</v>
+        <v>22000</v>
       </c>
       <c r="S233" t="n">
         <v>22100</v>
       </c>
       <c r="T233" t="n">
-        <v>-2.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="234">
@@ -16068,13 +16068,13 @@
         <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>312000</v>
+        <v>314000</v>
       </c>
       <c r="S234" t="n">
         <v>330500</v>
       </c>
       <c r="T234" t="n">
-        <v>-5.6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="235">
@@ -16131,13 +16131,13 @@
         <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>2721000</v>
+        <v>2770000</v>
       </c>
       <c r="S235" t="n">
         <v>2954000</v>
       </c>
       <c r="T235" t="n">
-        <v>-7.9</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="236">
@@ -16203,13 +16203,13 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>160600</v>
+        <v>165900</v>
       </c>
       <c r="S236" t="n">
         <v>177700</v>
       </c>
       <c r="T236" t="n">
-        <v>-9.6</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="237">
@@ -16266,13 +16266,13 @@
         <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>75200</v>
+        <v>75600</v>
       </c>
       <c r="S237" t="n">
         <v>84100</v>
       </c>
       <c r="T237" t="n">
-        <v>-10.6</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="238">
@@ -16329,13 +16329,13 @@
         <v>4.8</v>
       </c>
       <c r="R238" t="n">
-        <v>15520</v>
+        <v>16220</v>
       </c>
       <c r="S238" t="n">
         <v>14900</v>
       </c>
       <c r="T238" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="239">
@@ -16392,13 +16392,13 @@
         <v>-26.3</v>
       </c>
       <c r="R239" t="n">
-        <v>36500</v>
+        <v>38200</v>
       </c>
       <c r="S239" t="n">
         <v>37650</v>
       </c>
       <c r="T239" t="n">
-        <v>-3.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="240">
@@ -16464,13 +16464,13 @@
         <v>4.6</v>
       </c>
       <c r="R240" t="n">
-        <v>138500</v>
+        <v>137800</v>
       </c>
       <c r="S240" t="n">
         <v>132800</v>
       </c>
       <c r="T240" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="241">
@@ -16527,13 +16527,13 @@
         <v>0</v>
       </c>
       <c r="R241" t="n">
-        <v>448000</v>
+        <v>458000</v>
       </c>
       <c r="S241" t="n">
         <v>489500</v>
       </c>
       <c r="T241" t="n">
-        <v>-8.5</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="242">
@@ -16599,13 +16599,13 @@
         <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>31750</v>
+        <v>31850</v>
       </c>
       <c r="S242" t="n">
         <v>33700</v>
       </c>
       <c r="T242" t="n">
-        <v>-5.8</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="243">
@@ -16662,13 +16662,13 @@
         <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>10020</v>
+        <v>10260</v>
       </c>
       <c r="S243" t="n">
         <v>10030</v>
       </c>
       <c r="T243" t="n">
-        <v>-0.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="244">
@@ -16734,13 +16734,13 @@
         <v>-3.4</v>
       </c>
       <c r="R244" t="n">
-        <v>122200</v>
+        <v>125800</v>
       </c>
       <c r="S244" t="n">
         <v>134100</v>
       </c>
       <c r="T244" t="n">
-        <v>-8.9</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="245">
@@ -16806,13 +16806,13 @@
         <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>21300</v>
+        <v>21550</v>
       </c>
       <c r="S245" t="n">
         <v>22200</v>
       </c>
       <c r="T245" t="n">
-        <v>-4.1</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="246">
@@ -16869,13 +16869,13 @@
         <v>1.1</v>
       </c>
       <c r="R246" t="n">
-        <v>83700</v>
+        <v>86000</v>
       </c>
       <c r="S246" t="n">
         <v>87300</v>
       </c>
       <c r="T246" t="n">
-        <v>-4.1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="247">
@@ -16932,13 +16932,13 @@
         <v>0.4</v>
       </c>
       <c r="R247" t="n">
-        <v>453000</v>
+        <v>455000</v>
       </c>
       <c r="S247" t="n">
         <v>510000</v>
       </c>
       <c r="T247" t="n">
-        <v>-11.2</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="248">
@@ -17004,13 +17004,13 @@
         <v>0</v>
       </c>
       <c r="R248" t="n">
-        <v>167900</v>
+        <v>174400</v>
       </c>
       <c r="S248" t="n">
         <v>179400</v>
       </c>
       <c r="T248" t="n">
-        <v>-6.4</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="249">
@@ -17067,13 +17067,13 @@
         <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>104300</v>
+        <v>104500</v>
       </c>
       <c r="S249" t="n">
         <v>119100</v>
       </c>
       <c r="T249" t="n">
-        <v>-12.4</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="250">
@@ -17139,13 +17139,13 @@
         <v>1.1</v>
       </c>
       <c r="R250" t="n">
-        <v>326000</v>
+        <v>330500</v>
       </c>
       <c r="S250" t="n">
         <v>322000</v>
       </c>
       <c r="T250" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="251">
@@ -17202,13 +17202,13 @@
         <v>-4450</v>
       </c>
       <c r="R251" t="n">
-        <v>13950</v>
+        <v>15340</v>
       </c>
       <c r="S251" t="n">
         <v>15550</v>
       </c>
       <c r="T251" t="n">
-        <v>-10.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="252">
@@ -17265,13 +17265,13 @@
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>343500</v>
+        <v>361000</v>
       </c>
       <c r="S252" t="n">
         <v>369500</v>
       </c>
       <c r="T252" t="n">
-        <v>-7</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="253">
@@ -17337,13 +17337,13 @@
         <v>0</v>
       </c>
       <c r="R253" t="n">
-        <v>68200</v>
+        <v>68300</v>
       </c>
       <c r="S253" t="n">
         <v>73800</v>
       </c>
       <c r="T253" t="n">
-        <v>-7.6</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="254">
@@ -17409,13 +17409,13 @@
         <v>-1.5</v>
       </c>
       <c r="R254" t="n">
-        <v>18170</v>
+        <v>18340</v>
       </c>
       <c r="S254" t="n">
         <v>19800</v>
       </c>
       <c r="T254" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="255">
@@ -17481,13 +17481,13 @@
         <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>42500</v>
+        <v>44800</v>
       </c>
       <c r="S255" t="n">
         <v>45150</v>
       </c>
       <c r="T255" t="n">
-        <v>-5.9</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="256">
@@ -17553,13 +17553,13 @@
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>62200</v>
+        <v>63100</v>
       </c>
       <c r="S256" t="n">
         <v>67000</v>
       </c>
       <c r="T256" t="n">
-        <v>-7.2</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="257">
@@ -17598,13 +17598,13 @@
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>35500</v>
+        <v>36700</v>
       </c>
       <c r="S257" t="n">
         <v>41100</v>
       </c>
       <c r="T257" t="n">
-        <v>-13.6</v>
+        <v>-10.7</v>
       </c>
     </row>
     <row r="258">
@@ -17661,13 +17661,13 @@
         <v>0.7</v>
       </c>
       <c r="R258" t="n">
-        <v>1123000</v>
+        <v>1068000</v>
       </c>
       <c r="S258" t="n">
         <v>1154000</v>
       </c>
       <c r="T258" t="n">
-        <v>-2.7</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="259">
@@ -17706,13 +17706,13 @@
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>44900</v>
+        <v>44000</v>
       </c>
       <c r="S259" t="n">
         <v>40400</v>
       </c>
       <c r="T259" t="n">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="260">
@@ -17778,13 +17778,13 @@
         <v>5.1</v>
       </c>
       <c r="R260" t="n">
-        <v>105300</v>
+        <v>104700</v>
       </c>
       <c r="S260" t="n">
         <v>120100</v>
       </c>
       <c r="T260" t="n">
-        <v>-12.3</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="261">
@@ -17841,13 +17841,13 @@
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>49050</v>
+        <v>48750</v>
       </c>
       <c r="S261" t="n">
         <v>54700</v>
       </c>
       <c r="T261" t="n">
-        <v>-10.3</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="262">
@@ -17904,13 +17904,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="R262" t="n">
-        <v>61900</v>
+        <v>61700</v>
       </c>
       <c r="S262" t="n">
         <v>65500</v>
       </c>
       <c r="T262" t="n">
-        <v>-5.5</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="263">
@@ -17967,13 +17967,13 @@
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>197700</v>
+        <v>207000</v>
       </c>
       <c r="S263" t="n">
         <v>196800</v>
       </c>
       <c r="T263" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="264">
@@ -18093,13 +18093,13 @@
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>9140</v>
+        <v>9260</v>
       </c>
       <c r="S265" t="n">
         <v>9860</v>
       </c>
       <c r="T265" t="n">
-        <v>-7.3</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="266">
@@ -18156,13 +18156,13 @@
         <v>3.6</v>
       </c>
       <c r="R266" t="n">
-        <v>31800</v>
+        <v>31750</v>
       </c>
       <c r="S266" t="n">
         <v>31700</v>
       </c>
       <c r="T266" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="267">
@@ -18219,13 +18219,13 @@
         <v>-0.2</v>
       </c>
       <c r="R267" t="n">
-        <v>216500</v>
+        <v>232500</v>
       </c>
       <c r="S267" t="n">
         <v>228500</v>
       </c>
       <c r="T267" t="n">
-        <v>-5.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="268">
@@ -18282,13 +18282,13 @@
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>15140</v>
+        <v>15230</v>
       </c>
       <c r="S268" t="n">
         <v>17820</v>
       </c>
       <c r="T268" t="n">
-        <v>-15</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="269">
@@ -18345,13 +18345,13 @@
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>51200</v>
+        <v>50100</v>
       </c>
       <c r="S269" t="n">
         <v>53300</v>
       </c>
       <c r="T269" t="n">
-        <v>-3.9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="270">
@@ -18390,13 +18390,13 @@
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>33450</v>
+        <v>35000</v>
       </c>
       <c r="S270" t="n">
         <v>45900</v>
       </c>
       <c r="T270" t="n">
-        <v>-27.1</v>
+        <v>-23.7</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W270"/>
+  <dimension ref="A1:W272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-27 · 전주 2026-08-24</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-29 · 전주 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>15170</v>
+        <v>15720</v>
       </c>
       <c r="V3" t="n">
         <v>15470</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4">
@@ -714,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>82800</v>
+        <v>84900</v>
       </c>
       <c r="V4" t="n">
         <v>84500</v>
       </c>
       <c r="W4" t="n">
-        <v>-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>73200</v>
+        <v>74700</v>
       </c>
       <c r="V5" t="n">
         <v>73400</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -852,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1215000</v>
+        <v>1238000</v>
       </c>
       <c r="V6" t="n">
         <v>1084000</v>
       </c>
       <c r="W6" t="n">
-        <v>12.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="7">
@@ -990,13 +990,13 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>23950</v>
+        <v>24750</v>
       </c>
       <c r="V8" t="n">
         <v>23775</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="9">
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>126000</v>
+        <v>128000</v>
       </c>
       <c r="V9" t="n">
         <v>130800</v>
       </c>
       <c r="W9" t="n">
-        <v>-3.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="10">
@@ -1092,43 +1092,43 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="L10" t="n">
-        <v>1093.8</v>
+        <v>1103.7</v>
       </c>
       <c r="M10" t="n">
         <v>1093.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1199.2</v>
+        <v>1192.3</v>
       </c>
       <c r="P10" t="n">
         <v>1199.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1393.2</v>
+        <v>1394.3</v>
       </c>
       <c r="S10" t="n">
         <v>1393.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="U10" t="n">
-        <v>91400</v>
+        <v>96000</v>
       </c>
       <c r="V10" t="n">
         <v>92100</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -1194,13 +1194,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1720000</v>
+        <v>1653000</v>
       </c>
       <c r="V11" t="n">
         <v>1679000</v>
       </c>
       <c r="W11" t="n">
-        <v>2.4</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="12">
@@ -1260,13 +1260,13 @@
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>129000</v>
+        <v>128900</v>
       </c>
       <c r="V12" t="n">
         <v>104500</v>
       </c>
       <c r="W12" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="13">
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>677000</v>
+        <v>687000</v>
       </c>
       <c r="V13" t="n">
         <v>633000</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="14">
@@ -1395,13 +1395,13 @@
         <v>35.3</v>
       </c>
       <c r="U14" t="n">
-        <v>129700</v>
+        <v>134900</v>
       </c>
       <c r="V14" t="n">
         <v>83800</v>
       </c>
       <c r="W14" t="n">
-        <v>54.8</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -1461,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>95000</v>
+        <v>93900</v>
       </c>
       <c r="V15" t="n">
         <v>87000</v>
       </c>
       <c r="W15" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="16">
@@ -1527,13 +1527,13 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>126600</v>
+        <v>130500</v>
       </c>
       <c r="V16" t="n">
         <v>127200</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -1593,13 +1593,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>43300</v>
+        <v>42600</v>
       </c>
       <c r="V17" t="n">
         <v>41900</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -1629,43 +1629,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L18" t="n">
-        <v>2285.9</v>
+        <v>2290.1</v>
       </c>
       <c r="M18" t="n">
         <v>2285.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O18" t="n">
-        <v>2555.4</v>
+        <v>2566.1</v>
       </c>
       <c r="P18" t="n">
         <v>2555.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R18" t="n">
-        <v>3230</v>
+        <v>3257.1</v>
       </c>
       <c r="S18" t="n">
         <v>3230</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="U18" t="n">
-        <v>29550</v>
+        <v>29700</v>
       </c>
       <c r="V18" t="n">
         <v>26600</v>
       </c>
       <c r="W18" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="19">
@@ -1704,31 +1704,31 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>14370.6</v>
+        <v>14411.4</v>
       </c>
       <c r="P19" t="n">
         <v>14370.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R19" t="n">
-        <v>15745.8</v>
+        <v>15783.6</v>
       </c>
       <c r="S19" t="n">
         <v>15745.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U19" t="n">
-        <v>48700</v>
+        <v>52400</v>
       </c>
       <c r="V19" t="n">
         <v>50200</v>
       </c>
       <c r="W19" t="n">
-        <v>-3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="20">
@@ -1788,13 +1788,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>17480</v>
+        <v>18200</v>
       </c>
       <c r="V20" t="n">
         <v>17990</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
@@ -1860,13 +1860,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>6400</v>
+        <v>6500</v>
       </c>
       <c r="V21" t="n">
         <v>6550</v>
       </c>
       <c r="W21" t="n">
-        <v>-2.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="22">
@@ -1926,13 +1926,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>466500</v>
+        <v>473500</v>
       </c>
       <c r="V22" t="n">
         <v>450500</v>
       </c>
       <c r="W22" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="23">
@@ -1998,13 +1998,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>15090</v>
+        <v>17020</v>
       </c>
       <c r="V23" t="n">
         <v>14880</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="24">
@@ -2064,13 +2064,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>99700</v>
+        <v>103400</v>
       </c>
       <c r="V24" t="n">
         <v>100500</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -2100,25 +2100,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="L25" t="n">
-        <v>1251.5</v>
+        <v>1313</v>
       </c>
       <c r="M25" t="n">
         <v>1251.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1520.5</v>
+        <v>1531</v>
       </c>
       <c r="P25" t="n">
         <v>1520.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="R25" t="n">
         <v>1770</v>
@@ -2130,13 +2130,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>9890</v>
+        <v>9920</v>
       </c>
       <c r="V25" t="n">
         <v>9690</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
@@ -2202,13 +2202,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>7710</v>
+        <v>7880</v>
       </c>
       <c r="V26" t="n">
         <v>7810</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="27">
@@ -2274,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1481000</v>
+        <v>1547000</v>
       </c>
       <c r="V27" t="n">
         <v>1402000</v>
       </c>
       <c r="W27" t="n">
-        <v>5.6</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="28">
@@ -2340,13 +2340,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>28300</v>
+        <v>28700</v>
       </c>
       <c r="V28" t="n">
         <v>26050</v>
       </c>
       <c r="W28" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="29">
@@ -2379,40 +2379,40 @@
         <v>5183</v>
       </c>
       <c r="L29" t="n">
-        <v>16047</v>
+        <v>16183.1</v>
       </c>
       <c r="M29" t="n">
         <v>16294.7</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.5</v>
+        <v>-0.7</v>
       </c>
       <c r="O29" t="n">
-        <v>19654.1</v>
+        <v>19872.2</v>
       </c>
       <c r="P29" t="n">
         <v>20120.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>-2.3</v>
+        <v>-1.2</v>
       </c>
       <c r="R29" t="n">
-        <v>21670.2</v>
+        <v>21776.2</v>
       </c>
       <c r="S29" t="n">
         <v>22324</v>
       </c>
       <c r="T29" t="n">
-        <v>-2.9</v>
+        <v>-2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>114200</v>
+        <v>116300</v>
       </c>
       <c r="V29" t="n">
         <v>112300</v>
       </c>
       <c r="W29" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30">
@@ -2478,13 +2478,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>183800</v>
+        <v>186300</v>
       </c>
       <c r="V30" t="n">
         <v>170700</v>
       </c>
       <c r="W30" t="n">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="31">
@@ -2550,13 +2550,13 @@
         <v>0.7</v>
       </c>
       <c r="U31" t="n">
-        <v>47050</v>
+        <v>48350</v>
       </c>
       <c r="V31" t="n">
         <v>45500</v>
       </c>
       <c r="W31" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="32">
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>31650</v>
+        <v>31000</v>
       </c>
       <c r="V32" t="n">
         <v>27800</v>
       </c>
       <c r="W32" t="n">
-        <v>13.8</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="33">
@@ -2688,13 +2688,13 @@
         <v>0.6</v>
       </c>
       <c r="U33" t="n">
-        <v>422000</v>
+        <v>405500</v>
       </c>
       <c r="V33" t="n">
         <v>397500</v>
       </c>
       <c r="W33" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2760,13 +2760,13 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>427000</v>
+        <v>450500</v>
       </c>
       <c r="V34" t="n">
         <v>454500</v>
       </c>
       <c r="W34" t="n">
-        <v>-6.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="35">
@@ -2796,43 +2796,43 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2078</v>
+        <v>2015</v>
       </c>
       <c r="L35" t="n">
-        <v>3717</v>
+        <v>3676.7</v>
       </c>
       <c r="M35" t="n">
         <v>3717</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="O35" t="n">
-        <v>4522.5</v>
+        <v>4756.7</v>
       </c>
       <c r="P35" t="n">
         <v>4522.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R35" t="n">
-        <v>7457.5</v>
+        <v>8550</v>
       </c>
       <c r="S35" t="n">
         <v>7457.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="U35" t="n">
-        <v>23700</v>
+        <v>24150</v>
       </c>
       <c r="V35" t="n">
         <v>23050</v>
       </c>
       <c r="W35" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="36">
@@ -2898,13 +2898,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>97000</v>
+        <v>99600</v>
       </c>
       <c r="V36" t="n">
         <v>97700</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="37">
@@ -2934,49 +2934,49 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>31031</v>
+        <v>30765</v>
       </c>
       <c r="G37" t="n">
         <v>31144</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
       <c r="L37" t="n">
-        <v>115428.3</v>
+        <v>114810.8</v>
       </c>
       <c r="M37" t="n">
         <v>115689.5</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="O37" t="n">
-        <v>133148.8</v>
+        <v>132761.9</v>
       </c>
       <c r="P37" t="n">
         <v>133401.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="R37" t="n">
-        <v>143338.9</v>
+        <v>142985.6</v>
       </c>
       <c r="S37" t="n">
         <v>143483.7</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="U37" t="n">
-        <v>397000</v>
+        <v>399500</v>
       </c>
       <c r="V37" t="n">
         <v>410500</v>
       </c>
       <c r="W37" t="n">
-        <v>-3.3</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="38">
@@ -3042,13 +3042,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>340000</v>
+        <v>337500</v>
       </c>
       <c r="V38" t="n">
         <v>326500</v>
       </c>
       <c r="W38" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="39">
@@ -3105,13 +3105,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>183500</v>
+        <v>187400</v>
       </c>
       <c r="V39" t="n">
         <v>180400</v>
       </c>
       <c r="W39" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="40">
@@ -3141,43 +3141,43 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="L40" t="n">
-        <v>4412.2</v>
+        <v>4422</v>
       </c>
       <c r="M40" t="n">
         <v>4558.8</v>
       </c>
       <c r="N40" t="n">
-        <v>-3.2</v>
+        <v>-3</v>
       </c>
       <c r="O40" t="n">
-        <v>4870.2</v>
+        <v>4807.2</v>
       </c>
       <c r="P40" t="n">
         <v>4944.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.5</v>
+        <v>-2.8</v>
       </c>
       <c r="R40" t="n">
-        <v>5734.8</v>
+        <v>5682.2</v>
       </c>
       <c r="S40" t="n">
         <v>5947.4</v>
       </c>
       <c r="T40" t="n">
-        <v>-3.6</v>
+        <v>-4.5</v>
       </c>
       <c r="U40" t="n">
-        <v>52300</v>
+        <v>52400</v>
       </c>
       <c r="V40" t="n">
         <v>53500</v>
       </c>
       <c r="W40" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="41">
@@ -3234,22 +3234,22 @@
         <v>-0.2</v>
       </c>
       <c r="R41" t="n">
-        <v>5421469.6</v>
+        <v>5361095.1</v>
       </c>
       <c r="S41" t="n">
         <v>5438609.1</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.3</v>
+        <v>-1.4</v>
       </c>
       <c r="U41" t="n">
-        <v>265500</v>
+        <v>257000</v>
       </c>
       <c r="V41" t="n">
         <v>256750</v>
       </c>
       <c r="W41" t="n">
-        <v>3.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="42">
@@ -3306,13 +3306,13 @@
         <v>-0.8</v>
       </c>
       <c r="U42" t="n">
-        <v>26350</v>
+        <v>26650</v>
       </c>
       <c r="V42" t="n">
         <v>25900</v>
       </c>
       <c r="W42" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="43">
@@ -3378,13 +3378,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>37800</v>
+        <v>38650</v>
       </c>
       <c r="V43" t="n">
         <v>38000</v>
       </c>
       <c r="W43" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="44">
@@ -3450,13 +3450,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>311500</v>
+        <v>313000</v>
       </c>
       <c r="V44" t="n">
         <v>286000</v>
       </c>
       <c r="W44" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="45">
@@ -3486,43 +3486,43 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L45" t="n">
-        <v>733.2</v>
+        <v>725.6</v>
       </c>
       <c r="M45" t="n">
         <v>733.2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O45" t="n">
-        <v>963.5</v>
+        <v>980.8</v>
       </c>
       <c r="P45" t="n">
         <v>963.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R45" t="n">
-        <v>1318.2</v>
+        <v>1277.5</v>
       </c>
       <c r="S45" t="n">
         <v>1318.2</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="U45" t="n">
-        <v>126800</v>
+        <v>130500</v>
       </c>
       <c r="V45" t="n">
         <v>130600</v>
       </c>
       <c r="W45" t="n">
-        <v>-2.9</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="46">
@@ -3588,13 +3588,13 @@
         <v>1.7</v>
       </c>
       <c r="U46" t="n">
-        <v>36750</v>
+        <v>37150</v>
       </c>
       <c r="V46" t="n">
         <v>34150</v>
       </c>
       <c r="W46" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3654,13 +3654,13 @@
         <v>2.3</v>
       </c>
       <c r="U47" t="n">
-        <v>570000</v>
+        <v>571000</v>
       </c>
       <c r="V47" t="n">
         <v>514000</v>
       </c>
       <c r="W47" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="48">
@@ -3726,13 +3726,13 @@
         <v>2.4</v>
       </c>
       <c r="U48" t="n">
-        <v>89600</v>
+        <v>95800</v>
       </c>
       <c r="V48" t="n">
         <v>82700</v>
       </c>
       <c r="W48" t="n">
-        <v>8.300000000000001</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="49">
@@ -3789,13 +3789,13 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>35800</v>
+        <v>36150</v>
       </c>
       <c r="V49" t="n">
         <v>34550</v>
       </c>
       <c r="W49" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="50">
@@ -3861,13 +3861,13 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>25600</v>
+        <v>26650</v>
       </c>
       <c r="V50" t="n">
         <v>26800</v>
       </c>
       <c r="W50" t="n">
-        <v>-4.5</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="51">
@@ -3933,13 +3933,13 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>46000</v>
+        <v>47200</v>
       </c>
       <c r="V51" t="n">
         <v>47950</v>
       </c>
       <c r="W51" t="n">
-        <v>-4.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="52">
@@ -3968,23 +3968,26 @@
           <t>KOSPI200,커버리지</t>
         </is>
       </c>
+      <c r="F52" t="n">
+        <v>947</v>
+      </c>
       <c r="L52" t="n">
-        <v>3417</v>
+        <v>3444.1</v>
       </c>
       <c r="M52" t="n">
         <v>3403.1</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="O52" t="n">
-        <v>5026.6</v>
+        <v>5128.7</v>
       </c>
       <c r="P52" t="n">
         <v>4974</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
         <v>6235.6</v>
@@ -3996,13 +3999,13 @@
         <v>0.1</v>
       </c>
       <c r="U52" t="n">
-        <v>113300</v>
+        <v>112800</v>
       </c>
       <c r="V52" t="n">
         <v>101300</v>
       </c>
       <c r="W52" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="53">
@@ -4068,13 +4071,13 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>60600</v>
+        <v>60100</v>
       </c>
       <c r="V53" t="n">
         <v>55200</v>
       </c>
       <c r="W53" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="54">
@@ -4125,13 +4128,13 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>16000</v>
+        <v>16800</v>
       </c>
       <c r="V54" t="n">
         <v>15120</v>
       </c>
       <c r="W54" t="n">
-        <v>5.8</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="55">
@@ -4197,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>42050</v>
+        <v>43000</v>
       </c>
       <c r="V55" t="n">
         <v>42100</v>
       </c>
       <c r="W55" t="n">
-        <v>-0.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="56">
@@ -4269,13 +4272,13 @@
         <v>-0.1</v>
       </c>
       <c r="U56" t="n">
-        <v>1388000</v>
+        <v>1421000</v>
       </c>
       <c r="V56" t="n">
         <v>1318000</v>
       </c>
       <c r="W56" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="57">
@@ -4305,31 +4308,31 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G57" t="n">
         <v>92</v>
       </c>
       <c r="H57" t="n">
-        <v>10.9</v>
+        <v>4.3</v>
       </c>
       <c r="L57" t="n">
-        <v>393.2</v>
+        <v>389</v>
       </c>
       <c r="M57" t="n">
         <v>381</v>
       </c>
       <c r="N57" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="O57" t="n">
-        <v>434</v>
+        <v>426.8</v>
       </c>
       <c r="P57" t="n">
         <v>418.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
         <v>524.2</v>
@@ -4341,13 +4344,13 @@
         <v>3.4</v>
       </c>
       <c r="U57" t="n">
-        <v>38500</v>
+        <v>39700</v>
       </c>
       <c r="V57" t="n">
         <v>39050</v>
       </c>
       <c r="W57" t="n">
-        <v>-1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="58">
@@ -4380,13 +4383,13 @@
         <v>16</v>
       </c>
       <c r="U58" t="n">
-        <v>64200</v>
+        <v>64600</v>
       </c>
       <c r="V58" t="n">
         <v>60200</v>
       </c>
       <c r="W58" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="59">
@@ -4416,49 +4419,49 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>15751</v>
+        <v>15859</v>
       </c>
       <c r="G59" t="n">
         <v>15825</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L59" t="n">
-        <v>61329.5</v>
+        <v>61593.6</v>
       </c>
       <c r="M59" t="n">
         <v>60721.1</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="O59" t="n">
-        <v>73052.7</v>
+        <v>73613.8</v>
       </c>
       <c r="P59" t="n">
         <v>72094.60000000001</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="R59" t="n">
-        <v>83505.8</v>
+        <v>84268.8</v>
       </c>
       <c r="S59" t="n">
         <v>83644.7</v>
       </c>
       <c r="T59" t="n">
-        <v>-0.2</v>
+        <v>0.7</v>
       </c>
       <c r="U59" t="n">
-        <v>359500</v>
+        <v>354500</v>
       </c>
       <c r="V59" t="n">
         <v>351500</v>
       </c>
       <c r="W59" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="60">
@@ -4524,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>33250</v>
+        <v>33750</v>
       </c>
       <c r="V60" t="n">
         <v>31800</v>
       </c>
       <c r="W60" t="n">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="61">
@@ -4560,49 +4563,49 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1121</v>
+        <v>1064</v>
       </c>
       <c r="G61" t="n">
         <v>1121</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-5.1</v>
       </c>
       <c r="L61" t="n">
-        <v>3544.5</v>
+        <v>3467.9</v>
       </c>
       <c r="M61" t="n">
         <v>3544.5</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-2.2</v>
       </c>
       <c r="O61" t="n">
-        <v>5552.4</v>
+        <v>5565.4</v>
       </c>
       <c r="P61" t="n">
         <v>5552.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R61" t="n">
-        <v>6508.2</v>
+        <v>6588.9</v>
       </c>
       <c r="S61" t="n">
         <v>6508.2</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U61" t="n">
-        <v>276000</v>
+        <v>274500</v>
       </c>
       <c r="V61" t="n">
         <v>268000</v>
       </c>
       <c r="W61" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="62">
@@ -4662,13 +4665,13 @@
         <v>-0.3</v>
       </c>
       <c r="U62" t="n">
-        <v>218000</v>
+        <v>214500</v>
       </c>
       <c r="V62" t="n">
         <v>191300</v>
       </c>
       <c r="W62" t="n">
-        <v>14</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="63">
@@ -4734,13 +4737,13 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1367000</v>
+        <v>1375000</v>
       </c>
       <c r="V63" t="n">
         <v>1347000</v>
       </c>
       <c r="W63" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="64">
@@ -4770,10 +4773,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3533</v>
+        <v>3512</v>
       </c>
       <c r="L64" t="n">
-        <v>13812.8</v>
+        <v>13813.9</v>
       </c>
       <c r="M64" t="n">
         <v>13874.7</v>
@@ -4782,31 +4785,31 @@
         <v>-0.4</v>
       </c>
       <c r="O64" t="n">
-        <v>19832.5</v>
+        <v>19722.5</v>
       </c>
       <c r="P64" t="n">
         <v>19904.9</v>
       </c>
       <c r="Q64" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="R64" t="n">
-        <v>23581.9</v>
+        <v>23461.3</v>
       </c>
       <c r="S64" t="n">
         <v>23602.3</v>
       </c>
       <c r="T64" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="U64" t="n">
-        <v>20900</v>
+        <v>21200</v>
       </c>
       <c r="V64" t="n">
         <v>20050</v>
       </c>
       <c r="W64" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="65">
@@ -4872,13 +4875,13 @@
         <v>-7.2</v>
       </c>
       <c r="U65" t="n">
-        <v>16150</v>
+        <v>16340</v>
       </c>
       <c r="V65" t="n">
         <v>16010</v>
       </c>
       <c r="W65" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="66">
@@ -4908,49 +4911,49 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>10095</v>
+        <v>10574</v>
       </c>
       <c r="G66" t="n">
         <v>10095</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L66" t="n">
-        <v>42661.6</v>
+        <v>43721.9</v>
       </c>
       <c r="M66" t="n">
         <v>42661.6</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O66" t="n">
-        <v>31437.9</v>
+        <v>32570.5</v>
       </c>
       <c r="P66" t="n">
         <v>31437.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R66" t="n">
-        <v>27853.1</v>
+        <v>27677.9</v>
       </c>
       <c r="S66" t="n">
         <v>27853.1</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="U66" t="n">
-        <v>136500</v>
+        <v>149200</v>
       </c>
       <c r="V66" t="n">
         <v>141200</v>
       </c>
       <c r="W66" t="n">
-        <v>-3.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="67">
@@ -5016,13 +5019,13 @@
         <v>0.6</v>
       </c>
       <c r="U67" t="n">
-        <v>597000</v>
+        <v>611000</v>
       </c>
       <c r="V67" t="n">
         <v>571000</v>
       </c>
       <c r="W67" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -5082,13 +5085,13 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>57600</v>
+        <v>59500</v>
       </c>
       <c r="V68" t="n">
         <v>55000</v>
       </c>
       <c r="W68" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5154,13 +5157,13 @@
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>21500</v>
+        <v>21700</v>
       </c>
       <c r="V69" t="n">
         <v>22800</v>
       </c>
       <c r="W69" t="n">
-        <v>-5.7</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="70">
@@ -5220,13 +5223,13 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>59100</v>
+        <v>59700</v>
       </c>
       <c r="V70" t="n">
         <v>60200</v>
       </c>
       <c r="W70" t="n">
-        <v>-1.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="71">
@@ -5292,13 +5295,13 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>122500</v>
+        <v>125900</v>
       </c>
       <c r="V71" t="n">
         <v>119500</v>
       </c>
       <c r="W71" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="72">
@@ -5328,49 +5331,49 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>-132</v>
+        <v>-148</v>
       </c>
       <c r="G72" t="n">
         <v>-132</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>-12.1</v>
       </c>
       <c r="L72" t="n">
-        <v>-660</v>
+        <v>-688</v>
       </c>
       <c r="M72" t="n">
         <v>-660</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>-4.2</v>
       </c>
       <c r="O72" t="n">
-        <v>786.7</v>
+        <v>762.5</v>
       </c>
       <c r="P72" t="n">
         <v>786.7</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="R72" t="n">
-        <v>2600.3</v>
+        <v>2495</v>
       </c>
       <c r="S72" t="n">
         <v>2600.3</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="U72" t="n">
-        <v>90100</v>
+        <v>91300</v>
       </c>
       <c r="V72" t="n">
         <v>84500</v>
       </c>
       <c r="W72" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -5412,13 +5415,13 @@
         <v>501</v>
       </c>
       <c r="U73" t="n">
-        <v>16830</v>
+        <v>16910</v>
       </c>
       <c r="V73" t="n">
         <v>15760</v>
       </c>
       <c r="W73" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="74">
@@ -5484,13 +5487,13 @@
         <v>-0</v>
       </c>
       <c r="U74" t="n">
-        <v>450000</v>
+        <v>450500</v>
       </c>
       <c r="V74" t="n">
         <v>495500</v>
       </c>
       <c r="W74" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="75">
@@ -5556,13 +5559,13 @@
         <v>-0</v>
       </c>
       <c r="U75" t="n">
-        <v>1149000</v>
+        <v>1157000</v>
       </c>
       <c r="V75" t="n">
         <v>1107000</v>
       </c>
       <c r="W75" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="76">
@@ -5622,13 +5625,13 @@
         <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>85800</v>
+        <v>83500</v>
       </c>
       <c r="V76" t="n">
         <v>78900</v>
       </c>
       <c r="W76" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="77">
@@ -5685,13 +5688,13 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>22250</v>
+        <v>22300</v>
       </c>
       <c r="V77" t="n">
         <v>22000</v>
       </c>
       <c r="W77" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="78">
@@ -5751,13 +5754,13 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>30000</v>
+        <v>31850</v>
       </c>
       <c r="V78" t="n">
         <v>24100</v>
       </c>
       <c r="W78" t="n">
-        <v>24.5</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="79">
@@ -5823,13 +5826,13 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>205250</v>
+        <v>203000</v>
       </c>
       <c r="V79" t="n">
         <v>203000</v>
       </c>
       <c r="W79" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5859,49 +5862,40 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="G80" t="n">
         <v>303</v>
       </c>
       <c r="H80" t="n">
-        <v>-4.3</v>
+        <v>-10.9</v>
       </c>
       <c r="L80" t="n">
-        <v>1075</v>
+        <v>990</v>
       </c>
       <c r="M80" t="n">
         <v>1083.3</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.8</v>
+        <v>-8.6</v>
       </c>
       <c r="O80" t="n">
-        <v>1455</v>
+        <v>1360</v>
       </c>
       <c r="P80" t="n">
         <v>1530</v>
       </c>
       <c r="Q80" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="R80" t="n">
-        <v>1680</v>
-      </c>
-      <c r="S80" t="n">
-        <v>1745</v>
-      </c>
-      <c r="T80" t="n">
-        <v>-3.7</v>
+        <v>-11.1</v>
       </c>
       <c r="U80" t="n">
-        <v>2630</v>
+        <v>2620</v>
       </c>
       <c r="V80" t="n">
         <v>2470</v>
       </c>
       <c r="W80" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="81">
@@ -5931,43 +5925,43 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>25837</v>
+        <v>25646</v>
       </c>
       <c r="L81" t="n">
-        <v>78982.3</v>
+        <v>79212.5</v>
       </c>
       <c r="M81" t="n">
         <v>81094.60000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>-2.6</v>
+        <v>-2.3</v>
       </c>
       <c r="O81" t="n">
-        <v>114756.8</v>
+        <v>114256.6</v>
       </c>
       <c r="P81" t="n">
         <v>115679.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="R81" t="n">
-        <v>133649.7</v>
+        <v>131965.1</v>
       </c>
       <c r="S81" t="n">
         <v>133894.6</v>
       </c>
       <c r="T81" t="n">
-        <v>-0.2</v>
+        <v>-1.4</v>
       </c>
       <c r="U81" t="n">
-        <v>33450</v>
+        <v>32550</v>
       </c>
       <c r="V81" t="n">
         <v>31300</v>
       </c>
       <c r="W81" t="n">
-        <v>6.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -6024,13 +6018,13 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>88000</v>
+        <v>88500</v>
       </c>
       <c r="V82" t="n">
         <v>86200</v>
       </c>
       <c r="W82" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="83">
@@ -6069,13 +6063,13 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>19621.9</v>
+        <v>19621.7</v>
       </c>
       <c r="M83" t="n">
         <v>19621.9</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O83" t="n">
         <v>20797.1</v>
@@ -6096,13 +6090,13 @@
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>99500</v>
+        <v>98600</v>
       </c>
       <c r="V83" t="n">
         <v>103300</v>
       </c>
       <c r="W83" t="n">
-        <v>-3.7</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="84">
@@ -6162,13 +6156,13 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>75300</v>
+        <v>75600</v>
       </c>
       <c r="V84" t="n">
         <v>73900</v>
       </c>
       <c r="W84" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="85">
@@ -6234,13 +6228,13 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>23750</v>
+        <v>24950</v>
       </c>
       <c r="V85" t="n">
         <v>22700</v>
       </c>
       <c r="W85" t="n">
-        <v>4.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="86">
@@ -6306,13 +6300,13 @@
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>234000</v>
+        <v>243000</v>
       </c>
       <c r="V86" t="n">
         <v>226000</v>
       </c>
       <c r="W86" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="87">
@@ -6378,13 +6372,13 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>3475</v>
+        <v>3490</v>
       </c>
       <c r="V87" t="n">
         <v>3515</v>
       </c>
       <c r="W87" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="88">
@@ -6450,162 +6444,138 @@
         <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>98300</v>
+        <v>100400</v>
       </c>
       <c r="V88" t="n">
         <v>97000</v>
       </c>
       <c r="W88" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>023160</t>
+          <t>022100</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>태광</t>
+          <t>포스코DX</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>IT서비스·SW</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="L89" t="n">
-        <v>461.7</v>
-      </c>
-      <c r="M89" t="n">
-        <v>467.8</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-1.3</v>
+        <v>404</v>
       </c>
       <c r="O89" t="n">
-        <v>790.3</v>
-      </c>
-      <c r="P89" t="n">
-        <v>765.2</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>3.3</v>
+        <v>735</v>
       </c>
       <c r="R89" t="n">
-        <v>732</v>
-      </c>
-      <c r="S89" t="n">
-        <v>746.8</v>
-      </c>
-      <c r="T89" t="n">
-        <v>-2</v>
+        <v>1161</v>
       </c>
       <c r="U89" t="n">
-        <v>25200</v>
+        <v>21400</v>
       </c>
       <c r="V89" t="n">
-        <v>21250</v>
+        <v>20500</v>
       </c>
       <c r="W89" t="n">
-        <v>18.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>023530</t>
+          <t>023160</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>롯데쇼핑</t>
+          <t>태광</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1840</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1840</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L90" t="n">
-        <v>8034.1</v>
+        <v>461.7</v>
       </c>
       <c r="M90" t="n">
-        <v>8034.1</v>
+        <v>467.8</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="O90" t="n">
-        <v>8704.9</v>
+        <v>790.3</v>
       </c>
       <c r="P90" t="n">
-        <v>8704.9</v>
+        <v>765.2</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R90" t="n">
-        <v>9368.299999999999</v>
+        <v>732</v>
       </c>
       <c r="S90" t="n">
-        <v>9368.299999999999</v>
+        <v>746.8</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="U90" t="n">
-        <v>103600</v>
+        <v>26600</v>
       </c>
       <c r="V90" t="n">
-        <v>95400</v>
+        <v>21250</v>
       </c>
       <c r="W90" t="n">
-        <v>8.6</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>024110</t>
+          <t>023530</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>기업은행</t>
+          <t>롯데쇼핑</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6615,7 +6585,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>금융-은행지주</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6623,52 +6593,61 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F91" t="n">
+        <v>1830</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1840</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="L91" t="n">
-        <v>37151.2</v>
+        <v>8000.9</v>
       </c>
       <c r="M91" t="n">
-        <v>37151.2</v>
+        <v>8034.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O91" t="n">
-        <v>40117.5</v>
+        <v>8680</v>
       </c>
       <c r="P91" t="n">
-        <v>40117.5</v>
+        <v>8704.9</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="R91" t="n">
-        <v>42377.2</v>
+        <v>9341.299999999999</v>
       </c>
       <c r="S91" t="n">
-        <v>42377.2</v>
+        <v>9368.299999999999</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="U91" t="n">
-        <v>20350</v>
+        <v>102100</v>
       </c>
       <c r="V91" t="n">
-        <v>20200</v>
+        <v>95400</v>
       </c>
       <c r="W91" t="n">
-        <v>0.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>024110</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>기업은행</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6678,63 +6657,60 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>2490</v>
+          <t>KOSPI200</t>
+        </is>
       </c>
       <c r="L92" t="n">
-        <v>9821.4</v>
+        <v>37151.2</v>
       </c>
       <c r="M92" t="n">
-        <v>9821.4</v>
+        <v>37151.2</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>11916.4</v>
+        <v>40117.5</v>
       </c>
       <c r="P92" t="n">
-        <v>11916.4</v>
+        <v>40117.5</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>13245.8</v>
+        <v>42377.2</v>
       </c>
       <c r="S92" t="n">
-        <v>13245.8</v>
+        <v>42377.2</v>
       </c>
       <c r="T92" t="n">
         <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>50100</v>
+        <v>20850</v>
       </c>
       <c r="V92" t="n">
-        <v>44650</v>
+        <v>20200</v>
       </c>
       <c r="W92" t="n">
-        <v>12.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>028260</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6744,7 +6720,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>지주회사</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6753,60 +6729,54 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>10248</v>
-      </c>
-      <c r="G93" t="n">
-        <v>10216</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0.3</v>
+        <v>2490</v>
       </c>
       <c r="L93" t="n">
-        <v>38072.6</v>
+        <v>9821.4</v>
       </c>
       <c r="M93" t="n">
-        <v>37964.4</v>
+        <v>9821.4</v>
       </c>
       <c r="N93" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>44105.8</v>
+        <v>11916.4</v>
       </c>
       <c r="P93" t="n">
-        <v>43740.4</v>
+        <v>11916.4</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>47672.2</v>
+        <v>13245.8</v>
       </c>
       <c r="S93" t="n">
-        <v>47339.7</v>
+        <v>13245.8</v>
       </c>
       <c r="T93" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>373500</v>
+        <v>48750</v>
       </c>
       <c r="V93" t="n">
-        <v>361500</v>
+        <v>44650</v>
       </c>
       <c r="W93" t="n">
-        <v>3.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>028260</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6816,7 +6786,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>운송·물류</t>
+          <t>지주회사</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6825,60 +6795,60 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1768</v>
+        <v>10248</v>
       </c>
       <c r="G94" t="n">
-        <v>1768</v>
+        <v>10216</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L94" t="n">
-        <v>6763</v>
+        <v>38072.6</v>
       </c>
       <c r="M94" t="n">
-        <v>6761.5</v>
+        <v>37964.4</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O94" t="n">
-        <v>6810.9</v>
+        <v>44105.8</v>
       </c>
       <c r="P94" t="n">
-        <v>6793.2</v>
+        <v>43740.4</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="R94" t="n">
-        <v>6990.8</v>
+        <v>47672.2</v>
       </c>
       <c r="S94" t="n">
-        <v>7000.8</v>
+        <v>47339.7</v>
       </c>
       <c r="T94" t="n">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
       <c r="U94" t="n">
-        <v>5590</v>
+        <v>375000</v>
       </c>
       <c r="V94" t="n">
-        <v>6380</v>
+        <v>361500</v>
       </c>
       <c r="W94" t="n">
-        <v>-12.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>029780</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>삼성카드</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6888,60 +6858,69 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>금융-카드기타</t>
+          <t>운송·물류</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
-        </is>
+          <t>KOSPI200,커버리지</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1768</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1768</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>8147.5</v>
+        <v>6763</v>
       </c>
       <c r="M95" t="n">
-        <v>8147.5</v>
+        <v>6761.5</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>8496.700000000001</v>
+        <v>6810.9</v>
       </c>
       <c r="P95" t="n">
-        <v>8496.700000000001</v>
+        <v>6793.2</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R95" t="n">
-        <v>8763.299999999999</v>
+        <v>6990.8</v>
       </c>
       <c r="S95" t="n">
-        <v>8763.299999999999</v>
+        <v>7000.8</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="U95" t="n">
-        <v>46300</v>
+        <v>5790</v>
       </c>
       <c r="V95" t="n">
-        <v>46250</v>
+        <v>6380</v>
       </c>
       <c r="W95" t="n">
-        <v>0.1</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>030000</t>
+          <t>029780</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>제일기획</t>
+          <t>삼성카드</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6951,7 +6930,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>미디어·광고</t>
+          <t>금융-카드기타</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6959,61 +6938,52 @@
           <t>KOSPI200</t>
         </is>
       </c>
-      <c r="F96" t="n">
-        <v>1008</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1008</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
       <c r="L96" t="n">
-        <v>3286.2</v>
+        <v>8147.5</v>
       </c>
       <c r="M96" t="n">
-        <v>3286.2</v>
+        <v>8147.5</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>3564.1</v>
+        <v>8496.700000000001</v>
       </c>
       <c r="P96" t="n">
-        <v>3564.1</v>
+        <v>8496.700000000001</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3687.9</v>
+        <v>8763.299999999999</v>
       </c>
       <c r="S96" t="n">
-        <v>3687.9</v>
+        <v>8763.299999999999</v>
       </c>
       <c r="T96" t="n">
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>18990</v>
+        <v>47300</v>
       </c>
       <c r="V96" t="n">
-        <v>19090</v>
+        <v>46250</v>
       </c>
       <c r="W96" t="n">
-        <v>-0.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>030200</t>
+          <t>030000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>제일기획</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7023,174 +6993,201 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>미디어·광고</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>5502</v>
+        <v>1008</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1008</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>21112.1</v>
+        <v>3286.2</v>
       </c>
       <c r="M97" t="n">
-        <v>21112.1</v>
+        <v>3286.2</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>22520.7</v>
+        <v>3564.1</v>
       </c>
       <c r="P97" t="n">
-        <v>22520.7</v>
+        <v>3564.1</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>23547.7</v>
+        <v>3687.9</v>
       </c>
       <c r="S97" t="n">
-        <v>23547.7</v>
+        <v>3687.9</v>
       </c>
       <c r="T97" t="n">
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>54000</v>
+        <v>19340</v>
       </c>
       <c r="V97" t="n">
-        <v>52600</v>
+        <v>19090</v>
       </c>
       <c r="W97" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>030200</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>316</v>
+        <v>5502</v>
       </c>
       <c r="L98" t="n">
-        <v>1085.7</v>
+        <v>21112.1</v>
       </c>
       <c r="M98" t="n">
-        <v>1085.7</v>
+        <v>21112.1</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>1513.3</v>
+        <v>22520.7</v>
       </c>
       <c r="P98" t="n">
-        <v>1513.3</v>
+        <v>22520.7</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1910.3</v>
+        <v>23547.7</v>
       </c>
       <c r="S98" t="n">
-        <v>1910.3</v>
+        <v>23547.7</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>127900</v>
+        <v>54500</v>
       </c>
       <c r="V98" t="n">
-        <v>110800</v>
+        <v>52600</v>
       </c>
       <c r="W98" t="n">
-        <v>15.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>032350</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>롯데관광개발</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>레저/카지노/면세</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>666</v>
-      </c>
-      <c r="G99" t="n">
-        <v>668</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-0.3</v>
+        <v>316</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1085.7</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1085.7</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1513.3</v>
+      </c>
+      <c r="P99" t="n">
+        <v>1513.3</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1910.3</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1910.3</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>12880</v>
+        <v>120100</v>
       </c>
       <c r="V99" t="n">
-        <v>12940</v>
+        <v>110800</v>
       </c>
       <c r="W99" t="n">
-        <v>-0.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>032640</t>
+          <t>032350</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LG유플러스</t>
+          <t>롯데관광개발</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7200,69 +7197,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3001</v>
+        <v>656</v>
       </c>
       <c r="G100" t="n">
-        <v>3001</v>
+        <v>668</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>11498.4</v>
-      </c>
-      <c r="M100" t="n">
-        <v>11498.4</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
-        <v>12333.2</v>
-      </c>
-      <c r="P100" t="n">
-        <v>12333.2</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>13168.1</v>
-      </c>
-      <c r="S100" t="n">
-        <v>13168.1</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="U100" t="n">
-        <v>14750</v>
+        <v>13250</v>
       </c>
       <c r="V100" t="n">
-        <v>14870</v>
+        <v>12940</v>
       </c>
       <c r="W100" t="n">
-        <v>-0.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>032640</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>LG유플러스</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7272,183 +7242,189 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>금융-보험</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
-        </is>
+          <t>KOSPI200,커버리지</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>3001</v>
+      </c>
+      <c r="G101" t="n">
+        <v>3001</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>34544.2</v>
+        <v>11498.4</v>
       </c>
       <c r="M101" t="n">
-        <v>31613</v>
+        <v>11498.4</v>
       </c>
       <c r="N101" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>69533.2</v>
+        <v>12333.2</v>
       </c>
       <c r="P101" t="n">
-        <v>69350.8</v>
+        <v>12333.2</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>45800.4</v>
+        <v>13168.1</v>
       </c>
       <c r="S101" t="n">
-        <v>45771.6</v>
+        <v>13168.1</v>
       </c>
       <c r="T101" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>306500</v>
+        <v>15020</v>
       </c>
       <c r="V101" t="n">
-        <v>287000</v>
+        <v>14870</v>
       </c>
       <c r="W101" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>033500</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>동성화인텍</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>금융-보험</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>커버리지</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>250</v>
+          <t>KOSPI200</t>
+        </is>
       </c>
       <c r="L102" t="n">
-        <v>1120</v>
+        <v>34544.2</v>
       </c>
       <c r="M102" t="n">
-        <v>1120</v>
+        <v>31613</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O102" t="n">
-        <v>1330</v>
+        <v>69533.2</v>
       </c>
       <c r="P102" t="n">
-        <v>1330</v>
+        <v>69350.8</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="R102" t="n">
+        <v>45800.4</v>
+      </c>
+      <c r="S102" t="n">
+        <v>45771.6</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0.1</v>
       </c>
       <c r="U102" t="n">
-        <v>17730</v>
+        <v>310000</v>
       </c>
       <c r="V102" t="n">
-        <v>17040</v>
+        <v>287000</v>
       </c>
       <c r="W102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>033780</t>
+          <t>033500</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KT&amp;G</t>
+          <t>동성화인텍</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>음식료</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>4928</v>
+        <v>250</v>
       </c>
       <c r="L103" t="n">
-        <v>15328.5</v>
+        <v>1120</v>
       </c>
       <c r="M103" t="n">
-        <v>15328.5</v>
+        <v>1120</v>
       </c>
       <c r="N103" t="n">
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>16544.1</v>
+        <v>1330</v>
       </c>
       <c r="P103" t="n">
-        <v>16544.1</v>
+        <v>1330</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
-      <c r="R103" t="n">
-        <v>17495.8</v>
-      </c>
-      <c r="S103" t="n">
-        <v>17495.8</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
       <c r="U103" t="n">
-        <v>174100</v>
+        <v>18360</v>
       </c>
       <c r="V103" t="n">
-        <v>172600</v>
+        <v>17040</v>
       </c>
       <c r="W103" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>033780</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7458,63 +7434,63 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>그린인프라</t>
+          <t>음식료</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2482</v>
+        <v>4928</v>
       </c>
       <c r="L104" t="n">
-        <v>11307.5</v>
+        <v>15328.5</v>
       </c>
       <c r="M104" t="n">
-        <v>11302.1</v>
+        <v>15328.5</v>
       </c>
       <c r="N104" t="n">
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>16235.7</v>
+        <v>16544.1</v>
       </c>
       <c r="P104" t="n">
-        <v>16265.1</v>
+        <v>16544.1</v>
       </c>
       <c r="Q104" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>20569.3</v>
+        <v>17495.8</v>
       </c>
       <c r="S104" t="n">
-        <v>20594</v>
+        <v>17495.8</v>
       </c>
       <c r="T104" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>86000</v>
+        <v>176300</v>
       </c>
       <c r="V104" t="n">
-        <v>72300</v>
+        <v>172600</v>
       </c>
       <c r="W104" t="n">
-        <v>18.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>034020</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7524,7 +7500,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>전기전자</t>
+          <t>그린인프라</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7533,60 +7509,54 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4391</v>
-      </c>
-      <c r="G105" t="n">
-        <v>4391</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
+        <v>2482</v>
       </c>
       <c r="L105" t="n">
-        <v>9648.9</v>
+        <v>11307.5</v>
       </c>
       <c r="M105" t="n">
-        <v>9648.9</v>
+        <v>11302.1</v>
       </c>
       <c r="N105" t="n">
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>14046</v>
+        <v>16235.7</v>
       </c>
       <c r="P105" t="n">
-        <v>14046</v>
+        <v>16265.1</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="R105" t="n">
-        <v>17013.4</v>
+        <v>20569.3</v>
       </c>
       <c r="S105" t="n">
-        <v>17013.4</v>
+        <v>20594</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="U105" t="n">
-        <v>9600</v>
+        <v>88200</v>
       </c>
       <c r="V105" t="n">
-        <v>9580</v>
+        <v>72300</v>
       </c>
       <c r="W105" t="n">
-        <v>0.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>034230</t>
+          <t>034220</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>파라다이스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7596,69 +7566,69 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>레저/카지노/면세</t>
+          <t>전기전자</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>510</v>
+        <v>4391</v>
       </c>
       <c r="G106" t="n">
-        <v>510</v>
+        <v>4391</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>1672.8</v>
+        <v>9648.9</v>
       </c>
       <c r="M106" t="n">
-        <v>1672.8</v>
+        <v>9648.9</v>
       </c>
       <c r="N106" t="n">
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>2035.2</v>
+        <v>14046</v>
       </c>
       <c r="P106" t="n">
-        <v>2035.2</v>
+        <v>14046</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2411.8</v>
+        <v>17013.4</v>
       </c>
       <c r="S106" t="n">
-        <v>2411.8</v>
+        <v>17013.4</v>
       </c>
       <c r="T106" t="n">
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>9750</v>
+        <v>9620</v>
       </c>
       <c r="V106" t="n">
-        <v>9430</v>
+        <v>9580</v>
       </c>
       <c r="W106" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>034730</t>
+          <t>034230</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>파라다이스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7668,63 +7638,69 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>지주회사</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>39056</v>
+        <v>509</v>
+      </c>
+      <c r="G107" t="n">
+        <v>510</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-0.2</v>
       </c>
       <c r="L107" t="n">
-        <v>122584.8</v>
+        <v>1651.7</v>
       </c>
       <c r="M107" t="n">
-        <v>122584.8</v>
+        <v>1672.8</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="O107" t="n">
-        <v>130311.1</v>
+        <v>2027.3</v>
       </c>
       <c r="P107" t="n">
-        <v>130311.1</v>
+        <v>2035.2</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="R107" t="n">
-        <v>154273.3</v>
+        <v>2403.4</v>
       </c>
       <c r="S107" t="n">
-        <v>154273.3</v>
+        <v>2411.8</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="U107" t="n">
-        <v>556000</v>
+        <v>10030</v>
       </c>
       <c r="V107" t="n">
-        <v>544000</v>
+        <v>9430</v>
       </c>
       <c r="W107" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>035250</t>
+          <t>034730</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>강원랜드</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7734,63 +7710,63 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>레저/카지노/면세</t>
+          <t>지주회사</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>670</v>
+        <v>33195</v>
       </c>
       <c r="L108" t="n">
-        <v>2237.8</v>
+        <v>118212.3</v>
       </c>
       <c r="M108" t="n">
-        <v>2237.8</v>
+        <v>122584.8</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="O108" t="n">
-        <v>2217.5</v>
+        <v>114339.3</v>
       </c>
       <c r="P108" t="n">
-        <v>2217.5</v>
+        <v>130311.1</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>-12.3</v>
       </c>
       <c r="R108" t="n">
-        <v>2567.4</v>
+        <v>138400.1</v>
       </c>
       <c r="S108" t="n">
-        <v>2567.4</v>
+        <v>154273.3</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>-10.3</v>
       </c>
       <c r="U108" t="n">
-        <v>14500</v>
+        <v>543000</v>
       </c>
       <c r="V108" t="n">
-        <v>14460</v>
+        <v>544000</v>
       </c>
       <c r="W108" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>035420</t>
+          <t>035250</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>강원랜드</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7800,7 +7776,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>인터넷/AI</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7809,60 +7785,54 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5638</v>
-      </c>
-      <c r="G109" t="n">
-        <v>5638</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="L109" t="n">
-        <v>22171.3</v>
+        <v>2237.8</v>
       </c>
       <c r="M109" t="n">
-        <v>22171.3</v>
+        <v>2237.8</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>25835.1</v>
+        <v>2217.5</v>
       </c>
       <c r="P109" t="n">
-        <v>25835.1</v>
+        <v>2217.5</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>30038.4</v>
+        <v>2567.4</v>
       </c>
       <c r="S109" t="n">
-        <v>30038.4</v>
+        <v>2567.4</v>
       </c>
       <c r="T109" t="n">
         <v>0</v>
       </c>
       <c r="U109" t="n">
-        <v>216500</v>
+        <v>14790</v>
       </c>
       <c r="V109" t="n">
-        <v>223500</v>
+        <v>14460</v>
       </c>
       <c r="W109" t="n">
-        <v>-3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>035720</t>
+          <t>035420</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>카카오</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7881,117 +7851,126 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2672</v>
+        <v>5638</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5638</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>10352</v>
+        <v>22171.3</v>
       </c>
       <c r="M110" t="n">
-        <v>10255.7</v>
+        <v>22171.3</v>
       </c>
       <c r="N110" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>11836</v>
+        <v>25835.1</v>
       </c>
       <c r="P110" t="n">
-        <v>11699.3</v>
+        <v>25835.1</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>13421.6</v>
+        <v>30038.4</v>
       </c>
       <c r="S110" t="n">
-        <v>13243.3</v>
+        <v>30038.4</v>
       </c>
       <c r="T110" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U110" t="n">
-        <v>36000</v>
+        <v>220500</v>
       </c>
       <c r="V110" t="n">
-        <v>35750</v>
+        <v>223500</v>
       </c>
       <c r="W110" t="n">
-        <v>0.7</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>035760</t>
+          <t>035720</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CJ ENM</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>인터넷/AI</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>커버리지</t>
-        </is>
+          <t>KOSPI200,커버리지</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2672</v>
       </c>
       <c r="L111" t="n">
-        <v>1324.4</v>
+        <v>10352</v>
       </c>
       <c r="M111" t="n">
-        <v>1324.4</v>
+        <v>10255.7</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O111" t="n">
-        <v>2114.6</v>
+        <v>11836</v>
       </c>
       <c r="P111" t="n">
-        <v>2114.6</v>
+        <v>11699.3</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R111" t="n">
-        <v>2544.2</v>
+        <v>13421.6</v>
       </c>
       <c r="S111" t="n">
-        <v>2544.2</v>
+        <v>13243.3</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U111" t="n">
-        <v>32450</v>
+        <v>36850</v>
       </c>
       <c r="V111" t="n">
-        <v>32850</v>
+        <v>35750</v>
       </c>
       <c r="W111" t="n">
-        <v>-1.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>035900</t>
+          <t>035760</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JYP Ent.</t>
+          <t>CJ ENM</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8010,54 +7989,54 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>449</v>
+        <v>303</v>
       </c>
       <c r="L112" t="n">
-        <v>1529.1</v>
+        <v>1324.4</v>
       </c>
       <c r="M112" t="n">
-        <v>1529.1</v>
+        <v>1324.4</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>1681.4</v>
+        <v>2114.6</v>
       </c>
       <c r="P112" t="n">
-        <v>1681.4</v>
+        <v>2114.6</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>1679.3</v>
+        <v>2544.2</v>
       </c>
       <c r="S112" t="n">
-        <v>1679.3</v>
+        <v>2544.2</v>
       </c>
       <c r="T112" t="n">
         <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>39650</v>
+        <v>32850</v>
       </c>
       <c r="V112" t="n">
-        <v>39550</v>
+        <v>32850</v>
       </c>
       <c r="W112" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>036200</t>
+          <t>035900</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>유니셈</t>
+          <t>JYP Ent.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8067,7 +8046,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8076,126 +8055,120 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>91</v>
+        <v>449</v>
       </c>
       <c r="L113" t="n">
-        <v>280</v>
+        <v>1529.1</v>
       </c>
       <c r="M113" t="n">
-        <v>280</v>
+        <v>1529.1</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>422</v>
+        <v>1681.4</v>
       </c>
       <c r="P113" t="n">
-        <v>422</v>
+        <v>1681.4</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>502</v>
+        <v>1679.3</v>
       </c>
       <c r="S113" t="n">
-        <v>502</v>
+        <v>1679.3</v>
       </c>
       <c r="T113" t="n">
         <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>9050</v>
+        <v>40100</v>
       </c>
       <c r="V113" t="n">
-        <v>8830</v>
+        <v>39550</v>
       </c>
       <c r="W113" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>036460</t>
+          <t>036200</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>유니셈</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>유틸리티</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>4308</v>
-      </c>
-      <c r="G114" t="n">
-        <v>4308</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="L114" t="n">
-        <v>24950.4</v>
+        <v>280</v>
       </c>
       <c r="M114" t="n">
-        <v>24705.9</v>
+        <v>280</v>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>23724.1</v>
+        <v>422</v>
       </c>
       <c r="P114" t="n">
-        <v>23717</v>
+        <v>422</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>24366.8</v>
+        <v>502</v>
       </c>
       <c r="S114" t="n">
-        <v>24366.8</v>
+        <v>502</v>
       </c>
       <c r="T114" t="n">
         <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>36900</v>
+        <v>8870</v>
       </c>
       <c r="V114" t="n">
-        <v>36350</v>
+        <v>8830</v>
       </c>
       <c r="W114" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>036570</t>
+          <t>036460</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8205,129 +8178,135 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>유틸리티</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>947</v>
+        <v>4395</v>
+      </c>
+      <c r="G115" t="n">
+        <v>4308</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2</v>
       </c>
       <c r="L115" t="n">
-        <v>5265.5</v>
+        <v>25453.3</v>
       </c>
       <c r="M115" t="n">
-        <v>5232</v>
+        <v>24705.9</v>
       </c>
       <c r="N115" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>6026.1</v>
+        <v>24047.6</v>
       </c>
       <c r="P115" t="n">
-        <v>6075.7</v>
+        <v>23717</v>
       </c>
       <c r="Q115" t="n">
-        <v>-0.8</v>
+        <v>1.4</v>
       </c>
       <c r="R115" t="n">
-        <v>6071.2</v>
+        <v>24802</v>
       </c>
       <c r="S115" t="n">
-        <v>6167.6</v>
+        <v>24366.8</v>
       </c>
       <c r="T115" t="n">
-        <v>-1.6</v>
+        <v>1.8</v>
       </c>
       <c r="U115" t="n">
-        <v>222000</v>
+        <v>37100</v>
       </c>
       <c r="V115" t="n">
-        <v>225500</v>
+        <v>36350</v>
       </c>
       <c r="W115" t="n">
-        <v>-1.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>036570</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>KOSDAQ50,커버리지</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>213</v>
+        <v>901</v>
       </c>
       <c r="L116" t="n">
-        <v>483.5</v>
+        <v>5178.2</v>
       </c>
       <c r="M116" t="n">
-        <v>559</v>
+        <v>5232</v>
       </c>
       <c r="N116" t="n">
-        <v>-13.5</v>
+        <v>-1</v>
       </c>
       <c r="O116" t="n">
-        <v>1371.5</v>
+        <v>5983</v>
       </c>
       <c r="P116" t="n">
-        <v>1342</v>
+        <v>6075.7</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.2</v>
+        <v>-1.5</v>
       </c>
       <c r="R116" t="n">
-        <v>2472</v>
+        <v>6107.6</v>
       </c>
       <c r="S116" t="n">
-        <v>1780</v>
+        <v>6167.6</v>
       </c>
       <c r="T116" t="n">
-        <v>38.9</v>
+        <v>-1</v>
       </c>
       <c r="U116" t="n">
-        <v>178500</v>
+        <v>225000</v>
       </c>
       <c r="V116" t="n">
-        <v>167100</v>
+        <v>225500</v>
       </c>
       <c r="W116" t="n">
-        <v>6.8</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>039030</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8342,130 +8321,124 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>KOSDAQ50,커버리지</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>349</v>
+        <v>213</v>
       </c>
       <c r="L117" t="n">
-        <v>1332</v>
+        <v>483.5</v>
       </c>
       <c r="M117" t="n">
-        <v>1332</v>
+        <v>559</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>-13.5</v>
       </c>
       <c r="O117" t="n">
-        <v>2143.5</v>
+        <v>1371.5</v>
       </c>
       <c r="P117" t="n">
-        <v>2143.5</v>
+        <v>1342</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R117" t="n">
-        <v>2373</v>
+        <v>2472</v>
       </c>
       <c r="S117" t="n">
-        <v>2373</v>
+        <v>1780</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>38.9</v>
       </c>
       <c r="U117" t="n">
-        <v>404000</v>
+        <v>176800</v>
       </c>
       <c r="V117" t="n">
-        <v>388500</v>
+        <v>167100</v>
       </c>
       <c r="W117" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>039130</t>
+          <t>039030</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>하나투어</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>레저/카지노/면세</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>97</v>
-      </c>
-      <c r="G118" t="n">
-        <v>97</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="L118" t="n">
-        <v>507.8</v>
+        <v>1332</v>
       </c>
       <c r="M118" t="n">
-        <v>507.8</v>
+        <v>1332</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>651.2</v>
+        <v>2143.5</v>
       </c>
       <c r="P118" t="n">
-        <v>651.2</v>
+        <v>2143.5</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>723.5</v>
+        <v>2373</v>
       </c>
       <c r="S118" t="n">
-        <v>723.5</v>
+        <v>2373</v>
       </c>
       <c r="T118" t="n">
         <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>32100</v>
+        <v>398500</v>
       </c>
       <c r="V118" t="n">
-        <v>32000</v>
+        <v>388500</v>
       </c>
       <c r="W118" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>039490</t>
+          <t>039130</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>키움증권</t>
+          <t>하나투어</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8475,132 +8448,132 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>금융-증권</t>
+          <t>레저/카지노/면세</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
-        </is>
+          <t>커버리지</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>97</v>
+      </c>
+      <c r="G119" t="n">
+        <v>97</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>23068.3</v>
+        <v>507.8</v>
       </c>
       <c r="M119" t="n">
-        <v>23068.3</v>
+        <v>507.8</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>19332.1</v>
+        <v>651.2</v>
       </c>
       <c r="P119" t="n">
-        <v>19332.1</v>
+        <v>651.2</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>19518.9</v>
+        <v>723.5</v>
       </c>
       <c r="S119" t="n">
-        <v>19518.9</v>
+        <v>723.5</v>
       </c>
       <c r="T119" t="n">
         <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>277500</v>
+        <v>32900</v>
       </c>
       <c r="V119" t="n">
-        <v>266000</v>
+        <v>32000</v>
       </c>
       <c r="W119" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>039840</t>
+          <t>039490</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>디오</t>
+          <t>키움증권</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>의료기기</t>
+          <t>금융-증권</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>커버리지</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>63</v>
-      </c>
-      <c r="G120" t="n">
-        <v>63</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
+          <t>KOSPI200</t>
+        </is>
       </c>
       <c r="L120" t="n">
-        <v>233.3</v>
+        <v>23068.3</v>
       </c>
       <c r="M120" t="n">
-        <v>233.3</v>
+        <v>23068.3</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>296</v>
+        <v>19332.1</v>
       </c>
       <c r="P120" t="n">
-        <v>296</v>
+        <v>19332.1</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>350</v>
+        <v>19518.9</v>
       </c>
       <c r="S120" t="n">
-        <v>350</v>
+        <v>19518.9</v>
       </c>
       <c r="T120" t="n">
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>10720</v>
+        <v>278500</v>
       </c>
       <c r="V120" t="n">
-        <v>11200</v>
+        <v>266000</v>
       </c>
       <c r="W120" t="n">
-        <v>-4.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>041510</t>
+          <t>039840</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>에스엠</t>
+          <t>디오</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8610,7 +8583,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>엔터</t>
+          <t>의료기기</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8619,126 +8592,126 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>397</v>
+        <v>63</v>
+      </c>
+      <c r="G121" t="n">
+        <v>63</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>1886.6</v>
+        <v>233.3</v>
       </c>
       <c r="M121" t="n">
-        <v>1886.6</v>
+        <v>233.3</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>2167.6</v>
+        <v>296</v>
       </c>
       <c r="P121" t="n">
-        <v>2167.6</v>
+        <v>296</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2421.2</v>
+        <v>350</v>
       </c>
       <c r="S121" t="n">
-        <v>2421.2</v>
+        <v>350</v>
       </c>
       <c r="T121" t="n">
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>74400</v>
+        <v>11100</v>
       </c>
       <c r="V121" t="n">
-        <v>72000</v>
+        <v>11200</v>
       </c>
       <c r="W121" t="n">
-        <v>3.3</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>042660</t>
+          <t>041510</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>에스엠</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>엔터</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>5706</v>
-      </c>
-      <c r="G122" t="n">
-        <v>5706</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="L122" t="n">
-        <v>22530</v>
+        <v>1886.6</v>
       </c>
       <c r="M122" t="n">
-        <v>22530</v>
+        <v>1886.6</v>
       </c>
       <c r="N122" t="n">
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>25170.9</v>
+        <v>2167.6</v>
       </c>
       <c r="P122" t="n">
-        <v>25170.9</v>
+        <v>2167.6</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>28602</v>
+        <v>2421.2</v>
       </c>
       <c r="S122" t="n">
-        <v>28602</v>
+        <v>2421.2</v>
       </c>
       <c r="T122" t="n">
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>89300</v>
+        <v>75800</v>
       </c>
       <c r="V122" t="n">
-        <v>83000</v>
+        <v>72000</v>
       </c>
       <c r="W122" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>042700</t>
+          <t>042660</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>한미반도체</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8748,69 +8721,69 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1291</v>
+        <v>5706</v>
       </c>
       <c r="G123" t="n">
-        <v>1291</v>
+        <v>5706</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>3822</v>
+        <v>22530</v>
       </c>
       <c r="M123" t="n">
-        <v>3822</v>
+        <v>22530</v>
       </c>
       <c r="N123" t="n">
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>5617</v>
+        <v>25170.9</v>
       </c>
       <c r="P123" t="n">
-        <v>5617</v>
+        <v>25170.9</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>6843</v>
+        <v>28602</v>
       </c>
       <c r="S123" t="n">
-        <v>6843</v>
+        <v>28602</v>
       </c>
       <c r="T123" t="n">
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>222500</v>
+        <v>88500</v>
       </c>
       <c r="V123" t="n">
-        <v>209500</v>
+        <v>83000</v>
       </c>
       <c r="W123" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042700</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8820,69 +8793,69 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1671</v>
+        <v>1291</v>
       </c>
       <c r="G124" t="n">
-        <v>1677</v>
+        <v>1291</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>8310</v>
+        <v>3822</v>
       </c>
       <c r="M124" t="n">
-        <v>8314.700000000001</v>
+        <v>3822</v>
       </c>
       <c r="N124" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>8159.2</v>
+        <v>5617</v>
       </c>
       <c r="P124" t="n">
-        <v>8149.7</v>
+        <v>5617</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>9186.4</v>
+        <v>6843</v>
       </c>
       <c r="S124" t="n">
-        <v>9186.4</v>
+        <v>6843</v>
       </c>
       <c r="T124" t="n">
         <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>20150</v>
+        <v>219500</v>
       </c>
       <c r="V124" t="n">
-        <v>15640</v>
+        <v>209500</v>
       </c>
       <c r="W124" t="n">
-        <v>28.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>047050</t>
+          <t>047040</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>포스코인터내셔널</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8892,7 +8865,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>철강·비철</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8901,60 +8874,60 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>3776</v>
+        <v>1671</v>
       </c>
       <c r="G125" t="n">
-        <v>3776</v>
+        <v>1677</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="L125" t="n">
-        <v>14688.2</v>
+        <v>8310</v>
       </c>
       <c r="M125" t="n">
-        <v>14688.2</v>
+        <v>8314.700000000001</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O125" t="n">
-        <v>15554.8</v>
+        <v>8159.2</v>
       </c>
       <c r="P125" t="n">
-        <v>15554.8</v>
+        <v>8149.7</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R125" t="n">
-        <v>16386.5</v>
+        <v>9186.4</v>
       </c>
       <c r="S125" t="n">
-        <v>16386.5</v>
+        <v>9186.4</v>
       </c>
       <c r="T125" t="n">
         <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>52200</v>
+        <v>19690</v>
       </c>
       <c r="V125" t="n">
-        <v>53400</v>
+        <v>15640</v>
       </c>
       <c r="W125" t="n">
-        <v>-2.2</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>047810</t>
+          <t>047050</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한국항공우주</t>
+          <t>포스코인터내셔널</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8964,7 +8937,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>방산·항공우주</t>
+          <t>철강·비철</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8973,195 +8946,195 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>895</v>
+        <v>3776</v>
       </c>
       <c r="G126" t="n">
-        <v>895</v>
+        <v>3776</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>3569.9</v>
+        <v>14688.2</v>
       </c>
       <c r="M126" t="n">
-        <v>3653.6</v>
+        <v>14688.2</v>
       </c>
       <c r="N126" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>5910.1</v>
+        <v>15554.8</v>
       </c>
       <c r="P126" t="n">
-        <v>5956.6</v>
+        <v>15554.8</v>
       </c>
       <c r="Q126" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>7433.4</v>
+        <v>16386.5</v>
       </c>
       <c r="S126" t="n">
-        <v>7433.4</v>
+        <v>16386.5</v>
       </c>
       <c r="T126" t="n">
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>137100</v>
+        <v>52700</v>
       </c>
       <c r="V126" t="n">
-        <v>129600</v>
+        <v>53400</v>
       </c>
       <c r="W126" t="n">
-        <v>5.8</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>051500</t>
+          <t>047810</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CJ프레시웨이</t>
+          <t>한국항공우주</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>음식료</t>
+          <t>방산·항공우주</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>커버리지</t>
-        </is>
+          <t>KOSPI200,커버리지</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>895</v>
+      </c>
+      <c r="G127" t="n">
+        <v>895</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>1019.8</v>
+        <v>3569.9</v>
       </c>
       <c r="M127" t="n">
-        <v>1019.8</v>
+        <v>3653.6</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="O127" t="n">
-        <v>1160</v>
+        <v>5910.1</v>
       </c>
       <c r="P127" t="n">
-        <v>1160</v>
+        <v>5956.6</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="R127" t="n">
-        <v>1290.5</v>
+        <v>7433.4</v>
       </c>
       <c r="S127" t="n">
-        <v>1290.5</v>
+        <v>7433.4</v>
       </c>
       <c r="T127" t="n">
         <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>23850</v>
+        <v>133100</v>
       </c>
       <c r="V127" t="n">
-        <v>24000</v>
+        <v>129600</v>
       </c>
       <c r="W127" t="n">
-        <v>-0.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>051600</t>
+          <t>051500</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>한전KPS</t>
+          <t>CJ프레시웨이</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>유틸리티</t>
+          <t>음식료</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>475</v>
-      </c>
-      <c r="G128" t="n">
-        <v>475</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
+          <t>커버리지</t>
+        </is>
       </c>
       <c r="L128" t="n">
-        <v>1768.5</v>
+        <v>1019.8</v>
       </c>
       <c r="M128" t="n">
-        <v>1771.4</v>
+        <v>1019.8</v>
       </c>
       <c r="N128" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>1947</v>
+        <v>1160</v>
       </c>
       <c r="P128" t="n">
-        <v>1937.7</v>
+        <v>1160</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2016.2</v>
+        <v>1290.5</v>
       </c>
       <c r="S128" t="n">
-        <v>2009.8</v>
+        <v>1290.5</v>
       </c>
       <c r="T128" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>46900</v>
+        <v>24200</v>
       </c>
       <c r="V128" t="n">
-        <v>43900</v>
+        <v>24000</v>
       </c>
       <c r="W128" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>051900</t>
+          <t>051600</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LG생활건강</t>
+          <t>한전KPS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9171,7 +9144,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>유틸리티</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9180,54 +9153,60 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1119</v>
+        <v>476</v>
+      </c>
+      <c r="G129" t="n">
+        <v>475</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.2</v>
       </c>
       <c r="L129" t="n">
-        <v>3796.2</v>
+        <v>1757.4</v>
       </c>
       <c r="M129" t="n">
-        <v>3781.2</v>
+        <v>1771.4</v>
       </c>
       <c r="N129" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="O129" t="n">
-        <v>4488.2</v>
+        <v>1935.7</v>
       </c>
       <c r="P129" t="n">
-        <v>4481.1</v>
+        <v>1937.7</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="R129" t="n">
-        <v>4941.1</v>
+        <v>2010.8</v>
       </c>
       <c r="S129" t="n">
-        <v>4923.4</v>
+        <v>2009.8</v>
       </c>
       <c r="T129" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
-        <v>296500</v>
+        <v>47050</v>
       </c>
       <c r="V129" t="n">
-        <v>317000</v>
+        <v>43900</v>
       </c>
       <c r="W129" t="n">
-        <v>-6.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>051910</t>
+          <t>051900</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LG화학</t>
+          <t>LG생활건강</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9237,7 +9216,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>정유·화학</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9246,54 +9225,54 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>2233</v>
+        <v>1119</v>
       </c>
       <c r="L130" t="n">
-        <v>13021.5</v>
+        <v>3796.2</v>
       </c>
       <c r="M130" t="n">
-        <v>13021.5</v>
+        <v>3781.2</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O130" t="n">
-        <v>39507.7</v>
+        <v>4488.2</v>
       </c>
       <c r="P130" t="n">
-        <v>39507.7</v>
+        <v>4481.1</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R130" t="n">
-        <v>55674.8</v>
+        <v>4941.1</v>
       </c>
       <c r="S130" t="n">
-        <v>55674.8</v>
+        <v>4923.4</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U130" t="n">
-        <v>275500</v>
+        <v>318000</v>
       </c>
       <c r="V130" t="n">
-        <v>270000</v>
+        <v>317000</v>
       </c>
       <c r="W130" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>051910</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>LG화학</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9303,7 +9282,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>유틸리티</t>
+          <t>정유·화학</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9312,60 +9291,54 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>154</v>
-      </c>
-      <c r="G131" t="n">
-        <v>154</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
+        <v>2233</v>
       </c>
       <c r="L131" t="n">
-        <v>646</v>
+        <v>13021.5</v>
       </c>
       <c r="M131" t="n">
-        <v>660</v>
+        <v>13021.5</v>
       </c>
       <c r="N131" t="n">
-        <v>-2.1</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>949.6</v>
+        <v>39507.7</v>
       </c>
       <c r="P131" t="n">
-        <v>963.6</v>
+        <v>39507.7</v>
       </c>
       <c r="Q131" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>1513.1</v>
+        <v>55674.8</v>
       </c>
       <c r="S131" t="n">
-        <v>1482.1</v>
+        <v>55674.8</v>
       </c>
       <c r="T131" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>123000</v>
+        <v>277000</v>
       </c>
       <c r="V131" t="n">
-        <v>89700</v>
+        <v>270000</v>
       </c>
       <c r="W131" t="n">
-        <v>37.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>055550</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9375,7 +9348,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>금융-은행지주</t>
+          <t>유틸리티</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9383,124 +9356,124 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F132" t="n">
+        <v>154</v>
+      </c>
+      <c r="G132" t="n">
+        <v>154</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
       <c r="L132" t="n">
-        <v>80829.8</v>
+        <v>646</v>
       </c>
       <c r="M132" t="n">
-        <v>80829.8</v>
+        <v>660</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="O132" t="n">
-        <v>84632.8</v>
+        <v>949.6</v>
       </c>
       <c r="P132" t="n">
-        <v>84632.8</v>
+        <v>963.6</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="R132" t="n">
-        <v>87826.2</v>
+        <v>1513.1</v>
       </c>
       <c r="S132" t="n">
-        <v>87826.2</v>
+        <v>1482.1</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U132" t="n">
-        <v>108000</v>
+        <v>122400</v>
       </c>
       <c r="V132" t="n">
-        <v>103600</v>
+        <v>89700</v>
       </c>
       <c r="W132" t="n">
-        <v>4.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>058470</t>
+          <t>055550</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>금융-은행지주</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>558</v>
-      </c>
-      <c r="G133" t="n">
-        <v>558</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
+          <t>KOSPI200</t>
+        </is>
       </c>
       <c r="L133" t="n">
-        <v>2226.2</v>
+        <v>80829.8</v>
       </c>
       <c r="M133" t="n">
-        <v>2226.2</v>
+        <v>80829.8</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>2636.2</v>
+        <v>84632.8</v>
       </c>
       <c r="P133" t="n">
-        <v>2612.3</v>
+        <v>84632.8</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3057.3</v>
+        <v>87826.2</v>
       </c>
       <c r="S133" t="n">
-        <v>3077.7</v>
+        <v>87826.2</v>
       </c>
       <c r="T133" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>66400</v>
+        <v>109700</v>
       </c>
       <c r="V133" t="n">
-        <v>64700</v>
+        <v>103600</v>
       </c>
       <c r="W133" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>058610</t>
+          <t>058470</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9510,60 +9483,69 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KOSDAQ50,커버리지</t>
-        </is>
+          <t>KOSDAQ50</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>545</v>
+      </c>
+      <c r="G134" t="n">
+        <v>558</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-2.3</v>
       </c>
       <c r="L134" t="n">
-        <v>212.2</v>
+        <v>2229.7</v>
       </c>
       <c r="M134" t="n">
-        <v>224.8</v>
+        <v>2226.2</v>
       </c>
       <c r="N134" t="n">
-        <v>-5.6</v>
+        <v>0.2</v>
       </c>
       <c r="O134" t="n">
-        <v>283.2</v>
+        <v>2630.3</v>
       </c>
       <c r="P134" t="n">
-        <v>309</v>
+        <v>2612.3</v>
       </c>
       <c r="Q134" t="n">
-        <v>-8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="R134" t="n">
-        <v>343.2</v>
+        <v>3057.3</v>
       </c>
       <c r="S134" t="n">
-        <v>374</v>
+        <v>3077.7</v>
       </c>
       <c r="T134" t="n">
-        <v>-8.199999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="U134" t="n">
-        <v>94100</v>
+        <v>66800</v>
       </c>
       <c r="V134" t="n">
-        <v>93700</v>
+        <v>64700</v>
       </c>
       <c r="W134" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>060370</t>
+          <t>058610</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LS마린솔루션</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9573,25 +9555,49 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>로봇</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>KOSDAQ50,커버리지</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>213</v>
+        <v>212.2</v>
+      </c>
+      <c r="M135" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-5.6</v>
       </c>
       <c r="O135" t="n">
-        <v>661</v>
+        <v>283.2</v>
+      </c>
+      <c r="P135" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>-8.300000000000001</v>
       </c>
       <c r="R135" t="n">
-        <v>931</v>
+        <v>343.2</v>
+      </c>
+      <c r="S135" t="n">
+        <v>374</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-8.199999999999999</v>
       </c>
       <c r="U135" t="n">
-        <v>34250</v>
+        <v>92700</v>
+      </c>
+      <c r="V135" t="n">
+        <v>93700</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="136">
@@ -9648,13 +9654,13 @@
         <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>39500</v>
+        <v>40500</v>
       </c>
       <c r="V136" t="n">
         <v>39500</v>
       </c>
       <c r="W136" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="137">
@@ -9714,13 +9720,13 @@
         <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>198200</v>
+        <v>202500</v>
       </c>
       <c r="V137" t="n">
         <v>164900</v>
       </c>
       <c r="W137" t="n">
-        <v>20.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="138">
@@ -9777,22 +9783,22 @@
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>16810.8</v>
+        <v>16849.6</v>
       </c>
       <c r="S138" t="n">
         <v>16810.8</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U138" t="n">
-        <v>137800</v>
+        <v>139100</v>
       </c>
       <c r="V138" t="n">
         <v>133400</v>
       </c>
       <c r="W138" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="139">
@@ -9858,13 +9864,13 @@
         <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>74600</v>
+        <v>75800</v>
       </c>
       <c r="V139" t="n">
         <v>71900</v>
       </c>
       <c r="W139" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="140">
@@ -9924,13 +9930,13 @@
         <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>242000</v>
+        <v>238500</v>
       </c>
       <c r="V140" t="n">
         <v>227500</v>
       </c>
       <c r="W140" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="141">
@@ -9996,13 +10002,13 @@
         <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>25700</v>
+        <v>25850</v>
       </c>
       <c r="V141" t="n">
         <v>26450</v>
       </c>
       <c r="W141" t="n">
-        <v>-2.8</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="142">
@@ -10068,13 +10074,13 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>199000</v>
+        <v>201500</v>
       </c>
       <c r="V142" t="n">
         <v>199100</v>
       </c>
       <c r="W142" t="n">
-        <v>-0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="143">
@@ -10104,49 +10110,49 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G143" t="n">
         <v>366</v>
       </c>
       <c r="H143" t="n">
-        <v>-4.1</v>
+        <v>-4.6</v>
       </c>
       <c r="L143" t="n">
-        <v>2218.2</v>
+        <v>2208.3</v>
       </c>
       <c r="M143" t="n">
         <v>2315.3</v>
       </c>
       <c r="N143" t="n">
-        <v>-4.2</v>
+        <v>-4.6</v>
       </c>
       <c r="O143" t="n">
-        <v>2448.6</v>
+        <v>2380.1</v>
       </c>
       <c r="P143" t="n">
         <v>2424.5</v>
       </c>
       <c r="Q143" t="n">
-        <v>1</v>
+        <v>-1.8</v>
       </c>
       <c r="R143" t="n">
-        <v>3271</v>
+        <v>3179.8</v>
       </c>
       <c r="S143" t="n">
         <v>3313.1</v>
       </c>
       <c r="T143" t="n">
-        <v>-1.3</v>
+        <v>-4</v>
       </c>
       <c r="U143" t="n">
-        <v>130800</v>
+        <v>134800</v>
       </c>
       <c r="V143" t="n">
         <v>122500</v>
       </c>
       <c r="W143" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
@@ -10206,13 +10212,13 @@
         <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>38200</v>
+        <v>39500</v>
       </c>
       <c r="V144" t="n">
         <v>38100</v>
       </c>
       <c r="W144" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="145">
@@ -10272,13 +10278,13 @@
         <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>38600</v>
+        <v>35350</v>
       </c>
       <c r="V145" t="n">
         <v>34350</v>
       </c>
       <c r="W145" t="n">
-        <v>12.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="146">
@@ -10320,13 +10326,13 @@
         <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>21963.4</v>
+        <v>22666.6</v>
       </c>
       <c r="P146" t="n">
         <v>21963.4</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R146" t="n">
         <v>25636.6</v>
@@ -10338,13 +10344,13 @@
         <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>191100</v>
+        <v>190700</v>
       </c>
       <c r="V146" t="n">
         <v>193700</v>
       </c>
       <c r="W146" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="147">
@@ -10410,13 +10416,13 @@
         <v>7.3</v>
       </c>
       <c r="U147" t="n">
-        <v>16130</v>
+        <v>16390</v>
       </c>
       <c r="V147" t="n">
         <v>15940</v>
       </c>
       <c r="W147" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="148">
@@ -10482,13 +10488,13 @@
         <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>124600</v>
+        <v>128800</v>
       </c>
       <c r="V148" t="n">
         <v>124500</v>
       </c>
       <c r="W148" t="n">
-        <v>0.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="149">
@@ -10554,13 +10560,13 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>94900</v>
+        <v>93400</v>
       </c>
       <c r="V149" t="n">
         <v>93500</v>
       </c>
       <c r="W149" t="n">
-        <v>1.5</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="150">
@@ -10617,13 +10623,13 @@
         <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>189800</v>
+        <v>191300</v>
       </c>
       <c r="V150" t="n">
         <v>183100</v>
       </c>
       <c r="W150" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="151">
@@ -10689,13 +10695,13 @@
         <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>73900</v>
+        <v>74800</v>
       </c>
       <c r="V151" t="n">
         <v>72600</v>
       </c>
       <c r="W151" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -10761,13 +10767,13 @@
         <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>53300</v>
+        <v>53100</v>
       </c>
       <c r="V152" t="n">
         <v>50100</v>
       </c>
       <c r="W152" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153">
@@ -10833,13 +10839,13 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>7110</v>
+        <v>7360</v>
       </c>
       <c r="V153" t="n">
         <v>7160</v>
       </c>
       <c r="W153" t="n">
-        <v>-0.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="154">
@@ -10878,13 +10884,13 @@
         <v>-0.9</v>
       </c>
       <c r="U154" t="n">
-        <v>9940</v>
+        <v>9850</v>
       </c>
       <c r="V154" t="n">
         <v>9430</v>
       </c>
       <c r="W154" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="155">
@@ -10950,13 +10956,13 @@
         <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>26250</v>
+        <v>25300</v>
       </c>
       <c r="V155" t="n">
         <v>23400</v>
       </c>
       <c r="W155" t="n">
-        <v>12.2</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="156">
@@ -11022,13 +11028,13 @@
         <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>122900</v>
+        <v>129200</v>
       </c>
       <c r="V156" t="n">
         <v>114600</v>
       </c>
       <c r="W156" t="n">
-        <v>7.2</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="157">
@@ -11088,13 +11094,13 @@
         <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>747000</v>
+        <v>734000</v>
       </c>
       <c r="V157" t="n">
         <v>712000</v>
       </c>
       <c r="W157" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="158">
@@ -11160,13 +11166,13 @@
         <v>-0.5</v>
       </c>
       <c r="U158" t="n">
-        <v>40700</v>
+        <v>41350</v>
       </c>
       <c r="V158" t="n">
         <v>42150</v>
       </c>
       <c r="W158" t="n">
-        <v>-3.4</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="159">
@@ -11226,13 +11232,13 @@
         <v>1.9</v>
       </c>
       <c r="U159" t="n">
-        <v>48150</v>
+        <v>48250</v>
       </c>
       <c r="V159" t="n">
         <v>45050</v>
       </c>
       <c r="W159" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="160">
@@ -11292,13 +11298,13 @@
         <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>64100</v>
+        <v>65400</v>
       </c>
       <c r="V160" t="n">
         <v>55900</v>
       </c>
       <c r="W160" t="n">
-        <v>14.7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161">
@@ -11358,13 +11364,13 @@
         <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>137200</v>
+        <v>134000</v>
       </c>
       <c r="V161" t="n">
         <v>136300</v>
       </c>
       <c r="W161" t="n">
-        <v>0.7</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="162">
@@ -11430,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="U162" t="n">
-        <v>203500</v>
+        <v>205000</v>
       </c>
       <c r="V162" t="n">
         <v>198600</v>
       </c>
       <c r="W162" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="163">
@@ -11493,13 +11499,13 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>132900</v>
+        <v>136000</v>
       </c>
       <c r="V163" t="n">
         <v>127900</v>
       </c>
       <c r="W163" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="164">
@@ -11556,13 +11562,13 @@
         <v>0</v>
       </c>
       <c r="U164" t="n">
-        <v>5480</v>
+        <v>5950</v>
       </c>
       <c r="V164" t="n">
         <v>5230</v>
       </c>
       <c r="W164" t="n">
-        <v>4.8</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="165">
@@ -11622,13 +11628,13 @@
         <v>0</v>
       </c>
       <c r="U165" t="n">
-        <v>47150</v>
+        <v>47700</v>
       </c>
       <c r="V165" t="n">
         <v>46100</v>
       </c>
       <c r="W165" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="166">
@@ -11694,13 +11700,13 @@
         <v>0</v>
       </c>
       <c r="U166" t="n">
-        <v>60200</v>
+        <v>58000</v>
       </c>
       <c r="V166" t="n">
         <v>58400</v>
       </c>
       <c r="W166" t="n">
-        <v>3.1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="167">
@@ -11760,13 +11766,13 @@
         <v>0.4</v>
       </c>
       <c r="U167" t="n">
-        <v>142200</v>
+        <v>150600</v>
       </c>
       <c r="V167" t="n">
         <v>139100</v>
       </c>
       <c r="W167" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -11805,13 +11811,13 @@
         <v>0</v>
       </c>
       <c r="U168" t="n">
-        <v>13070</v>
+        <v>12520</v>
       </c>
       <c r="V168" t="n">
         <v>12180</v>
       </c>
       <c r="W168" t="n">
-        <v>7.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="169">
@@ -11868,13 +11874,13 @@
         <v>0</v>
       </c>
       <c r="U169" t="n">
-        <v>171300</v>
+        <v>173400</v>
       </c>
       <c r="V169" t="n">
         <v>153400</v>
       </c>
       <c r="W169" t="n">
-        <v>11.7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
@@ -11940,13 +11946,13 @@
         <v>0</v>
       </c>
       <c r="U170" t="n">
-        <v>146300</v>
+        <v>142700</v>
       </c>
       <c r="V170" t="n">
         <v>133500</v>
       </c>
       <c r="W170" t="n">
-        <v>9.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="171">
@@ -12006,13 +12012,13 @@
         <v>0</v>
       </c>
       <c r="U171" t="n">
-        <v>17950</v>
+        <v>18470</v>
       </c>
       <c r="V171" t="n">
         <v>18200</v>
       </c>
       <c r="W171" t="n">
-        <v>-1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="172">
@@ -12038,7 +12044,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSDAQ50,커버리지</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -12072,13 +12078,13 @@
         <v>0</v>
       </c>
       <c r="U172" t="n">
-        <v>31750</v>
+        <v>35650</v>
       </c>
       <c r="V172" t="n">
         <v>32050</v>
       </c>
       <c r="W172" t="n">
-        <v>-0.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="173">
@@ -12108,43 +12114,43 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>16575</v>
+        <v>17066</v>
       </c>
       <c r="L173" t="n">
-        <v>86805.7</v>
+        <v>87325.3</v>
       </c>
       <c r="M173" t="n">
         <v>84273.89999999999</v>
       </c>
       <c r="N173" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="O173" t="n">
-        <v>42690.8</v>
+        <v>45473.2</v>
       </c>
       <c r="P173" t="n">
         <v>41287.8</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="R173" t="n">
-        <v>43216.7</v>
+        <v>43849.8</v>
       </c>
       <c r="S173" t="n">
         <v>43216.7</v>
       </c>
       <c r="T173" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U173" t="n">
-        <v>111900</v>
+        <v>116900</v>
       </c>
       <c r="V173" t="n">
         <v>129100</v>
       </c>
       <c r="W173" t="n">
-        <v>-13.3</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="174">
@@ -12210,13 +12216,13 @@
         <v>0</v>
       </c>
       <c r="U174" t="n">
-        <v>186600</v>
+        <v>189300</v>
       </c>
       <c r="V174" t="n">
         <v>189800</v>
       </c>
       <c r="W174" t="n">
-        <v>-1.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="175">
@@ -12245,6 +12251,9 @@
           <t>커버리지</t>
         </is>
       </c>
+      <c r="F175" t="n">
+        <v>32</v>
+      </c>
       <c r="L175" t="n">
         <v>142.5</v>
       </c>
@@ -12273,13 +12282,13 @@
         <v>0</v>
       </c>
       <c r="U175" t="n">
-        <v>17750</v>
+        <v>18110</v>
       </c>
       <c r="V175" t="n">
         <v>17900</v>
       </c>
       <c r="W175" t="n">
-        <v>-0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="176">
@@ -12345,13 +12354,13 @@
         <v>0</v>
       </c>
       <c r="U176" t="n">
-        <v>74000</v>
+        <v>74500</v>
       </c>
       <c r="V176" t="n">
         <v>70500</v>
       </c>
       <c r="W176" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="177">
@@ -12411,13 +12420,13 @@
         <v>0</v>
       </c>
       <c r="U177" t="n">
-        <v>83200</v>
+        <v>86400</v>
       </c>
       <c r="V177" t="n">
         <v>81900</v>
       </c>
       <c r="W177" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="178">
@@ -12474,13 +12483,13 @@
         <v>0</v>
       </c>
       <c r="U178" t="n">
-        <v>168000</v>
+        <v>171600</v>
       </c>
       <c r="V178" t="n">
         <v>162500</v>
       </c>
       <c r="W178" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="179">
@@ -12509,6 +12518,9 @@
           <t>KOSDAQ50,커버리지</t>
         </is>
       </c>
+      <c r="F179" t="n">
+        <v>25</v>
+      </c>
       <c r="L179" t="n">
         <v>-22.9</v>
       </c>
@@ -12537,13 +12549,13 @@
         <v>-1.8</v>
       </c>
       <c r="U179" t="n">
-        <v>252500</v>
+        <v>242000</v>
       </c>
       <c r="V179" t="n">
         <v>245500</v>
       </c>
       <c r="W179" t="n">
-        <v>2.9</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="180">
@@ -12603,13 +12615,13 @@
         <v>2</v>
       </c>
       <c r="U180" t="n">
-        <v>73100</v>
+        <v>74300</v>
       </c>
       <c r="V180" t="n">
         <v>75400</v>
       </c>
       <c r="W180" t="n">
-        <v>-3.1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="181">
@@ -12639,49 +12651,49 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="G181" t="n">
         <v>825</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L181" t="n">
-        <v>3038.6</v>
+        <v>3043.4</v>
       </c>
       <c r="M181" t="n">
         <v>3038.6</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O181" t="n">
-        <v>3405.8</v>
+        <v>3380.8</v>
       </c>
       <c r="P181" t="n">
         <v>3405.8</v>
       </c>
       <c r="Q181" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="R181" t="n">
-        <v>2679.1</v>
+        <v>2642.8</v>
       </c>
       <c r="S181" t="n">
         <v>2679.1</v>
       </c>
       <c r="T181" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="U181" t="n">
-        <v>49700</v>
+        <v>49400</v>
       </c>
       <c r="V181" t="n">
         <v>46900</v>
       </c>
       <c r="W181" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="182">
@@ -12711,22 +12723,22 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G182" t="n">
         <v>193</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="U182" t="n">
-        <v>9240</v>
+        <v>9610</v>
       </c>
       <c r="V182" t="n">
         <v>9210</v>
       </c>
       <c r="W182" t="n">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="183">
@@ -12792,13 +12804,13 @@
         <v>-1.4</v>
       </c>
       <c r="U183" t="n">
-        <v>52900</v>
+        <v>56500</v>
       </c>
       <c r="V183" t="n">
         <v>50000</v>
       </c>
       <c r="W183" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184">
@@ -12827,6 +12839,9 @@
           <t>커버리지</t>
         </is>
       </c>
+      <c r="F184" t="n">
+        <v>216</v>
+      </c>
       <c r="L184" t="n">
         <v>773.6</v>
       </c>
@@ -12855,13 +12870,13 @@
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>39750</v>
+        <v>40450</v>
       </c>
       <c r="V184" t="n">
         <v>39350</v>
       </c>
       <c r="W184" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="185">
@@ -12891,43 +12906,43 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>764</v>
+        <v>916</v>
       </c>
       <c r="L185" t="n">
-        <v>3528.5</v>
+        <v>3667.8</v>
       </c>
       <c r="M185" t="n">
         <v>2979.1</v>
       </c>
       <c r="N185" t="n">
-        <v>18.4</v>
+        <v>23.1</v>
       </c>
       <c r="O185" t="n">
-        <v>3007.5</v>
+        <v>3096.4</v>
       </c>
       <c r="P185" t="n">
         <v>2880.7</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.4</v>
+        <v>7.5</v>
       </c>
       <c r="R185" t="n">
-        <v>3122.3</v>
+        <v>3116.8</v>
       </c>
       <c r="S185" t="n">
         <v>3117.6</v>
       </c>
       <c r="T185" t="n">
-        <v>0.2</v>
+        <v>-0</v>
       </c>
       <c r="U185" t="n">
-        <v>500000</v>
+        <v>509000</v>
       </c>
       <c r="V185" t="n">
         <v>540000</v>
       </c>
       <c r="W185" t="n">
-        <v>-7.4</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="186">
@@ -12987,13 +13002,13 @@
         <v>0</v>
       </c>
       <c r="U186" t="n">
-        <v>251500</v>
+        <v>238500</v>
       </c>
       <c r="V186" t="n">
         <v>245500</v>
       </c>
       <c r="W186" t="n">
-        <v>2.4</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="187">
@@ -13050,13 +13065,13 @@
         <v>0</v>
       </c>
       <c r="U187" t="n">
-        <v>118300</v>
+        <v>122000</v>
       </c>
       <c r="V187" t="n">
         <v>114800</v>
       </c>
       <c r="W187" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="188">
@@ -13113,13 +13128,13 @@
         <v>0</v>
       </c>
       <c r="U188" t="n">
-        <v>14860</v>
+        <v>15120</v>
       </c>
       <c r="V188" t="n">
         <v>14300</v>
       </c>
       <c r="W188" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="189">
@@ -13176,13 +13191,13 @@
         <v>0</v>
       </c>
       <c r="U189" t="n">
-        <v>17510</v>
+        <v>18120</v>
       </c>
       <c r="V189" t="n">
         <v>17100</v>
       </c>
       <c r="W189" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
@@ -13242,13 +13257,13 @@
         <v>0</v>
       </c>
       <c r="U190" t="n">
-        <v>73900</v>
+        <v>75100</v>
       </c>
       <c r="V190" t="n">
         <v>72600</v>
       </c>
       <c r="W190" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="191">
@@ -13277,6 +13292,9 @@
           <t>KOSDAQ50</t>
         </is>
       </c>
+      <c r="F191" t="n">
+        <v>186</v>
+      </c>
       <c r="L191" t="n">
         <v>501.9</v>
       </c>
@@ -13305,13 +13323,13 @@
         <v>-0.5</v>
       </c>
       <c r="U191" t="n">
-        <v>269500</v>
+        <v>271000</v>
       </c>
       <c r="V191" t="n">
         <v>265500</v>
       </c>
       <c r="W191" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="192">
@@ -13368,13 +13386,13 @@
         <v>0</v>
       </c>
       <c r="U192" t="n">
-        <v>99000</v>
+        <v>101000</v>
       </c>
       <c r="V192" t="n">
         <v>102500</v>
       </c>
       <c r="W192" t="n">
-        <v>-3.4</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="193">
@@ -13403,6 +13421,9 @@
           <t>KOSDAQ50,커버리지</t>
         </is>
       </c>
+      <c r="F193" t="n">
+        <v>549</v>
+      </c>
       <c r="L193" t="n">
         <v>2192.1</v>
       </c>
@@ -13431,13 +13452,13 @@
         <v>0</v>
       </c>
       <c r="U193" t="n">
-        <v>245000</v>
+        <v>259000</v>
       </c>
       <c r="V193" t="n">
         <v>252000</v>
       </c>
       <c r="W193" t="n">
-        <v>-2.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="194">
@@ -13503,13 +13524,13 @@
         <v>0</v>
       </c>
       <c r="U194" t="n">
-        <v>36950</v>
+        <v>38200</v>
       </c>
       <c r="V194" t="n">
         <v>36850</v>
       </c>
       <c r="W194" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="195">
@@ -13575,13 +13596,13 @@
         <v>0</v>
       </c>
       <c r="U195" t="n">
-        <v>65200</v>
+        <v>66400</v>
       </c>
       <c r="V195" t="n">
         <v>66400</v>
       </c>
       <c r="W195" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -13641,13 +13662,13 @@
         <v>0.4</v>
       </c>
       <c r="U196" t="n">
-        <v>145100</v>
+        <v>161700</v>
       </c>
       <c r="V196" t="n">
         <v>143300</v>
       </c>
       <c r="W196" t="n">
-        <v>1.3</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="197">
@@ -13707,13 +13728,13 @@
         <v>0</v>
       </c>
       <c r="U197" t="n">
-        <v>37650</v>
+        <v>38250</v>
       </c>
       <c r="V197" t="n">
         <v>37750</v>
       </c>
       <c r="W197" t="n">
-        <v>-0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="198">
@@ -13770,13 +13791,13 @@
         <v>0</v>
       </c>
       <c r="U198" t="n">
-        <v>27850</v>
+        <v>29050</v>
       </c>
       <c r="V198" t="n">
         <v>27250</v>
       </c>
       <c r="W198" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="199">
@@ -13805,41 +13826,44 @@
           <t>KOSDAQ50</t>
         </is>
       </c>
+      <c r="F199" t="n">
+        <v>483</v>
+      </c>
       <c r="L199" t="n">
-        <v>898.5</v>
+        <v>634.7</v>
       </c>
       <c r="M199" t="n">
         <v>898.5</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>-29.4</v>
       </c>
       <c r="O199" t="n">
-        <v>3371.5</v>
+        <v>2904</v>
       </c>
       <c r="P199" t="n">
         <v>3371.5</v>
       </c>
       <c r="Q199" t="n">
-        <v>0</v>
+        <v>-13.9</v>
       </c>
       <c r="R199" t="n">
-        <v>4450</v>
+        <v>3491.5</v>
       </c>
       <c r="S199" t="n">
         <v>4450</v>
       </c>
       <c r="T199" t="n">
-        <v>0</v>
+        <v>-21.5</v>
       </c>
       <c r="U199" t="n">
-        <v>41250</v>
+        <v>38950</v>
       </c>
       <c r="V199" t="n">
         <v>38200</v>
       </c>
       <c r="W199" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -13899,13 +13923,13 @@
         <v>-0.1</v>
       </c>
       <c r="U200" t="n">
-        <v>66900</v>
+        <v>68500</v>
       </c>
       <c r="V200" t="n">
         <v>68800</v>
       </c>
       <c r="W200" t="n">
-        <v>-2.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="201">
@@ -13934,6 +13958,9 @@
           <t>커버리지</t>
         </is>
       </c>
+      <c r="F201" t="n">
+        <v>79</v>
+      </c>
       <c r="L201" t="n">
         <v>366.4</v>
       </c>
@@ -13962,13 +13989,13 @@
         <v>0</v>
       </c>
       <c r="U201" t="n">
-        <v>65600</v>
+        <v>63800</v>
       </c>
       <c r="V201" t="n">
         <v>65600</v>
       </c>
       <c r="W201" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="202">
@@ -14034,13 +14061,13 @@
         <v>0</v>
       </c>
       <c r="U202" t="n">
-        <v>57100</v>
+        <v>59200</v>
       </c>
       <c r="V202" t="n">
         <v>58700</v>
       </c>
       <c r="W202" t="n">
-        <v>-2.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="203">
@@ -14106,13 +14133,13 @@
         <v>0.2</v>
       </c>
       <c r="U203" t="n">
-        <v>280500</v>
+        <v>303000</v>
       </c>
       <c r="V203" t="n">
         <v>287000</v>
       </c>
       <c r="W203" t="n">
-        <v>-2.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="204">
@@ -14172,13 +14199,13 @@
         <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>43000</v>
+        <v>43650</v>
       </c>
       <c r="V204" t="n">
         <v>44150</v>
       </c>
       <c r="W204" t="n">
-        <v>-2.6</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="205">
@@ -14207,6 +14234,9 @@
           <t>KOSDAQ50</t>
         </is>
       </c>
+      <c r="F205" t="n">
+        <v>659</v>
+      </c>
       <c r="L205" t="n">
         <v>2641.5</v>
       </c>
@@ -14235,13 +14265,13 @@
         <v>0</v>
       </c>
       <c r="U205" t="n">
-        <v>308500</v>
+        <v>320000</v>
       </c>
       <c r="V205" t="n">
         <v>320500</v>
       </c>
       <c r="W205" t="n">
-        <v>-3.7</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="206">
@@ -14379,13 +14409,13 @@
         <v>0</v>
       </c>
       <c r="U207" t="n">
-        <v>1588000</v>
+        <v>1486000</v>
       </c>
       <c r="V207" t="n">
         <v>1567000</v>
       </c>
       <c r="W207" t="n">
-        <v>1.3</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="208">
@@ -14414,41 +14444,44 @@
           <t>KOSDAQ50,커버리지</t>
         </is>
       </c>
+      <c r="F208" t="n">
+        <v>506</v>
+      </c>
       <c r="L208" t="n">
-        <v>1935.1</v>
+        <v>1924.8</v>
       </c>
       <c r="M208" t="n">
         <v>1935.1</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O208" t="n">
-        <v>2547</v>
+        <v>2548.9</v>
       </c>
       <c r="P208" t="n">
         <v>2547</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R208" t="n">
-        <v>3193.8</v>
+        <v>3206.6</v>
       </c>
       <c r="S208" t="n">
         <v>3193.8</v>
       </c>
       <c r="T208" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U208" t="n">
-        <v>32200</v>
+        <v>33250</v>
       </c>
       <c r="V208" t="n">
         <v>33300</v>
       </c>
       <c r="W208" t="n">
-        <v>-3.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="209">
@@ -14477,17 +14510,20 @@
           <t>KOSDAQ50,커버리지</t>
         </is>
       </c>
+      <c r="F209" t="n">
+        <v>732</v>
+      </c>
       <c r="L209" t="n">
-        <v>2714.2</v>
+        <v>2711.7</v>
       </c>
       <c r="M209" t="n">
         <v>2714.2</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="O209" t="n">
-        <v>3375.3</v>
+        <v>3375.5</v>
       </c>
       <c r="P209" t="n">
         <v>3375.3</v>
@@ -14496,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>4061.1</v>
+        <v>4062.4</v>
       </c>
       <c r="S209" t="n">
         <v>4061.1</v>
@@ -14505,13 +14541,13 @@
         <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>433500</v>
+        <v>461500</v>
       </c>
       <c r="V209" t="n">
         <v>416000</v>
       </c>
       <c r="W209" t="n">
-        <v>4.2</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="210">
@@ -14577,13 +14613,13 @@
         <v>0</v>
       </c>
       <c r="U210" t="n">
-        <v>48800</v>
+        <v>46800</v>
       </c>
       <c r="V210" t="n">
         <v>46350</v>
       </c>
       <c r="W210" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -14613,31 +14649,31 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="G211" t="n">
         <v>790</v>
       </c>
       <c r="H211" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="L211" t="n">
-        <v>2485.2</v>
+        <v>2537.6</v>
       </c>
       <c r="M211" t="n">
         <v>2453.7</v>
       </c>
       <c r="N211" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="O211" t="n">
-        <v>4156</v>
+        <v>4227.5</v>
       </c>
       <c r="P211" t="n">
         <v>4074.3</v>
       </c>
       <c r="Q211" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="R211" t="n">
         <v>5469.5</v>
@@ -14649,13 +14685,13 @@
         <v>6.1</v>
       </c>
       <c r="U211" t="n">
-        <v>125200</v>
+        <v>122800</v>
       </c>
       <c r="V211" t="n">
         <v>105500</v>
       </c>
       <c r="W211" t="n">
-        <v>18.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="212">
@@ -14712,13 +14748,13 @@
         <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>110000</v>
+        <v>110200</v>
       </c>
       <c r="V212" t="n">
         <v>110700</v>
       </c>
       <c r="W212" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="213">
@@ -14747,6 +14783,9 @@
           <t>KOSDAQ50</t>
         </is>
       </c>
+      <c r="F213" t="n">
+        <v>695</v>
+      </c>
       <c r="L213" t="n">
         <v>1838.7</v>
       </c>
@@ -14775,13 +14814,13 @@
         <v>0</v>
       </c>
       <c r="U213" t="n">
-        <v>112400</v>
+        <v>111100</v>
       </c>
       <c r="V213" t="n">
         <v>106800</v>
       </c>
       <c r="W213" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -14847,13 +14886,13 @@
         <v>0</v>
       </c>
       <c r="U214" t="n">
-        <v>61800</v>
+        <v>63100</v>
       </c>
       <c r="V214" t="n">
         <v>60000</v>
       </c>
       <c r="W214" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="215">
@@ -14882,6 +14921,9 @@
           <t>커버리지</t>
         </is>
       </c>
+      <c r="F215" t="n">
+        <v>331</v>
+      </c>
       <c r="L215" t="n">
         <v>1143.9</v>
       </c>
@@ -14910,13 +14952,13 @@
         <v>0</v>
       </c>
       <c r="U215" t="n">
-        <v>139500</v>
+        <v>153900</v>
       </c>
       <c r="V215" t="n">
         <v>139900</v>
       </c>
       <c r="W215" t="n">
-        <v>-0.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216">
@@ -14976,13 +15018,13 @@
         <v>0</v>
       </c>
       <c r="U216" t="n">
-        <v>117400</v>
+        <v>118200</v>
       </c>
       <c r="V216" t="n">
         <v>117000</v>
       </c>
       <c r="W216" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -15011,6 +15053,9 @@
           <t>KOSPI200,커버리지</t>
         </is>
       </c>
+      <c r="F217" t="n">
+        <v>978</v>
+      </c>
       <c r="L217" t="n">
         <v>3346.9</v>
       </c>
@@ -15039,13 +15084,13 @@
         <v>0</v>
       </c>
       <c r="U217" t="n">
-        <v>36150</v>
+        <v>37450</v>
       </c>
       <c r="V217" t="n">
         <v>37750</v>
       </c>
       <c r="W217" t="n">
-        <v>-4.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="218">
@@ -15074,6 +15119,9 @@
           <t>커버리지</t>
         </is>
       </c>
+      <c r="F218" t="n">
+        <v>206</v>
+      </c>
       <c r="L218" t="n">
         <v>732.5</v>
       </c>
@@ -15102,13 +15150,13 @@
         <v>0</v>
       </c>
       <c r="U218" t="n">
-        <v>56300</v>
+        <v>61700</v>
       </c>
       <c r="V218" t="n">
         <v>63000</v>
       </c>
       <c r="W218" t="n">
-        <v>-10.6</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="219">
@@ -15165,13 +15213,13 @@
         <v>0</v>
       </c>
       <c r="U219" t="n">
-        <v>21500</v>
+        <v>22000</v>
       </c>
       <c r="V219" t="n">
         <v>21450</v>
       </c>
       <c r="W219" t="n">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="220">
@@ -15200,41 +15248,44 @@
           <t>KOSDAQ50</t>
         </is>
       </c>
+      <c r="F220" t="n">
+        <v>874</v>
+      </c>
       <c r="L220" t="n">
-        <v>2950.8</v>
+        <v>2955.7</v>
       </c>
       <c r="M220" t="n">
         <v>2950.6</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O220" t="n">
-        <v>3749.7</v>
+        <v>3766.7</v>
       </c>
       <c r="P220" t="n">
         <v>3741.7</v>
       </c>
       <c r="Q220" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="R220" t="n">
-        <v>4572.5</v>
+        <v>4587.8</v>
       </c>
       <c r="S220" t="n">
         <v>4556.2</v>
       </c>
       <c r="T220" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="U220" t="n">
-        <v>49200</v>
+        <v>53300</v>
       </c>
       <c r="V220" t="n">
         <v>49450</v>
       </c>
       <c r="W220" t="n">
-        <v>-0.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="221">
@@ -15294,13 +15345,13 @@
         <v>0</v>
       </c>
       <c r="U221" t="n">
-        <v>219500</v>
+        <v>222500</v>
       </c>
       <c r="V221" t="n">
         <v>223500</v>
       </c>
       <c r="W221" t="n">
-        <v>-1.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="222">
@@ -15330,40 +15381,40 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>4064.4</v>
+        <v>3930.3</v>
       </c>
       <c r="M222" t="n">
         <v>4064.4</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="O222" t="n">
-        <v>1302.6</v>
+        <v>1404.8</v>
       </c>
       <c r="P222" t="n">
         <v>1302.6</v>
       </c>
       <c r="Q222" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R222" t="n">
-        <v>2600.5</v>
+        <v>2262.8</v>
       </c>
       <c r="S222" t="n">
         <v>2600.5</v>
       </c>
       <c r="T222" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="U222" t="n">
-        <v>31550</v>
+        <v>32500</v>
       </c>
       <c r="V222" t="n">
         <v>32050</v>
       </c>
       <c r="W222" t="n">
-        <v>-1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="223">
@@ -15423,13 +15474,13 @@
         <v>0</v>
       </c>
       <c r="U223" t="n">
-        <v>214500</v>
+        <v>218000</v>
       </c>
       <c r="V223" t="n">
         <v>210500</v>
       </c>
       <c r="W223" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="224">
@@ -15495,13 +15546,13 @@
         <v>-0.8</v>
       </c>
       <c r="U224" t="n">
-        <v>810000</v>
+        <v>814000</v>
       </c>
       <c r="V224" t="n">
         <v>716000</v>
       </c>
       <c r="W224" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="225">
@@ -15567,13 +15618,13 @@
         <v>0</v>
       </c>
       <c r="U225" t="n">
-        <v>139300</v>
+        <v>136600</v>
       </c>
       <c r="V225" t="n">
         <v>126900</v>
       </c>
       <c r="W225" t="n">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="226">
@@ -15639,13 +15690,13 @@
         <v>0</v>
       </c>
       <c r="U226" t="n">
-        <v>125900</v>
+        <v>129500</v>
       </c>
       <c r="V226" t="n">
         <v>128000</v>
       </c>
       <c r="W226" t="n">
-        <v>-1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="227">
@@ -15711,13 +15762,13 @@
         <v>-1.8</v>
       </c>
       <c r="U227" t="n">
-        <v>78100</v>
+        <v>75800</v>
       </c>
       <c r="V227" t="n">
         <v>69300</v>
       </c>
       <c r="W227" t="n">
-        <v>12.7</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="228">
@@ -15747,49 +15798,49 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>-98</v>
+        <v>-97</v>
       </c>
       <c r="G228" t="n">
         <v>-151</v>
       </c>
       <c r="H228" t="n">
-        <v>35.1</v>
+        <v>35.8</v>
       </c>
       <c r="L228" t="n">
-        <v>-170</v>
+        <v>-140</v>
       </c>
       <c r="M228" t="n">
         <v>-204</v>
       </c>
       <c r="N228" t="n">
-        <v>16.7</v>
+        <v>31.4</v>
       </c>
       <c r="O228" t="n">
-        <v>695.2</v>
+        <v>799</v>
       </c>
       <c r="P228" t="n">
         <v>748.5</v>
       </c>
       <c r="Q228" t="n">
-        <v>-7.1</v>
+        <v>6.7</v>
       </c>
       <c r="R228" t="n">
-        <v>1166.8</v>
+        <v>1281</v>
       </c>
       <c r="S228" t="n">
         <v>1272.8</v>
       </c>
       <c r="T228" t="n">
-        <v>-8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="U228" t="n">
-        <v>5920</v>
+        <v>5910</v>
       </c>
       <c r="V228" t="n">
         <v>5720</v>
       </c>
       <c r="W228" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="229">
@@ -15846,13 +15897,13 @@
         <v>0</v>
       </c>
       <c r="U229" t="n">
-        <v>469500</v>
+        <v>456000</v>
       </c>
       <c r="V229" t="n">
         <v>443000</v>
       </c>
       <c r="W229" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="230">
@@ -15882,25 +15933,25 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>1951</v>
+        <v>1962</v>
       </c>
       <c r="L230" t="n">
-        <v>7624.8</v>
+        <v>7668.8</v>
       </c>
       <c r="M230" t="n">
         <v>7579.2</v>
       </c>
       <c r="N230" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="O230" t="n">
-        <v>10707.6</v>
+        <v>10738.6</v>
       </c>
       <c r="P230" t="n">
         <v>10647.1</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="R230" t="n">
         <v>13385.8</v>
@@ -15912,13 +15963,13 @@
         <v>0.9</v>
       </c>
       <c r="U230" t="n">
-        <v>431500</v>
+        <v>461500</v>
       </c>
       <c r="V230" t="n">
         <v>407000</v>
       </c>
       <c r="W230" t="n">
-        <v>6</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="231">
@@ -15984,13 +16035,13 @@
         <v>0</v>
       </c>
       <c r="U231" t="n">
-        <v>135600</v>
+        <v>146300</v>
       </c>
       <c r="V231" t="n">
         <v>130700</v>
       </c>
       <c r="W231" t="n">
-        <v>3.7</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="232">
@@ -16020,49 +16071,49 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="G232" t="n">
         <v>1110</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="L232" t="n">
-        <v>3078.8</v>
+        <v>3071.4</v>
       </c>
       <c r="M232" t="n">
         <v>3078.8</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O232" t="n">
-        <v>3412</v>
+        <v>3401.5</v>
       </c>
       <c r="P232" t="n">
         <v>3412</v>
       </c>
       <c r="Q232" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="R232" t="n">
-        <v>3676.3</v>
+        <v>3662.5</v>
       </c>
       <c r="S232" t="n">
         <v>3676.3</v>
       </c>
       <c r="T232" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="U232" t="n">
-        <v>139000</v>
+        <v>147000</v>
       </c>
       <c r="V232" t="n">
         <v>145600</v>
       </c>
       <c r="W232" t="n">
-        <v>-4.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -16128,13 +16179,13 @@
         <v>0</v>
       </c>
       <c r="U233" t="n">
-        <v>50000</v>
+        <v>54200</v>
       </c>
       <c r="V233" t="n">
         <v>50000</v>
       </c>
       <c r="W233" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="234">
@@ -16194,13 +16245,13 @@
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>22900</v>
+        <v>23150</v>
       </c>
       <c r="V234" t="n">
         <v>22000</v>
       </c>
       <c r="W234" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="235">
@@ -16266,13 +16317,13 @@
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>332500</v>
+        <v>346000</v>
       </c>
       <c r="V235" t="n">
         <v>314000</v>
       </c>
       <c r="W235" t="n">
-        <v>5.9</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="236">
@@ -16338,13 +16389,13 @@
         <v>-2.4</v>
       </c>
       <c r="U236" t="n">
-        <v>3061000</v>
+        <v>3153000</v>
       </c>
       <c r="V236" t="n">
         <v>2770000</v>
       </c>
       <c r="W236" t="n">
-        <v>10.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="237">
@@ -16374,43 +16425,43 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="L237" t="n">
-        <v>2363.8</v>
+        <v>2369.5</v>
       </c>
       <c r="M237" t="n">
         <v>2363.8</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O237" t="n">
-        <v>2787.4</v>
+        <v>2776.8</v>
       </c>
       <c r="P237" t="n">
         <v>2787.4</v>
       </c>
       <c r="Q237" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="R237" t="n">
-        <v>3003.6</v>
+        <v>2979.5</v>
       </c>
       <c r="S237" t="n">
         <v>3003.6</v>
       </c>
       <c r="T237" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="U237" t="n">
-        <v>170100</v>
+        <v>178800</v>
       </c>
       <c r="V237" t="n">
         <v>165900</v>
       </c>
       <c r="W237" t="n">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="238">
@@ -16467,13 +16518,13 @@
         <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>75300</v>
+        <v>76900</v>
       </c>
       <c r="V238" t="n">
         <v>75600</v>
       </c>
       <c r="W238" t="n">
-        <v>-0.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="239">
@@ -16539,13 +16590,13 @@
         <v>0</v>
       </c>
       <c r="U239" t="n">
-        <v>16340</v>
+        <v>16950</v>
       </c>
       <c r="V239" t="n">
         <v>16220</v>
       </c>
       <c r="W239" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="240">
@@ -16602,13 +16653,13 @@
         <v>0</v>
       </c>
       <c r="U240" t="n">
-        <v>38400</v>
+        <v>38950</v>
       </c>
       <c r="V240" t="n">
         <v>38200</v>
       </c>
       <c r="W240" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241">
@@ -16668,13 +16719,13 @@
         <v>0</v>
       </c>
       <c r="U241" t="n">
-        <v>137400</v>
+        <v>139300</v>
       </c>
       <c r="V241" t="n">
         <v>137800</v>
       </c>
       <c r="W241" t="n">
-        <v>-0.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="242">
@@ -16740,13 +16791,13 @@
         <v>0</v>
       </c>
       <c r="U242" t="n">
-        <v>413000</v>
+        <v>416000</v>
       </c>
       <c r="V242" t="n">
         <v>458000</v>
       </c>
       <c r="W242" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -16776,40 +16827,40 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>43798.2</v>
+        <v>43792.6</v>
       </c>
       <c r="M243" t="n">
         <v>43798.2</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O243" t="n">
-        <v>47992.2</v>
+        <v>47979.7</v>
       </c>
       <c r="P243" t="n">
         <v>47992.2</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R243" t="n">
-        <v>50426.3</v>
+        <v>50413.7</v>
       </c>
       <c r="S243" t="n">
         <v>50426.3</v>
       </c>
       <c r="T243" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U243" t="n">
-        <v>32800</v>
+        <v>33900</v>
       </c>
       <c r="V243" t="n">
         <v>31850</v>
       </c>
       <c r="W243" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="244">
@@ -16875,13 +16926,13 @@
         <v>0</v>
       </c>
       <c r="U244" t="n">
-        <v>10990</v>
+        <v>11250</v>
       </c>
       <c r="V244" t="n">
         <v>10260</v>
       </c>
       <c r="W244" t="n">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="245">
@@ -16941,13 +16992,13 @@
         <v>1</v>
       </c>
       <c r="U245" t="n">
-        <v>133200</v>
+        <v>128600</v>
       </c>
       <c r="V245" t="n">
         <v>125800</v>
       </c>
       <c r="W245" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="246">
@@ -17004,13 +17055,13 @@
         <v>0</v>
       </c>
       <c r="U246" t="n">
-        <v>21500</v>
+        <v>21850</v>
       </c>
       <c r="V246" t="n">
         <v>21550</v>
       </c>
       <c r="W246" t="n">
-        <v>-0.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="247">
@@ -17040,49 +17091,49 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>929</v>
+        <v>898</v>
       </c>
       <c r="G247" t="n">
         <v>928</v>
       </c>
       <c r="H247" t="n">
-        <v>0.1</v>
+        <v>-3.2</v>
       </c>
       <c r="L247" t="n">
-        <v>3547.8</v>
+        <v>3470.2</v>
       </c>
       <c r="M247" t="n">
         <v>3544.2</v>
       </c>
       <c r="N247" t="n">
-        <v>0.1</v>
+        <v>-2.1</v>
       </c>
       <c r="O247" t="n">
-        <v>4754.7</v>
+        <v>4678.1</v>
       </c>
       <c r="P247" t="n">
         <v>4758.3</v>
       </c>
       <c r="Q247" t="n">
-        <v>-0.1</v>
+        <v>-1.7</v>
       </c>
       <c r="R247" t="n">
-        <v>5818.2</v>
+        <v>6051.4</v>
       </c>
       <c r="S247" t="n">
         <v>5859.8</v>
       </c>
       <c r="T247" t="n">
-        <v>-0.7</v>
+        <v>3.3</v>
       </c>
       <c r="U247" t="n">
-        <v>87600</v>
+        <v>88000</v>
       </c>
       <c r="V247" t="n">
         <v>86000</v>
       </c>
       <c r="W247" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="248">
@@ -17112,49 +17163,49 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>10067</v>
+        <v>10073</v>
       </c>
       <c r="G248" t="n">
         <v>10067</v>
       </c>
       <c r="H248" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L248" t="n">
-        <v>40482.9</v>
+        <v>40521.2</v>
       </c>
       <c r="M248" t="n">
         <v>40333.9</v>
       </c>
       <c r="N248" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O248" t="n">
-        <v>47289.5</v>
+        <v>47403.9</v>
       </c>
       <c r="P248" t="n">
         <v>47069</v>
       </c>
       <c r="Q248" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="R248" t="n">
-        <v>54416.8</v>
+        <v>54808.5</v>
       </c>
       <c r="S248" t="n">
         <v>53882.8</v>
       </c>
       <c r="T248" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="U248" t="n">
-        <v>467500</v>
+        <v>457000</v>
       </c>
       <c r="V248" t="n">
         <v>455000</v>
       </c>
       <c r="W248" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="249">
@@ -17183,6 +17234,9 @@
           <t>KOSPI200,커버리지</t>
         </is>
       </c>
+      <c r="F249" t="n">
+        <v>1627</v>
+      </c>
       <c r="L249" t="n">
         <v>2847.2</v>
       </c>
@@ -17211,13 +17265,13 @@
         <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>177700</v>
+        <v>180000</v>
       </c>
       <c r="V249" t="n">
         <v>174400</v>
       </c>
       <c r="W249" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="250">
@@ -17283,13 +17337,13 @@
         <v>0.4</v>
       </c>
       <c r="U250" t="n">
-        <v>110700</v>
+        <v>107600</v>
       </c>
       <c r="V250" t="n">
         <v>104500</v>
       </c>
       <c r="W250" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251">
@@ -17318,23 +17372,26 @@
           <t>KOSDAQ50</t>
         </is>
       </c>
+      <c r="F251" t="n">
+        <v>540</v>
+      </c>
       <c r="L251" t="n">
-        <v>2002</v>
+        <v>2013.7</v>
       </c>
       <c r="M251" t="n">
         <v>1967.1</v>
       </c>
       <c r="N251" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O251" t="n">
-        <v>2722.1</v>
+        <v>2725.3</v>
       </c>
       <c r="P251" t="n">
         <v>2632.9</v>
       </c>
       <c r="Q251" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R251" t="n">
         <v>3656.4</v>
@@ -17346,13 +17403,13 @@
         <v>8.5</v>
       </c>
       <c r="U251" t="n">
-        <v>339500</v>
+        <v>346500</v>
       </c>
       <c r="V251" t="n">
         <v>330500</v>
       </c>
       <c r="W251" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="252">
@@ -17418,13 +17475,13 @@
         <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>18170</v>
+        <v>16680</v>
       </c>
       <c r="V252" t="n">
         <v>15340</v>
       </c>
       <c r="W252" t="n">
-        <v>18.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="253">
@@ -17490,13 +17547,13 @@
         <v>0</v>
       </c>
       <c r="U253" t="n">
-        <v>371500</v>
+        <v>370000</v>
       </c>
       <c r="V253" t="n">
         <v>361000</v>
       </c>
       <c r="W253" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="254">
@@ -17556,13 +17613,13 @@
         <v>0</v>
       </c>
       <c r="U254" t="n">
-        <v>74600</v>
+        <v>73300</v>
       </c>
       <c r="V254" t="n">
         <v>68300</v>
       </c>
       <c r="W254" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="255">
@@ -17591,6 +17648,9 @@
           <t>커버리지</t>
         </is>
       </c>
+      <c r="F255" t="n">
+        <v>95</v>
+      </c>
       <c r="L255" t="n">
         <v>389</v>
       </c>
@@ -17619,13 +17679,13 @@
         <v>-0.5</v>
       </c>
       <c r="U255" t="n">
-        <v>18690</v>
+        <v>18910</v>
       </c>
       <c r="V255" t="n">
         <v>18340</v>
       </c>
       <c r="W255" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="256">
@@ -17685,13 +17745,13 @@
         <v>6.1</v>
       </c>
       <c r="U256" t="n">
-        <v>47050</v>
+        <v>47350</v>
       </c>
       <c r="V256" t="n">
         <v>44800</v>
       </c>
       <c r="W256" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="257">
@@ -17751,13 +17811,13 @@
         <v>0</v>
       </c>
       <c r="U257" t="n">
-        <v>62900</v>
+        <v>66900</v>
       </c>
       <c r="V257" t="n">
         <v>63100</v>
       </c>
       <c r="W257" t="n">
-        <v>-0.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="258">
@@ -17790,13 +17850,13 @@
         <v>-13</v>
       </c>
       <c r="U258" t="n">
-        <v>38800</v>
+        <v>37900</v>
       </c>
       <c r="V258" t="n">
         <v>36700</v>
       </c>
       <c r="W258" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="259">
@@ -17835,13 +17895,13 @@
         <v>0</v>
       </c>
       <c r="U259" t="n">
-        <v>33150</v>
+        <v>33000</v>
       </c>
       <c r="V259" t="n">
         <v>32900</v>
       </c>
       <c r="W259" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="260">
@@ -17898,24 +17958,24 @@
         <v>0</v>
       </c>
       <c r="U260" t="n">
-        <v>1068000</v>
+        <v>1028000</v>
       </c>
       <c r="V260" t="n">
         <v>1068000</v>
       </c>
       <c r="W260" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>420770</t>
+          <t>403870</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -17925,73 +17985,46 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>전기전자</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>107</v>
-      </c>
-      <c r="L261" t="n">
-        <v>313.4</v>
-      </c>
-      <c r="M261" t="n">
-        <v>313.4</v>
-      </c>
-      <c r="N261" t="n">
-        <v>0</v>
-      </c>
-      <c r="O261" t="n">
-        <v>894</v>
-      </c>
-      <c r="P261" t="n">
-        <v>894</v>
-      </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
-      <c r="R261" t="n">
-        <v>846</v>
-      </c>
-      <c r="S261" t="n">
-        <v>846</v>
-      </c>
-      <c r="T261" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="U261" t="n">
-        <v>107900</v>
+        <v>51100</v>
       </c>
       <c r="V261" t="n">
-        <v>104700</v>
+        <v>44000</v>
       </c>
       <c r="W261" t="n">
-        <v>3.1</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>439260</t>
+          <t>420770</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>대한조선</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>전기전자</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -18000,204 +18033,198 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>892</v>
-      </c>
-      <c r="G262" t="n">
-        <v>892</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="L262" t="n">
-        <v>3646.8</v>
+        <v>313.4</v>
       </c>
       <c r="M262" t="n">
-        <v>3646.8</v>
+        <v>313.4</v>
       </c>
       <c r="N262" t="n">
         <v>0</v>
       </c>
       <c r="O262" t="n">
-        <v>3749.2</v>
+        <v>894</v>
       </c>
       <c r="P262" t="n">
-        <v>3749.2</v>
+        <v>894</v>
       </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>4301.8</v>
+        <v>846</v>
       </c>
       <c r="S262" t="n">
-        <v>4301.8</v>
+        <v>846</v>
       </c>
       <c r="T262" t="n">
         <v>0</v>
       </c>
       <c r="U262" t="n">
-        <v>49300</v>
+        <v>109800</v>
       </c>
       <c r="V262" t="n">
-        <v>48750</v>
+        <v>104700</v>
       </c>
       <c r="W262" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>439260</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>대한조선</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>코스피</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>반도체소부장</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>KOSDAQ50</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>321</v>
+        <v>892</v>
       </c>
       <c r="G263" t="n">
-        <v>321</v>
+        <v>892</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>879.5</v>
+        <v>3646.8</v>
       </c>
       <c r="M263" t="n">
-        <v>879.5</v>
+        <v>3646.8</v>
       </c>
       <c r="N263" t="n">
         <v>0</v>
       </c>
       <c r="O263" t="n">
-        <v>2170</v>
+        <v>3749.2</v>
       </c>
       <c r="P263" t="n">
-        <v>2170</v>
+        <v>3749.2</v>
       </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>2874</v>
+        <v>4301.8</v>
       </c>
       <c r="S263" t="n">
-        <v>2874</v>
+        <v>4301.8</v>
       </c>
       <c r="T263" t="n">
         <v>0</v>
       </c>
       <c r="U263" t="n">
-        <v>64100</v>
+        <v>49000</v>
       </c>
       <c r="V263" t="n">
-        <v>61700</v>
+        <v>48750</v>
       </c>
       <c r="W263" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>443060</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>HD현대마린솔루션</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>조선</t>
+          <t>반도체소부장</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>KOSDAQ50</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>1079</v>
+        <v>321</v>
       </c>
       <c r="G264" t="n">
-        <v>1079</v>
+        <v>321</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>4184.6</v>
+        <v>879.5</v>
       </c>
       <c r="M264" t="n">
-        <v>4204.2</v>
+        <v>879.5</v>
       </c>
       <c r="N264" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>5358.9</v>
+        <v>2170</v>
       </c>
       <c r="P264" t="n">
-        <v>5358.1</v>
+        <v>2170</v>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>6713.7</v>
+        <v>2874</v>
       </c>
       <c r="S264" t="n">
-        <v>6713.7</v>
+        <v>2874</v>
       </c>
       <c r="T264" t="n">
         <v>0</v>
       </c>
       <c r="U264" t="n">
-        <v>220500</v>
+        <v>63300</v>
       </c>
       <c r="V264" t="n">
-        <v>207000</v>
+        <v>61700</v>
       </c>
       <c r="W264" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>456040</t>
+          <t>443060</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>OCI</t>
+          <t>HD현대마린솔루션</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -18207,69 +18234,69 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>그린인프라</t>
+          <t>조선</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>KOSPI200</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>480</v>
+        <v>1079</v>
       </c>
       <c r="G265" t="n">
-        <v>480</v>
+        <v>1079</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>1648</v>
+        <v>4184.6</v>
       </c>
       <c r="M265" t="n">
-        <v>1648</v>
+        <v>4204.2</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="O265" t="n">
-        <v>1880.7</v>
+        <v>5358.9</v>
       </c>
       <c r="P265" t="n">
-        <v>1880.7</v>
+        <v>5358.1</v>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>1966.7</v>
+        <v>6713.7</v>
       </c>
       <c r="S265" t="n">
-        <v>1966.7</v>
+        <v>6713.7</v>
       </c>
       <c r="T265" t="n">
         <v>0</v>
       </c>
       <c r="U265" t="n">
-        <v>80100</v>
+        <v>221000</v>
       </c>
       <c r="V265" t="n">
-        <v>80100</v>
+        <v>207000</v>
       </c>
       <c r="W265" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>460860</t>
+          <t>456040</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>동국제강</t>
+          <t>OCI</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -18279,69 +18306,69 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>철강·비철</t>
+          <t>그린인프라</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>220</v>
+        <v>480</v>
       </c>
       <c r="G266" t="n">
-        <v>220</v>
+        <v>480</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>1234.7</v>
+        <v>1648</v>
       </c>
       <c r="M266" t="n">
-        <v>1234.7</v>
+        <v>1648</v>
       </c>
       <c r="N266" t="n">
         <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>1485</v>
+        <v>1880.7</v>
       </c>
       <c r="P266" t="n">
-        <v>1485</v>
+        <v>1880.7</v>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>1601.7</v>
+        <v>1966.7</v>
       </c>
       <c r="S266" t="n">
-        <v>1601.7</v>
+        <v>1966.7</v>
       </c>
       <c r="T266" t="n">
         <v>0</v>
       </c>
       <c r="U266" t="n">
-        <v>10740</v>
+        <v>82000</v>
       </c>
       <c r="V266" t="n">
-        <v>9260</v>
+        <v>80100</v>
       </c>
       <c r="W266" t="n">
-        <v>16</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>462870</t>
+          <t>460860</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>시프트업</t>
+          <t>동국제강</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -18351,7 +18378,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>게임</t>
+          <t>철강·비철</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -18360,60 +18387,60 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="G267" t="n">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
       </c>
       <c r="L267" t="n">
-        <v>1066.5</v>
+        <v>1234.7</v>
       </c>
       <c r="M267" t="n">
-        <v>1066.5</v>
+        <v>1234.7</v>
       </c>
       <c r="N267" t="n">
         <v>0</v>
       </c>
       <c r="O267" t="n">
-        <v>1024</v>
+        <v>1485</v>
       </c>
       <c r="P267" t="n">
-        <v>1024</v>
+        <v>1485</v>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>2543.8</v>
+        <v>1601.7</v>
       </c>
       <c r="S267" t="n">
-        <v>2543.8</v>
+        <v>1601.7</v>
       </c>
       <c r="T267" t="n">
         <v>0</v>
       </c>
       <c r="U267" t="n">
-        <v>32550</v>
+        <v>10380</v>
       </c>
       <c r="V267" t="n">
-        <v>31750</v>
+        <v>9260</v>
       </c>
       <c r="W267" t="n">
-        <v>2.5</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>462870</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>시프트업</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -18423,69 +18450,69 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>게임</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>KOSPI200,커버리지</t>
+          <t>커버리지</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>325</v>
+        <v>260</v>
       </c>
       <c r="G268" t="n">
-        <v>325</v>
+        <v>261</v>
       </c>
       <c r="H268" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="L268" t="n">
-        <v>1642.4</v>
+        <v>1071.3</v>
       </c>
       <c r="M268" t="n">
-        <v>1628.2</v>
+        <v>1066.5</v>
       </c>
       <c r="N268" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O268" t="n">
-        <v>2222.2</v>
+        <v>1055.8</v>
       </c>
       <c r="P268" t="n">
-        <v>2207.5</v>
+        <v>1024</v>
       </c>
       <c r="Q268" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="R268" t="n">
-        <v>2805.5</v>
+        <v>2404.4</v>
       </c>
       <c r="S268" t="n">
-        <v>2789.2</v>
+        <v>2543.8</v>
       </c>
       <c r="T268" t="n">
-        <v>0.6</v>
+        <v>-5.5</v>
       </c>
       <c r="U268" t="n">
-        <v>222000</v>
+        <v>32900</v>
       </c>
       <c r="V268" t="n">
-        <v>232500</v>
+        <v>31750</v>
       </c>
       <c r="W268" t="n">
-        <v>-4.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>484870</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>엠앤씨솔루션</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -18495,130 +18522,241 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>방산·항공우주</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>커버리지</t>
+          <t>KOSPI200,커버리지</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>142</v>
+        <v>325</v>
       </c>
       <c r="G269" t="n">
-        <v>142</v>
+        <v>325</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>636</v>
+        <v>1642.4</v>
       </c>
       <c r="M269" t="n">
-        <v>636</v>
+        <v>1628.2</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O269" t="n">
-        <v>847</v>
+        <v>2222.2</v>
       </c>
       <c r="P269" t="n">
-        <v>847</v>
+        <v>2207.5</v>
       </c>
       <c r="Q269" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="R269" t="n">
-        <v>1111</v>
+        <v>2805.5</v>
       </c>
       <c r="S269" t="n">
-        <v>1111</v>
+        <v>2789.2</v>
       </c>
       <c r="T269" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U269" t="n">
-        <v>15200</v>
+        <v>229000</v>
       </c>
       <c r="V269" t="n">
-        <v>15230</v>
+        <v>232500</v>
       </c>
       <c r="W269" t="n">
-        <v>-0.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
+          <t>484870</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>엠앤씨솔루션</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>방산·항공우주</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>커버리지</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>142</v>
+      </c>
+      <c r="G270" t="n">
+        <v>142</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>636</v>
+      </c>
+      <c r="M270" t="n">
+        <v>636</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>847</v>
+      </c>
+      <c r="P270" t="n">
+        <v>847</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>1111</v>
+      </c>
+      <c r="S270" t="n">
+        <v>1111</v>
+      </c>
+      <c r="T270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="n">
+        <v>15110</v>
+      </c>
+      <c r="V270" t="n">
+        <v>15230</v>
+      </c>
+      <c r="W270" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>489790</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>한화비전</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>코스피</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>코스피</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
         <is>
           <t>반도체소부장</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E271" t="inlineStr">
         <is>
           <t>커버리지</t>
         </is>
       </c>
-      <c r="F270" t="n">
+      <c r="F271" t="n">
         <v>566</v>
       </c>
-      <c r="G270" t="n">
+      <c r="G271" t="n">
         <v>566</v>
       </c>
-      <c r="H270" t="n">
-        <v>0</v>
-      </c>
-      <c r="L270" t="n">
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
         <v>2034</v>
       </c>
-      <c r="M270" t="n">
+      <c r="M271" t="n">
         <v>2034</v>
       </c>
-      <c r="N270" t="n">
-        <v>0</v>
-      </c>
-      <c r="O270" t="n">
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
         <v>2967.3</v>
       </c>
-      <c r="P270" t="n">
+      <c r="P271" t="n">
         <v>2967.3</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
-      <c r="R270" t="n">
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
         <v>3731</v>
       </c>
-      <c r="S270" t="n">
+      <c r="S271" t="n">
         <v>3731</v>
       </c>
-      <c r="T270" t="n">
-        <v>0</v>
-      </c>
-      <c r="U270" t="n">
-        <v>51300</v>
-      </c>
-      <c r="V270" t="n">
+      <c r="T271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="n">
+        <v>50200</v>
+      </c>
+      <c r="V271" t="n">
         <v>50100</v>
       </c>
-      <c r="W270" t="n">
-        <v>2.4</v>
+      <c r="W271" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>491000</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>리브스메드</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>의료기기</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>커버리지</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>-90</v>
+      </c>
+      <c r="U272" t="n">
+        <v>33450</v>
+      </c>
+      <c r="V272" t="n">
+        <v>35000</v>
+      </c>
+      <c r="W272" t="n">
+        <v>-4.4</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-29 · 전주 2026-08-24</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-08-30 · 전주 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-03 · 전주 2026-08-30</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-04 · 전주 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>15590</v>
+        <v>15540</v>
       </c>
       <c r="V3" t="n">
         <v>15720</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="4">
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>73500</v>
+        <v>73400</v>
       </c>
       <c r="V5" t="n">
         <v>74700</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="6">
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1125000</v>
+        <v>1142000</v>
       </c>
       <c r="V6" t="n">
         <v>1238000</v>
       </c>
       <c r="W6" t="n">
-        <v>-9.1</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="7">
@@ -930,13 +930,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>55000</v>
+        <v>53600</v>
       </c>
       <c r="V7" t="n">
         <v>50000</v>
       </c>
       <c r="W7" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
@@ -1002,13 +1002,13 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>24400</v>
+        <v>24550</v>
       </c>
       <c r="V8" t="n">
         <v>24750</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="9">
@@ -1074,13 +1074,13 @@
         <v>-0.4</v>
       </c>
       <c r="U9" t="n">
-        <v>127400</v>
+        <v>126500</v>
       </c>
       <c r="V9" t="n">
         <v>128000</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="10">
@@ -1146,13 +1146,13 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>94000</v>
+        <v>92600</v>
       </c>
       <c r="V10" t="n">
         <v>96000</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.1</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="11">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>787166</v>
+        <v>788035</v>
       </c>
       <c r="G11" t="n">
         <v>788035</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>2664365</v>
@@ -1218,13 +1218,13 @@
         <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1596000</v>
+        <v>1647000</v>
       </c>
       <c r="V11" t="n">
         <v>1653000</v>
       </c>
       <c r="W11" t="n">
-        <v>-3.4</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="12">
@@ -1290,13 +1290,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>119500</v>
+        <v>119700</v>
       </c>
       <c r="V12" t="n">
         <v>128900</v>
       </c>
       <c r="W12" t="n">
-        <v>-7.3</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="13">
@@ -1353,13 +1353,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>702000</v>
+        <v>663000</v>
       </c>
       <c r="V13" t="n">
         <v>687000</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="14">
@@ -1425,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>133700</v>
+        <v>137400</v>
       </c>
       <c r="V14" t="n">
         <v>134900</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.9</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15">
@@ -1497,13 +1497,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>88100</v>
+        <v>89900</v>
       </c>
       <c r="V15" t="n">
         <v>93900</v>
       </c>
       <c r="W15" t="n">
-        <v>-6.2</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="16">
@@ -1569,13 +1569,13 @@
         <v>-4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>128500</v>
+        <v>131400</v>
       </c>
       <c r="V16" t="n">
         <v>130500</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -1641,13 +1641,13 @@
         <v>1.1</v>
       </c>
       <c r="U17" t="n">
-        <v>40400</v>
+        <v>42350</v>
       </c>
       <c r="V17" t="n">
         <v>42600</v>
       </c>
       <c r="W17" t="n">
-        <v>-5.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="18">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>26950</v>
+        <v>27400</v>
       </c>
       <c r="V18" t="n">
         <v>29700</v>
       </c>
       <c r="W18" t="n">
-        <v>-9.300000000000001</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="19">
@@ -1776,13 +1776,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>53500</v>
+        <v>51100</v>
       </c>
       <c r="V19" t="n">
         <v>52400</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="20">
@@ -1839,13 +1839,13 @@
         <v>-0.8</v>
       </c>
       <c r="U20" t="n">
-        <v>19050</v>
+        <v>19210</v>
       </c>
       <c r="V20" t="n">
         <v>18200</v>
       </c>
       <c r="W20" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="21">
@@ -1887,13 +1887,13 @@
         <v>6750</v>
       </c>
       <c r="U21" t="n">
-        <v>25300</v>
+        <v>25550</v>
       </c>
       <c r="V21" t="n">
         <v>26200</v>
       </c>
       <c r="W21" t="n">
-        <v>-3.4</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="22">
@@ -2031,13 +2031,13 @@
         <v>-0.2</v>
       </c>
       <c r="U23" t="n">
-        <v>485000</v>
+        <v>482000</v>
       </c>
       <c r="V23" t="n">
         <v>473500</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24">
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>16510</v>
+        <v>16090</v>
       </c>
       <c r="V24" t="n">
         <v>17020</v>
       </c>
       <c r="W24" t="n">
-        <v>-3</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="25">
@@ -2175,13 +2175,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>104300</v>
+        <v>103000</v>
       </c>
       <c r="V25" t="n">
         <v>103400</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="26">
@@ -2247,13 +2247,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>9440</v>
+        <v>9350</v>
       </c>
       <c r="V26" t="n">
         <v>9920</v>
       </c>
       <c r="W26" t="n">
-        <v>-4.8</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="27">
@@ -2319,13 +2319,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>7990</v>
+        <v>8070</v>
       </c>
       <c r="V27" t="n">
         <v>7880</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
@@ -2391,13 +2391,13 @@
         <v>0.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1424000</v>
+        <v>1417000</v>
       </c>
       <c r="V28" t="n">
         <v>1547000</v>
       </c>
       <c r="W28" t="n">
-        <v>-8</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="29">
@@ -2463,13 +2463,13 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>29150</v>
+        <v>30200</v>
       </c>
       <c r="V29" t="n">
         <v>28700</v>
       </c>
       <c r="W29" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="30">
@@ -2535,13 +2535,13 @@
         <v>1.2</v>
       </c>
       <c r="U30" t="n">
-        <v>118300</v>
+        <v>121100</v>
       </c>
       <c r="V30" t="n">
         <v>116300</v>
       </c>
       <c r="W30" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="31">
@@ -2607,13 +2607,13 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>183800</v>
+        <v>183600</v>
       </c>
       <c r="V31" t="n">
         <v>186300</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="32">
@@ -2679,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>46100</v>
+        <v>45700</v>
       </c>
       <c r="V32" t="n">
         <v>48350</v>
       </c>
       <c r="W32" t="n">
-        <v>-4.7</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="33">
@@ -2751,13 +2751,13 @@
         <v>-0.9</v>
       </c>
       <c r="U33" t="n">
-        <v>31650</v>
+        <v>31500</v>
       </c>
       <c r="V33" t="n">
         <v>31000</v>
       </c>
       <c r="W33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="34">
@@ -2823,13 +2823,13 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>379500</v>
+        <v>382500</v>
       </c>
       <c r="V34" t="n">
         <v>405500</v>
       </c>
       <c r="W34" t="n">
-        <v>-6.4</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="35">
@@ -2895,13 +2895,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>430500</v>
+        <v>430000</v>
       </c>
       <c r="V35" t="n">
         <v>450500</v>
       </c>
       <c r="W35" t="n">
-        <v>-4.4</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="36">
@@ -2931,49 +2931,49 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2015</v>
+        <v>1920</v>
       </c>
       <c r="G36" t="n">
         <v>2015</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-4.7</v>
       </c>
       <c r="L36" t="n">
-        <v>3676.7</v>
+        <v>3528.7</v>
       </c>
       <c r="M36" t="n">
         <v>3676.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="O36" t="n">
-        <v>4756.7</v>
+        <v>4472.7</v>
       </c>
       <c r="P36" t="n">
         <v>4756.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="R36" t="n">
-        <v>8550</v>
+        <v>5370</v>
       </c>
       <c r="S36" t="n">
         <v>8550</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>-37.2</v>
       </c>
       <c r="U36" t="n">
-        <v>24850</v>
+        <v>24750</v>
       </c>
       <c r="V36" t="n">
         <v>24150</v>
       </c>
       <c r="W36" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="37">
@@ -3183,13 +3183,13 @@
         <v>0.3</v>
       </c>
       <c r="U39" t="n">
-        <v>342000</v>
+        <v>337000</v>
       </c>
       <c r="V39" t="n">
         <v>337500</v>
       </c>
       <c r="W39" t="n">
-        <v>1.3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="40">
@@ -3219,40 +3219,40 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>23905.3</v>
+        <v>23716.6</v>
       </c>
       <c r="M40" t="n">
         <v>23581.9</v>
       </c>
       <c r="N40" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="O40" t="n">
-        <v>23943.7</v>
+        <v>23553.1</v>
       </c>
       <c r="P40" t="n">
         <v>23706.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>-0.6</v>
       </c>
       <c r="R40" t="n">
-        <v>25222.9</v>
+        <v>24819.6</v>
       </c>
       <c r="S40" t="n">
         <v>25033.1</v>
       </c>
       <c r="T40" t="n">
-        <v>0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="U40" t="n">
-        <v>203000</v>
+        <v>195700</v>
       </c>
       <c r="V40" t="n">
         <v>187400</v>
       </c>
       <c r="W40" t="n">
-        <v>8.300000000000001</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="41">
@@ -3318,13 +3318,13 @@
         <v>-3.4</v>
       </c>
       <c r="U41" t="n">
-        <v>50800</v>
+        <v>51400</v>
       </c>
       <c r="V41" t="n">
         <v>52400</v>
       </c>
       <c r="W41" t="n">
-        <v>-3.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="42">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1149671</v>
+        <v>1145149</v>
       </c>
       <c r="G42" t="n">
         <v>1145149</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>3933478.7</v>
@@ -3390,13 +3390,13 @@
         <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>250000</v>
+        <v>255500</v>
       </c>
       <c r="V42" t="n">
         <v>257000</v>
       </c>
       <c r="W42" t="n">
-        <v>-2.7</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="43">
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>26300</v>
+        <v>26650</v>
       </c>
       <c r="V43" t="n">
         <v>26650</v>
       </c>
       <c r="W43" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3525,13 +3525,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>37850</v>
+        <v>38100</v>
       </c>
       <c r="V44" t="n">
         <v>38650</v>
       </c>
       <c r="W44" t="n">
-        <v>-2.1</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="45">
@@ -3597,13 +3597,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>292000</v>
+        <v>299500</v>
       </c>
       <c r="V45" t="n">
         <v>313000</v>
       </c>
       <c r="W45" t="n">
-        <v>-6.7</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="46">
@@ -3669,13 +3669,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>127000</v>
+        <v>127600</v>
       </c>
       <c r="V46" t="n">
         <v>130500</v>
       </c>
       <c r="W46" t="n">
-        <v>-2.7</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="47">
@@ -3741,13 +3741,13 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>33600</v>
+        <v>34250</v>
       </c>
       <c r="V47" t="n">
         <v>37150</v>
       </c>
       <c r="W47" t="n">
-        <v>-9.6</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="48">
@@ -3813,13 +3813,13 @@
         <v>1.7</v>
       </c>
       <c r="U48" t="n">
-        <v>539000</v>
+        <v>548000</v>
       </c>
       <c r="V48" t="n">
         <v>571000</v>
       </c>
       <c r="W48" t="n">
-        <v>-5.6</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="49">
@@ -3885,13 +3885,13 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>96400</v>
+        <v>96700</v>
       </c>
       <c r="V49" t="n">
         <v>95800</v>
       </c>
       <c r="W49" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
@@ -3948,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>33200</v>
+        <v>34450</v>
       </c>
       <c r="V50" t="n">
         <v>36150</v>
       </c>
       <c r="W50" t="n">
-        <v>-8.199999999999999</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="51">
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>25650</v>
+        <v>25400</v>
       </c>
       <c r="V51" t="n">
         <v>26650</v>
       </c>
       <c r="W51" t="n">
-        <v>-3.8</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="52">
@@ -4092,13 +4092,13 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>46000</v>
+        <v>45100</v>
       </c>
       <c r="V52" t="n">
         <v>47200</v>
       </c>
       <c r="W52" t="n">
-        <v>-2.5</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="53">
@@ -4164,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>106000</v>
+        <v>111100</v>
       </c>
       <c r="V53" t="n">
         <v>112800</v>
       </c>
       <c r="W53" t="n">
-        <v>-6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="54">
@@ -4200,49 +4200,49 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="G54" t="n">
         <v>338</v>
       </c>
       <c r="H54" t="n">
-        <v>-18.6</v>
+        <v>-49.1</v>
       </c>
       <c r="L54" t="n">
-        <v>1350.3</v>
+        <v>1197.3</v>
       </c>
       <c r="M54" t="n">
         <v>1421.8</v>
       </c>
       <c r="N54" t="n">
-        <v>-5</v>
+        <v>-15.8</v>
       </c>
       <c r="O54" t="n">
-        <v>2081.3</v>
+        <v>1920.3</v>
       </c>
       <c r="P54" t="n">
         <v>2222.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>-6.3</v>
+        <v>-13.6</v>
       </c>
       <c r="R54" t="n">
-        <v>2772.7</v>
+        <v>2429</v>
       </c>
       <c r="S54" t="n">
         <v>2924.5</v>
       </c>
       <c r="T54" t="n">
-        <v>-5.2</v>
+        <v>-16.9</v>
       </c>
       <c r="U54" t="n">
-        <v>51400</v>
+        <v>51000</v>
       </c>
       <c r="V54" t="n">
         <v>60100</v>
       </c>
       <c r="W54" t="n">
-        <v>-14.5</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="55">
@@ -4299,13 +4299,13 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>16490</v>
+        <v>16260</v>
       </c>
       <c r="V55" t="n">
         <v>16800</v>
       </c>
       <c r="W55" t="n">
-        <v>-1.8</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="56">
@@ -4371,13 +4371,13 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>41800</v>
+        <v>42200</v>
       </c>
       <c r="V56" t="n">
         <v>43000</v>
       </c>
       <c r="W56" t="n">
-        <v>-2.8</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="57">
@@ -4407,49 +4407,49 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5960</v>
+        <v>5972</v>
       </c>
       <c r="G57" t="n">
         <v>5913</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>19445.5</v>
+        <v>19468</v>
       </c>
       <c r="M57" t="n">
         <v>19307</v>
       </c>
       <c r="N57" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O57" t="n">
-        <v>37303</v>
+        <v>37338.5</v>
       </c>
       <c r="P57" t="n">
         <v>37111</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="R57" t="n">
-        <v>58720</v>
+        <v>58742.2</v>
       </c>
       <c r="S57" t="n">
         <v>58230.6</v>
       </c>
       <c r="T57" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="U57" t="n">
-        <v>1348000</v>
+        <v>1401000</v>
       </c>
       <c r="V57" t="n">
         <v>1421000</v>
       </c>
       <c r="W57" t="n">
-        <v>-5.1</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="58">
@@ -4515,13 +4515,13 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>37000</v>
+        <v>37400</v>
       </c>
       <c r="V58" t="n">
         <v>39700</v>
       </c>
       <c r="W58" t="n">
-        <v>-6.8</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="59">
@@ -4587,13 +4587,13 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>344000</v>
+        <v>348500</v>
       </c>
       <c r="V59" t="n">
         <v>354500</v>
       </c>
       <c r="W59" t="n">
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="60">
@@ -4659,13 +4659,13 @@
         <v>5.5</v>
       </c>
       <c r="U60" t="n">
-        <v>29900</v>
+        <v>30050</v>
       </c>
       <c r="V60" t="n">
         <v>33750</v>
       </c>
       <c r="W60" t="n">
-        <v>-11.4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="61">
@@ -4803,13 +4803,13 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>192100</v>
+        <v>195300</v>
       </c>
       <c r="V62" t="n">
         <v>214500</v>
       </c>
       <c r="W62" t="n">
-        <v>-10.4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="63">
@@ -4875,13 +4875,13 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1224000</v>
+        <v>1222000</v>
       </c>
       <c r="V63" t="n">
         <v>1375000</v>
       </c>
       <c r="W63" t="n">
-        <v>-11</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="64">
@@ -4947,13 +4947,13 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>21650</v>
+        <v>21400</v>
       </c>
       <c r="V64" t="n">
         <v>21200</v>
       </c>
       <c r="W64" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="65">
@@ -4986,13 +4986,13 @@
         <v>59</v>
       </c>
       <c r="U65" t="n">
-        <v>12850</v>
+        <v>13010</v>
       </c>
       <c r="V65" t="n">
         <v>14310</v>
       </c>
       <c r="W65" t="n">
-        <v>-10.2</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="66">
@@ -5058,13 +5058,13 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>15670</v>
+        <v>15740</v>
       </c>
       <c r="V66" t="n">
         <v>16340</v>
       </c>
       <c r="W66" t="n">
-        <v>-4.1</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="67">
@@ -5130,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>147900</v>
+        <v>157300</v>
       </c>
       <c r="V67" t="n">
         <v>149200</v>
       </c>
       <c r="W67" t="n">
-        <v>-0.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="68">
@@ -5202,13 +5202,13 @@
         <v>0.9</v>
       </c>
       <c r="U68" t="n">
-        <v>556000</v>
+        <v>562000</v>
       </c>
       <c r="V68" t="n">
         <v>611000</v>
       </c>
       <c r="W68" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="69">
@@ -5274,13 +5274,13 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>61000</v>
+        <v>60000</v>
       </c>
       <c r="V69" t="n">
         <v>59500</v>
       </c>
       <c r="W69" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="70">
@@ -5346,13 +5346,13 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>21350</v>
+        <v>21050</v>
       </c>
       <c r="V70" t="n">
         <v>21700</v>
       </c>
       <c r="W70" t="n">
-        <v>-1.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="71">
@@ -5418,13 +5418,13 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>57200</v>
+        <v>57600</v>
       </c>
       <c r="V71" t="n">
         <v>59700</v>
       </c>
       <c r="W71" t="n">
-        <v>-4.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="72">
@@ -5490,13 +5490,13 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>133100</v>
+        <v>125900</v>
       </c>
       <c r="V72" t="n">
         <v>125900</v>
       </c>
       <c r="W72" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -5562,13 +5562,13 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>83900</v>
+        <v>84300</v>
       </c>
       <c r="V73" t="n">
         <v>91300</v>
       </c>
       <c r="W73" t="n">
-        <v>-8.1</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="74">
@@ -5634,13 +5634,13 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>15880</v>
+        <v>16110</v>
       </c>
       <c r="V74" t="n">
         <v>16910</v>
       </c>
       <c r="W74" t="n">
-        <v>-6.1</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="75">
@@ -5706,13 +5706,13 @@
         <v>-0.1</v>
       </c>
       <c r="U75" t="n">
-        <v>423500</v>
+        <v>422000</v>
       </c>
       <c r="V75" t="n">
         <v>450500</v>
       </c>
       <c r="W75" t="n">
-        <v>-6</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="76">
@@ -5778,13 +5778,13 @@
         <v>0.4</v>
       </c>
       <c r="U76" t="n">
-        <v>1047000</v>
+        <v>1055000</v>
       </c>
       <c r="V76" t="n">
         <v>1157000</v>
       </c>
       <c r="W76" t="n">
-        <v>-9.5</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5850,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>80300</v>
+        <v>79200</v>
       </c>
       <c r="V77" t="n">
         <v>83500</v>
       </c>
       <c r="W77" t="n">
-        <v>-3.8</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="78">
@@ -5922,13 +5922,13 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>30400</v>
+        <v>30850</v>
       </c>
       <c r="V78" t="n">
         <v>31850</v>
       </c>
       <c r="W78" t="n">
-        <v>-4.6</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="79">
@@ -5994,13 +5994,13 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>192500</v>
+        <v>193100</v>
       </c>
       <c r="V79" t="n">
         <v>203000</v>
       </c>
       <c r="W79" t="n">
-        <v>-5.2</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="80">
@@ -6129,13 +6129,13 @@
         <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>32450</v>
+        <v>32150</v>
       </c>
       <c r="V81" t="n">
         <v>32550</v>
       </c>
       <c r="W81" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="82">
@@ -6192,13 +6192,13 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>86600</v>
+        <v>86800</v>
       </c>
       <c r="V82" t="n">
         <v>88500</v>
       </c>
       <c r="W82" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="83">
@@ -6264,13 +6264,13 @@
         <v>0.2</v>
       </c>
       <c r="U83" t="n">
-        <v>89000</v>
+        <v>92500</v>
       </c>
       <c r="V83" t="n">
         <v>98600</v>
       </c>
       <c r="W83" t="n">
-        <v>-9.699999999999999</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="84">
@@ -6336,13 +6336,13 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>74700</v>
+        <v>74900</v>
       </c>
       <c r="V84" t="n">
         <v>75600</v>
       </c>
       <c r="W84" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="85">
@@ -6408,13 +6408,13 @@
         <v>1.5</v>
       </c>
       <c r="U85" t="n">
-        <v>22350</v>
+        <v>22550</v>
       </c>
       <c r="V85" t="n">
         <v>24950</v>
       </c>
       <c r="W85" t="n">
-        <v>-10.4</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="86">
@@ -6480,13 +6480,13 @@
         <v>-0.4</v>
       </c>
       <c r="U86" t="n">
-        <v>226000</v>
+        <v>238000</v>
       </c>
       <c r="V86" t="n">
         <v>243000</v>
       </c>
       <c r="W86" t="n">
-        <v>-7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="87">
@@ -6552,13 +6552,13 @@
         <v>-0.2</v>
       </c>
       <c r="U87" t="n">
-        <v>3495</v>
+        <v>3525</v>
       </c>
       <c r="V87" t="n">
         <v>3490</v>
       </c>
       <c r="W87" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -6624,13 +6624,13 @@
         <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>98200</v>
+        <v>99400</v>
       </c>
       <c r="V88" t="n">
         <v>100400</v>
       </c>
       <c r="W88" t="n">
-        <v>-2.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="89">
@@ -6696,13 +6696,13 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>21400</v>
+        <v>21650</v>
       </c>
       <c r="V89" t="n">
         <v>21400</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="90">
@@ -6768,13 +6768,13 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>25800</v>
+        <v>26150</v>
       </c>
       <c r="V90" t="n">
         <v>26600</v>
       </c>
       <c r="W90" t="n">
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="91">
@@ -6840,13 +6840,13 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>105300</v>
+        <v>107500</v>
       </c>
       <c r="V91" t="n">
         <v>102100</v>
       </c>
       <c r="W91" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="92">
@@ -6906,13 +6906,13 @@
         <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>21150</v>
+        <v>20700</v>
       </c>
       <c r="V92" t="n">
         <v>20850</v>
       </c>
       <c r="W92" t="n">
-        <v>1.4</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="93">
@@ -6978,13 +6978,13 @@
         <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>46100</v>
+        <v>45850</v>
       </c>
       <c r="V93" t="n">
         <v>48750</v>
       </c>
       <c r="W93" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="94">
@@ -7050,13 +7050,13 @@
         <v>0.1</v>
       </c>
       <c r="U94" t="n">
-        <v>372000</v>
+        <v>367000</v>
       </c>
       <c r="V94" t="n">
         <v>375000</v>
       </c>
       <c r="W94" t="n">
-        <v>-0.8</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="95">
@@ -7122,13 +7122,13 @@
         <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>5940</v>
+        <v>5960</v>
       </c>
       <c r="V95" t="n">
         <v>5790</v>
       </c>
       <c r="W95" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="96">
@@ -7185,13 +7185,13 @@
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>46600</v>
+        <v>46150</v>
       </c>
       <c r="V96" t="n">
         <v>47300</v>
       </c>
       <c r="W96" t="n">
-        <v>-1.5</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="97">
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>18940</v>
+        <v>18930</v>
       </c>
       <c r="V97" t="n">
         <v>19340</v>
@@ -7329,13 +7329,13 @@
         <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>53800</v>
+        <v>54300</v>
       </c>
       <c r="V98" t="n">
         <v>54500</v>
       </c>
       <c r="W98" t="n">
-        <v>-1.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="99">
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>129500</v>
+        <v>144000</v>
       </c>
       <c r="V99" t="n">
         <v>120100</v>
       </c>
       <c r="W99" t="n">
-        <v>7.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="100">
@@ -7446,13 +7446,13 @@
         <v>-1.1</v>
       </c>
       <c r="U100" t="n">
-        <v>12560</v>
+        <v>12530</v>
       </c>
       <c r="V100" t="n">
         <v>13250</v>
       </c>
       <c r="W100" t="n">
-        <v>-5.2</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="101">
@@ -7518,13 +7518,13 @@
         <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>14810</v>
+        <v>14760</v>
       </c>
       <c r="V101" t="n">
         <v>15020</v>
       </c>
       <c r="W101" t="n">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="102">
@@ -7581,13 +7581,13 @@
         <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>303000</v>
+        <v>297500</v>
       </c>
       <c r="V102" t="n">
         <v>310000</v>
       </c>
       <c r="W102" t="n">
-        <v>-2.3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="103">
@@ -7647,13 +7647,13 @@
         <v>1565</v>
       </c>
       <c r="U103" t="n">
-        <v>17030</v>
+        <v>17160</v>
       </c>
       <c r="V103" t="n">
         <v>18360</v>
       </c>
       <c r="W103" t="n">
-        <v>-7.2</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="104">
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>174700</v>
+        <v>172500</v>
       </c>
       <c r="V104" t="n">
         <v>176300</v>
       </c>
       <c r="W104" t="n">
-        <v>-0.9</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="105">
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>9040</v>
+        <v>9130</v>
       </c>
       <c r="V106" t="n">
         <v>9620</v>
       </c>
       <c r="W106" t="n">
-        <v>-6</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="107">
@@ -7935,13 +7935,13 @@
         <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>9820</v>
+        <v>10090</v>
       </c>
       <c r="V107" t="n">
         <v>10030</v>
       </c>
       <c r="W107" t="n">
-        <v>-2.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="108">
@@ -8007,13 +8007,13 @@
         <v>-3.9</v>
       </c>
       <c r="U108" t="n">
-        <v>545000</v>
+        <v>573000</v>
       </c>
       <c r="V108" t="n">
         <v>543000</v>
       </c>
       <c r="W108" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="109">
@@ -8079,13 +8079,13 @@
         <v>0.5</v>
       </c>
       <c r="U109" t="n">
-        <v>14720</v>
+        <v>14750</v>
       </c>
       <c r="V109" t="n">
         <v>14790</v>
       </c>
       <c r="W109" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="110">
@@ -8151,13 +8151,13 @@
         <v>0.1</v>
       </c>
       <c r="U110" t="n">
-        <v>207500</v>
+        <v>213500</v>
       </c>
       <c r="V110" t="n">
         <v>220500</v>
       </c>
       <c r="W110" t="n">
-        <v>-5.9</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="111">
@@ -8223,13 +8223,13 @@
         <v>0.4</v>
       </c>
       <c r="U111" t="n">
-        <v>35350</v>
+        <v>36200</v>
       </c>
       <c r="V111" t="n">
         <v>36850</v>
       </c>
       <c r="W111" t="n">
-        <v>-4.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="112">
@@ -8295,13 +8295,13 @@
         <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>32200</v>
+        <v>33050</v>
       </c>
       <c r="V112" t="n">
         <v>32850</v>
       </c>
       <c r="W112" t="n">
-        <v>-2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="113">
@@ -8367,13 +8367,13 @@
         <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>38500</v>
+        <v>39300</v>
       </c>
       <c r="V113" t="n">
         <v>40100</v>
       </c>
       <c r="W113" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="114">
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>8790</v>
+        <v>8910</v>
       </c>
       <c r="V114" t="n">
         <v>8870</v>
       </c>
       <c r="W114" t="n">
-        <v>-0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="115">
@@ -8511,13 +8511,13 @@
         <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>37700</v>
+        <v>35100</v>
       </c>
       <c r="V115" t="n">
         <v>37100</v>
       </c>
       <c r="W115" t="n">
-        <v>1.6</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="116">
@@ -8583,13 +8583,13 @@
         <v>3.1</v>
       </c>
       <c r="U116" t="n">
-        <v>217000</v>
+        <v>222000</v>
       </c>
       <c r="V116" t="n">
         <v>225000</v>
       </c>
       <c r="W116" t="n">
-        <v>-3.6</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="117">
@@ -8655,13 +8655,13 @@
         <v>0</v>
       </c>
       <c r="U117" t="n">
-        <v>168000</v>
+        <v>178300</v>
       </c>
       <c r="V117" t="n">
         <v>176800</v>
       </c>
       <c r="W117" t="n">
-        <v>-5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="118">
@@ -8727,13 +8727,13 @@
         <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>418000</v>
+        <v>443000</v>
       </c>
       <c r="V118" t="n">
         <v>398500</v>
       </c>
       <c r="W118" t="n">
-        <v>4.9</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="119">
@@ -8799,13 +8799,13 @@
         <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>32450</v>
+        <v>32500</v>
       </c>
       <c r="V119" t="n">
         <v>32900</v>
       </c>
       <c r="W119" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="120">
@@ -8862,13 +8862,13 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>268500</v>
+        <v>270500</v>
       </c>
       <c r="V120" t="n">
         <v>278500</v>
       </c>
       <c r="W120" t="n">
-        <v>-3.6</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="121">
@@ -8934,13 +8934,13 @@
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>11010</v>
+        <v>10910</v>
       </c>
       <c r="V121" t="n">
         <v>11100</v>
       </c>
       <c r="W121" t="n">
-        <v>-0.8</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="122">
@@ -9006,13 +9006,13 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>75300</v>
+        <v>79000</v>
       </c>
       <c r="V122" t="n">
         <v>75800</v>
       </c>
       <c r="W122" t="n">
-        <v>-0.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="123">
@@ -9078,13 +9078,13 @@
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>86500</v>
+        <v>86800</v>
       </c>
       <c r="V123" t="n">
         <v>88500</v>
       </c>
       <c r="W123" t="n">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="124">
@@ -9150,13 +9150,13 @@
         <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>210500</v>
+        <v>230000</v>
       </c>
       <c r="V124" t="n">
         <v>219500</v>
       </c>
       <c r="W124" t="n">
-        <v>-4.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="125">
@@ -9222,13 +9222,13 @@
         <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>16750</v>
+        <v>16850</v>
       </c>
       <c r="V125" t="n">
         <v>19690</v>
       </c>
       <c r="W125" t="n">
-        <v>-14.9</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="126">
@@ -9294,13 +9294,13 @@
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>55500</v>
+        <v>54700</v>
       </c>
       <c r="V126" t="n">
         <v>52700</v>
       </c>
       <c r="W126" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="127">
@@ -9366,13 +9366,13 @@
         <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>125000</v>
+        <v>126500</v>
       </c>
       <c r="V127" t="n">
         <v>133100</v>
       </c>
       <c r="W127" t="n">
-        <v>-6.1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="128">
@@ -9432,13 +9432,13 @@
         <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>23600</v>
+        <v>23700</v>
       </c>
       <c r="V128" t="n">
         <v>24200</v>
       </c>
       <c r="W128" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="129">
@@ -9504,13 +9504,13 @@
         <v>0</v>
       </c>
       <c r="U129" t="n">
-        <v>45300</v>
+        <v>45800</v>
       </c>
       <c r="V129" t="n">
         <v>47050</v>
       </c>
       <c r="W129" t="n">
-        <v>-3.7</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="130">
@@ -9576,13 +9576,13 @@
         <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>291500</v>
+        <v>294000</v>
       </c>
       <c r="V130" t="n">
         <v>318000</v>
       </c>
       <c r="W130" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="131">
@@ -9648,13 +9648,13 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>287000</v>
+        <v>282000</v>
       </c>
       <c r="V131" t="n">
         <v>277000</v>
       </c>
       <c r="W131" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="132">
@@ -9720,13 +9720,13 @@
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>107400</v>
+        <v>107600</v>
       </c>
       <c r="V132" t="n">
         <v>122400</v>
       </c>
       <c r="W132" t="n">
-        <v>-12.3</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="133">
@@ -9786,13 +9786,13 @@
         <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>114500</v>
+        <v>110300</v>
       </c>
       <c r="V133" t="n">
         <v>109700</v>
       </c>
       <c r="W133" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
@@ -9858,13 +9858,13 @@
         <v>1.7</v>
       </c>
       <c r="U134" t="n">
-        <v>64300</v>
+        <v>66600</v>
       </c>
       <c r="V134" t="n">
         <v>66800</v>
       </c>
       <c r="W134" t="n">
-        <v>-3.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="135">
@@ -9924,13 +9924,13 @@
         <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>83800</v>
+        <v>94200</v>
       </c>
       <c r="V135" t="n">
         <v>92700</v>
       </c>
       <c r="W135" t="n">
-        <v>-9.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="136">
@@ -9987,13 +9987,13 @@
         <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>39750</v>
+        <v>40150</v>
       </c>
       <c r="V136" t="n">
         <v>40500</v>
       </c>
       <c r="W136" t="n">
-        <v>-1.9</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="137">
@@ -10059,13 +10059,13 @@
         <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>186500</v>
+        <v>191700</v>
       </c>
       <c r="V137" t="n">
         <v>202500</v>
       </c>
       <c r="W137" t="n">
-        <v>-7.9</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="138">
@@ -10131,13 +10131,13 @@
         <v>-2.1</v>
       </c>
       <c r="U138" t="n">
-        <v>126400</v>
+        <v>126800</v>
       </c>
       <c r="V138" t="n">
         <v>139100</v>
       </c>
       <c r="W138" t="n">
-        <v>-9.1</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -10203,13 +10203,13 @@
         <v>0.2</v>
       </c>
       <c r="U139" t="n">
-        <v>72500</v>
+        <v>74100</v>
       </c>
       <c r="V139" t="n">
         <v>75800</v>
       </c>
       <c r="W139" t="n">
-        <v>-4.4</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="140">
@@ -10248,40 +10248,40 @@
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>1236.5</v>
+        <v>1234.1</v>
       </c>
       <c r="M140" t="n">
         <v>1236.5</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O140" t="n">
-        <v>1677.2</v>
+        <v>1666.1</v>
       </c>
       <c r="P140" t="n">
         <v>1677.2</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="R140" t="n">
-        <v>2108.8</v>
+        <v>2046.1</v>
       </c>
       <c r="S140" t="n">
         <v>2108.8</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="U140" t="n">
-        <v>240500</v>
+        <v>252000</v>
       </c>
       <c r="V140" t="n">
         <v>238500</v>
       </c>
       <c r="W140" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="141">
@@ -10347,13 +10347,13 @@
         <v>-3.3</v>
       </c>
       <c r="U141" t="n">
-        <v>26800</v>
+        <v>26250</v>
       </c>
       <c r="V141" t="n">
         <v>25850</v>
       </c>
       <c r="W141" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="142">
@@ -10419,13 +10419,13 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>199700</v>
+        <v>201500</v>
       </c>
       <c r="V142" t="n">
         <v>201500</v>
       </c>
       <c r="W142" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -10491,13 +10491,13 @@
         <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>120900</v>
+        <v>121300</v>
       </c>
       <c r="V143" t="n">
         <v>134800</v>
       </c>
       <c r="W143" t="n">
-        <v>-10.3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="144">
@@ -10563,13 +10563,13 @@
         <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>37700</v>
+        <v>38050</v>
       </c>
       <c r="V144" t="n">
         <v>39500</v>
       </c>
       <c r="W144" t="n">
-        <v>-4.6</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="145">
@@ -10635,13 +10635,13 @@
         <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>34700</v>
+        <v>34850</v>
       </c>
       <c r="V145" t="n">
         <v>35350</v>
       </c>
       <c r="W145" t="n">
-        <v>-1.8</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="146">
@@ -10707,13 +10707,13 @@
         <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>187100</v>
+        <v>188100</v>
       </c>
       <c r="V146" t="n">
         <v>190700</v>
       </c>
       <c r="W146" t="n">
-        <v>-1.9</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="147">
@@ -10827,7 +10827,7 @@
         <v>-0</v>
       </c>
       <c r="U148" t="n">
-        <v>16330</v>
+        <v>16320</v>
       </c>
       <c r="V148" t="n">
         <v>16390</v>
@@ -10899,13 +10899,13 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>114800</v>
+        <v>116100</v>
       </c>
       <c r="V149" t="n">
         <v>128800</v>
       </c>
       <c r="W149" t="n">
-        <v>-10.9</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="150">
@@ -10971,13 +10971,13 @@
         <v>0.4</v>
       </c>
       <c r="U150" t="n">
-        <v>94600</v>
+        <v>96200</v>
       </c>
       <c r="V150" t="n">
         <v>93400</v>
       </c>
       <c r="W150" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
@@ -11006,6 +11006,9 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F151" t="n">
+        <v>9012</v>
+      </c>
       <c r="L151" t="n">
         <v>40740.8</v>
       </c>
@@ -11034,13 +11037,13 @@
         <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>186600</v>
+        <v>188800</v>
       </c>
       <c r="V151" t="n">
         <v>191300</v>
       </c>
       <c r="W151" t="n">
-        <v>-2.5</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="152">
@@ -11106,13 +11109,13 @@
         <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>76500</v>
+        <v>75600</v>
       </c>
       <c r="V152" t="n">
         <v>74800</v>
       </c>
       <c r="W152" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="153">
@@ -11178,13 +11181,13 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>49500</v>
+        <v>50200</v>
       </c>
       <c r="V153" t="n">
         <v>53100</v>
       </c>
       <c r="W153" t="n">
-        <v>-6.8</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="154">
@@ -11250,13 +11253,13 @@
         <v>0</v>
       </c>
       <c r="U154" t="n">
-        <v>7120</v>
+        <v>7180</v>
       </c>
       <c r="V154" t="n">
         <v>7360</v>
       </c>
       <c r="W154" t="n">
-        <v>-3.3</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="155">
@@ -11289,13 +11292,13 @@
         <v>230</v>
       </c>
       <c r="U155" t="n">
-        <v>10190</v>
+        <v>10280</v>
       </c>
       <c r="V155" t="n">
         <v>10660</v>
       </c>
       <c r="W155" t="n">
-        <v>-4.4</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="156">
@@ -11334,13 +11337,13 @@
         <v>4.5</v>
       </c>
       <c r="U156" t="n">
-        <v>9700</v>
+        <v>10060</v>
       </c>
       <c r="V156" t="n">
         <v>9850</v>
       </c>
       <c r="W156" t="n">
-        <v>-1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="157">
@@ -11406,13 +11409,13 @@
         <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>23450</v>
+        <v>23550</v>
       </c>
       <c r="V157" t="n">
         <v>25300</v>
       </c>
       <c r="W157" t="n">
-        <v>-7.3</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="158">
@@ -11478,13 +11481,13 @@
         <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>118900</v>
+        <v>123900</v>
       </c>
       <c r="V158" t="n">
         <v>129200</v>
       </c>
       <c r="W158" t="n">
-        <v>-8</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="159">
@@ -11550,13 +11553,13 @@
         <v>0</v>
       </c>
       <c r="U159" t="n">
-        <v>665000</v>
+        <v>652000</v>
       </c>
       <c r="V159" t="n">
         <v>734000</v>
       </c>
       <c r="W159" t="n">
-        <v>-9.4</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="160">
@@ -11589,13 +11592,13 @@
         <v>10</v>
       </c>
       <c r="U160" t="n">
-        <v>8860</v>
+        <v>8970</v>
       </c>
       <c r="V160" t="n">
         <v>9150</v>
       </c>
       <c r="W160" t="n">
-        <v>-3.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="161">
@@ -11661,13 +11664,13 @@
         <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>40900</v>
+        <v>41400</v>
       </c>
       <c r="V161" t="n">
         <v>41350</v>
       </c>
       <c r="W161" t="n">
-        <v>-1.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="162">
@@ -11805,13 +11808,13 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>59300</v>
+        <v>60000</v>
       </c>
       <c r="V163" t="n">
         <v>65400</v>
       </c>
       <c r="W163" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -11877,13 +11880,13 @@
         <v>0</v>
       </c>
       <c r="U164" t="n">
-        <v>130800</v>
+        <v>136500</v>
       </c>
       <c r="V164" t="n">
         <v>134000</v>
       </c>
       <c r="W164" t="n">
-        <v>-2.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="165">
@@ -11949,13 +11952,13 @@
         <v>0</v>
       </c>
       <c r="U165" t="n">
-        <v>202000</v>
+        <v>206000</v>
       </c>
       <c r="V165" t="n">
         <v>205000</v>
       </c>
       <c r="W165" t="n">
-        <v>-1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="166">
@@ -12015,13 +12018,13 @@
         <v>-0</v>
       </c>
       <c r="U166" t="n">
-        <v>139500</v>
+        <v>134300</v>
       </c>
       <c r="V166" t="n">
         <v>136000</v>
       </c>
       <c r="W166" t="n">
-        <v>2.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="167">
@@ -12078,13 +12081,13 @@
         <v>0</v>
       </c>
       <c r="U167" t="n">
-        <v>6110</v>
+        <v>5740</v>
       </c>
       <c r="V167" t="n">
         <v>5950</v>
       </c>
       <c r="W167" t="n">
-        <v>2.7</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="168">
@@ -12150,13 +12153,13 @@
         <v>0.1</v>
       </c>
       <c r="U168" t="n">
-        <v>50400</v>
+        <v>50900</v>
       </c>
       <c r="V168" t="n">
         <v>47700</v>
       </c>
       <c r="W168" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="169">
@@ -12222,13 +12225,13 @@
         <v>0</v>
       </c>
       <c r="U169" t="n">
-        <v>51900</v>
+        <v>52800</v>
       </c>
       <c r="V169" t="n">
         <v>58000</v>
       </c>
       <c r="W169" t="n">
-        <v>-10.5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="170">
@@ -12294,13 +12297,13 @@
         <v>0.9</v>
       </c>
       <c r="U170" t="n">
-        <v>142500</v>
+        <v>143300</v>
       </c>
       <c r="V170" t="n">
         <v>150600</v>
       </c>
       <c r="W170" t="n">
-        <v>-5.4</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="171">
@@ -12339,13 +12342,13 @@
         <v>0</v>
       </c>
       <c r="U171" t="n">
-        <v>12250</v>
+        <v>12500</v>
       </c>
       <c r="V171" t="n">
         <v>12520</v>
       </c>
       <c r="W171" t="n">
-        <v>-2.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="172">
@@ -12405,13 +12408,13 @@
         <v>2.6</v>
       </c>
       <c r="U172" t="n">
-        <v>171700</v>
+        <v>182000</v>
       </c>
       <c r="V172" t="n">
         <v>173400</v>
       </c>
       <c r="W172" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -12477,13 +12480,13 @@
         <v>0</v>
       </c>
       <c r="U173" t="n">
-        <v>133900</v>
+        <v>146800</v>
       </c>
       <c r="V173" t="n">
         <v>142700</v>
       </c>
       <c r="W173" t="n">
-        <v>-6.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="174">
@@ -12549,13 +12552,13 @@
         <v>6.1</v>
       </c>
       <c r="U174" t="n">
-        <v>17550</v>
+        <v>17910</v>
       </c>
       <c r="V174" t="n">
         <v>18470</v>
       </c>
       <c r="W174" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="175">
@@ -12621,13 +12624,13 @@
         <v>0</v>
       </c>
       <c r="U175" t="n">
-        <v>31550</v>
+        <v>31900</v>
       </c>
       <c r="V175" t="n">
         <v>35650</v>
       </c>
       <c r="W175" t="n">
-        <v>-11.5</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="176">
@@ -12693,13 +12696,13 @@
         <v>0</v>
       </c>
       <c r="U176" t="n">
-        <v>130800</v>
+        <v>138300</v>
       </c>
       <c r="V176" t="n">
         <v>116900</v>
       </c>
       <c r="W176" t="n">
-        <v>11.9</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="177">
@@ -12765,13 +12768,13 @@
         <v>0</v>
       </c>
       <c r="U177" t="n">
-        <v>185900</v>
+        <v>183400</v>
       </c>
       <c r="V177" t="n">
         <v>189300</v>
       </c>
       <c r="W177" t="n">
-        <v>-1.8</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="178">
@@ -12804,13 +12807,13 @@
         <v>151</v>
       </c>
       <c r="U178" t="n">
-        <v>27550</v>
+        <v>27900</v>
       </c>
       <c r="V178" t="n">
         <v>28700</v>
       </c>
       <c r="W178" t="n">
-        <v>-4</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="179">
@@ -12948,13 +12951,13 @@
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>67400</v>
+        <v>70700</v>
       </c>
       <c r="V180" t="n">
         <v>74500</v>
       </c>
       <c r="W180" t="n">
-        <v>-9.5</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="181">
@@ -13020,13 +13023,13 @@
         <v>0</v>
       </c>
       <c r="U181" t="n">
-        <v>78600</v>
+        <v>78400</v>
       </c>
       <c r="V181" t="n">
         <v>86400</v>
       </c>
       <c r="W181" t="n">
-        <v>-9</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="182">
@@ -13086,13 +13089,13 @@
         <v>0</v>
       </c>
       <c r="U182" t="n">
-        <v>177900</v>
+        <v>172000</v>
       </c>
       <c r="V182" t="n">
         <v>171600</v>
       </c>
       <c r="W182" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="183">
@@ -13158,13 +13161,13 @@
         <v>-0.1</v>
       </c>
       <c r="U183" t="n">
-        <v>248500</v>
+        <v>304500</v>
       </c>
       <c r="V183" t="n">
         <v>242000</v>
       </c>
       <c r="W183" t="n">
-        <v>2.7</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="184">
@@ -13230,13 +13233,13 @@
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>75600</v>
+        <v>75000</v>
       </c>
       <c r="V184" t="n">
         <v>74300</v>
       </c>
       <c r="W184" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="185">
@@ -13302,13 +13305,13 @@
         <v>0</v>
       </c>
       <c r="U185" t="n">
-        <v>45900</v>
+        <v>46950</v>
       </c>
       <c r="V185" t="n">
         <v>49400</v>
       </c>
       <c r="W185" t="n">
-        <v>-7.1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="186">
@@ -13347,13 +13350,13 @@
         <v>1.1</v>
       </c>
       <c r="U186" t="n">
-        <v>9390</v>
+        <v>9580</v>
       </c>
       <c r="V186" t="n">
         <v>9610</v>
       </c>
       <c r="W186" t="n">
-        <v>-2.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="187">
@@ -13419,13 +13422,13 @@
         <v>0</v>
       </c>
       <c r="U187" t="n">
-        <v>58200</v>
+        <v>55800</v>
       </c>
       <c r="V187" t="n">
         <v>56500</v>
       </c>
       <c r="W187" t="n">
-        <v>3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="188">
@@ -13491,13 +13494,13 @@
         <v>0.1</v>
       </c>
       <c r="U188" t="n">
-        <v>40650</v>
+        <v>41950</v>
       </c>
       <c r="V188" t="n">
         <v>40450</v>
       </c>
       <c r="W188" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="189">
@@ -13563,13 +13566,13 @@
         <v>0</v>
       </c>
       <c r="U189" t="n">
-        <v>460500</v>
+        <v>473500</v>
       </c>
       <c r="V189" t="n">
         <v>509000</v>
       </c>
       <c r="W189" t="n">
-        <v>-9.5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="190">
@@ -13635,13 +13638,13 @@
         <v>0</v>
       </c>
       <c r="U190" t="n">
-        <v>224000</v>
+        <v>236500</v>
       </c>
       <c r="V190" t="n">
         <v>238500</v>
       </c>
       <c r="W190" t="n">
-        <v>-6.1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="191">
@@ -13670,6 +13673,9 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F191" t="n">
+        <v>8497</v>
+      </c>
       <c r="L191" t="n">
         <v>32423.4</v>
       </c>
@@ -13698,13 +13704,13 @@
         <v>0</v>
       </c>
       <c r="U191" t="n">
-        <v>136900</v>
+        <v>135500</v>
       </c>
       <c r="V191" t="n">
         <v>122000</v>
       </c>
       <c r="W191" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="192">
@@ -13733,6 +13739,9 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F192" t="n">
+        <v>3418</v>
+      </c>
       <c r="L192" t="n">
         <v>10035.1</v>
       </c>
@@ -13761,13 +13770,13 @@
         <v>0</v>
       </c>
       <c r="U192" t="n">
-        <v>15820</v>
+        <v>15390</v>
       </c>
       <c r="V192" t="n">
         <v>15120</v>
       </c>
       <c r="W192" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="193">
@@ -13827,13 +13836,13 @@
         <v>0</v>
       </c>
       <c r="U193" t="n">
-        <v>19050</v>
+        <v>18120</v>
       </c>
       <c r="V193" t="n">
         <v>18120</v>
       </c>
       <c r="W193" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -13899,13 +13908,13 @@
         <v>0</v>
       </c>
       <c r="U194" t="n">
-        <v>73800</v>
+        <v>73500</v>
       </c>
       <c r="V194" t="n">
         <v>75100</v>
       </c>
       <c r="W194" t="n">
-        <v>-1.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="195">
@@ -13971,13 +13980,13 @@
         <v>0</v>
       </c>
       <c r="U195" t="n">
-        <v>254000</v>
+        <v>262500</v>
       </c>
       <c r="V195" t="n">
         <v>271000</v>
       </c>
       <c r="W195" t="n">
-        <v>-6.3</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="196">
@@ -14034,13 +14043,13 @@
         <v>-62.6</v>
       </c>
       <c r="U196" t="n">
-        <v>88300</v>
+        <v>92000</v>
       </c>
       <c r="V196" t="n">
         <v>101000</v>
       </c>
       <c r="W196" t="n">
-        <v>-12.6</v>
+        <v>-8.9</v>
       </c>
     </row>
     <row r="197">
@@ -14106,13 +14115,13 @@
         <v>0.1</v>
       </c>
       <c r="U197" t="n">
-        <v>240500</v>
+        <v>244000</v>
       </c>
       <c r="V197" t="n">
         <v>259000</v>
       </c>
       <c r="W197" t="n">
-        <v>-7.1</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="198">
@@ -14178,13 +14187,13 @@
         <v>0</v>
       </c>
       <c r="U198" t="n">
-        <v>37250</v>
+        <v>37550</v>
       </c>
       <c r="V198" t="n">
         <v>38200</v>
       </c>
       <c r="W198" t="n">
-        <v>-2.5</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="199">
@@ -14217,13 +14226,13 @@
         <v>27</v>
       </c>
       <c r="U199" t="n">
-        <v>9360</v>
+        <v>9440</v>
       </c>
       <c r="V199" t="n">
         <v>9960</v>
       </c>
       <c r="W199" t="n">
-        <v>-6</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="200">
@@ -14289,13 +14298,13 @@
         <v>0</v>
       </c>
       <c r="U200" t="n">
-        <v>66500</v>
+        <v>65400</v>
       </c>
       <c r="V200" t="n">
         <v>66400</v>
       </c>
       <c r="W200" t="n">
-        <v>0.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="201">
@@ -14361,13 +14370,13 @@
         <v>0</v>
       </c>
       <c r="U201" t="n">
-        <v>150600</v>
+        <v>145800</v>
       </c>
       <c r="V201" t="n">
         <v>161700</v>
       </c>
       <c r="W201" t="n">
-        <v>-6.9</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -14433,13 +14442,13 @@
         <v>0</v>
       </c>
       <c r="U202" t="n">
-        <v>36900</v>
+        <v>36950</v>
       </c>
       <c r="V202" t="n">
         <v>38250</v>
       </c>
       <c r="W202" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="203">
@@ -14468,6 +14477,9 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F203" t="n">
+        <v>3043</v>
+      </c>
       <c r="L203" t="n">
         <v>10225.2</v>
       </c>
@@ -14496,13 +14508,13 @@
         <v>0</v>
       </c>
       <c r="U203" t="n">
-        <v>31600</v>
+        <v>31000</v>
       </c>
       <c r="V203" t="n">
         <v>29050</v>
       </c>
       <c r="W203" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="204">
@@ -14568,13 +14580,13 @@
         <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>33200</v>
+        <v>33650</v>
       </c>
       <c r="V204" t="n">
         <v>38950</v>
       </c>
       <c r="W204" t="n">
-        <v>-14.8</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="205">
@@ -14640,13 +14652,13 @@
         <v>0</v>
       </c>
       <c r="U205" t="n">
-        <v>68200</v>
+        <v>68000</v>
       </c>
       <c r="V205" t="n">
         <v>68500</v>
       </c>
       <c r="W205" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="206">
@@ -14712,13 +14724,13 @@
         <v>0</v>
       </c>
       <c r="U206" t="n">
-        <v>60700</v>
+        <v>63100</v>
       </c>
       <c r="V206" t="n">
         <v>63800</v>
       </c>
       <c r="W206" t="n">
-        <v>-4.9</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="207">
@@ -14784,13 +14796,13 @@
         <v>-1.3</v>
       </c>
       <c r="U207" t="n">
-        <v>58000</v>
+        <v>57200</v>
       </c>
       <c r="V207" t="n">
         <v>59200</v>
       </c>
       <c r="W207" t="n">
-        <v>-2</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="208">
@@ -14856,13 +14868,13 @@
         <v>0</v>
       </c>
       <c r="U208" t="n">
-        <v>282000</v>
+        <v>275500</v>
       </c>
       <c r="V208" t="n">
         <v>303000</v>
       </c>
       <c r="W208" t="n">
-        <v>-6.9</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="209">
@@ -14928,13 +14940,13 @@
         <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>41750</v>
+        <v>42050</v>
       </c>
       <c r="V209" t="n">
         <v>43650</v>
       </c>
       <c r="W209" t="n">
-        <v>-4.4</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="210">
@@ -14973,40 +14985,40 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>2641.5</v>
+        <v>2885.2</v>
       </c>
       <c r="M210" t="n">
         <v>2641.5</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O210" t="n">
-        <v>4463</v>
+        <v>4519.2</v>
       </c>
       <c r="P210" t="n">
         <v>4463</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R210" t="n">
-        <v>5872.8</v>
+        <v>6203</v>
       </c>
       <c r="S210" t="n">
         <v>5872.8</v>
       </c>
       <c r="T210" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="U210" t="n">
-        <v>283000</v>
+        <v>288500</v>
       </c>
       <c r="V210" t="n">
         <v>320000</v>
       </c>
       <c r="W210" t="n">
-        <v>-11.6</v>
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -15072,13 +15084,13 @@
         <v>0</v>
       </c>
       <c r="U211" t="n">
-        <v>47650</v>
+        <v>48500</v>
       </c>
       <c r="V211" t="n">
         <v>50300</v>
       </c>
       <c r="W211" t="n">
-        <v>-5.3</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="212">
@@ -15144,13 +15156,13 @@
         <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>1477000</v>
+        <v>1447000</v>
       </c>
       <c r="V212" t="n">
         <v>1486000</v>
       </c>
       <c r="W212" t="n">
-        <v>-0.6</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="213">
@@ -15216,13 +15228,13 @@
         <v>0</v>
       </c>
       <c r="U213" t="n">
-        <v>31700</v>
+        <v>31800</v>
       </c>
       <c r="V213" t="n">
         <v>33250</v>
       </c>
       <c r="W213" t="n">
-        <v>-4.7</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="214">
@@ -15288,13 +15300,13 @@
         <v>0.3</v>
       </c>
       <c r="U214" t="n">
-        <v>381000</v>
+        <v>386500</v>
       </c>
       <c r="V214" t="n">
         <v>461500</v>
       </c>
       <c r="W214" t="n">
-        <v>-17.4</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="215">
@@ -15360,13 +15372,13 @@
         <v>0</v>
       </c>
       <c r="U215" t="n">
-        <v>46400</v>
+        <v>48300</v>
       </c>
       <c r="V215" t="n">
         <v>46800</v>
       </c>
       <c r="W215" t="n">
-        <v>-0.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="216">
@@ -15432,13 +15444,13 @@
         <v>0</v>
       </c>
       <c r="U216" t="n">
-        <v>117500</v>
+        <v>117900</v>
       </c>
       <c r="V216" t="n">
         <v>122800</v>
       </c>
       <c r="W216" t="n">
-        <v>-4.3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="217">
@@ -15498,13 +15510,13 @@
         <v>0</v>
       </c>
       <c r="U217" t="n">
-        <v>99000</v>
+        <v>101200</v>
       </c>
       <c r="V217" t="n">
         <v>110200</v>
       </c>
       <c r="W217" t="n">
-        <v>-10.2</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="218">
@@ -15570,13 +15582,13 @@
         <v>0</v>
       </c>
       <c r="U218" t="n">
-        <v>105000</v>
+        <v>114800</v>
       </c>
       <c r="V218" t="n">
         <v>111100</v>
       </c>
       <c r="W218" t="n">
-        <v>-5.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="219">
@@ -15714,13 +15726,13 @@
         <v>0</v>
       </c>
       <c r="U220" t="n">
-        <v>134200</v>
+        <v>134500</v>
       </c>
       <c r="V220" t="n">
         <v>153900</v>
       </c>
       <c r="W220" t="n">
-        <v>-12.8</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="221">
@@ -15786,13 +15798,13 @@
         <v>0</v>
       </c>
       <c r="U221" t="n">
-        <v>106500</v>
+        <v>106000</v>
       </c>
       <c r="V221" t="n">
         <v>118200</v>
       </c>
       <c r="W221" t="n">
-        <v>-9.9</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="222">
@@ -15858,13 +15870,13 @@
         <v>-3.4</v>
       </c>
       <c r="U222" t="n">
-        <v>36700</v>
+        <v>36300</v>
       </c>
       <c r="V222" t="n">
         <v>37450</v>
       </c>
       <c r="W222" t="n">
-        <v>-2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="223">
@@ -15930,13 +15942,13 @@
         <v>0</v>
       </c>
       <c r="U223" t="n">
-        <v>57500</v>
+        <v>55300</v>
       </c>
       <c r="V223" t="n">
         <v>61700</v>
       </c>
       <c r="W223" t="n">
-        <v>-6.8</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="224">
@@ -15996,13 +16008,13 @@
         <v>0</v>
       </c>
       <c r="U224" t="n">
-        <v>21200</v>
+        <v>21650</v>
       </c>
       <c r="V224" t="n">
         <v>22000</v>
       </c>
       <c r="W224" t="n">
-        <v>-3.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="225">
@@ -16068,13 +16080,13 @@
         <v>0</v>
       </c>
       <c r="U225" t="n">
-        <v>48500</v>
+        <v>48000</v>
       </c>
       <c r="V225" t="n">
         <v>53300</v>
       </c>
       <c r="W225" t="n">
-        <v>-9</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="226">
@@ -16140,13 +16152,13 @@
         <v>-0.3</v>
       </c>
       <c r="U226" t="n">
-        <v>218000</v>
+        <v>216500</v>
       </c>
       <c r="V226" t="n">
         <v>222500</v>
       </c>
       <c r="W226" t="n">
-        <v>-2</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="227">
@@ -16206,13 +16218,13 @@
         <v>0</v>
       </c>
       <c r="U227" t="n">
-        <v>30950</v>
+        <v>34500</v>
       </c>
       <c r="V227" t="n">
         <v>32500</v>
       </c>
       <c r="W227" t="n">
-        <v>-4.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="228">
@@ -16278,13 +16290,13 @@
         <v>0</v>
       </c>
       <c r="U228" t="n">
-        <v>213500</v>
+        <v>240500</v>
       </c>
       <c r="V228" t="n">
         <v>218000</v>
       </c>
       <c r="W228" t="n">
-        <v>-2.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="229">
@@ -16350,13 +16362,13 @@
         <v>0</v>
       </c>
       <c r="U229" t="n">
-        <v>706000</v>
+        <v>714000</v>
       </c>
       <c r="V229" t="n">
         <v>814000</v>
       </c>
       <c r="W229" t="n">
-        <v>-13.3</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="230">
@@ -16422,13 +16434,13 @@
         <v>0</v>
       </c>
       <c r="U230" t="n">
-        <v>135300</v>
+        <v>140000</v>
       </c>
       <c r="V230" t="n">
         <v>136600</v>
       </c>
       <c r="W230" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="231">
@@ -16494,13 +16506,13 @@
         <v>0</v>
       </c>
       <c r="U231" t="n">
-        <v>129300</v>
+        <v>126300</v>
       </c>
       <c r="V231" t="n">
         <v>129500</v>
       </c>
       <c r="W231" t="n">
-        <v>-0.2</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="232">
@@ -16566,13 +16578,13 @@
         <v>1</v>
       </c>
       <c r="U232" t="n">
-        <v>68000</v>
+        <v>68800</v>
       </c>
       <c r="V232" t="n">
         <v>75800</v>
       </c>
       <c r="W232" t="n">
-        <v>-10.3</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="233">
@@ -16638,13 +16650,13 @@
         <v>0</v>
       </c>
       <c r="U233" t="n">
-        <v>5820</v>
+        <v>6140</v>
       </c>
       <c r="V233" t="n">
         <v>5910</v>
       </c>
       <c r="W233" t="n">
-        <v>-1.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="234">
@@ -16701,13 +16713,13 @@
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>436500</v>
+        <v>459000</v>
       </c>
       <c r="V234" t="n">
         <v>456000</v>
       </c>
       <c r="W234" t="n">
-        <v>-4.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="235">
@@ -16773,13 +16785,13 @@
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>406000</v>
+        <v>394000</v>
       </c>
       <c r="V235" t="n">
         <v>461500</v>
       </c>
       <c r="W235" t="n">
-        <v>-12</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="236">
@@ -16845,13 +16857,13 @@
         <v>0.4</v>
       </c>
       <c r="U236" t="n">
-        <v>146600</v>
+        <v>145500</v>
       </c>
       <c r="V236" t="n">
         <v>146300</v>
       </c>
       <c r="W236" t="n">
-        <v>0.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="237">
@@ -16917,13 +16929,13 @@
         <v>0</v>
       </c>
       <c r="U237" t="n">
-        <v>150600</v>
+        <v>147600</v>
       </c>
       <c r="V237" t="n">
         <v>147000</v>
       </c>
       <c r="W237" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="238">
@@ -16989,13 +17001,13 @@
         <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>54900</v>
+        <v>55200</v>
       </c>
       <c r="V238" t="n">
         <v>54200</v>
       </c>
       <c r="W238" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="239">
@@ -17061,13 +17073,13 @@
         <v>0</v>
       </c>
       <c r="U239" t="n">
-        <v>23200</v>
+        <v>23300</v>
       </c>
       <c r="V239" t="n">
         <v>23150</v>
       </c>
       <c r="W239" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="240">
@@ -17133,13 +17145,13 @@
         <v>0</v>
       </c>
       <c r="U240" t="n">
-        <v>354500</v>
+        <v>347000</v>
       </c>
       <c r="V240" t="n">
         <v>346000</v>
       </c>
       <c r="W240" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="241">
@@ -17205,13 +17217,13 @@
         <v>0</v>
       </c>
       <c r="U241" t="n">
-        <v>2725000</v>
+        <v>2732000</v>
       </c>
       <c r="V241" t="n">
         <v>3153000</v>
       </c>
       <c r="W241" t="n">
-        <v>-13.6</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="242">
@@ -17277,13 +17289,13 @@
         <v>0</v>
       </c>
       <c r="U242" t="n">
-        <v>175300</v>
+        <v>172800</v>
       </c>
       <c r="V242" t="n">
         <v>178800</v>
       </c>
       <c r="W242" t="n">
-        <v>-2</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="243">
@@ -17349,13 +17361,13 @@
         <v>0</v>
       </c>
       <c r="U243" t="n">
-        <v>16780</v>
+        <v>16670</v>
       </c>
       <c r="V243" t="n">
         <v>16950</v>
       </c>
       <c r="W243" t="n">
-        <v>-1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="244">
@@ -17412,13 +17424,13 @@
         <v>0</v>
       </c>
       <c r="U244" t="n">
-        <v>37750</v>
+        <v>37900</v>
       </c>
       <c r="V244" t="n">
         <v>38950</v>
       </c>
       <c r="W244" t="n">
-        <v>-3.1</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="245">
@@ -17484,13 +17496,13 @@
         <v>-1.3</v>
       </c>
       <c r="U245" t="n">
-        <v>147500</v>
+        <v>144700</v>
       </c>
       <c r="V245" t="n">
         <v>139300</v>
       </c>
       <c r="W245" t="n">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="246">
@@ -17556,13 +17568,13 @@
         <v>0</v>
       </c>
       <c r="U246" t="n">
-        <v>384500</v>
+        <v>395000</v>
       </c>
       <c r="V246" t="n">
         <v>416000</v>
       </c>
       <c r="W246" t="n">
-        <v>-7.6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="247">
@@ -17622,13 +17634,13 @@
         <v>0</v>
       </c>
       <c r="U247" t="n">
-        <v>34650</v>
+        <v>33200</v>
       </c>
       <c r="V247" t="n">
         <v>33900</v>
       </c>
       <c r="W247" t="n">
-        <v>2.2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="248">
@@ -17694,13 +17706,13 @@
         <v>0</v>
       </c>
       <c r="U248" t="n">
-        <v>11240</v>
+        <v>11230</v>
       </c>
       <c r="V248" t="n">
         <v>11250</v>
       </c>
       <c r="W248" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="249">
@@ -17766,13 +17778,13 @@
         <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>122400</v>
+        <v>126500</v>
       </c>
       <c r="V249" t="n">
         <v>128600</v>
       </c>
       <c r="W249" t="n">
-        <v>-4.8</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="250">
@@ -17832,13 +17844,13 @@
         <v>0</v>
       </c>
       <c r="U250" t="n">
-        <v>21800</v>
+        <v>21950</v>
       </c>
       <c r="V250" t="n">
         <v>21850</v>
       </c>
       <c r="W250" t="n">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="251">
@@ -17904,13 +17916,13 @@
         <v>0</v>
       </c>
       <c r="U251" t="n">
-        <v>86400</v>
+        <v>86600</v>
       </c>
       <c r="V251" t="n">
         <v>88000</v>
       </c>
       <c r="W251" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="252">
@@ -17976,13 +17988,13 @@
         <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>435000</v>
+        <v>436500</v>
       </c>
       <c r="V252" t="n">
         <v>457000</v>
       </c>
       <c r="W252" t="n">
-        <v>-4.8</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="253">
@@ -18048,13 +18060,13 @@
         <v>0</v>
       </c>
       <c r="U253" t="n">
-        <v>176000</v>
+        <v>178500</v>
       </c>
       <c r="V253" t="n">
         <v>180000</v>
       </c>
       <c r="W253" t="n">
-        <v>-2.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="254">
@@ -18120,13 +18132,13 @@
         <v>-0.7</v>
       </c>
       <c r="U254" t="n">
-        <v>101600</v>
+        <v>99500</v>
       </c>
       <c r="V254" t="n">
         <v>107600</v>
       </c>
       <c r="W254" t="n">
-        <v>-5.6</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="255">
@@ -18192,13 +18204,13 @@
         <v>-2.3</v>
       </c>
       <c r="U255" t="n">
-        <v>319500</v>
+        <v>325000</v>
       </c>
       <c r="V255" t="n">
         <v>346500</v>
       </c>
       <c r="W255" t="n">
-        <v>-7.8</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="256">
@@ -18264,13 +18276,13 @@
         <v>0</v>
       </c>
       <c r="U256" t="n">
-        <v>15790</v>
+        <v>16280</v>
       </c>
       <c r="V256" t="n">
         <v>16680</v>
       </c>
       <c r="W256" t="n">
-        <v>-5.3</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="257">
@@ -18336,13 +18348,13 @@
         <v>0</v>
       </c>
       <c r="U257" t="n">
-        <v>365500</v>
+        <v>358500</v>
       </c>
       <c r="V257" t="n">
         <v>370000</v>
       </c>
       <c r="W257" t="n">
-        <v>-1.2</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="258">
@@ -18408,13 +18420,13 @@
         <v>0</v>
       </c>
       <c r="U258" t="n">
-        <v>72500</v>
+        <v>73400</v>
       </c>
       <c r="V258" t="n">
         <v>73300</v>
       </c>
       <c r="W258" t="n">
-        <v>-1.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="259">
@@ -18480,13 +18492,13 @@
         <v>0</v>
       </c>
       <c r="U259" t="n">
-        <v>17810</v>
+        <v>18060</v>
       </c>
       <c r="V259" t="n">
         <v>18910</v>
       </c>
       <c r="W259" t="n">
-        <v>-5.8</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="260">
@@ -18552,13 +18564,13 @@
         <v>0</v>
       </c>
       <c r="U260" t="n">
-        <v>44800</v>
+        <v>47300</v>
       </c>
       <c r="V260" t="n">
         <v>47350</v>
       </c>
       <c r="W260" t="n">
-        <v>-5.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="261">
@@ -18624,13 +18636,13 @@
         <v>0</v>
       </c>
       <c r="U261" t="n">
-        <v>66300</v>
+        <v>66900</v>
       </c>
       <c r="V261" t="n">
         <v>66900</v>
       </c>
       <c r="W261" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -18669,13 +18681,13 @@
         <v>0</v>
       </c>
       <c r="U262" t="n">
-        <v>34600</v>
+        <v>37750</v>
       </c>
       <c r="V262" t="n">
         <v>37900</v>
       </c>
       <c r="W262" t="n">
-        <v>-8.699999999999999</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="263">
@@ -18714,13 +18726,13 @@
         <v>-40</v>
       </c>
       <c r="U263" t="n">
-        <v>31100</v>
+        <v>31050</v>
       </c>
       <c r="V263" t="n">
         <v>33000</v>
       </c>
       <c r="W263" t="n">
-        <v>-5.8</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="264">
@@ -18780,13 +18792,13 @@
         <v>2.5</v>
       </c>
       <c r="U264" t="n">
-        <v>981000</v>
+        <v>1041000</v>
       </c>
       <c r="V264" t="n">
         <v>1028000</v>
       </c>
       <c r="W264" t="n">
-        <v>-4.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="265">
@@ -18816,22 +18828,22 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="G265" t="n">
         <v>314</v>
       </c>
       <c r="H265" t="n">
-        <v>0</v>
+        <v>-5.1</v>
       </c>
       <c r="U265" t="n">
-        <v>50200</v>
+        <v>50800</v>
       </c>
       <c r="V265" t="n">
         <v>51100</v>
       </c>
       <c r="W265" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="266">
@@ -18897,13 +18909,13 @@
         <v>0</v>
       </c>
       <c r="U266" t="n">
-        <v>99900</v>
+        <v>101200</v>
       </c>
       <c r="V266" t="n">
         <v>109800</v>
       </c>
       <c r="W266" t="n">
-        <v>-9</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="267">
@@ -18969,13 +18981,13 @@
         <v>0</v>
       </c>
       <c r="U267" t="n">
-        <v>46600</v>
+        <v>46950</v>
       </c>
       <c r="V267" t="n">
         <v>49000</v>
       </c>
       <c r="W267" t="n">
-        <v>-4.9</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="268">
@@ -19041,13 +19053,13 @@
         <v>0</v>
       </c>
       <c r="U268" t="n">
-        <v>61500</v>
+        <v>67300</v>
       </c>
       <c r="V268" t="n">
         <v>63300</v>
       </c>
       <c r="W268" t="n">
-        <v>-2.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="269">
@@ -19113,13 +19125,13 @@
         <v>0</v>
       </c>
       <c r="U269" t="n">
-        <v>205500</v>
+        <v>210500</v>
       </c>
       <c r="V269" t="n">
         <v>221000</v>
       </c>
       <c r="W269" t="n">
-        <v>-7</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="270">
@@ -19185,13 +19197,13 @@
         <v>0</v>
       </c>
       <c r="U270" t="n">
-        <v>79800</v>
+        <v>79300</v>
       </c>
       <c r="V270" t="n">
         <v>82000</v>
       </c>
       <c r="W270" t="n">
-        <v>-2.7</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="271">
@@ -19257,13 +19269,13 @@
         <v>0</v>
       </c>
       <c r="U271" t="n">
-        <v>10670</v>
+        <v>10510</v>
       </c>
       <c r="V271" t="n">
         <v>10380</v>
       </c>
       <c r="W271" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="272">
@@ -19329,13 +19341,13 @@
         <v>-3.8</v>
       </c>
       <c r="U272" t="n">
-        <v>32000</v>
+        <v>31850</v>
       </c>
       <c r="V272" t="n">
         <v>32900</v>
       </c>
       <c r="W272" t="n">
-        <v>-2.7</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="273">
@@ -19401,7 +19413,7 @@
         <v>0</v>
       </c>
       <c r="U273" t="n">
-        <v>190500</v>
+        <v>190600</v>
       </c>
       <c r="V273" t="n">
         <v>229000</v>
@@ -19437,49 +19449,49 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="G274" t="n">
         <v>142</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>-14.1</v>
       </c>
       <c r="L274" t="n">
-        <v>636</v>
+        <v>571</v>
       </c>
       <c r="M274" t="n">
         <v>636</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>-10.2</v>
       </c>
       <c r="O274" t="n">
-        <v>847</v>
+        <v>733</v>
       </c>
       <c r="P274" t="n">
         <v>847</v>
       </c>
       <c r="Q274" t="n">
-        <v>0</v>
+        <v>-13.5</v>
       </c>
       <c r="R274" t="n">
-        <v>1111</v>
+        <v>948</v>
       </c>
       <c r="S274" t="n">
         <v>1111</v>
       </c>
       <c r="T274" t="n">
-        <v>0</v>
+        <v>-14.7</v>
       </c>
       <c r="U274" t="n">
-        <v>17280</v>
+        <v>16560</v>
       </c>
       <c r="V274" t="n">
         <v>15110</v>
       </c>
       <c r="W274" t="n">
-        <v>14.4</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="275">
@@ -19545,13 +19557,13 @@
         <v>0</v>
       </c>
       <c r="U275" t="n">
-        <v>48700</v>
+        <v>49400</v>
       </c>
       <c r="V275" t="n">
         <v>50200</v>
       </c>
       <c r="W275" t="n">
-        <v>-3</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="276">
@@ -19590,13 +19602,13 @@
         <v>0</v>
       </c>
       <c r="U276" t="n">
-        <v>33300</v>
+        <v>34500</v>
       </c>
       <c r="V276" t="n">
         <v>33450</v>
       </c>
       <c r="W276" t="n">
-        <v>-0.4</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-04 · 전주 2026-08-30</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-05 · 전주 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1325,6 +1325,9 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>7942</v>
+      </c>
       <c r="L13" t="n">
         <v>31986.2</v>
       </c>
@@ -1923,40 +1926,40 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G22" t="n">
         <v>415</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1771.6</v>
+        <v>1757.7</v>
       </c>
       <c r="M22" t="n">
         <v>1771.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2132.2</v>
+        <v>2107.1</v>
       </c>
       <c r="P22" t="n">
         <v>2132.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2400.2</v>
+        <v>2357.9</v>
       </c>
       <c r="S22" t="n">
         <v>2400.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="U22" t="n">
         <v>6080</v>
@@ -3354,31 +3357,31 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1145149</v>
+        <v>1141888</v>
       </c>
       <c r="G42" t="n">
         <v>1145149</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="L42" t="n">
-        <v>3933478.7</v>
+        <v>3927530.9</v>
       </c>
       <c r="M42" t="n">
         <v>3917860.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="O42" t="n">
-        <v>5542251.7</v>
+        <v>5533556</v>
       </c>
       <c r="P42" t="n">
         <v>5433530.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="R42" t="n">
         <v>5520887.9</v>
@@ -3777,25 +3780,25 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="G48" t="n">
         <v>995</v>
       </c>
       <c r="H48" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="L48" t="n">
-        <v>3621.1</v>
+        <v>3662.4</v>
       </c>
       <c r="M48" t="n">
         <v>3521.7</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>14400.7</v>
+        <v>14401.2</v>
       </c>
       <c r="P48" t="n">
         <v>14225.1</v>
@@ -7437,13 +7440,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G100" t="n">
         <v>656</v>
       </c>
       <c r="H100" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="U100" t="n">
         <v>12530</v>
@@ -7553,6 +7556,9 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F102" t="n">
+        <v>8596</v>
+      </c>
       <c r="L102" t="n">
         <v>34544.2</v>
       </c>
@@ -7908,22 +7914,22 @@
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>1651.7</v>
+        <v>1685.7</v>
       </c>
       <c r="M107" t="n">
         <v>1651.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O107" t="n">
-        <v>2027.3</v>
+        <v>2065.2</v>
       </c>
       <c r="P107" t="n">
         <v>2027.3</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R107" t="n">
         <v>2403.4</v>
@@ -8061,13 +8067,13 @@
         <v>-0.9</v>
       </c>
       <c r="O109" t="n">
-        <v>2218.8</v>
+        <v>2201</v>
       </c>
       <c r="P109" t="n">
         <v>2217.5</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="R109" t="n">
         <v>2580</v>
@@ -8340,22 +8346,22 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>1529.1</v>
+        <v>1525.1</v>
       </c>
       <c r="M113" t="n">
         <v>1529.1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="O113" t="n">
-        <v>1681.4</v>
+        <v>1673.1</v>
       </c>
       <c r="P113" t="n">
         <v>1681.4</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R113" t="n">
         <v>1679.3</v>
@@ -8979,13 +8985,13 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>1886.6</v>
+        <v>1880.3</v>
       </c>
       <c r="M122" t="n">
         <v>1886.6</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="O122" t="n">
         <v>2167.6</v>
@@ -9330,13 +9336,13 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="G127" t="n">
         <v>895</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="L127" t="n">
         <v>3569.9</v>
@@ -9612,40 +9618,40 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>2233</v>
+        <v>1906</v>
       </c>
       <c r="G131" t="n">
         <v>2233</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>-14.6</v>
       </c>
       <c r="L131" t="n">
-        <v>13021.5</v>
+        <v>12712.8</v>
       </c>
       <c r="M131" t="n">
         <v>13021.5</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="O131" t="n">
-        <v>39507.7</v>
+        <v>38502.2</v>
       </c>
       <c r="P131" t="n">
         <v>39507.7</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="R131" t="n">
-        <v>55674.8</v>
+        <v>53851.1</v>
       </c>
       <c r="S131" t="n">
         <v>55674.8</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>-3.3</v>
       </c>
       <c r="U131" t="n">
         <v>282000</v>
@@ -11517,40 +11523,40 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="G159" t="n">
         <v>1054</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" t="n">
-        <v>4475.1</v>
+        <v>4486.7</v>
       </c>
       <c r="M159" t="n">
         <v>4475.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O159" t="n">
-        <v>6270.8</v>
+        <v>6274.2</v>
       </c>
       <c r="P159" t="n">
         <v>6270.8</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R159" t="n">
-        <v>8419.6</v>
+        <v>8410.1</v>
       </c>
       <c r="S159" t="n">
         <v>8419.6</v>
       </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="U159" t="n">
         <v>652000</v>
@@ -12053,6 +12059,9 @@
           <t>KOSPI200</t>
         </is>
       </c>
+      <c r="F167" t="n">
+        <v>4601</v>
+      </c>
       <c r="L167" t="n">
         <v>9399.1</v>
       </c>
@@ -13476,13 +13485,13 @@
         <v>0</v>
       </c>
       <c r="O188" t="n">
-        <v>709.1</v>
+        <v>709.9</v>
       </c>
       <c r="P188" t="n">
         <v>709.2</v>
       </c>
       <c r="Q188" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="R188" t="n">
         <v>831.4</v>
@@ -14985,13 +14994,13 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>2885.2</v>
+        <v>2886.2</v>
       </c>
       <c r="M210" t="n">
         <v>2641.5</v>
       </c>
       <c r="N210" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O210" t="n">
         <v>4519.2</v>
@@ -15546,31 +15555,31 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="G218" t="n">
         <v>695</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L218" t="n">
-        <v>1838.7</v>
+        <v>1794.3</v>
       </c>
       <c r="M218" t="n">
         <v>1838.7</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="O218" t="n">
-        <v>2755.7</v>
+        <v>2739.7</v>
       </c>
       <c r="P218" t="n">
         <v>2755.7</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="R218" t="n">
         <v>3478.3</v>
@@ -15618,40 +15627,40 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>1756</v>
+        <v>1851</v>
       </c>
       <c r="G219" t="n">
         <v>1756</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="L219" t="n">
-        <v>8433.200000000001</v>
+        <v>8718</v>
       </c>
       <c r="M219" t="n">
         <v>8433.200000000001</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O219" t="n">
-        <v>9515.799999999999</v>
+        <v>9654.4</v>
       </c>
       <c r="P219" t="n">
         <v>9515.799999999999</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R219" t="n">
-        <v>10663</v>
+        <v>10489.8</v>
       </c>
       <c r="S219" t="n">
         <v>10663</v>
       </c>
       <c r="T219" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="U219" t="n">
         <v>62800</v>
@@ -15843,31 +15852,31 @@
         <v>-1.1</v>
       </c>
       <c r="L222" t="n">
-        <v>3333.1</v>
+        <v>3272.2</v>
       </c>
       <c r="M222" t="n">
         <v>3346.9</v>
       </c>
       <c r="N222" t="n">
-        <v>-0.4</v>
+        <v>-2.2</v>
       </c>
       <c r="O222" t="n">
-        <v>3779.4</v>
+        <v>3717.2</v>
       </c>
       <c r="P222" t="n">
         <v>3866.4</v>
       </c>
       <c r="Q222" t="n">
-        <v>-2.3</v>
+        <v>-3.9</v>
       </c>
       <c r="R222" t="n">
-        <v>4067.6</v>
+        <v>3985.4</v>
       </c>
       <c r="S222" t="n">
         <v>4212</v>
       </c>
       <c r="T222" t="n">
-        <v>-3.4</v>
+        <v>-5.4</v>
       </c>
       <c r="U222" t="n">
         <v>36300</v>
@@ -15981,22 +15990,22 @@
         <v>136</v>
       </c>
       <c r="L224" t="n">
-        <v>476</v>
+        <v>474.2</v>
       </c>
       <c r="M224" t="n">
         <v>476</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O224" t="n">
-        <v>591.5</v>
+        <v>589.8</v>
       </c>
       <c r="P224" t="n">
         <v>591.5</v>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="R224" t="n">
         <v>686.1</v>
@@ -16044,40 +16053,40 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="G225" t="n">
         <v>874</v>
       </c>
       <c r="H225" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L225" t="n">
-        <v>2955.7</v>
+        <v>2959.7</v>
       </c>
       <c r="M225" t="n">
         <v>2955.7</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O225" t="n">
-        <v>3766.7</v>
+        <v>3772.7</v>
       </c>
       <c r="P225" t="n">
         <v>3766.7</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R225" t="n">
-        <v>4587.8</v>
+        <v>4604.4</v>
       </c>
       <c r="S225" t="n">
         <v>4587.8</v>
       </c>
       <c r="T225" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="U225" t="n">
         <v>48000</v>
@@ -16398,40 +16407,40 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="G230" t="n">
         <v>1864</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L230" t="n">
-        <v>7602</v>
+        <v>7886.2</v>
       </c>
       <c r="M230" t="n">
         <v>7602</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O230" t="n">
-        <v>9271.200000000001</v>
+        <v>9327.299999999999</v>
       </c>
       <c r="P230" t="n">
         <v>9271.200000000001</v>
       </c>
       <c r="Q230" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R230" t="n">
-        <v>10903.7</v>
+        <v>11424</v>
       </c>
       <c r="S230" t="n">
         <v>10903.7</v>
       </c>
       <c r="T230" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U230" t="n">
         <v>140000</v>
@@ -16542,40 +16551,40 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G232" t="n">
         <v>593</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="L232" t="n">
-        <v>2485.8</v>
+        <v>2485.6</v>
       </c>
       <c r="M232" t="n">
         <v>2485.8</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O232" t="n">
-        <v>4550.2</v>
+        <v>4530.6</v>
       </c>
       <c r="P232" t="n">
         <v>4550.2</v>
       </c>
       <c r="Q232" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="R232" t="n">
-        <v>5838.5</v>
+        <v>5778.4</v>
       </c>
       <c r="S232" t="n">
         <v>5779.9</v>
       </c>
       <c r="T232" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="U232" t="n">
         <v>68800</v>
@@ -17532,40 +17541,40 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="G246" t="n">
         <v>777</v>
       </c>
       <c r="H246" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="L246" t="n">
-        <v>2823.7</v>
+        <v>2817.1</v>
       </c>
       <c r="M246" t="n">
         <v>2823.7</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O246" t="n">
-        <v>3537</v>
+        <v>3535.8</v>
       </c>
       <c r="P246" t="n">
         <v>3537</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R246" t="n">
-        <v>4478.6</v>
+        <v>4487.9</v>
       </c>
       <c r="S246" t="n">
         <v>4478.6</v>
       </c>
       <c r="T246" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U246" t="n">
         <v>395000</v>
@@ -18321,7 +18330,7 @@
         <v>-5</v>
       </c>
       <c r="L257" t="n">
-        <v>8298.799999999999</v>
+        <v>8298.6</v>
       </c>
       <c r="M257" t="n">
         <v>8254.1</v>
@@ -18330,7 +18339,7 @@
         <v>0.5</v>
       </c>
       <c r="O257" t="n">
-        <v>39816.5</v>
+        <v>39816.3</v>
       </c>
       <c r="P257" t="n">
         <v>38513.5</v>
@@ -18474,13 +18483,13 @@
         <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>438.4</v>
+        <v>447.6</v>
       </c>
       <c r="P259" t="n">
         <v>438.4</v>
       </c>
       <c r="Q259" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R259" t="n">
         <v>514.6</v>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -642,13 +642,13 @@
         <v>-1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>15290</v>
+        <v>15320</v>
       </c>
       <c r="V3" t="n">
         <v>15540</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="4">
@@ -714,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>78900</v>
+        <v>79400</v>
       </c>
       <c r="V4" t="n">
         <v>81400</v>
       </c>
       <c r="W4" t="n">
-        <v>-3.1</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="5">
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>71800</v>
+        <v>72200</v>
       </c>
       <c r="V5" t="n">
         <v>73400</v>
       </c>
       <c r="W5" t="n">
-        <v>-2.2</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="6">
@@ -858,13 +858,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1370000</v>
+        <v>1356000</v>
       </c>
       <c r="V6" t="n">
         <v>1142000</v>
       </c>
       <c r="W6" t="n">
-        <v>20</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="7">
@@ -930,13 +930,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>55300</v>
+        <v>55000</v>
       </c>
       <c r="V7" t="n">
         <v>53600</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1002,13 +1002,13 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>24450</v>
+        <v>24500</v>
       </c>
       <c r="V8" t="n">
         <v>24550</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9">
@@ -1074,13 +1074,13 @@
         <v>-0.4</v>
       </c>
       <c r="U9" t="n">
-        <v>126000</v>
+        <v>126600</v>
       </c>
       <c r="V9" t="n">
         <v>126500</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1146,13 +1146,13 @@
         <v>0.1</v>
       </c>
       <c r="U10" t="n">
-        <v>90400</v>
+        <v>90700</v>
       </c>
       <c r="V10" t="n">
         <v>92600</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="11">
@@ -1218,13 +1218,13 @@
         <v>0.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1780000</v>
+        <v>1812000</v>
       </c>
       <c r="V11" t="n">
         <v>1647000</v>
       </c>
       <c r="W11" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1290,13 +1290,13 @@
         <v>0.2</v>
       </c>
       <c r="U12" t="n">
-        <v>135700</v>
+        <v>134900</v>
       </c>
       <c r="V12" t="n">
         <v>119700</v>
       </c>
       <c r="W12" t="n">
-        <v>13.4</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="13">
@@ -1362,13 +1362,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>684000</v>
+        <v>686000</v>
       </c>
       <c r="V13" t="n">
         <v>663000</v>
       </c>
       <c r="W13" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>137200</v>
+        <v>137300</v>
       </c>
       <c r="V14" t="n">
         <v>137400</v>
@@ -1506,13 +1506,13 @@
         <v>20</v>
       </c>
       <c r="U15" t="n">
-        <v>108600</v>
+        <v>105800</v>
       </c>
       <c r="V15" t="n">
         <v>89900</v>
       </c>
       <c r="W15" t="n">
-        <v>20.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="16">
@@ -1578,13 +1578,13 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>126900</v>
+        <v>128300</v>
       </c>
       <c r="V16" t="n">
         <v>131400</v>
       </c>
       <c r="W16" t="n">
-        <v>-3.4</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="17">
@@ -1650,13 +1650,13 @@
         <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>41200</v>
+        <v>41450</v>
       </c>
       <c r="V17" t="n">
         <v>42350</v>
       </c>
       <c r="W17" t="n">
-        <v>-2.7</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="18">
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>29150</v>
+        <v>29500</v>
       </c>
       <c r="V18" t="n">
         <v>27400</v>
       </c>
       <c r="W18" t="n">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="19">
@@ -1785,13 +1785,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>50700</v>
+        <v>51300</v>
       </c>
       <c r="V19" t="n">
         <v>51100</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -1839,13 +1839,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>18780</v>
+        <v>18760</v>
       </c>
       <c r="V20" t="n">
         <v>19210</v>
       </c>
       <c r="W20" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="21">
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5830</v>
+        <v>5800</v>
       </c>
       <c r="V22" t="n">
         <v>6080</v>
       </c>
       <c r="W22" t="n">
-        <v>-4.1</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="23">
@@ -2055,13 +2055,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>483500</v>
+        <v>485500</v>
       </c>
       <c r="V23" t="n">
         <v>482000</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="24">
@@ -2127,13 +2127,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>14910</v>
+        <v>14710</v>
       </c>
       <c r="V24" t="n">
         <v>16090</v>
       </c>
       <c r="W24" t="n">
-        <v>-7.3</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="25">
@@ -2199,13 +2199,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>106200</v>
+        <v>107100</v>
       </c>
       <c r="V25" t="n">
         <v>103000</v>
       </c>
       <c r="W25" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2271,13 +2271,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>9300</v>
+        <v>9260</v>
       </c>
       <c r="V26" t="n">
         <v>9350</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27">
@@ -2343,13 +2343,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>8000</v>
+        <v>7970</v>
       </c>
       <c r="V27" t="n">
         <v>8070</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="28">
@@ -2487,13 +2487,13 @@
         <v>-0.7</v>
       </c>
       <c r="U29" t="n">
-        <v>28650</v>
+        <v>28950</v>
       </c>
       <c r="V29" t="n">
         <v>30200</v>
       </c>
       <c r="W29" t="n">
-        <v>-5.1</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="30">
@@ -2559,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>112700</v>
+        <v>112500</v>
       </c>
       <c r="V30" t="n">
         <v>121100</v>
       </c>
       <c r="W30" t="n">
-        <v>-6.9</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="31">
@@ -2631,13 +2631,13 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>188200</v>
+        <v>185300</v>
       </c>
       <c r="V31" t="n">
         <v>183600</v>
       </c>
       <c r="W31" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32">
@@ -2703,13 +2703,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>45800</v>
+        <v>46150</v>
       </c>
       <c r="V32" t="n">
         <v>45700</v>
       </c>
       <c r="W32" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2775,13 +2775,13 @@
         <v>-0.8</v>
       </c>
       <c r="U33" t="n">
-        <v>33550</v>
+        <v>33600</v>
       </c>
       <c r="V33" t="n">
         <v>31500</v>
       </c>
       <c r="W33" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="34">
@@ -2847,13 +2847,13 @@
         <v>0.4</v>
       </c>
       <c r="U34" t="n">
-        <v>385500</v>
+        <v>381000</v>
       </c>
       <c r="V34" t="n">
         <v>382500</v>
       </c>
       <c r="W34" t="n">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="35">
@@ -2919,13 +2919,13 @@
         <v>0.2</v>
       </c>
       <c r="U35" t="n">
-        <v>409500</v>
+        <v>414500</v>
       </c>
       <c r="V35" t="n">
         <v>430000</v>
       </c>
       <c r="W35" t="n">
-        <v>-4.8</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="36">
@@ -2991,13 +2991,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>25000</v>
+        <v>25050</v>
       </c>
       <c r="V36" t="n">
         <v>24750</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="37">
@@ -3063,13 +3063,13 @@
         <v>-1.7</v>
       </c>
       <c r="U37" t="n">
-        <v>97200</v>
+        <v>97600</v>
       </c>
       <c r="V37" t="n">
         <v>98300</v>
       </c>
       <c r="W37" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="38">
@@ -3135,13 +3135,13 @@
         <v>-0</v>
       </c>
       <c r="U38" t="n">
-        <v>381000</v>
+        <v>382500</v>
       </c>
       <c r="V38" t="n">
         <v>383500</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="39">
@@ -3207,13 +3207,13 @@
         <v>0.6</v>
       </c>
       <c r="U39" t="n">
-        <v>332000</v>
+        <v>334000</v>
       </c>
       <c r="V39" t="n">
         <v>337000</v>
       </c>
       <c r="W39" t="n">
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="40">
@@ -3270,13 +3270,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>189100</v>
+        <v>191700</v>
       </c>
       <c r="V40" t="n">
         <v>195700</v>
       </c>
       <c r="W40" t="n">
-        <v>-3.4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="41">
@@ -3342,13 +3342,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>52100</v>
+        <v>52200</v>
       </c>
       <c r="V41" t="n">
         <v>51400</v>
       </c>
       <c r="W41" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="42">
@@ -3414,13 +3414,13 @@
         <v>-0.1</v>
       </c>
       <c r="U42" t="n">
-        <v>257500</v>
+        <v>259500</v>
       </c>
       <c r="V42" t="n">
         <v>255500</v>
       </c>
       <c r="W42" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="43">
@@ -3480,13 +3480,13 @@
         <v>-0.4</v>
       </c>
       <c r="U43" t="n">
-        <v>26200</v>
+        <v>26300</v>
       </c>
       <c r="V43" t="n">
         <v>26650</v>
       </c>
       <c r="W43" t="n">
-        <v>-1.7</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="44">
@@ -3522,13 +3522,13 @@
         <v>932</v>
       </c>
       <c r="U44" t="n">
-        <v>8330</v>
+        <v>8240</v>
       </c>
       <c r="V44" t="n">
         <v>7520</v>
       </c>
       <c r="W44" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="45">
@@ -3666,13 +3666,13 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>312000</v>
+        <v>319500</v>
       </c>
       <c r="V46" t="n">
         <v>299500</v>
       </c>
       <c r="W46" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="47">
@@ -3738,13 +3738,13 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>129400</v>
+        <v>128300</v>
       </c>
       <c r="V47" t="n">
         <v>127600</v>
       </c>
       <c r="W47" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
@@ -3810,13 +3810,13 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>38250</v>
+        <v>38500</v>
       </c>
       <c r="V48" t="n">
         <v>34250</v>
       </c>
       <c r="W48" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="49">
@@ -3882,13 +3882,13 @@
         <v>0.7</v>
       </c>
       <c r="U49" t="n">
-        <v>548000</v>
+        <v>545000</v>
       </c>
       <c r="V49" t="n">
         <v>548000</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="50">
@@ -3954,13 +3954,13 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>100600</v>
+        <v>102200</v>
       </c>
       <c r="V50" t="n">
         <v>96700</v>
       </c>
       <c r="W50" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="51">
@@ -4020,13 +4020,13 @@
         <v>1.2</v>
       </c>
       <c r="U51" t="n">
-        <v>33650</v>
+        <v>33450</v>
       </c>
       <c r="V51" t="n">
         <v>34450</v>
       </c>
       <c r="W51" t="n">
-        <v>-2.3</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="52">
@@ -4092,13 +4092,13 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>24950</v>
+        <v>25050</v>
       </c>
       <c r="V52" t="n">
         <v>25400</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.8</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="53">
@@ -4164,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>46550</v>
+        <v>46800</v>
       </c>
       <c r="V53" t="n">
         <v>45100</v>
       </c>
       <c r="W53" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="54">
@@ -4236,13 +4236,13 @@
         <v>3.2</v>
       </c>
       <c r="U54" t="n">
-        <v>109700</v>
+        <v>109900</v>
       </c>
       <c r="V54" t="n">
         <v>111100</v>
       </c>
       <c r="W54" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="55">
@@ -4308,13 +4308,13 @@
         <v>-22.7</v>
       </c>
       <c r="U55" t="n">
-        <v>50900</v>
+        <v>51100</v>
       </c>
       <c r="V55" t="n">
         <v>51000</v>
       </c>
       <c r="W55" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="56">
@@ -4380,13 +4380,13 @@
         <v>0.5</v>
       </c>
       <c r="U56" t="n">
-        <v>41250</v>
+        <v>41100</v>
       </c>
       <c r="V56" t="n">
         <v>42200</v>
       </c>
       <c r="W56" t="n">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="57">
@@ -4452,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1387000</v>
+        <v>1400000</v>
       </c>
       <c r="V57" t="n">
         <v>1401000</v>
       </c>
       <c r="W57" t="n">
-        <v>-1</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="58">
@@ -4524,13 +4524,13 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>39400</v>
+        <v>39350</v>
       </c>
       <c r="V58" t="n">
         <v>37400</v>
       </c>
       <c r="W58" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="59">
@@ -4596,13 +4596,13 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>363000</v>
+        <v>365500</v>
       </c>
       <c r="V59" t="n">
         <v>348500</v>
       </c>
       <c r="W59" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="60">
@@ -4668,13 +4668,13 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>30100</v>
+        <v>29800</v>
       </c>
       <c r="V60" t="n">
         <v>30050</v>
       </c>
       <c r="W60" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="61">
@@ -4740,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>218000</v>
+        <v>218500</v>
       </c>
       <c r="V61" t="n">
         <v>227500</v>
       </c>
       <c r="W61" t="n">
-        <v>-4.2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="62">
@@ -4812,13 +4812,13 @@
         <v>1.2</v>
       </c>
       <c r="U62" t="n">
-        <v>202500</v>
+        <v>204500</v>
       </c>
       <c r="V62" t="n">
         <v>195300</v>
       </c>
       <c r="W62" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="63">
@@ -4884,13 +4884,13 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1181000</v>
+        <v>1179000</v>
       </c>
       <c r="V63" t="n">
         <v>1222000</v>
       </c>
       <c r="W63" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="64">
@@ -5028,13 +5028,13 @@
         <v>-1.9</v>
       </c>
       <c r="U65" t="n">
-        <v>15850</v>
+        <v>15770</v>
       </c>
       <c r="V65" t="n">
         <v>15740</v>
       </c>
       <c r="W65" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="66">
@@ -5100,13 +5100,13 @@
         <v>1.6</v>
       </c>
       <c r="U66" t="n">
-        <v>152800</v>
+        <v>150000</v>
       </c>
       <c r="V66" t="n">
         <v>157300</v>
       </c>
       <c r="W66" t="n">
-        <v>-2.9</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="67">
@@ -5172,13 +5172,13 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>540000</v>
+        <v>543000</v>
       </c>
       <c r="V67" t="n">
         <v>562000</v>
       </c>
       <c r="W67" t="n">
-        <v>-3.9</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="68">
@@ -5244,13 +5244,13 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>63800</v>
+        <v>65500</v>
       </c>
       <c r="V68" t="n">
         <v>60000</v>
       </c>
       <c r="W68" t="n">
-        <v>6.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5316,13 +5316,13 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>20700</v>
+        <v>20850</v>
       </c>
       <c r="V69" t="n">
         <v>21050</v>
       </c>
       <c r="W69" t="n">
-        <v>-1.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="70">
@@ -5388,13 +5388,13 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>57200</v>
+        <v>57400</v>
       </c>
       <c r="V70" t="n">
         <v>57600</v>
       </c>
       <c r="W70" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="71">
@@ -5460,13 +5460,13 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>124300</v>
+        <v>124900</v>
       </c>
       <c r="V71" t="n">
         <v>125900</v>
       </c>
       <c r="W71" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="72">
@@ -5532,13 +5532,13 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>89500</v>
+        <v>89600</v>
       </c>
       <c r="V72" t="n">
         <v>84300</v>
       </c>
       <c r="W72" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="73">
@@ -5604,13 +5604,13 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>16460</v>
+        <v>16180</v>
       </c>
       <c r="V73" t="n">
         <v>16110</v>
       </c>
       <c r="W73" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="74">
@@ -5676,13 +5676,13 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>417000</v>
+        <v>415500</v>
       </c>
       <c r="V74" t="n">
         <v>422000</v>
       </c>
       <c r="W74" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="75">
@@ -5748,13 +5748,13 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>1071000</v>
+        <v>1081000</v>
       </c>
       <c r="V75" t="n">
         <v>1055000</v>
       </c>
       <c r="W75" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="76">
@@ -5820,13 +5820,13 @@
         <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>81600</v>
+        <v>81400</v>
       </c>
       <c r="V76" t="n">
         <v>79200</v>
       </c>
       <c r="W76" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="77">
@@ -5892,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>35325</v>
+        <v>34300</v>
       </c>
       <c r="V77" t="n">
         <v>30850</v>
       </c>
       <c r="W77" t="n">
-        <v>14.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="78">
@@ -5964,13 +5964,13 @@
         <v>-0.9</v>
       </c>
       <c r="U78" t="n">
-        <v>198000</v>
+        <v>200000</v>
       </c>
       <c r="V78" t="n">
         <v>193100</v>
       </c>
       <c r="W78" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="79">
@@ -6027,13 +6027,13 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>2515</v>
+        <v>2530</v>
       </c>
       <c r="V79" t="n">
         <v>2555</v>
       </c>
       <c r="W79" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
@@ -6099,13 +6099,13 @@
         <v>-1.8</v>
       </c>
       <c r="U80" t="n">
-        <v>33350</v>
+        <v>33100</v>
       </c>
       <c r="V80" t="n">
         <v>32150</v>
       </c>
       <c r="W80" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -6165,13 +6165,13 @@
         <v>0.3</v>
       </c>
       <c r="U81" t="n">
-        <v>87300</v>
+        <v>87400</v>
       </c>
       <c r="V81" t="n">
         <v>86800</v>
       </c>
       <c r="W81" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="82">
@@ -6237,13 +6237,13 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>90600</v>
+        <v>90900</v>
       </c>
       <c r="V82" t="n">
         <v>92500</v>
       </c>
       <c r="W82" t="n">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="83">
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>74500</v>
+        <v>74300</v>
       </c>
       <c r="V83" t="n">
         <v>74900</v>
       </c>
       <c r="W83" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="84">
@@ -6381,13 +6381,13 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>21850</v>
+        <v>21700</v>
       </c>
       <c r="V84" t="n">
         <v>22550</v>
       </c>
       <c r="W84" t="n">
-        <v>-3.1</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="85">
@@ -6453,13 +6453,13 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>221750</v>
+        <v>222500</v>
       </c>
       <c r="V85" t="n">
         <v>238000</v>
       </c>
       <c r="W85" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="86">
@@ -6525,13 +6525,13 @@
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>3465</v>
+        <v>3520</v>
       </c>
       <c r="V86" t="n">
         <v>3525</v>
       </c>
       <c r="W86" t="n">
-        <v>-1.7</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="87">
@@ -6597,13 +6597,13 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>95400</v>
+        <v>95200</v>
       </c>
       <c r="V87" t="n">
         <v>99400</v>
       </c>
       <c r="W87" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="88">
@@ -6669,13 +6669,13 @@
         <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>21650</v>
+        <v>22150</v>
       </c>
       <c r="V88" t="n">
         <v>21650</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="89">
@@ -6741,13 +6741,13 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>28700</v>
+        <v>28300</v>
       </c>
       <c r="V89" t="n">
         <v>26150</v>
       </c>
       <c r="W89" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -6813,13 +6813,13 @@
         <v>0.4</v>
       </c>
       <c r="U90" t="n">
-        <v>112900</v>
+        <v>112000</v>
       </c>
       <c r="V90" t="n">
         <v>107500</v>
       </c>
       <c r="W90" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="91">
@@ -6885,13 +6885,13 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>20700</v>
+        <v>20850</v>
       </c>
       <c r="V91" t="n">
         <v>20700</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="92">
@@ -6957,13 +6957,13 @@
         <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>50900</v>
+        <v>51000</v>
       </c>
       <c r="V92" t="n">
         <v>45850</v>
       </c>
       <c r="W92" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="93">
@@ -7029,13 +7029,13 @@
         <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>366000</v>
+        <v>367000</v>
       </c>
       <c r="V93" t="n">
         <v>367000</v>
       </c>
       <c r="W93" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -7101,13 +7101,13 @@
         <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>6100</v>
+        <v>6030</v>
       </c>
       <c r="V94" t="n">
         <v>5960</v>
       </c>
       <c r="W94" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="95">
@@ -7167,13 +7167,13 @@
         <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>45450</v>
+        <v>45500</v>
       </c>
       <c r="V95" t="n">
         <v>46150</v>
       </c>
       <c r="W95" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="96">
@@ -7239,13 +7239,13 @@
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>18970</v>
+        <v>18910</v>
       </c>
       <c r="V96" t="n">
         <v>18930</v>
       </c>
       <c r="W96" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="97">
@@ -7311,13 +7311,13 @@
         <v>0.5</v>
       </c>
       <c r="U97" t="n">
-        <v>52600</v>
+        <v>52700</v>
       </c>
       <c r="V97" t="n">
         <v>54300</v>
       </c>
       <c r="W97" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="98">
@@ -7356,13 +7356,13 @@
         <v>-2.3</v>
       </c>
       <c r="U98" t="n">
-        <v>12150</v>
+        <v>12050</v>
       </c>
       <c r="V98" t="n">
         <v>12530</v>
       </c>
       <c r="W98" t="n">
-        <v>-3</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="99">
@@ -7428,13 +7428,13 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>14740</v>
+        <v>14890</v>
       </c>
       <c r="V99" t="n">
         <v>14760</v>
       </c>
       <c r="W99" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="100">
@@ -7500,13 +7500,13 @@
         <v>0</v>
       </c>
       <c r="U100" t="n">
-        <v>304500</v>
+        <v>307500</v>
       </c>
       <c r="V100" t="n">
         <v>297500</v>
       </c>
       <c r="W100" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="101">
@@ -7572,13 +7572,13 @@
         <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>17000</v>
+        <v>16790</v>
       </c>
       <c r="V101" t="n">
         <v>17160</v>
       </c>
       <c r="W101" t="n">
-        <v>-0.9</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="102">
@@ -7644,13 +7644,13 @@
         <v>-0.2</v>
       </c>
       <c r="U102" t="n">
-        <v>171100</v>
+        <v>171800</v>
       </c>
       <c r="V102" t="n">
         <v>172500</v>
       </c>
       <c r="W102" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="103">
@@ -7716,13 +7716,13 @@
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>89900</v>
+        <v>90800</v>
       </c>
       <c r="V103" t="n">
         <v>79200</v>
       </c>
       <c r="W103" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="104">
@@ -7788,13 +7788,13 @@
         <v>1.9</v>
       </c>
       <c r="U104" t="n">
-        <v>8810</v>
+        <v>8900</v>
       </c>
       <c r="V104" t="n">
         <v>9130</v>
       </c>
       <c r="W104" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="105">
@@ -7860,13 +7860,13 @@
         <v>-0.1</v>
       </c>
       <c r="U105" t="n">
-        <v>9780</v>
+        <v>9930</v>
       </c>
       <c r="V105" t="n">
         <v>10090</v>
       </c>
       <c r="W105" t="n">
-        <v>-3.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="106">
@@ -7932,13 +7932,13 @@
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>579000</v>
+        <v>585000</v>
       </c>
       <c r="V106" t="n">
         <v>573000</v>
       </c>
       <c r="W106" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="107">
@@ -8004,13 +8004,13 @@
         <v>5.2</v>
       </c>
       <c r="U107" t="n">
-        <v>14700</v>
+        <v>14800</v>
       </c>
       <c r="V107" t="n">
         <v>14750</v>
       </c>
       <c r="W107" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="108">
@@ -8076,13 +8076,13 @@
         <v>-0</v>
       </c>
       <c r="U108" t="n">
-        <v>204500</v>
+        <v>206500</v>
       </c>
       <c r="V108" t="n">
         <v>213500</v>
       </c>
       <c r="W108" t="n">
-        <v>-4.2</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="109">
@@ -8148,13 +8148,13 @@
         <v>0</v>
       </c>
       <c r="U109" t="n">
-        <v>34550</v>
+        <v>34500</v>
       </c>
       <c r="V109" t="n">
         <v>36200</v>
       </c>
       <c r="W109" t="n">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="110">
@@ -8220,13 +8220,13 @@
         <v>0</v>
       </c>
       <c r="U110" t="n">
-        <v>34400</v>
+        <v>35000</v>
       </c>
       <c r="V110" t="n">
         <v>33050</v>
       </c>
       <c r="W110" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="111">
@@ -8292,13 +8292,13 @@
         <v>-0.1</v>
       </c>
       <c r="U111" t="n">
-        <v>39450</v>
+        <v>39350</v>
       </c>
       <c r="V111" t="n">
         <v>39300</v>
       </c>
       <c r="W111" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="112">
@@ -8364,13 +8364,13 @@
         <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>8980</v>
+        <v>9010</v>
       </c>
       <c r="V112" t="n">
         <v>8910</v>
       </c>
       <c r="W112" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="113">
@@ -8436,13 +8436,13 @@
         <v>-0.5</v>
       </c>
       <c r="U113" t="n">
-        <v>36550</v>
+        <v>37000</v>
       </c>
       <c r="V113" t="n">
         <v>35100</v>
       </c>
       <c r="W113" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="114">
@@ -8508,13 +8508,13 @@
         <v>-3.5</v>
       </c>
       <c r="U114" t="n">
-        <v>206500</v>
+        <v>205500</v>
       </c>
       <c r="V114" t="n">
         <v>222000</v>
       </c>
       <c r="W114" t="n">
-        <v>-7</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="115">
@@ -8580,13 +8580,13 @@
         <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>219500</v>
+        <v>209000</v>
       </c>
       <c r="V115" t="n">
         <v>178300</v>
       </c>
       <c r="W115" t="n">
-        <v>23.1</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="116">
@@ -8652,13 +8652,13 @@
         <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>33200</v>
+        <v>33250</v>
       </c>
       <c r="V116" t="n">
         <v>32500</v>
       </c>
       <c r="W116" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="117">
@@ -8718,13 +8718,13 @@
         <v>0.6</v>
       </c>
       <c r="U117" t="n">
-        <v>275500</v>
+        <v>278000</v>
       </c>
       <c r="V117" t="n">
         <v>270500</v>
       </c>
       <c r="W117" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="118">
@@ -8790,13 +8790,13 @@
         <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>10930</v>
+        <v>11110</v>
       </c>
       <c r="V118" t="n">
         <v>10910</v>
       </c>
       <c r="W118" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="119">
@@ -8862,13 +8862,13 @@
         <v>0.1</v>
       </c>
       <c r="U119" t="n">
-        <v>83600</v>
+        <v>84000</v>
       </c>
       <c r="V119" t="n">
         <v>79000</v>
       </c>
       <c r="W119" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="120">
@@ -8934,13 +8934,13 @@
         <v>-0.1</v>
       </c>
       <c r="U120" t="n">
-        <v>85700</v>
+        <v>85600</v>
       </c>
       <c r="V120" t="n">
         <v>86800</v>
       </c>
       <c r="W120" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="121">
@@ -9006,13 +9006,13 @@
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>232500</v>
+        <v>231000</v>
       </c>
       <c r="V121" t="n">
         <v>230000</v>
       </c>
       <c r="W121" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="122">
@@ -9078,13 +9078,13 @@
         <v>-1.4</v>
       </c>
       <c r="U122" t="n">
-        <v>19690</v>
+        <v>19890</v>
       </c>
       <c r="V122" t="n">
         <v>16850</v>
       </c>
       <c r="W122" t="n">
-        <v>16.9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123">
@@ -9150,13 +9150,13 @@
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>57600</v>
+        <v>57700</v>
       </c>
       <c r="V123" t="n">
         <v>54700</v>
       </c>
       <c r="W123" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="124">
@@ -9222,13 +9222,13 @@
         <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>131500</v>
+        <v>130500</v>
       </c>
       <c r="V124" t="n">
         <v>126500</v>
       </c>
       <c r="W124" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="125">
@@ -9294,13 +9294,13 @@
         <v>-2.7</v>
       </c>
       <c r="U125" t="n">
-        <v>22950</v>
+        <v>22850</v>
       </c>
       <c r="V125" t="n">
         <v>23700</v>
       </c>
       <c r="W125" t="n">
-        <v>-3.2</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="126">
@@ -9366,13 +9366,13 @@
         <v>3.9</v>
       </c>
       <c r="U126" t="n">
-        <v>48800</v>
+        <v>49300</v>
       </c>
       <c r="V126" t="n">
         <v>45800</v>
       </c>
       <c r="W126" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="127">
@@ -9438,13 +9438,13 @@
         <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>292000</v>
+        <v>291000</v>
       </c>
       <c r="V127" t="n">
         <v>294000</v>
       </c>
       <c r="W127" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="128">
@@ -9510,13 +9510,13 @@
         <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>270500</v>
+        <v>273000</v>
       </c>
       <c r="V128" t="n">
         <v>282000</v>
       </c>
       <c r="W128" t="n">
-        <v>-4.1</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="129">
@@ -9582,13 +9582,13 @@
         <v>-0.4</v>
       </c>
       <c r="U129" t="n">
-        <v>145900</v>
+        <v>152000</v>
       </c>
       <c r="V129" t="n">
         <v>107600</v>
       </c>
       <c r="W129" t="n">
-        <v>35.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="130">
@@ -9654,13 +9654,13 @@
         <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>112300</v>
+        <v>112900</v>
       </c>
       <c r="V130" t="n">
         <v>110300</v>
       </c>
       <c r="W130" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="131">
@@ -9726,13 +9726,13 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>94200</v>
+        <v>96800</v>
       </c>
       <c r="V131" t="n">
         <v>94200</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="132">
@@ -9789,13 +9789,13 @@
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>40050</v>
+        <v>39900</v>
       </c>
       <c r="V132" t="n">
         <v>40150</v>
       </c>
       <c r="W132" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="133">
@@ -9861,13 +9861,13 @@
         <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>194700</v>
+        <v>198600</v>
       </c>
       <c r="V133" t="n">
         <v>191700</v>
       </c>
       <c r="W133" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="134">
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>123800</v>
+        <v>124100</v>
       </c>
       <c r="V134" t="n">
         <v>126800</v>
       </c>
       <c r="W134" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="135">
@@ -10005,13 +10005,13 @@
         <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>71500</v>
+        <v>71900</v>
       </c>
       <c r="V135" t="n">
         <v>74100</v>
       </c>
       <c r="W135" t="n">
-        <v>-3.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="136">
@@ -10077,13 +10077,13 @@
         <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>26800</v>
+        <v>26850</v>
       </c>
       <c r="V136" t="n">
         <v>26250</v>
       </c>
       <c r="W136" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="137">
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>199550</v>
+        <v>199500</v>
       </c>
       <c r="V137" t="n">
         <v>201500</v>
@@ -10221,13 +10221,13 @@
         <v>0.3</v>
       </c>
       <c r="U138" t="n">
-        <v>120400</v>
+        <v>120000</v>
       </c>
       <c r="V138" t="n">
         <v>121300</v>
       </c>
       <c r="W138" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="139">
@@ -10293,13 +10293,13 @@
         <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>37050</v>
+        <v>37100</v>
       </c>
       <c r="V139" t="n">
         <v>38050</v>
       </c>
       <c r="W139" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="140">
@@ -10437,13 +10437,13 @@
         <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>16460</v>
+        <v>16430</v>
       </c>
       <c r="V141" t="n">
         <v>16320</v>
       </c>
       <c r="W141" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="142">
@@ -10509,13 +10509,13 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>111500</v>
+        <v>111900</v>
       </c>
       <c r="V142" t="n">
         <v>116100</v>
       </c>
       <c r="W142" t="n">
-        <v>-4</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="143">
@@ -10581,13 +10581,13 @@
         <v>0.5</v>
       </c>
       <c r="U143" t="n">
-        <v>99600</v>
+        <v>99000</v>
       </c>
       <c r="V143" t="n">
         <v>96200</v>
       </c>
       <c r="W143" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="144">
@@ -10653,13 +10653,13 @@
         <v>-0.5</v>
       </c>
       <c r="U144" t="n">
-        <v>192400</v>
+        <v>193600</v>
       </c>
       <c r="V144" t="n">
         <v>188800</v>
       </c>
       <c r="W144" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="145">
@@ -10725,13 +10725,13 @@
         <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>74800</v>
+        <v>74700</v>
       </c>
       <c r="V145" t="n">
         <v>75600</v>
       </c>
       <c r="W145" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="146">
@@ -10797,13 +10797,13 @@
         <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>53100</v>
+        <v>52500</v>
       </c>
       <c r="V146" t="n">
         <v>50200</v>
       </c>
       <c r="W146" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="147">
@@ -10869,13 +10869,13 @@
         <v>0.5</v>
       </c>
       <c r="U147" t="n">
-        <v>7400</v>
+        <v>7370</v>
       </c>
       <c r="V147" t="n">
         <v>7180</v>
       </c>
       <c r="W147" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="148">
@@ -10914,13 +10914,13 @@
         <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>10570</v>
+        <v>10390</v>
       </c>
       <c r="V148" t="n">
         <v>10280</v>
       </c>
       <c r="W148" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="149">
@@ -10959,13 +10959,13 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>10170</v>
+        <v>10030</v>
       </c>
       <c r="V149" t="n">
         <v>10060</v>
       </c>
       <c r="W149" t="n">
-        <v>1.1</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="150">
@@ -11031,13 +11031,13 @@
         <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>25600</v>
+        <v>24800</v>
       </c>
       <c r="V150" t="n">
         <v>23550</v>
       </c>
       <c r="W150" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="151">
@@ -11103,13 +11103,13 @@
         <v>0</v>
       </c>
       <c r="U151" t="n">
-        <v>117400</v>
+        <v>119000</v>
       </c>
       <c r="V151" t="n">
         <v>123900</v>
       </c>
       <c r="W151" t="n">
-        <v>-5.2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="152">
@@ -11175,13 +11175,13 @@
         <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>679000</v>
+        <v>678000</v>
       </c>
       <c r="V152" t="n">
         <v>652000</v>
       </c>
       <c r="W152" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
@@ -11220,13 +11220,13 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>9560</v>
+        <v>9480</v>
       </c>
       <c r="V153" t="n">
         <v>8970</v>
       </c>
       <c r="W153" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="154">
@@ -11292,13 +11292,13 @@
         <v>0.5</v>
       </c>
       <c r="U154" t="n">
-        <v>39600</v>
+        <v>39950</v>
       </c>
       <c r="V154" t="n">
         <v>41400</v>
       </c>
       <c r="W154" t="n">
-        <v>-4.3</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="155">
@@ -11364,13 +11364,13 @@
         <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>50100</v>
+        <v>50300</v>
       </c>
       <c r="V155" t="n">
         <v>45600</v>
       </c>
       <c r="W155" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="156">
@@ -11436,13 +11436,13 @@
         <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>206000</v>
+        <v>208500</v>
       </c>
       <c r="V156" t="n">
         <v>206000</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="157">
@@ -11508,13 +11508,13 @@
         <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>136900</v>
+        <v>137800</v>
       </c>
       <c r="V157" t="n">
         <v>134300</v>
       </c>
       <c r="W157" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="158">
@@ -11580,13 +11580,13 @@
         <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>5900</v>
+        <v>5990</v>
       </c>
       <c r="V158" t="n">
         <v>5740</v>
       </c>
       <c r="W158" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="159">
@@ -11652,13 +11652,13 @@
         <v>0</v>
       </c>
       <c r="U159" t="n">
-        <v>48900</v>
+        <v>49300</v>
       </c>
       <c r="V159" t="n">
         <v>50900</v>
       </c>
       <c r="W159" t="n">
-        <v>-3.9</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="160">
@@ -11724,13 +11724,13 @@
         <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>48700</v>
+        <v>48650</v>
       </c>
       <c r="V160" t="n">
         <v>52800</v>
       </c>
       <c r="W160" t="n">
-        <v>-7.8</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="161">
@@ -11796,13 +11796,13 @@
         <v>0.2</v>
       </c>
       <c r="U161" t="n">
-        <v>137200</v>
+        <v>140500</v>
       </c>
       <c r="V161" t="n">
         <v>143300</v>
       </c>
       <c r="W161" t="n">
-        <v>-4.3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="162">
@@ -11841,13 +11841,13 @@
         <v>0</v>
       </c>
       <c r="U162" t="n">
-        <v>13420</v>
+        <v>13310</v>
       </c>
       <c r="V162" t="n">
         <v>12500</v>
       </c>
       <c r="W162" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="163">
@@ -11913,13 +11913,13 @@
         <v>-1.1</v>
       </c>
       <c r="U163" t="n">
-        <v>17790</v>
+        <v>17890</v>
       </c>
       <c r="V163" t="n">
         <v>17910</v>
       </c>
       <c r="W163" t="n">
-        <v>-0.7</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="164">
@@ -11985,13 +11985,13 @@
         <v>0</v>
       </c>
       <c r="U164" t="n">
-        <v>31300</v>
+        <v>31550</v>
       </c>
       <c r="V164" t="n">
         <v>31900</v>
       </c>
       <c r="W164" t="n">
-        <v>-1.9</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="165">
@@ -12057,13 +12057,13 @@
         <v>0</v>
       </c>
       <c r="U165" t="n">
-        <v>144200</v>
+        <v>144800</v>
       </c>
       <c r="V165" t="n">
         <v>138300</v>
       </c>
       <c r="W165" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="166">
@@ -12129,13 +12129,13 @@
         <v>-1.3</v>
       </c>
       <c r="U166" t="n">
-        <v>179200</v>
+        <v>179700</v>
       </c>
       <c r="V166" t="n">
         <v>183400</v>
       </c>
       <c r="W166" t="n">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="167">
@@ -12201,13 +12201,13 @@
         <v>0</v>
       </c>
       <c r="U167" t="n">
-        <v>16470</v>
+        <v>16550</v>
       </c>
       <c r="V167" t="n">
         <v>16470</v>
       </c>
       <c r="W167" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="168">
@@ -12273,13 +12273,13 @@
         <v>0</v>
       </c>
       <c r="U168" t="n">
-        <v>71100</v>
+        <v>70300</v>
       </c>
       <c r="V168" t="n">
         <v>70700</v>
       </c>
       <c r="W168" t="n">
-        <v>0.6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="169">
@@ -12345,13 +12345,13 @@
         <v>0.6</v>
       </c>
       <c r="U169" t="n">
-        <v>77400</v>
+        <v>77500</v>
       </c>
       <c r="V169" t="n">
         <v>78400</v>
       </c>
       <c r="W169" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="170">
@@ -12417,13 +12417,13 @@
         <v>0</v>
       </c>
       <c r="U170" t="n">
-        <v>177100</v>
+        <v>177900</v>
       </c>
       <c r="V170" t="n">
         <v>172000</v>
       </c>
       <c r="W170" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="171">
@@ -12489,13 +12489,13 @@
         <v>0</v>
       </c>
       <c r="U171" t="n">
-        <v>324000</v>
+        <v>323500</v>
       </c>
       <c r="V171" t="n">
         <v>304500</v>
       </c>
       <c r="W171" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="172">
@@ -12561,13 +12561,13 @@
         <v>0</v>
       </c>
       <c r="U172" t="n">
-        <v>72500</v>
+        <v>72900</v>
       </c>
       <c r="V172" t="n">
         <v>75000</v>
       </c>
       <c r="W172" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="173">
@@ -12633,13 +12633,13 @@
         <v>0</v>
       </c>
       <c r="U173" t="n">
-        <v>52500</v>
+        <v>52800</v>
       </c>
       <c r="V173" t="n">
         <v>46950</v>
       </c>
       <c r="W173" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="174">
@@ -12750,13 +12750,13 @@
         <v>0</v>
       </c>
       <c r="U175" t="n">
-        <v>57500</v>
+        <v>57400</v>
       </c>
       <c r="V175" t="n">
         <v>55800</v>
       </c>
       <c r="W175" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="176">
@@ -12822,13 +12822,13 @@
         <v>0.3</v>
       </c>
       <c r="U176" t="n">
-        <v>43500</v>
+        <v>43400</v>
       </c>
       <c r="V176" t="n">
         <v>41950</v>
       </c>
       <c r="W176" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="177">
@@ -12894,13 +12894,13 @@
         <v>0</v>
       </c>
       <c r="U177" t="n">
-        <v>462500</v>
+        <v>464000</v>
       </c>
       <c r="V177" t="n">
         <v>473500</v>
       </c>
       <c r="W177" t="n">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="178">
@@ -12966,13 +12966,13 @@
         <v>0</v>
       </c>
       <c r="U178" t="n">
-        <v>129200</v>
+        <v>128400</v>
       </c>
       <c r="V178" t="n">
         <v>135500</v>
       </c>
       <c r="W178" t="n">
-        <v>-4.6</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="179">
@@ -13038,13 +13038,13 @@
         <v>0</v>
       </c>
       <c r="U179" t="n">
-        <v>16120</v>
+        <v>15930</v>
       </c>
       <c r="V179" t="n">
         <v>15390</v>
       </c>
       <c r="W179" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="180">
@@ -13110,13 +13110,13 @@
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>18430</v>
+        <v>18450</v>
       </c>
       <c r="V180" t="n">
         <v>18120</v>
       </c>
       <c r="W180" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="181">
@@ -13182,13 +13182,13 @@
         <v>-0.2</v>
       </c>
       <c r="U181" t="n">
-        <v>73500</v>
+        <v>73700</v>
       </c>
       <c r="V181" t="n">
         <v>73500</v>
       </c>
       <c r="W181" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="182">
@@ -13245,13 +13245,13 @@
         <v>0</v>
       </c>
       <c r="U182" t="n">
-        <v>83900</v>
+        <v>85200</v>
       </c>
       <c r="V182" t="n">
         <v>92000</v>
       </c>
       <c r="W182" t="n">
-        <v>-8.800000000000001</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="183">
@@ -13317,13 +13317,13 @@
         <v>0</v>
       </c>
       <c r="U183" t="n">
-        <v>231500</v>
+        <v>231000</v>
       </c>
       <c r="V183" t="n">
         <v>244000</v>
       </c>
       <c r="W183" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="184">
@@ -13389,13 +13389,13 @@
         <v>0</v>
       </c>
       <c r="U184" t="n">
-        <v>37250</v>
+        <v>37850</v>
       </c>
       <c r="V184" t="n">
         <v>37550</v>
       </c>
       <c r="W184" t="n">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="185">
@@ -13434,13 +13434,13 @@
         <v>0</v>
       </c>
       <c r="U185" t="n">
-        <v>9010</v>
+        <v>8980</v>
       </c>
       <c r="V185" t="n">
         <v>9440</v>
       </c>
       <c r="W185" t="n">
-        <v>-4.6</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="186">
@@ -13578,13 +13578,13 @@
         <v>0</v>
       </c>
       <c r="U187" t="n">
-        <v>140400</v>
+        <v>141300</v>
       </c>
       <c r="V187" t="n">
         <v>145800</v>
       </c>
       <c r="W187" t="n">
-        <v>-3.7</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="188">
@@ -13650,13 +13650,13 @@
         <v>0</v>
       </c>
       <c r="U188" t="n">
-        <v>35950</v>
+        <v>36250</v>
       </c>
       <c r="V188" t="n">
         <v>36950</v>
       </c>
       <c r="W188" t="n">
-        <v>-2.7</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="189">
@@ -13722,13 +13722,13 @@
         <v>0.5</v>
       </c>
       <c r="U189" t="n">
-        <v>31650</v>
+        <v>31750</v>
       </c>
       <c r="V189" t="n">
         <v>31000</v>
       </c>
       <c r="W189" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="190">
@@ -13866,13 +13866,13 @@
         <v>0</v>
       </c>
       <c r="U191" t="n">
-        <v>64600</v>
+        <v>63400</v>
       </c>
       <c r="V191" t="n">
         <v>63100</v>
       </c>
       <c r="W191" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="192">
@@ -13938,13 +13938,13 @@
         <v>0</v>
       </c>
       <c r="U192" t="n">
-        <v>57100</v>
+        <v>58100</v>
       </c>
       <c r="V192" t="n">
         <v>57200</v>
       </c>
       <c r="W192" t="n">
-        <v>-0.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="193">
@@ -14082,13 +14082,13 @@
         <v>0</v>
       </c>
       <c r="U194" t="n">
-        <v>40575</v>
+        <v>40700</v>
       </c>
       <c r="V194" t="n">
         <v>42050</v>
       </c>
       <c r="W194" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="195">
@@ -14154,13 +14154,13 @@
         <v>0</v>
       </c>
       <c r="U195" t="n">
-        <v>49550</v>
+        <v>49750</v>
       </c>
       <c r="V195" t="n">
         <v>48500</v>
       </c>
       <c r="W195" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="196">
@@ -14226,13 +14226,13 @@
         <v>0</v>
       </c>
       <c r="U196" t="n">
-        <v>1401000</v>
+        <v>1415000</v>
       </c>
       <c r="V196" t="n">
         <v>1447000</v>
       </c>
       <c r="W196" t="n">
-        <v>-3.2</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="197">
@@ -14298,13 +14298,13 @@
         <v>0</v>
       </c>
       <c r="U197" t="n">
-        <v>31850</v>
+        <v>32050</v>
       </c>
       <c r="V197" t="n">
         <v>31800</v>
       </c>
       <c r="W197" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="198">
@@ -14370,13 +14370,13 @@
         <v>0</v>
       </c>
       <c r="U198" t="n">
-        <v>339000</v>
+        <v>342000</v>
       </c>
       <c r="V198" t="n">
         <v>386500</v>
       </c>
       <c r="W198" t="n">
-        <v>-12.3</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="199">
@@ -14442,13 +14442,13 @@
         <v>0</v>
       </c>
       <c r="U199" t="n">
-        <v>49450</v>
+        <v>48800</v>
       </c>
       <c r="V199" t="n">
         <v>48300</v>
       </c>
       <c r="W199" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -14514,13 +14514,13 @@
         <v>0</v>
       </c>
       <c r="U200" t="n">
-        <v>89600</v>
+        <v>90000</v>
       </c>
       <c r="V200" t="n">
         <v>101200</v>
       </c>
       <c r="W200" t="n">
-        <v>-11.5</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="201">
@@ -14586,13 +14586,13 @@
         <v>-1.3</v>
       </c>
       <c r="U201" t="n">
-        <v>61400</v>
+        <v>61600</v>
       </c>
       <c r="V201" t="n">
         <v>62800</v>
       </c>
       <c r="W201" t="n">
-        <v>-2.2</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="202">
@@ -14730,13 +14730,13 @@
         <v>0</v>
       </c>
       <c r="U203" t="n">
-        <v>112600</v>
+        <v>110300</v>
       </c>
       <c r="V203" t="n">
         <v>106000</v>
       </c>
       <c r="W203" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="204">
@@ -14802,13 +14802,13 @@
         <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>34950</v>
+        <v>35200</v>
       </c>
       <c r="V204" t="n">
         <v>36300</v>
       </c>
       <c r="W204" t="n">
-        <v>-3.7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="205">
@@ -14874,13 +14874,13 @@
         <v>0</v>
       </c>
       <c r="U205" t="n">
-        <v>53600</v>
+        <v>52800</v>
       </c>
       <c r="V205" t="n">
         <v>55300</v>
       </c>
       <c r="W205" t="n">
-        <v>-3.1</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="206">
@@ -14946,13 +14946,13 @@
         <v>0</v>
       </c>
       <c r="U206" t="n">
-        <v>21400</v>
+        <v>21450</v>
       </c>
       <c r="V206" t="n">
         <v>21650</v>
       </c>
       <c r="W206" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="207">
@@ -15018,13 +15018,13 @@
         <v>-0.5</v>
       </c>
       <c r="U207" t="n">
-        <v>209500</v>
+        <v>212500</v>
       </c>
       <c r="V207" t="n">
         <v>216500</v>
       </c>
       <c r="W207" t="n">
-        <v>-3.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="208">
@@ -15090,13 +15090,13 @@
         <v>0</v>
       </c>
       <c r="U208" t="n">
-        <v>254000</v>
+        <v>247500</v>
       </c>
       <c r="V208" t="n">
         <v>240500</v>
       </c>
       <c r="W208" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="209">
@@ -15162,13 +15162,13 @@
         <v>-0</v>
       </c>
       <c r="U209" t="n">
-        <v>740000</v>
+        <v>747000</v>
       </c>
       <c r="V209" t="n">
         <v>714000</v>
       </c>
       <c r="W209" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="210">
@@ -15234,13 +15234,13 @@
         <v>0.3</v>
       </c>
       <c r="U210" t="n">
-        <v>141600</v>
+        <v>142500</v>
       </c>
       <c r="V210" t="n">
         <v>140000</v>
       </c>
       <c r="W210" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="211">
@@ -15306,13 +15306,13 @@
         <v>0</v>
       </c>
       <c r="U211" t="n">
-        <v>118800</v>
+        <v>119300</v>
       </c>
       <c r="V211" t="n">
         <v>126300</v>
       </c>
       <c r="W211" t="n">
-        <v>-5.9</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="212">
@@ -15378,13 +15378,13 @@
         <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>71800</v>
+        <v>70900</v>
       </c>
       <c r="V212" t="n">
         <v>68800</v>
       </c>
       <c r="W212" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="213">
@@ -15450,13 +15450,13 @@
         <v>0</v>
       </c>
       <c r="U213" t="n">
-        <v>5990</v>
+        <v>5930</v>
       </c>
       <c r="V213" t="n">
         <v>6140</v>
       </c>
       <c r="W213" t="n">
-        <v>-2.4</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="214">
@@ -15585,13 +15585,13 @@
         <v>0.1</v>
       </c>
       <c r="U215" t="n">
-        <v>365000</v>
+        <v>372000</v>
       </c>
       <c r="V215" t="n">
         <v>394000</v>
       </c>
       <c r="W215" t="n">
-        <v>-7.4</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="216">
@@ -15657,13 +15657,13 @@
         <v>0</v>
       </c>
       <c r="U216" t="n">
-        <v>145700</v>
+        <v>142900</v>
       </c>
       <c r="V216" t="n">
         <v>145500</v>
       </c>
       <c r="W216" t="n">
-        <v>0.1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="217">
@@ -15729,13 +15729,13 @@
         <v>0</v>
       </c>
       <c r="U217" t="n">
-        <v>143800</v>
+        <v>145000</v>
       </c>
       <c r="V217" t="n">
         <v>147600</v>
       </c>
       <c r="W217" t="n">
-        <v>-2.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="218">
@@ -15801,13 +15801,13 @@
         <v>0</v>
       </c>
       <c r="U218" t="n">
-        <v>53700</v>
+        <v>54100</v>
       </c>
       <c r="V218" t="n">
         <v>55200</v>
       </c>
       <c r="W218" t="n">
-        <v>-2.7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="219">
@@ -15873,13 +15873,13 @@
         <v>0</v>
       </c>
       <c r="U219" t="n">
-        <v>24750</v>
+        <v>24850</v>
       </c>
       <c r="V219" t="n">
         <v>23300</v>
       </c>
       <c r="W219" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="220">
@@ -15945,13 +15945,13 @@
         <v>0</v>
       </c>
       <c r="U220" t="n">
-        <v>337000</v>
+        <v>341000</v>
       </c>
       <c r="V220" t="n">
         <v>347000</v>
       </c>
       <c r="W220" t="n">
-        <v>-2.9</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="221">
@@ -16017,13 +16017,13 @@
         <v>0.9</v>
       </c>
       <c r="U221" t="n">
-        <v>2809000</v>
+        <v>2854000</v>
       </c>
       <c r="V221" t="n">
         <v>2732000</v>
       </c>
       <c r="W221" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="222">
@@ -16089,13 +16089,13 @@
         <v>0</v>
       </c>
       <c r="U222" t="n">
-        <v>171200</v>
+        <v>172100</v>
       </c>
       <c r="V222" t="n">
         <v>172800</v>
       </c>
       <c r="W222" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="223">
@@ -16161,13 +16161,13 @@
         <v>0.9</v>
       </c>
       <c r="U223" t="n">
-        <v>16660</v>
+        <v>16600</v>
       </c>
       <c r="V223" t="n">
         <v>16670</v>
       </c>
       <c r="W223" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="224">
@@ -16224,13 +16224,13 @@
         <v>0</v>
       </c>
       <c r="U224" t="n">
-        <v>37500</v>
+        <v>37250</v>
       </c>
       <c r="V224" t="n">
         <v>37900</v>
       </c>
       <c r="W224" t="n">
-        <v>-1.1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="225">
@@ -16296,13 +16296,13 @@
         <v>0</v>
       </c>
       <c r="U225" t="n">
-        <v>150200</v>
+        <v>150600</v>
       </c>
       <c r="V225" t="n">
         <v>144700</v>
       </c>
       <c r="W225" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="226">
@@ -16368,13 +16368,13 @@
         <v>-1.5</v>
       </c>
       <c r="U226" t="n">
-        <v>388500</v>
+        <v>390000</v>
       </c>
       <c r="V226" t="n">
         <v>395000</v>
       </c>
       <c r="W226" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="227">
@@ -16440,13 +16440,13 @@
         <v>0</v>
       </c>
       <c r="U227" t="n">
-        <v>34950</v>
+        <v>35100</v>
       </c>
       <c r="V227" t="n">
         <v>33200</v>
       </c>
       <c r="W227" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="228">
@@ -16512,13 +16512,13 @@
         <v>0</v>
       </c>
       <c r="U228" t="n">
-        <v>10750</v>
+        <v>11330</v>
       </c>
       <c r="V228" t="n">
         <v>11230</v>
       </c>
       <c r="W228" t="n">
-        <v>-4.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="229">
@@ -16584,13 +16584,13 @@
         <v>0</v>
       </c>
       <c r="U229" t="n">
-        <v>21450</v>
+        <v>21350</v>
       </c>
       <c r="V229" t="n">
         <v>21950</v>
       </c>
       <c r="W229" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="230">
@@ -16656,13 +16656,13 @@
         <v>0</v>
       </c>
       <c r="U230" t="n">
-        <v>78600</v>
+        <v>79400</v>
       </c>
       <c r="V230" t="n">
         <v>86600</v>
       </c>
       <c r="W230" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="231">
@@ -16728,13 +16728,13 @@
         <v>-0</v>
       </c>
       <c r="U231" t="n">
-        <v>479500</v>
+        <v>479000</v>
       </c>
       <c r="V231" t="n">
         <v>436500</v>
       </c>
       <c r="W231" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="232">
@@ -16800,7 +16800,7 @@
         <v>-0.7</v>
       </c>
       <c r="U232" t="n">
-        <v>172900</v>
+        <v>173000</v>
       </c>
       <c r="V232" t="n">
         <v>178500</v>
@@ -16872,13 +16872,13 @@
         <v>0</v>
       </c>
       <c r="U233" t="n">
-        <v>99000</v>
+        <v>100000</v>
       </c>
       <c r="V233" t="n">
         <v>99500</v>
       </c>
       <c r="W233" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="234">
@@ -16944,13 +16944,13 @@
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>16620</v>
+        <v>16690</v>
       </c>
       <c r="V234" t="n">
         <v>16280</v>
       </c>
       <c r="W234" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="235">
@@ -17016,13 +17016,13 @@
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>355500</v>
+        <v>360000</v>
       </c>
       <c r="V235" t="n">
         <v>358500</v>
       </c>
       <c r="W235" t="n">
-        <v>-0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="236">
@@ -17088,13 +17088,13 @@
         <v>0</v>
       </c>
       <c r="U236" t="n">
-        <v>86100</v>
+        <v>85800</v>
       </c>
       <c r="V236" t="n">
         <v>73400</v>
       </c>
       <c r="W236" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="237">
@@ -17160,13 +17160,13 @@
         <v>-0.3</v>
       </c>
       <c r="U237" t="n">
-        <v>17940</v>
+        <v>17850</v>
       </c>
       <c r="V237" t="n">
         <v>18060</v>
       </c>
       <c r="W237" t="n">
-        <v>-0.7</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="238">
@@ -17232,13 +17232,13 @@
         <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>46300</v>
+        <v>46250</v>
       </c>
       <c r="V238" t="n">
         <v>47300</v>
       </c>
       <c r="W238" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="239">
@@ -17304,13 +17304,13 @@
         <v>0</v>
       </c>
       <c r="U239" t="n">
-        <v>64700</v>
+        <v>64800</v>
       </c>
       <c r="V239" t="n">
         <v>66900</v>
       </c>
       <c r="W239" t="n">
-        <v>-3.3</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="240">
@@ -17349,13 +17349,13 @@
         <v>0</v>
       </c>
       <c r="U240" t="n">
-        <v>40750</v>
+        <v>40350</v>
       </c>
       <c r="V240" t="n">
         <v>37750</v>
       </c>
       <c r="W240" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="241">
@@ -17394,13 +17394,13 @@
         <v>0</v>
       </c>
       <c r="U241" t="n">
-        <v>28750</v>
+        <v>29500</v>
       </c>
       <c r="V241" t="n">
         <v>31050</v>
       </c>
       <c r="W241" t="n">
-        <v>-7.4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="242">
@@ -17466,13 +17466,13 @@
         <v>0</v>
       </c>
       <c r="U242" t="n">
-        <v>1074000</v>
+        <v>1089000</v>
       </c>
       <c r="V242" t="n">
         <v>1041000</v>
       </c>
       <c r="W242" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="243">
@@ -17538,13 +17538,13 @@
         <v>0</v>
       </c>
       <c r="U243" t="n">
-        <v>92700</v>
+        <v>93800</v>
       </c>
       <c r="V243" t="n">
         <v>101200</v>
       </c>
       <c r="W243" t="n">
-        <v>-8.4</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="244">
@@ -17610,13 +17610,13 @@
         <v>0</v>
       </c>
       <c r="U244" t="n">
-        <v>47950</v>
+        <v>47300</v>
       </c>
       <c r="V244" t="n">
         <v>46950</v>
       </c>
       <c r="W244" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="245">
@@ -17682,13 +17682,13 @@
         <v>-2</v>
       </c>
       <c r="U245" t="n">
-        <v>248000</v>
+        <v>247000</v>
       </c>
       <c r="V245" t="n">
         <v>210500</v>
       </c>
       <c r="W245" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="246">
@@ -17754,13 +17754,13 @@
         <v>0</v>
       </c>
       <c r="U246" t="n">
-        <v>79000</v>
+        <v>80200</v>
       </c>
       <c r="V246" t="n">
         <v>79300</v>
       </c>
       <c r="W246" t="n">
-        <v>-0.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="247">
@@ -17826,13 +17826,13 @@
         <v>0</v>
       </c>
       <c r="U247" t="n">
-        <v>10400</v>
+        <v>10320</v>
       </c>
       <c r="V247" t="n">
         <v>10510</v>
       </c>
       <c r="W247" t="n">
-        <v>-1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="248">
@@ -17898,13 +17898,13 @@
         <v>0.2</v>
       </c>
       <c r="U248" t="n">
-        <v>31700</v>
+        <v>31400</v>
       </c>
       <c r="V248" t="n">
         <v>31850</v>
       </c>
       <c r="W248" t="n">
-        <v>-0.5</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="249">
@@ -17970,13 +17970,13 @@
         <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>167100</v>
+        <v>167600</v>
       </c>
       <c r="V249" t="n">
         <v>190600</v>
       </c>
       <c r="W249" t="n">
-        <v>-12.3</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="250">
@@ -18042,13 +18042,13 @@
         <v>0</v>
       </c>
       <c r="U250" t="n">
-        <v>18360</v>
+        <v>17930</v>
       </c>
       <c r="V250" t="n">
         <v>16560</v>
       </c>
       <c r="W250" t="n">
-        <v>10.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="251">
@@ -18114,13 +18114,13 @@
         <v>0</v>
       </c>
       <c r="U251" t="n">
-        <v>47150</v>
+        <v>47200</v>
       </c>
       <c r="V251" t="n">
         <v>49400</v>
       </c>
       <c r="W251" t="n">
-        <v>-4.6</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="252">
@@ -18159,13 +18159,13 @@
         <v>0</v>
       </c>
       <c r="U252" t="n">
-        <v>32450</v>
+        <v>32550</v>
       </c>
       <c r="V252" t="n">
         <v>34500</v>
       </c>
       <c r="W252" t="n">
-        <v>-5.9</v>
+        <v>-5.7</v>
       </c>
     </row>
   </sheetData>

--- a/telegram_research_dashboard/static/consensus_full.xlsx
+++ b/telegram_research_dashboard/static/consensus_full.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-11 · 전주 2026-09-05</t>
+          <t>영업이익 컨센(KOSPI200·KOSDAQ50·커버리지) · 기준일 2026-09-12 · 전주 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -1326,40 +1326,40 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7942</v>
+        <v>8076</v>
       </c>
       <c r="G13" t="n">
         <v>7942</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L13" t="n">
-        <v>31986.2</v>
+        <v>32316.9</v>
       </c>
       <c r="M13" t="n">
         <v>31986.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>37928.1</v>
+        <v>38353.5</v>
       </c>
       <c r="P13" t="n">
         <v>37928.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="R13" t="n">
-        <v>36586.3</v>
+        <v>37044</v>
       </c>
       <c r="S13" t="n">
         <v>36586.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U13" t="n">
         <v>686000</v>
@@ -1758,31 +1758,31 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>13301.4</v>
+        <v>13355.3</v>
       </c>
       <c r="M19" t="n">
         <v>13301.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>14411.4</v>
+        <v>14475.3</v>
       </c>
       <c r="P19" t="n">
         <v>14411.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R19" t="n">
-        <v>15783.6</v>
+        <v>15992.7</v>
       </c>
       <c r="S19" t="n">
         <v>15783.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U19" t="n">
         <v>51300</v>
@@ -2811,16 +2811,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="G34" t="n">
         <v>1817</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="L34" t="n">
-        <v>7910.7</v>
+        <v>7906</v>
       </c>
       <c r="M34" t="n">
         <v>7892.4</v>
@@ -2829,7 +2829,7 @@
         <v>0.2</v>
       </c>
       <c r="O34" t="n">
-        <v>8704.299999999999</v>
+        <v>8700.200000000001</v>
       </c>
       <c r="P34" t="n">
         <v>8712.799999999999</v>
@@ -2838,13 +2838,13 @@
         <v>-0.1</v>
       </c>
       <c r="R34" t="n">
-        <v>9361.200000000001</v>
+        <v>9352.4</v>
       </c>
       <c r="S34" t="n">
         <v>9323.9</v>
       </c>
       <c r="T34" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="U34" t="n">
         <v>381000</v>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>23716.6</v>
+        <v>23970.6</v>
       </c>
       <c r="M40" t="n">
         <v>23716.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O40" t="n">
-        <v>23553.1</v>
+        <v>24081.6</v>
       </c>
       <c r="P40" t="n">
         <v>23553.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R40" t="n">
-        <v>24819.6</v>
+        <v>25469.6</v>
       </c>
       <c r="S40" t="n">
         <v>24819.6</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U40" t="n">
         <v>191700</v>
@@ -3630,40 +3630,40 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4936</v>
+        <v>4900</v>
       </c>
       <c r="G46" t="n">
         <v>4936</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="L46" t="n">
-        <v>19998.9</v>
+        <v>19996.3</v>
       </c>
       <c r="M46" t="n">
         <v>19998.9</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O46" t="n">
-        <v>22439.8</v>
+        <v>22339.8</v>
       </c>
       <c r="P46" t="n">
         <v>22439.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="R46" t="n">
-        <v>25550.7</v>
+        <v>25700.6</v>
       </c>
       <c r="S46" t="n">
         <v>25550.7</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U46" t="n">
         <v>319500</v>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3373</v>
+        <v>3300</v>
       </c>
       <c r="L51" t="n">
-        <v>47821.3</v>
+        <v>47817.2</v>
       </c>
       <c r="M51" t="n">
         <v>47797.9</v>
@@ -4002,22 +4002,22 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>26286.9</v>
+        <v>26232.4</v>
       </c>
       <c r="P51" t="n">
         <v>26153.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="R51" t="n">
-        <v>27528.3</v>
+        <v>27610.4</v>
       </c>
       <c r="S51" t="n">
         <v>27203.7</v>
       </c>
       <c r="T51" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="U51" t="n">
         <v>33450</v>
@@ -4632,40 +4632,40 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2085</v>
+        <v>2092</v>
       </c>
       <c r="G60" t="n">
         <v>2085</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L60" t="n">
-        <v>8727.4</v>
+        <v>8899.700000000001</v>
       </c>
       <c r="M60" t="n">
         <v>8727.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>12809.5</v>
+        <v>12961.1</v>
       </c>
       <c r="P60" t="n">
         <v>12809.5</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R60" t="n">
-        <v>14612.6</v>
+        <v>14572.8</v>
       </c>
       <c r="S60" t="n">
         <v>14612.6</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="U60" t="n">
         <v>29800</v>
@@ -6135,34 +6135,34 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>5558</v>
+        <v>5563</v>
       </c>
       <c r="L81" t="n">
-        <v>23139.6</v>
+        <v>23117.3</v>
       </c>
       <c r="M81" t="n">
         <v>23242.3</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="O81" t="n">
-        <v>20886.3</v>
+        <v>21025.9</v>
       </c>
       <c r="P81" t="n">
         <v>20844.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="R81" t="n">
-        <v>21226.2</v>
+        <v>21395.8</v>
       </c>
       <c r="S81" t="n">
         <v>21165.2</v>
       </c>
       <c r="T81" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="U81" t="n">
         <v>87400</v>
@@ -6777,40 +6777,40 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1832</v>
+        <v>1823</v>
       </c>
       <c r="G90" t="n">
         <v>1830</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L90" t="n">
-        <v>7995.5</v>
+        <v>7987.8</v>
       </c>
       <c r="M90" t="n">
         <v>8000.9</v>
       </c>
       <c r="N90" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="O90" t="n">
-        <v>8680.799999999999</v>
+        <v>8679.299999999999</v>
       </c>
       <c r="P90" t="n">
         <v>8680</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R90" t="n">
-        <v>9374.700000000001</v>
+        <v>9373.200000000001</v>
       </c>
       <c r="S90" t="n">
         <v>9341.299999999999</v>
       </c>
       <c r="T90" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="U90" t="n">
         <v>112000</v>
@@ -8688,34 +8688,34 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5293</v>
+        <v>5229</v>
       </c>
       <c r="L117" t="n">
-        <v>22944.8</v>
+        <v>22916.7</v>
       </c>
       <c r="M117" t="n">
         <v>22983.8</v>
       </c>
       <c r="N117" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="O117" t="n">
-        <v>19125.1</v>
+        <v>19010.9</v>
       </c>
       <c r="P117" t="n">
         <v>19067.2</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="R117" t="n">
-        <v>19634.6</v>
+        <v>19670.8</v>
       </c>
       <c r="S117" t="n">
         <v>19518.9</v>
       </c>
       <c r="T117" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="U117" t="n">
         <v>278000</v>
@@ -9051,7 +9051,7 @@
         <v>-1.9</v>
       </c>
       <c r="L122" t="n">
-        <v>8268.799999999999</v>
+        <v>8269.299999999999</v>
       </c>
       <c r="M122" t="n">
         <v>8310</v>
@@ -9060,22 +9060,22 @@
         <v>-0.5</v>
       </c>
       <c r="O122" t="n">
-        <v>8090.3</v>
+        <v>8120.3</v>
       </c>
       <c r="P122" t="n">
         <v>8159.2</v>
       </c>
       <c r="Q122" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="R122" t="n">
-        <v>9053.799999999999</v>
+        <v>9066.200000000001</v>
       </c>
       <c r="S122" t="n">
         <v>9186.4</v>
       </c>
       <c r="T122" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="U122" t="n">
         <v>19890</v>
@@ -9114,40 +9114,40 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3776</v>
+        <v>3754</v>
       </c>
       <c r="G123" t="n">
         <v>3776</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L123" t="n">
-        <v>14688.2</v>
+        <v>14652.1</v>
       </c>
       <c r="M123" t="n">
         <v>14688.2</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O123" t="n">
-        <v>15554.8</v>
+        <v>15480.2</v>
       </c>
       <c r="P123" t="n">
         <v>15554.8</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R123" t="n">
-        <v>16386.5</v>
+        <v>16311.2</v>
       </c>
       <c r="S123" t="n">
         <v>16386.5</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="U123" t="n">
         <v>57700</v>
@@ -9258,40 +9258,40 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G125" t="n">
         <v>342</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="L125" t="n">
-        <v>1019.8</v>
+        <v>1006.1</v>
       </c>
       <c r="M125" t="n">
         <v>1019.8</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="O125" t="n">
-        <v>1160</v>
+        <v>1145.7</v>
       </c>
       <c r="P125" t="n">
         <v>1160</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="R125" t="n">
-        <v>1255.7</v>
+        <v>1244.2</v>
       </c>
       <c r="S125" t="n">
         <v>1290.5</v>
       </c>
       <c r="T125" t="n">
-        <v>-2.7</v>
+        <v>-3.6</v>
       </c>
       <c r="U125" t="n">
         <v>22850</v>
@@ -10617,40 +10617,40 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>8771</v>
+        <v>8784</v>
       </c>
       <c r="G144" t="n">
         <v>9012</v>
       </c>
       <c r="H144" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="L144" t="n">
-        <v>40568.7</v>
+        <v>40613.8</v>
       </c>
       <c r="M144" t="n">
         <v>40740.8</v>
       </c>
       <c r="N144" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="O144" t="n">
-        <v>32676.4</v>
+        <v>32549.8</v>
       </c>
       <c r="P144" t="n">
         <v>32826.1</v>
       </c>
       <c r="Q144" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="R144" t="n">
-        <v>33367.7</v>
+        <v>33383.2</v>
       </c>
       <c r="S144" t="n">
         <v>33520.6</v>
       </c>
       <c r="T144" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="U144" t="n">
         <v>193600</v>
@@ -12309,40 +12309,40 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="G169" t="n">
         <v>1083</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.6</v>
+        <v>0.3</v>
       </c>
       <c r="L169" t="n">
-        <v>4242.3</v>
+        <v>4253.7</v>
       </c>
       <c r="M169" t="n">
         <v>4266.3</v>
       </c>
       <c r="N169" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="O169" t="n">
-        <v>3878</v>
+        <v>3853.9</v>
       </c>
       <c r="P169" t="n">
         <v>3867.1</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="R169" t="n">
-        <v>4169</v>
+        <v>4142.7</v>
       </c>
       <c r="S169" t="n">
         <v>4143.9</v>
       </c>
       <c r="T169" t="n">
-        <v>0.6</v>
+        <v>-0</v>
       </c>
       <c r="U169" t="n">
         <v>77500</v>
@@ -14046,40 +14046,40 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G194" t="n">
         <v>314</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="L194" t="n">
-        <v>1304.1</v>
+        <v>1307.2</v>
       </c>
       <c r="M194" t="n">
         <v>1304.1</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O194" t="n">
-        <v>1479.1</v>
+        <v>1480.5</v>
       </c>
       <c r="P194" t="n">
         <v>1479.1</v>
       </c>
       <c r="Q194" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R194" t="n">
-        <v>1684.3</v>
+        <v>1688.6</v>
       </c>
       <c r="S194" t="n">
         <v>1684.3</v>
       </c>
       <c r="T194" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="U194" t="n">
         <v>40700</v>
@@ -15342,13 +15342,13 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="G212" t="n">
         <v>588</v>
       </c>
       <c r="H212" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L212" t="n">
         <v>2485.5</v>
@@ -16692,40 +16692,40 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>10073</v>
+        <v>10106</v>
       </c>
       <c r="G231" t="n">
         <v>10073</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L231" t="n">
-        <v>40520</v>
+        <v>40491.8</v>
       </c>
       <c r="M231" t="n">
         <v>40521.2</v>
       </c>
       <c r="N231" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="O231" t="n">
-        <v>47401.8</v>
+        <v>47253.1</v>
       </c>
       <c r="P231" t="n">
         <v>47403.9</v>
       </c>
       <c r="Q231" t="n">
-        <v>-0</v>
+        <v>-0.3</v>
       </c>
       <c r="R231" t="n">
-        <v>54806.5</v>
+        <v>55163</v>
       </c>
       <c r="S231" t="n">
         <v>54808.5</v>
       </c>
       <c r="T231" t="n">
-        <v>-0</v>
+        <v>0.6</v>
       </c>
       <c r="U231" t="n">
         <v>479000</v>
@@ -17655,7 +17655,7 @@
         <v>-1.5</v>
       </c>
       <c r="L245" t="n">
-        <v>4148.6</v>
+        <v>4149</v>
       </c>
       <c r="M245" t="n">
         <v>4184.6</v>
@@ -17664,22 +17664,22 @@
         <v>-0.9</v>
       </c>
       <c r="O245" t="n">
-        <v>5280.9</v>
+        <v>5281.3</v>
       </c>
       <c r="P245" t="n">
         <v>5358.9</v>
       </c>
       <c r="Q245" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="R245" t="n">
-        <v>6579.7</v>
+        <v>6584.7</v>
       </c>
       <c r="S245" t="n">
         <v>6713.7</v>
       </c>
       <c r="T245" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="U245" t="n">
         <v>247000</v>
